--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -593,7 +593,7 @@
         <v>36.03138885531489</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1293773523170486</v>
+        <v>0.1293773523170485</v>
       </c>
       <c r="S2" t="n">
         <v>-0.7375148762927999</v>
@@ -812,13 +812,13 @@
         <v>1.911472491838996</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3048585867839391</v>
+        <v>0.3048585867839389</v>
       </c>
       <c r="S5" t="n">
         <v>-0.1982415669926141</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2802746963633374</v>
+        <v>0.2802746963633371</v>
       </c>
       <c r="U5" t="n">
         <v>6.7925</v>
@@ -885,13 +885,13 @@
         <v>1.494575642227743</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5089368211856863</v>
+        <v>0.5089368211856861</v>
       </c>
       <c r="S6" t="n">
         <v>0.07464598933846722</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5050749116393327</v>
+        <v>0.5050749116393324</v>
       </c>
       <c r="U6" t="n">
         <v>6.109972296151311</v>
@@ -958,13 +958,13 @@
         <v>1.822552420274826</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8095836655428075</v>
+        <v>0.8095836655428076</v>
       </c>
       <c r="S7" t="n">
         <v>0.6303570018110684</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7999405823947843</v>
+        <v>0.7999405823947844</v>
       </c>
       <c r="U7" t="n">
         <v>5.981758060466298</v>
@@ -1031,13 +1031,13 @@
         <v>1.920219108146032</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7617101500500636</v>
+        <v>0.761710150050064</v>
       </c>
       <c r="S8" t="n">
         <v>0.5361813343167756</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7596994888028805</v>
+        <v>0.759699488802881</v>
       </c>
       <c r="U8" t="n">
         <v>6.53</v>
@@ -1104,13 +1104,13 @@
         <v>2.697554223649582</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3563464980514018</v>
+        <v>0.3563464980514016</v>
       </c>
       <c r="S9" t="n">
         <v>-0.1199845211161212</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3354417007720807</v>
+        <v>0.3354417007720805</v>
       </c>
       <c r="U9" t="n">
         <v>10.1014171617984</v>
@@ -1250,13 +1250,13 @@
         <v>1.199886337673197</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8289306355739895</v>
+        <v>0.8289306355739893</v>
       </c>
       <c r="S11" t="n">
         <v>0.6527307562356639</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8272897533000165</v>
+        <v>0.8272897533000163</v>
       </c>
       <c r="U11" t="n">
         <v>5.281336733095788</v>
@@ -1323,13 +1323,13 @@
         <v>2.15549715055829</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8231978258912493</v>
+        <v>0.8231978258912499</v>
       </c>
       <c r="S12" t="n">
         <v>0.6484391411092192</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8114941091534823</v>
+        <v>0.8114941091534829</v>
       </c>
       <c r="U12" t="n">
         <v>7.867834263294696</v>
@@ -1396,13 +1396,13 @@
         <v>2.285705332728494</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7807763859794405</v>
+        <v>0.7807763859794399</v>
       </c>
       <c r="S13" t="n">
         <v>0.5650135915856762</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7804109910934738</v>
+        <v>0.7804109910934731</v>
       </c>
       <c r="U13" t="n">
         <v>6.401922929815592</v>
@@ -1469,13 +1469,13 @@
         <v>2.700889385683155</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7944316950721653</v>
+        <v>0.7944316950721657</v>
       </c>
       <c r="S14" t="n">
         <v>0.6086556188833412</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7858592938199808</v>
+        <v>0.7858592938199812</v>
       </c>
       <c r="U14" t="n">
         <v>8.388284851374982</v>
@@ -1615,13 +1615,13 @@
         <v>2.579583230291027</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5181653642573085</v>
+        <v>0.5181653642573086</v>
       </c>
       <c r="S16" t="n">
         <v>0.01527028269559583</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5148572754275724</v>
+        <v>0.5148572754275725</v>
       </c>
       <c r="U16" t="n">
         <v>3.950317923339689</v>
@@ -1688,13 +1688,13 @@
         <v>1.488644272773963</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5997299970012603</v>
+        <v>0.5997299970012602</v>
       </c>
       <c r="S17" t="n">
         <v>0.2151241668148857</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5967713101904909</v>
+        <v>0.5967713101904908</v>
       </c>
       <c r="U17" t="n">
         <v>4.866268240618501</v>
@@ -1761,13 +1761,13 @@
         <v>2.750576503734912</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7262145542217276</v>
+        <v>0.7262145542217279</v>
       </c>
       <c r="S18" t="n">
         <v>0.4688815464657763</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6791774910414113</v>
+        <v>0.6791774910414116</v>
       </c>
       <c r="U18" t="n">
         <v>7.962271702191409</v>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -548,28 +548,28 @@
         <v>9038134</v>
       </c>
       <c r="C2" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D2" t="n">
+        <v>9956</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
         <v>9955</v>
-      </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9954</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>36161</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I2" t="n">
         <v>1.78</v>
       </c>
       <c r="J2" t="n">
-        <v>102.9386727278816</v>
+        <v>102.9289963167587</v>
       </c>
       <c r="K2" t="n">
         <v>118.97</v>
@@ -578,37 +578,37 @@
         <v>1.846246418338109</v>
       </c>
       <c r="M2" t="n">
-        <v>102.9238545827922</v>
+        <v>102.9170511931064</v>
       </c>
       <c r="N2" t="n">
         <v>118.8938450398262</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01481814508937319</v>
+        <v>-0.01194512365233252</v>
       </c>
       <c r="P2" t="n">
-        <v>17.69130143854802</v>
+        <v>17.70716511535175</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.03138885531489</v>
+        <v>36.05387757898497</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1293773523170485</v>
+        <v>0.1290752763692524</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7375148762927999</v>
+        <v>-0.7376914900802976</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1293746975580475</v>
+        <v>0.1290719879859945</v>
       </c>
       <c r="U2" t="n">
-        <v>110.4</v>
+        <v>108.92</v>
       </c>
       <c r="V2" t="n">
-        <v>111.5269391266153</v>
+        <v>111.0004576696035</v>
       </c>
       <c r="W2" t="n">
-        <v>112.1735135554431</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="3">
@@ -621,28 +621,28 @@
         <v>9038269</v>
       </c>
       <c r="C3" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D3" t="n">
+        <v>14534</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
         <v>14533</v>
-      </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14532</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>30317</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I3" t="n">
         <v>0.01</v>
       </c>
       <c r="J3" t="n">
-        <v>4.907141308835673</v>
+        <v>4.90708645840501</v>
       </c>
       <c r="K3" t="n">
         <v>11.07</v>
@@ -651,37 +651,37 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>4.962824520547223</v>
+        <v>4.962793072120321</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05568321171154988</v>
+        <v>0.05570661371531164</v>
       </c>
       <c r="P3" t="n">
-        <v>1.351081012808745</v>
+        <v>1.351051258592869</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.725750306030747</v>
+        <v>1.725722029455693</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7795402860026719</v>
+        <v>0.7795317466831925</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5665089881318111</v>
+        <v>0.5664961233501915</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7784611145815252</v>
+        <v>0.7784514678238366</v>
       </c>
       <c r="U3" t="n">
-        <v>3.294996605386324</v>
+        <v>3.22</v>
       </c>
       <c r="V3" t="n">
-        <v>3.578404500385561</v>
+        <v>3.577055019346781</v>
       </c>
       <c r="W3" t="n">
-        <v>3.760762815054337</v>
+        <v>3.763740493038803</v>
       </c>
     </row>
     <row r="4">
@@ -694,28 +694,28 @@
         <v>9039635</v>
       </c>
       <c r="C4" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D4" t="n">
+        <v>10216</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
         <v>10215</v>
-      </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10214</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>35065</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="J4" t="n">
-        <v>6.919873213236733</v>
+        <v>6.919808614782183</v>
       </c>
       <c r="K4" t="n">
         <v>12.93</v>
@@ -724,37 +724,37 @@
         <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>7.250320580868626</v>
+        <v>7.250324656947725</v>
       </c>
       <c r="N4" t="n">
         <v>12.73</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3304473676318928</v>
+        <v>0.3305160421655411</v>
       </c>
       <c r="P4" t="n">
-        <v>1.294971634922388</v>
+        <v>1.294985088704803</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.684863320901164</v>
+        <v>1.684893275203564</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8674657929444423</v>
+        <v>0.8674480989548822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7370155707958398</v>
+        <v>0.736981510075724</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8471587770042971</v>
+        <v>0.8471285821647787</v>
       </c>
       <c r="U4" t="n">
-        <v>4.591856200822604</v>
+        <v>4.578499577620378</v>
       </c>
       <c r="V4" t="n">
-        <v>5.024862499234708</v>
+        <v>4.925266228568185</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4833324385695</v>
+        <v>5.451759562285003</v>
       </c>
     </row>
     <row r="5">
@@ -767,7 +767,7 @@
         <v>9032282</v>
       </c>
       <c r="C5" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D5" t="n">
         <v>8826</v>
@@ -776,19 +776,19 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>8825</v>
+        <v>8826</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>36892</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I5" t="n">
         <v>1.52</v>
       </c>
       <c r="J5" t="n">
-        <v>6.729329178470254</v>
+        <v>6.729487876727848</v>
       </c>
       <c r="K5" t="n">
         <v>10.6125</v>
@@ -797,37 +797,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="M5" t="n">
-        <v>7.018114520583111</v>
+        <v>7.018097311255914</v>
       </c>
       <c r="N5" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2887853421128562</v>
+        <v>0.2886094345280652</v>
       </c>
       <c r="P5" t="n">
-        <v>1.482634948821431</v>
+        <v>1.482614743801566</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.911472491838996</v>
+        <v>1.911425821856646</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3048585867839389</v>
+        <v>0.3048444464891431</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1982415669926141</v>
+        <v>-0.1982314784303485</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2802746963633371</v>
+        <v>0.2802624044083285</v>
       </c>
       <c r="U5" t="n">
-        <v>6.7925</v>
+        <v>6.723965927316091</v>
       </c>
       <c r="V5" t="n">
-        <v>7.006594522804919</v>
+        <v>6.974847164306932</v>
       </c>
       <c r="W5" t="n">
-        <v>7.170251828872009</v>
+        <v>7.157154318487135</v>
       </c>
     </row>
     <row r="6">
@@ -840,28 +840,28 @@
         <v>9036028</v>
       </c>
       <c r="C6" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D6" t="n">
+        <v>14189</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
         <v>14188</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14187</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>31048</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I6" t="n">
         <v>1.025</v>
       </c>
       <c r="J6" t="n">
-        <v>5.58268890533587</v>
+        <v>5.582724661685933</v>
       </c>
       <c r="K6" t="n">
         <v>10.01</v>
@@ -870,34 +870,34 @@
         <v>1.345</v>
       </c>
       <c r="M6" t="n">
-        <v>5.588859410424097</v>
+        <v>5.588883574706596</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006170505088226082</v>
+        <v>0.006158913020665243</v>
       </c>
       <c r="P6" t="n">
-        <v>1.156318526835137</v>
+        <v>1.156236783577111</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.494575642227743</v>
+        <v>1.494513578755264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5089368211856861</v>
+        <v>0.5089447418462268</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07464598933846722</v>
+        <v>0.07466457325693443</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5050749116393324</v>
+        <v>0.5050822435353698</v>
       </c>
       <c r="U6" t="n">
-        <v>6.109972296151311</v>
+        <v>6.06</v>
       </c>
       <c r="V6" t="n">
-        <v>6.175436427332438</v>
+        <v>6.165309716055784</v>
       </c>
       <c r="W6" t="n">
         <v>6.22</v>
@@ -913,28 +913,28 @@
         <v>9040454</v>
       </c>
       <c r="C7" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D7" t="n">
+        <v>8987</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
         <v>8986</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8985</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>36161</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I7" t="n">
         <v>0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>7.880406789092933</v>
+        <v>7.880473514355664</v>
       </c>
       <c r="K7" t="n">
         <v>15.14</v>
@@ -943,37 +943,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="M7" t="n">
-        <v>8.118354108497044</v>
+        <v>8.118473609709923</v>
       </c>
       <c r="N7" t="n">
         <v>14.26345655220743</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2379473194041127</v>
+        <v>0.2380000953542593</v>
       </c>
       <c r="P7" t="n">
-        <v>1.443324006912627</v>
+        <v>1.443649252208346</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.822552420274826</v>
+        <v>1.823005908252468</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8095836655428076</v>
+        <v>0.809461294277773</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6303570018110684</v>
+        <v>0.6301335158010737</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7999405823947844</v>
+        <v>0.799811790557847</v>
       </c>
       <c r="U7" t="n">
-        <v>5.981758060466298</v>
+        <v>5.93</v>
       </c>
       <c r="V7" t="n">
-        <v>6.186911210785491</v>
+        <v>6.18629150856284</v>
       </c>
       <c r="W7" t="n">
-        <v>6.352571029113949</v>
+        <v>6.361594181372594</v>
       </c>
     </row>
     <row r="8">
@@ -986,28 +986,28 @@
         <v>9040439</v>
       </c>
       <c r="C8" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D8" t="n">
+        <v>13852</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
         <v>13851</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13850</v>
       </c>
       <c r="G8" s="1" t="n">
         <v>31778</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I8" t="n">
         <v>0.06</v>
       </c>
       <c r="J8" t="n">
-        <v>7.617061191335739</v>
+        <v>7.617002202007075</v>
       </c>
       <c r="K8" t="n">
         <v>14.03</v>
@@ -1016,37 +1016,37 @@
         <v>0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>7.683037078161146</v>
+        <v>7.682990004007297</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06597588682540657</v>
+        <v>0.06598780200022202</v>
       </c>
       <c r="P8" t="n">
-        <v>1.477757297390211</v>
+        <v>1.477659973322899</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.920219108146032</v>
+        <v>1.920151342390373</v>
       </c>
       <c r="R8" t="n">
-        <v>0.761710150050064</v>
+        <v>0.7617096190455039</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5361813343167756</v>
+        <v>0.536183396339482</v>
       </c>
       <c r="T8" t="n">
-        <v>0.759699488802881</v>
+        <v>0.7596979144976741</v>
       </c>
       <c r="U8" t="n">
-        <v>6.53</v>
+        <v>6.389071605361553</v>
       </c>
       <c r="V8" t="n">
-        <v>6.925364799728411</v>
+        <v>6.893267100462258</v>
       </c>
       <c r="W8" t="n">
-        <v>7.205357163325993</v>
+        <v>7.205198970971844</v>
       </c>
     </row>
     <row r="9">
@@ -1059,7 +1059,7 @@
         <v>9042153</v>
       </c>
       <c r="C9" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D9" t="n">
         <v>3737</v>
@@ -1089,37 +1089,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>10.62187323654579</v>
+        <v>10.62166578549552</v>
       </c>
       <c r="N9" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3168136968080291</v>
+        <v>0.3166062457577587</v>
       </c>
       <c r="P9" t="n">
-        <v>2.051612675066247</v>
+        <v>2.05156683843098</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.697554223649582</v>
+        <v>2.69749636657411</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3563464980514016</v>
+        <v>0.356385083965104</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1199845211161212</v>
+        <v>-0.1199364788313784</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3354417007720805</v>
+        <v>0.3354893575308939</v>
       </c>
       <c r="U9" t="n">
-        <v>10.1014171617984</v>
+        <v>10.08050066385531</v>
       </c>
       <c r="V9" t="n">
-        <v>10.74867082005867</v>
+        <v>10.59140060260334</v>
       </c>
       <c r="W9" t="n">
-        <v>11.50413608173295</v>
+        <v>11.36869558040371</v>
       </c>
     </row>
     <row r="10">
@@ -1132,28 +1132,28 @@
         <v>9040208</v>
       </c>
       <c r="C10" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D10" t="n">
+        <v>13793</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>13792</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13791</v>
       </c>
       <c r="G10" s="1" t="n">
         <v>31413</v>
       </c>
       <c r="H10" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I10" t="n">
         <v>0.4375</v>
       </c>
       <c r="J10" t="n">
-        <v>5.246338191574215</v>
+        <v>5.246294953596287</v>
       </c>
       <c r="K10" t="n">
         <v>10.15</v>
@@ -1162,37 +1162,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="M10" t="n">
-        <v>5.220975925670021</v>
+        <v>5.220953023477025</v>
       </c>
       <c r="N10" t="n">
         <v>9.94</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0253622659041944</v>
+        <v>-0.02534193011926178</v>
       </c>
       <c r="P10" t="n">
-        <v>1.158396947832663</v>
+        <v>1.158351208468454</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.477259301030481</v>
+        <v>1.477199336231334</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4293784450221183</v>
+        <v>0.4293858996067023</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.08239962516985089</v>
+        <v>-0.08237639078345116</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4267673046481669</v>
+        <v>0.4267739623486192</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="V10" t="n">
-        <v>4.884937707151636</v>
+        <v>4.788344398913265</v>
       </c>
       <c r="W10" t="n">
-        <v>5.41</v>
+        <v>5.147904245727468</v>
       </c>
     </row>
     <row r="11">
@@ -1205,28 +1205,28 @@
         <v>9043597</v>
       </c>
       <c r="C11" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D11" t="n">
+        <v>4111</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
         <v>4110</v>
-      </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4109</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>41640</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I11" t="n">
         <v>2.195</v>
       </c>
       <c r="J11" t="n">
-        <v>7.498993672426381</v>
+        <v>7.498414841849149</v>
       </c>
       <c r="K11" t="n">
         <v>19.1775</v>
@@ -1235,37 +1235,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="M11" t="n">
-        <v>7.671260773631204</v>
+        <v>7.670831780816735</v>
       </c>
       <c r="N11" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="O11" t="n">
-        <v>0.172267101204823</v>
+        <v>0.1724169389675873</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9167024717145627</v>
+        <v>0.9166204802271911</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.199886337673197</v>
+        <v>1.199735299509699</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8289306355739893</v>
+        <v>0.8289788017743478</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6527307562356639</v>
+        <v>0.6528489894799561</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8272897533000163</v>
+        <v>0.8273309016821457</v>
       </c>
       <c r="U11" t="n">
-        <v>5.281336733095788</v>
+        <v>5.234564177848553</v>
       </c>
       <c r="V11" t="n">
-        <v>5.500300815107519</v>
+        <v>5.425673149854016</v>
       </c>
       <c r="W11" t="n">
-        <v>5.803600994371898</v>
+        <v>5.800010996031258</v>
       </c>
     </row>
     <row r="12">
@@ -1278,67 +1278,67 @@
         <v>9042214</v>
       </c>
       <c r="C12" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
         <v>6445</v>
-      </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6444</v>
       </c>
       <c r="G12" s="1" t="n">
         <v>39083</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I12" t="n">
         <v>1.54</v>
       </c>
       <c r="J12" t="n">
-        <v>9.619932753983033</v>
+        <v>9.619745021980863</v>
       </c>
       <c r="K12" t="n">
         <v>16.215</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8575</v>
+        <v>2.858246962115797</v>
       </c>
       <c r="M12" t="n">
-        <v>10.03359886334009</v>
+        <v>10.03373186703846</v>
       </c>
       <c r="N12" t="n">
         <v>16.21</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4136661093570556</v>
+        <v>0.4139868450575971</v>
       </c>
       <c r="P12" t="n">
-        <v>1.69622508769057</v>
+        <v>1.696130515055037</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.15549715055829</v>
+        <v>2.155457248136254</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8231978258912499</v>
+        <v>0.8231773250069385</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6484391411092192</v>
+        <v>0.6484036457994256</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8114941091534829</v>
+        <v>0.8114410738343276</v>
       </c>
       <c r="U12" t="n">
-        <v>7.867834263294696</v>
+        <v>7.85190473353983</v>
       </c>
       <c r="V12" t="n">
-        <v>8.516559170734414</v>
+        <v>8.40249222980437</v>
       </c>
       <c r="W12" t="n">
-        <v>8.969020050728336</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="13">
@@ -1351,28 +1351,28 @@
         <v>9043425</v>
       </c>
       <c r="C13" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D13" t="n">
+        <v>14033</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
         <v>14032</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>14031</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>30682</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I13" t="n">
         <v>0.26</v>
       </c>
       <c r="J13" t="n">
-        <v>8.134668769154016</v>
+        <v>8.134642780786773</v>
       </c>
       <c r="K13" t="n">
         <v>34.0025</v>
@@ -1381,37 +1381,37 @@
         <v>0.91</v>
       </c>
       <c r="M13" t="n">
-        <v>8.206602479349204</v>
+        <v>8.206587957624482</v>
       </c>
       <c r="N13" t="n">
         <v>14.32</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07193371019518742</v>
+        <v>0.07194517683770971</v>
       </c>
       <c r="P13" t="n">
-        <v>1.760463127307876</v>
+        <v>1.7604718760402</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.285705332728494</v>
+        <v>2.285687286373392</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7807763859794399</v>
+        <v>0.7807618668754858</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5650135915856762</v>
+        <v>0.5649898021947302</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7804109910934731</v>
+        <v>0.7803959319131399</v>
       </c>
       <c r="U13" t="n">
-        <v>6.401922929815592</v>
+        <v>6.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.605024291926516</v>
+        <v>6.566414003683034</v>
       </c>
       <c r="W13" t="n">
-        <v>6.777114158437722</v>
+        <v>6.750451371464945</v>
       </c>
     </row>
     <row r="14">
@@ -1424,7 +1424,7 @@
         <v>9044756</v>
       </c>
       <c r="C14" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D14" t="n">
         <v>3099</v>
@@ -1454,37 +1454,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="M14" t="n">
-        <v>11.82991730479071</v>
+        <v>11.82976027619945</v>
       </c>
       <c r="N14" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1339645925955439</v>
+        <v>-0.1341216211868068</v>
       </c>
       <c r="P14" t="n">
-        <v>2.054671306863648</v>
+        <v>2.054715168272937</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.700889385683155</v>
+        <v>2.70092606967962</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7944316950721657</v>
+        <v>0.7944329014284488</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6086556188833412</v>
+        <v>0.6086449881826076</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7858592938199812</v>
+        <v>0.7858697473581794</v>
       </c>
       <c r="U14" t="n">
-        <v>8.388284851374982</v>
+        <v>8.373747332692069</v>
       </c>
       <c r="V14" t="n">
-        <v>9.278345768560447</v>
+        <v>8.9163070600595</v>
       </c>
       <c r="W14" t="n">
-        <v>11.87757474831278</v>
+        <v>11.65170801317788</v>
       </c>
     </row>
     <row r="15">
@@ -1497,28 +1497,28 @@
         <v>9053555</v>
       </c>
       <c r="C15" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D15" t="n">
+        <v>9796</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
         <v>9795</v>
-      </c>
-      <c r="E15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9794</v>
       </c>
       <c r="G15" s="1" t="n">
         <v>35804</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I15" t="n">
         <v>0.26</v>
       </c>
       <c r="J15" t="n">
-        <v>8.41058641345041</v>
+        <v>8.410415858431172</v>
       </c>
       <c r="K15" t="n">
         <v>131.9</v>
@@ -1527,37 +1527,37 @@
         <v>0.5533496846531183</v>
       </c>
       <c r="M15" t="n">
-        <v>8.666707445806294</v>
+        <v>8.666563780527913</v>
       </c>
       <c r="N15" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2561210323558812</v>
+        <v>0.2561479220967398</v>
       </c>
       <c r="P15" t="n">
-        <v>3.535900893574056</v>
+        <v>3.536120545697759</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.06825052239683</v>
+        <v>11.06783894954386</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04979578723417655</v>
+        <v>0.04977497231777698</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5967274776803495</v>
+        <v>-0.5967658204418818</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03303134753792825</v>
+        <v>0.03301122257670919</v>
       </c>
       <c r="U15" t="n">
-        <v>11.69375175871256</v>
+        <v>11.58398395507021</v>
       </c>
       <c r="V15" t="n">
-        <v>12.05564604886525</v>
+        <v>11.97590046735823</v>
       </c>
       <c r="W15" t="n">
-        <v>12.30420186122824</v>
+        <v>12.28283464086624</v>
       </c>
     </row>
     <row r="16">
@@ -1570,7 +1570,7 @@
         <v>9037610</v>
       </c>
       <c r="C16" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D16" t="n">
         <v>2305</v>
@@ -1600,37 +1600,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="M16" t="n">
-        <v>6.955445824186186</v>
+        <v>6.955439398346412</v>
       </c>
       <c r="N16" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3723124185462727</v>
+        <v>0.3723059927064985</v>
       </c>
       <c r="P16" t="n">
-        <v>2.040482915585456</v>
+        <v>2.040505915968536</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.579583230291027</v>
+        <v>2.579607293092381</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5181653642573086</v>
+        <v>0.5181625064570999</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01527028269559583</v>
+        <v>0.01525191114951552</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5148572754275725</v>
+        <v>0.5148545345039233</v>
       </c>
       <c r="U16" t="n">
-        <v>3.950317923339689</v>
+        <v>3.68</v>
       </c>
       <c r="V16" t="n">
-        <v>4.769974859387426</v>
+        <v>4.56064475578337</v>
       </c>
       <c r="W16" t="n">
-        <v>5.452338752483355</v>
+        <v>4.968709032792764</v>
       </c>
     </row>
     <row r="17">
@@ -1643,28 +1643,28 @@
         <v>9037738</v>
       </c>
       <c r="C17" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D17" t="n">
+        <v>3199</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
         <v>3198</v>
-      </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3197</v>
       </c>
       <c r="G17" s="1" t="n">
         <v>42370</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I17" t="n">
         <v>1.81</v>
       </c>
       <c r="J17" t="n">
-        <v>6.50663903659681</v>
+        <v>6.506024077548469</v>
       </c>
       <c r="K17" t="n">
         <v>18.4925</v>
@@ -1673,37 +1673,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="M17" t="n">
-        <v>6.70242689571704</v>
+        <v>6.701768280673227</v>
       </c>
       <c r="N17" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1957878591202306</v>
+        <v>0.1957442031247602</v>
       </c>
       <c r="P17" t="n">
-        <v>1.098036915434718</v>
+        <v>1.097974304620363</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.488644272773963</v>
+        <v>1.488456983411003</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5997299970012602</v>
+        <v>0.5998791580945382</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2151241668148857</v>
+        <v>0.2154122772756815</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5967713101904908</v>
+        <v>0.5969205052125228</v>
       </c>
       <c r="U17" t="n">
-        <v>4.866268240618501</v>
+        <v>4.64212430872437</v>
       </c>
       <c r="V17" t="n">
-        <v>5.784262039012978</v>
+        <v>5.60268598013267</v>
       </c>
       <c r="W17" t="n">
-        <v>6.420409819879463</v>
+        <v>6.187589063047058</v>
       </c>
     </row>
     <row r="18">
@@ -1716,28 +1716,28 @@
         <v>9043370</v>
       </c>
       <c r="C18" t="n">
-        <v>16650</v>
+        <v>16651</v>
       </c>
       <c r="D18" t="n">
+        <v>7153</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
         <v>7152</v>
-      </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7151</v>
       </c>
       <c r="G18" s="1" t="n">
         <v>37987</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="I18" t="n">
         <v>0.04</v>
       </c>
       <c r="J18" t="n">
-        <v>10.3829149769263</v>
+        <v>10.38179879753915</v>
       </c>
       <c r="K18" t="n">
         <v>24.5875</v>
@@ -1746,37 +1746,37 @@
         <v>4.73</v>
       </c>
       <c r="M18" t="n">
-        <v>11.16560733641282</v>
+        <v>11.16475164774853</v>
       </c>
       <c r="N18" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7826923594865154</v>
+        <v>0.7829528502093831</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03225138682031</v>
+        <v>2.032763432977918</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.750576503734912</v>
+        <v>2.751186176004485</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7262145542217279</v>
+        <v>0.7262243876252635</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4688815464657763</v>
+        <v>0.4689039778545669</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6791774910414116</v>
+        <v>0.6791529476148039</v>
       </c>
       <c r="U18" t="n">
-        <v>7.962271702191409</v>
+        <v>7.936486572883429</v>
       </c>
       <c r="V18" t="n">
-        <v>8.061692602861564</v>
+        <v>8.038687834800559</v>
       </c>
       <c r="W18" t="n">
-        <v>8.143559947814314</v>
+        <v>8.123346621446284</v>
       </c>
     </row>
   </sheetData>
@@ -1845,22 +1845,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.962271702191409</v>
+        <v>7.936486572883429</v>
       </c>
       <c r="G2" t="n">
-        <v>8.061692602861564</v>
+        <v>8.038687834800559</v>
       </c>
       <c r="H2" t="n">
-        <v>8.143559947814314</v>
+        <v>8.123346621446284</v>
       </c>
     </row>
     <row r="3">
@@ -1873,19 +1873,19 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>6.109972296151311</v>
+        <v>6.06</v>
       </c>
       <c r="G3" t="n">
-        <v>6.175436427332439</v>
+        <v>6.165309716055784</v>
       </c>
       <c r="H3" t="n">
         <v>6.22</v>
@@ -1901,22 +1901,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="G4" t="n">
-        <v>4.884937707151636</v>
+        <v>4.788344398913265</v>
       </c>
       <c r="H4" t="n">
-        <v>5.41</v>
+        <v>5.147904245727468</v>
       </c>
     </row>
     <row r="5">
@@ -1929,22 +1929,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.69375175871256</v>
+        <v>11.58398395507021</v>
       </c>
       <c r="G5" t="n">
-        <v>12.05564604886525</v>
+        <v>11.97590046735823</v>
       </c>
       <c r="H5" t="n">
-        <v>12.30420186122824</v>
+        <v>12.28283464086624</v>
       </c>
     </row>
     <row r="6">
@@ -1957,22 +1957,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>110.4</v>
+        <v>108.92</v>
       </c>
       <c r="G6" t="n">
-        <v>111.5269391266153</v>
+        <v>111.0004576696035</v>
       </c>
       <c r="H6" t="n">
-        <v>112.1735135554431</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="7">
@@ -1985,22 +1985,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.388284851374982</v>
+        <v>8.373747332692069</v>
       </c>
       <c r="G7" t="n">
-        <v>9.278345768560447</v>
+        <v>8.916307060059498</v>
       </c>
       <c r="H7" t="n">
-        <v>11.87757474831278</v>
+        <v>11.65170801317788</v>
       </c>
     </row>
     <row r="8">
@@ -2013,22 +2013,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.867834263294696</v>
+        <v>7.85190473353983</v>
       </c>
       <c r="G8" t="n">
-        <v>8.516559170734416</v>
+        <v>8.40249222980437</v>
       </c>
       <c r="H8" t="n">
-        <v>8.969020050728336</v>
+        <v>8.9275</v>
       </c>
     </row>
     <row r="9">
@@ -2041,22 +2041,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.281336733095788</v>
+        <v>5.234564177848553</v>
       </c>
       <c r="G9" t="n">
-        <v>5.500300815107519</v>
+        <v>5.425673149854016</v>
       </c>
       <c r="H9" t="n">
-        <v>5.803600994371898</v>
+        <v>5.800010996031258</v>
       </c>
     </row>
     <row r="10">
@@ -2069,22 +2069,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.981758060466298</v>
+        <v>5.93</v>
       </c>
       <c r="G10" t="n">
-        <v>6.186911210785491</v>
+        <v>6.18629150856284</v>
       </c>
       <c r="H10" t="n">
-        <v>6.352571029113949</v>
+        <v>6.361594181372594</v>
       </c>
     </row>
     <row r="11">
@@ -2097,22 +2097,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.950317923339689</v>
+        <v>3.68</v>
       </c>
       <c r="G11" t="n">
-        <v>4.769974859387426</v>
+        <v>4.56064475578337</v>
       </c>
       <c r="H11" t="n">
-        <v>5.452338752483355</v>
+        <v>4.968709032792764</v>
       </c>
     </row>
     <row r="12">
@@ -2125,22 +2125,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.401922929815592</v>
+        <v>6.37</v>
       </c>
       <c r="G12" t="n">
-        <v>6.605024291926516</v>
+        <v>6.566414003683033</v>
       </c>
       <c r="H12" t="n">
-        <v>6.777114158437722</v>
+        <v>6.750451371464945</v>
       </c>
     </row>
     <row r="13">
@@ -2153,22 +2153,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1014171617984</v>
+        <v>10.08050066385531</v>
       </c>
       <c r="G13" t="n">
-        <v>10.74867082005867</v>
+        <v>10.59140060260334</v>
       </c>
       <c r="H13" t="n">
-        <v>11.50413608173295</v>
+        <v>11.36869558040371</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.53</v>
+        <v>6.389071605361553</v>
       </c>
       <c r="G14" t="n">
-        <v>6.925364799728411</v>
+        <v>6.893267100462259</v>
       </c>
       <c r="H14" t="n">
-        <v>7.205357163325993</v>
+        <v>7.205198970971844</v>
       </c>
     </row>
     <row r="15">
@@ -2209,22 +2209,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.7925</v>
+        <v>6.723965927316091</v>
       </c>
       <c r="G15" t="n">
-        <v>7.006594522804919</v>
+        <v>6.974847164306932</v>
       </c>
       <c r="H15" t="n">
-        <v>7.170251828872009</v>
+        <v>7.157154318487135</v>
       </c>
     </row>
     <row r="16">
@@ -2237,22 +2237,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.866268240618501</v>
+        <v>4.64212430872437</v>
       </c>
       <c r="G16" t="n">
-        <v>5.784262039012978</v>
+        <v>5.602685980132671</v>
       </c>
       <c r="H16" t="n">
-        <v>6.420409819879463</v>
+        <v>6.187589063047058</v>
       </c>
     </row>
     <row r="17">
@@ -2265,22 +2265,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.591856200822604</v>
+        <v>4.578499577620378</v>
       </c>
       <c r="G17" t="n">
-        <v>5.024862499234708</v>
+        <v>4.925266228568185</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4833324385695</v>
+        <v>5.451759562285003</v>
       </c>
     </row>
     <row r="18">
@@ -2293,22 +2293,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.294996605386324</v>
+        <v>3.22</v>
       </c>
       <c r="G18" t="n">
-        <v>3.578404500385561</v>
+        <v>3.577055019346781</v>
       </c>
       <c r="H18" t="n">
-        <v>3.760762815054337</v>
+        <v>3.763740493038803</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,105 +434,120 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>metodo_dwlt</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>n_hist_sonics</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>n_obs_nivel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>n_fore_sonics</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>n_validacion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meses_curva_ok</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n_meses_curva_ok</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>fecha_inicio_validacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>fecha_fin_validacion</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>nivel_obs_min</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>nivel_obs_prom</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>nivel_obs_max</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>nivel_dwlt_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>nivel_dwlt_prom</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nivel_dwlt_max</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>bias_m</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>mae_m</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rmse_m</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>r_pearson</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>nse</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>kge_2009</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>forecast_nivel_min_m</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>forecast_nivel_prom_m</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>forecast_nivel_max_m</t>
         </is>
@@ -547,68 +562,81 @@
       <c r="B2" t="n">
         <v>9038134</v>
       </c>
-      <c r="C2" t="n">
-        <v>16651</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D2" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E2" t="n">
+        <v>9957</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9956</v>
       </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" t="n">
-        <v>9955</v>
-      </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="K2" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.78</v>
       </c>
-      <c r="J2" t="n">
-        <v>102.9289963167587</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
+        <v>102.9193027655015</v>
+      </c>
+      <c r="N2" t="n">
         <v>118.97</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.846246418338109</v>
-      </c>
-      <c r="M2" t="n">
-        <v>102.9170511931064</v>
-      </c>
-      <c r="N2" t="n">
-        <v>118.8938450398262</v>
-      </c>
       <c r="O2" t="n">
-        <v>-0.01194512365233252</v>
+        <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>17.70716511535175</v>
+        <v>95.33228138807371</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.05387757898497</v>
+        <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1290752763692524</v>
+        <v>-7.587021377427829</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7376914900802976</v>
+        <v>22.63546395925188</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1290719879859945</v>
+        <v>31.50605303978796</v>
       </c>
       <c r="U2" t="n">
-        <v>108.92</v>
+        <v>0.135872469013921</v>
       </c>
       <c r="V2" t="n">
-        <v>111.0004576696035</v>
+        <v>-0.325432292243546</v>
       </c>
       <c r="W2" t="n">
-        <v>112.08</v>
+        <v>0.06575096893762122</v>
+      </c>
+      <c r="X2" t="n">
+        <v>95.87613444605</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>105.2705788003175</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>113.5603298057117</v>
       </c>
     </row>
     <row r="3">
@@ -620,68 +648,81 @@
       <c r="B3" t="n">
         <v>9038269</v>
       </c>
-      <c r="C3" t="n">
-        <v>16651</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D3" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14535</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14534</v>
       </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
-      <c r="F3" t="n">
-        <v>14533</v>
-      </c>
-      <c r="G3" s="1" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>30317</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="K3" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.01</v>
       </c>
-      <c r="J3" t="n">
-        <v>4.90708645840501</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.02</v>
-      </c>
       <c r="M3" t="n">
-        <v>4.962793072120321</v>
+        <v>4.907021982936563</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05570661371531164</v>
+        <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>1.351051258592869</v>
+        <v>4.955666697532456</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.725722029455693</v>
+        <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7795317466831925</v>
+        <v>0.04864471459589358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5664961233501915</v>
+        <v>1.354207997255708</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7784514678238366</v>
+        <v>1.729961778437443</v>
       </c>
       <c r="U3" t="n">
-        <v>3.22</v>
+        <v>0.7784487092992268</v>
       </c>
       <c r="V3" t="n">
-        <v>3.577055019346781</v>
+        <v>0.5643373004804404</v>
       </c>
       <c r="W3" t="n">
-        <v>3.763740493038803</v>
+        <v>0.7774711695412868</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.094948531881759</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.509218087994149</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.720518324039409</v>
       </c>
     </row>
     <row r="4">
@@ -693,68 +734,81 @@
       <c r="B4" t="n">
         <v>9039635</v>
       </c>
-      <c r="C4" t="n">
-        <v>16651</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D4" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10217</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10216</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10215</v>
-      </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>35065</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="K4" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
-      <c r="J4" t="n">
-        <v>6.919808614782183</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
+        <v>6.919731303837119</v>
+      </c>
+      <c r="N4" t="n">
         <v>12.93</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7.250324656947725</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12.73</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.3305160421655411</v>
+        <v>0.5041527473520986</v>
       </c>
       <c r="P4" t="n">
-        <v>1.294985088704803</v>
+        <v>7.238244863604294</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.684893275203564</v>
+        <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8674480989548822</v>
+        <v>0.3185135597671748</v>
       </c>
       <c r="S4" t="n">
-        <v>0.736981510075724</v>
+        <v>1.290174170464782</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8471285821647787</v>
+        <v>1.677634763737211</v>
       </c>
       <c r="U4" t="n">
-        <v>4.578499577620378</v>
+        <v>0.8680638408964237</v>
       </c>
       <c r="V4" t="n">
-        <v>4.925266228568185</v>
+        <v>0.7392187417451412</v>
       </c>
       <c r="W4" t="n">
-        <v>5.451759562285003</v>
+        <v>0.8471996502193058</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.671984847195314</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.929646257864516</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.409095512259854</v>
       </c>
     </row>
     <row r="5">
@@ -766,68 +820,81 @@
       <c r="B5" t="n">
         <v>9032282</v>
       </c>
-      <c r="C5" t="n">
-        <v>16651</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>8826</v>
+        <v>16652</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>8828</v>
       </c>
       <c r="F5" t="n">
-        <v>8826</v>
-      </c>
-      <c r="G5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8827</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>36892</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="K5" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.52</v>
       </c>
-      <c r="J5" t="n">
-        <v>6.729487876727848</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
+        <v>6.729641724255126</v>
+      </c>
+      <c r="N5" t="n">
         <v>10.6125</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.616683937823834</v>
-      </c>
-      <c r="M5" t="n">
-        <v>7.018097311255914</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.19100035038542</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.2886094345280652</v>
+        <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>1.482614743801566</v>
+        <v>6.922251982269803</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.911425821856646</v>
+        <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3048444464891431</v>
+        <v>0.1926102580146766</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1982314784303485</v>
+        <v>1.446658943345836</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2802624044083285</v>
+        <v>1.844914671307581</v>
       </c>
       <c r="U5" t="n">
-        <v>6.723965927316091</v>
+        <v>0.2963341860774601</v>
       </c>
       <c r="V5" t="n">
-        <v>6.974847164306932</v>
+        <v>-0.1163434864810704</v>
       </c>
       <c r="W5" t="n">
-        <v>7.157154318487135</v>
+        <v>0.2473681852403379</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.813301189812796</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.034254552129413</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.223379445853321</v>
       </c>
     </row>
     <row r="6">
@@ -839,68 +906,81 @@
       <c r="B6" t="n">
         <v>9036028</v>
       </c>
-      <c r="C6" t="n">
-        <v>16651</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D6" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14190</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14189</v>
       </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" t="n">
-        <v>14188</v>
-      </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>31048</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="K6" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L6" t="n">
         <v>1.025</v>
       </c>
-      <c r="J6" t="n">
-        <v>5.582724661685933</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.345</v>
-      </c>
       <c r="M6" t="n">
-        <v>5.588883574706596</v>
+        <v>5.582744203256043</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006158913020665243</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.156236783577111</v>
+        <v>5.585585018220065</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.494513578755264</v>
+        <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5089447418462268</v>
+        <v>0.002840814964022571</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07466457325693443</v>
+        <v>1.162756957105505</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5050822435353698</v>
+        <v>1.501002611837489</v>
       </c>
       <c r="U6" t="n">
-        <v>6.06</v>
+        <v>0.5076459723344227</v>
       </c>
       <c r="V6" t="n">
-        <v>6.165309716055784</v>
+        <v>0.06654800348817924</v>
       </c>
       <c r="W6" t="n">
-        <v>6.22</v>
+        <v>0.5045673123816072</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.971933596703742</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.13724344826476</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.238725709542586</v>
       </c>
     </row>
     <row r="7">
@@ -912,68 +992,81 @@
       <c r="B7" t="n">
         <v>9040454</v>
       </c>
-      <c r="C7" t="n">
-        <v>16651</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D7" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8988</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8987</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8986</v>
-      </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L7" t="n">
         <v>0.16</v>
       </c>
-      <c r="J7" t="n">
-        <v>7.880473514355664</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
+        <v>7.880510181373095</v>
+      </c>
+      <c r="N7" t="n">
         <v>15.14</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.6453438395415473</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8.118473609709923</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14.26345655220743</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.2380000953542593</v>
+        <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>1.443649252208346</v>
+        <v>8.092733281453045</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.823005908252468</v>
+        <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.809461294277773</v>
+        <v>0.2122231000799516</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6301335158010737</v>
+        <v>1.421045293572391</v>
       </c>
       <c r="T7" t="n">
-        <v>0.799811790557847</v>
+        <v>1.793485647513805</v>
       </c>
       <c r="U7" t="n">
-        <v>5.93</v>
+        <v>0.8127966556249928</v>
       </c>
       <c r="V7" t="n">
-        <v>6.18629150856284</v>
+        <v>0.6419758014149836</v>
       </c>
       <c r="W7" t="n">
-        <v>6.361594181372594</v>
+        <v>0.7982017156770616</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.7516263767111</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.148325690464379</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.360177905602171</v>
       </c>
     </row>
     <row r="8">
@@ -985,68 +1078,81 @@
       <c r="B8" t="n">
         <v>9040439</v>
       </c>
-      <c r="C8" t="n">
-        <v>16651</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D8" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E8" t="n">
+        <v>13853</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13852</v>
       </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F8" t="n">
-        <v>13851</v>
-      </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>31778</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="K8" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.06</v>
       </c>
-      <c r="J8" t="n">
-        <v>7.617002202007075</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.52</v>
-      </c>
       <c r="M8" t="n">
-        <v>7.682990004007297</v>
+        <v>7.616930948599481</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06598780200022202</v>
+        <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>1.477659973322899</v>
+        <v>7.660260953499951</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.920151342390373</v>
+        <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7617096190455039</v>
+        <v>0.04333000490047045</v>
       </c>
       <c r="S8" t="n">
-        <v>0.536183396339482</v>
+        <v>1.502824612746873</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7596979144976741</v>
+        <v>1.962141263783013</v>
       </c>
       <c r="U8" t="n">
-        <v>6.389071605361553</v>
+        <v>0.7529676822909155</v>
       </c>
       <c r="V8" t="n">
-        <v>6.893267100462258</v>
+        <v>0.5156454047052352</v>
       </c>
       <c r="W8" t="n">
-        <v>7.205198970971844</v>
+        <v>0.7520092109960104</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6.27246912544592</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.804012839769075</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.132008751417632</v>
       </c>
     </row>
     <row r="9">
@@ -1058,68 +1164,81 @@
       <c r="B9" t="n">
         <v>9042153</v>
       </c>
-      <c r="C9" t="n">
-        <v>16651</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D9" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E9" t="n">
         <v>3737</v>
       </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
       <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>3737</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>37257</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>3.7875</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>10.30505953973775</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>39.075</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>4.255000000000001</v>
       </c>
-      <c r="M9" t="n">
-        <v>10.62166578549552</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14.31645908761767</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3166062457577587</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.05156683843098</v>
+        <v>10.74327467642422</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.69749636657411</v>
+        <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.356385083965104</v>
+        <v>0.4382151366864612</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1199364788313784</v>
+        <v>2.151393985812674</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3354893575308939</v>
+        <v>2.874483279762739</v>
       </c>
       <c r="U9" t="n">
-        <v>10.08050066385531</v>
+        <v>0.3307111867665943</v>
       </c>
       <c r="V9" t="n">
-        <v>10.59140060260334</v>
+        <v>-0.2717191984699869</v>
       </c>
       <c r="W9" t="n">
-        <v>11.36869558040371</v>
+        <v>0.3250253771885661</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.97983771132594</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10.45404182878192</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>11.09200246171443</v>
       </c>
     </row>
     <row r="10">
@@ -1131,68 +1250,81 @@
       <c r="B10" t="n">
         <v>9040208</v>
       </c>
-      <c r="C10" t="n">
-        <v>16651</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D10" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E10" t="n">
         <v>13793</v>
       </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
       <c r="F10" t="n">
-        <v>13792</v>
-      </c>
-      <c r="G10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13793</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>31413</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="K10" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L10" t="n">
         <v>0.4375</v>
       </c>
-      <c r="J10" t="n">
-        <v>5.246294953596287</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>5.246255346915103</v>
+      </c>
+      <c r="N10" t="n">
         <v>10.15</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.8401943005181348</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.220953023477025</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
+        <v>0.4490779286658197</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.219128521481942</v>
+      </c>
+      <c r="Q10" t="n">
         <v>9.94</v>
       </c>
-      <c r="O10" t="n">
-        <v>-0.02534193011926178</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.158351208468454</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.477199336231334</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.4293858996067023</v>
+        <v>-0.02712682543316047</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.08237639078345116</v>
+        <v>1.160865364036006</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4267739623486192</v>
+        <v>1.48195026311239</v>
       </c>
       <c r="U10" t="n">
-        <v>4.48</v>
+        <v>0.4295915808765946</v>
       </c>
       <c r="V10" t="n">
-        <v>4.788344398913265</v>
+        <v>-0.08941709567383782</v>
       </c>
       <c r="W10" t="n">
-        <v>5.147904245727468</v>
+        <v>0.4276071820917159</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.463381747207493</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.716982645215031</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.034019748827397</v>
       </c>
     </row>
     <row r="11">
@@ -1204,68 +1336,81 @@
       <c r="B11" t="n">
         <v>9043597</v>
       </c>
-      <c r="C11" t="n">
-        <v>16651</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D11" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4112</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4111</v>
       </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4110</v>
-      </c>
-      <c r="G11" s="1" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>41640</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="K11" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L11" t="n">
         <v>2.195</v>
       </c>
-      <c r="J11" t="n">
-        <v>7.498414841849149</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>7.497826562880078</v>
+      </c>
+      <c r="N11" t="n">
         <v>19.1775</v>
       </c>
-      <c r="L11" t="n">
-        <v>2.204850111028867</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7.670831780816735</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16.78594914040094</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.1724169389675873</v>
+        <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9166204802271911</v>
+        <v>7.714007674049111</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.199735299509699</v>
+        <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8289788017743478</v>
+        <v>0.2161811111690331</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6528489894799561</v>
+        <v>0.9634700656381733</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8273309016821457</v>
+        <v>1.343175418165205</v>
       </c>
       <c r="U11" t="n">
-        <v>5.234564177848553</v>
+        <v>0.7907299120879707</v>
       </c>
       <c r="V11" t="n">
-        <v>5.425673149854016</v>
+        <v>0.5649194293213557</v>
       </c>
       <c r="W11" t="n">
-        <v>5.800010996031258</v>
+        <v>0.7883990835444079</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.148394978812007</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.364282616906164</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.717378126389128</v>
       </c>
     </row>
     <row r="12">
@@ -1277,68 +1422,81 @@
       <c r="B12" t="n">
         <v>9042214</v>
       </c>
-      <c r="C12" t="n">
-        <v>16651</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D12" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6447</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6446</v>
       </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6445</v>
-      </c>
-      <c r="G12" s="1" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>39083</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="K12" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L12" t="n">
         <v>1.54</v>
       </c>
-      <c r="J12" t="n">
-        <v>9.619745021980863</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
+        <v>9.619540283379875</v>
+      </c>
+      <c r="N12" t="n">
         <v>16.215</v>
       </c>
-      <c r="L12" t="n">
-        <v>2.858246962115797</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.03373186703846</v>
-      </c>
-      <c r="N12" t="n">
-        <v>16.21</v>
-      </c>
       <c r="O12" t="n">
-        <v>0.4139868450575971</v>
+        <v>2.94898927519542</v>
       </c>
       <c r="P12" t="n">
-        <v>1.696130515055037</v>
+        <v>10.01675651933839</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.155457248136254</v>
+        <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8231773250069385</v>
+        <v>0.3972162359585186</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6484036457994256</v>
+        <v>1.683682222863671</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8114410738343276</v>
+        <v>2.138509287101883</v>
       </c>
       <c r="U12" t="n">
-        <v>7.85190473353983</v>
+        <v>0.8253476307668026</v>
       </c>
       <c r="V12" t="n">
-        <v>8.40249222980437</v>
+        <v>0.6538643617691298</v>
       </c>
       <c r="W12" t="n">
-        <v>8.9275</v>
+        <v>0.8135394599631032</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.827541425908806</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.272883015002295</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8.843579048263145</v>
       </c>
     </row>
     <row r="13">
@@ -1350,68 +1508,81 @@
       <c r="B13" t="n">
         <v>9043425</v>
       </c>
-      <c r="C13" t="n">
-        <v>16651</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D13" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E13" t="n">
+        <v>14034</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14033</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>14032</v>
-      </c>
-      <c r="G13" s="1" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>30682</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="K13" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.26</v>
       </c>
-      <c r="J13" t="n">
-        <v>8.134642780786773</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>8.134611807881422</v>
+      </c>
+      <c r="N13" t="n">
         <v>34.0025</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M13" t="n">
-        <v>8.206587957624482</v>
-      </c>
-      <c r="N13" t="n">
-        <v>14.32</v>
-      </c>
       <c r="O13" t="n">
-        <v>0.07194517683770971</v>
+        <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>1.7604718760402</v>
+        <v>8.211891129130818</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.285687286373392</v>
+        <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7807618668754858</v>
+        <v>0.0772793212493936</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5649898021947302</v>
+        <v>1.786859542982717</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7803959319131399</v>
+        <v>2.321874367784248</v>
       </c>
       <c r="U13" t="n">
-        <v>6.37</v>
+        <v>0.7762522116689691</v>
       </c>
       <c r="V13" t="n">
-        <v>6.566414003683034</v>
+        <v>0.5510750844921338</v>
       </c>
       <c r="W13" t="n">
-        <v>6.750451371464945</v>
+        <v>0.7760410260374765</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.451617700269322</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.615536371713238</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.773556308194289</v>
       </c>
     </row>
     <row r="14">
@@ -1423,68 +1594,81 @@
       <c r="B14" t="n">
         <v>9044756</v>
       </c>
-      <c r="C14" t="n">
-        <v>16651</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D14" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E14" t="n">
         <v>3099</v>
       </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>3099</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>3.305</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>11.96388189738625</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>30.745</v>
       </c>
-      <c r="L14" t="n">
-        <v>4.682413027387121</v>
-      </c>
-      <c r="M14" t="n">
-        <v>11.82976027619945</v>
-      </c>
-      <c r="N14" t="n">
-        <v>21.32952932657494</v>
-      </c>
       <c r="O14" t="n">
-        <v>-0.1341216211868068</v>
+        <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>2.054715168272937</v>
+        <v>11.83379077686753</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.70092606967962</v>
+        <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7944329014284488</v>
+        <v>-0.1300911205187242</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6086449881826076</v>
+        <v>2.042973450164269</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7858697473581794</v>
+        <v>2.65876393855271</v>
       </c>
       <c r="U14" t="n">
-        <v>8.373747332692069</v>
+        <v>0.8009612127948786</v>
       </c>
       <c r="V14" t="n">
-        <v>8.9163070600595</v>
+        <v>0.6207679219620057</v>
       </c>
       <c r="W14" t="n">
-        <v>11.65170801317788</v>
+        <v>0.7923691355419947</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.480440672056586</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.931262274532168</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.854705827971273</v>
       </c>
     </row>
     <row r="15">
@@ -1496,68 +1680,81 @@
       <c r="B15" t="n">
         <v>9053555</v>
       </c>
-      <c r="C15" t="n">
-        <v>16651</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D15" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9797</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9796</v>
       </c>
-      <c r="E15" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" t="n">
-        <v>9795</v>
-      </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>35804</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="K15" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L15" t="n">
         <v>0.26</v>
       </c>
-      <c r="J15" t="n">
-        <v>8.410415858431172</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
+        <v>8.410231046685722</v>
+      </c>
+      <c r="N15" t="n">
         <v>131.9</v>
       </c>
-      <c r="L15" t="n">
-        <v>0.5533496846531183</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8.666563780527913</v>
-      </c>
-      <c r="N15" t="n">
-        <v>131.7868211440985</v>
-      </c>
       <c r="O15" t="n">
-        <v>0.2561479220967398</v>
+        <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>3.536120545697759</v>
+        <v>9.377474681304339</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.06783894954386</v>
+        <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04977497231777698</v>
+        <v>0.9672436346186157</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5967658204418818</v>
+        <v>4.182807358680301</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03301122257670919</v>
+        <v>11.62297588456514</v>
       </c>
       <c r="U15" t="n">
-        <v>11.58398395507021</v>
+        <v>0.03405679618924165</v>
       </c>
       <c r="V15" t="n">
-        <v>11.97590046735823</v>
+        <v>-0.7611351341083314</v>
       </c>
       <c r="W15" t="n">
-        <v>12.28283464086624</v>
+        <v>0.02212204471794355</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.48177075474107</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.90242513707105</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12.24842507881084</v>
       </c>
     </row>
     <row r="16">
@@ -1569,68 +1766,81 @@
       <c r="B16" t="n">
         <v>9037610</v>
       </c>
-      <c r="C16" t="n">
-        <v>16651</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D16" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E16" t="n">
         <v>2305</v>
       </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
       <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>2305</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>43252</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>6.583133405639913</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>12.23</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.395549592894153</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.955439398346412</v>
-      </c>
-      <c r="N16" t="n">
-        <v>12.15738414192614</v>
-      </c>
       <c r="O16" t="n">
-        <v>0.3723059927064985</v>
+        <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>2.040505915968536</v>
+        <v>6.927511842767152</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.579607293092381</v>
+        <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5181625064570999</v>
+        <v>0.3443784371272393</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01525191114951552</v>
+        <v>1.971851086623644</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5148545345039233</v>
+        <v>2.479796253308504</v>
       </c>
       <c r="U16" t="n">
-        <v>3.68</v>
+        <v>0.533512878767687</v>
       </c>
       <c r="V16" t="n">
-        <v>4.56064475578337</v>
+        <v>0.08998206134685227</v>
       </c>
       <c r="W16" t="n">
-        <v>4.968709032792764</v>
+        <v>0.5283743247183654</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.46199237455926</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.659597346823183</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.955987477451191</v>
       </c>
     </row>
     <row r="17">
@@ -1642,68 +1852,81 @@
       <c r="B17" t="n">
         <v>9037738</v>
       </c>
-      <c r="C17" t="n">
-        <v>16651</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D17" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3199</v>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3198</v>
-      </c>
-      <c r="G17" s="1" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="K17" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L17" t="n">
         <v>1.81</v>
       </c>
-      <c r="J17" t="n">
-        <v>6.506024077548469</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>6.505378243201001</v>
+      </c>
+      <c r="N17" t="n">
         <v>18.4925</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.826106587712805</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.701768280673227</v>
-      </c>
-      <c r="N17" t="n">
-        <v>14.92774999999984</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.1957442031247602</v>
+        <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>1.097974304620363</v>
+        <v>6.730766586273819</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.488456983411003</v>
+        <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5998791580945382</v>
+        <v>0.225388343072818</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2154122772756815</v>
+        <v>1.089059679961258</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5969205052125228</v>
+        <v>1.47862775726344</v>
       </c>
       <c r="U17" t="n">
-        <v>4.64212430872437</v>
+        <v>0.6071369822113528</v>
       </c>
       <c r="V17" t="n">
-        <v>5.60268598013267</v>
+        <v>0.2258640160580968</v>
       </c>
       <c r="W17" t="n">
-        <v>6.187589063047058</v>
+        <v>0.6036247712056213</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.553891627231145</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.724578393091734</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.57838991195923</v>
       </c>
     </row>
     <row r="18">
@@ -1715,68 +1938,81 @@
       <c r="B18" t="n">
         <v>9043370</v>
       </c>
-      <c r="C18" t="n">
-        <v>16651</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
       </c>
       <c r="D18" t="n">
+        <v>16652</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7154</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7153</v>
       </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
-      <c r="F18" t="n">
-        <v>7152</v>
-      </c>
-      <c r="G18" s="1" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>37987</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="I18" t="n">
+      <c r="K18" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.04</v>
       </c>
-      <c r="J18" t="n">
-        <v>10.38179879753915</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>10.38065077589822</v>
+      </c>
+      <c r="N18" t="n">
         <v>24.5875</v>
       </c>
-      <c r="L18" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="M18" t="n">
-        <v>11.16475164774853</v>
-      </c>
-      <c r="N18" t="n">
-        <v>17.53862298528381</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.7829528502093831</v>
+        <v>4.811036695388214</v>
       </c>
       <c r="P18" t="n">
-        <v>2.032763432977918</v>
+        <v>11.17040274555884</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.751186176004485</v>
+        <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7262243876252635</v>
+        <v>0.7897519696606117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4689039778545669</v>
+        <v>2.035567518892357</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6791529476148039</v>
+        <v>2.755944403040442</v>
       </c>
       <c r="U18" t="n">
-        <v>7.936486572883429</v>
+        <v>0.7252161039056807</v>
       </c>
       <c r="V18" t="n">
-        <v>8.038687834800559</v>
+        <v>0.467343138799824</v>
       </c>
       <c r="W18" t="n">
-        <v>8.123346621446284</v>
+        <v>0.6764658353038074</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.094495847291423</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.156417798751182</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.233989985488543</v>
       </c>
     </row>
   </sheetData>
@@ -1845,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.936486572883429</v>
+        <v>8.094495847291423</v>
       </c>
       <c r="G2" t="n">
-        <v>8.038687834800559</v>
+        <v>8.156417798751182</v>
       </c>
       <c r="H2" t="n">
-        <v>8.123346621446284</v>
+        <v>8.233989985488543</v>
       </c>
     </row>
     <row r="3">
@@ -1873,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>6.06</v>
+        <v>5.971933596703742</v>
       </c>
       <c r="G3" t="n">
-        <v>6.165309716055784</v>
+        <v>6.13724344826476</v>
       </c>
       <c r="H3" t="n">
-        <v>6.22</v>
+        <v>6.238725709542586</v>
       </c>
     </row>
     <row r="4">
@@ -1901,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.48</v>
+        <v>4.463381747207493</v>
       </c>
       <c r="G4" t="n">
-        <v>4.788344398913265</v>
+        <v>4.716982645215031</v>
       </c>
       <c r="H4" t="n">
-        <v>5.147904245727468</v>
+        <v>5.034019748827397</v>
       </c>
     </row>
     <row r="5">
@@ -1929,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.58398395507021</v>
+        <v>11.48177075474107</v>
       </c>
       <c r="G5" t="n">
-        <v>11.97590046735823</v>
+        <v>11.90242513707105</v>
       </c>
       <c r="H5" t="n">
-        <v>12.28283464086624</v>
+        <v>12.24842507881084</v>
       </c>
     </row>
     <row r="6">
@@ -1957,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>108.92</v>
+        <v>95.87613444605</v>
       </c>
       <c r="G6" t="n">
-        <v>111.0004576696035</v>
+        <v>105.2705788003175</v>
       </c>
       <c r="H6" t="n">
-        <v>112.08</v>
+        <v>113.5603298057117</v>
       </c>
     </row>
     <row r="7">
@@ -1985,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.373747332692069</v>
+        <v>8.480440672056586</v>
       </c>
       <c r="G7" t="n">
-        <v>8.916307060059498</v>
+        <v>8.931262274532168</v>
       </c>
       <c r="H7" t="n">
-        <v>11.65170801317788</v>
+        <v>9.854705827971273</v>
       </c>
     </row>
     <row r="8">
@@ -2013,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.85190473353983</v>
+        <v>7.827541425908806</v>
       </c>
       <c r="G8" t="n">
-        <v>8.40249222980437</v>
+        <v>8.272883015002295</v>
       </c>
       <c r="H8" t="n">
-        <v>8.9275</v>
+        <v>8.843579048263145</v>
       </c>
     </row>
     <row r="9">
@@ -2041,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.234564177848553</v>
+        <v>5.148394978812007</v>
       </c>
       <c r="G9" t="n">
-        <v>5.425673149854016</v>
+        <v>5.364282616906164</v>
       </c>
       <c r="H9" t="n">
-        <v>5.800010996031258</v>
+        <v>5.717378126389128</v>
       </c>
     </row>
     <row r="10">
@@ -2069,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.93</v>
+        <v>5.7516263767111</v>
       </c>
       <c r="G10" t="n">
-        <v>6.18629150856284</v>
+        <v>6.148325690464379</v>
       </c>
       <c r="H10" t="n">
-        <v>6.361594181372594</v>
+        <v>6.360177905602171</v>
       </c>
     </row>
     <row r="11">
@@ -2097,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.68</v>
+        <v>3.46199237455926</v>
       </c>
       <c r="G11" t="n">
-        <v>4.56064475578337</v>
+        <v>4.659597346823184</v>
       </c>
       <c r="H11" t="n">
-        <v>4.968709032792764</v>
+        <v>5.955987477451191</v>
       </c>
     </row>
     <row r="12">
@@ -2125,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.37</v>
+        <v>6.451617700269322</v>
       </c>
       <c r="G12" t="n">
-        <v>6.566414003683033</v>
+        <v>6.615536371713238</v>
       </c>
       <c r="H12" t="n">
-        <v>6.750451371464945</v>
+        <v>6.773556308194289</v>
       </c>
     </row>
     <row r="13">
@@ -2153,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10.08050066385531</v>
+        <v>9.97983771132594</v>
       </c>
       <c r="G13" t="n">
-        <v>10.59140060260334</v>
+        <v>10.45404182878192</v>
       </c>
       <c r="H13" t="n">
-        <v>11.36869558040371</v>
+        <v>11.09200246171443</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.389071605361553</v>
+        <v>6.27246912544592</v>
       </c>
       <c r="G14" t="n">
-        <v>6.893267100462259</v>
+        <v>6.804012839769075</v>
       </c>
       <c r="H14" t="n">
-        <v>7.205198970971844</v>
+        <v>7.132008751417632</v>
       </c>
     </row>
     <row r="15">
@@ -2209,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.723965927316091</v>
+        <v>6.813301189812796</v>
       </c>
       <c r="G15" t="n">
-        <v>6.974847164306932</v>
+        <v>7.034254552129411</v>
       </c>
       <c r="H15" t="n">
-        <v>7.157154318487135</v>
+        <v>7.223379445853321</v>
       </c>
     </row>
     <row r="16">
@@ -2237,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.64212430872437</v>
+        <v>4.553891627231145</v>
       </c>
       <c r="G16" t="n">
-        <v>5.602685980132671</v>
+        <v>5.724578393091734</v>
       </c>
       <c r="H16" t="n">
-        <v>6.187589063047058</v>
+        <v>6.57838991195923</v>
       </c>
     </row>
     <row r="17">
@@ -2265,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.578499577620378</v>
+        <v>4.671984847195314</v>
       </c>
       <c r="G17" t="n">
-        <v>4.925266228568185</v>
+        <v>4.929646257864516</v>
       </c>
       <c r="H17" t="n">
-        <v>5.451759562285003</v>
+        <v>5.409095512259854</v>
       </c>
     </row>
     <row r="18">
@@ -2293,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.22</v>
+        <v>3.094948531881759</v>
       </c>
       <c r="G18" t="n">
-        <v>3.577055019346781</v>
+        <v>3.509218087994149</v>
       </c>
       <c r="H18" t="n">
-        <v>3.763740493038803</v>
+        <v>3.720518324039409</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,120 +434,105 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>metodo_dwlt</t>
+          <t>n_hist_sonics</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>n_hist_sonics</t>
+          <t>n_obs_nivel</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>n_obs_nivel</t>
+          <t>n_fore_sonics</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>n_fore_sonics</t>
+          <t>n_validacion</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>n_validacion</t>
+          <t>fecha_inicio_validacion</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>meses_curva_ok</t>
+          <t>fecha_fin_validacion</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>n_meses_curva_ok</t>
+          <t>nivel_obs_min</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>fecha_inicio_validacion</t>
+          <t>nivel_obs_prom</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>fecha_fin_validacion</t>
+          <t>nivel_obs_max</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>nivel_obs_min</t>
+          <t>nivel_dwlt_min</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>nivel_obs_prom</t>
+          <t>nivel_dwlt_prom</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>nivel_obs_max</t>
+          <t>nivel_dwlt_max</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>nivel_dwlt_min</t>
+          <t>bias_m</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>nivel_dwlt_prom</t>
+          <t>mae_m</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>nivel_dwlt_max</t>
+          <t>rmse_m</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>bias_m</t>
+          <t>r_pearson</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>mae_m</t>
+          <t>nse</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>rmse_m</t>
+          <t>kge_2009</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>r_pearson</t>
+          <t>forecast_nivel_min_m</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>nse</t>
+          <t>forecast_nivel_prom_m</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
-        <is>
-          <t>kge_2009</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>forecast_nivel_min_m</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>forecast_nivel_prom_m</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
         <is>
           <t>forecast_nivel_max_m</t>
         </is>
@@ -562,81 +547,68 @@
       <c r="B2" t="n">
         <v>9038134</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C2" t="n">
+        <v>16652</v>
       </c>
       <c r="D2" t="n">
-        <v>16652</v>
+        <v>9957</v>
       </c>
       <c r="E2" t="n">
-        <v>9957</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
         <v>9956</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G2" s="1" t="n">
+        <v>36161</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>36161</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>46238</v>
+        <v>1.78</v>
+      </c>
+      <c r="J2" t="n">
+        <v>102.9193027655015</v>
+      </c>
+      <c r="K2" t="n">
+        <v>118.97</v>
       </c>
       <c r="L2" t="n">
-        <v>1.78</v>
+        <v>1.846246418338109</v>
       </c>
       <c r="M2" t="n">
-        <v>102.9193027655015</v>
+        <v>102.9096886676712</v>
       </c>
       <c r="N2" t="n">
-        <v>118.97</v>
+        <v>118.8938450398262</v>
       </c>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>-0.009614097830322561</v>
       </c>
       <c r="P2" t="n">
-        <v>95.33228138807371</v>
+        <v>17.72126574414639</v>
       </c>
       <c r="Q2" t="n">
-        <v>118.38</v>
+        <v>36.07130049628272</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.587021377427829</v>
+        <v>0.1289586119157143</v>
       </c>
       <c r="S2" t="n">
-        <v>22.63546395925188</v>
+        <v>-0.7373733225377321</v>
       </c>
       <c r="T2" t="n">
-        <v>31.50605303978796</v>
+        <v>0.128954398599308</v>
       </c>
       <c r="U2" t="n">
-        <v>0.135872469013921</v>
+        <v>109.97</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.325432292243546</v>
+        <v>111.2362235153552</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06575096893762122</v>
-      </c>
-      <c r="X2" t="n">
-        <v>95.87613444605</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>105.2705788003175</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>113.5603298057117</v>
+        <v>113.6596310966422</v>
       </c>
     </row>
     <row r="3">
@@ -648,81 +620,68 @@
       <c r="B3" t="n">
         <v>9038269</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C3" t="n">
+        <v>16652</v>
       </c>
       <c r="D3" t="n">
-        <v>16652</v>
+        <v>14535</v>
       </c>
       <c r="E3" t="n">
-        <v>14535</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
         <v>14534</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G3" s="1" t="n">
+        <v>30317</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>30317</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>46238</v>
+        <v>0.01</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4.907021982936563</v>
+      </c>
+      <c r="K3" t="n">
+        <v>11.07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>4.907021982936563</v>
+        <v>4.962746029544062</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01185120904911286</v>
+        <v>0.05572404660749876</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955666697532456</v>
+        <v>1.350996637610684</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.07</v>
+        <v>1.725673188965019</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04864471459589358</v>
+        <v>0.7795292564500442</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354207997255708</v>
+        <v>0.5664946459514866</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729961778437443</v>
+        <v>0.7784480230371622</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784487092992268</v>
+        <v>3.106497578124999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643373004804404</v>
+        <v>3.559131656317599</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774711695412868</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.094948531881759</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.509218087994149</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.720518324039409</v>
+        <v>3.767849276123047</v>
       </c>
     </row>
     <row r="4">
@@ -734,81 +693,68 @@
       <c r="B4" t="n">
         <v>9039635</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C4" t="n">
+        <v>16652</v>
       </c>
       <c r="D4" t="n">
-        <v>16652</v>
+        <v>10217</v>
       </c>
       <c r="E4" t="n">
-        <v>10217</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
         <v>10216</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G4" s="1" t="n">
+        <v>35065</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>35065</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>46238</v>
+        <v>3.469446951953614e-18</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.919731303837119</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12.93</v>
       </c>
       <c r="L4" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0.37</v>
       </c>
       <c r="M4" t="n">
-        <v>6.919731303837119</v>
+        <v>7.250304954826767</v>
       </c>
       <c r="N4" t="n">
-        <v>12.93</v>
+        <v>12.73</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5041527473520986</v>
+        <v>0.3305736509896475</v>
       </c>
       <c r="P4" t="n">
-        <v>7.238244863604294</v>
+        <v>1.294961596766595</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.79092695825988</v>
+        <v>1.68490109483858</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3185135597671748</v>
+        <v>0.867434132652752</v>
       </c>
       <c r="S4" t="n">
-        <v>1.290174170464782</v>
+        <v>0.7369548083267738</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677634763737211</v>
+        <v>0.8471030107239369</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680638408964237</v>
+        <v>4.577857142857143</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392187417451412</v>
+        <v>4.865434176627113</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8471996502193058</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.671984847195314</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>4.929646257864516</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>5.409095512259854</v>
+        <v>5.361428571428573</v>
       </c>
     </row>
     <row r="5">
@@ -820,81 +766,68 @@
       <c r="B5" t="n">
         <v>9032282</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C5" t="n">
+        <v>16652</v>
       </c>
       <c r="D5" t="n">
-        <v>16652</v>
+        <v>8828</v>
       </c>
       <c r="E5" t="n">
-        <v>8828</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
         <v>8827</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G5" s="1" t="n">
+        <v>36892</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>36892</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>46238</v>
+        <v>1.52</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.729641724255126</v>
+      </c>
+      <c r="K5" t="n">
+        <v>10.6125</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.616683937823834</v>
       </c>
       <c r="M5" t="n">
-        <v>6.729641724255126</v>
+        <v>7.018568133838615</v>
       </c>
       <c r="N5" t="n">
-        <v>10.6125</v>
+        <v>10.19100035038542</v>
       </c>
       <c r="O5" t="n">
-        <v>2.074263578685523</v>
+        <v>0.2889264095834884</v>
       </c>
       <c r="P5" t="n">
-        <v>6.922251982269803</v>
+        <v>1.482613296405483</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.02216567852482</v>
+        <v>1.911407989081738</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1926102580146766</v>
+        <v>0.3048464079305496</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446658943345836</v>
+        <v>-0.1982627741300567</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844914671307581</v>
+        <v>0.2802549803328918</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963341860774601</v>
+        <v>6.67</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1163434864810704</v>
+        <v>6.93961567764318</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473681852403379</v>
-      </c>
-      <c r="X5" t="n">
-        <v>6.813301189812796</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>7.034254552129413</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7.223379445853321</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="6">
@@ -906,81 +839,68 @@
       <c r="B6" t="n">
         <v>9036028</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16652</v>
       </c>
       <c r="D6" t="n">
-        <v>16652</v>
+        <v>14190</v>
       </c>
       <c r="E6" t="n">
-        <v>14190</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
         <v>14189</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G6" s="1" t="n">
+        <v>31048</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>31048</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>46238</v>
+        <v>1.025</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.582744203256043</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10.01</v>
       </c>
       <c r="L6" t="n">
-        <v>1.025</v>
+        <v>1.345</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582744203256043</v>
+        <v>5.588887180127378</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>0.0061429768713352</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585585018220065</v>
+        <v>1.156166844397233</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.01</v>
+        <v>1.494446791103823</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002840814964022571</v>
+        <v>0.5089534397019244</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162756957105505</v>
+        <v>0.07468413857457523</v>
       </c>
       <c r="T6" t="n">
-        <v>1.501002611837489</v>
+        <v>0.5050904206512818</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076459723344227</v>
+        <v>5.99</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06654800348817924</v>
+        <v>6.149606686868073</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045673123816072</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.971933596703742</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>6.13724344826476</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.238725709542586</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="7">
@@ -992,81 +912,68 @@
       <c r="B7" t="n">
         <v>9040454</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C7" t="n">
+        <v>16652</v>
       </c>
       <c r="D7" t="n">
-        <v>16652</v>
+        <v>8988</v>
       </c>
       <c r="E7" t="n">
-        <v>8988</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
         <v>8987</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G7" s="1" t="n">
+        <v>36161</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>36161</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>46238</v>
+        <v>0.16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7.880510181373095</v>
+      </c>
+      <c r="K7" t="n">
+        <v>15.14</v>
       </c>
       <c r="L7" t="n">
-        <v>0.16</v>
+        <v>0.6453438395415473</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880510181373095</v>
+        <v>8.118590391002964</v>
       </c>
       <c r="N7" t="n">
-        <v>15.14</v>
+        <v>14.26345655220743</v>
       </c>
       <c r="O7" t="n">
-        <v>1.098396014558873</v>
+        <v>0.2380802096298701</v>
       </c>
       <c r="P7" t="n">
-        <v>8.092733281453045</v>
+        <v>1.443930109169861</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.93778665249157</v>
+        <v>1.823434294283678</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2122231000799516</v>
+        <v>0.8093447975663098</v>
       </c>
       <c r="S7" t="n">
-        <v>1.421045293572391</v>
+        <v>0.6299189843988305</v>
       </c>
       <c r="T7" t="n">
-        <v>1.793485647513805</v>
+        <v>0.7996887430616872</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8127966556249928</v>
+        <v>5.778806226576279</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6419758014149836</v>
+        <v>6.160113821780614</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7982017156770616</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5.7516263767111</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>6.148325690464379</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.360177905602171</v>
+        <v>6.370959240362812</v>
       </c>
     </row>
     <row r="8">
@@ -1078,81 +985,68 @@
       <c r="B8" t="n">
         <v>9040439</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C8" t="n">
+        <v>16652</v>
       </c>
       <c r="D8" t="n">
-        <v>16652</v>
+        <v>13853</v>
       </c>
       <c r="E8" t="n">
-        <v>13853</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
         <v>13852</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G8" s="1" t="n">
+        <v>31778</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>31778</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>46238</v>
+        <v>0.06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.616930948599481</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14.03</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616930948599481</v>
+        <v>7.682928815841117</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
       </c>
       <c r="O8" t="n">
-        <v>1.106025794920669</v>
+        <v>0.06599786724163774</v>
       </c>
       <c r="P8" t="n">
-        <v>7.660260953499951</v>
+        <v>1.477577365700045</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.03</v>
+        <v>1.920084194344837</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04333000490047045</v>
+        <v>0.7617097241109143</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502824612746873</v>
+        <v>0.536186454860199</v>
       </c>
       <c r="T8" t="n">
-        <v>1.962141263783013</v>
+        <v>0.7596970591686734</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529676822909155</v>
+        <v>6.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156454047052352</v>
+        <v>6.825976473196578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520092109960104</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6.27246912544592</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>6.804012839769075</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>7.132008751417632</v>
+        <v>7.205024437910757</v>
       </c>
     </row>
     <row r="9">
@@ -1164,81 +1058,68 @@
       <c r="B9" t="n">
         <v>9042153</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C9" t="n">
+        <v>16652</v>
       </c>
       <c r="D9" t="n">
-        <v>16652</v>
+        <v>3737</v>
       </c>
       <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
         <v>3737</v>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3737</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G9" s="1" t="n">
+        <v>37257</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>45930</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>37257</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>45930</v>
+        <v>3.7875</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.30505953973775</v>
+      </c>
+      <c r="K9" t="n">
+        <v>39.075</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7875</v>
+        <v>4.255000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>10.30505953973775</v>
+        <v>10.62146893509687</v>
       </c>
       <c r="N9" t="n">
-        <v>39.075</v>
+        <v>14.31645908761767</v>
       </c>
       <c r="O9" t="n">
-        <v>4.255000000000001</v>
+        <v>0.3164093953591094</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74327467642422</v>
+        <v>2.051523643827713</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.3656067150359</v>
+        <v>2.697439998101684</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4382151366864612</v>
+        <v>0.3564237390149727</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151393985812674</v>
+        <v>-0.1198896736162036</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874483279762739</v>
+        <v>0.3355371108595818</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3307111867665943</v>
+        <v>9.9275</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2717191984699869</v>
+        <v>10.44914356732097</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3250253771885661</v>
-      </c>
-      <c r="X9" t="n">
-        <v>9.97983771132594</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10.45404182878192</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11.09200246171443</v>
+        <v>11.09672653698335</v>
       </c>
     </row>
     <row r="10">
@@ -1250,81 +1131,68 @@
       <c r="B10" t="n">
         <v>9040208</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C10" t="n">
+        <v>16652</v>
       </c>
       <c r="D10" t="n">
-        <v>16652</v>
+        <v>13793</v>
       </c>
       <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
         <v>13793</v>
       </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13793</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G10" s="1" t="n">
+        <v>31413</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>31413</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>46238</v>
+        <v>0.4375</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.246255346915103</v>
+      </c>
+      <c r="K10" t="n">
+        <v>10.15</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4375</v>
+        <v>0.8401943005181348</v>
       </c>
       <c r="M10" t="n">
-        <v>5.246255346915103</v>
+        <v>5.220890837973054</v>
       </c>
       <c r="N10" t="n">
-        <v>10.15</v>
+        <v>9.94</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4490779286658197</v>
+        <v>-0.0253645089420472</v>
       </c>
       <c r="P10" t="n">
-        <v>5.219128521481942</v>
+        <v>1.158288125185018</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.94</v>
+        <v>1.477151332872959</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02712682543316047</v>
+        <v>0.4294047168429331</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160865364036006</v>
+        <v>-0.08237290273375519</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48195026311239</v>
+        <v>0.4267955556327421</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4295915808765946</v>
+        <v>4.474347154017857</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08941709567383782</v>
+        <v>4.744472911127402</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4276071820917159</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4.463381747207493</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>4.716982645215031</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>5.034019748827397</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="11">
@@ -1336,81 +1204,68 @@
       <c r="B11" t="n">
         <v>9043597</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C11" t="n">
+        <v>16652</v>
       </c>
       <c r="D11" t="n">
-        <v>16652</v>
+        <v>4112</v>
       </c>
       <c r="E11" t="n">
-        <v>4112</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
         <v>4111</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G11" s="1" t="n">
+        <v>41640</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>41640</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>46238</v>
+        <v>2.195</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7.497826562880078</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19.1775</v>
       </c>
       <c r="L11" t="n">
-        <v>2.195</v>
+        <v>2.204850111028867</v>
       </c>
       <c r="M11" t="n">
-        <v>7.497826562880078</v>
+        <v>7.670499750850943</v>
       </c>
       <c r="N11" t="n">
-        <v>19.1775</v>
+        <v>16.78594914040094</v>
       </c>
       <c r="O11" t="n">
-        <v>2.365562336565191</v>
+        <v>0.1726731879708652</v>
       </c>
       <c r="P11" t="n">
-        <v>7.714007674049111</v>
+        <v>0.9165877355586763</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.28491592512375</v>
+        <v>1.199636255742461</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2161811111690331</v>
+        <v>0.8290078136337993</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9634700656381733</v>
+        <v>0.6529409411716278</v>
       </c>
       <c r="T11" t="n">
-        <v>1.343175418165205</v>
+        <v>0.8273488400014355</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907299120879707</v>
+        <v>5.13413027933809</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5649194293213557</v>
+        <v>5.354445522617185</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7883990835444079</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5.148394978812007</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>5.364282616906164</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.717378126389128</v>
+        <v>5.693073142536776</v>
       </c>
     </row>
     <row r="12">
@@ -1422,81 +1277,68 @@
       <c r="B12" t="n">
         <v>9042214</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C12" t="n">
+        <v>16652</v>
       </c>
       <c r="D12" t="n">
-        <v>16652</v>
+        <v>6447</v>
       </c>
       <c r="E12" t="n">
-        <v>6447</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
         <v>6446</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G12" s="1" t="n">
+        <v>39083</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>39083</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>46238</v>
+        <v>1.54</v>
+      </c>
+      <c r="J12" t="n">
+        <v>9.619540283379875</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16.215</v>
       </c>
       <c r="L12" t="n">
-        <v>1.54</v>
+        <v>2.858992857142857</v>
       </c>
       <c r="M12" t="n">
-        <v>9.619540283379875</v>
+        <v>10.03382708162889</v>
       </c>
       <c r="N12" t="n">
-        <v>16.215</v>
+        <v>16.21</v>
       </c>
       <c r="O12" t="n">
-        <v>2.94898927519542</v>
+        <v>0.4142867982490123</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01675651933839</v>
+        <v>1.696011757032605</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.13</v>
+        <v>2.155382221181184</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3972162359585186</v>
+        <v>0.8231633382529105</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683682222863671</v>
+        <v>0.6483807624694042</v>
       </c>
       <c r="T12" t="n">
-        <v>2.138509287101883</v>
+        <v>0.8113956925957926</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253476307668026</v>
+        <v>7.81859874726753</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6538643617691298</v>
+        <v>8.28583178822227</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135394599631032</v>
-      </c>
-      <c r="X12" t="n">
-        <v>7.827541425908806</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>8.272883015002295</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>8.843579048263145</v>
+        <v>8.85941322011322</v>
       </c>
     </row>
     <row r="13">
@@ -1508,81 +1350,68 @@
       <c r="B13" t="n">
         <v>9043425</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C13" t="n">
+        <v>16652</v>
       </c>
       <c r="D13" t="n">
-        <v>16652</v>
+        <v>14034</v>
       </c>
       <c r="E13" t="n">
-        <v>14034</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
         <v>14033</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G13" s="1" t="n">
+        <v>30682</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>30682</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>46238</v>
+        <v>0.26</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.134611807881422</v>
+      </c>
+      <c r="K13" t="n">
+        <v>34.0025</v>
       </c>
       <c r="L13" t="n">
-        <v>0.26</v>
+        <v>0.91</v>
       </c>
       <c r="M13" t="n">
-        <v>8.134611807881422</v>
+        <v>8.206572818477236</v>
       </c>
       <c r="N13" t="n">
-        <v>34.0025</v>
+        <v>14.32</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8778757365545877</v>
+        <v>0.07196101059581282</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211891129130818</v>
+        <v>1.760477911476969</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.64109372411599</v>
+        <v>2.285669248034841</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0772793212493936</v>
+        <v>0.7807474435102667</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786859542982717</v>
+        <v>0.5649661550891822</v>
       </c>
       <c r="T13" t="n">
-        <v>2.321874367784248</v>
+        <v>0.7803809454177161</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7762522116689691</v>
+        <v>6.321136959128066</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5510750844921338</v>
+        <v>6.521854043191349</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7760410260374765</v>
-      </c>
-      <c r="X13" t="n">
-        <v>6.451617700269322</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>6.615536371713238</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.773556308194289</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="14">
@@ -1594,81 +1423,68 @@
       <c r="B14" t="n">
         <v>9044756</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C14" t="n">
+        <v>16652</v>
       </c>
       <c r="D14" t="n">
-        <v>16652</v>
+        <v>3099</v>
       </c>
       <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
         <v>3099</v>
       </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3099</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G14" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>46156</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>42370</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>46156</v>
+        <v>3.305</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.96388189738625</v>
+      </c>
+      <c r="K14" t="n">
+        <v>30.745</v>
       </c>
       <c r="L14" t="n">
-        <v>3.305</v>
+        <v>4.682413027387121</v>
       </c>
       <c r="M14" t="n">
-        <v>11.96388189738625</v>
+        <v>11.82960861990874</v>
       </c>
       <c r="N14" t="n">
-        <v>30.745</v>
+        <v>21.32952932657494</v>
       </c>
       <c r="O14" t="n">
-        <v>4.975807364456732</v>
+        <v>-0.1342732774775101</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83379077686753</v>
+        <v>2.05475332810729</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.27195770556229</v>
+        <v>2.70096157985602</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1300911205187242</v>
+        <v>0.7944343080616713</v>
       </c>
       <c r="S14" t="n">
-        <v>2.042973450164269</v>
+        <v>0.6086346975071124</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65876393855271</v>
+        <v>0.7858805126025762</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009612127948786</v>
+        <v>8.33805916315718</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207679219620057</v>
+        <v>8.572208431333483</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7923691355419947</v>
-      </c>
-      <c r="X14" t="n">
-        <v>8.480440672056586</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>8.931262274532168</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>9.854705827971273</v>
+        <v>9.320573452893479</v>
       </c>
     </row>
     <row r="15">
@@ -1680,81 +1496,68 @@
       <c r="B15" t="n">
         <v>9053555</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C15" t="n">
+        <v>16652</v>
       </c>
       <c r="D15" t="n">
-        <v>16652</v>
+        <v>9797</v>
       </c>
       <c r="E15" t="n">
-        <v>9797</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
         <v>9796</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G15" s="1" t="n">
+        <v>35804</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>35804</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>46238</v>
+        <v>0.26</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.410231046685722</v>
+      </c>
+      <c r="K15" t="n">
+        <v>131.9</v>
       </c>
       <c r="L15" t="n">
-        <v>0.26</v>
+        <v>0.5533496846531183</v>
       </c>
       <c r="M15" t="n">
-        <v>8.410231046685722</v>
+        <v>8.666458280116437</v>
       </c>
       <c r="N15" t="n">
-        <v>131.9</v>
+        <v>131.7868211440985</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5804528488899593</v>
+        <v>0.2562272334307154</v>
       </c>
       <c r="P15" t="n">
-        <v>9.377474681304339</v>
+        <v>3.536323509536679</v>
       </c>
       <c r="Q15" t="n">
-        <v>119.6249412815277</v>
+        <v>11.06742783691293</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9672436346186157</v>
+        <v>0.04975418409864492</v>
       </c>
       <c r="S15" t="n">
-        <v>4.182807358680301</v>
+        <v>-0.5968032416521016</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62297588456514</v>
+        <v>0.03299078086638241</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03405679618924165</v>
+        <v>11.47827512622279</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7611351341083314</v>
+        <v>11.88722968461222</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02212204471794355</v>
-      </c>
-      <c r="X15" t="n">
-        <v>11.48177075474107</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>11.90242513707105</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>12.24842507881084</v>
+        <v>12.2288503999256</v>
       </c>
     </row>
     <row r="16">
@@ -1766,81 +1569,68 @@
       <c r="B16" t="n">
         <v>9037610</v>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C16" t="n">
+        <v>16652</v>
       </c>
       <c r="D16" t="n">
-        <v>16652</v>
+        <v>2305</v>
       </c>
       <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
         <v>2305</v>
       </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2305</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G16" s="1" t="n">
+        <v>43252</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46203</v>
       </c>
       <c r="I16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>43252</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>46203</v>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.583133405639913</v>
+      </c>
+      <c r="K16" t="n">
+        <v>12.23</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>1.395549592894153</v>
       </c>
       <c r="M16" t="n">
-        <v>6.583133405639913</v>
+        <v>6.955433537930599</v>
       </c>
       <c r="N16" t="n">
-        <v>12.23</v>
+        <v>12.15738414192614</v>
       </c>
       <c r="O16" t="n">
-        <v>1.467998349796847</v>
+        <v>0.3723001322906852</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927511842767152</v>
+        <v>2.040529191829841</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.11960615380856</v>
+        <v>2.579631571111889</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443784371272393</v>
+        <v>0.5181594635390239</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971851086623644</v>
+        <v>0.01523337511429768</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479796253308504</v>
+        <v>0.5148515996556228</v>
       </c>
       <c r="U16" t="n">
-        <v>0.533512878767687</v>
+        <v>3.386460613131638</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08998206134685227</v>
+        <v>4.710738475096667</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283743247183654</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.46199237455926</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>4.659597346823183</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.955987477451191</v>
+        <v>5.971203217970821</v>
       </c>
     </row>
     <row r="17">
@@ -1852,81 +1642,68 @@
       <c r="B17" t="n">
         <v>9037738</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C17" t="n">
+        <v>16652</v>
       </c>
       <c r="D17" t="n">
-        <v>16652</v>
+        <v>3200</v>
       </c>
       <c r="E17" t="n">
-        <v>3200</v>
+        <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
         <v>3199</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G17" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>42370</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>46238</v>
+        <v>1.81</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.505378243201001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18.4925</v>
       </c>
       <c r="L17" t="n">
-        <v>1.81</v>
+        <v>1.826106587712805</v>
       </c>
       <c r="M17" t="n">
-        <v>6.505378243201001</v>
+        <v>6.70115201854554</v>
       </c>
       <c r="N17" t="n">
-        <v>18.4925</v>
+        <v>14.92774999999984</v>
       </c>
       <c r="O17" t="n">
-        <v>1.923435659174772</v>
+        <v>0.1957737753445393</v>
       </c>
       <c r="P17" t="n">
-        <v>6.730766586273819</v>
+        <v>1.097990660379317</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.28173148390984</v>
+        <v>1.488328424915735</v>
       </c>
       <c r="R17" t="n">
-        <v>0.225388343072818</v>
+        <v>0.6000048356663508</v>
       </c>
       <c r="S17" t="n">
-        <v>1.089059679961258</v>
+        <v>0.2156731215955732</v>
       </c>
       <c r="T17" t="n">
-        <v>1.47862775726344</v>
+        <v>0.5970419244941374</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6071369822113528</v>
+        <v>4.44</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2258640160580968</v>
+        <v>5.760416713789708</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036247712056213</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.553891627231145</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>5.724578393091734</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.57838991195923</v>
+        <v>6.452158261188455</v>
       </c>
     </row>
     <row r="18">
@@ -1938,81 +1715,68 @@
       <c r="B18" t="n">
         <v>9043370</v>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>histograma_cdf_mensual_optimizado</t>
-        </is>
+      <c r="C18" t="n">
+        <v>16652</v>
       </c>
       <c r="D18" t="n">
-        <v>16652</v>
+        <v>7154</v>
       </c>
       <c r="E18" t="n">
-        <v>7154</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
         <v>7153</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
-        </is>
+      <c r="G18" s="1" t="n">
+        <v>37987</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46238</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>37987</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>46238</v>
+        <v>0.04</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10.38065077589822</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24.5875</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04</v>
+        <v>4.73</v>
       </c>
       <c r="M18" t="n">
-        <v>10.38065077589822</v>
+        <v>11.16388384523434</v>
       </c>
       <c r="N18" t="n">
-        <v>24.5875</v>
+        <v>17.53862298528381</v>
       </c>
       <c r="O18" t="n">
-        <v>4.811036695388214</v>
+        <v>0.783233069336113</v>
       </c>
       <c r="P18" t="n">
-        <v>11.17040274555884</v>
+        <v>2.033278928483426</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.5154399668629</v>
+        <v>2.751839974059838</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7897519696606117</v>
+        <v>0.7262344971135102</v>
       </c>
       <c r="S18" t="n">
-        <v>2.035567518892357</v>
+        <v>0.4689285294646608</v>
       </c>
       <c r="T18" t="n">
-        <v>2.755944403040442</v>
+        <v>0.6791238760217631</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252161039056807</v>
+        <v>7.98408425925926</v>
       </c>
       <c r="V18" t="n">
-        <v>0.467343138799824</v>
+        <v>8.030569217931692</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6764658353038074</v>
-      </c>
-      <c r="X18" t="n">
-        <v>8.094495847291423</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>8.156417798751182</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8.233989985488543</v>
+        <v>8.106069911447895</v>
       </c>
     </row>
   </sheetData>
@@ -2090,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.094495847291423</v>
+        <v>7.98408425925926</v>
       </c>
       <c r="G2" t="n">
-        <v>8.156417798751182</v>
+        <v>8.030569217931692</v>
       </c>
       <c r="H2" t="n">
-        <v>8.233989985488543</v>
+        <v>8.106069911447895</v>
       </c>
     </row>
     <row r="3">
@@ -2118,13 +1882,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.971933596703742</v>
+        <v>5.99</v>
       </c>
       <c r="G3" t="n">
-        <v>6.13724344826476</v>
+        <v>6.149606686868074</v>
       </c>
       <c r="H3" t="n">
-        <v>6.238725709542586</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="4">
@@ -2146,13 +1910,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.463381747207493</v>
+        <v>4.474347154017857</v>
       </c>
       <c r="G4" t="n">
-        <v>4.716982645215031</v>
+        <v>4.744472911127402</v>
       </c>
       <c r="H4" t="n">
-        <v>5.034019748827397</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="5">
@@ -2174,13 +1938,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.48177075474107</v>
+        <v>11.47827512622279</v>
       </c>
       <c r="G5" t="n">
-        <v>11.90242513707105</v>
+        <v>11.88722968461222</v>
       </c>
       <c r="H5" t="n">
-        <v>12.24842507881084</v>
+        <v>12.2288503999256</v>
       </c>
     </row>
     <row r="6">
@@ -2202,13 +1966,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>95.87613444605</v>
+        <v>109.97</v>
       </c>
       <c r="G6" t="n">
-        <v>105.2705788003175</v>
+        <v>111.2362235153552</v>
       </c>
       <c r="H6" t="n">
-        <v>113.5603298057117</v>
+        <v>113.6596310966422</v>
       </c>
     </row>
     <row r="7">
@@ -2230,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.480440672056586</v>
+        <v>8.33805916315718</v>
       </c>
       <c r="G7" t="n">
-        <v>8.931262274532168</v>
+        <v>8.572208431333483</v>
       </c>
       <c r="H7" t="n">
-        <v>9.854705827971273</v>
+        <v>9.320573452893479</v>
       </c>
     </row>
     <row r="8">
@@ -2258,13 +2022,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.827541425908806</v>
+        <v>7.81859874726753</v>
       </c>
       <c r="G8" t="n">
-        <v>8.272883015002295</v>
+        <v>8.28583178822227</v>
       </c>
       <c r="H8" t="n">
-        <v>8.843579048263145</v>
+        <v>8.85941322011322</v>
       </c>
     </row>
     <row r="9">
@@ -2286,13 +2050,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.148394978812007</v>
+        <v>5.13413027933809</v>
       </c>
       <c r="G9" t="n">
-        <v>5.364282616906164</v>
+        <v>5.354445522617186</v>
       </c>
       <c r="H9" t="n">
-        <v>5.717378126389128</v>
+        <v>5.693073142536776</v>
       </c>
     </row>
     <row r="10">
@@ -2314,13 +2078,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7516263767111</v>
+        <v>5.778806226576279</v>
       </c>
       <c r="G10" t="n">
-        <v>6.148325690464379</v>
+        <v>6.160113821780614</v>
       </c>
       <c r="H10" t="n">
-        <v>6.360177905602171</v>
+        <v>6.370959240362812</v>
       </c>
     </row>
     <row r="11">
@@ -2342,13 +2106,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.46199237455926</v>
+        <v>3.386460613131638</v>
       </c>
       <c r="G11" t="n">
-        <v>4.659597346823184</v>
+        <v>4.710738475096667</v>
       </c>
       <c r="H11" t="n">
-        <v>5.955987477451191</v>
+        <v>5.971203217970821</v>
       </c>
     </row>
     <row r="12">
@@ -2370,13 +2134,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.451617700269322</v>
+        <v>6.321136959128066</v>
       </c>
       <c r="G12" t="n">
-        <v>6.615536371713238</v>
+        <v>6.521854043191349</v>
       </c>
       <c r="H12" t="n">
-        <v>6.773556308194289</v>
+        <v>6.72</v>
       </c>
     </row>
     <row r="13">
@@ -2398,13 +2162,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.97983771132594</v>
+        <v>9.9275</v>
       </c>
       <c r="G13" t="n">
-        <v>10.45404182878192</v>
+        <v>10.44914356732097</v>
       </c>
       <c r="H13" t="n">
-        <v>11.09200246171443</v>
+        <v>11.09672653698335</v>
       </c>
     </row>
     <row r="14">
@@ -2426,13 +2190,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.27246912544592</v>
+        <v>6.24</v>
       </c>
       <c r="G14" t="n">
-        <v>6.804012839769075</v>
+        <v>6.825976473196579</v>
       </c>
       <c r="H14" t="n">
-        <v>7.132008751417632</v>
+        <v>7.205024437910757</v>
       </c>
     </row>
     <row r="15">
@@ -2454,13 +2218,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.813301189812796</v>
+        <v>6.67</v>
       </c>
       <c r="G15" t="n">
-        <v>7.034254552129411</v>
+        <v>6.93961567764318</v>
       </c>
       <c r="H15" t="n">
-        <v>7.223379445853321</v>
+        <v>7.18</v>
       </c>
     </row>
     <row r="16">
@@ -2482,13 +2246,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.553891627231145</v>
+        <v>4.44</v>
       </c>
       <c r="G16" t="n">
-        <v>5.724578393091734</v>
+        <v>5.760416713789708</v>
       </c>
       <c r="H16" t="n">
-        <v>6.57838991195923</v>
+        <v>6.452158261188455</v>
       </c>
     </row>
     <row r="17">
@@ -2510,13 +2274,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.671984847195314</v>
+        <v>4.577857142857143</v>
       </c>
       <c r="G17" t="n">
-        <v>4.929646257864516</v>
+        <v>4.865434176627113</v>
       </c>
       <c r="H17" t="n">
-        <v>5.409095512259854</v>
+        <v>5.361428571428573</v>
       </c>
     </row>
     <row r="18">
@@ -2538,13 +2302,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.094948531881759</v>
+        <v>3.106497578124999</v>
       </c>
       <c r="G18" t="n">
-        <v>3.509218087994149</v>
+        <v>3.559131656317599</v>
       </c>
       <c r="H18" t="n">
-        <v>3.720518324039409</v>
+        <v>3.767849276123047</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,105 +434,120 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>metodo_dwlt</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>n_hist_sonics</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>n_obs_nivel</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>n_fore_sonics</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>n_validacion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meses_curva_ok</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n_meses_curva_ok</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>fecha_inicio_validacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>fecha_fin_validacion</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>nivel_obs_min</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>nivel_obs_prom</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>nivel_obs_max</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>nivel_dwlt_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>nivel_dwlt_prom</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nivel_dwlt_max</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>bias_m</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>mae_m</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rmse_m</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>r_pearson</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>nse</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>kge_2009</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>forecast_nivel_min_m</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>forecast_nivel_prom_m</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>forecast_nivel_max_m</t>
         </is>
@@ -547,68 +562,81 @@
       <c r="B2" t="n">
         <v>9038134</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>16652</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>9957</v>
       </c>
-      <c r="E2" t="n">
-        <v>10</v>
-      </c>
       <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9956</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>1.78</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>102.9193027655015</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>118.97</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.846246418338109</v>
-      </c>
-      <c r="M2" t="n">
-        <v>102.9096886676712</v>
-      </c>
-      <c r="N2" t="n">
-        <v>118.8938450398262</v>
-      </c>
       <c r="O2" t="n">
-        <v>-0.009614097830322561</v>
+        <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>17.72126574414639</v>
+        <v>95.33228138807371</v>
       </c>
       <c r="Q2" t="n">
-        <v>36.07130049628272</v>
+        <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1289586119157143</v>
+        <v>-7.587021377427829</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7373733225377321</v>
+        <v>22.63546395925188</v>
       </c>
       <c r="T2" t="n">
-        <v>0.128954398599308</v>
+        <v>31.50605303978796</v>
       </c>
       <c r="U2" t="n">
-        <v>109.97</v>
+        <v>0.135872469013921</v>
       </c>
       <c r="V2" t="n">
-        <v>111.2362235153552</v>
+        <v>-0.325432292243546</v>
       </c>
       <c r="W2" t="n">
-        <v>113.6596310966422</v>
+        <v>0.06575096893762122</v>
+      </c>
+      <c r="X2" t="n">
+        <v>95.87613444605</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>105.2705788003175</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>113.5603298057117</v>
       </c>
     </row>
     <row r="3">
@@ -620,68 +648,81 @@
       <c r="B3" t="n">
         <v>9038269</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>16652</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>14535</v>
       </c>
-      <c r="E3" t="n">
-        <v>10</v>
-      </c>
       <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14534</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>30317</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="K3" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>0.01</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>4.907021982936563</v>
-      </c>
-      <c r="K3" t="n">
-        <v>11.07</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.962746029544062</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05572404660749876</v>
+        <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>1.350996637610684</v>
+        <v>4.955666697532456</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.725673188965019</v>
+        <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7795292564500442</v>
+        <v>0.04864471459589358</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5664946459514866</v>
+        <v>1.354207997255708</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7784480230371622</v>
+        <v>1.729961778437443</v>
       </c>
       <c r="U3" t="n">
-        <v>3.106497578124999</v>
+        <v>0.7784487092992268</v>
       </c>
       <c r="V3" t="n">
-        <v>3.559131656317599</v>
+        <v>0.5643373004804404</v>
       </c>
       <c r="W3" t="n">
-        <v>3.767849276123047</v>
+        <v>0.7774711695412868</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.094948531881759</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.509218087994149</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.720518324039409</v>
       </c>
     </row>
     <row r="4">
@@ -693,68 +734,81 @@
       <c r="B4" t="n">
         <v>9039635</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>16652</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>10217</v>
       </c>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
       <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10216</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>35065</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>6.919731303837119</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>12.93</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M4" t="n">
-        <v>7.250304954826767</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12.73</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.3305736509896475</v>
+        <v>0.5041527473520986</v>
       </c>
       <c r="P4" t="n">
-        <v>1.294961596766595</v>
+        <v>7.238244863604294</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68490109483858</v>
+        <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.867434132652752</v>
+        <v>0.3185135597671748</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7369548083267738</v>
+        <v>1.290174170464782</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8471030107239369</v>
+        <v>1.677634763737211</v>
       </c>
       <c r="U4" t="n">
-        <v>4.577857142857143</v>
+        <v>0.8680638408964237</v>
       </c>
       <c r="V4" t="n">
-        <v>4.865434176627113</v>
+        <v>0.7392187417451412</v>
       </c>
       <c r="W4" t="n">
-        <v>5.361428571428573</v>
+        <v>0.8471996502193058</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.671984847195314</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4.929646257864516</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.409095512259854</v>
       </c>
     </row>
     <row r="5">
@@ -766,68 +820,81 @@
       <c r="B5" t="n">
         <v>9032282</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>16652</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8828</v>
       </c>
-      <c r="E5" t="n">
-        <v>10</v>
-      </c>
       <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8827</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>36892</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>1.52</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>6.729641724255126</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>10.6125</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.616683937823834</v>
-      </c>
-      <c r="M5" t="n">
-        <v>7.018568133838615</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.19100035038542</v>
-      </c>
       <c r="O5" t="n">
-        <v>0.2889264095834884</v>
+        <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>1.482613296405483</v>
+        <v>6.922251982269803</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.911407989081738</v>
+        <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3048464079305496</v>
+        <v>0.1926102580146766</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1982627741300567</v>
+        <v>1.446658943345836</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2802549803328918</v>
+        <v>1.844914671307581</v>
       </c>
       <c r="U5" t="n">
-        <v>6.67</v>
+        <v>0.2963341860774601</v>
       </c>
       <c r="V5" t="n">
-        <v>6.93961567764318</v>
+        <v>-0.1163434864810704</v>
       </c>
       <c r="W5" t="n">
-        <v>7.18</v>
+        <v>0.2473681852403379</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6.813301189812796</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.034254552129413</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>7.223379445853321</v>
       </c>
     </row>
     <row r="6">
@@ -839,68 +906,81 @@
       <c r="B6" t="n">
         <v>9036028</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>16652</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>14190</v>
       </c>
-      <c r="E6" t="n">
-        <v>10</v>
-      </c>
       <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14189</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>31048</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>1.025</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>5.582744203256043</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.01</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.345</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5.588887180127378</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0061429768713352</v>
+        <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>1.156166844397233</v>
+        <v>5.585585018220065</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.494446791103823</v>
+        <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5089534397019244</v>
+        <v>0.002840814964022571</v>
       </c>
       <c r="S6" t="n">
-        <v>0.07468413857457523</v>
+        <v>1.162756957105505</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5050904206512818</v>
+        <v>1.501002611837489</v>
       </c>
       <c r="U6" t="n">
-        <v>5.99</v>
+        <v>0.5076459723344227</v>
       </c>
       <c r="V6" t="n">
-        <v>6.149606686868073</v>
+        <v>0.06654800348817924</v>
       </c>
       <c r="W6" t="n">
-        <v>6.22</v>
+        <v>0.5045673123816072</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.971933596703742</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.13724344826476</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6.238725709542586</v>
       </c>
     </row>
     <row r="7">
@@ -912,68 +992,81 @@
       <c r="B7" t="n">
         <v>9040454</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>16652</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>8988</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
       <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8987</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>0.16</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>7.880510181373095</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>15.14</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.6453438395415473</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8.118590391002964</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14.26345655220743</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.2380802096298701</v>
+        <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>1.443930109169861</v>
+        <v>8.092733281453045</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.823434294283678</v>
+        <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8093447975663098</v>
+        <v>0.2122231000799516</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6299189843988305</v>
+        <v>1.421045293572391</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7996887430616872</v>
+        <v>1.793485647513805</v>
       </c>
       <c r="U7" t="n">
-        <v>5.778806226576279</v>
+        <v>0.8127966556249928</v>
       </c>
       <c r="V7" t="n">
-        <v>6.160113821780614</v>
+        <v>0.6419758014149836</v>
       </c>
       <c r="W7" t="n">
-        <v>6.370959240362812</v>
+        <v>0.7982017156770616</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.7516263767111</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.148325690464379</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>6.360177905602171</v>
       </c>
     </row>
     <row r="8">
@@ -985,68 +1078,81 @@
       <c r="B8" t="n">
         <v>9040439</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>16652</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>13853</v>
       </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
       <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13852</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>31778</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>0.06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>7.616930948599481</v>
-      </c>
-      <c r="K8" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7.682928815841117</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06599786724163774</v>
+        <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>1.477577365700045</v>
+        <v>7.660260953499951</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.920084194344837</v>
+        <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7617097241109143</v>
+        <v>0.04333000490047045</v>
       </c>
       <c r="S8" t="n">
-        <v>0.536186454860199</v>
+        <v>1.502824612746873</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7596970591686734</v>
+        <v>1.962141263783013</v>
       </c>
       <c r="U8" t="n">
-        <v>6.24</v>
+        <v>0.7529676822909155</v>
       </c>
       <c r="V8" t="n">
-        <v>6.825976473196578</v>
+        <v>0.5156454047052352</v>
       </c>
       <c r="W8" t="n">
-        <v>7.205024437910757</v>
+        <v>0.7520092109960104</v>
+      </c>
+      <c r="X8" t="n">
+        <v>6.27246912544592</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.804012839769075</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>7.132008751417632</v>
       </c>
     </row>
     <row r="9">
@@ -1058,68 +1164,81 @@
       <c r="B9" t="n">
         <v>9042153</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>16652</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>3737</v>
       </c>
-      <c r="E9" t="n">
-        <v>10</v>
-      </c>
       <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>3737</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>37257</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="K9" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>3.7875</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>10.30505953973775</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>39.075</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>4.255000000000001</v>
       </c>
-      <c r="M9" t="n">
-        <v>10.62146893509687</v>
-      </c>
-      <c r="N9" t="n">
-        <v>14.31645908761767</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3164093953591094</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.051523643827713</v>
+        <v>10.74327467642422</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.697439998101684</v>
+        <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3564237390149727</v>
+        <v>0.4382151366864612</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1198896736162036</v>
+        <v>2.151393985812674</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3355371108595818</v>
+        <v>2.874483279762739</v>
       </c>
       <c r="U9" t="n">
-        <v>9.9275</v>
+        <v>0.3307111867665943</v>
       </c>
       <c r="V9" t="n">
-        <v>10.44914356732097</v>
+        <v>-0.2717191984699869</v>
       </c>
       <c r="W9" t="n">
-        <v>11.09672653698335</v>
+        <v>0.3250253771885661</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.97983771132594</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>10.45404182878192</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>11.09200246171443</v>
       </c>
     </row>
     <row r="10">
@@ -1131,68 +1250,81 @@
       <c r="B10" t="n">
         <v>9040208</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>16652</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>13793</v>
       </c>
-      <c r="E10" t="n">
-        <v>10</v>
-      </c>
       <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13793</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>31413</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="K10" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>0.4375</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>5.246255346915103</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>10.15</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.8401943005181348</v>
-      </c>
-      <c r="M10" t="n">
-        <v>5.220890837973054</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
+        <v>0.4490779286658197</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.219128521481942</v>
+      </c>
+      <c r="Q10" t="n">
         <v>9.94</v>
       </c>
-      <c r="O10" t="n">
-        <v>-0.0253645089420472</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.158288125185018</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.477151332872959</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.4294047168429331</v>
+        <v>-0.02712682543316047</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.08237290273375519</v>
+        <v>1.160865364036006</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4267955556327421</v>
+        <v>1.48195026311239</v>
       </c>
       <c r="U10" t="n">
-        <v>4.474347154017857</v>
+        <v>0.4295915808765946</v>
       </c>
       <c r="V10" t="n">
-        <v>4.744472911127402</v>
+        <v>-0.08941709567383782</v>
       </c>
       <c r="W10" t="n">
-        <v>5.04</v>
+        <v>0.4276071820917159</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.463381747207493</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.716982645215031</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5.034019748827397</v>
       </c>
     </row>
     <row r="11">
@@ -1204,68 +1336,81 @@
       <c r="B11" t="n">
         <v>9043597</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>16652</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>4112</v>
       </c>
-      <c r="E11" t="n">
-        <v>10</v>
-      </c>
       <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4111</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>41640</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="K11" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>2.195</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>7.497826562880078</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>19.1775</v>
       </c>
-      <c r="L11" t="n">
-        <v>2.204850111028867</v>
-      </c>
-      <c r="M11" t="n">
-        <v>7.670499750850943</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16.78594914040094</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.1726731879708652</v>
+        <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9165877355586763</v>
+        <v>7.714007674049111</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.199636255742461</v>
+        <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8290078136337993</v>
+        <v>0.2161811111690331</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6529409411716278</v>
+        <v>0.9634700656381733</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8273488400014355</v>
+        <v>1.343175418165205</v>
       </c>
       <c r="U11" t="n">
-        <v>5.13413027933809</v>
+        <v>0.7907299120879707</v>
       </c>
       <c r="V11" t="n">
-        <v>5.354445522617185</v>
+        <v>0.5649194293213557</v>
       </c>
       <c r="W11" t="n">
-        <v>5.693073142536776</v>
+        <v>0.7883990835444079</v>
+      </c>
+      <c r="X11" t="n">
+        <v>5.148394978812007</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>5.364282616906164</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.717378126389128</v>
       </c>
     </row>
     <row r="12">
@@ -1277,68 +1422,81 @@
       <c r="B12" t="n">
         <v>9042214</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>16652</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>6447</v>
       </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
       <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6446</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>39083</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="K12" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>1.54</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>9.619540283379875</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>16.215</v>
       </c>
-      <c r="L12" t="n">
-        <v>2.858992857142857</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10.03382708162889</v>
-      </c>
-      <c r="N12" t="n">
-        <v>16.21</v>
-      </c>
       <c r="O12" t="n">
-        <v>0.4142867982490123</v>
+        <v>2.94898927519542</v>
       </c>
       <c r="P12" t="n">
-        <v>1.696011757032605</v>
+        <v>10.01675651933839</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.155382221181184</v>
+        <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8231633382529105</v>
+        <v>0.3972162359585186</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6483807624694042</v>
+        <v>1.683682222863671</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8113956925957926</v>
+        <v>2.138509287101883</v>
       </c>
       <c r="U12" t="n">
-        <v>7.81859874726753</v>
+        <v>0.8253476307668026</v>
       </c>
       <c r="V12" t="n">
-        <v>8.28583178822227</v>
+        <v>0.6538643617691298</v>
       </c>
       <c r="W12" t="n">
-        <v>8.85941322011322</v>
+        <v>0.8135394599631032</v>
+      </c>
+      <c r="X12" t="n">
+        <v>7.827541425908806</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.272883015002295</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8.843579048263145</v>
       </c>
     </row>
     <row r="13">
@@ -1350,68 +1508,81 @@
       <c r="B13" t="n">
         <v>9043425</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>16652</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>14034</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
       <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14033</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>30682</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="K13" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>0.26</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>8.134611807881422</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>34.0025</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="M13" t="n">
-        <v>8.206572818477236</v>
-      </c>
-      <c r="N13" t="n">
-        <v>14.32</v>
-      </c>
       <c r="O13" t="n">
-        <v>0.07196101059581282</v>
+        <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>1.760477911476969</v>
+        <v>8.211891129130818</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.285669248034841</v>
+        <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7807474435102667</v>
+        <v>0.0772793212493936</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5649661550891822</v>
+        <v>1.786859542982717</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7803809454177161</v>
+        <v>2.321874367784248</v>
       </c>
       <c r="U13" t="n">
-        <v>6.321136959128066</v>
+        <v>0.7762522116689691</v>
       </c>
       <c r="V13" t="n">
-        <v>6.521854043191349</v>
+        <v>0.5510750844921338</v>
       </c>
       <c r="W13" t="n">
-        <v>6.72</v>
+        <v>0.7760410260374765</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.451617700269322</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>6.615536371713238</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.773556308194289</v>
       </c>
     </row>
     <row r="14">
@@ -1423,68 +1594,81 @@
       <c r="B14" t="n">
         <v>9044756</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>16652</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>3099</v>
       </c>
-      <c r="E14" t="n">
-        <v>10</v>
-      </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>3099</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="K14" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>3.305</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>11.96388189738625</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>30.745</v>
       </c>
-      <c r="L14" t="n">
-        <v>4.682413027387121</v>
-      </c>
-      <c r="M14" t="n">
-        <v>11.82960861990874</v>
-      </c>
-      <c r="N14" t="n">
-        <v>21.32952932657494</v>
-      </c>
       <c r="O14" t="n">
-        <v>-0.1342732774775101</v>
+        <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05475332810729</v>
+        <v>11.83379077686753</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.70096157985602</v>
+        <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7944343080616713</v>
+        <v>-0.1300911205187242</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6086346975071124</v>
+        <v>2.042973450164269</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7858805126025762</v>
+        <v>2.65876393855271</v>
       </c>
       <c r="U14" t="n">
-        <v>8.33805916315718</v>
+        <v>0.8009612127948786</v>
       </c>
       <c r="V14" t="n">
-        <v>8.572208431333483</v>
+        <v>0.6207679219620057</v>
       </c>
       <c r="W14" t="n">
-        <v>9.320573452893479</v>
+        <v>0.7923691355419947</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8.480440672056586</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.931262274532168</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.854705827971273</v>
       </c>
     </row>
     <row r="15">
@@ -1496,68 +1680,81 @@
       <c r="B15" t="n">
         <v>9053555</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>16652</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>9797</v>
       </c>
-      <c r="E15" t="n">
-        <v>10</v>
-      </c>
       <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9796</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>35804</v>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>0.26</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>8.410231046685722</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>131.9</v>
       </c>
-      <c r="L15" t="n">
-        <v>0.5533496846531183</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8.666458280116437</v>
-      </c>
-      <c r="N15" t="n">
-        <v>131.7868211440985</v>
-      </c>
       <c r="O15" t="n">
-        <v>0.2562272334307154</v>
+        <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>3.536323509536679</v>
+        <v>9.377474681304339</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.06742783691293</v>
+        <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04975418409864492</v>
+        <v>0.9672436346186157</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5968032416521016</v>
+        <v>4.182807358680301</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03299078086638241</v>
+        <v>11.62297588456514</v>
       </c>
       <c r="U15" t="n">
-        <v>11.47827512622279</v>
+        <v>0.03405679618924165</v>
       </c>
       <c r="V15" t="n">
-        <v>11.88722968461222</v>
+        <v>-0.7611351341083314</v>
       </c>
       <c r="W15" t="n">
-        <v>12.2288503999256</v>
+        <v>0.02212204471794355</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.48177075474107</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.90242513707105</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>12.24842507881084</v>
       </c>
     </row>
     <row r="16">
@@ -1569,68 +1766,81 @@
       <c r="B16" t="n">
         <v>9037610</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>16652</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>2305</v>
       </c>
-      <c r="E16" t="n">
-        <v>10</v>
-      </c>
       <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>2305</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>43252</v>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>6.583133405639913</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>12.23</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.395549592894153</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.955433537930599</v>
-      </c>
-      <c r="N16" t="n">
-        <v>12.15738414192614</v>
-      </c>
       <c r="O16" t="n">
-        <v>0.3723001322906852</v>
+        <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>2.040529191829841</v>
+        <v>6.927511842767152</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.579631571111889</v>
+        <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5181594635390239</v>
+        <v>0.3443784371272393</v>
       </c>
       <c r="S16" t="n">
-        <v>0.01523337511429768</v>
+        <v>1.971851086623644</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5148515996556228</v>
+        <v>2.479796253308504</v>
       </c>
       <c r="U16" t="n">
-        <v>3.386460613131638</v>
+        <v>0.533512878767687</v>
       </c>
       <c r="V16" t="n">
-        <v>4.710738475096667</v>
+        <v>0.08998206134685227</v>
       </c>
       <c r="W16" t="n">
-        <v>5.971203217970821</v>
+        <v>0.5283743247183654</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.46199237455926</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.659597346823183</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.955987477451191</v>
       </c>
     </row>
     <row r="17">
@@ -1642,68 +1852,81 @@
       <c r="B17" t="n">
         <v>9037738</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>16652</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>3200</v>
       </c>
-      <c r="E17" t="n">
-        <v>10</v>
-      </c>
       <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3199</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="K17" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>1.81</v>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>6.505378243201001</v>
       </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>18.4925</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.826106587712805</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.70115201854554</v>
-      </c>
-      <c r="N17" t="n">
-        <v>14.92774999999984</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.1957737753445393</v>
+        <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>1.097990660379317</v>
+        <v>6.730766586273819</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.488328424915735</v>
+        <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6000048356663508</v>
+        <v>0.225388343072818</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2156731215955732</v>
+        <v>1.089059679961258</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5970419244941374</v>
+        <v>1.47862775726344</v>
       </c>
       <c r="U17" t="n">
-        <v>4.44</v>
+        <v>0.6071369822113528</v>
       </c>
       <c r="V17" t="n">
-        <v>5.760416713789708</v>
+        <v>0.2258640160580968</v>
       </c>
       <c r="W17" t="n">
-        <v>6.452158261188455</v>
+        <v>0.6036247712056213</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.553891627231145</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5.724578393091734</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.57838991195923</v>
       </c>
     </row>
     <row r="18">
@@ -1715,68 +1938,81 @@
       <c r="B18" t="n">
         <v>9043370</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>histograma_cdf_mensual_optimizado</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>16652</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>7154</v>
       </c>
-      <c r="E18" t="n">
-        <v>10</v>
-      </c>
       <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7153</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>37987</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="K18" s="1" t="n">
         <v>46238</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>0.04</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>10.38065077589822</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>24.5875</v>
       </c>
-      <c r="L18" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="M18" t="n">
-        <v>11.16388384523434</v>
-      </c>
-      <c r="N18" t="n">
-        <v>17.53862298528381</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.783233069336113</v>
+        <v>4.811036695388214</v>
       </c>
       <c r="P18" t="n">
-        <v>2.033278928483426</v>
+        <v>11.17040274555884</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.751839974059838</v>
+        <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7262344971135102</v>
+        <v>0.7897519696606117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4689285294646608</v>
+        <v>2.035567518892357</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6791238760217631</v>
+        <v>2.755944403040442</v>
       </c>
       <c r="U18" t="n">
-        <v>7.98408425925926</v>
+        <v>0.7252161039056807</v>
       </c>
       <c r="V18" t="n">
-        <v>8.030569217931692</v>
+        <v>0.467343138799824</v>
       </c>
       <c r="W18" t="n">
-        <v>8.106069911447895</v>
+        <v>0.6764658353038074</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8.094495847291423</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8.156417798751182</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.233989985488543</v>
       </c>
     </row>
   </sheetData>
@@ -1854,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.98408425925926</v>
+        <v>8.094495847291423</v>
       </c>
       <c r="G2" t="n">
-        <v>8.030569217931692</v>
+        <v>8.156417798751182</v>
       </c>
       <c r="H2" t="n">
-        <v>8.106069911447895</v>
+        <v>8.233989985488543</v>
       </c>
     </row>
     <row r="3">
@@ -1882,13 +2118,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.99</v>
+        <v>5.971933596703742</v>
       </c>
       <c r="G3" t="n">
-        <v>6.149606686868074</v>
+        <v>6.13724344826476</v>
       </c>
       <c r="H3" t="n">
-        <v>6.22</v>
+        <v>6.238725709542586</v>
       </c>
     </row>
     <row r="4">
@@ -1910,13 +2146,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.474347154017857</v>
+        <v>4.463381747207493</v>
       </c>
       <c r="G4" t="n">
-        <v>4.744472911127402</v>
+        <v>4.716982645215031</v>
       </c>
       <c r="H4" t="n">
-        <v>5.04</v>
+        <v>5.034019748827397</v>
       </c>
     </row>
     <row r="5">
@@ -1938,13 +2174,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.47827512622279</v>
+        <v>11.48177075474107</v>
       </c>
       <c r="G5" t="n">
-        <v>11.88722968461222</v>
+        <v>11.90242513707105</v>
       </c>
       <c r="H5" t="n">
-        <v>12.2288503999256</v>
+        <v>12.24842507881084</v>
       </c>
     </row>
     <row r="6">
@@ -1966,13 +2202,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>109.97</v>
+        <v>95.87613444605</v>
       </c>
       <c r="G6" t="n">
-        <v>111.2362235153552</v>
+        <v>105.2705788003175</v>
       </c>
       <c r="H6" t="n">
-        <v>113.6596310966422</v>
+        <v>113.5603298057117</v>
       </c>
     </row>
     <row r="7">
@@ -1994,13 +2230,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.33805916315718</v>
+        <v>8.480440672056586</v>
       </c>
       <c r="G7" t="n">
-        <v>8.572208431333483</v>
+        <v>8.931262274532168</v>
       </c>
       <c r="H7" t="n">
-        <v>9.320573452893479</v>
+        <v>9.854705827971273</v>
       </c>
     </row>
     <row r="8">
@@ -2022,13 +2258,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.81859874726753</v>
+        <v>7.827541425908806</v>
       </c>
       <c r="G8" t="n">
-        <v>8.28583178822227</v>
+        <v>8.272883015002295</v>
       </c>
       <c r="H8" t="n">
-        <v>8.85941322011322</v>
+        <v>8.843579048263145</v>
       </c>
     </row>
     <row r="9">
@@ -2050,13 +2286,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.13413027933809</v>
+        <v>5.148394978812007</v>
       </c>
       <c r="G9" t="n">
-        <v>5.354445522617186</v>
+        <v>5.364282616906164</v>
       </c>
       <c r="H9" t="n">
-        <v>5.693073142536776</v>
+        <v>5.717378126389128</v>
       </c>
     </row>
     <row r="10">
@@ -2078,13 +2314,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.778806226576279</v>
+        <v>5.7516263767111</v>
       </c>
       <c r="G10" t="n">
-        <v>6.160113821780614</v>
+        <v>6.148325690464379</v>
       </c>
       <c r="H10" t="n">
-        <v>6.370959240362812</v>
+        <v>6.360177905602171</v>
       </c>
     </row>
     <row r="11">
@@ -2106,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.386460613131638</v>
+        <v>3.46199237455926</v>
       </c>
       <c r="G11" t="n">
-        <v>4.710738475096667</v>
+        <v>4.659597346823184</v>
       </c>
       <c r="H11" t="n">
-        <v>5.971203217970821</v>
+        <v>5.955987477451191</v>
       </c>
     </row>
     <row r="12">
@@ -2134,13 +2370,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.321136959128066</v>
+        <v>6.451617700269322</v>
       </c>
       <c r="G12" t="n">
-        <v>6.521854043191349</v>
+        <v>6.615536371713238</v>
       </c>
       <c r="H12" t="n">
-        <v>6.72</v>
+        <v>6.773556308194289</v>
       </c>
     </row>
     <row r="13">
@@ -2162,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.9275</v>
+        <v>9.97983771132594</v>
       </c>
       <c r="G13" t="n">
-        <v>10.44914356732097</v>
+        <v>10.45404182878192</v>
       </c>
       <c r="H13" t="n">
-        <v>11.09672653698335</v>
+        <v>11.09200246171443</v>
       </c>
     </row>
     <row r="14">
@@ -2190,13 +2426,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.24</v>
+        <v>6.27246912544592</v>
       </c>
       <c r="G14" t="n">
-        <v>6.825976473196579</v>
+        <v>6.804012839769075</v>
       </c>
       <c r="H14" t="n">
-        <v>7.205024437910757</v>
+        <v>7.132008751417632</v>
       </c>
     </row>
     <row r="15">
@@ -2218,13 +2454,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.67</v>
+        <v>6.813301189812796</v>
       </c>
       <c r="G15" t="n">
-        <v>6.93961567764318</v>
+        <v>7.034254552129411</v>
       </c>
       <c r="H15" t="n">
-        <v>7.18</v>
+        <v>7.223379445853321</v>
       </c>
     </row>
     <row r="16">
@@ -2246,13 +2482,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.44</v>
+        <v>4.553891627231145</v>
       </c>
       <c r="G16" t="n">
-        <v>5.760416713789708</v>
+        <v>5.724578393091734</v>
       </c>
       <c r="H16" t="n">
-        <v>6.452158261188455</v>
+        <v>6.57838991195923</v>
       </c>
     </row>
     <row r="17">
@@ -2274,13 +2510,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.577857142857143</v>
+        <v>4.671984847195314</v>
       </c>
       <c r="G17" t="n">
-        <v>4.865434176627113</v>
+        <v>4.929646257864516</v>
       </c>
       <c r="H17" t="n">
-        <v>5.361428571428573</v>
+        <v>5.409095512259854</v>
       </c>
     </row>
     <row r="18">
@@ -2302,13 +2538,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.106497578124999</v>
+        <v>3.094948531881759</v>
       </c>
       <c r="G18" t="n">
-        <v>3.559131656317599</v>
+        <v>3.509218087994149</v>
       </c>
       <c r="H18" t="n">
-        <v>3.767849276123047</v>
+        <v>3.720518324039409</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E2" t="n">
+        <v>9959</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9957</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9956</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         <v>36161</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L2" t="n">
         <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>102.9193027655015</v>
+        <v>102.9095920792742</v>
       </c>
       <c r="N2" t="n">
         <v>118.97</v>
@@ -606,37 +606,37 @@
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>95.33228138807371</v>
+        <v>95.32702986779948</v>
       </c>
       <c r="Q2" t="n">
         <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.587021377427829</v>
+        <v>-7.582562211474739</v>
       </c>
       <c r="S2" t="n">
-        <v>22.63546395925188</v>
+        <v>22.64929757531536</v>
       </c>
       <c r="T2" t="n">
-        <v>31.50605303978796</v>
+        <v>31.52573995813171</v>
       </c>
       <c r="U2" t="n">
-        <v>0.135872469013921</v>
+        <v>0.135448274487471</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.325432292243546</v>
+        <v>-0.3255606565608451</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06575096893762122</v>
+        <v>0.06527282382095589</v>
       </c>
       <c r="X2" t="n">
-        <v>95.87613444605</v>
+        <v>92.31754146199668</v>
       </c>
       <c r="Y2" t="n">
-        <v>105.2705788003175</v>
+        <v>100.6190063282841</v>
       </c>
       <c r="Z2" t="n">
-        <v>113.5603298057117</v>
+        <v>107.3736001341237</v>
       </c>
     </row>
     <row r="3">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E3" t="n">
+        <v>14537</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14535</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14534</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         <v>30317</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L3" t="n">
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>4.907021982936563</v>
+        <v>4.906947884416925</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
@@ -692,37 +692,37 @@
         <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955666697532456</v>
+        <v>4.955755972935311</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04864471459589358</v>
+        <v>0.04880808851838554</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354207997255708</v>
+        <v>1.354144458388229</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729961778437443</v>
+        <v>1.729901898208585</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784487092992268</v>
+        <v>0.7784396832593301</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643373004804404</v>
+        <v>0.5643425475744006</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774711695412868</v>
+        <v>0.7774555545606983</v>
       </c>
       <c r="X3" t="n">
-        <v>3.094948531881759</v>
+        <v>3.002068576525643</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.509218087994149</v>
+        <v>3.47158846778119</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.720518324039409</v>
+        <v>3.720867493433415</v>
       </c>
     </row>
     <row r="4">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E4" t="n">
+        <v>10219</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10217</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10216</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -763,52 +763,52 @@
         <v>35065</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="M4" t="n">
-        <v>6.919731303837119</v>
+        <v>6.919640305373397</v>
       </c>
       <c r="N4" t="n">
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5041527473520986</v>
+        <v>0.5049466340293568</v>
       </c>
       <c r="P4" t="n">
-        <v>7.238244863604294</v>
+        <v>7.238336267030447</v>
       </c>
       <c r="Q4" t="n">
         <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3185135597671748</v>
+        <v>0.3186959616570492</v>
       </c>
       <c r="S4" t="n">
-        <v>1.290174170464782</v>
+        <v>1.290117017370452</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677634763737211</v>
+        <v>1.677582438188358</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680638408964237</v>
+        <v>0.8680597340214387</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392187417451412</v>
+        <v>0.7392115282872569</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8471996502193058</v>
+        <v>0.8471530024872428</v>
       </c>
       <c r="X4" t="n">
-        <v>4.671984847195314</v>
+        <v>4.709671470792896</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.929646257864516</v>
+        <v>4.892544901685405</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.409095512259854</v>
+        <v>5.26251553929249</v>
       </c>
     </row>
     <row r="5">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E5" t="n">
         <v>8828</v>
@@ -835,7 +835,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8827</v>
+        <v>8828</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>36892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.729641724255126</v>
+        <v>6.729811678749433</v>
       </c>
       <c r="N5" t="n">
         <v>10.6125</v>
@@ -864,37 +864,37 @@
         <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>6.922251982269803</v>
+        <v>6.922282271723101</v>
       </c>
       <c r="Q5" t="n">
         <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1926102580146766</v>
+        <v>0.1924705929736681</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446658943345836</v>
+        <v>1.446627511165031</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844914671307581</v>
+        <v>1.844862671727467</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963341860774601</v>
+        <v>0.2963428545920298</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1163434864810704</v>
+        <v>-0.1163136607066493</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473681852403379</v>
+        <v>0.2473771816239473</v>
       </c>
       <c r="X5" t="n">
-        <v>6.813301189812796</v>
+        <v>6.769510783246245</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.034254552129413</v>
+        <v>6.988881629971563</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.223379445853321</v>
+        <v>7.223970406132397</v>
       </c>
     </row>
     <row r="6">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E6" t="n">
+        <v>14192</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14190</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14189</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>31048</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L6" t="n">
         <v>1.025</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582744203256043</v>
+        <v>5.582749647639182</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
@@ -950,37 +950,37 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585585018220065</v>
+        <v>5.585579028461491</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002840814964022571</v>
+        <v>0.002829380822308103</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162756957105505</v>
+        <v>1.162678974618376</v>
       </c>
       <c r="T6" t="n">
-        <v>1.501002611837489</v>
+        <v>1.500917106889101</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076459723344227</v>
+        <v>0.5076589301835807</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06654800348817924</v>
+        <v>0.06658873219871109</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045673123816072</v>
+        <v>0.5045781272662816</v>
       </c>
       <c r="X6" t="n">
-        <v>5.971933596703742</v>
+        <v>5.927758284397236</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.13724344826476</v>
+        <v>6.113142163135605</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.238725709542586</v>
+        <v>6.237461904263632</v>
       </c>
     </row>
     <row r="7">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E7" t="n">
+        <v>8990</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8988</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8987</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>36161</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L7" t="n">
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880510181373095</v>
+        <v>7.880541277258568</v>
       </c>
       <c r="N7" t="n">
         <v>15.14</v>
@@ -1036,37 +1036,37 @@
         <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>8.092733281453045</v>
+        <v>8.093234889727841</v>
       </c>
       <c r="Q7" t="n">
         <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2122231000799516</v>
+        <v>0.2126936124692732</v>
       </c>
       <c r="S7" t="n">
-        <v>1.421045293572391</v>
+        <v>1.42142902188953</v>
       </c>
       <c r="T7" t="n">
-        <v>1.793485647513805</v>
+        <v>1.794106844046855</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8127966556249928</v>
+        <v>0.8126359625405885</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6419758014149836</v>
+        <v>0.6416882270094619</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7982017156770616</v>
+        <v>0.7979939628881411</v>
       </c>
       <c r="X7" t="n">
-        <v>5.7516263767111</v>
+        <v>5.669963560387359</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.148325690464379</v>
+        <v>6.107341055065111</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.360177905602171</v>
+        <v>6.372416907439858</v>
       </c>
     </row>
     <row r="8">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E8" t="n">
+        <v>13855</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13853</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13852</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L8" t="n">
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616930948599481</v>
+        <v>7.616849599364758</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
@@ -1122,37 +1122,37 @@
         <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>7.660260953499951</v>
+        <v>7.660342157697491</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04333000490047045</v>
+        <v>0.04349255833273215</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502824612746873</v>
+        <v>1.502746519206235</v>
       </c>
       <c r="T8" t="n">
-        <v>1.962141263783013</v>
+        <v>1.962074237290711</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529676822909155</v>
+        <v>0.7529574275742911</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156454047052352</v>
+        <v>0.5156491172731368</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520092109960104</v>
+        <v>0.7519936991502403</v>
       </c>
       <c r="X8" t="n">
-        <v>6.27246912544592</v>
+        <v>6.168846665265119</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.804012839769075</v>
+        <v>6.71997660825924</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.132008751417632</v>
+        <v>7.130969125817297</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74327467642422</v>
+        <v>10.74312423195003</v>
       </c>
       <c r="Q9" t="n">
         <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4382151366864612</v>
+        <v>0.4380646922122765</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151393985812674</v>
+        <v>2.15137874003638</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874483279762739</v>
+        <v>2.874458807248082</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3307111867665943</v>
+        <v>0.3307382859178874</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2717191984699869</v>
+        <v>-0.2716975444673633</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3250253771885661</v>
+        <v>0.3250578139777767</v>
       </c>
       <c r="X9" t="n">
-        <v>9.97983771132594</v>
+        <v>9.913680384347211</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.45404182878192</v>
+        <v>10.3253669102009</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.09200246171443</v>
+        <v>10.856622485473</v>
       </c>
     </row>
     <row r="10">
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E10" t="n">
-        <v>13793</v>
+        <v>13796</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>13793</v>
+        <v>13794</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         <v>31413</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L10" t="n">
         <v>0.4375</v>
       </c>
       <c r="M10" t="n">
-        <v>5.246255346915103</v>
+        <v>5.246194359866609</v>
       </c>
       <c r="N10" t="n">
         <v>10.15</v>
@@ -1294,37 +1294,37 @@
         <v>0.4490779286658197</v>
       </c>
       <c r="P10" t="n">
-        <v>5.219128521481942</v>
+        <v>5.219041680939133</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02712682543316047</v>
+        <v>-0.02715267892747541</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160865364036006</v>
+        <v>1.160749125298407</v>
       </c>
       <c r="T10" t="n">
-        <v>1.48195026311239</v>
+        <v>1.481826736197105</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4295915808765946</v>
+        <v>0.4296402373774472</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08941709567383782</v>
+        <v>-0.08928673558548339</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4276071820917159</v>
+        <v>0.4276525897933733</v>
       </c>
       <c r="X10" t="n">
-        <v>4.463381747207493</v>
+        <v>4.408895225582928</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.716982645215031</v>
+        <v>4.663693174371073</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.034019748827397</v>
+        <v>5.446405386332255</v>
       </c>
     </row>
     <row r="11">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E11" t="n">
+        <v>4114</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4112</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4111</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         <v>41640</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L11" t="n">
         <v>2.195</v>
       </c>
       <c r="M11" t="n">
-        <v>7.497826562880078</v>
+        <v>7.497323686770429</v>
       </c>
       <c r="N11" t="n">
         <v>19.1775</v>
@@ -1380,37 +1380,37 @@
         <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>7.714007674049111</v>
+        <v>7.713997640085126</v>
       </c>
       <c r="Q11" t="n">
         <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2161811111690331</v>
+        <v>0.2166739533146976</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9634700656381733</v>
+        <v>0.9635055803480705</v>
       </c>
       <c r="T11" t="n">
-        <v>1.343175418165205</v>
+        <v>1.343110969119288</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907299120879707</v>
+        <v>0.7907045155783793</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5649194293213557</v>
+        <v>0.564964452605409</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7883990835444079</v>
+        <v>0.7883837720585336</v>
       </c>
       <c r="X11" t="n">
-        <v>5.148394978812007</v>
+        <v>4.978045280776665</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.364282616906164</v>
+        <v>5.296939028777364</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.717378126389128</v>
+        <v>5.54997588347624</v>
       </c>
     </row>
     <row r="12">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E12" t="n">
+        <v>6448</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6447</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6446</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1451,52 +1451,52 @@
         <v>39083</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L12" t="n">
         <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>9.619540283379875</v>
+        <v>9.619315443875704</v>
       </c>
       <c r="N12" t="n">
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.94898927519542</v>
+        <v>2.950446313880026</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01675651933839</v>
+        <v>10.01677912464472</v>
       </c>
       <c r="Q12" t="n">
         <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3972162359585186</v>
+        <v>0.3974636807690156</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683682222863671</v>
+        <v>1.683527873822874</v>
       </c>
       <c r="T12" t="n">
-        <v>2.138509287101883</v>
+        <v>2.138351694469705</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253476307668026</v>
+        <v>0.825348443924796</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6538643617691298</v>
+        <v>0.6538702236289162</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135394599631032</v>
+        <v>0.8135115855109972</v>
       </c>
       <c r="X12" t="n">
-        <v>7.827541425908806</v>
+        <v>7.742412028968356</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.272883015002295</v>
+        <v>8.153627447990477</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.843579048263145</v>
+        <v>8.774956261222856</v>
       </c>
     </row>
     <row r="13">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E13" t="n">
+        <v>14036</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14034</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14033</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         <v>30682</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L13" t="n">
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>8.134611807881422</v>
+        <v>8.1345730012826</v>
       </c>
       <c r="N13" t="n">
         <v>34.0025</v>
@@ -1552,37 +1552,37 @@
         <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211891129130818</v>
+        <v>8.212168443046242</v>
       </c>
       <c r="Q13" t="n">
         <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0772793212493936</v>
+        <v>0.07759544176364219</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786859542982717</v>
+        <v>1.78705110451749</v>
       </c>
       <c r="T13" t="n">
-        <v>2.321874367784248</v>
+        <v>2.32202463100081</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7762522116689691</v>
+        <v>0.7761909162365284</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5510750844921338</v>
+        <v>0.5509857724770675</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7760410260374765</v>
+        <v>0.7759788908820439</v>
       </c>
       <c r="X13" t="n">
-        <v>6.451617700269322</v>
+        <v>6.433688273245068</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.615536371713238</v>
+        <v>6.598885815562232</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.773556308194289</v>
+        <v>6.759946706174473</v>
       </c>
     </row>
     <row r="14">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1638,37 +1638,37 @@
         <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83379077686753</v>
+        <v>11.83364189947522</v>
       </c>
       <c r="Q14" t="n">
         <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1300911205187242</v>
+        <v>-0.1302399979110323</v>
       </c>
       <c r="S14" t="n">
-        <v>2.042973450164269</v>
+        <v>2.042997056035585</v>
       </c>
       <c r="T14" t="n">
-        <v>2.65876393855271</v>
+        <v>2.658779107944695</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009612127948786</v>
+        <v>0.8009653813099707</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207679219620057</v>
+        <v>0.6207635945853838</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7923691355419947</v>
+        <v>0.7923825036046889</v>
       </c>
       <c r="X14" t="n">
-        <v>8.480440672056586</v>
+        <v>8.286206596806183</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.931262274532168</v>
+        <v>8.770158558818942</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.854705827971273</v>
+        <v>9.164669400706343</v>
       </c>
     </row>
     <row r="15">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E15" t="n">
+        <v>9799</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9797</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9796</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         <v>35804</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L15" t="n">
         <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>8.410231046685722</v>
+        <v>8.410072811404852</v>
       </c>
       <c r="N15" t="n">
         <v>131.9</v>
@@ -1724,37 +1724,37 @@
         <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>9.377474681304339</v>
+        <v>9.377024868403437</v>
       </c>
       <c r="Q15" t="n">
         <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9672436346186157</v>
+        <v>0.9669520569985842</v>
       </c>
       <c r="S15" t="n">
-        <v>4.182807358680301</v>
+        <v>4.182882361726556</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62297588456514</v>
+        <v>11.62251114237721</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03405679618924165</v>
+        <v>0.03403609080167429</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7611351341083314</v>
+        <v>-0.7611684344276113</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02212204471794355</v>
+        <v>0.02210554248460961</v>
       </c>
       <c r="X15" t="n">
-        <v>11.48177075474107</v>
+        <v>11.32440008986133</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.90242513707105</v>
+        <v>11.80526301269906</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.24842507881084</v>
+        <v>12.18865966287645</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1810,37 +1810,37 @@
         <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927511842767152</v>
+        <v>6.927507338456755</v>
       </c>
       <c r="Q16" t="n">
         <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443784371272393</v>
+        <v>0.3443739328168423</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971851086623644</v>
+        <v>1.971882612471731</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479796253308504</v>
+        <v>2.479823194849092</v>
       </c>
       <c r="U16" t="n">
-        <v>0.533512878767687</v>
+        <v>0.5335076956338095</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08998206134685227</v>
+        <v>0.08996228761069902</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283743247183654</v>
+        <v>0.5283704628412715</v>
       </c>
       <c r="X16" t="n">
-        <v>3.46199237455926</v>
+        <v>3.502982235415164</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.659597346823183</v>
+        <v>4.358566894220392</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.955987477451191</v>
+        <v>5.407769007949702</v>
       </c>
     </row>
     <row r="17">
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E17" t="n">
+        <v>3202</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3200</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3199</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         <v>42370</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L17" t="n">
         <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6.505378243201001</v>
+        <v>6.504732812499999</v>
       </c>
       <c r="N17" t="n">
         <v>18.4925</v>
@@ -1896,37 +1896,37 @@
         <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>6.730766586273819</v>
+        <v>6.72979734323804</v>
       </c>
       <c r="Q17" t="n">
         <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.225388343072818</v>
+        <v>0.2250645307380403</v>
       </c>
       <c r="S17" t="n">
-        <v>1.089059679961258</v>
+        <v>1.08908989602634</v>
       </c>
       <c r="T17" t="n">
-        <v>1.47862775726344</v>
+        <v>1.478500121259408</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6071369822113528</v>
+        <v>0.6072984731886163</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2258640160580968</v>
+        <v>0.226120983266128</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6036247712056213</v>
+        <v>0.6038041111651332</v>
       </c>
       <c r="X17" t="n">
-        <v>4.553891627231145</v>
+        <v>4.66094211979913</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.724578393091734</v>
+        <v>5.428968108320791</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.57838991195923</v>
+        <v>6.227798328907924</v>
       </c>
     </row>
     <row r="18">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16652</v>
+        <v>16653</v>
       </c>
       <c r="E18" t="n">
+        <v>7156</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7154</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7153</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1967,52 +1967,52 @@
         <v>37987</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="L18" t="n">
         <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>10.38065077589822</v>
+        <v>10.37947651663405</v>
       </c>
       <c r="N18" t="n">
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.811036695388214</v>
+        <v>4.780961591918786</v>
       </c>
       <c r="P18" t="n">
-        <v>11.17040274555884</v>
+        <v>11.16920353932105</v>
       </c>
       <c r="Q18" t="n">
         <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7897519696606117</v>
+        <v>0.7897270226869993</v>
       </c>
       <c r="S18" t="n">
-        <v>2.035567518892357</v>
+        <v>2.036041063631464</v>
       </c>
       <c r="T18" t="n">
-        <v>2.755944403040442</v>
+        <v>2.756628553439029</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252161039056807</v>
+        <v>0.7252258153135749</v>
       </c>
       <c r="V18" t="n">
-        <v>0.467343138799824</v>
+        <v>0.4673726177553663</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6764658353038074</v>
+        <v>0.6764994979782712</v>
       </c>
       <c r="X18" t="n">
-        <v>8.094495847291423</v>
+        <v>8.065677502174216</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.156417798751182</v>
+        <v>8.131478010273794</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.233989985488543</v>
+        <v>8.206066294312304</v>
       </c>
     </row>
   </sheetData>
@@ -2081,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.094495847291423</v>
+        <v>8.065677502174216</v>
       </c>
       <c r="G2" t="n">
-        <v>8.156417798751182</v>
+        <v>8.131478010273794</v>
       </c>
       <c r="H2" t="n">
-        <v>8.233989985488543</v>
+        <v>8.206066294312304</v>
       </c>
     </row>
     <row r="3">
@@ -2109,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.971933596703742</v>
+        <v>5.927758284397236</v>
       </c>
       <c r="G3" t="n">
-        <v>6.13724344826476</v>
+        <v>6.113142163135606</v>
       </c>
       <c r="H3" t="n">
-        <v>6.238725709542586</v>
+        <v>6.237461904263632</v>
       </c>
     </row>
     <row r="4">
@@ -2137,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.463381747207493</v>
+        <v>4.408895225582928</v>
       </c>
       <c r="G4" t="n">
-        <v>4.716982645215031</v>
+        <v>4.663693174371073</v>
       </c>
       <c r="H4" t="n">
-        <v>5.034019748827397</v>
+        <v>5.446405386332255</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.48177075474107</v>
+        <v>11.32440008986133</v>
       </c>
       <c r="G5" t="n">
-        <v>11.90242513707105</v>
+        <v>11.80526301269906</v>
       </c>
       <c r="H5" t="n">
-        <v>12.24842507881084</v>
+        <v>12.18865966287645</v>
       </c>
     </row>
     <row r="6">
@@ -2193,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>95.87613444605</v>
+        <v>92.31754146199668</v>
       </c>
       <c r="G6" t="n">
-        <v>105.2705788003175</v>
+        <v>100.6190063282841</v>
       </c>
       <c r="H6" t="n">
-        <v>113.5603298057117</v>
+        <v>107.3736001341237</v>
       </c>
     </row>
     <row r="7">
@@ -2221,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.480440672056586</v>
+        <v>8.286206596806183</v>
       </c>
       <c r="G7" t="n">
-        <v>8.931262274532168</v>
+        <v>8.770158558818942</v>
       </c>
       <c r="H7" t="n">
-        <v>9.854705827971273</v>
+        <v>9.164669400706343</v>
       </c>
     </row>
     <row r="8">
@@ -2249,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.827541425908806</v>
+        <v>7.742412028968356</v>
       </c>
       <c r="G8" t="n">
-        <v>8.272883015002295</v>
+        <v>8.153627447990477</v>
       </c>
       <c r="H8" t="n">
-        <v>8.843579048263145</v>
+        <v>8.774956261222856</v>
       </c>
     </row>
     <row r="9">
@@ -2277,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.148394978812007</v>
+        <v>4.978045280776665</v>
       </c>
       <c r="G9" t="n">
-        <v>5.364282616906164</v>
+        <v>5.296939028777365</v>
       </c>
       <c r="H9" t="n">
-        <v>5.717378126389128</v>
+        <v>5.54997588347624</v>
       </c>
     </row>
     <row r="10">
@@ -2305,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.7516263767111</v>
+        <v>5.669963560387359</v>
       </c>
       <c r="G10" t="n">
-        <v>6.148325690464379</v>
+        <v>6.107341055065111</v>
       </c>
       <c r="H10" t="n">
-        <v>6.360177905602171</v>
+        <v>6.372416907439858</v>
       </c>
     </row>
     <row r="11">
@@ -2333,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.46199237455926</v>
+        <v>3.502982235415164</v>
       </c>
       <c r="G11" t="n">
-        <v>4.659597346823184</v>
+        <v>4.358566894220393</v>
       </c>
       <c r="H11" t="n">
-        <v>5.955987477451191</v>
+        <v>5.407769007949702</v>
       </c>
     </row>
     <row r="12">
@@ -2361,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.451617700269322</v>
+        <v>6.433688273245068</v>
       </c>
       <c r="G12" t="n">
-        <v>6.615536371713238</v>
+        <v>6.598885815562232</v>
       </c>
       <c r="H12" t="n">
-        <v>6.773556308194289</v>
+        <v>6.759946706174473</v>
       </c>
     </row>
     <row r="13">
@@ -2389,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.97983771132594</v>
+        <v>9.913680384347211</v>
       </c>
       <c r="G13" t="n">
-        <v>10.45404182878192</v>
+        <v>10.3253669102009</v>
       </c>
       <c r="H13" t="n">
-        <v>11.09200246171443</v>
+        <v>10.856622485473</v>
       </c>
     </row>
     <row r="14">
@@ -2417,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.27246912544592</v>
+        <v>6.168846665265119</v>
       </c>
       <c r="G14" t="n">
-        <v>6.804012839769075</v>
+        <v>6.71997660825924</v>
       </c>
       <c r="H14" t="n">
-        <v>7.132008751417632</v>
+        <v>7.130969125817297</v>
       </c>
     </row>
     <row r="15">
@@ -2445,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.813301189812796</v>
+        <v>6.769510783246245</v>
       </c>
       <c r="G15" t="n">
-        <v>7.034254552129411</v>
+        <v>6.988881629971563</v>
       </c>
       <c r="H15" t="n">
-        <v>7.223379445853321</v>
+        <v>7.223970406132397</v>
       </c>
     </row>
     <row r="16">
@@ -2473,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.553891627231145</v>
+        <v>4.66094211979913</v>
       </c>
       <c r="G16" t="n">
-        <v>5.724578393091734</v>
+        <v>5.42896810832079</v>
       </c>
       <c r="H16" t="n">
-        <v>6.57838991195923</v>
+        <v>6.227798328907924</v>
       </c>
     </row>
     <row r="17">
@@ -2501,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.671984847195314</v>
+        <v>4.709671470792896</v>
       </c>
       <c r="G17" t="n">
-        <v>4.929646257864516</v>
+        <v>4.892544901685405</v>
       </c>
       <c r="H17" t="n">
-        <v>5.409095512259854</v>
+        <v>5.26251553929249</v>
       </c>
     </row>
     <row r="18">
@@ -2529,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.094948531881759</v>
+        <v>3.002068576525643</v>
       </c>
       <c r="G18" t="n">
-        <v>3.509218087994149</v>
+        <v>3.47158846778119</v>
       </c>
       <c r="H18" t="n">
-        <v>3.720518324039409</v>
+        <v>3.720867493433415</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E2" t="n">
         <v>9959</v>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9957</v>
+        <v>9958</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         <v>36161</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L2" t="n">
         <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>102.9095920792742</v>
+        <v>102.8998662716744</v>
       </c>
       <c r="N2" t="n">
         <v>118.97</v>
@@ -606,37 +606,37 @@
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>95.32702986779948</v>
+        <v>95.32746005787514</v>
       </c>
       <c r="Q2" t="n">
         <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.582562211474739</v>
+        <v>-7.572406213799228</v>
       </c>
       <c r="S2" t="n">
-        <v>22.64929757531536</v>
+        <v>22.65783173651169</v>
       </c>
       <c r="T2" t="n">
-        <v>31.52573995813171</v>
+        <v>31.54070844801757</v>
       </c>
       <c r="U2" t="n">
-        <v>0.135448274487471</v>
+        <v>0.1351208062408296</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3255606565608451</v>
+        <v>-0.3252880124995701</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06527282382095589</v>
+        <v>0.06483100351578397</v>
       </c>
       <c r="X2" t="n">
-        <v>92.31754146199668</v>
+        <v>88.94841056899354</v>
       </c>
       <c r="Y2" t="n">
-        <v>100.6190063282841</v>
+        <v>97.08795894066915</v>
       </c>
       <c r="Z2" t="n">
-        <v>107.3736001341237</v>
+        <v>105.5563859801998</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E3" t="n">
         <v>14537</v>
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14535</v>
+        <v>14536</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         <v>30317</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L3" t="n">
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>4.906947884416925</v>
+        <v>4.906862100990645</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
@@ -692,37 +692,37 @@
         <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955755972935311</v>
+        <v>4.95559517118877</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04880808851838554</v>
+        <v>0.04873307019812478</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354144458388229</v>
+        <v>1.354049271353809</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729901898208585</v>
+        <v>1.729846176193558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784396832593301</v>
+        <v>0.778448146578506</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643425475744006</v>
+        <v>0.564347426187931</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774555545606983</v>
+        <v>0.7774672527515455</v>
       </c>
       <c r="X3" t="n">
-        <v>3.002068576525643</v>
+        <v>2.908274702068205</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.47158846778119</v>
+        <v>3.403035439589797</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.720867493433415</v>
+        <v>3.722180496520003</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E4" t="n">
         <v>10219</v>
@@ -749,7 +749,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10217</v>
+        <v>10218</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -763,52 +763,52 @@
         <v>35065</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="M4" t="n">
-        <v>6.919640305373397</v>
+        <v>6.919521677431983</v>
       </c>
       <c r="N4" t="n">
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5049466340293568</v>
+        <v>0.5046004908216271</v>
       </c>
       <c r="P4" t="n">
-        <v>7.238336267030447</v>
+        <v>7.238063367407995</v>
       </c>
       <c r="Q4" t="n">
         <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3186959616570492</v>
+        <v>0.3185416899760126</v>
       </c>
       <c r="S4" t="n">
-        <v>1.290117017370452</v>
+        <v>1.29003228040476</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677582438188358</v>
+        <v>1.677502997254421</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680597340214387</v>
+        <v>0.8680602342838106</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392115282872569</v>
+        <v>0.7392141790524942</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8471530024872428</v>
+        <v>0.8471789954629139</v>
       </c>
       <c r="X4" t="n">
-        <v>4.709671470792896</v>
+        <v>4.728180555913503</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.892544901685405</v>
+        <v>4.875882186484379</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.26251553929249</v>
+        <v>5.143749694598814</v>
       </c>
     </row>
     <row r="5">
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E5" t="n">
-        <v>8828</v>
+        <v>8830</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8828</v>
+        <v>8829</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>36892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.729811678749433</v>
+        <v>6.729960357911428</v>
       </c>
       <c r="N5" t="n">
         <v>10.6125</v>
@@ -864,37 +864,37 @@
         <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>6.922282271723101</v>
+        <v>6.922908532664749</v>
       </c>
       <c r="Q5" t="n">
         <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1924705929736681</v>
+        <v>0.1929481747533212</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446627511165031</v>
+        <v>1.446704682318504</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844862671727467</v>
+        <v>1.84493523233121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963428545920298</v>
+        <v>0.2963222612737363</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1163136607066493</v>
+        <v>-0.1164564676933406</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473771816239473</v>
+        <v>0.2473760116108497</v>
       </c>
       <c r="X5" t="n">
-        <v>6.769510783246245</v>
+        <v>6.730177169417159</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.988881629971563</v>
+        <v>6.945944196930904</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.223970406132397</v>
+        <v>7.184174667080817</v>
       </c>
     </row>
     <row r="6">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E6" t="n">
         <v>14192</v>
@@ -921,7 +921,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>14190</v>
+        <v>14191</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>31048</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L6" t="n">
         <v>1.025</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582749647639182</v>
+        <v>5.582752977239095</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
@@ -950,37 +950,37 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585579028461491</v>
+        <v>5.585567775854428</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002829380822308103</v>
+        <v>0.002814798615333034</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162678974618376</v>
+        <v>1.162643181347835</v>
       </c>
       <c r="T6" t="n">
-        <v>1.500917106889101</v>
+        <v>1.50087574663464</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076589301835807</v>
+        <v>0.5076568036606871</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06658873219871109</v>
+        <v>0.06657445983433918</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045781272662816</v>
+        <v>0.5045773265450826</v>
       </c>
       <c r="X6" t="n">
-        <v>5.927758284397236</v>
+        <v>5.878415660464427</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.113142163135605</v>
+        <v>6.083414698648705</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.237461904263632</v>
+        <v>6.236250653327139</v>
       </c>
     </row>
     <row r="7">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E7" t="n">
         <v>8990</v>
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8988</v>
+        <v>8989</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>36161</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L7" t="n">
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880541277258568</v>
+        <v>7.880546779397041</v>
       </c>
       <c r="N7" t="n">
         <v>15.14</v>
@@ -1036,37 +1036,37 @@
         <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>8.093234889727841</v>
+        <v>8.092883009536809</v>
       </c>
       <c r="Q7" t="n">
         <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2126936124692732</v>
+        <v>0.2123362301397671</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42142902188953</v>
+        <v>1.421452047766606</v>
       </c>
       <c r="T7" t="n">
-        <v>1.794106844046855</v>
+        <v>1.794082418672475</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8126359625405885</v>
+        <v>0.8126202758292569</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6416882270094619</v>
+        <v>0.6416581295846144</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7979939628881411</v>
+        <v>0.7980112678053485</v>
       </c>
       <c r="X7" t="n">
-        <v>5.669963560387359</v>
+        <v>5.59670893584352</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.107341055065111</v>
+        <v>6.036176288569788</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.372416907439858</v>
+        <v>6.369554136184569</v>
       </c>
     </row>
     <row r="8">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E8" t="n">
         <v>13855</v>
@@ -1093,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>13853</v>
+        <v>13854</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L8" t="n">
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616849599364758</v>
+        <v>7.616767540060632</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
@@ -1122,37 +1122,37 @@
         <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>7.660342157697491</v>
+        <v>7.660173914957888</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04349255833273215</v>
+        <v>0.04340637489725574</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502746519206235</v>
+        <v>1.502691569092577</v>
       </c>
       <c r="T8" t="n">
-        <v>1.962074237290711</v>
+        <v>1.962010555323946</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529574275742911</v>
+        <v>0.7529665376219868</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156491172731368</v>
+        <v>0.5156512808842362</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7519936991502403</v>
+        <v>0.752006152574433</v>
       </c>
       <c r="X8" t="n">
-        <v>6.168846665265119</v>
+        <v>6.06431821309257</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.71997660825924</v>
+        <v>6.614317863657368</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.130969125817297</v>
+        <v>7.131657936470599</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74312423195003</v>
+        <v>10.74297400224312</v>
       </c>
       <c r="Q9" t="n">
         <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4380646922122765</v>
+        <v>0.4379144625053638</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15137874003638</v>
+        <v>2.15136414431218</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874458807248082</v>
+        <v>2.874434500205714</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3307382859178874</v>
+        <v>0.3307653235554932</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2716975444673633</v>
+        <v>-0.2716760370619904</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3250578139777767</v>
+        <v>0.3250901859353447</v>
       </c>
       <c r="X9" t="n">
-        <v>9.913680384347211</v>
+        <v>9.908184584954775</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.3253669102009</v>
+        <v>10.27613984984273</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.856622485473</v>
+        <v>10.66121806310734</v>
       </c>
     </row>
     <row r="10">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E10" t="n">
         <v>13796</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>13794</v>
+        <v>13795</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         <v>31413</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L10" t="n">
         <v>0.4375</v>
       </c>
       <c r="M10" t="n">
-        <v>5.246194359866609</v>
+        <v>5.246111090974992</v>
       </c>
       <c r="N10" t="n">
         <v>10.15</v>
@@ -1294,37 +1294,37 @@
         <v>0.4490779286658197</v>
       </c>
       <c r="P10" t="n">
-        <v>5.219041680939133</v>
+        <v>5.218972936189636</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02715267892747541</v>
+        <v>-0.02713815478535559</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160749125298407</v>
+        <v>1.160722426250821</v>
       </c>
       <c r="T10" t="n">
-        <v>1.481826736197105</v>
+        <v>1.481798520620404</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4296402373774472</v>
+        <v>0.4296555478169507</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08928673558548339</v>
+        <v>-0.08927253295033477</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4276525897933733</v>
+        <v>0.4276690859409936</v>
       </c>
       <c r="X10" t="n">
-        <v>4.408895225582928</v>
+        <v>4.406099944577184</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.663693174371073</v>
+        <v>4.675104309026638</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.446405386332255</v>
+        <v>5.308118535165622</v>
       </c>
     </row>
     <row r="11">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E11" t="n">
         <v>4114</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4112</v>
+        <v>4113</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         <v>41640</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L11" t="n">
         <v>2.195</v>
       </c>
       <c r="M11" t="n">
-        <v>7.497323686770429</v>
+        <v>7.496862995380502</v>
       </c>
       <c r="N11" t="n">
         <v>19.1775</v>
@@ -1380,37 +1380,37 @@
         <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>7.713997640085126</v>
+        <v>7.713412030842163</v>
       </c>
       <c r="Q11" t="n">
         <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2166739533146976</v>
+        <v>0.2165490354616622</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9635055803480705</v>
+        <v>0.9632600483966266</v>
       </c>
       <c r="T11" t="n">
-        <v>1.343110969119288</v>
+        <v>1.342936651703074</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907045155783793</v>
+        <v>0.7907622661354156</v>
       </c>
       <c r="V11" t="n">
-        <v>0.564964452605409</v>
+        <v>0.5650631595275413</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7883837720585336</v>
+        <v>0.7884389878192268</v>
       </c>
       <c r="X11" t="n">
-        <v>4.978045280776665</v>
+        <v>4.861199235195812</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.296939028777364</v>
+        <v>5.224133290969142</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.54997588347624</v>
+        <v>5.401311783857174</v>
       </c>
     </row>
     <row r="12">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E12" t="n">
         <v>6448</v>
@@ -1437,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>6447</v>
+        <v>6448</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1451,52 +1451,52 @@
         <v>39083</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L12" t="n">
         <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>9.619315443875704</v>
+        <v>9.619056555004134</v>
       </c>
       <c r="N12" t="n">
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.950446313880026</v>
+        <v>2.949464738881011</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01677912464472</v>
+        <v>10.01634847764179</v>
       </c>
       <c r="Q12" t="n">
         <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3974636807690156</v>
+        <v>0.3972919226376544</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683527873822874</v>
+        <v>1.683293167765912</v>
       </c>
       <c r="T12" t="n">
-        <v>2.138351694469705</v>
+        <v>2.138088529178442</v>
       </c>
       <c r="U12" t="n">
-        <v>0.825348443924796</v>
+        <v>0.8253745321604737</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6538702236289162</v>
+        <v>0.6539130608040014</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135115855109972</v>
+        <v>0.8135567762143144</v>
       </c>
       <c r="X12" t="n">
-        <v>7.742412028968356</v>
+        <v>7.638523148752649</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.153627447990477</v>
+        <v>8.036477192794568</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.774956261222856</v>
+        <v>8.621946243924967</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E13" t="n">
         <v>14036</v>
@@ -1523,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>14034</v>
+        <v>14035</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         <v>30682</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L13" t="n">
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1345730012826</v>
+        <v>8.134524225151408</v>
       </c>
       <c r="N13" t="n">
         <v>34.0025</v>
@@ -1552,37 +1552,37 @@
         <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>8.212168443046242</v>
+        <v>8.211894504608958</v>
       </c>
       <c r="Q13" t="n">
         <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07759544176364219</v>
+        <v>0.07737027945755186</v>
       </c>
       <c r="S13" t="n">
-        <v>1.78705110451749</v>
+        <v>1.786868940432639</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32202463100081</v>
+        <v>2.321854034492398</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7761909162365284</v>
+        <v>0.7762190993330601</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5509857724770675</v>
+        <v>0.5510210056145823</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7759788908820439</v>
+        <v>0.7760077411626636</v>
       </c>
       <c r="X13" t="n">
-        <v>6.433688273245068</v>
+        <v>6.392719712612755</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.598885815562232</v>
+        <v>6.561024153221164</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.759946706174473</v>
+        <v>6.722848953602786</v>
       </c>
     </row>
     <row r="14">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1638,37 +1638,37 @@
         <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83364189947522</v>
+        <v>11.8334932346131</v>
       </c>
       <c r="Q14" t="n">
         <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1302399979110323</v>
+        <v>-0.1303886627731586</v>
       </c>
       <c r="S14" t="n">
-        <v>2.042997056035585</v>
+        <v>2.043020628208298</v>
       </c>
       <c r="T14" t="n">
-        <v>2.658779107944695</v>
+        <v>2.658794417052651</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009653813099707</v>
+        <v>0.8009695249964965</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207635945853838</v>
+        <v>0.6207592273269162</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7923825036046889</v>
+        <v>0.7923958344475076</v>
       </c>
       <c r="X14" t="n">
-        <v>8.286206596806183</v>
+        <v>8.214536191178311</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.770158558818942</v>
+        <v>8.670374084533359</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.164669400706343</v>
+        <v>9.037183390929531</v>
       </c>
     </row>
     <row r="15">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E15" t="n">
         <v>9799</v>
@@ -1695,7 +1695,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>9797</v>
+        <v>9798</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         <v>35804</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L15" t="n">
         <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>8.410072811404852</v>
+        <v>8.409926855820915</v>
       </c>
       <c r="N15" t="n">
         <v>131.9</v>
@@ -1724,37 +1724,37 @@
         <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>9.377024868403437</v>
+        <v>9.377122318821856</v>
       </c>
       <c r="Q15" t="n">
         <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9669520569985842</v>
+        <v>0.9671954630009391</v>
       </c>
       <c r="S15" t="n">
-        <v>4.182882361726556</v>
+        <v>4.182932932296252</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62251114237721</v>
+        <v>11.62202662827685</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03403609080167429</v>
+        <v>0.03402684499361657</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7611684344276113</v>
+        <v>-0.7611965581936886</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02210554248460961</v>
+        <v>0.02209301490129234</v>
       </c>
       <c r="X15" t="n">
-        <v>11.32440008986133</v>
+        <v>11.14463348656781</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.80526301269906</v>
+        <v>11.70025366970526</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.18865966287645</v>
+        <v>12.11729634183836</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1810,37 +1810,37 @@
         <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927507338456755</v>
+        <v>6.927502840576494</v>
       </c>
       <c r="Q16" t="n">
         <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443739328168423</v>
+        <v>0.3443694349365816</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971882612471731</v>
+        <v>1.971914093315039</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479823194849092</v>
+        <v>2.479850117799189</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5335076956338095</v>
+        <v>0.5335025157883491</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08996228761069902</v>
+        <v>0.08994252730442509</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283704628412715</v>
+        <v>0.5283666028000784</v>
       </c>
       <c r="X16" t="n">
-        <v>3.502982235415164</v>
+        <v>3.597791638580349</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.358566894220392</v>
+        <v>4.425736345971985</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.407769007949702</v>
+        <v>6.327172175625766</v>
       </c>
     </row>
     <row r="17">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E17" t="n">
         <v>3202</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>3200</v>
+        <v>3201</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         <v>42370</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L17" t="n">
         <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6.504732812499999</v>
+        <v>6.504075288972196</v>
       </c>
       <c r="N17" t="n">
         <v>18.4925</v>
@@ -1896,37 +1896,37 @@
         <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>6.72979734323804</v>
+        <v>6.729406294169347</v>
       </c>
       <c r="Q17" t="n">
         <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2250645307380403</v>
+        <v>0.2253310051971512</v>
       </c>
       <c r="S17" t="n">
-        <v>1.08908989602634</v>
+        <v>1.089131073274831</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478500121259408</v>
+        <v>1.478428450564475</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6072984731886163</v>
+        <v>0.6073809690217238</v>
       </c>
       <c r="V17" t="n">
-        <v>0.226120983266128</v>
+        <v>0.2263332422418055</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6038041111651332</v>
+        <v>0.6038688286289533</v>
       </c>
       <c r="X17" t="n">
-        <v>4.66094211979913</v>
+        <v>4.645449640017119</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.428968108320791</v>
+        <v>5.407649912928195</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.227798328907924</v>
+        <v>6.869415796338449</v>
       </c>
     </row>
     <row r="18">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16653</v>
+        <v>16654</v>
       </c>
       <c r="E18" t="n">
         <v>7156</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>7154</v>
+        <v>7155</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1967,52 +1967,52 @@
         <v>37987</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="L18" t="n">
         <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>10.37947651663405</v>
+        <v>10.37831236897275</v>
       </c>
       <c r="N18" t="n">
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.780961591918786</v>
+        <v>4.779425692614537</v>
       </c>
       <c r="P18" t="n">
-        <v>11.16920353932105</v>
+        <v>11.16863363269499</v>
       </c>
       <c r="Q18" t="n">
         <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7897270226869993</v>
+        <v>0.7903212637222425</v>
       </c>
       <c r="S18" t="n">
-        <v>2.036041063631464</v>
+        <v>2.03659228236621</v>
       </c>
       <c r="T18" t="n">
-        <v>2.756628553439029</v>
+        <v>2.757381255040436</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252258153135749</v>
+        <v>0.7252224498513669</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4673726177553663</v>
+        <v>0.4673692249775152</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6764994979782712</v>
+        <v>0.6763948375165297</v>
       </c>
       <c r="X18" t="n">
-        <v>8.065677502174216</v>
+        <v>8.00955846185372</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.131478010273794</v>
+        <v>8.143818256209778</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.206066294312304</v>
+        <v>8.516197587701171</v>
       </c>
     </row>
   </sheetData>
@@ -2081,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.065677502174216</v>
+        <v>8.00955846185372</v>
       </c>
       <c r="G2" t="n">
-        <v>8.131478010273794</v>
+        <v>8.143818256209778</v>
       </c>
       <c r="H2" t="n">
-        <v>8.206066294312304</v>
+        <v>8.516197587701171</v>
       </c>
     </row>
     <row r="3">
@@ -2109,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.927758284397236</v>
+        <v>5.878415660464427</v>
       </c>
       <c r="G3" t="n">
-        <v>6.113142163135606</v>
+        <v>6.083414698648706</v>
       </c>
       <c r="H3" t="n">
-        <v>6.237461904263632</v>
+        <v>6.236250653327139</v>
       </c>
     </row>
     <row r="4">
@@ -2137,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.408895225582928</v>
+        <v>4.406099944577184</v>
       </c>
       <c r="G4" t="n">
-        <v>4.663693174371073</v>
+        <v>4.675104309026639</v>
       </c>
       <c r="H4" t="n">
-        <v>5.446405386332255</v>
+        <v>5.308118535165622</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.32440008986133</v>
+        <v>11.14463348656781</v>
       </c>
       <c r="G5" t="n">
-        <v>11.80526301269906</v>
+        <v>11.70025366970526</v>
       </c>
       <c r="H5" t="n">
-        <v>12.18865966287645</v>
+        <v>12.11729634183836</v>
       </c>
     </row>
     <row r="6">
@@ -2193,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>92.31754146199668</v>
+        <v>88.94841056899354</v>
       </c>
       <c r="G6" t="n">
-        <v>100.6190063282841</v>
+        <v>97.08795894066915</v>
       </c>
       <c r="H6" t="n">
-        <v>107.3736001341237</v>
+        <v>105.5563859801998</v>
       </c>
     </row>
     <row r="7">
@@ -2221,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.286206596806183</v>
+        <v>8.214536191178311</v>
       </c>
       <c r="G7" t="n">
-        <v>8.770158558818942</v>
+        <v>8.670374084533361</v>
       </c>
       <c r="H7" t="n">
-        <v>9.164669400706343</v>
+        <v>9.037183390929531</v>
       </c>
     </row>
     <row r="8">
@@ -2249,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.742412028968356</v>
+        <v>7.638523148752649</v>
       </c>
       <c r="G8" t="n">
-        <v>8.153627447990477</v>
+        <v>8.036477192794568</v>
       </c>
       <c r="H8" t="n">
-        <v>8.774956261222856</v>
+        <v>8.621946243924967</v>
       </c>
     </row>
     <row r="9">
@@ -2277,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.978045280776665</v>
+        <v>4.861199235195812</v>
       </c>
       <c r="G9" t="n">
-        <v>5.296939028777365</v>
+        <v>5.224133290969143</v>
       </c>
       <c r="H9" t="n">
-        <v>5.54997588347624</v>
+        <v>5.401311783857174</v>
       </c>
     </row>
     <row r="10">
@@ -2305,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.669963560387359</v>
+        <v>5.59670893584352</v>
       </c>
       <c r="G10" t="n">
-        <v>6.107341055065111</v>
+        <v>6.036176288569789</v>
       </c>
       <c r="H10" t="n">
-        <v>6.372416907439858</v>
+        <v>6.369554136184569</v>
       </c>
     </row>
     <row r="11">
@@ -2333,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.502982235415164</v>
+        <v>3.597791638580349</v>
       </c>
       <c r="G11" t="n">
-        <v>4.358566894220393</v>
+        <v>4.425736345971985</v>
       </c>
       <c r="H11" t="n">
-        <v>5.407769007949702</v>
+        <v>6.327172175625766</v>
       </c>
     </row>
     <row r="12">
@@ -2361,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.433688273245068</v>
+        <v>6.392719712612755</v>
       </c>
       <c r="G12" t="n">
-        <v>6.598885815562232</v>
+        <v>6.561024153221164</v>
       </c>
       <c r="H12" t="n">
-        <v>6.759946706174473</v>
+        <v>6.722848953602786</v>
       </c>
     </row>
     <row r="13">
@@ -2389,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.913680384347211</v>
+        <v>9.908184584954775</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3253669102009</v>
+        <v>10.27613984984273</v>
       </c>
       <c r="H13" t="n">
-        <v>10.856622485473</v>
+        <v>10.66121806310734</v>
       </c>
     </row>
     <row r="14">
@@ -2417,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.168846665265119</v>
+        <v>6.06431821309257</v>
       </c>
       <c r="G14" t="n">
-        <v>6.71997660825924</v>
+        <v>6.614317863657369</v>
       </c>
       <c r="H14" t="n">
-        <v>7.130969125817297</v>
+        <v>7.131657936470599</v>
       </c>
     </row>
     <row r="15">
@@ -2445,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.769510783246245</v>
+        <v>6.730177169417159</v>
       </c>
       <c r="G15" t="n">
-        <v>6.988881629971563</v>
+        <v>6.945944196930904</v>
       </c>
       <c r="H15" t="n">
-        <v>7.223970406132397</v>
+        <v>7.184174667080817</v>
       </c>
     </row>
     <row r="16">
@@ -2473,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.66094211979913</v>
+        <v>4.645449640017119</v>
       </c>
       <c r="G16" t="n">
-        <v>5.42896810832079</v>
+        <v>5.407649912928195</v>
       </c>
       <c r="H16" t="n">
-        <v>6.227798328907924</v>
+        <v>6.869415796338449</v>
       </c>
     </row>
     <row r="17">
@@ -2501,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.709671470792896</v>
+        <v>4.728180555913503</v>
       </c>
       <c r="G17" t="n">
-        <v>4.892544901685405</v>
+        <v>4.87588218648438</v>
       </c>
       <c r="H17" t="n">
-        <v>5.26251553929249</v>
+        <v>5.143749694598814</v>
       </c>
     </row>
     <row r="18">
@@ -2529,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.002068576525643</v>
+        <v>2.908274702068205</v>
       </c>
       <c r="G18" t="n">
-        <v>3.47158846778119</v>
+        <v>3.403035439589797</v>
       </c>
       <c r="H18" t="n">
-        <v>3.720867493433415</v>
+        <v>3.722180496520003</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -707,13 +707,13 @@
         <v>1.729846176193558</v>
       </c>
       <c r="U3" t="n">
-        <v>0.778448146578506</v>
+        <v>0.7784481465785061</v>
       </c>
       <c r="V3" t="n">
         <v>0.564347426187931</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774672527515455</v>
+        <v>0.7774672527515456</v>
       </c>
       <c r="X3" t="n">
         <v>2.908274702068205</v>
@@ -879,7 +879,7 @@
         <v>1.84493523233121</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963222612737363</v>
+        <v>0.2963222612737365</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1164564676933406</v>
@@ -965,13 +965,13 @@
         <v>1.50087574663464</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076568036606871</v>
+        <v>0.5076568036606872</v>
       </c>
       <c r="V6" t="n">
         <v>0.06657445983433918</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045773265450826</v>
+        <v>0.5045773265450827</v>
       </c>
       <c r="X6" t="n">
         <v>5.878415660464427</v>
@@ -1051,13 +1051,13 @@
         <v>1.794082418672475</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8126202758292569</v>
+        <v>0.8126202758292573</v>
       </c>
       <c r="V7" t="n">
         <v>0.6416581295846144</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7980112678053485</v>
+        <v>0.7980112678053489</v>
       </c>
       <c r="X7" t="n">
         <v>5.59670893584352</v>
@@ -1137,13 +1137,13 @@
         <v>1.962010555323946</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529665376219868</v>
+        <v>0.7529665376219867</v>
       </c>
       <c r="V8" t="n">
         <v>0.5156512808842362</v>
       </c>
       <c r="W8" t="n">
-        <v>0.752006152574433</v>
+        <v>0.7520061525744329</v>
       </c>
       <c r="X8" t="n">
         <v>6.06431821309257</v>
@@ -1223,13 +1223,13 @@
         <v>2.874434500205714</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3307653235554932</v>
+        <v>0.330765323555493</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2716760370619904</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3250901859353447</v>
+        <v>0.3250901859353446</v>
       </c>
       <c r="X9" t="n">
         <v>9.908184584954775</v>
@@ -1395,13 +1395,13 @@
         <v>1.342936651703074</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907622661354156</v>
+        <v>0.7907622661354154</v>
       </c>
       <c r="V11" t="n">
         <v>0.5650631595275413</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7884389878192268</v>
+        <v>0.7884389878192266</v>
       </c>
       <c r="X11" t="n">
         <v>4.861199235195812</v>
@@ -1481,13 +1481,13 @@
         <v>2.138088529178442</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253745321604737</v>
+        <v>0.8253745321604735</v>
       </c>
       <c r="V12" t="n">
         <v>0.6539130608040014</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135567762143144</v>
+        <v>0.8135567762143142</v>
       </c>
       <c r="X12" t="n">
         <v>7.638523148752649</v>
@@ -1567,13 +1567,13 @@
         <v>2.321854034492398</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7762190993330601</v>
+        <v>0.77621909933306</v>
       </c>
       <c r="V13" t="n">
         <v>0.5510210056145823</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7760077411626636</v>
+        <v>0.7760077411626635</v>
       </c>
       <c r="X13" t="n">
         <v>6.392719712612755</v>
@@ -1653,13 +1653,13 @@
         <v>2.658794417052651</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009695249964965</v>
+        <v>0.8009695249964964</v>
       </c>
       <c r="V14" t="n">
         <v>0.6207592273269162</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7923958344475076</v>
+        <v>0.7923958344475075</v>
       </c>
       <c r="X14" t="n">
         <v>8.214536191178311</v>
@@ -1739,7 +1739,7 @@
         <v>11.62202662827685</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03402684499361657</v>
+        <v>0.03402684499361658</v>
       </c>
       <c r="V15" t="n">
         <v>-0.7611965581936886</v>
@@ -1825,13 +1825,13 @@
         <v>2.479850117799189</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5335025157883491</v>
+        <v>0.5335025157883488</v>
       </c>
       <c r="V16" t="n">
         <v>0.08994252730442509</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283666028000784</v>
+        <v>0.5283666028000781</v>
       </c>
       <c r="X16" t="n">
         <v>3.597791638580349</v>
@@ -1911,13 +1911,13 @@
         <v>1.478428450564475</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6073809690217238</v>
+        <v>0.6073809690217241</v>
       </c>
       <c r="V17" t="n">
         <v>0.2263332422418055</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6038688286289533</v>
+        <v>0.6038688286289535</v>
       </c>
       <c r="X17" t="n">
         <v>4.645449640017119</v>
@@ -1997,13 +1997,13 @@
         <v>2.757381255040436</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252224498513669</v>
+        <v>0.7252224498513666</v>
       </c>
       <c r="V18" t="n">
         <v>0.4673692249775152</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6763948375165297</v>
+        <v>0.6763948375165296</v>
       </c>
       <c r="X18" t="n">
         <v>8.00955846185372</v>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E2" t="n">
         <v>9959</v>
@@ -577,7 +577,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9958</v>
+        <v>9959</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         <v>36161</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L2" t="n">
         <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>102.8998662716744</v>
+        <v>102.8901293637246</v>
       </c>
       <c r="N2" t="n">
         <v>118.97</v>
@@ -606,37 +606,37 @@
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>95.32746005787514</v>
+        <v>95.32771092231937</v>
       </c>
       <c r="Q2" t="n">
         <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.572406213799228</v>
+        <v>-7.562418441405232</v>
       </c>
       <c r="S2" t="n">
-        <v>22.65783173651169</v>
+        <v>22.66619598107006</v>
       </c>
       <c r="T2" t="n">
-        <v>31.54070844801757</v>
+        <v>31.55513436670174</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1351208062408296</v>
+        <v>0.1348298539431507</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3252880124995701</v>
+        <v>-0.3249672092626599</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06483100351578397</v>
+        <v>0.06442112808095746</v>
       </c>
       <c r="X2" t="n">
-        <v>88.94841056899354</v>
+        <v>91.11390972185244</v>
       </c>
       <c r="Y2" t="n">
-        <v>97.08795894066915</v>
+        <v>97.69369833179732</v>
       </c>
       <c r="Z2" t="n">
-        <v>105.5563859801998</v>
+        <v>104.6407543583591</v>
       </c>
     </row>
     <row r="3">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E3" t="n">
+        <v>14538</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14537</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14536</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         <v>30317</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L3" t="n">
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>4.906862100990645</v>
+        <v>4.906774953566761</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
@@ -692,37 +692,37 @@
         <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>4.95559517118877</v>
+        <v>4.955525799308179</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04873307019812478</v>
+        <v>0.04875084574141872</v>
       </c>
       <c r="S3" t="n">
-        <v>1.354049271353809</v>
+        <v>1.353957210340001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729846176193558</v>
+        <v>1.729780711652324</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784481465785061</v>
+        <v>0.7784515602343153</v>
       </c>
       <c r="V3" t="n">
-        <v>0.564347426187931</v>
+        <v>0.5643574333119465</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774672527515456</v>
+        <v>0.777469755775442</v>
       </c>
       <c r="X3" t="n">
-        <v>2.908274702068205</v>
+        <v>2.848013924775333</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.403035439589797</v>
+        <v>3.319812766613585</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.722180496520003</v>
+        <v>3.719734910267425</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E4" t="n">
         <v>10219</v>
@@ -749,7 +749,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10218</v>
+        <v>10219</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -763,52 +763,52 @@
         <v>35065</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="M4" t="n">
-        <v>6.919521677431983</v>
+        <v>6.91938863881006</v>
       </c>
       <c r="N4" t="n">
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5046004908216271</v>
+        <v>0.5042548413987871</v>
       </c>
       <c r="P4" t="n">
-        <v>7.238063367407995</v>
+        <v>7.237779016971388</v>
       </c>
       <c r="Q4" t="n">
         <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3185416899760126</v>
+        <v>0.3183903781613278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.29003228040476</v>
+        <v>1.289944941951443</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677502997254421</v>
+        <v>1.677422985376267</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680602342838106</v>
+        <v>0.8680614391652761</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392141790524942</v>
+        <v>0.7392179072869149</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8471789954629139</v>
+        <v>0.8472057005173457</v>
       </c>
       <c r="X4" t="n">
-        <v>4.728180555913503</v>
+        <v>4.720645423709897</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.875882186484379</v>
+        <v>4.819133891730353</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.143749694598814</v>
+        <v>4.9933731699336</v>
       </c>
     </row>
     <row r="5">
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E5" t="n">
+        <v>8831</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8830</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8829</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>36892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.729960357911428</v>
+        <v>6.730098527746319</v>
       </c>
       <c r="N5" t="n">
         <v>10.6125</v>
@@ -864,37 +864,37 @@
         <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>6.922908532664749</v>
+        <v>6.923231021263554</v>
       </c>
       <c r="Q5" t="n">
         <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1929481747533212</v>
+        <v>0.1931324935172344</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446704682318504</v>
+        <v>1.446708616991822</v>
       </c>
       <c r="T5" t="n">
-        <v>1.84493523233121</v>
+        <v>1.844937105578919</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963222612737365</v>
+        <v>0.2963144371454246</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1164564676933406</v>
+        <v>-0.1165234530185957</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473760116108497</v>
+        <v>0.2473803246145574</v>
       </c>
       <c r="X5" t="n">
-        <v>6.730177169417159</v>
+        <v>6.687429295000265</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.945944196930904</v>
+        <v>6.898445201385703</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.184174667080817</v>
+        <v>7.138061333848699</v>
       </c>
     </row>
     <row r="6">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E6" t="n">
+        <v>14193</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14192</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14191</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>31048</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L6" t="n">
         <v>1.025</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582752977239095</v>
+        <v>5.582753487880496</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
@@ -950,37 +950,37 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585567775854428</v>
+        <v>5.585547899441337</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002814798615333034</v>
+        <v>0.002794411560841684</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162643181347835</v>
+        <v>1.162589802413234</v>
       </c>
       <c r="T6" t="n">
-        <v>1.50087574663464</v>
+        <v>1.500808618774979</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076568036606872</v>
+        <v>0.5076632235851052</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06657445983433918</v>
+        <v>0.06659218579725046</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045773265450827</v>
+        <v>0.5045830039942141</v>
       </c>
       <c r="X6" t="n">
-        <v>5.878415660464427</v>
+        <v>5.841270304737385</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.083414698648705</v>
+        <v>6.042829892313495</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.236250653327139</v>
+        <v>6.234118721836728</v>
       </c>
     </row>
     <row r="7">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E7" t="n">
+        <v>8991</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8990</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8989</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>36161</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L7" t="n">
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880546779397041</v>
+        <v>7.880558954393772</v>
       </c>
       <c r="N7" t="n">
         <v>15.14</v>
@@ -1036,37 +1036,37 @@
         <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>8.092883009536809</v>
+        <v>8.092968168291826</v>
       </c>
       <c r="Q7" t="n">
         <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2123362301397671</v>
+        <v>0.2124092138980552</v>
       </c>
       <c r="S7" t="n">
-        <v>1.421452047766606</v>
+        <v>1.42163079289638</v>
       </c>
       <c r="T7" t="n">
-        <v>1.794082418672475</v>
+        <v>1.794353616329833</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8126202758292573</v>
+        <v>0.8125379397481374</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6416581295846144</v>
+        <v>0.641509962466041</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7980112678053489</v>
+        <v>0.7979203711592324</v>
       </c>
       <c r="X7" t="n">
-        <v>5.59670893584352</v>
+        <v>5.535450259362285</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.036176288569788</v>
+        <v>5.957435211433337</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.369554136184569</v>
+        <v>6.374288318080099</v>
       </c>
     </row>
     <row r="8">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E8" t="n">
+        <v>13856</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13855</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13854</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L8" t="n">
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616767540060632</v>
+        <v>7.616690544929628</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
@@ -1122,37 +1122,37 @@
         <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>7.660173914957888</v>
+        <v>7.660105984257958</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04340637489725574</v>
+        <v>0.04341543932832881</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502691569092577</v>
+        <v>1.502616445702726</v>
       </c>
       <c r="T8" t="n">
-        <v>1.962010555323946</v>
+        <v>1.961935714028187</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529665376219867</v>
+        <v>0.7529684752282861</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156512808842362</v>
+        <v>0.5156582784985032</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520061525744329</v>
+        <v>0.7520074309317248</v>
       </c>
       <c r="X8" t="n">
-        <v>6.06431821309257</v>
+        <v>5.983842080053911</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.614317863657368</v>
+        <v>6.497463462005913</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.131657936470599</v>
+        <v>7.092535412279281</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74297400224312</v>
+        <v>10.74282398684392</v>
       </c>
       <c r="Q9" t="n">
         <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4379144625053638</v>
+        <v>0.4377644471061643</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15136414431218</v>
+        <v>2.151350966384145</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874434500205714</v>
+        <v>2.874410358005736</v>
       </c>
       <c r="U9" t="n">
-        <v>0.330765323555493</v>
+        <v>0.3307922998606091</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2716760370619904</v>
+        <v>-0.271654675692814</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3250901859353446</v>
+        <v>0.3251224932292014</v>
       </c>
       <c r="X9" t="n">
-        <v>9.908184584954775</v>
+        <v>9.894349717847238</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.27613984984273</v>
+        <v>10.21363869315348</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.66121806310734</v>
+        <v>10.78342560509235</v>
       </c>
     </row>
     <row r="10">
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E10" t="n">
+        <v>13797</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13796</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13795</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         <v>31413</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L10" t="n">
         <v>0.4375</v>
       </c>
       <c r="M10" t="n">
-        <v>5.246111090974992</v>
+        <v>5.246009894172224</v>
       </c>
       <c r="N10" t="n">
         <v>10.15</v>
@@ -1294,37 +1294,37 @@
         <v>0.4490779286658197</v>
       </c>
       <c r="P10" t="n">
-        <v>5.218972936189636</v>
+        <v>5.218835647866789</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02713815478535559</v>
+        <v>-0.02717424630543453</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160722426250821</v>
+        <v>1.160682329177553</v>
       </c>
       <c r="T10" t="n">
-        <v>1.481798520620404</v>
+        <v>1.481758911613596</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4296555478169507</v>
+        <v>0.4296971466287318</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08927253295033477</v>
+        <v>-0.08921691634568707</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4276690859409936</v>
+        <v>0.4277122703930689</v>
       </c>
       <c r="X10" t="n">
-        <v>4.406099944577184</v>
+        <v>4.342615204771958</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.675104309026638</v>
+        <v>4.669756533252069</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.308118535165622</v>
+        <v>5.49135637650624</v>
       </c>
     </row>
     <row r="11">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E11" t="n">
+        <v>4115</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4114</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4113</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         <v>41640</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L11" t="n">
         <v>2.195</v>
       </c>
       <c r="M11" t="n">
-        <v>7.496862995380502</v>
+        <v>7.496389766650462</v>
       </c>
       <c r="N11" t="n">
         <v>19.1775</v>
@@ -1380,37 +1380,37 @@
         <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>7.713412030842163</v>
+        <v>7.712943956940581</v>
       </c>
       <c r="Q11" t="n">
         <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2165490354616622</v>
+        <v>0.216554190290119</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9632600483966266</v>
+        <v>0.9630766629672474</v>
       </c>
       <c r="T11" t="n">
-        <v>1.342936651703074</v>
+        <v>1.342763916061838</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7907622661354154</v>
+        <v>0.7908049698376037</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5650631595275413</v>
+        <v>0.5651659355842318</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7884389878192266</v>
+        <v>0.7884830666339837</v>
       </c>
       <c r="X11" t="n">
-        <v>4.861199235195812</v>
+        <v>4.936913930289047</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.224133290969142</v>
+        <v>5.217380181101914</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.401311783857174</v>
+        <v>5.346197382112028</v>
       </c>
     </row>
     <row r="12">
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E12" t="n">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -1463,40 +1463,40 @@
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.949464738881011</v>
+        <v>2.950919359918645</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01634847764179</v>
+        <v>10.01655395030387</v>
       </c>
       <c r="Q12" t="n">
         <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3972919226376544</v>
+        <v>0.397497395299737</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683293167765912</v>
+        <v>1.683296807952146</v>
       </c>
       <c r="T12" t="n">
-        <v>2.138088529178442</v>
+        <v>2.138084341118466</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253745321604735</v>
+        <v>0.8253712504189005</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6539130608040014</v>
+        <v>0.6539144166238553</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135567762143142</v>
+        <v>0.8135271148436152</v>
       </c>
       <c r="X12" t="n">
-        <v>7.638523148752649</v>
+        <v>7.527918493133351</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.036477192794568</v>
+        <v>7.914675621964551</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.621946243924967</v>
+        <v>8.403257281991904</v>
       </c>
     </row>
     <row r="13">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E13" t="n">
+        <v>14037</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14036</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14035</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         <v>30682</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L13" t="n">
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>8.134524225151408</v>
+        <v>8.134469756340838</v>
       </c>
       <c r="N13" t="n">
         <v>34.0025</v>
@@ -1552,37 +1552,37 @@
         <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211894504608958</v>
+        <v>8.211870744260445</v>
       </c>
       <c r="Q13" t="n">
         <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07737027945755186</v>
+        <v>0.0774009879196083</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786868940432639</v>
+        <v>1.786843937290656</v>
       </c>
       <c r="T13" t="n">
-        <v>2.321854034492398</v>
+        <v>2.321827803535769</v>
       </c>
       <c r="U13" t="n">
-        <v>0.77621909933306</v>
+        <v>0.77620625943993</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5510210056145823</v>
+        <v>0.551000718121724</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7760077411626635</v>
+        <v>0.7759948686120691</v>
       </c>
       <c r="X13" t="n">
-        <v>6.392719712612755</v>
+        <v>6.353614048835431</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.561024153221164</v>
+        <v>6.525813714049566</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.722848953602786</v>
+        <v>6.695515236014383</v>
       </c>
     </row>
     <row r="14">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1638,37 +1638,37 @@
         <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>11.8334932346131</v>
+        <v>11.83334478182638</v>
       </c>
       <c r="Q14" t="n">
         <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1303886627731586</v>
+        <v>-0.1305371155598752</v>
       </c>
       <c r="S14" t="n">
-        <v>2.043020628208298</v>
+        <v>2.043044166754517</v>
       </c>
       <c r="T14" t="n">
-        <v>2.658794417052651</v>
+        <v>2.658809865229781</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009695249964964</v>
+        <v>0.8009736439519193</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207592273269162</v>
+        <v>0.6207548203704298</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7923958344475075</v>
+        <v>0.7924091281783679</v>
       </c>
       <c r="X14" t="n">
-        <v>8.214536191178311</v>
+        <v>8.154926381494922</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.670374084533359</v>
+        <v>8.576137216650341</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.037183390929531</v>
+        <v>8.929891277214288</v>
       </c>
     </row>
     <row r="15">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E15" t="n">
+        <v>9800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9799</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9798</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         <v>35804</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L15" t="n">
         <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>8.409926855820915</v>
+        <v>8.40976766336701</v>
       </c>
       <c r="N15" t="n">
         <v>131.9</v>
@@ -1724,37 +1724,37 @@
         <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>9.377122318821856</v>
+        <v>9.37693624721066</v>
       </c>
       <c r="Q15" t="n">
         <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9671954630009391</v>
+        <v>0.9671685838436495</v>
       </c>
       <c r="S15" t="n">
-        <v>4.182932932296252</v>
+        <v>4.182989029323052</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62202662827685</v>
+        <v>11.62154982109379</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03402684499361658</v>
+        <v>0.03401195738048901</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7611965581936886</v>
+        <v>-0.761226083975417</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02209301490129234</v>
+        <v>0.02207855829538707</v>
       </c>
       <c r="X15" t="n">
-        <v>11.14463348656781</v>
+        <v>10.96945705943471</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.70025366970526</v>
+        <v>11.57874351453578</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.11729634183836</v>
+        <v>12.03817048285889</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1810,37 +1810,37 @@
         <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927502840576494</v>
+        <v>6.927498349112612</v>
       </c>
       <c r="Q16" t="n">
         <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443694349365816</v>
+        <v>0.3443649434726979</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971914093315039</v>
+        <v>1.971945529249868</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479850117799189</v>
+        <v>2.479877022155442</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5335025157883488</v>
+        <v>0.533497339233504</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08994252730442509</v>
+        <v>0.08992278043093593</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283666028000781</v>
+        <v>0.5283627445984957</v>
       </c>
       <c r="X16" t="n">
-        <v>3.597791638580349</v>
+        <v>3.680750957251655</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.425736345971985</v>
+        <v>4.311300944058082</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.327172175625766</v>
+        <v>6.326454167072461</v>
       </c>
     </row>
     <row r="17">
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E17" t="n">
+        <v>3203</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3202</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3201</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         <v>42370</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L17" t="n">
         <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6.504075288972196</v>
+        <v>6.503411930043721</v>
       </c>
       <c r="N17" t="n">
         <v>18.4925</v>
@@ -1896,37 +1896,37 @@
         <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>6.729406294169347</v>
+        <v>6.728596335689756</v>
       </c>
       <c r="Q17" t="n">
         <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2253310051971512</v>
+        <v>0.225184405646033</v>
       </c>
       <c r="S17" t="n">
-        <v>1.089131073274831</v>
+        <v>1.089047415881351</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478428450564475</v>
+        <v>1.478248424789303</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6073809690217241</v>
+        <v>0.6075637421685574</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2263332422418055</v>
+        <v>0.2266657011421501</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6038688286289535</v>
+        <v>0.6040580651929409</v>
       </c>
       <c r="X17" t="n">
-        <v>4.645449640017119</v>
+        <v>4.757431817730801</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.407649912928195</v>
+        <v>5.307672170218031</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.869415796338449</v>
+        <v>6.476579968536771</v>
       </c>
     </row>
     <row r="18">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16654</v>
+        <v>16655</v>
       </c>
       <c r="E18" t="n">
+        <v>7157</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7156</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7155</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1967,52 +1967,52 @@
         <v>37987</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L18" t="n">
         <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>10.37831236897275</v>
+        <v>10.37717230296255</v>
       </c>
       <c r="N18" t="n">
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.779425692614537</v>
+        <v>4.763616119547357</v>
       </c>
       <c r="P18" t="n">
-        <v>11.16863363269499</v>
+        <v>11.16774229057527</v>
       </c>
       <c r="Q18" t="n">
         <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7903212637222425</v>
+        <v>0.7905699876127182</v>
       </c>
       <c r="S18" t="n">
-        <v>2.03659228236621</v>
+        <v>2.037071377942448</v>
       </c>
       <c r="T18" t="n">
-        <v>2.757381255040436</v>
+        <v>2.75802267042174</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252224498513666</v>
+        <v>0.7252334199417133</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4673692249775152</v>
+        <v>0.4673939528008918</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6763948375165296</v>
+        <v>0.6763745936262493</v>
       </c>
       <c r="X18" t="n">
-        <v>8.00955846185372</v>
+        <v>7.999442591833116</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.143818256209778</v>
+        <v>8.085808437401571</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.516197587701171</v>
+        <v>8.152149710361638</v>
       </c>
     </row>
   </sheetData>
@@ -2081,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>8.00955846185372</v>
+        <v>7.999442591833116</v>
       </c>
       <c r="G2" t="n">
-        <v>8.143818256209778</v>
+        <v>8.085808437401569</v>
       </c>
       <c r="H2" t="n">
-        <v>8.516197587701171</v>
+        <v>8.152149710361638</v>
       </c>
     </row>
     <row r="3">
@@ -2109,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.878415660464427</v>
+        <v>5.841270304737385</v>
       </c>
       <c r="G3" t="n">
-        <v>6.083414698648706</v>
+        <v>6.042829892313496</v>
       </c>
       <c r="H3" t="n">
-        <v>6.236250653327139</v>
+        <v>6.234118721836728</v>
       </c>
     </row>
     <row r="4">
@@ -2137,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.406099944577184</v>
+        <v>4.342615204771958</v>
       </c>
       <c r="G4" t="n">
-        <v>4.675104309026639</v>
+        <v>4.669756533252069</v>
       </c>
       <c r="H4" t="n">
-        <v>5.308118535165622</v>
+        <v>5.49135637650624</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.14463348656781</v>
+        <v>10.96945705943471</v>
       </c>
       <c r="G5" t="n">
-        <v>11.70025366970526</v>
+        <v>11.57874351453578</v>
       </c>
       <c r="H5" t="n">
-        <v>12.11729634183836</v>
+        <v>12.03817048285889</v>
       </c>
     </row>
     <row r="6">
@@ -2193,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>88.94841056899354</v>
+        <v>91.11390972185244</v>
       </c>
       <c r="G6" t="n">
-        <v>97.08795894066915</v>
+        <v>97.69369833179734</v>
       </c>
       <c r="H6" t="n">
-        <v>105.5563859801998</v>
+        <v>104.6407543583591</v>
       </c>
     </row>
     <row r="7">
@@ -2221,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.214536191178311</v>
+        <v>8.154926381494922</v>
       </c>
       <c r="G7" t="n">
-        <v>8.670374084533361</v>
+        <v>8.576137216650343</v>
       </c>
       <c r="H7" t="n">
-        <v>9.037183390929531</v>
+        <v>8.929891277214288</v>
       </c>
     </row>
     <row r="8">
@@ -2249,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.638523148752649</v>
+        <v>7.527918493133351</v>
       </c>
       <c r="G8" t="n">
-        <v>8.036477192794568</v>
+        <v>7.914675621964551</v>
       </c>
       <c r="H8" t="n">
-        <v>8.621946243924967</v>
+        <v>8.403257281991904</v>
       </c>
     </row>
     <row r="9">
@@ -2277,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.861199235195812</v>
+        <v>4.936913930289047</v>
       </c>
       <c r="G9" t="n">
-        <v>5.224133290969143</v>
+        <v>5.217380181101914</v>
       </c>
       <c r="H9" t="n">
-        <v>5.401311783857174</v>
+        <v>5.346197382112028</v>
       </c>
     </row>
     <row r="10">
@@ -2305,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.59670893584352</v>
+        <v>5.535450259362285</v>
       </c>
       <c r="G10" t="n">
-        <v>6.036176288569789</v>
+        <v>5.957435211433337</v>
       </c>
       <c r="H10" t="n">
-        <v>6.369554136184569</v>
+        <v>6.374288318080099</v>
       </c>
     </row>
     <row r="11">
@@ -2333,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.597791638580349</v>
+        <v>3.680750957251655</v>
       </c>
       <c r="G11" t="n">
-        <v>4.425736345971985</v>
+        <v>4.311300944058082</v>
       </c>
       <c r="H11" t="n">
-        <v>6.327172175625766</v>
+        <v>6.326454167072461</v>
       </c>
     </row>
     <row r="12">
@@ -2361,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.392719712612755</v>
+        <v>6.353614048835431</v>
       </c>
       <c r="G12" t="n">
-        <v>6.561024153221164</v>
+        <v>6.525813714049566</v>
       </c>
       <c r="H12" t="n">
-        <v>6.722848953602786</v>
+        <v>6.695515236014383</v>
       </c>
     </row>
     <row r="13">
@@ -2389,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.908184584954775</v>
+        <v>9.894349717847238</v>
       </c>
       <c r="G13" t="n">
-        <v>10.27613984984273</v>
+        <v>10.21363869315348</v>
       </c>
       <c r="H13" t="n">
-        <v>10.66121806310734</v>
+        <v>10.78342560509235</v>
       </c>
     </row>
     <row r="14">
@@ -2417,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>6.06431821309257</v>
+        <v>5.983842080053911</v>
       </c>
       <c r="G14" t="n">
-        <v>6.614317863657369</v>
+        <v>6.497463462005913</v>
       </c>
       <c r="H14" t="n">
-        <v>7.131657936470599</v>
+        <v>7.092535412279281</v>
       </c>
     </row>
     <row r="15">
@@ -2445,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.730177169417159</v>
+        <v>6.687429295000265</v>
       </c>
       <c r="G15" t="n">
-        <v>6.945944196930904</v>
+        <v>6.898445201385703</v>
       </c>
       <c r="H15" t="n">
-        <v>7.184174667080817</v>
+        <v>7.138061333848699</v>
       </c>
     </row>
     <row r="16">
@@ -2473,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.645449640017119</v>
+        <v>4.757431817730801</v>
       </c>
       <c r="G16" t="n">
-        <v>5.407649912928195</v>
+        <v>5.307672170218032</v>
       </c>
       <c r="H16" t="n">
-        <v>6.869415796338449</v>
+        <v>6.476579968536771</v>
       </c>
     </row>
     <row r="17">
@@ -2501,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.728180555913503</v>
+        <v>4.720645423709897</v>
       </c>
       <c r="G17" t="n">
-        <v>4.87588218648438</v>
+        <v>4.819133891730353</v>
       </c>
       <c r="H17" t="n">
-        <v>5.143749694598814</v>
+        <v>4.9933731699336</v>
       </c>
     </row>
     <row r="18">
@@ -2529,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.908274702068205</v>
+        <v>2.848013924775333</v>
       </c>
       <c r="G18" t="n">
-        <v>3.403035439589797</v>
+        <v>3.319812766613585</v>
       </c>
       <c r="H18" t="n">
-        <v>3.722180496520003</v>
+        <v>3.719734910267425</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E2" t="n">
         <v>9959</v>
@@ -606,37 +606,37 @@
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>95.32771092231937</v>
+        <v>95.32741531987904</v>
       </c>
       <c r="Q2" t="n">
         <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.562418441405232</v>
+        <v>-7.562714043845553</v>
       </c>
       <c r="S2" t="n">
-        <v>22.66619598107006</v>
+        <v>22.66648011805397</v>
       </c>
       <c r="T2" t="n">
-        <v>31.55513436670174</v>
+        <v>31.55536094560263</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1348298539431507</v>
+        <v>0.1348266406889619</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3249672092626599</v>
+        <v>-0.3249862369548453</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06442112808095746</v>
+        <v>0.06442113433485186</v>
       </c>
       <c r="X2" t="n">
-        <v>91.11390972185244</v>
+        <v>88.71926840947754</v>
       </c>
       <c r="Y2" t="n">
-        <v>97.69369833179732</v>
+        <v>93.90852521107296</v>
       </c>
       <c r="Z2" t="n">
-        <v>104.6407543583591</v>
+        <v>103.545009483644</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E3" t="n">
         <v>14538</v>
@@ -663,7 +663,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14537</v>
+        <v>14538</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         <v>30317</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L3" t="n">
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>4.906774953566761</v>
+        <v>4.906685066721694</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
@@ -692,37 +692,37 @@
         <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955525799308179</v>
+        <v>4.955328913551968</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04875084574141872</v>
+        <v>0.04864384683027237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.353957210340001</v>
+        <v>1.353866109052305</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729780711652324</v>
+        <v>1.72971914927921</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784515602343153</v>
+        <v>0.7784632111736615</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643574333119465</v>
+        <v>0.5643659260065242</v>
       </c>
       <c r="W3" t="n">
-        <v>0.777469755775442</v>
+        <v>0.7774855416902485</v>
       </c>
       <c r="X3" t="n">
-        <v>2.848013924775333</v>
+        <v>2.786274782923502</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.319812766613585</v>
+        <v>3.22390112725679</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.719734910267425</v>
+        <v>3.716176609818405</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E4" t="n">
         <v>10219</v>
@@ -775,40 +775,40 @@
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5042548413987871</v>
+        <v>0.503909684704989</v>
       </c>
       <c r="P4" t="n">
-        <v>7.237779016971388</v>
+        <v>7.237699721549809</v>
       </c>
       <c r="Q4" t="n">
         <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3183903781613278</v>
+        <v>0.3183110827397495</v>
       </c>
       <c r="S4" t="n">
-        <v>1.289944941951443</v>
+        <v>1.28994302695558</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677422985376267</v>
+        <v>1.677420108559649</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680614391652761</v>
+        <v>0.8680619959674725</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392179072869149</v>
+        <v>0.7392188017799812</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8472057005173457</v>
+        <v>0.8472235570844796</v>
       </c>
       <c r="X4" t="n">
-        <v>4.720645423709897</v>
+        <v>4.702348657004088</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.819133891730353</v>
+        <v>4.77641137838293</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.9933731699336</v>
+        <v>4.844329609199468</v>
       </c>
     </row>
     <row r="5">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E5" t="n">
         <v>8831</v>
@@ -835,7 +835,7 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8830</v>
+        <v>8831</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>36892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.730098527746319</v>
+        <v>6.730240063412977</v>
       </c>
       <c r="N5" t="n">
         <v>10.6125</v>
@@ -864,37 +864,37 @@
         <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>6.923231021263554</v>
+        <v>6.923252201004961</v>
       </c>
       <c r="Q5" t="n">
         <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931324935172344</v>
+        <v>0.1930121375919838</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446708616991822</v>
+        <v>1.44665702182825</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844937105578919</v>
+        <v>1.844875186589797</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963144371454246</v>
+        <v>0.2963187104745749</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1165234530185957</v>
+        <v>-0.1165101576590812</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473803246145574</v>
+        <v>0.2473880633014304</v>
       </c>
       <c r="X5" t="n">
-        <v>6.687429295000265</v>
+        <v>6.635635249521554</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.898445201385703</v>
+        <v>6.845831844242211</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.138061333848699</v>
+        <v>7.077302882147989</v>
       </c>
     </row>
     <row r="6">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E6" t="n">
         <v>14193</v>
@@ -921,7 +921,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>14192</v>
+        <v>14193</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>31048</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L6" t="n">
         <v>1.025</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582753487880496</v>
+        <v>5.582744134432468</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
@@ -950,37 +950,37 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585547899441337</v>
+        <v>5.585540397973577</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002794411560841684</v>
+        <v>0.002796263541109814</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162589802413234</v>
+        <v>1.162570644465137</v>
       </c>
       <c r="T6" t="n">
-        <v>1.500808618774979</v>
+        <v>1.500774587985406</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076632235851052</v>
+        <v>0.507656897390259</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06659218579725046</v>
+        <v>0.06656922859797199</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045830039942141</v>
+        <v>0.5045781169913075</v>
       </c>
       <c r="X6" t="n">
-        <v>5.841270304737385</v>
+        <v>5.778674430305634</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.042829892313495</v>
+        <v>5.993550747597633</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.234118721836728</v>
+        <v>6.220392731897288</v>
       </c>
     </row>
     <row r="7">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E7" t="n">
         <v>8991</v>
@@ -1007,7 +1007,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8990</v>
+        <v>8991</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>36161</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L7" t="n">
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880558954393772</v>
+        <v>7.880571126682238</v>
       </c>
       <c r="N7" t="n">
         <v>15.14</v>
@@ -1036,37 +1036,37 @@
         <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>8.092968168291826</v>
+        <v>8.092626091878373</v>
       </c>
       <c r="Q7" t="n">
         <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2124092138980552</v>
+        <v>0.2120549651961344</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42163079289638</v>
+        <v>1.421650909998138</v>
       </c>
       <c r="T7" t="n">
-        <v>1.794353616329833</v>
+        <v>1.794326543509386</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8125379397481374</v>
+        <v>0.8125226695868086</v>
       </c>
       <c r="V7" t="n">
-        <v>0.641509962466041</v>
+        <v>0.6414809578720708</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7979203711592324</v>
+        <v>0.7979372272793581</v>
       </c>
       <c r="X7" t="n">
-        <v>5.535450259362285</v>
+        <v>5.465709112516045</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.957435211433337</v>
+        <v>5.864012272780123</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.374288318080099</v>
+        <v>6.342392215017304</v>
       </c>
     </row>
     <row r="8">
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E8" t="n">
         <v>13856</v>
@@ -1093,7 +1093,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>13855</v>
+        <v>13856</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L8" t="n">
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616690544929628</v>
+        <v>7.616612117494226</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
@@ -1122,37 +1122,37 @@
         <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>7.660105984257958</v>
+        <v>7.659937698784861</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04341543932832881</v>
+        <v>0.04332558129063499</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502616445702726</v>
+        <v>1.502557489313858</v>
       </c>
       <c r="T8" t="n">
-        <v>1.961935714028187</v>
+        <v>1.961870959056085</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529684752282861</v>
+        <v>0.7529776904289334</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156582784985032</v>
+        <v>0.5156604884582825</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520074309317248</v>
+        <v>0.7520200326624376</v>
       </c>
       <c r="X8" t="n">
-        <v>5.983842080053911</v>
+        <v>5.874910157446822</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.497463462005913</v>
+        <v>6.372076500948078</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.092535412279281</v>
+        <v>6.981131900650488</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74282398684392</v>
+        <v>10.74267408248077</v>
       </c>
       <c r="Q9" t="n">
         <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4377644471061643</v>
+        <v>0.4376145427430093</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151350966384145</v>
+        <v>2.151337969359972</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874410358005736</v>
+        <v>2.874386262816496</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3307922998606091</v>
+        <v>0.3308192857035197</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.271654675692814</v>
+        <v>-0.2716333560983115</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3251224932292014</v>
+        <v>0.3251548106320369</v>
       </c>
       <c r="X9" t="n">
-        <v>9.894349717847238</v>
+        <v>9.789444247440565</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.21363869315348</v>
+        <v>10.10914520265792</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.78342560509235</v>
+        <v>10.37908160050649</v>
       </c>
     </row>
     <row r="10">
@@ -1256,7 +1256,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E10" t="n">
         <v>13797</v>
@@ -1265,7 +1265,7 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>13796</v>
+        <v>13797</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         <v>31413</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L10" t="n">
         <v>0.4375</v>
       </c>
       <c r="M10" t="n">
-        <v>5.246009894172224</v>
+        <v>5.245903638472131</v>
       </c>
       <c r="N10" t="n">
         <v>10.15</v>
@@ -1294,37 +1294,37 @@
         <v>0.4490779286658197</v>
       </c>
       <c r="P10" t="n">
-        <v>5.218835647866789</v>
+        <v>5.218752068863286</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02717424630543453</v>
+        <v>-0.02715156960884612</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160682329177553</v>
+        <v>1.160663642749955</v>
       </c>
       <c r="T10" t="n">
-        <v>1.481758911613596</v>
+        <v>1.481735009804921</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4296971466287318</v>
+        <v>0.4297203499208604</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08921691634568707</v>
+        <v>-0.08917655812414438</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4277122703930689</v>
+        <v>0.4277357844612971</v>
       </c>
       <c r="X10" t="n">
-        <v>4.342615204771958</v>
+        <v>4.313173749197579</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.669756533252069</v>
+        <v>4.54132205164761</v>
       </c>
       <c r="Z10" t="n">
-        <v>5.49135637650624</v>
+        <v>4.80479549559218</v>
       </c>
     </row>
     <row r="11">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E11" t="n">
         <v>4115</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         <v>41640</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L11" t="n">
         <v>2.195</v>
       </c>
       <c r="M11" t="n">
-        <v>7.496389766650462</v>
+        <v>7.495851154313487</v>
       </c>
       <c r="N11" t="n">
         <v>19.1775</v>
@@ -1380,37 +1380,37 @@
         <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>7.712943956940581</v>
+        <v>7.712329228490995</v>
       </c>
       <c r="Q11" t="n">
         <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.216554190290119</v>
+        <v>0.2164780741775076</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9630766629672474</v>
+        <v>0.9628432361954222</v>
       </c>
       <c r="T11" t="n">
-        <v>1.342763916061838</v>
+        <v>1.342601641605984</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7908049698376037</v>
+        <v>0.7908726642392341</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5651659355842318</v>
+        <v>0.5652905132306503</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7884830666339837</v>
+        <v>0.788548451193079</v>
       </c>
       <c r="X11" t="n">
-        <v>4.936913930289047</v>
+        <v>4.830641002960155</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.217380181101914</v>
+        <v>5.157611375445773</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.346197382112028</v>
+        <v>5.345664197048527</v>
       </c>
     </row>
     <row r="12">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E12" t="n">
         <v>6449</v>
@@ -1437,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>6448</v>
+        <v>6449</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1451,52 +1451,52 @@
         <v>39083</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="L12" t="n">
         <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>9.619056555004134</v>
+        <v>9.618769835116556</v>
       </c>
       <c r="N12" t="n">
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.950919359918645</v>
+        <v>2.949938847003706</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01655395030387</v>
+        <v>10.01606573113089</v>
       </c>
       <c r="Q12" t="n">
         <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.397497395299737</v>
+        <v>0.3972958960143328</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683296807952146</v>
+        <v>1.683032230251143</v>
       </c>
       <c r="T12" t="n">
-        <v>2.138084341118466</v>
+        <v>2.137812244904523</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253712504189005</v>
+        <v>0.8253996194585755</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6539144166238553</v>
+        <v>0.6539627270253066</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135271148436152</v>
+        <v>0.8135759195940824</v>
       </c>
       <c r="X12" t="n">
-        <v>7.527918493133351</v>
+        <v>7.412643419006733</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.914675621964551</v>
+        <v>7.808961144625357</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.403257281991904</v>
+        <v>8.200975680169341</v>
       </c>
     </row>
     <row r="13">
@@ -1514,7 +1514,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E13" t="n">
         <v>14037</v>
@@ -1523,7 +1523,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>14036</v>
+        <v>14037</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         <v>30682</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L13" t="n">
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>8.134469756340838</v>
+        <v>8.134408171261665</v>
       </c>
       <c r="N13" t="n">
         <v>34.0025</v>
@@ -1552,37 +1552,37 @@
         <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211870744260445</v>
+        <v>8.211592249321622</v>
       </c>
       <c r="Q13" t="n">
         <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0774009879196083</v>
+        <v>0.07718407805995597</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786843937290656</v>
+        <v>1.786655194584772</v>
       </c>
       <c r="T13" t="n">
-        <v>2.321827803535769</v>
+        <v>2.32165546126316</v>
       </c>
       <c r="U13" t="n">
-        <v>0.77620625943993</v>
+        <v>0.7762351470941621</v>
       </c>
       <c r="V13" t="n">
-        <v>0.551000718121724</v>
+        <v>0.551037377771278</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7759948686120691</v>
+        <v>0.7760243693735041</v>
       </c>
       <c r="X13" t="n">
-        <v>6.353614048835431</v>
+        <v>6.305315894748492</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.525813714049566</v>
+        <v>6.480178475840186</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.695515236014383</v>
+        <v>6.652111576946956</v>
       </c>
     </row>
     <row r="14">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1638,37 +1638,37 @@
         <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83334478182638</v>
+        <v>11.83319654066159</v>
       </c>
       <c r="Q14" t="n">
         <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1305371155598752</v>
+        <v>-0.1306853567246579</v>
       </c>
       <c r="S14" t="n">
-        <v>2.043044166754517</v>
+        <v>2.043067671746144</v>
       </c>
       <c r="T14" t="n">
-        <v>2.658809865229781</v>
+        <v>2.6588254518321</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009736439519193</v>
+        <v>0.8009777382732908</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207548203704298</v>
+        <v>0.6207503738989466</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7924091281783679</v>
+        <v>0.7924223849048234</v>
       </c>
       <c r="X14" t="n">
-        <v>8.154926381494922</v>
+        <v>8.100704530347437</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.576137216650341</v>
+        <v>8.488625415905204</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.929891277214288</v>
+        <v>8.850986301542065</v>
       </c>
     </row>
     <row r="15">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E15" t="n">
         <v>9800</v>
@@ -1695,7 +1695,7 @@
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>9799</v>
+        <v>9800</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         <v>35804</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L15" t="n">
         <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>8.40976766336701</v>
+        <v>8.409597278911564</v>
       </c>
       <c r="N15" t="n">
         <v>131.9</v>
@@ -1724,37 +1724,37 @@
         <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>9.37693624721066</v>
+        <v>9.377018103525684</v>
       </c>
       <c r="Q15" t="n">
         <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9671685838436495</v>
+        <v>0.9674208246141196</v>
       </c>
       <c r="S15" t="n">
-        <v>4.182989029323052</v>
+        <v>4.183047757646241</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62154982109379</v>
+        <v>11.6210693578073</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03401195738048901</v>
+        <v>0.03400212793373993</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.761226083975417</v>
+        <v>-0.7612536463888346</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02207855829538707</v>
+        <v>0.02206518263153723</v>
       </c>
       <c r="X15" t="n">
-        <v>10.96945705943471</v>
+        <v>10.82493208759487</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.57874351453578</v>
+        <v>11.44811476503503</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.03817048285889</v>
+        <v>11.96241612784637</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1810,37 +1810,37 @@
         <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927498349112612</v>
+        <v>6.927493829478454</v>
       </c>
       <c r="Q16" t="n">
         <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443649434726979</v>
+        <v>0.3443604238385402</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971945529249868</v>
+        <v>1.971976954945176</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479877022155442</v>
+        <v>2.479903959926924</v>
       </c>
       <c r="U16" t="n">
-        <v>0.533497339233504</v>
+        <v>0.5334921542519799</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08992278043093593</v>
+        <v>0.08990300881718005</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283627445984957</v>
+        <v>0.5283588794508602</v>
       </c>
       <c r="X16" t="n">
-        <v>3.680750957251655</v>
+        <v>3.417542897072725</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.311300944058082</v>
+        <v>4.046515215537529</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.326454167072461</v>
+        <v>5.121801330434913</v>
       </c>
     </row>
     <row r="17">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E17" t="n">
         <v>3203</v>
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         <v>42370</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L17" t="n">
         <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6.503411930043721</v>
+        <v>6.5026740555729</v>
       </c>
       <c r="N17" t="n">
         <v>18.4925</v>
@@ -1896,37 +1896,37 @@
         <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>6.728596335689756</v>
+        <v>6.728090406086487</v>
       </c>
       <c r="Q17" t="n">
         <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.225184405646033</v>
+        <v>0.2254163505135869</v>
       </c>
       <c r="S17" t="n">
-        <v>1.089047415881351</v>
+        <v>1.088960374618325</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478248424789303</v>
+        <v>1.478090198142928</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6075637421685574</v>
+        <v>0.6077381223020669</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2266657011421501</v>
+        <v>0.2270667977450529</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6040580651929409</v>
+        <v>0.6042135723664874</v>
       </c>
       <c r="X17" t="n">
-        <v>4.757431817730801</v>
+        <v>4.499103597989199</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.307672170218031</v>
+        <v>5.207199533252256</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.476579968536771</v>
+        <v>6.179453305744518</v>
       </c>
     </row>
     <row r="18">
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16655</v>
+        <v>16656</v>
       </c>
       <c r="E18" t="n">
         <v>7157</v>
@@ -1953,7 +1953,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>7156</v>
+        <v>7157</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1967,52 +1967,52 @@
         <v>37987</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="L18" t="n">
         <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>10.37717230296255</v>
+        <v>10.37605071957524</v>
       </c>
       <c r="N18" t="n">
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.763616119547357</v>
+        <v>4.762082151061103</v>
       </c>
       <c r="P18" t="n">
-        <v>11.16774229057527</v>
+        <v>11.16716464559427</v>
       </c>
       <c r="Q18" t="n">
         <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7905699876127182</v>
+        <v>0.7911139260190347</v>
       </c>
       <c r="S18" t="n">
-        <v>2.037071377942448</v>
+        <v>2.037572989096702</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75802267042174</v>
+        <v>2.758666400212955</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252334199417133</v>
+        <v>0.7252408126098214</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4673939528008918</v>
+        <v>0.4674065757276417</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6763745936262493</v>
+        <v>0.6762909907631836</v>
       </c>
       <c r="X18" t="n">
-        <v>7.999442591833116</v>
+        <v>7.924354754784328</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.085808437401571</v>
+        <v>8.046317934473063</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.152149710361638</v>
+        <v>8.127339883958451</v>
       </c>
     </row>
   </sheetData>
@@ -2081,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.999442591833116</v>
+        <v>7.924354754784328</v>
       </c>
       <c r="G2" t="n">
-        <v>8.085808437401569</v>
+        <v>8.046317934473063</v>
       </c>
       <c r="H2" t="n">
-        <v>8.152149710361638</v>
+        <v>8.127339883958451</v>
       </c>
     </row>
     <row r="3">
@@ -2109,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.841270304737385</v>
+        <v>5.778674430305634</v>
       </c>
       <c r="G3" t="n">
-        <v>6.042829892313496</v>
+        <v>5.993550747597632</v>
       </c>
       <c r="H3" t="n">
-        <v>6.234118721836728</v>
+        <v>6.220392731897288</v>
       </c>
     </row>
     <row r="4">
@@ -2137,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.342615204771958</v>
+        <v>4.313173749197579</v>
       </c>
       <c r="G4" t="n">
-        <v>4.669756533252069</v>
+        <v>4.54132205164761</v>
       </c>
       <c r="H4" t="n">
-        <v>5.49135637650624</v>
+        <v>4.80479549559218</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.96945705943471</v>
+        <v>10.82493208759487</v>
       </c>
       <c r="G5" t="n">
-        <v>11.57874351453578</v>
+        <v>11.44811476503503</v>
       </c>
       <c r="H5" t="n">
-        <v>12.03817048285889</v>
+        <v>11.96241612784637</v>
       </c>
     </row>
     <row r="6">
@@ -2193,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>91.11390972185244</v>
+        <v>88.71926840947754</v>
       </c>
       <c r="G6" t="n">
-        <v>97.69369833179734</v>
+        <v>93.90852521107294</v>
       </c>
       <c r="H6" t="n">
-        <v>104.6407543583591</v>
+        <v>103.545009483644</v>
       </c>
     </row>
     <row r="7">
@@ -2221,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.154926381494922</v>
+        <v>8.100704530347437</v>
       </c>
       <c r="G7" t="n">
-        <v>8.576137216650343</v>
+        <v>8.488625415905204</v>
       </c>
       <c r="H7" t="n">
-        <v>8.929891277214288</v>
+        <v>8.850986301542065</v>
       </c>
     </row>
     <row r="8">
@@ -2249,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.527918493133351</v>
+        <v>7.412643419006733</v>
       </c>
       <c r="G8" t="n">
-        <v>7.914675621964551</v>
+        <v>7.808961144625357</v>
       </c>
       <c r="H8" t="n">
-        <v>8.403257281991904</v>
+        <v>8.200975680169341</v>
       </c>
     </row>
     <row r="9">
@@ -2277,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.936913930289047</v>
+        <v>4.830641002960155</v>
       </c>
       <c r="G9" t="n">
-        <v>5.217380181101914</v>
+        <v>5.157611375445773</v>
       </c>
       <c r="H9" t="n">
-        <v>5.346197382112028</v>
+        <v>5.345664197048527</v>
       </c>
     </row>
     <row r="10">
@@ -2305,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.535450259362285</v>
+        <v>5.465709112516045</v>
       </c>
       <c r="G10" t="n">
-        <v>5.957435211433337</v>
+        <v>5.864012272780123</v>
       </c>
       <c r="H10" t="n">
-        <v>6.374288318080099</v>
+        <v>6.342392215017304</v>
       </c>
     </row>
     <row r="11">
@@ -2333,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.680750957251655</v>
+        <v>3.417542897072725</v>
       </c>
       <c r="G11" t="n">
-        <v>4.311300944058082</v>
+        <v>4.046515215537529</v>
       </c>
       <c r="H11" t="n">
-        <v>6.326454167072461</v>
+        <v>5.121801330434913</v>
       </c>
     </row>
     <row r="12">
@@ -2361,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.353614048835431</v>
+        <v>6.305315894748492</v>
       </c>
       <c r="G12" t="n">
-        <v>6.525813714049566</v>
+        <v>6.480178475840186</v>
       </c>
       <c r="H12" t="n">
-        <v>6.695515236014383</v>
+        <v>6.652111576946956</v>
       </c>
     </row>
     <row r="13">
@@ -2389,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.894349717847238</v>
+        <v>9.789444247440565</v>
       </c>
       <c r="G13" t="n">
-        <v>10.21363869315348</v>
+        <v>10.10914520265792</v>
       </c>
       <c r="H13" t="n">
-        <v>10.78342560509235</v>
+        <v>10.37908160050649</v>
       </c>
     </row>
     <row r="14">
@@ -2417,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.983842080053911</v>
+        <v>5.874910157446822</v>
       </c>
       <c r="G14" t="n">
-        <v>6.497463462005913</v>
+        <v>6.372076500948078</v>
       </c>
       <c r="H14" t="n">
-        <v>7.092535412279281</v>
+        <v>6.981131900650488</v>
       </c>
     </row>
     <row r="15">
@@ -2445,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.687429295000265</v>
+        <v>6.635635249521554</v>
       </c>
       <c r="G15" t="n">
-        <v>6.898445201385703</v>
+        <v>6.84583184424221</v>
       </c>
       <c r="H15" t="n">
-        <v>7.138061333848699</v>
+        <v>7.077302882147989</v>
       </c>
     </row>
     <row r="16">
@@ -2473,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.757431817730801</v>
+        <v>4.499103597989199</v>
       </c>
       <c r="G16" t="n">
-        <v>5.307672170218032</v>
+        <v>5.207199533252255</v>
       </c>
       <c r="H16" t="n">
-        <v>6.476579968536771</v>
+        <v>6.179453305744518</v>
       </c>
     </row>
     <row r="17">
@@ -2501,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.720645423709897</v>
+        <v>4.702348657004088</v>
       </c>
       <c r="G17" t="n">
-        <v>4.819133891730353</v>
+        <v>4.77641137838293</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9933731699336</v>
+        <v>4.844329609199468</v>
       </c>
     </row>
     <row r="18">
@@ -2529,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.848013924775333</v>
+        <v>2.786274782923502</v>
       </c>
       <c r="G18" t="n">
-        <v>3.319812766613585</v>
+        <v>3.223901127256791</v>
       </c>
       <c r="H18" t="n">
-        <v>3.719734910267425</v>
+        <v>3.716176609818405</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -568,16 +568,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E2" t="n">
-        <v>9959</v>
+        <v>9962</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9959</v>
+        <v>9961</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -591,13 +591,13 @@
         <v>36161</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="L2" t="n">
         <v>1.78</v>
       </c>
       <c r="M2" t="n">
-        <v>102.8901293637246</v>
+        <v>102.8811824448683</v>
       </c>
       <c r="N2" t="n">
         <v>118.97</v>
@@ -606,37 +606,37 @@
         <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>95.32741531987904</v>
+        <v>95.32108891119333</v>
       </c>
       <c r="Q2" t="n">
         <v>118.38</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.562714043845553</v>
+        <v>-7.560093533675002</v>
       </c>
       <c r="S2" t="n">
-        <v>22.66648011805397</v>
+        <v>22.67654031248787</v>
       </c>
       <c r="T2" t="n">
-        <v>31.55536094560263</v>
+        <v>31.5619114901981</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1348266406889619</v>
+        <v>0.1346527683752431</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3249862369548453</v>
+        <v>-0.3250996326126141</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06442113433485186</v>
+        <v>0.06424909254152456</v>
       </c>
       <c r="X2" t="n">
-        <v>88.71926840947754</v>
+        <v>87.20004320936965</v>
       </c>
       <c r="Y2" t="n">
-        <v>93.90852521107296</v>
+        <v>91.79737419881558</v>
       </c>
       <c r="Z2" t="n">
-        <v>103.545009483644</v>
+        <v>103.6245390887595</v>
       </c>
     </row>
     <row r="3">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E3" t="n">
-        <v>14538</v>
+        <v>14540</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14538</v>
+        <v>14539</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -677,13 +677,13 @@
         <v>30317</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L3" t="n">
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>4.906685066721694</v>
+        <v>4.906590549556365</v>
       </c>
       <c r="N3" t="n">
         <v>11.07</v>
@@ -692,37 +692,37 @@
         <v>0.01185120904911286</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955328913551968</v>
+        <v>4.955393767974834</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04864384683027237</v>
+        <v>0.04880321841846751</v>
       </c>
       <c r="S3" t="n">
-        <v>1.353866109052305</v>
+        <v>1.35378970316816</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72971914927921</v>
+        <v>1.729651006670732</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784632111736615</v>
+        <v>0.7784584130179306</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643659260065242</v>
+        <v>0.5643785245295188</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774855416902485</v>
+        <v>0.7774743743353822</v>
       </c>
       <c r="X3" t="n">
-        <v>2.786274782923502</v>
+        <v>2.726657362903647</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.22390112725679</v>
+        <v>3.1287505843467</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.716176609818405</v>
+        <v>3.673135756733777</v>
       </c>
     </row>
     <row r="4">
@@ -740,16 +740,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E4" t="n">
-        <v>10219</v>
+        <v>10222</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10219</v>
+        <v>10221</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -763,52 +763,52 @@
         <v>35065</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="L4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="M4" t="n">
-        <v>6.91938863881006</v>
+        <v>6.919057332941982</v>
       </c>
       <c r="N4" t="n">
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.503909684704989</v>
+        <v>0.5052697142338819</v>
       </c>
       <c r="P4" t="n">
-        <v>7.237699721549809</v>
+        <v>7.237698632435657</v>
       </c>
       <c r="Q4" t="n">
         <v>12.79092695825988</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3183110827397495</v>
+        <v>0.3186412994936734</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28994302695558</v>
+        <v>1.289777543834538</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677420108559649</v>
+        <v>1.677310713563687</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680619959674725</v>
+        <v>0.8680610691971837</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392188017799812</v>
+        <v>0.7392154023818902</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8472235570844796</v>
+        <v>0.8471523306135846</v>
       </c>
       <c r="X4" t="n">
-        <v>4.702348657004088</v>
+        <v>4.659168758156628</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.77641137838293</v>
+        <v>4.782537555386879</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.844329609199468</v>
+        <v>4.87826428304801</v>
       </c>
     </row>
     <row r="5">
@@ -826,16 +826,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E5" t="n">
-        <v>8831</v>
+        <v>8833</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8831</v>
+        <v>8832</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -849,13 +849,13 @@
         <v>36892</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.730240063412977</v>
+        <v>6.730387794384058</v>
       </c>
       <c r="N5" t="n">
         <v>10.6125</v>
@@ -864,37 +864,37 @@
         <v>2.074263578685523</v>
       </c>
       <c r="P5" t="n">
-        <v>6.923252201004961</v>
+        <v>6.923698638566593</v>
       </c>
       <c r="Q5" t="n">
         <v>10.02216567852482</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1930121375919838</v>
+        <v>0.1933108441825349</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44665702182825</v>
+        <v>1.446668089612012</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844875186589797</v>
+        <v>1.844871649448231</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963187104745749</v>
+        <v>0.2963057040290977</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1165101576590812</v>
+        <v>-0.1165617051816392</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473880633014304</v>
+        <v>0.2473718084235209</v>
       </c>
       <c r="X5" t="n">
-        <v>6.635635249521554</v>
+        <v>6.655022829612451</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.845831844242211</v>
+        <v>6.819912168590496</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.077302882147989</v>
+        <v>7.020748537994402</v>
       </c>
     </row>
     <row r="6">
@@ -912,16 +912,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E6" t="n">
-        <v>14193</v>
+        <v>14195</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>14193</v>
+        <v>14194</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -935,13 +935,13 @@
         <v>31048</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L6" t="n">
         <v>1.025</v>
       </c>
       <c r="M6" t="n">
-        <v>5.582744134432468</v>
+        <v>5.582731259687193</v>
       </c>
       <c r="N6" t="n">
         <v>10.01</v>
@@ -950,37 +950,37 @@
         <v>1.18</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585540397973577</v>
+        <v>5.585509222811802</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.002796263541109814</v>
+        <v>0.00277796312461025</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162570644465137</v>
+        <v>1.162507910021187</v>
       </c>
       <c r="T6" t="n">
-        <v>1.500774587985406</v>
+        <v>1.500686020616032</v>
       </c>
       <c r="U6" t="n">
-        <v>0.507656897390259</v>
+        <v>0.5076689963535944</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06656922859797199</v>
+        <v>0.06661454802383027</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045781169913075</v>
+        <v>0.5045872899967179</v>
       </c>
       <c r="X6" t="n">
-        <v>5.778674430305634</v>
+        <v>5.726760030246275</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.993550747597633</v>
+        <v>5.944611091641512</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.220392731897288</v>
+        <v>6.177788607260648</v>
       </c>
     </row>
     <row r="7">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E7" t="n">
-        <v>8991</v>
+        <v>8993</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8991</v>
+        <v>8992</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1021,13 +1021,13 @@
         <v>36161</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L7" t="n">
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>7.880571126682238</v>
+        <v>7.880568560943061</v>
       </c>
       <c r="N7" t="n">
         <v>15.14</v>
@@ -1036,37 +1036,37 @@
         <v>1.098396014558873</v>
       </c>
       <c r="P7" t="n">
-        <v>8.092626091878373</v>
+        <v>8.09313870584355</v>
       </c>
       <c r="Q7" t="n">
         <v>13.93778665249157</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2120549651961344</v>
+        <v>0.2125701449004903</v>
       </c>
       <c r="S7" t="n">
-        <v>1.421650909998138</v>
+        <v>1.421964885303135</v>
       </c>
       <c r="T7" t="n">
-        <v>1.794326543509386</v>
+        <v>1.794874374992412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8125226695868086</v>
+        <v>0.8123781964764707</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6414809578720708</v>
+        <v>0.6412221059864125</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7979372272793581</v>
+        <v>0.7977428869926722</v>
       </c>
       <c r="X7" t="n">
-        <v>5.465709112516045</v>
+        <v>5.425722835462518</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.864012272780123</v>
+        <v>5.780232245256398</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.342392215017304</v>
+        <v>6.275026515803463</v>
       </c>
     </row>
     <row r="8">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E8" t="n">
-        <v>13856</v>
+        <v>13858</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>13856</v>
+        <v>13857</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>31778</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L8" t="n">
         <v>0.06</v>
       </c>
       <c r="M8" t="n">
-        <v>7.616612117494226</v>
+        <v>7.616519448654109</v>
       </c>
       <c r="N8" t="n">
         <v>14.03</v>
@@ -1122,37 +1122,37 @@
         <v>1.106025794920669</v>
       </c>
       <c r="P8" t="n">
-        <v>7.659937698784861</v>
+        <v>7.66001777880603</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04332558129063499</v>
+        <v>0.04349833015191976</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502557489313858</v>
+        <v>1.502488439761694</v>
       </c>
       <c r="T8" t="n">
-        <v>1.961870959056085</v>
+        <v>1.961806731289439</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529776904289334</v>
+        <v>0.7529672973981634</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156604884582825</v>
+        <v>0.5156645002114295</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520200326624376</v>
+        <v>0.7520042259461893</v>
       </c>
       <c r="X8" t="n">
-        <v>5.874910157446822</v>
+        <v>5.867810134768883</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.372076500948078</v>
+        <v>6.267092667943198</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.981131900650488</v>
+        <v>6.796228742714516</v>
       </c>
     </row>
     <row r="9">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74267408248077</v>
+        <v>10.74252406872358</v>
       </c>
       <c r="Q9" t="n">
         <v>23.3656067150359</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4376145427430093</v>
+        <v>0.4374645289858261</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151337969359972</v>
+        <v>2.151324667917073</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874386262816496</v>
+        <v>2.874361963841202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3308192857035197</v>
+        <v>0.3308464323914269</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2716333560983115</v>
+        <v>-0.2716118563734509</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3251548106320369</v>
+        <v>0.3251872978382808</v>
       </c>
       <c r="X9" t="n">
-        <v>9.789444247440565</v>
+        <v>10.02178617217574</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.10914520265792</v>
+        <v>10.17595530833749</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.37908160050649</v>
+        <v>10.29171099478866</v>
       </c>
     </row>
     <row r="10">
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E10" t="n">
-        <v>13797</v>
+        <v>13799</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>13797</v>
+        <v>13798</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         <v>31413</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L10" t="n">
         <v>0.4375</v>
       </c>
       <c r="M10" t="n">
-        <v>5.245903638472131</v>
+        <v>5.245871321930714</v>
       </c>
       <c r="N10" t="n">
         <v>10.15</v>
@@ -1294,37 +1294,37 @@
         <v>0.4490779286658197</v>
       </c>
       <c r="P10" t="n">
-        <v>5.218752068863286</v>
+        <v>5.218764597108932</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02715156960884612</v>
+        <v>-0.02710672482178227</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160663642749955</v>
+        <v>1.160595399939246</v>
       </c>
       <c r="T10" t="n">
-        <v>1.481735009804921</v>
+        <v>1.481666993510793</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4297203499208604</v>
+        <v>0.4297098221582691</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08917655812414438</v>
+        <v>-0.08914771699724922</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4277357844612971</v>
+        <v>0.4277215945596142</v>
       </c>
       <c r="X10" t="n">
-        <v>4.313173749197579</v>
+        <v>4.44803834147273</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.54132205164761</v>
+        <v>4.636119518503951</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.80479549559218</v>
+        <v>4.799240421107129</v>
       </c>
     </row>
     <row r="11">
@@ -1342,16 +1342,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E11" t="n">
-        <v>4115</v>
+        <v>4117</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4115</v>
+        <v>4116</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1365,13 +1365,13 @@
         <v>41640</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L11" t="n">
         <v>2.195</v>
       </c>
       <c r="M11" t="n">
-        <v>7.495851154313487</v>
+        <v>7.495250850340136</v>
       </c>
       <c r="N11" t="n">
         <v>19.1775</v>
@@ -1380,37 +1380,37 @@
         <v>2.365562336565191</v>
       </c>
       <c r="P11" t="n">
-        <v>7.712329228490995</v>
+        <v>7.711831118294073</v>
       </c>
       <c r="Q11" t="n">
         <v>13.28491592512375</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2164780741775076</v>
+        <v>0.2165802679539373</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9628432361954222</v>
+        <v>0.9626458364738362</v>
       </c>
       <c r="T11" t="n">
-        <v>1.342601641605984</v>
+        <v>1.342385845624896</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7908726642392341</v>
+        <v>0.7909457516916999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5652905132306503</v>
+        <v>0.5654800662863657</v>
       </c>
       <c r="W11" t="n">
-        <v>0.788548451193079</v>
+        <v>0.7886250637390947</v>
       </c>
       <c r="X11" t="n">
-        <v>4.830641002960155</v>
+        <v>4.915233112762575</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.157611375445773</v>
+        <v>5.160518194367339</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.345664197048527</v>
+        <v>5.34356916065347</v>
       </c>
     </row>
     <row r="12">
@@ -1428,16 +1428,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E12" t="n">
-        <v>6449</v>
+        <v>6451</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>6449</v>
+        <v>6450</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1451,52 +1451,52 @@
         <v>39083</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L12" t="n">
         <v>1.54</v>
       </c>
       <c r="M12" t="n">
-        <v>9.618769835116556</v>
+        <v>9.618477002583978</v>
       </c>
       <c r="N12" t="n">
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.949938847003706</v>
+        <v>2.953822385664691</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01606573113089</v>
+        <v>10.01642806999197</v>
       </c>
       <c r="Q12" t="n">
         <v>16.13</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3972958960143328</v>
+        <v>0.3979510674079892</v>
       </c>
       <c r="S12" t="n">
-        <v>1.683032230251143</v>
+        <v>1.682949594310256</v>
       </c>
       <c r="T12" t="n">
-        <v>2.137812244904523</v>
+        <v>2.13777110892555</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253996194585755</v>
+        <v>0.8253777564634406</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6539627270253066</v>
+        <v>0.6539368807194608</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8135759195940824</v>
+        <v>0.8134780543479637</v>
       </c>
       <c r="X12" t="n">
-        <v>7.412643419006733</v>
+        <v>7.329069077238741</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.808961144625357</v>
+        <v>7.719598520648679</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.200975680169341</v>
+        <v>8.022530992927182</v>
       </c>
     </row>
     <row r="13">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E13" t="n">
-        <v>14037</v>
+        <v>14039</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>14037</v>
+        <v>14038</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1537,13 +1537,13 @@
         <v>30682</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L13" t="n">
         <v>0.26</v>
       </c>
       <c r="M13" t="n">
-        <v>8.134408171261665</v>
+        <v>8.134345882604359</v>
       </c>
       <c r="N13" t="n">
         <v>34.0025</v>
@@ -1552,37 +1552,37 @@
         <v>0.8778757365545877</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211592249321622</v>
+        <v>8.211816165527123</v>
       </c>
       <c r="Q13" t="n">
         <v>19.64109372411599</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07718407805995597</v>
+        <v>0.07747028292276292</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786655194584772</v>
+        <v>1.786781978331799</v>
       </c>
       <c r="T13" t="n">
-        <v>2.32165546126316</v>
+        <v>2.321771379560974</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7762351470941621</v>
+        <v>0.7761818370206299</v>
       </c>
       <c r="V13" t="n">
-        <v>0.551037377771278</v>
+        <v>0.5509625937169469</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7760243693735041</v>
+        <v>0.7759703359358315</v>
       </c>
       <c r="X13" t="n">
-        <v>6.305315894748492</v>
+        <v>6.290375714976573</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.480178475840186</v>
+        <v>6.4632821178661</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.652111576946956</v>
+        <v>6.634535108837767</v>
       </c>
     </row>
     <row r="14">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1638,37 +1638,37 @@
         <v>4.975807364456732</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83319654066159</v>
+        <v>11.83304847267143</v>
       </c>
       <c r="Q14" t="n">
         <v>21.27195770556229</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1306853567246579</v>
+        <v>-0.1308334247148275</v>
       </c>
       <c r="S14" t="n">
-        <v>2.043067671746144</v>
+        <v>2.043091105259739</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6588254518321</v>
+        <v>2.658841148422919</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009777382732908</v>
+        <v>0.8009818143304313</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207503738989466</v>
+        <v>0.6207458960241264</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7924223849048234</v>
+        <v>0.7924356139012816</v>
       </c>
       <c r="X14" t="n">
-        <v>8.100704530347437</v>
+        <v>8.054630084232455</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.488625415905204</v>
+        <v>8.405661885264568</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.850986301542065</v>
+        <v>8.794140384354014</v>
       </c>
     </row>
     <row r="15">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E15" t="n">
-        <v>9800</v>
+        <v>9802</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>9800</v>
+        <v>9801</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1709,13 +1709,13 @@
         <v>35804</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L15" t="n">
         <v>0.26</v>
       </c>
       <c r="M15" t="n">
-        <v>8.409597278911564</v>
+        <v>8.409413155120225</v>
       </c>
       <c r="N15" t="n">
         <v>131.9</v>
@@ -1724,37 +1724,37 @@
         <v>0.5804528488899593</v>
       </c>
       <c r="P15" t="n">
-        <v>9.377018103525684</v>
+        <v>9.376418874129996</v>
       </c>
       <c r="Q15" t="n">
         <v>119.6249412815277</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9674208246141196</v>
+        <v>0.9670057190097701</v>
       </c>
       <c r="S15" t="n">
-        <v>4.183047757646241</v>
+        <v>4.183232496061627</v>
       </c>
       <c r="T15" t="n">
-        <v>11.6210693578073</v>
+        <v>11.62063429137672</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03400212793373993</v>
+        <v>0.03397869450270663</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7612536463888346</v>
+        <v>-0.7612938482567244</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02206518263153723</v>
+        <v>0.02204797432166528</v>
       </c>
       <c r="X15" t="n">
-        <v>10.82493208759487</v>
+        <v>10.88721575317732</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.44811476503503</v>
+        <v>11.3663279587366</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.96241612784637</v>
+        <v>11.84771123132677</v>
       </c>
     </row>
     <row r="16">
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1810,37 +1810,37 @@
         <v>1.467998349796847</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927493829478454</v>
+        <v>6.927568537229587</v>
       </c>
       <c r="Q16" t="n">
         <v>12.11960615380856</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3443604238385402</v>
+        <v>0.3444351315896731</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971976954945176</v>
+        <v>1.971989331991212</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479903959926924</v>
+        <v>2.479912148565002</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5334921542519799</v>
+        <v>0.5334811347299319</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08990300881718005</v>
+        <v>0.08989699853024857</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283588794508602</v>
+        <v>0.5283441202157942</v>
       </c>
       <c r="X16" t="n">
-        <v>3.417542897072725</v>
+        <v>3.370754207582492</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.046515215537529</v>
+        <v>4.201833754927192</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.121801330434913</v>
+        <v>5.238002578823759</v>
       </c>
     </row>
     <row r="17">
@@ -1858,16 +1858,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E17" t="n">
-        <v>3203</v>
+        <v>3205</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1881,13 +1881,13 @@
         <v>42370</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L17" t="n">
         <v>1.81</v>
       </c>
       <c r="M17" t="n">
-        <v>6.5026740555729</v>
+        <v>6.501852372034955</v>
       </c>
       <c r="N17" t="n">
         <v>18.4925</v>
@@ -1896,37 +1896,37 @@
         <v>1.923435659174772</v>
       </c>
       <c r="P17" t="n">
-        <v>6.728090406086487</v>
+        <v>6.724897375817505</v>
       </c>
       <c r="Q17" t="n">
         <v>13.28173148390984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2254163505135869</v>
+        <v>0.2230450037825492</v>
       </c>
       <c r="S17" t="n">
-        <v>1.088960374618325</v>
+        <v>1.08906507232978</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478090198142928</v>
+        <v>1.478031836906768</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6077381223020669</v>
+        <v>0.6081939627971509</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2270667977450529</v>
+        <v>0.2274777624876755</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6042135723664874</v>
+        <v>0.604815791493112</v>
       </c>
       <c r="X17" t="n">
-        <v>4.499103597989199</v>
+        <v>4.477105858498857</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.207199533252256</v>
+        <v>5.447938047516743</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.179453305744518</v>
+        <v>6.238323917510907</v>
       </c>
     </row>
     <row r="18">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16656</v>
+        <v>16657</v>
       </c>
       <c r="E18" t="n">
-        <v>7157</v>
+        <v>7159</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>7157</v>
+        <v>7158</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1967,52 +1967,52 @@
         <v>37987</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="L18" t="n">
         <v>0.04</v>
       </c>
       <c r="M18" t="n">
-        <v>10.37605071957524</v>
+        <v>10.37492246437552</v>
       </c>
       <c r="N18" t="n">
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.762082151061103</v>
+        <v>4.731988859052884</v>
       </c>
       <c r="P18" t="n">
-        <v>11.16716464559427</v>
+        <v>11.16594572584583</v>
       </c>
       <c r="Q18" t="n">
         <v>17.5154399668629</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7911139260190347</v>
+        <v>0.7910232614702994</v>
       </c>
       <c r="S18" t="n">
-        <v>2.037572989096702</v>
+        <v>2.037989632240806</v>
       </c>
       <c r="T18" t="n">
-        <v>2.758666400212955</v>
+        <v>2.759216533459643</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252408126098214</v>
+        <v>0.7252654719829723</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4674065757276417</v>
+        <v>0.4674592809286297</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6762909907631836</v>
+        <v>0.6763526951715143</v>
       </c>
       <c r="X18" t="n">
-        <v>7.924354754784328</v>
+        <v>7.883441301049346</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.046317934473063</v>
+        <v>8.025719050129879</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.127339883958451</v>
+        <v>8.101192844461115</v>
       </c>
     </row>
   </sheetData>
@@ -2081,22 +2081,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.924354754784328</v>
+        <v>7.883441301049346</v>
       </c>
       <c r="G2" t="n">
-        <v>8.046317934473063</v>
+        <v>8.025719050129879</v>
       </c>
       <c r="H2" t="n">
-        <v>8.127339883958451</v>
+        <v>8.101192844461115</v>
       </c>
     </row>
     <row r="3">
@@ -2109,22 +2109,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.778674430305634</v>
+        <v>5.726760030246275</v>
       </c>
       <c r="G3" t="n">
-        <v>5.993550747597632</v>
+        <v>5.944611091641513</v>
       </c>
       <c r="H3" t="n">
-        <v>6.220392731897288</v>
+        <v>6.177788607260648</v>
       </c>
     </row>
     <row r="4">
@@ -2137,22 +2137,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.313173749197579</v>
+        <v>4.44803834147273</v>
       </c>
       <c r="G4" t="n">
-        <v>4.54132205164761</v>
+        <v>4.636119518503951</v>
       </c>
       <c r="H4" t="n">
-        <v>4.80479549559218</v>
+        <v>4.799240421107129</v>
       </c>
     </row>
     <row r="5">
@@ -2165,22 +2165,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.82493208759487</v>
+        <v>10.88721575317732</v>
       </c>
       <c r="G5" t="n">
-        <v>11.44811476503503</v>
+        <v>11.3663279587366</v>
       </c>
       <c r="H5" t="n">
-        <v>11.96241612784637</v>
+        <v>11.84771123132677</v>
       </c>
     </row>
     <row r="6">
@@ -2193,22 +2193,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>88.71926840947754</v>
+        <v>87.20004320936965</v>
       </c>
       <c r="G6" t="n">
-        <v>93.90852521107294</v>
+        <v>91.79737419881558</v>
       </c>
       <c r="H6" t="n">
-        <v>103.545009483644</v>
+        <v>103.6245390887595</v>
       </c>
     </row>
     <row r="7">
@@ -2221,22 +2221,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.100704530347437</v>
+        <v>8.054630084232455</v>
       </c>
       <c r="G7" t="n">
-        <v>8.488625415905204</v>
+        <v>8.405661885264564</v>
       </c>
       <c r="H7" t="n">
-        <v>8.850986301542065</v>
+        <v>8.794140384354014</v>
       </c>
     </row>
     <row r="8">
@@ -2249,22 +2249,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.412643419006733</v>
+        <v>7.329069077238741</v>
       </c>
       <c r="G8" t="n">
-        <v>7.808961144625357</v>
+        <v>7.719598520648679</v>
       </c>
       <c r="H8" t="n">
-        <v>8.200975680169341</v>
+        <v>8.022530992927182</v>
       </c>
     </row>
     <row r="9">
@@ -2277,22 +2277,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.830641002960155</v>
+        <v>4.915233112762575</v>
       </c>
       <c r="G9" t="n">
-        <v>5.157611375445773</v>
+        <v>5.160518194367338</v>
       </c>
       <c r="H9" t="n">
-        <v>5.345664197048527</v>
+        <v>5.34356916065347</v>
       </c>
     </row>
     <row r="10">
@@ -2305,22 +2305,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.465709112516045</v>
+        <v>5.425722835462518</v>
       </c>
       <c r="G10" t="n">
-        <v>5.864012272780123</v>
+        <v>5.780232245256398</v>
       </c>
       <c r="H10" t="n">
-        <v>6.342392215017304</v>
+        <v>6.275026515803463</v>
       </c>
     </row>
     <row r="11">
@@ -2333,22 +2333,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.417542897072725</v>
+        <v>3.370754207582492</v>
       </c>
       <c r="G11" t="n">
-        <v>4.046515215537529</v>
+        <v>4.201833754927192</v>
       </c>
       <c r="H11" t="n">
-        <v>5.121801330434913</v>
+        <v>5.238002578823759</v>
       </c>
     </row>
     <row r="12">
@@ -2361,22 +2361,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.305315894748492</v>
+        <v>6.290375714976573</v>
       </c>
       <c r="G12" t="n">
-        <v>6.480178475840186</v>
+        <v>6.4632821178661</v>
       </c>
       <c r="H12" t="n">
-        <v>6.652111576946956</v>
+        <v>6.634535108837767</v>
       </c>
     </row>
     <row r="13">
@@ -2389,22 +2389,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.789444247440565</v>
+        <v>10.02178617217574</v>
       </c>
       <c r="G13" t="n">
-        <v>10.10914520265792</v>
+        <v>10.17595530833749</v>
       </c>
       <c r="H13" t="n">
-        <v>10.37908160050649</v>
+        <v>10.29171099478866</v>
       </c>
     </row>
     <row r="14">
@@ -2417,22 +2417,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.874910157446822</v>
+        <v>5.867810134768883</v>
       </c>
       <c r="G14" t="n">
-        <v>6.372076500948078</v>
+        <v>6.267092667943198</v>
       </c>
       <c r="H14" t="n">
-        <v>6.981131900650488</v>
+        <v>6.796228742714516</v>
       </c>
     </row>
     <row r="15">
@@ -2445,22 +2445,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.635635249521554</v>
+        <v>6.655022829612451</v>
       </c>
       <c r="G15" t="n">
-        <v>6.84583184424221</v>
+        <v>6.819912168590496</v>
       </c>
       <c r="H15" t="n">
-        <v>7.077302882147989</v>
+        <v>7.020748537994402</v>
       </c>
     </row>
     <row r="16">
@@ -2473,22 +2473,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.499103597989199</v>
+        <v>4.477105858498857</v>
       </c>
       <c r="G16" t="n">
-        <v>5.207199533252255</v>
+        <v>5.447938047516743</v>
       </c>
       <c r="H16" t="n">
-        <v>6.179453305744518</v>
+        <v>6.238323917510907</v>
       </c>
     </row>
     <row r="17">
@@ -2501,22 +2501,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.702348657004088</v>
+        <v>4.659168758156628</v>
       </c>
       <c r="G17" t="n">
-        <v>4.77641137838293</v>
+        <v>4.782537555386879</v>
       </c>
       <c r="H17" t="n">
-        <v>4.844329609199468</v>
+        <v>4.87826428304801</v>
       </c>
     </row>
     <row r="18">
@@ -2529,22 +2529,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.786274782923502</v>
+        <v>2.726657362903647</v>
       </c>
       <c r="G18" t="n">
-        <v>3.223901127256791</v>
+        <v>3.1287505843467</v>
       </c>
       <c r="H18" t="n">
-        <v>3.716176609818405</v>
+        <v>3.673135756733777</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -603,40 +603,40 @@
         <v>118.97</v>
       </c>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>1.843123209169055</v>
       </c>
       <c r="P2" t="n">
-        <v>95.32108891119333</v>
+        <v>102.8805069991831</v>
       </c>
       <c r="Q2" t="n">
-        <v>118.38</v>
+        <v>118.8919225199131</v>
       </c>
       <c r="R2" t="n">
-        <v>-7.560093533675002</v>
+        <v>-0.0006754456851761013</v>
       </c>
       <c r="S2" t="n">
-        <v>22.67654031248787</v>
+        <v>17.76440495292452</v>
       </c>
       <c r="T2" t="n">
-        <v>31.5619114901981</v>
+        <v>36.12789924823703</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1346527683752431</v>
+        <v>0.1290306914977253</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.3250996326126141</v>
+        <v>-0.7362304019696044</v>
       </c>
       <c r="W2" t="n">
-        <v>0.06424909254152456</v>
+        <v>0.1290245036301099</v>
       </c>
       <c r="X2" t="n">
-        <v>87.20004320936965</v>
+        <v>58.62662276669903</v>
       </c>
       <c r="Y2" t="n">
-        <v>91.79737419881558</v>
+        <v>105.0571713563318</v>
       </c>
       <c r="Z2" t="n">
-        <v>103.6245390887595</v>
+        <v>110.9100723655944</v>
       </c>
     </row>
     <row r="3">
@@ -650,7 +650,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -689,40 +689,40 @@
         <v>11.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01185120904911286</v>
+        <v>0.01756303724928367</v>
       </c>
       <c r="P3" t="n">
-        <v>4.955393767974834</v>
+        <v>4.960253486539629</v>
       </c>
       <c r="Q3" t="n">
         <v>11.07</v>
       </c>
       <c r="R3" t="n">
-        <v>0.04880321841846751</v>
+        <v>0.05366293698326334</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35378970316816</v>
+        <v>1.350867190817886</v>
       </c>
       <c r="T3" t="n">
-        <v>1.729651006670732</v>
+        <v>1.725583767663616</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7784584130179306</v>
+        <v>0.7794857527669876</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5643785245295188</v>
+        <v>0.5664248257801628</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7774743743353822</v>
+        <v>0.7784293892948898</v>
       </c>
       <c r="X3" t="n">
-        <v>2.726657362903647</v>
+        <v>2.712659863698741</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.1287505843467</v>
+        <v>3.151962644367367</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.673135756733777</v>
+        <v>3.734334088493765</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +736,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -775,40 +775,40 @@
         <v>12.93</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5052697142338819</v>
+        <v>0.3662633451957295</v>
       </c>
       <c r="P4" t="n">
-        <v>7.237698632435657</v>
+        <v>7.247986940912678</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.79092695825988</v>
+        <v>12.72990889978977</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3186412994936734</v>
+        <v>0.3289296079706954</v>
       </c>
       <c r="S4" t="n">
-        <v>1.289777543834538</v>
+        <v>1.294332688333304</v>
       </c>
       <c r="T4" t="n">
-        <v>1.677310713563687</v>
+        <v>1.684282371589636</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8680610691971837</v>
+        <v>0.8674230549645812</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7392154023818902</v>
+        <v>0.7370430207935936</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8471523306135846</v>
+        <v>0.8471326096588474</v>
       </c>
       <c r="X4" t="n">
-        <v>4.659168758156628</v>
+        <v>4.564022737736554</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.782537555386879</v>
+        <v>4.704556034058134</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.87826428304801</v>
+        <v>4.850516014234875</v>
       </c>
     </row>
     <row r="5">
@@ -822,7 +822,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -861,40 +861,40 @@
         <v>10.6125</v>
       </c>
       <c r="O5" t="n">
-        <v>2.074263578685523</v>
+        <v>1.616683937823834</v>
       </c>
       <c r="P5" t="n">
-        <v>6.923698638566593</v>
+        <v>7.018400774846545</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.02216567852482</v>
+        <v>10.19100035038542</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1933108441825349</v>
+        <v>0.2880129804624863</v>
       </c>
       <c r="S5" t="n">
-        <v>1.446668089612012</v>
+        <v>1.482517678733487</v>
       </c>
       <c r="T5" t="n">
-        <v>1.844871649448231</v>
+        <v>1.911088301545514</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2963057040290977</v>
+        <v>0.3047869471349391</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1165617051816392</v>
+        <v>-0.198152015826023</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2473718084235209</v>
+        <v>0.280195644835217</v>
       </c>
       <c r="X5" t="n">
-        <v>6.655022829612451</v>
+        <v>6.583047424731074</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.819912168590496</v>
+        <v>6.698516263439359</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.020748537994402</v>
+        <v>6.900139837360185</v>
       </c>
     </row>
     <row r="6">
@@ -908,7 +908,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -947,40 +947,40 @@
         <v>10.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18</v>
+        <v>1.33253223495702</v>
       </c>
       <c r="P6" t="n">
-        <v>5.585509222811802</v>
+        <v>5.586612252363356</v>
       </c>
       <c r="Q6" t="n">
         <v>10.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00277796312461025</v>
+        <v>0.003880992676163806</v>
       </c>
       <c r="S6" t="n">
-        <v>1.162507910021187</v>
+        <v>1.156005201629343</v>
       </c>
       <c r="T6" t="n">
-        <v>1.500686020616032</v>
+        <v>1.494185346244633</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5076689963535944</v>
+        <v>0.5089834682959363</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06661454802383027</v>
+        <v>0.0746835150260281</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5045872899967179</v>
+        <v>0.5051305807576973</v>
       </c>
       <c r="X6" t="n">
-        <v>5.726760030246275</v>
+        <v>5.734153605288033</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.944611091641512</v>
+        <v>5.961456061839657</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.177788607260648</v>
+        <v>6.171095644044707</v>
       </c>
     </row>
     <row r="7">
@@ -994,7 +994,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1033,40 +1033,40 @@
         <v>15.14</v>
       </c>
       <c r="O7" t="n">
-        <v>1.098396014558873</v>
+        <v>0.6453438395415473</v>
       </c>
       <c r="P7" t="n">
-        <v>8.09313870584355</v>
+        <v>8.116958313273042</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.93778665249157</v>
+        <v>14.26297827610371</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2125701449004903</v>
+        <v>0.2363897523299814</v>
       </c>
       <c r="S7" t="n">
-        <v>1.421964885303135</v>
+        <v>1.444727910070825</v>
       </c>
       <c r="T7" t="n">
-        <v>1.794874374992412</v>
+        <v>1.824450631234724</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8123781964764707</v>
+        <v>0.8089378617134542</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6412221059864125</v>
+        <v>0.6293006761981014</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7977428869926722</v>
+        <v>0.7992692537450868</v>
       </c>
       <c r="X7" t="n">
-        <v>5.425722835462518</v>
+        <v>5.431714396783157</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.780232245256398</v>
+        <v>5.792866714554191</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.275026515803463</v>
+        <v>6.23841994793755</v>
       </c>
     </row>
     <row r="8">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1119,40 +1119,40 @@
         <v>14.03</v>
       </c>
       <c r="O8" t="n">
-        <v>1.106025794920669</v>
+        <v>0.5109074733096085</v>
       </c>
       <c r="P8" t="n">
-        <v>7.66001777880603</v>
+        <v>7.680453857551946</v>
       </c>
       <c r="Q8" t="n">
         <v>14.03</v>
       </c>
       <c r="R8" t="n">
-        <v>0.04349833015191976</v>
+        <v>0.06393440889783572</v>
       </c>
       <c r="S8" t="n">
-        <v>1.502488439761694</v>
+        <v>1.477664670365433</v>
       </c>
       <c r="T8" t="n">
-        <v>1.961806731289439</v>
+        <v>1.920049134906619</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7529672973981634</v>
+        <v>0.7616658933081911</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5156645002114295</v>
+        <v>0.5360634946554466</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7520042259461893</v>
+        <v>0.7596843787542078</v>
       </c>
       <c r="X8" t="n">
-        <v>5.867810134768883</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.267092667943198</v>
+        <v>6.246853956131093</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.796228742714516</v>
+        <v>6.819118199903117</v>
       </c>
     </row>
     <row r="9">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1208,37 +1208,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>10.74252406872358</v>
+        <v>10.61997044208291</v>
       </c>
       <c r="Q9" t="n">
-        <v>23.3656067150359</v>
+        <v>14.31645908761767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4374645289858261</v>
+        <v>0.3149109023451558</v>
       </c>
       <c r="S9" t="n">
-        <v>2.151324667917073</v>
+        <v>2.051512150992676</v>
       </c>
       <c r="T9" t="n">
-        <v>2.874361963841202</v>
+        <v>2.697239871879806</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3308464323914269</v>
+        <v>0.3565374589986294</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2716118563734509</v>
+        <v>-0.1197235079364318</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3251872978382808</v>
+        <v>0.3356971120163307</v>
       </c>
       <c r="X9" t="n">
-        <v>10.02178617217574</v>
+        <v>9.985830193984139</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.17595530833749</v>
+        <v>10.14751528255746</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.29171099478866</v>
+        <v>10.26376587323174</v>
       </c>
     </row>
     <row r="10">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1291,40 +1291,40 @@
         <v>10.15</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4490779286658197</v>
+        <v>0.8401943005181348</v>
       </c>
       <c r="P10" t="n">
-        <v>5.218764597108932</v>
+        <v>5.218400961295386</v>
       </c>
       <c r="Q10" t="n">
         <v>9.94</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.02710672482178227</v>
+        <v>-0.02747036063532915</v>
       </c>
       <c r="S10" t="n">
-        <v>1.160595399939246</v>
+        <v>1.158007997174354</v>
       </c>
       <c r="T10" t="n">
-        <v>1.481666993510793</v>
+        <v>1.476930319096901</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4297098221582691</v>
+        <v>0.4295536771628595</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.08914771699724922</v>
+        <v>-0.0821951534883727</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4277215945596142</v>
+        <v>0.4269447872355635</v>
       </c>
       <c r="X10" t="n">
-        <v>4.44803834147273</v>
+        <v>4.448242129297602</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.636119518503951</v>
+        <v>4.673430666105889</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.799240421107129</v>
+        <v>4.84023487544484</v>
       </c>
     </row>
     <row r="11">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1377,40 +1377,40 @@
         <v>19.1775</v>
       </c>
       <c r="O11" t="n">
-        <v>2.365562336565191</v>
+        <v>2.204850111028867</v>
       </c>
       <c r="P11" t="n">
-        <v>7.711831118294073</v>
+        <v>7.667681588419747</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.28491592512375</v>
+        <v>16.78594914040094</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2165802679539373</v>
+        <v>0.1724307380796102</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9626458364738362</v>
+        <v>0.9154934511717434</v>
       </c>
       <c r="T11" t="n">
-        <v>1.342385845624896</v>
+        <v>1.198712428655893</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7909457516916999</v>
+        <v>0.8292281531466016</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5654800662863657</v>
+        <v>0.6535145573915913</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7886250637390947</v>
+        <v>0.8275572060890022</v>
       </c>
       <c r="X11" t="n">
-        <v>4.915233112762575</v>
+        <v>4.926820442691524</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.160518194367339</v>
+        <v>5.154828226624991</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.34356916065347</v>
+        <v>5.339127765106988</v>
       </c>
     </row>
     <row r="12">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1463,40 +1463,40 @@
         <v>16.215</v>
       </c>
       <c r="O12" t="n">
-        <v>2.953822385664691</v>
+        <v>2.860487544483985</v>
       </c>
       <c r="P12" t="n">
-        <v>10.01642806999197</v>
+        <v>10.03206015250905</v>
       </c>
       <c r="Q12" t="n">
-        <v>16.13</v>
+        <v>16.20563653352021</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3979510674079892</v>
+        <v>0.4135831499250696</v>
       </c>
       <c r="S12" t="n">
-        <v>1.682949594310256</v>
+        <v>1.695183761897019</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13777110892555</v>
+        <v>2.154633561662434</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8253777564634406</v>
+        <v>0.8231449621794996</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6539368807194608</v>
+        <v>0.6484559499651469</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8134780543479637</v>
+        <v>0.8113194274977851</v>
       </c>
       <c r="X12" t="n">
-        <v>7.329069077238741</v>
+        <v>7.327769604254384</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.719598520648679</v>
+        <v>7.688770065273216</v>
       </c>
       <c r="Z12" t="n">
-        <v>8.022530992927182</v>
+        <v>8.015356698101943</v>
       </c>
     </row>
     <row r="13">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1549,40 +1549,40 @@
         <v>34.0025</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8778757365545877</v>
+        <v>0.91</v>
       </c>
       <c r="P13" t="n">
-        <v>8.211816165527123</v>
+        <v>8.204022517489584</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.64109372411599</v>
+        <v>14.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0.07747028292276292</v>
+        <v>0.06967663488522495</v>
       </c>
       <c r="S13" t="n">
-        <v>1.786781978331799</v>
+        <v>1.759977967731633</v>
       </c>
       <c r="T13" t="n">
-        <v>2.321771379560974</v>
+        <v>2.285358155561822</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7761818370206299</v>
+        <v>0.7806980901130567</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5509625937169469</v>
+        <v>0.5649369937042079</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7759703359358315</v>
+        <v>0.7803386521161693</v>
       </c>
       <c r="X13" t="n">
-        <v>6.290375714976573</v>
+        <v>6.175338062833483</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.4632821178661</v>
+        <v>6.330156553077177</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.634535108837767</v>
+        <v>6.512216211567904</v>
       </c>
     </row>
     <row r="14">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1635,40 +1635,40 @@
         <v>30.745</v>
       </c>
       <c r="O14" t="n">
-        <v>4.975807364456732</v>
+        <v>4.682413027387121</v>
       </c>
       <c r="P14" t="n">
-        <v>11.83304847267143</v>
+        <v>11.82552192549244</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.27195770556229</v>
+        <v>21.32952932657494</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.1308334247148275</v>
+        <v>-0.1383599718938091</v>
       </c>
       <c r="S14" t="n">
-        <v>2.043091105259739</v>
+        <v>2.052549934730245</v>
       </c>
       <c r="T14" t="n">
-        <v>2.658841148422919</v>
+        <v>2.698059965267305</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8009818143304313</v>
+        <v>0.794744098747145</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6207458960241264</v>
+        <v>0.6094751250813673</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7924356139012816</v>
+        <v>0.7858579931677233</v>
       </c>
       <c r="X14" t="n">
-        <v>8.054630084232455</v>
+        <v>8.171810589981328</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.405661885264568</v>
+        <v>8.296913495104311</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.794140384354014</v>
+        <v>8.389419204380809</v>
       </c>
     </row>
     <row r="15">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1721,40 +1721,40 @@
         <v>131.9</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5804528488899593</v>
+        <v>0.5268935553946416</v>
       </c>
       <c r="P15" t="n">
-        <v>9.376418874129996</v>
+        <v>8.66355542641087</v>
       </c>
       <c r="Q15" t="n">
-        <v>119.6249412815277</v>
+        <v>131.7868211440985</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9670057190097701</v>
+        <v>0.2541422712906439</v>
       </c>
       <c r="S15" t="n">
-        <v>4.183232496061627</v>
+        <v>3.53679365639656</v>
       </c>
       <c r="T15" t="n">
-        <v>11.62063429137672</v>
+        <v>11.06520679939195</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03397869450270663</v>
+        <v>0.04964511346769675</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7612938482567244</v>
+        <v>-0.596949638179824</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02204797432166528</v>
+        <v>0.03288895518929591</v>
       </c>
       <c r="X15" t="n">
-        <v>10.88721575317732</v>
+        <v>10.81954001023077</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.3663279587366</v>
+        <v>11.35346457164039</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.84771123132677</v>
+        <v>11.81034798284707</v>
       </c>
     </row>
     <row r="16">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1807,40 +1807,40 @@
         <v>12.23</v>
       </c>
       <c r="O16" t="n">
-        <v>1.467998349796847</v>
+        <v>1.395549592894153</v>
       </c>
       <c r="P16" t="n">
-        <v>6.927568537229587</v>
+        <v>6.954939778501083</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.11960615380856</v>
+        <v>12.15738414192614</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3444351315896731</v>
+        <v>0.3718063728611686</v>
       </c>
       <c r="S16" t="n">
-        <v>1.971989331991212</v>
+        <v>2.040734871266995</v>
       </c>
       <c r="T16" t="n">
-        <v>2.479912148565002</v>
+        <v>2.579822443878717</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5334811347299319</v>
+        <v>0.518110315037839</v>
       </c>
       <c r="V16" t="n">
-        <v>0.08989699853024857</v>
+        <v>0.01508763950890413</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5283441202157942</v>
+        <v>0.5148113820469902</v>
       </c>
       <c r="X16" t="n">
-        <v>3.370754207582492</v>
+        <v>3.256802654783871</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.201833754927192</v>
+        <v>4.216359069012279</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.238002578823759</v>
+        <v>5.085508762630371</v>
       </c>
     </row>
     <row r="17">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1893,40 +1893,40 @@
         <v>18.4925</v>
       </c>
       <c r="O17" t="n">
-        <v>1.923435659174772</v>
+        <v>1.826106587712805</v>
       </c>
       <c r="P17" t="n">
-        <v>6.724897375817505</v>
+        <v>6.69644383013072</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.28173148390984</v>
+        <v>14.92774999999984</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2230450037825492</v>
+        <v>0.1945914580957638</v>
       </c>
       <c r="S17" t="n">
-        <v>1.08906507232978</v>
+        <v>1.098093270421765</v>
       </c>
       <c r="T17" t="n">
-        <v>1.478031836906768</v>
+        <v>1.4879502314557</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6081939627971509</v>
+        <v>0.6007892903475741</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2274777624876755</v>
+        <v>0.2170748890872708</v>
       </c>
       <c r="W17" t="n">
-        <v>0.604815791493112</v>
+        <v>0.5978707599418338</v>
       </c>
       <c r="X17" t="n">
-        <v>4.477105858498857</v>
+        <v>4.407509507712392</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.447938047516743</v>
+        <v>5.481337855009455</v>
       </c>
       <c r="Z17" t="n">
-        <v>6.238323917510907</v>
+        <v>6.282784819998072</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>histograma_cdf_mensual_optimizado</t>
+          <t>cdf_empirica_mensual_ordenada</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1979,40 +1979,40 @@
         <v>24.5875</v>
       </c>
       <c r="O18" t="n">
-        <v>4.731988859052884</v>
+        <v>4.725023439427584</v>
       </c>
       <c r="P18" t="n">
-        <v>11.16594572584583</v>
+        <v>11.1579530595688</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.5154399668629</v>
+        <v>17.53862298528381</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7910232614702994</v>
+        <v>0.783030595193274</v>
       </c>
       <c r="S18" t="n">
-        <v>2.037989632240806</v>
+        <v>2.035657657160924</v>
       </c>
       <c r="T18" t="n">
-        <v>2.759216533459643</v>
+        <v>2.754661476283585</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7252654719829723</v>
+        <v>0.7262807610849884</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4674592809286297</v>
+        <v>0.4692161210425043</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6763526951715143</v>
+        <v>0.6790166987374697</v>
       </c>
       <c r="X18" t="n">
-        <v>7.883441301049346</v>
+        <v>7.820460753846925</v>
       </c>
       <c r="Y18" t="n">
-        <v>8.025719050129879</v>
+        <v>7.920922767604085</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.101192844461115</v>
+        <v>7.979100294050045</v>
       </c>
     </row>
   </sheetData>
@@ -2090,13 +2090,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.883441301049346</v>
+        <v>7.820460753846925</v>
       </c>
       <c r="G2" t="n">
-        <v>8.025719050129879</v>
+        <v>7.920922767604085</v>
       </c>
       <c r="H2" t="n">
-        <v>8.101192844461115</v>
+        <v>7.979100294050045</v>
       </c>
     </row>
     <row r="3">
@@ -2118,13 +2118,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.726760030246275</v>
+        <v>5.734153605288033</v>
       </c>
       <c r="G3" t="n">
-        <v>5.944611091641513</v>
+        <v>5.961456061839657</v>
       </c>
       <c r="H3" t="n">
-        <v>6.177788607260648</v>
+        <v>6.171095644044707</v>
       </c>
     </row>
     <row r="4">
@@ -2146,13 +2146,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.44803834147273</v>
+        <v>4.448242129297602</v>
       </c>
       <c r="G4" t="n">
-        <v>4.636119518503951</v>
+        <v>4.673430666105889</v>
       </c>
       <c r="H4" t="n">
-        <v>4.799240421107129</v>
+        <v>4.84023487544484</v>
       </c>
     </row>
     <row r="5">
@@ -2174,13 +2174,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.88721575317732</v>
+        <v>10.81954001023077</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3663279587366</v>
+        <v>11.35346457164039</v>
       </c>
       <c r="H5" t="n">
-        <v>11.84771123132677</v>
+        <v>11.81034798284707</v>
       </c>
     </row>
     <row r="6">
@@ -2202,13 +2202,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>87.20004320936965</v>
+        <v>58.62662276669903</v>
       </c>
       <c r="G6" t="n">
-        <v>91.79737419881558</v>
+        <v>105.0571713563318</v>
       </c>
       <c r="H6" t="n">
-        <v>103.6245390887595</v>
+        <v>110.9100723655944</v>
       </c>
     </row>
     <row r="7">
@@ -2230,13 +2230,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.054630084232455</v>
+        <v>8.171810589981328</v>
       </c>
       <c r="G7" t="n">
-        <v>8.405661885264564</v>
+        <v>8.296913495104311</v>
       </c>
       <c r="H7" t="n">
-        <v>8.794140384354014</v>
+        <v>8.389419204380809</v>
       </c>
     </row>
     <row r="8">
@@ -2258,13 +2258,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.329069077238741</v>
+        <v>7.327769604254384</v>
       </c>
       <c r="G8" t="n">
-        <v>7.719598520648679</v>
+        <v>7.688770065273216</v>
       </c>
       <c r="H8" t="n">
-        <v>8.022530992927182</v>
+        <v>8.015356698101943</v>
       </c>
     </row>
     <row r="9">
@@ -2286,13 +2286,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.915233112762575</v>
+        <v>4.926820442691524</v>
       </c>
       <c r="G9" t="n">
-        <v>5.160518194367338</v>
+        <v>5.154828226624991</v>
       </c>
       <c r="H9" t="n">
-        <v>5.34356916065347</v>
+        <v>5.339127765106988</v>
       </c>
     </row>
     <row r="10">
@@ -2314,13 +2314,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.425722835462518</v>
+        <v>5.431714396783157</v>
       </c>
       <c r="G10" t="n">
-        <v>5.780232245256398</v>
+        <v>5.792866714554192</v>
       </c>
       <c r="H10" t="n">
-        <v>6.275026515803463</v>
+        <v>6.23841994793755</v>
       </c>
     </row>
     <row r="11">
@@ -2342,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.370754207582492</v>
+        <v>3.256802654783871</v>
       </c>
       <c r="G11" t="n">
-        <v>4.201833754927192</v>
+        <v>4.216359069012278</v>
       </c>
       <c r="H11" t="n">
-        <v>5.238002578823759</v>
+        <v>5.085508762630371</v>
       </c>
     </row>
     <row r="12">
@@ -2370,13 +2370,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.290375714976573</v>
+        <v>6.175338062833483</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4632821178661</v>
+        <v>6.330156553077177</v>
       </c>
       <c r="H12" t="n">
-        <v>6.634535108837767</v>
+        <v>6.512216211567904</v>
       </c>
     </row>
     <row r="13">
@@ -2398,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>10.02178617217574</v>
+        <v>9.985830193984139</v>
       </c>
       <c r="G13" t="n">
-        <v>10.17595530833749</v>
+        <v>10.14751528255746</v>
       </c>
       <c r="H13" t="n">
-        <v>10.29171099478866</v>
+        <v>10.26376587323174</v>
       </c>
     </row>
     <row r="14">
@@ -2426,13 +2426,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.867810134768883</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.267092667943198</v>
+        <v>6.246853956131094</v>
       </c>
       <c r="H14" t="n">
-        <v>6.796228742714516</v>
+        <v>6.819118199903117</v>
       </c>
     </row>
     <row r="15">
@@ -2454,13 +2454,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.655022829612451</v>
+        <v>6.583047424731074</v>
       </c>
       <c r="G15" t="n">
-        <v>6.819912168590496</v>
+        <v>6.698516263439359</v>
       </c>
       <c r="H15" t="n">
-        <v>7.020748537994402</v>
+        <v>6.900139837360185</v>
       </c>
     </row>
     <row r="16">
@@ -2482,13 +2482,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.477105858498857</v>
+        <v>4.407509507712392</v>
       </c>
       <c r="G16" t="n">
-        <v>5.447938047516743</v>
+        <v>5.481337855009455</v>
       </c>
       <c r="H16" t="n">
-        <v>6.238323917510907</v>
+        <v>6.282784819998072</v>
       </c>
     </row>
     <row r="17">
@@ -2510,13 +2510,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.659168758156628</v>
+        <v>4.564022737736554</v>
       </c>
       <c r="G17" t="n">
-        <v>4.782537555386879</v>
+        <v>4.704556034058134</v>
       </c>
       <c r="H17" t="n">
-        <v>4.87826428304801</v>
+        <v>4.850516014234875</v>
       </c>
     </row>
     <row r="18">
@@ -2538,13 +2538,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.726657362903647</v>
+        <v>2.712659863698741</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1287505843467</v>
+        <v>3.151962644367367</v>
       </c>
       <c r="H18" t="n">
-        <v>3.673135756733777</v>
+        <v>3.734334088493765</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="metricas_dwlt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="resumen_forecast_nivel" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="estaciones_saltadas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z18"/>
+  <dimension ref="A1:AA18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,85 +470,90 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>forecast_mes_inicio_valido</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>fecha_inicio_validacion</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fecha_fin_validacion</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>nivel_obs_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>nivel_obs_prom</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>nivel_obs_max</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>nivel_dwlt_min</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>nivel_dwlt_prom</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>nivel_dwlt_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>bias_m</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>mae_m</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rmse_m</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>r_pearson</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>nse</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>kge_2009</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>forecast_nivel_min_m</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>forecast_nivel_prom_m</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>forecast_nivel_max_m</t>
         </is>
@@ -587,55 +593,58 @@
       <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>1.78</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>102.8811824448683</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>118.97</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1.843123209169055</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>102.8805069991831</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>-0.0006754456851761013</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>17.76440495292452</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>36.12789924823703</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.1290306914977253</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>-0.7362304019696044</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.1290245036301099</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>58.62662276669903</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>105.0571713563318</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>110.9100723655944</v>
       </c>
     </row>
@@ -673,55 +682,58 @@
       <c r="I3" t="n">
         <v>12</v>
       </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>30317</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.01</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>4.906590549556365</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>11.07</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.01756303724928367</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4.960253486539629</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>11.07</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0.05366293698326334</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1.350867190817886</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.725583767663616</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.7794857527669876</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.5664248257801628</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.7784293892948898</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>2.712659863698741</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>3.151962644367367</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>3.734334088493765</v>
       </c>
     </row>
@@ -759,55 +771,58 @@
       <c r="I4" t="n">
         <v>12</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>35065</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>6.919057332941982</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>12.93</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.3662633451957295</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>7.247986940912678</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.3289296079706954</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.294332688333304</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.684282371589636</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.8674230549645812</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.7370430207935936</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0.8471326096588474</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>4.564022737736554</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>4.704556034058134</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>4.850516014234875</v>
       </c>
     </row>
@@ -845,55 +860,58 @@
       <c r="I5" t="n">
         <v>12</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>36892</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1.52</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>6.730387794384058</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>10.6125</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1.616683937823834</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>7.018400774846545</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10.19100035038542</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.2880129804624863</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>1.482517678733487</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.911088301545514</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.3047869471349391</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>-0.198152015826023</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>0.280195644835217</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>6.583047424731074</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>6.698516263439359</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>6.900139837360185</v>
       </c>
     </row>
@@ -931,55 +949,58 @@
       <c r="I6" t="n">
         <v>12</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>31048</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>1.025</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>5.582731259687193</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>10.01</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1.33253223495702</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>5.586612252363356</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>10.01</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0.003880992676163806</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1.156005201629343</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.494185346244633</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>0.5089834682959363</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>0.0746835150260281</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>0.5051305807576973</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>5.734153605288033</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>5.961456061839657</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>6.171095644044707</v>
       </c>
     </row>
@@ -1017,55 +1038,58 @@
       <c r="I7" t="n">
         <v>12</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>36161</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.16</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>7.880568560943061</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>15.14</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>0.6453438395415473</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>8.116958313273042</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>14.26297827610371</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.2363897523299814</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1.444727910070825</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1.824450631234724</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>0.8089378617134542</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0.6293006761981014</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>0.7992692537450868</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>5.431714396783157</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>5.792866714554191</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>6.23841994793755</v>
       </c>
     </row>
@@ -1103,55 +1127,58 @@
       <c r="I8" t="n">
         <v>12</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>31778</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.06</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7.616519448654109</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>14.03</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>0.5109074733096085</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>7.680453857551946</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>14.03</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.06393440889783572</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>1.477664670365433</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1.920049134906619</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>0.7616658933081911</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>0.5360634946554466</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>0.7596843787542078</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>5.824999999999999</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>6.246853956131093</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>6.819118199903117</v>
       </c>
     </row>
@@ -1189,55 +1216,58 @@
       <c r="I9" t="n">
         <v>12</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>37257</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>3.7875</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>10.30505953973775</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>39.075</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>4.255000000000001</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>10.61997044208291</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>14.31645908761767</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>0.3149109023451558</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>2.051512150992676</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>2.697239871879806</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>0.3565374589986294</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>-0.1197235079364318</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>0.3356971120163307</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>9.985830193984139</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>10.14751528255746</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>10.26376587323174</v>
       </c>
     </row>
@@ -1275,55 +1305,58 @@
       <c r="I10" t="n">
         <v>12</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>31413</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.4375</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>5.245871321930714</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>10.15</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>0.8401943005181348</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>5.218400961295386</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>9.94</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-0.02747036063532915</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>1.158007997174354</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1.476930319096901</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>0.4295536771628595</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>-0.0821951534883727</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>0.4269447872355635</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>4.448242129297602</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>4.673430666105889</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>4.84023487544484</v>
       </c>
     </row>
@@ -1361,55 +1394,58 @@
       <c r="I11" t="n">
         <v>12</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>41640</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>2.195</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>7.495250850340136</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>19.1775</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>2.204850111028867</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>7.667681588419747</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>16.78594914040094</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>0.1724307380796102</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>0.9154934511717434</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1.198712428655893</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>0.8292281531466016</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>0.6535145573915913</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>0.8275572060890022</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>4.926820442691524</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>5.154828226624991</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>5.339127765106988</v>
       </c>
     </row>
@@ -1447,55 +1483,58 @@
       <c r="I12" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>39083</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1.54</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9.618477002583978</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>16.215</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2.860487544483985</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>10.03206015250905</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>16.20563653352021</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>0.4135831499250696</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>1.695183761897019</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>2.154633561662434</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>0.8231449621794996</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>0.6484559499651469</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>0.8113194274977851</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>7.327769604254384</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>7.688770065273216</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>8.015356698101943</v>
       </c>
     </row>
@@ -1533,55 +1572,58 @@
       <c r="I13" t="n">
         <v>12</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1" t="n">
         <v>30682</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>0.26</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>8.134345882604359</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>34.0025</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>0.91</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>8.204022517489584</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>14.32</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>0.06967663488522495</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>1.759977967731633</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>2.285358155561822</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>0.7806980901130567</v>
       </c>
-      <c r="V13" t="n">
+      <c r="W13" t="n">
         <v>0.5649369937042079</v>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>0.7803386521161693</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Y13" t="n">
         <v>6.175338062833483</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>6.330156553077177</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AA13" t="n">
         <v>6.512216211567904</v>
       </c>
     </row>
@@ -1619,55 +1661,58 @@
       <c r="I14" t="n">
         <v>12</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="K14" s="1" t="n">
+      <c r="L14" s="1" t="n">
         <v>46156</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3.305</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>11.96388189738625</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>30.745</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>4.682413027387121</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>11.82552192549244</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>21.32952932657494</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>-0.1383599718938091</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>2.052549934730245</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>2.698059965267305</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>0.794744098747145</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>0.6094751250813673</v>
       </c>
-      <c r="W14" t="n">
+      <c r="X14" t="n">
         <v>0.7858579931677233</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Y14" t="n">
         <v>8.171810589981328</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Z14" t="n">
         <v>8.296913495104311</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
         <v>8.389419204380809</v>
       </c>
     </row>
@@ -1705,55 +1750,58 @@
       <c r="I15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>35804</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>0.26</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>8.409413155120225</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>131.9</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>0.5268935553946416</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>8.66355542641087</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>131.7868211440985</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>0.2541422712906439</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>3.53679365639656</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>11.06520679939195</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>0.04964511346769675</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>-0.596949638179824</v>
       </c>
-      <c r="W15" t="n">
+      <c r="X15" t="n">
         <v>0.03288895518929591</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Y15" t="n">
         <v>10.81954001023077</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Z15" t="n">
         <v>11.35346457164039</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AA15" t="n">
         <v>11.81034798284707</v>
       </c>
     </row>
@@ -1791,55 +1839,58 @@
       <c r="I16" t="n">
         <v>12</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>43252</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <v>46203</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>6.583133405639913</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>12.23</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.395549592894153</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>6.954939778501083</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>12.15738414192614</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>0.3718063728611686</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>2.040734871266995</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>2.579822443878717</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.518110315037839</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>0.01508763950890413</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>0.5148113820469902</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Y16" t="n">
         <v>3.256802654783871</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
         <v>4.216359069012279</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AA16" t="n">
         <v>5.085508762630371</v>
       </c>
     </row>
@@ -1877,55 +1928,58 @@
       <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>42370</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1.81</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>6.501852372034955</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>18.4925</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.826106587712805</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>6.69644383013072</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>14.92774999999984</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>0.1945914580957638</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>1.098093270421765</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1.4879502314557</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.6007892903475741</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W17" t="n">
         <v>0.2170748890872708</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
         <v>0.5978707599418338</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y17" t="n">
         <v>4.407509507712392</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
         <v>5.481337855009455</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA17" t="n">
         <v>6.282784819998072</v>
       </c>
     </row>
@@ -1963,55 +2017,58 @@
       <c r="I18" t="n">
         <v>12</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>37987</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" s="1" t="n">
         <v>46243</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>0.04</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>10.37492246437552</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>24.5875</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>4.725023439427584</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>11.1579530595688</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>17.53862298528381</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>0.783030595193274</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>2.035657657160924</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>2.754661476283585</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>0.7262807610849884</v>
       </c>
-      <c r="V18" t="n">
+      <c r="W18" t="n">
         <v>0.4692161210425043</v>
       </c>
-      <c r="W18" t="n">
+      <c r="X18" t="n">
         <v>0.6790166987374697</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Y18" t="n">
         <v>7.820460753846925</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Z18" t="n">
         <v>7.920922767604085</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AA18" t="n">
         <v>7.979100294050045</v>
       </c>
     </row>
@@ -2550,4 +2607,50 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>estacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>comid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>observado_insuficiente</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E2" t="n">
+        <v>9963</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9962</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9961</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -600,13 +600,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.8811824448683</v>
+        <v>102.876695777287</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -615,37 +615,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8805069991831</v>
+        <v>102.8745675582081</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0006754456851761013</v>
+        <v>-0.002128219078937251</v>
       </c>
       <c r="T2" t="n">
-        <v>17.76440495292452</v>
+        <v>17.76677761155148</v>
       </c>
       <c r="U2" t="n">
-        <v>36.12789924823703</v>
+        <v>36.12808208295553</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1290306914977253</v>
+        <v>0.1291784860658599</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7362304019696044</v>
+        <v>-0.7359592001629935</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1290245036301099</v>
+        <v>0.1291723476924668</v>
       </c>
       <c r="Y2" t="n">
-        <v>58.62662276669903</v>
+        <v>55.4505356325888</v>
       </c>
       <c r="Z2" t="n">
-        <v>105.0571713563318</v>
+        <v>102.0729227715629</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.9100723655944</v>
+        <v>109.6310784803326</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E3" t="n">
+        <v>14541</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14540</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14539</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906590549556365</v>
+        <v>4.906489683631362</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -704,37 +704,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.960253486539629</v>
+        <v>4.960161877454675</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05366293698326334</v>
+        <v>0.05367219382331281</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350867190817886</v>
+        <v>1.350800405444579</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725583767663616</v>
+        <v>1.72552312298772</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7794857527669876</v>
+        <v>0.7794896778081066</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664248257801628</v>
+        <v>0.5664348203213234</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784293892948898</v>
+        <v>0.7784326797389758</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.712659863698741</v>
+        <v>2.676102418207682</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.151962644367367</v>
+        <v>3.045592579602153</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.734334088493765</v>
+        <v>3.660177650505923</v>
       </c>
     </row>
     <row r="4">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E4" t="n">
+        <v>10223</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10222</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10221</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -778,52 +778,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.919057332941982</v>
+        <v>6.918870573273333</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3662633451957295</v>
+        <v>0.3663371266002845</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.247986940912678</v>
+        <v>7.24779854718647</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289296079706954</v>
+        <v>0.3289279739131383</v>
       </c>
       <c r="T4" t="n">
-        <v>1.294332688333304</v>
+        <v>1.294242323477599</v>
       </c>
       <c r="U4" t="n">
-        <v>1.684282371589636</v>
+        <v>1.684204387947582</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674230549645812</v>
+        <v>0.8674265445656839</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370430207935936</v>
+        <v>0.7370503359235272</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471326096588474</v>
+        <v>0.8471318531279164</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.564022737736554</v>
+        <v>4.521540468305478</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.704556034058134</v>
+        <v>4.710263992510255</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.850516014234875</v>
+        <v>4.853795080236487</v>
       </c>
     </row>
     <row r="5">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E5" t="n">
+        <v>8834</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8833</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8832</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         <v>36892</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
       </c>
       <c r="N5" t="n">
-        <v>6.730387794384058</v>
+        <v>6.730521340427941</v>
       </c>
       <c r="O5" t="n">
         <v>10.6125</v>
@@ -882,37 +882,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.018400774846545</v>
+        <v>7.018542851353087</v>
       </c>
       <c r="R5" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2880129804624863</v>
+        <v>0.2880215109251464</v>
       </c>
       <c r="T5" t="n">
-        <v>1.482517678733487</v>
+        <v>1.482472894787415</v>
       </c>
       <c r="U5" t="n">
-        <v>1.911088301545514</v>
+        <v>1.911024146930933</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3047869471349391</v>
+        <v>0.3047712353938641</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.198152015826023</v>
+        <v>-0.1981453053548712</v>
       </c>
       <c r="X5" t="n">
-        <v>0.280195644835217</v>
+        <v>0.2801716747966886</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.583047424731074</v>
+        <v>6.585224086335303</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.698516263439359</v>
+        <v>6.669992491979627</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.900139837360185</v>
+        <v>6.851500946161667</v>
       </c>
     </row>
     <row r="6">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E6" t="n">
+        <v>14196</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14195</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14194</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>31048</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M6" t="n">
         <v>1.025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.582731259687193</v>
+        <v>5.582716273335682</v>
       </c>
       <c r="O6" t="n">
         <v>10.01</v>
@@ -971,37 +971,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.586612252363356</v>
+        <v>5.586594436298406</v>
       </c>
       <c r="R6" t="n">
         <v>10.01</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003880992676163806</v>
+        <v>0.003878162962725149</v>
       </c>
       <c r="T6" t="n">
-        <v>1.156005201629343</v>
+        <v>1.155969894764106</v>
       </c>
       <c r="U6" t="n">
-        <v>1.494185346244633</v>
+        <v>1.494133060665485</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5089834682959363</v>
+        <v>0.5089831812198492</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0746835150260281</v>
+        <v>0.0746843090607513</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5051305807576973</v>
+        <v>0.5051301046062906</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.734153605288033</v>
+        <v>5.695600140793879</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.961456061839657</v>
+        <v>5.916496453723633</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.171095644044707</v>
+        <v>6.132555252878289</v>
       </c>
     </row>
     <row r="7">
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E7" t="n">
+        <v>8994</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8993</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8992</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>36161</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M7" t="n">
         <v>0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>7.880568560943061</v>
+        <v>7.880552930056712</v>
       </c>
       <c r="O7" t="n">
         <v>15.14</v>
@@ -1060,37 +1060,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.116958313273042</v>
+        <v>8.117027593516593</v>
       </c>
       <c r="R7" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2363897523299814</v>
+        <v>0.2364746634598817</v>
       </c>
       <c r="T7" t="n">
-        <v>1.444727910070825</v>
+        <v>1.444883725553443</v>
       </c>
       <c r="U7" t="n">
-        <v>1.824450631234724</v>
+        <v>1.824648387221298</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8089378617134542</v>
+        <v>0.808870822299501</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6293006761981014</v>
+        <v>0.6291791664490274</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7992692537450868</v>
+        <v>0.7991935657167738</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.431714396783157</v>
+        <v>5.41779519305913</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.792866714554191</v>
+        <v>5.714109989087143</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.23841994793755</v>
+        <v>6.16549590047524</v>
       </c>
     </row>
     <row r="8">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E8" t="n">
+        <v>13859</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13858</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13857</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1134,52 +1134,52 @@
         <v>31778</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M8" t="n">
         <v>0.06</v>
       </c>
       <c r="N8" t="n">
-        <v>7.616519448654109</v>
+        <v>7.616416510318948</v>
       </c>
       <c r="O8" t="n">
         <v>14.03</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5109074733096085</v>
+        <v>0.5109672830725462</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680453857551946</v>
+        <v>7.680353320811876</v>
       </c>
       <c r="R8" t="n">
         <v>14.03</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06393440889783572</v>
+        <v>0.06393681049292603</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477664670365433</v>
+        <v>1.477599350058033</v>
       </c>
       <c r="U8" t="n">
-        <v>1.920049134906619</v>
+        <v>1.919979072220288</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7616658933081911</v>
+        <v>0.7616695815522693</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5360634946554466</v>
+        <v>0.5360724474324461</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7596843787542078</v>
+        <v>0.7596874717771415</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.824999999999999</v>
+        <v>5.80397675954893</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.246853956131093</v>
+        <v>6.147170062631207</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.819118199903117</v>
+        <v>6.618566214769787</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1238,37 +1238,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.61997044208291</v>
+        <v>10.61987154496531</v>
       </c>
       <c r="R9" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3149109023451558</v>
+        <v>0.3148120052275556</v>
       </c>
       <c r="T9" t="n">
-        <v>2.051512150992676</v>
+        <v>2.051521053247226</v>
       </c>
       <c r="U9" t="n">
-        <v>2.697239871879806</v>
+        <v>2.697244012183474</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3565374589986294</v>
+        <v>0.356553750210395</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1197235079364318</v>
+        <v>-0.1197269455238359</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3356971120163307</v>
+        <v>0.3357235633391252</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.985830193984139</v>
+        <v>9.913633413042616</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.14751528255746</v>
+        <v>10.13451417450528</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.26376587323174</v>
+        <v>10.33241706939511</v>
       </c>
     </row>
     <row r="10">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E10" t="n">
+        <v>13800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13799</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13798</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>31413</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M10" t="n">
         <v>0.4375</v>
       </c>
       <c r="N10" t="n">
-        <v>5.245871321930714</v>
+        <v>5.245831763171244</v>
       </c>
       <c r="O10" t="n">
         <v>10.15</v>
@@ -1327,37 +1327,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.218400961295386</v>
+        <v>5.218409558136631</v>
       </c>
       <c r="R10" t="n">
         <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02747036063532915</v>
+        <v>-0.0274222050346136</v>
       </c>
       <c r="T10" t="n">
-        <v>1.158007997174354</v>
+        <v>1.157957943254914</v>
       </c>
       <c r="U10" t="n">
-        <v>1.476930319096901</v>
+        <v>1.476894227139439</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4295536771628595</v>
+        <v>0.4295389285743149</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0821951534883727</v>
+        <v>-0.0822090961875257</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4269447872355635</v>
+        <v>0.426929025260595</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.448242129297602</v>
+        <v>4.397513821108633</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.673430666105889</v>
+        <v>4.66971273037175</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.84023487544484</v>
+        <v>4.87543918918919</v>
       </c>
     </row>
     <row r="11">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E11" t="n">
+        <v>4118</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4117</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4116</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         <v>41640</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M11" t="n">
         <v>2.195</v>
       </c>
       <c r="N11" t="n">
-        <v>7.495250850340136</v>
+        <v>7.494608331309206</v>
       </c>
       <c r="O11" t="n">
         <v>19.1775</v>
@@ -1416,37 +1416,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.667681588419747</v>
+        <v>7.667031242045945</v>
       </c>
       <c r="R11" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1724307380796102</v>
+        <v>0.1724229107367392</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9154934511717434</v>
+        <v>0.9153372311500512</v>
       </c>
       <c r="U11" t="n">
-        <v>1.198712428655893</v>
+        <v>1.198541677287495</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8292281531466016</v>
+        <v>0.8293048436034099</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6535145573915913</v>
+        <v>0.6536710422245208</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8275572060890022</v>
+        <v>0.8276327612164939</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.926820442691524</v>
+        <v>4.988427302724435</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.154828226624991</v>
+        <v>5.18679164091085</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.339127765106988</v>
+        <v>5.369563763865793</v>
       </c>
     </row>
     <row r="12">
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E12" t="n">
+        <v>6452</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6451</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6450</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1490,52 +1490,52 @@
         <v>39083</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M12" t="n">
         <v>1.54</v>
       </c>
       <c r="N12" t="n">
-        <v>9.618477002583978</v>
+        <v>9.61817961039632</v>
       </c>
       <c r="O12" t="n">
         <v>16.215</v>
       </c>
       <c r="P12" t="n">
-        <v>2.860487544483985</v>
+        <v>2.860734352773826</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.03206015250905</v>
+        <v>10.03200122611163</v>
       </c>
       <c r="R12" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4135831499250696</v>
+        <v>0.4138216157153068</v>
       </c>
       <c r="T12" t="n">
-        <v>1.695183761897019</v>
+        <v>1.695016552894801</v>
       </c>
       <c r="U12" t="n">
-        <v>2.154633561662434</v>
+        <v>2.154532433623876</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8231449621794996</v>
+        <v>0.8231390521301486</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6484559499651469</v>
+        <v>0.6484496391058878</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8113194274977851</v>
+        <v>0.8112858132214468</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.327769604254384</v>
+        <v>7.263344373683893</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.688770065273216</v>
+        <v>7.612175530291583</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.015356698101943</v>
+        <v>7.951290212581002</v>
       </c>
     </row>
     <row r="13">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E13" t="n">
+        <v>14040</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14039</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14038</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         <v>30682</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M13" t="n">
         <v>0.26</v>
       </c>
       <c r="N13" t="n">
-        <v>8.134345882604359</v>
+        <v>8.134272918299024</v>
       </c>
       <c r="O13" t="n">
         <v>34.0025</v>
@@ -1594,37 +1594,37 @@
         <v>0.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.204022517489584</v>
+        <v>8.20398606578612</v>
       </c>
       <c r="R13" t="n">
         <v>14.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06967663488522495</v>
+        <v>0.06971314748709657</v>
       </c>
       <c r="T13" t="n">
-        <v>1.759977967731633</v>
+        <v>1.759940800674382</v>
       </c>
       <c r="U13" t="n">
-        <v>2.285358155561822</v>
+        <v>2.285324126909901</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7806980901130567</v>
+        <v>0.7806878590301031</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649369937042079</v>
+        <v>0.5649216675177244</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7803386521161693</v>
+        <v>0.7803277220727809</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.175338062833483</v>
+        <v>6.150060621123949</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.330156553077177</v>
+        <v>6.294321744634845</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.512216211567904</v>
+        <v>6.417577083736757</v>
       </c>
     </row>
     <row r="14">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1683,37 +1683,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.82552192549244</v>
+        <v>11.82540296008992</v>
       </c>
       <c r="R14" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1383599718938091</v>
+        <v>-0.1384789372963315</v>
       </c>
       <c r="T14" t="n">
-        <v>2.052549934730245</v>
+        <v>2.05254790086228</v>
       </c>
       <c r="U14" t="n">
-        <v>2.698059965267305</v>
+        <v>2.698035029382869</v>
       </c>
       <c r="V14" t="n">
-        <v>0.794744098747145</v>
+        <v>0.7947537377267091</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6094751250813673</v>
+        <v>0.609482343629713</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7858579931677233</v>
+        <v>0.7858754930769789</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.171810589981328</v>
+        <v>8.112198383532567</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.296913495104311</v>
+        <v>8.266944188555764</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.389419204380809</v>
+        <v>8.386190456843899</v>
       </c>
     </row>
     <row r="15">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E15" t="n">
+        <v>9803</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9802</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9801</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
         <v>35804</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M15" t="n">
         <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>8.409413155120225</v>
+        <v>8.409206114398422</v>
       </c>
       <c r="O15" t="n">
         <v>131.9</v>
@@ -1772,37 +1772,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.66355542641087</v>
+        <v>8.663410365066063</v>
       </c>
       <c r="R15" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2541422712906439</v>
+        <v>0.2542042506676397</v>
       </c>
       <c r="T15" t="n">
-        <v>3.53679365639656</v>
+        <v>3.53704702128188</v>
       </c>
       <c r="U15" t="n">
-        <v>11.06520679939195</v>
+        <v>11.06480267116538</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04964511346769675</v>
+        <v>0.04962423525881914</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.596949638179824</v>
+        <v>-0.5969871650191567</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03288895518929591</v>
+        <v>0.0328684986362866</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.81954001023077</v>
+        <v>10.80710432166193</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.35346457164039</v>
+        <v>11.27870079799203</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.81034798284707</v>
+        <v>11.72446986015789</v>
       </c>
     </row>
     <row r="16">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1861,37 +1861,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.954939778501083</v>
+        <v>6.954977017902347</v>
       </c>
       <c r="R16" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3718063728611686</v>
+        <v>0.3718436122624336</v>
       </c>
       <c r="T16" t="n">
-        <v>2.040734871266995</v>
+        <v>2.040766775093611</v>
       </c>
       <c r="U16" t="n">
-        <v>2.579822443878717</v>
+        <v>2.579850801617949</v>
       </c>
       <c r="V16" t="n">
-        <v>0.518110315037839</v>
+        <v>0.5180994345523291</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01508763950890413</v>
+        <v>0.0150659868238866</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5148113820469902</v>
+        <v>0.5147999233341668</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.256802654783871</v>
+        <v>3.066768957281612</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.216359069012279</v>
+        <v>4.666772670401492</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.085508762630371</v>
+        <v>6.098798888117923</v>
       </c>
     </row>
     <row r="17">
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E17" t="n">
+        <v>3206</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3205</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3204</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         <v>42370</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M17" t="n">
         <v>1.81</v>
       </c>
       <c r="N17" t="n">
-        <v>6.501852372034955</v>
+        <v>6.500984399375975</v>
       </c>
       <c r="O17" t="n">
         <v>18.4925</v>
@@ -1950,37 +1950,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.69644383013072</v>
+        <v>6.695353468669601</v>
       </c>
       <c r="R17" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1945914580957638</v>
+        <v>0.1943690692936249</v>
       </c>
       <c r="T17" t="n">
-        <v>1.098093270421765</v>
+        <v>1.098300453856818</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4879502314557</v>
+        <v>1.488080911776046</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6007892903475741</v>
+        <v>0.6009810474556556</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2170748890872708</v>
+        <v>0.2173612186605975</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5978707599418338</v>
+        <v>0.5980790990002245</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.407509507712392</v>
+        <v>4.223859953760695</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.481337855009455</v>
+        <v>5.704976102164053</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.282784819998072</v>
+        <v>6.566954957711856</v>
       </c>
     </row>
     <row r="18">
@@ -1998,16 +1998,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16657</v>
+        <v>16658</v>
       </c>
       <c r="E18" t="n">
+        <v>7160</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7159</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7158</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2024,13 +2024,13 @@
         <v>37987</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="M18" t="n">
         <v>0.04</v>
       </c>
       <c r="N18" t="n">
-        <v>10.37492246437552</v>
+        <v>10.37378474647297</v>
       </c>
       <c r="O18" t="n">
         <v>24.5875</v>
@@ -2039,37 +2039,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.1579530595688</v>
+        <v>11.1570890277509</v>
       </c>
       <c r="R18" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S18" t="n">
-        <v>0.783030595193274</v>
+        <v>0.7833042812779266</v>
       </c>
       <c r="T18" t="n">
-        <v>2.035657657160924</v>
+        <v>2.036155551266067</v>
       </c>
       <c r="U18" t="n">
-        <v>2.754661476283585</v>
+        <v>2.755276833184246</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7262807610849884</v>
+        <v>0.7262960380052531</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4692161210425043</v>
+        <v>0.4692487959277398</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6790166987374697</v>
+        <v>0.6789935937513916</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.820460753846925</v>
+        <v>7.808866337979607</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.920922767604085</v>
+        <v>7.900997672454197</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.979100294050045</v>
+        <v>7.957081724282849</v>
       </c>
     </row>
   </sheetData>
@@ -2138,22 +2138,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.820460753846925</v>
+        <v>7.808866337979607</v>
       </c>
       <c r="G2" t="n">
-        <v>7.920922767604085</v>
+        <v>7.900997672454196</v>
       </c>
       <c r="H2" t="n">
-        <v>7.979100294050045</v>
+        <v>7.957081724282849</v>
       </c>
     </row>
     <row r="3">
@@ -2166,22 +2166,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.734153605288033</v>
+        <v>5.695600140793879</v>
       </c>
       <c r="G3" t="n">
-        <v>5.961456061839657</v>
+        <v>5.916496453723633</v>
       </c>
       <c r="H3" t="n">
-        <v>6.171095644044707</v>
+        <v>6.132555252878289</v>
       </c>
     </row>
     <row r="4">
@@ -2194,22 +2194,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.448242129297602</v>
+        <v>4.397513821108633</v>
       </c>
       <c r="G4" t="n">
-        <v>4.673430666105889</v>
+        <v>4.669712730371749</v>
       </c>
       <c r="H4" t="n">
-        <v>4.84023487544484</v>
+        <v>4.87543918918919</v>
       </c>
     </row>
     <row r="5">
@@ -2222,22 +2222,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81954001023077</v>
+        <v>10.80710432166193</v>
       </c>
       <c r="G5" t="n">
-        <v>11.35346457164039</v>
+        <v>11.27870079799203</v>
       </c>
       <c r="H5" t="n">
-        <v>11.81034798284707</v>
+        <v>11.72446986015789</v>
       </c>
     </row>
     <row r="6">
@@ -2250,22 +2250,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>58.62662276669903</v>
+        <v>55.4505356325888</v>
       </c>
       <c r="G6" t="n">
-        <v>105.0571713563318</v>
+        <v>102.0729227715629</v>
       </c>
       <c r="H6" t="n">
-        <v>110.9100723655944</v>
+        <v>109.6310784803326</v>
       </c>
     </row>
     <row r="7">
@@ -2278,22 +2278,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.171810589981328</v>
+        <v>8.112198383532567</v>
       </c>
       <c r="G7" t="n">
-        <v>8.296913495104311</v>
+        <v>8.266944188555765</v>
       </c>
       <c r="H7" t="n">
-        <v>8.389419204380809</v>
+        <v>8.386190456843899</v>
       </c>
     </row>
     <row r="8">
@@ -2306,22 +2306,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.327769604254384</v>
+        <v>7.263344373683893</v>
       </c>
       <c r="G8" t="n">
-        <v>7.688770065273216</v>
+        <v>7.612175530291583</v>
       </c>
       <c r="H8" t="n">
-        <v>8.015356698101943</v>
+        <v>7.951290212581002</v>
       </c>
     </row>
     <row r="9">
@@ -2334,22 +2334,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.926820442691524</v>
+        <v>4.988427302724435</v>
       </c>
       <c r="G9" t="n">
-        <v>5.154828226624991</v>
+        <v>5.186791640910849</v>
       </c>
       <c r="H9" t="n">
-        <v>5.339127765106988</v>
+        <v>5.369563763865793</v>
       </c>
     </row>
     <row r="10">
@@ -2362,22 +2362,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.431714396783157</v>
+        <v>5.41779519305913</v>
       </c>
       <c r="G10" t="n">
-        <v>5.792866714554192</v>
+        <v>5.714109989087143</v>
       </c>
       <c r="H10" t="n">
-        <v>6.23841994793755</v>
+        <v>6.16549590047524</v>
       </c>
     </row>
     <row r="11">
@@ -2390,22 +2390,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.256802654783871</v>
+        <v>3.066768957281612</v>
       </c>
       <c r="G11" t="n">
-        <v>4.216359069012278</v>
+        <v>4.666772670401492</v>
       </c>
       <c r="H11" t="n">
-        <v>5.085508762630371</v>
+        <v>6.098798888117923</v>
       </c>
     </row>
     <row r="12">
@@ -2418,22 +2418,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.175338062833483</v>
+        <v>6.150060621123949</v>
       </c>
       <c r="G12" t="n">
-        <v>6.330156553077177</v>
+        <v>6.294321744634845</v>
       </c>
       <c r="H12" t="n">
-        <v>6.512216211567904</v>
+        <v>6.417577083736757</v>
       </c>
     </row>
     <row r="13">
@@ -2446,22 +2446,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.985830193984139</v>
+        <v>9.913633413042616</v>
       </c>
       <c r="G13" t="n">
-        <v>10.14751528255746</v>
+        <v>10.13451417450528</v>
       </c>
       <c r="H13" t="n">
-        <v>10.26376587323174</v>
+        <v>10.33241706939511</v>
       </c>
     </row>
     <row r="14">
@@ -2474,22 +2474,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.824999999999999</v>
+        <v>5.80397675954893</v>
       </c>
       <c r="G14" t="n">
-        <v>6.246853956131094</v>
+        <v>6.147170062631207</v>
       </c>
       <c r="H14" t="n">
-        <v>6.819118199903117</v>
+        <v>6.618566214769787</v>
       </c>
     </row>
     <row r="15">
@@ -2502,22 +2502,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.583047424731074</v>
+        <v>6.585224086335303</v>
       </c>
       <c r="G15" t="n">
-        <v>6.698516263439359</v>
+        <v>6.669992491979627</v>
       </c>
       <c r="H15" t="n">
-        <v>6.900139837360185</v>
+        <v>6.851500946161667</v>
       </c>
     </row>
     <row r="16">
@@ -2530,22 +2530,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.407509507712392</v>
+        <v>4.223859953760695</v>
       </c>
       <c r="G16" t="n">
-        <v>5.481337855009455</v>
+        <v>5.704976102164053</v>
       </c>
       <c r="H16" t="n">
-        <v>6.282784819998072</v>
+        <v>6.566954957711856</v>
       </c>
     </row>
     <row r="17">
@@ -2558,22 +2558,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.564022737736554</v>
+        <v>4.521540468305478</v>
       </c>
       <c r="G17" t="n">
-        <v>4.704556034058134</v>
+        <v>4.710263992510255</v>
       </c>
       <c r="H17" t="n">
-        <v>4.850516014234875</v>
+        <v>4.853795080236487</v>
       </c>
     </row>
     <row r="18">
@@ -2586,22 +2586,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.712659863698741</v>
+        <v>2.676102418207682</v>
       </c>
       <c r="G18" t="n">
-        <v>3.151962644367367</v>
+        <v>3.045592579602153</v>
       </c>
       <c r="H18" t="n">
-        <v>3.734334088493765</v>
+        <v>3.660177650505923</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E2" t="n">
+        <v>9964</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9963</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9962</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -600,13 +600,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.876695777287</v>
+        <v>102.8721959583793</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -615,37 +615,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8745675582081</v>
+        <v>102.864006527594</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002128219078937251</v>
+        <v>-0.00818943078533025</v>
       </c>
       <c r="T2" t="n">
-        <v>17.76677761155148</v>
+        <v>17.78075958173597</v>
       </c>
       <c r="U2" t="n">
-        <v>36.12808208295553</v>
+        <v>36.1477791156893</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1291784860658599</v>
+        <v>0.1289632051107624</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7359592001629935</v>
+        <v>-0.7375608569834766</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1291723476924668</v>
+        <v>0.1289593378881614</v>
       </c>
       <c r="Y2" t="n">
-        <v>55.4505356325888</v>
+        <v>57.96440290374161</v>
       </c>
       <c r="Z2" t="n">
-        <v>102.0729227715629</v>
+        <v>103.0217884101631</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.6310784803326</v>
+        <v>112.2083162635633</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E3" t="n">
+        <v>14542</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14541</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14540</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906489683631362</v>
+        <v>4.9063785159205</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -704,37 +704,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.960161877454675</v>
+        <v>4.960060031058719</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05367219382331281</v>
+        <v>0.05368151513821828</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350800405444579</v>
+        <v>1.350742968104097</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72552312298772</v>
+        <v>1.725466234802212</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7794896778081066</v>
+        <v>0.7794937250659775</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664348203213234</v>
+        <v>0.5664449362637322</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784326797389758</v>
+        <v>0.7784361146748828</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.676102418207682</v>
+        <v>2.641143707730877</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.045592579602153</v>
+        <v>2.943885749466707</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.660177650505923</v>
+        <v>3.4159287109375</v>
       </c>
     </row>
     <row r="4">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E4" t="n">
+        <v>10224</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10223</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10222</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -778,52 +778,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.918870573273333</v>
+        <v>6.918667220972318</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3663371266002845</v>
+        <v>0.366410803127221</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.24779854718647</v>
+        <v>7.247591640115879</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289279739131383</v>
+        <v>0.3289244191435617</v>
       </c>
       <c r="T4" t="n">
-        <v>1.294242323477599</v>
+        <v>1.294137205572635</v>
       </c>
       <c r="U4" t="n">
-        <v>1.684204387947582</v>
+        <v>1.684127504716384</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674265445656839</v>
+        <v>0.8674307256654163</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370503359235272</v>
+        <v>0.7370589252026587</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471318531279164</v>
+        <v>0.8471322919886305</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.521540468305478</v>
+        <v>4.468795816834197</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.710263992510255</v>
+        <v>4.729571572790228</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.853795080236487</v>
+        <v>4.920186567164179</v>
       </c>
     </row>
     <row r="5">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E5" t="n">
+        <v>8835</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8834</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8833</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         <v>36892</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
       </c>
       <c r="N5" t="n">
-        <v>6.730521340427941</v>
+        <v>6.730629952456419</v>
       </c>
       <c r="O5" t="n">
         <v>10.6125</v>
@@ -882,37 +882,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.018542851353087</v>
+        <v>7.018644709774542</v>
       </c>
       <c r="R5" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2880215109251464</v>
+        <v>0.2880147573181243</v>
       </c>
       <c r="T5" t="n">
-        <v>1.482472894787415</v>
+        <v>1.482378119144737</v>
       </c>
       <c r="U5" t="n">
-        <v>1.911024146930933</v>
+        <v>1.9109253965041</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3047712353938641</v>
+        <v>0.3047665475051852</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1981453053548712</v>
+        <v>-0.198116149848639</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2801716747966886</v>
+        <v>0.280157987386268</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.585224086335303</v>
+        <v>6.584877592602586</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.669992491979627</v>
+        <v>6.644070024738618</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.851500946161667</v>
+        <v>6.796114150792287</v>
       </c>
     </row>
     <row r="6">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E6" t="n">
+        <v>14197</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14196</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14195</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>31048</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M6" t="n">
         <v>1.025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.582716273335682</v>
+        <v>5.582698471400394</v>
       </c>
       <c r="O6" t="n">
         <v>10.01</v>
@@ -971,37 +971,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.586594436298406</v>
+        <v>5.586562850491277</v>
       </c>
       <c r="R6" t="n">
         <v>10.01</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003878162962725149</v>
+        <v>0.003864379090882288</v>
       </c>
       <c r="T6" t="n">
-        <v>1.155969894764106</v>
+        <v>1.155939817776509</v>
       </c>
       <c r="U6" t="n">
-        <v>1.494133060665485</v>
+        <v>1.494086231089972</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5089831812198492</v>
+        <v>0.5089804101466687</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0746843090607513</v>
+        <v>0.07467885472077418</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5051301046062906</v>
+        <v>0.5051274017166605</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.695600140793879</v>
+        <v>5.667835392777893</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.916496453723633</v>
+        <v>5.864670803933005</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.132555252878289</v>
+        <v>6.074785442525926</v>
       </c>
     </row>
     <row r="7">
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E7" t="n">
+        <v>8995</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8994</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8993</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>36161</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M7" t="n">
         <v>0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>7.880552930056712</v>
+        <v>7.880523960418057</v>
       </c>
       <c r="O7" t="n">
         <v>15.14</v>
@@ -1060,37 +1060,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.117027593516593</v>
+        <v>8.117066828355105</v>
       </c>
       <c r="R7" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2364746634598817</v>
+        <v>0.2365428679370481</v>
       </c>
       <c r="T7" t="n">
-        <v>1.444883725553443</v>
+        <v>1.445007382837185</v>
       </c>
       <c r="U7" t="n">
-        <v>1.824648387221298</v>
+        <v>1.824776667903271</v>
       </c>
       <c r="V7" t="n">
-        <v>0.808870822299501</v>
+        <v>0.8088185882426118</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6291791664490274</v>
+        <v>0.6290860956416819</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7991935657167738</v>
+        <v>0.7991327320662163</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.41779519305913</v>
+        <v>5.414231966861299</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.714109989087143</v>
+        <v>5.641419862059164</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.16549590047524</v>
+        <v>6.071345084680269</v>
       </c>
     </row>
     <row r="8">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E8" t="n">
+        <v>13860</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13859</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13858</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1134,52 +1134,52 @@
         <v>31778</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M8" t="n">
         <v>0.06</v>
       </c>
       <c r="N8" t="n">
-        <v>7.616416510318948</v>
+        <v>7.616299155783245</v>
       </c>
       <c r="O8" t="n">
         <v>14.03</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5109672830725462</v>
+        <v>0.5110270078180525</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680353320811876</v>
+        <v>7.680244747569352</v>
       </c>
       <c r="R8" t="n">
         <v>14.03</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06393681049292603</v>
+        <v>0.06394559178610675</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477599350058033</v>
+        <v>1.477535848102087</v>
       </c>
       <c r="U8" t="n">
-        <v>1.919979072220288</v>
+        <v>1.919912243287635</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7616695815522693</v>
+        <v>0.7616736283703898</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5360724474324461</v>
+        <v>0.5360824116297338</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7596874717771415</v>
+        <v>0.7596907677158721</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.80397675954893</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.147170062631207</v>
+        <v>6.066138632022915</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.618566214769787</v>
+        <v>6.477126581101191</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1238,37 +1238,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.61987154496531</v>
+        <v>10.6197870453843</v>
       </c>
       <c r="R9" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3148120052275556</v>
+        <v>0.3147275056465388</v>
       </c>
       <c r="T9" t="n">
-        <v>2.051521053247226</v>
+        <v>2.051536659807487</v>
       </c>
       <c r="U9" t="n">
-        <v>2.697244012183474</v>
+        <v>2.697254360268108</v>
       </c>
       <c r="V9" t="n">
-        <v>0.356553750210395</v>
+        <v>0.3565672197896378</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1197269455238359</v>
+        <v>-0.1197355372948243</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3357235633391252</v>
+        <v>0.3357469684442652</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.913633413042616</v>
+        <v>9.756580107230132</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.13451417450528</v>
+        <v>10.06457785048013</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.33241706939511</v>
+        <v>10.1961277443124</v>
       </c>
     </row>
     <row r="10">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E10" t="n">
+        <v>13801</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13799</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>31413</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M10" t="n">
         <v>0.4375</v>
       </c>
       <c r="N10" t="n">
-        <v>5.245831763171244</v>
+        <v>5.245828442028985</v>
       </c>
       <c r="O10" t="n">
         <v>10.15</v>
@@ -1327,37 +1327,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.218409558136631</v>
+        <v>5.218435813488892</v>
       </c>
       <c r="R10" t="n">
         <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0274222050346136</v>
+        <v>-0.02739262854009375</v>
       </c>
       <c r="T10" t="n">
-        <v>1.157957943254914</v>
+        <v>1.157944244510758</v>
       </c>
       <c r="U10" t="n">
-        <v>1.476894227139439</v>
+        <v>1.476874657568389</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4295389285743149</v>
+        <v>0.4295094039357884</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0822090961875257</v>
+        <v>-0.08225875959828732</v>
       </c>
       <c r="X10" t="n">
-        <v>0.426929025260595</v>
+        <v>0.4268991902669584</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.397513821108633</v>
+        <v>4.268691804475113</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.66971273037175</v>
+        <v>4.619736655811471</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.87543918918919</v>
+        <v>4.799026174321612</v>
       </c>
     </row>
     <row r="11">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E11" t="n">
+        <v>4119</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4118</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4117</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         <v>41640</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M11" t="n">
         <v>2.195</v>
       </c>
       <c r="N11" t="n">
-        <v>7.494608331309206</v>
+        <v>7.493898130160273</v>
       </c>
       <c r="O11" t="n">
         <v>19.1775</v>
@@ -1416,37 +1416,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.667031242045945</v>
+        <v>7.666327514913565</v>
       </c>
       <c r="R11" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1724229107367392</v>
+        <v>0.1724293847532928</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9153372311500512</v>
+        <v>0.9152331543356148</v>
       </c>
       <c r="U11" t="n">
-        <v>1.198541677287495</v>
+        <v>1.198393850858718</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8293048436034099</v>
+        <v>0.8293903185810912</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6536710422245208</v>
+        <v>0.6538457084815417</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8276327612164939</v>
+        <v>0.827716581812971</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.988427302724435</v>
+        <v>5.023687734348782</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.18679164091085</v>
+        <v>5.286410178018048</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.369563763865793</v>
+        <v>5.619216533870701</v>
       </c>
     </row>
     <row r="12">
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6452</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6451</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1490,52 +1490,52 @@
         <v>39083</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M12" t="n">
         <v>1.54</v>
       </c>
       <c r="N12" t="n">
-        <v>9.61817961039632</v>
+        <v>9.617873010952676</v>
       </c>
       <c r="O12" t="n">
         <v>16.215</v>
       </c>
       <c r="P12" t="n">
-        <v>2.860734352773826</v>
+        <v>2.860980810234541</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.03200122611163</v>
+        <v>10.03193252979777</v>
       </c>
       <c r="R12" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4138216157153068</v>
+        <v>0.4140595188450917</v>
       </c>
       <c r="T12" t="n">
-        <v>1.695016552894801</v>
+        <v>1.694832412828065</v>
       </c>
       <c r="U12" t="n">
-        <v>2.154532433623876</v>
+        <v>2.154409930589408</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8231390521301486</v>
+        <v>0.8231373031638333</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6484496391058878</v>
+        <v>0.6484512732446618</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8112858132214468</v>
+        <v>0.8112560756573297</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.263344373683893</v>
+        <v>7.15658241422304</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.612175530291583</v>
+        <v>7.532969780822566</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.951290212581002</v>
+        <v>7.834697946931337</v>
       </c>
     </row>
     <row r="13">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E13" t="n">
+        <v>14041</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14040</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14039</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         <v>30682</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M13" t="n">
         <v>0.26</v>
       </c>
       <c r="N13" t="n">
-        <v>8.134272918299024</v>
+        <v>8.134192841880342</v>
       </c>
       <c r="O13" t="n">
         <v>34.0025</v>
@@ -1594,37 +1594,37 @@
         <v>0.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.20398606578612</v>
+        <v>8.203936183413795</v>
       </c>
       <c r="R13" t="n">
         <v>14.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06971314748709657</v>
+        <v>0.06974334153345253</v>
       </c>
       <c r="T13" t="n">
-        <v>1.759940800674382</v>
+        <v>1.759901329554981</v>
       </c>
       <c r="U13" t="n">
-        <v>2.285324126909901</v>
+        <v>2.285289654438297</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7806878590301031</v>
+        <v>0.7806781373497919</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649216675177244</v>
+        <v>0.5649070664480205</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7803277220727809</v>
+        <v>0.7803173655835214</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.150060621123949</v>
+        <v>6.113195594044903</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.294321744634845</v>
+        <v>6.264803192168804</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.417577083736757</v>
+        <v>6.402061259389914</v>
       </c>
     </row>
     <row r="14">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1683,37 +1683,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.82540296008992</v>
+        <v>11.82528296146499</v>
       </c>
       <c r="R14" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1384789372963315</v>
+        <v>-0.1385989359212623</v>
       </c>
       <c r="T14" t="n">
-        <v>2.05254790086228</v>
+        <v>2.052538522902051</v>
       </c>
       <c r="U14" t="n">
-        <v>2.698035029382869</v>
+        <v>2.698006141586156</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7947537377267091</v>
+        <v>0.7947640378037472</v>
       </c>
       <c r="W14" t="n">
-        <v>0.609482343629713</v>
+        <v>0.6094907061114105</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7858754930769789</v>
+        <v>0.7858936962881927</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.112198383532567</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.266944188555764</v>
+        <v>8.231572699741008</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.386190456843899</v>
+        <v>8.379490765351326</v>
       </c>
     </row>
     <row r="15">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E15" t="n">
+        <v>9804</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9803</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9802</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
         <v>35804</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M15" t="n">
         <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>8.409206114398422</v>
+        <v>8.408984834574451</v>
       </c>
       <c r="O15" t="n">
         <v>131.9</v>
@@ -1772,37 +1772,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.663410365066063</v>
+        <v>8.663247524463072</v>
       </c>
       <c r="R15" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2542042506676397</v>
+        <v>0.2542626898886213</v>
       </c>
       <c r="T15" t="n">
-        <v>3.53704702128188</v>
+        <v>3.537309818500055</v>
       </c>
       <c r="U15" t="n">
-        <v>11.06480267116538</v>
+        <v>11.06440405070521</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04962423525881914</v>
+        <v>0.04960286730216647</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5969871650191567</v>
+        <v>-0.5970250146195217</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0328684986362866</v>
+        <v>0.03284751799204799</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.80710432166193</v>
+        <v>10.81663708336081</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.27870079799203</v>
+        <v>11.24830266386778</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.72446986015789</v>
+        <v>11.6585795361902</v>
       </c>
     </row>
     <row r="16">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1861,37 +1861,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.954977017902347</v>
+        <v>6.955010370116171</v>
       </c>
       <c r="R16" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3718436122624336</v>
+        <v>0.3718769644762583</v>
       </c>
       <c r="T16" t="n">
-        <v>2.040766775093611</v>
+        <v>2.040802723748258</v>
       </c>
       <c r="U16" t="n">
-        <v>2.579850801617949</v>
+        <v>2.579880654520218</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5180994345523291</v>
+        <v>0.5180885849489347</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0150659868238866</v>
+        <v>0.01504319224294559</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5147999233341668</v>
+        <v>0.5147885615474337</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.066768957281612</v>
+        <v>2.974543113419943</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.666772670401492</v>
+        <v>4.321948019601132</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.098798888117923</v>
+        <v>5.376756815138862</v>
       </c>
     </row>
     <row r="17">
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E17" t="n">
+        <v>3207</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3206</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3205</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         <v>42370</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M17" t="n">
         <v>1.81</v>
       </c>
       <c r="N17" t="n">
-        <v>6.500984399375975</v>
+        <v>6.500110729881471</v>
       </c>
       <c r="O17" t="n">
         <v>18.4925</v>
@@ -1950,37 +1950,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.695353468669601</v>
+        <v>6.694541996572474</v>
       </c>
       <c r="R17" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1943690692936249</v>
+        <v>0.1944312666910016</v>
       </c>
       <c r="T17" t="n">
-        <v>1.098300453856818</v>
+        <v>1.098595129605603</v>
       </c>
       <c r="U17" t="n">
-        <v>1.488080911776046</v>
+        <v>1.488259517178445</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6009810474556556</v>
+        <v>0.6010870244738611</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2173612186605975</v>
+        <v>0.2176057779773122</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5980790990002245</v>
+        <v>0.5981778486328866</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.223859953760695</v>
+        <v>4.014713786450042</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.704976102164053</v>
+        <v>5.452258349987021</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.566954957711856</v>
+        <v>6.356710696226234</v>
       </c>
     </row>
     <row r="18">
@@ -1998,16 +1998,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16658</v>
+        <v>16659</v>
       </c>
       <c r="E18" t="n">
+        <v>7161</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7160</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7159</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2024,13 +2024,13 @@
         <v>37987</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="M18" t="n">
         <v>0.04</v>
       </c>
       <c r="N18" t="n">
-        <v>10.37378474647297</v>
+        <v>10.37262360335196</v>
       </c>
       <c r="O18" t="n">
         <v>24.5875</v>
@@ -2039,37 +2039,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.1570890277509</v>
+        <v>11.15623499521204</v>
       </c>
       <c r="R18" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7833042812779266</v>
+        <v>0.7836113918600843</v>
       </c>
       <c r="T18" t="n">
-        <v>2.036155551266067</v>
+        <v>2.036690174271222</v>
       </c>
       <c r="U18" t="n">
-        <v>2.755276833184246</v>
+        <v>2.75594590995638</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7262960380052531</v>
+        <v>0.7263065624995827</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4692487959277398</v>
+        <v>0.4692750123222601</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6789935937513916</v>
+        <v>0.6789578264397955</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.808866337979607</v>
+        <v>7.809368026845428</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.900997672454197</v>
+        <v>7.897331356302781</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.957081724282849</v>
+        <v>7.957121221481099</v>
       </c>
     </row>
   </sheetData>
@@ -2138,22 +2138,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.808866337979607</v>
+        <v>7.809368026845428</v>
       </c>
       <c r="G2" t="n">
-        <v>7.900997672454196</v>
+        <v>7.89733135630278</v>
       </c>
       <c r="H2" t="n">
-        <v>7.957081724282849</v>
+        <v>7.957121221481099</v>
       </c>
     </row>
     <row r="3">
@@ -2166,22 +2166,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.695600140793879</v>
+        <v>5.667835392777893</v>
       </c>
       <c r="G3" t="n">
-        <v>5.916496453723633</v>
+        <v>5.864670803933005</v>
       </c>
       <c r="H3" t="n">
-        <v>6.132555252878289</v>
+        <v>6.074785442525926</v>
       </c>
     </row>
     <row r="4">
@@ -2194,22 +2194,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.397513821108633</v>
+        <v>4.268691804475113</v>
       </c>
       <c r="G4" t="n">
-        <v>4.669712730371749</v>
+        <v>4.619736655811471</v>
       </c>
       <c r="H4" t="n">
-        <v>4.87543918918919</v>
+        <v>4.799026174321612</v>
       </c>
     </row>
     <row r="5">
@@ -2222,22 +2222,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.80710432166193</v>
+        <v>10.81663708336081</v>
       </c>
       <c r="G5" t="n">
-        <v>11.27870079799203</v>
+        <v>11.24830266386778</v>
       </c>
       <c r="H5" t="n">
-        <v>11.72446986015789</v>
+        <v>11.6585795361902</v>
       </c>
     </row>
     <row r="6">
@@ -2250,22 +2250,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>55.4505356325888</v>
+        <v>57.96440290374161</v>
       </c>
       <c r="G6" t="n">
-        <v>102.0729227715629</v>
+        <v>103.0217884101631</v>
       </c>
       <c r="H6" t="n">
-        <v>109.6310784803326</v>
+        <v>112.2083162635633</v>
       </c>
     </row>
     <row r="7">
@@ -2278,22 +2278,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.112198383532567</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>8.266944188555765</v>
+        <v>8.231572699741008</v>
       </c>
       <c r="H7" t="n">
-        <v>8.386190456843899</v>
+        <v>8.379490765351326</v>
       </c>
     </row>
     <row r="8">
@@ -2306,22 +2306,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.263344373683893</v>
+        <v>7.15658241422304</v>
       </c>
       <c r="G8" t="n">
-        <v>7.612175530291583</v>
+        <v>7.532969780822566</v>
       </c>
       <c r="H8" t="n">
-        <v>7.951290212581002</v>
+        <v>7.834697946931337</v>
       </c>
     </row>
     <row r="9">
@@ -2334,22 +2334,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.988427302724435</v>
+        <v>5.023687734348782</v>
       </c>
       <c r="G9" t="n">
-        <v>5.186791640910849</v>
+        <v>5.286410178018049</v>
       </c>
       <c r="H9" t="n">
-        <v>5.369563763865793</v>
+        <v>5.619216533870701</v>
       </c>
     </row>
     <row r="10">
@@ -2362,22 +2362,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.41779519305913</v>
+        <v>5.414231966861299</v>
       </c>
       <c r="G10" t="n">
-        <v>5.714109989087143</v>
+        <v>5.641419862059164</v>
       </c>
       <c r="H10" t="n">
-        <v>6.16549590047524</v>
+        <v>6.071345084680269</v>
       </c>
     </row>
     <row r="11">
@@ -2390,22 +2390,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.066768957281612</v>
+        <v>2.974543113419943</v>
       </c>
       <c r="G11" t="n">
-        <v>4.666772670401492</v>
+        <v>4.321948019601132</v>
       </c>
       <c r="H11" t="n">
-        <v>6.098798888117923</v>
+        <v>5.376756815138862</v>
       </c>
     </row>
     <row r="12">
@@ -2418,22 +2418,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.150060621123949</v>
+        <v>6.113195594044903</v>
       </c>
       <c r="G12" t="n">
-        <v>6.294321744634845</v>
+        <v>6.264803192168804</v>
       </c>
       <c r="H12" t="n">
-        <v>6.417577083736757</v>
+        <v>6.402061259389914</v>
       </c>
     </row>
     <row r="13">
@@ -2446,22 +2446,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.913633413042616</v>
+        <v>9.756580107230132</v>
       </c>
       <c r="G13" t="n">
-        <v>10.13451417450528</v>
+        <v>10.06457785048013</v>
       </c>
       <c r="H13" t="n">
-        <v>10.33241706939511</v>
+        <v>10.1961277443124</v>
       </c>
     </row>
     <row r="14">
@@ -2474,22 +2474,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.80397675954893</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.147170062631207</v>
+        <v>6.066138632022914</v>
       </c>
       <c r="H14" t="n">
-        <v>6.618566214769787</v>
+        <v>6.477126581101191</v>
       </c>
     </row>
     <row r="15">
@@ -2502,22 +2502,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.585224086335303</v>
+        <v>6.584877592602586</v>
       </c>
       <c r="G15" t="n">
-        <v>6.669992491979627</v>
+        <v>6.644070024738618</v>
       </c>
       <c r="H15" t="n">
-        <v>6.851500946161667</v>
+        <v>6.796114150792287</v>
       </c>
     </row>
     <row r="16">
@@ -2530,22 +2530,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.223859953760695</v>
+        <v>4.014713786450042</v>
       </c>
       <c r="G16" t="n">
-        <v>5.704976102164053</v>
+        <v>5.452258349987021</v>
       </c>
       <c r="H16" t="n">
-        <v>6.566954957711856</v>
+        <v>6.356710696226234</v>
       </c>
     </row>
     <row r="17">
@@ -2558,22 +2558,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.521540468305478</v>
+        <v>4.468795816834197</v>
       </c>
       <c r="G17" t="n">
-        <v>4.710263992510255</v>
+        <v>4.729571572790228</v>
       </c>
       <c r="H17" t="n">
-        <v>4.853795080236487</v>
+        <v>4.920186567164179</v>
       </c>
     </row>
     <row r="18">
@@ -2586,22 +2586,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.676102418207682</v>
+        <v>2.641143707730877</v>
       </c>
       <c r="G18" t="n">
-        <v>3.045592579602153</v>
+        <v>2.943885749466707</v>
       </c>
       <c r="H18" t="n">
-        <v>3.660177650505923</v>
+        <v>3.4159287109375</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E2" t="n">
+        <v>9965</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>9964</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>9963</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -600,13 +600,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.8721959583793</v>
+        <v>102.8624175364646</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -615,37 +615,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.864006527594</v>
+        <v>102.8519253584598</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.00818943078533025</v>
+        <v>-0.01049217800477509</v>
       </c>
       <c r="T2" t="n">
-        <v>17.78075958173597</v>
+        <v>17.80157038404047</v>
       </c>
       <c r="U2" t="n">
-        <v>36.1477791156893</v>
+        <v>36.17718519485685</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1289632051107624</v>
+        <v>0.1286615177056522</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7375608569834766</v>
+        <v>-0.7383613312981927</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1289593378881614</v>
+        <v>0.128657982310455</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.96440290374161</v>
+        <v>55.34978867161523</v>
       </c>
       <c r="Z2" t="n">
-        <v>103.0217884101631</v>
+        <v>94.58901961180834</v>
       </c>
       <c r="AA2" t="n">
-        <v>112.2083162635633</v>
+        <v>111.9386664488551</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E3" t="n">
+        <v>14543</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14542</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14541</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9063785159205</v>
+        <v>4.906259799202311</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -704,37 +704,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.960060031058719</v>
+        <v>4.959951368118586</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05368151513821828</v>
+        <v>0.05369156891627525</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350742968104097</v>
+        <v>1.35067257340534</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725466234802212</v>
+        <v>1.725407881848078</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7794937250659775</v>
+        <v>0.779498975060154</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664449362637322</v>
+        <v>0.56645738555179</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784361146748828</v>
+        <v>0.7784407417753088</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.641143707730877</v>
+        <v>2.618647017045455</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.943885749466707</v>
+        <v>2.863510902027563</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.4159287109375</v>
+        <v>3.213587376286024</v>
       </c>
     </row>
     <row r="4">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E4" t="n">
+        <v>10225</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10224</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10223</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -778,52 +778,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.918667220972318</v>
+        <v>6.918452171361503</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.366410803127221</v>
+        <v>0.366484375</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.247591640115879</v>
+        <v>7.247365402245439</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289244191435617</v>
+        <v>0.3289132308839373</v>
       </c>
       <c r="T4" t="n">
-        <v>1.294137205572635</v>
+        <v>1.294020939390829</v>
       </c>
       <c r="U4" t="n">
-        <v>1.684127504716384</v>
+        <v>1.68405083491661</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674307256654163</v>
+        <v>0.8674354598407927</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370589252026587</v>
+        <v>0.7370686724260412</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471322919886305</v>
+        <v>0.8471345771736677</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.468795816834197</v>
+        <v>4.366803950110907</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.729571572790228</v>
+        <v>4.702666687417636</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.920186567164179</v>
+        <v>4.908515625000001</v>
       </c>
     </row>
     <row r="5">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E5" t="n">
+        <v>8836</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8835</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8834</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         <v>36892</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
       </c>
       <c r="N5" t="n">
-        <v>6.730629952456419</v>
+        <v>6.730712507074137</v>
       </c>
       <c r="O5" t="n">
         <v>10.6125</v>
@@ -882,37 +882,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.018644709774542</v>
+        <v>7.018704464435805</v>
       </c>
       <c r="R5" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2880147573181243</v>
+        <v>0.2879919573616675</v>
       </c>
       <c r="T5" t="n">
-        <v>1.482378119144737</v>
+        <v>1.482255793371226</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9109253965041</v>
+        <v>1.910801624714779</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3047665475051852</v>
+        <v>0.3047693000535027</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.198116149848639</v>
+        <v>-0.1980728882287346</v>
       </c>
       <c r="X5" t="n">
-        <v>0.280157987386268</v>
+        <v>0.2801517905521779</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.584877592602586</v>
+        <v>6.584780165674451</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.644070024738618</v>
+        <v>6.623875175206199</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.796114150792287</v>
+        <v>6.751020666045311</v>
       </c>
     </row>
     <row r="6">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E6" t="n">
+        <v>14198</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14197</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14196</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>31048</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M6" t="n">
         <v>1.025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.582698471400394</v>
+        <v>5.582667993238009</v>
       </c>
       <c r="O6" t="n">
         <v>10.01</v>
@@ -971,37 +971,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.586562850491277</v>
+        <v>5.586515318657749</v>
       </c>
       <c r="R6" t="n">
         <v>10.01</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003864379090882288</v>
+        <v>0.003847325419740975</v>
       </c>
       <c r="T6" t="n">
-        <v>1.155939817776509</v>
+        <v>1.155923263788208</v>
       </c>
       <c r="U6" t="n">
-        <v>1.494086231089972</v>
+        <v>1.494046470565302</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5089804101466687</v>
+        <v>0.5089754762504918</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07467885472077418</v>
+        <v>0.07466798328048252</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5051274017166605</v>
+        <v>0.5051227520644512</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.667835392777893</v>
+        <v>5.635907912543326</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.864670803933005</v>
+        <v>5.818283667797244</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.074785442525926</v>
+        <v>6.022846078872679</v>
       </c>
     </row>
     <row r="7">
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E7" t="n">
+        <v>8996</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8995</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8994</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>36161</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M7" t="n">
         <v>0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>7.880523960418057</v>
+        <v>7.880470539188439</v>
       </c>
       <c r="O7" t="n">
         <v>15.14</v>
@@ -1060,37 +1060,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.117066828355105</v>
+        <v>8.117100625335533</v>
       </c>
       <c r="R7" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2365428679370481</v>
+        <v>0.2366300861470961</v>
       </c>
       <c r="T7" t="n">
-        <v>1.445007382837185</v>
+        <v>1.445103762672603</v>
       </c>
       <c r="U7" t="n">
-        <v>1.824776667903271</v>
+        <v>1.824884636356038</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8088185882426118</v>
+        <v>0.8087715673180205</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6290860956416819</v>
+        <v>0.6290020176687918</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7991327320662163</v>
+        <v>0.7990763713461138</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.414231966861299</v>
+        <v>5.417649374249502</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.641419862059164</v>
+        <v>5.578357533350208</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.071345084680269</v>
+        <v>5.959028507264875</v>
       </c>
     </row>
     <row r="8">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E8" t="n">
+        <v>13861</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13860</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13859</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1134,52 +1134,52 @@
         <v>31778</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M8" t="n">
         <v>0.06</v>
       </c>
       <c r="N8" t="n">
-        <v>7.616299155783245</v>
+        <v>7.616176767676767</v>
       </c>
       <c r="O8" t="n">
         <v>14.03</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5110270078180525</v>
+        <v>0.5110866477272727</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680244747569352</v>
+        <v>7.680142439800599</v>
       </c>
       <c r="R8" t="n">
         <v>14.03</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06394559178610675</v>
+        <v>0.06396567212383042</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477535848102087</v>
+        <v>1.477469189116053</v>
       </c>
       <c r="U8" t="n">
-        <v>1.919912243287635</v>
+        <v>1.919843438642987</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7616736283703898</v>
+        <v>0.7616782264988169</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5360824116297338</v>
+        <v>0.5360943118286992</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7596907677158721</v>
+        <v>0.7596942486868571</v>
       </c>
       <c r="Y8" t="n">
         <v>5.824999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.066138632022915</v>
+        <v>6.002507932875021</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.477126581101191</v>
+        <v>6.377110368382586</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1238,37 +1238,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.6197870453843</v>
+        <v>10.6197052933109</v>
       </c>
       <c r="R9" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3147275056465388</v>
+        <v>0.3146457535731448</v>
       </c>
       <c r="T9" t="n">
-        <v>2.051536659807487</v>
+        <v>2.051556897641879</v>
       </c>
       <c r="U9" t="n">
-        <v>2.697254360268108</v>
+        <v>2.697266547771196</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3565672197896378</v>
+        <v>0.3565797419176347</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1197355372948243</v>
+        <v>-0.1197456563339114</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3357469684442652</v>
+        <v>0.3357693578191221</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.756580107230132</v>
+        <v>9.6975</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.06457785048013</v>
+        <v>10.02425683814955</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.1961277443124</v>
+        <v>10.18839784026962</v>
       </c>
     </row>
     <row r="10">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E10" t="n">
+        <v>13802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13801</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13800</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>31413</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M10" t="n">
         <v>0.4375</v>
       </c>
       <c r="N10" t="n">
-        <v>5.245828442028985</v>
+        <v>5.245846858923266</v>
       </c>
       <c r="O10" t="n">
         <v>10.15</v>
@@ -1327,37 +1327,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.218435813488892</v>
+        <v>5.218486579585917</v>
       </c>
       <c r="R10" t="n">
         <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02739262854009375</v>
+        <v>-0.02736027933734994</v>
       </c>
       <c r="T10" t="n">
-        <v>1.157944244510758</v>
+        <v>1.157955757584128</v>
       </c>
       <c r="U10" t="n">
-        <v>1.476874657568389</v>
+        <v>1.476876203054406</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4295094039357884</v>
+        <v>0.4294668766830239</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.08225875959828732</v>
+        <v>-0.08233693547658794</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4268991902669584</v>
+        <v>0.426856784306594</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.268691804475113</v>
+        <v>4.362436079545454</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.619736655811471</v>
+        <v>4.58919519803784</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.799026174321612</v>
+        <v>4.797168501420455</v>
       </c>
     </row>
     <row r="11">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E11" t="n">
+        <v>4120</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4119</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4118</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         <v>41640</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M11" t="n">
         <v>2.195</v>
       </c>
       <c r="N11" t="n">
-        <v>7.493898130160273</v>
+        <v>7.493154285020636</v>
       </c>
       <c r="O11" t="n">
         <v>19.1775</v>
@@ -1416,37 +1416,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.666327514913565</v>
+        <v>7.66563218171054</v>
       </c>
       <c r="R11" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1724293847532928</v>
+        <v>0.1724778966899043</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9152331543356148</v>
+        <v>0.9151631727551706</v>
       </c>
       <c r="U11" t="n">
-        <v>1.198393850858718</v>
+        <v>1.19825801027288</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8293903185810912</v>
+        <v>0.8294769171695218</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6538457084815417</v>
+        <v>0.6540301879762359</v>
       </c>
       <c r="X11" t="n">
-        <v>0.827716581812971</v>
+        <v>0.8277994753486901</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.023687734348782</v>
+        <v>5.018376582911224</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.286410178018048</v>
+        <v>5.299119453921174</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.619216533870701</v>
+        <v>5.611274962795059</v>
       </c>
     </row>
     <row r="12">
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E12" t="n">
+        <v>6454</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6453</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6452</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1490,52 +1490,52 @@
         <v>39083</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M12" t="n">
         <v>1.54</v>
       </c>
       <c r="N12" t="n">
-        <v>9.617873010952676</v>
+        <v>9.617554109199855</v>
       </c>
       <c r="O12" t="n">
         <v>16.215</v>
       </c>
       <c r="P12" t="n">
-        <v>2.860980810234541</v>
+        <v>2.861226917613636</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.03193252979777</v>
+        <v>10.03184074321753</v>
       </c>
       <c r="R12" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4140595188450917</v>
+        <v>0.4142866340176777</v>
       </c>
       <c r="T12" t="n">
-        <v>1.694832412828065</v>
+        <v>1.694633891344969</v>
       </c>
       <c r="U12" t="n">
-        <v>2.154409930589408</v>
+        <v>2.154284918952813</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8231373031638333</v>
+        <v>0.8231367298256138</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6484512732446618</v>
+        <v>0.6484550631950872</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8112560756573297</v>
+        <v>0.8112284592389722</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.15658241422304</v>
+        <v>7.087816773678604</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.532969780822566</v>
+        <v>7.457557648149839</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.834697946931337</v>
+        <v>7.827565013797048</v>
       </c>
     </row>
     <row r="13">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E13" t="n">
+        <v>14042</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14041</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14040</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         <v>30682</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M13" t="n">
         <v>0.26</v>
       </c>
       <c r="N13" t="n">
-        <v>8.134192841880342</v>
+        <v>8.134099245068015</v>
       </c>
       <c r="O13" t="n">
         <v>34.0025</v>
@@ -1594,37 +1594,37 @@
         <v>0.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.203936183413795</v>
+        <v>8.20387555673298</v>
       </c>
       <c r="R13" t="n">
         <v>14.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06974334153345253</v>
+        <v>0.06977631166496498</v>
       </c>
       <c r="T13" t="n">
-        <v>1.759901329554981</v>
+        <v>1.759841247556907</v>
       </c>
       <c r="U13" t="n">
-        <v>2.285289654438297</v>
+        <v>2.285247044839636</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7806781373497919</v>
+        <v>0.7806705733855706</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649070664480205</v>
+        <v>0.5648967614231388</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7803173655835214</v>
+        <v>0.7803091435569753</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.113195594044903</v>
+        <v>6.099426426196878</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.264803192168804</v>
+        <v>6.234345802131548</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.402061259389914</v>
+        <v>6.361473138534987</v>
       </c>
     </row>
     <row r="14">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1683,37 +1683,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.82528296146499</v>
+        <v>11.82516058367071</v>
       </c>
       <c r="R14" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1385989359212623</v>
+        <v>-0.1387213137155465</v>
       </c>
       <c r="T14" t="n">
-        <v>2.052538522902051</v>
+        <v>2.052526096424659</v>
       </c>
       <c r="U14" t="n">
-        <v>2.698006141586156</v>
+        <v>2.697974384932118</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7947640378037472</v>
+        <v>0.7947749016721485</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6094907061114105</v>
+        <v>0.6094998989708111</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7858936962881927</v>
+        <v>0.7859126097196837</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.050000000000001</v>
+        <v>8.032085718465092</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.231572699741008</v>
+        <v>8.195354409550784</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.379490765351326</v>
+        <v>8.368535819238222</v>
       </c>
     </row>
     <row r="15">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E15" t="n">
+        <v>9805</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9804</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9803</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
         <v>35804</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M15" t="n">
         <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>8.408984834574451</v>
+        <v>8.40875135998912</v>
       </c>
       <c r="O15" t="n">
         <v>131.9</v>
@@ -1772,37 +1772,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.663247524463072</v>
+        <v>8.663077033502896</v>
       </c>
       <c r="R15" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2542626898886213</v>
+        <v>0.2543256735137758</v>
       </c>
       <c r="T15" t="n">
-        <v>3.537309818500055</v>
+        <v>3.537584691909693</v>
       </c>
       <c r="U15" t="n">
-        <v>11.06440405070521</v>
+        <v>11.0640081714426</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04960286730216647</v>
+        <v>0.04958133622931484</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5970250146195217</v>
+        <v>-0.5970625010100612</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03284751799204799</v>
+        <v>0.03282628058713966</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.81663708336081</v>
+        <v>10.81315097454897</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.24830266386778</v>
+        <v>11.24476057726472</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.6585795361902</v>
+        <v>11.70095704640943</v>
       </c>
     </row>
     <row r="16">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1861,37 +1861,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.955010370116171</v>
+        <v>6.955019680519424</v>
       </c>
       <c r="R16" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3718769644762583</v>
+        <v>0.37188627487951</v>
       </c>
       <c r="T16" t="n">
-        <v>2.040802723748258</v>
+        <v>2.040835315932505</v>
       </c>
       <c r="U16" t="n">
-        <v>2.579880654520218</v>
+        <v>2.579908578748651</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5180885849489347</v>
+        <v>0.5180820786482546</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01504319224294559</v>
+        <v>0.01502187008783062</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5147885615474337</v>
+        <v>0.5147819240135021</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.974543113419943</v>
+        <v>2.872021247406188</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.321948019601132</v>
+        <v>4.497102840075323</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.376756815138862</v>
+        <v>5.515992224545575</v>
       </c>
     </row>
     <row r="17">
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E17" t="n">
+        <v>3208</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3207</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3206</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         <v>42370</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M17" t="n">
         <v>1.81</v>
       </c>
       <c r="N17" t="n">
-        <v>6.500110729881471</v>
+        <v>6.499281259744309</v>
       </c>
       <c r="O17" t="n">
         <v>18.4925</v>
@@ -1950,37 +1950,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.694541996572474</v>
+        <v>6.693917952402354</v>
       </c>
       <c r="R17" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1944312666910016</v>
+        <v>0.1946366926580461</v>
       </c>
       <c r="T17" t="n">
-        <v>1.098595129605603</v>
+        <v>1.09897784278212</v>
       </c>
       <c r="U17" t="n">
-        <v>1.488259517178445</v>
+        <v>1.488589078525427</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6010870244738611</v>
+        <v>0.6010710624863992</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2176057779773122</v>
+        <v>0.2176248778453787</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5981778486328866</v>
+        <v>0.598149978119344</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.014713786450042</v>
+        <v>3.904206801461247</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.452258349987021</v>
+        <v>5.605974386543087</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.356710696226234</v>
+        <v>6.431727052779645</v>
       </c>
     </row>
     <row r="18">
@@ -1998,16 +1998,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16659</v>
+        <v>16660</v>
       </c>
       <c r="E18" t="n">
+        <v>7162</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7161</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7160</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2024,13 +2024,13 @@
         <v>37987</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="M18" t="n">
         <v>0.04</v>
       </c>
       <c r="N18" t="n">
-        <v>10.37262360335196</v>
+        <v>10.3714474235442</v>
       </c>
       <c r="O18" t="n">
         <v>24.5875</v>
@@ -2039,37 +2039,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.15623499521204</v>
+        <v>11.15534910830626</v>
       </c>
       <c r="R18" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7836113918600843</v>
+        <v>0.7839016847620595</v>
       </c>
       <c r="T18" t="n">
-        <v>2.036690174271222</v>
+        <v>2.037245963529109</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75594590995638</v>
+        <v>2.756649005134139</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7263065624995827</v>
+        <v>0.7263142473708095</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4692750123222601</v>
+        <v>0.4692973872044116</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6789578264397955</v>
+        <v>0.6789229805380611</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.809368026845428</v>
+        <v>7.805692940984459</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.897331356302781</v>
+        <v>7.874745514765029</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.957121221481099</v>
+        <v>7.950231605569276</v>
       </c>
     </row>
   </sheetData>
@@ -2138,22 +2138,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.809368026845428</v>
+        <v>7.805692940984459</v>
       </c>
       <c r="G2" t="n">
-        <v>7.89733135630278</v>
+        <v>7.874745514765027</v>
       </c>
       <c r="H2" t="n">
-        <v>7.957121221481099</v>
+        <v>7.950231605569276</v>
       </c>
     </row>
     <row r="3">
@@ -2166,22 +2166,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.667835392777893</v>
+        <v>5.635907912543326</v>
       </c>
       <c r="G3" t="n">
-        <v>5.864670803933005</v>
+        <v>5.818283667797243</v>
       </c>
       <c r="H3" t="n">
-        <v>6.074785442525926</v>
+        <v>6.022846078872679</v>
       </c>
     </row>
     <row r="4">
@@ -2194,22 +2194,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.268691804475113</v>
+        <v>4.362436079545454</v>
       </c>
       <c r="G4" t="n">
-        <v>4.619736655811471</v>
+        <v>4.58919519803784</v>
       </c>
       <c r="H4" t="n">
-        <v>4.799026174321612</v>
+        <v>4.797168501420455</v>
       </c>
     </row>
     <row r="5">
@@ -2222,22 +2222,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81663708336081</v>
+        <v>10.81315097454897</v>
       </c>
       <c r="G5" t="n">
-        <v>11.24830266386778</v>
+        <v>11.24476057726472</v>
       </c>
       <c r="H5" t="n">
-        <v>11.6585795361902</v>
+        <v>11.70095704640943</v>
       </c>
     </row>
     <row r="6">
@@ -2250,22 +2250,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>57.96440290374161</v>
+        <v>55.34978867161523</v>
       </c>
       <c r="G6" t="n">
-        <v>103.0217884101631</v>
+        <v>94.58901961180834</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2083162635633</v>
+        <v>111.9386664488551</v>
       </c>
     </row>
     <row r="7">
@@ -2278,22 +2278,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.050000000000001</v>
+        <v>8.032085718465092</v>
       </c>
       <c r="G7" t="n">
-        <v>8.231572699741008</v>
+        <v>8.195354409550784</v>
       </c>
       <c r="H7" t="n">
-        <v>8.379490765351326</v>
+        <v>8.368535819238222</v>
       </c>
     </row>
     <row r="8">
@@ -2306,22 +2306,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.15658241422304</v>
+        <v>7.087816773678604</v>
       </c>
       <c r="G8" t="n">
-        <v>7.532969780822566</v>
+        <v>7.457557648149839</v>
       </c>
       <c r="H8" t="n">
-        <v>7.834697946931337</v>
+        <v>7.827565013797048</v>
       </c>
     </row>
     <row r="9">
@@ -2334,22 +2334,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.023687734348782</v>
+        <v>5.018376582911224</v>
       </c>
       <c r="G9" t="n">
-        <v>5.286410178018049</v>
+        <v>5.299119453921174</v>
       </c>
       <c r="H9" t="n">
-        <v>5.619216533870701</v>
+        <v>5.611274962795059</v>
       </c>
     </row>
     <row r="10">
@@ -2362,22 +2362,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.414231966861299</v>
+        <v>5.417649374249502</v>
       </c>
       <c r="G10" t="n">
-        <v>5.641419862059164</v>
+        <v>5.578357533350209</v>
       </c>
       <c r="H10" t="n">
-        <v>6.071345084680269</v>
+        <v>5.959028507264875</v>
       </c>
     </row>
     <row r="11">
@@ -2390,22 +2390,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.974543113419943</v>
+        <v>2.872021247406188</v>
       </c>
       <c r="G11" t="n">
-        <v>4.321948019601132</v>
+        <v>4.497102840075322</v>
       </c>
       <c r="H11" t="n">
-        <v>5.376756815138862</v>
+        <v>5.515992224545575</v>
       </c>
     </row>
     <row r="12">
@@ -2418,22 +2418,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.113195594044903</v>
+        <v>6.099426426196878</v>
       </c>
       <c r="G12" t="n">
-        <v>6.264803192168804</v>
+        <v>6.234345802131548</v>
       </c>
       <c r="H12" t="n">
-        <v>6.402061259389914</v>
+        <v>6.361473138534987</v>
       </c>
     </row>
     <row r="13">
@@ -2446,22 +2446,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.756580107230132</v>
+        <v>9.6975</v>
       </c>
       <c r="G13" t="n">
-        <v>10.06457785048013</v>
+        <v>10.02425683814955</v>
       </c>
       <c r="H13" t="n">
-        <v>10.1961277443124</v>
+        <v>10.18839784026962</v>
       </c>
     </row>
     <row r="14">
@@ -2474,10 +2474,10 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
         <v>5.824999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.066138632022914</v>
+        <v>6.002507932875021</v>
       </c>
       <c r="H14" t="n">
-        <v>6.477126581101191</v>
+        <v>6.377110368382586</v>
       </c>
     </row>
     <row r="15">
@@ -2502,22 +2502,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.584877592602586</v>
+        <v>6.584780165674451</v>
       </c>
       <c r="G15" t="n">
-        <v>6.644070024738618</v>
+        <v>6.623875175206199</v>
       </c>
       <c r="H15" t="n">
-        <v>6.796114150792287</v>
+        <v>6.751020666045311</v>
       </c>
     </row>
     <row r="16">
@@ -2530,22 +2530,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.014713786450042</v>
+        <v>3.904206801461247</v>
       </c>
       <c r="G16" t="n">
-        <v>5.452258349987021</v>
+        <v>5.605974386543087</v>
       </c>
       <c r="H16" t="n">
-        <v>6.356710696226234</v>
+        <v>6.431727052779645</v>
       </c>
     </row>
     <row r="17">
@@ -2558,22 +2558,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.468795816834197</v>
+        <v>4.366803950110907</v>
       </c>
       <c r="G17" t="n">
-        <v>4.729571572790228</v>
+        <v>4.702666687417636</v>
       </c>
       <c r="H17" t="n">
-        <v>4.920186567164179</v>
+        <v>4.908515625000001</v>
       </c>
     </row>
     <row r="18">
@@ -2586,22 +2586,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.641143707730877</v>
+        <v>2.618647017045455</v>
       </c>
       <c r="G18" t="n">
-        <v>2.943885749466707</v>
+        <v>2.863510902027563</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4159287109375</v>
+        <v>3.213587376286024</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -583,7 +583,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9964</v>
+        <v>9965</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -600,13 +600,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.8624175364646</v>
+        <v>102.8526290349557</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -615,37 +615,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8519253584598</v>
+        <v>102.8517400704246</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01049217800477509</v>
+        <v>-0.0008889645310845734</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80157038404047</v>
+        <v>17.8102554245504</v>
       </c>
       <c r="U2" t="n">
-        <v>36.17718519485685</v>
+        <v>36.18961960822894</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1286615177056522</v>
+        <v>0.1285504339773765</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7383613312981927</v>
+        <v>-0.7375276062683822</v>
       </c>
       <c r="X2" t="n">
-        <v>0.128657982310455</v>
+        <v>0.1285449648154223</v>
       </c>
       <c r="Y2" t="n">
-        <v>55.34978867161523</v>
+        <v>54.62002736156155</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.58901961180834</v>
+        <v>94.19075793545417</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.9386664488551</v>
+        <v>110.2660116977248</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E3" t="n">
+        <v>14544</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14543</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14542</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -689,13 +689,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906259799202311</v>
+        <v>4.906135597882142</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -704,37 +704,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959951368118586</v>
+        <v>4.959843685721722</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05369156891627525</v>
+        <v>0.05370808783957928</v>
       </c>
       <c r="T3" t="n">
-        <v>1.35067257340534</v>
+        <v>1.350587164245165</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725407881848078</v>
+        <v>1.725346438099607</v>
       </c>
       <c r="V3" t="n">
-        <v>0.779498975060154</v>
+        <v>0.7795053382774603</v>
       </c>
       <c r="W3" t="n">
-        <v>0.56645738555179</v>
+        <v>0.5664726154068926</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784407417753088</v>
+        <v>0.7784462656546735</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.618647017045455</v>
+        <v>2.592601135557133</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.863510902027563</v>
+        <v>2.800783134391457</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.213587376286024</v>
+        <v>3.099729136443566</v>
       </c>
     </row>
     <row r="4">
@@ -752,16 +752,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E4" t="n">
+        <v>10226</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10225</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10224</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -778,52 +778,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.918452171361503</v>
+        <v>6.918221515892421</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.366484375</v>
+        <v>0.3665578424414478</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.247365402245439</v>
+        <v>7.24712127535387</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289132308839373</v>
+        <v>0.3288997594614492</v>
       </c>
       <c r="T4" t="n">
-        <v>1.294020939390829</v>
+        <v>1.293917409639079</v>
       </c>
       <c r="U4" t="n">
-        <v>1.68405083491661</v>
+        <v>1.683972951679149</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674354598407927</v>
+        <v>0.8674413508999779</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370686724260412</v>
+        <v>0.7370805370957414</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471345771736677</v>
+        <v>0.8471386373670609</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.366803950110907</v>
+        <v>4.242369588360539</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.702666687417636</v>
+        <v>4.654691175076457</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.908515625000001</v>
+        <v>4.907998580553584</v>
       </c>
     </row>
     <row r="5">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E5" t="n">
+        <v>8837</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
         <v>8836</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8835</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         <v>36892</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M5" t="n">
         <v>1.52</v>
       </c>
       <c r="N5" t="n">
-        <v>6.730712507074137</v>
+        <v>6.730774671797193</v>
       </c>
       <c r="O5" t="n">
         <v>10.6125</v>
@@ -882,37 +882,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.018704464435805</v>
+        <v>7.018731073071335</v>
       </c>
       <c r="R5" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2879919573616675</v>
+        <v>0.287956401274142</v>
       </c>
       <c r="T5" t="n">
-        <v>1.482255793371226</v>
+        <v>1.482115137231137</v>
       </c>
       <c r="U5" t="n">
-        <v>1.910801624714779</v>
+        <v>1.910672252159408</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3047693000535027</v>
+        <v>0.3047696908443753</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1980728882287346</v>
+        <v>-0.1980328239852089</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2801517905521779</v>
+        <v>0.280143786521527</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.584780165674451</v>
+        <v>6.571068511422081</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.623875175206199</v>
+        <v>6.606384527979982</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.751020666045311</v>
+        <v>6.678056700139964</v>
       </c>
     </row>
     <row r="6">
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E6" t="n">
+        <v>14199</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>14198</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>14197</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -956,13 +956,13 @@
         <v>31048</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M6" t="n">
         <v>1.025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.582667993238009</v>
+        <v>5.582624841526975</v>
       </c>
       <c r="O6" t="n">
         <v>10.01</v>
@@ -971,37 +971,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.586515318657749</v>
+        <v>5.586455636561203</v>
       </c>
       <c r="R6" t="n">
         <v>10.01</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003847325419740975</v>
+        <v>0.003830795034226368</v>
       </c>
       <c r="T6" t="n">
-        <v>1.155923263788208</v>
+        <v>1.155923939521207</v>
       </c>
       <c r="U6" t="n">
-        <v>1.494046470565302</v>
+        <v>1.49401941594255</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5089754762504918</v>
+        <v>0.5089653155571648</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07466798328048252</v>
+        <v>0.07464646115237838</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5051227520644512</v>
+        <v>0.5051130378454496</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.635907912543326</v>
+        <v>5.621515615205388</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.818283667797244</v>
+        <v>5.77421969213418</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.022846078872679</v>
+        <v>5.964795628363793</v>
       </c>
     </row>
     <row r="7">
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E7" t="n">
+        <v>8997</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>8996</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8995</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>36161</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M7" t="n">
         <v>0.16</v>
       </c>
       <c r="N7" t="n">
-        <v>7.880470539188439</v>
+        <v>7.880412683414852</v>
       </c>
       <c r="O7" t="n">
         <v>15.14</v>
@@ -1060,37 +1060,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.117100625335533</v>
+        <v>8.117138943756959</v>
       </c>
       <c r="R7" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2366300861470961</v>
+        <v>0.2367262603421096</v>
       </c>
       <c r="T7" t="n">
-        <v>1.445103762672603</v>
+        <v>1.445208063119896</v>
       </c>
       <c r="U7" t="n">
-        <v>1.824884636356038</v>
+        <v>1.824992953055081</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8087715673180205</v>
+        <v>0.8087247744568659</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6290020176687918</v>
+        <v>0.6289179699499088</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7990763713461138</v>
+        <v>0.799019987712574</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.417649374249502</v>
+        <v>5.417876837077897</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.578357533350208</v>
+        <v>5.525841267246117</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.959028507264875</v>
+        <v>5.822456982157617</v>
       </c>
     </row>
     <row r="8">
@@ -1108,16 +1108,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E8" t="n">
+        <v>13862</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>13861</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13860</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1134,52 +1134,52 @@
         <v>31778</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M8" t="n">
         <v>0.06</v>
       </c>
       <c r="N8" t="n">
-        <v>7.616176767676767</v>
+        <v>7.616058725921651</v>
       </c>
       <c r="O8" t="n">
         <v>14.03</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5110866477272727</v>
+        <v>0.5111462029808375</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680142439800599</v>
+        <v>7.680051219233575</v>
       </c>
       <c r="R8" t="n">
         <v>14.03</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06396567212383042</v>
+        <v>0.06399249331192496</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477469189116053</v>
+        <v>1.477393422227689</v>
       </c>
       <c r="U8" t="n">
-        <v>1.919843438642987</v>
+        <v>1.919777958916156</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7616782264988169</v>
+        <v>0.7616813207885352</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5360943118286992</v>
+        <v>0.5361037641974629</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7596942486868571</v>
+        <v>0.7596960354318436</v>
       </c>
       <c r="Y8" t="n">
         <v>5.824999999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.002507932875021</v>
+        <v>5.9542641943926</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.377110368382586</v>
+        <v>6.229175915694021</v>
       </c>
     </row>
     <row r="9">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E9" t="n">
         <v>3737</v>
@@ -1238,37 +1238,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.6197052933109</v>
+        <v>10.61962564999381</v>
       </c>
       <c r="R9" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3146457535731448</v>
+        <v>0.3145661102560481</v>
       </c>
       <c r="T9" t="n">
-        <v>2.051556897641879</v>
+        <v>2.051578190706187</v>
       </c>
       <c r="U9" t="n">
-        <v>2.697266547771196</v>
+        <v>2.697278764864449</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3565797419176347</v>
+        <v>0.3565918615084092</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1197456563339114</v>
+        <v>-0.1197557999870078</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3357693578191221</v>
+        <v>0.3357911284612216</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.6975</v>
+        <v>9.638635098665931</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.02425683814955</v>
+        <v>9.983637656221976</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.18839784026962</v>
+        <v>10.18847836147522</v>
       </c>
     </row>
     <row r="10">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E10" t="n">
+        <v>13803</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
         <v>13802</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" t="n">
-        <v>13801</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1312,13 +1312,13 @@
         <v>31413</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M10" t="n">
         <v>0.4375</v>
       </c>
       <c r="N10" t="n">
-        <v>5.245846858923266</v>
+        <v>5.245892805390523</v>
       </c>
       <c r="O10" t="n">
         <v>10.15</v>
@@ -1327,37 +1327,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.218486579585917</v>
+        <v>5.218481096109767</v>
       </c>
       <c r="R10" t="n">
         <v>9.94</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02736027933734994</v>
+        <v>-0.02741170928075623</v>
       </c>
       <c r="T10" t="n">
-        <v>1.157955757584128</v>
+        <v>1.157959341415278</v>
       </c>
       <c r="U10" t="n">
-        <v>1.476876203054406</v>
+        <v>1.476858501200477</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4294668766830239</v>
+        <v>0.429441008037597</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.08233693547658794</v>
+        <v>-0.08237376307301725</v>
       </c>
       <c r="X10" t="n">
-        <v>0.426856784306594</v>
+        <v>0.426829702165243</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.362436079545454</v>
+        <v>4.208148868904629</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.58919519803784</v>
+        <v>4.514783153919013</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.797168501420455</v>
+        <v>4.798307807960266</v>
       </c>
     </row>
     <row r="11">
@@ -1375,16 +1375,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E11" t="n">
+        <v>4121</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>4120</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4119</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1401,13 +1401,13 @@
         <v>41640</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M11" t="n">
         <v>2.195</v>
       </c>
       <c r="N11" t="n">
-        <v>7.493154285020636</v>
+        <v>7.492422936893204</v>
       </c>
       <c r="O11" t="n">
         <v>19.1775</v>
@@ -1416,37 +1416,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.66563218171054</v>
+        <v>7.66499505620931</v>
       </c>
       <c r="R11" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1724778966899043</v>
+        <v>0.1725721193161059</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9151631727551706</v>
+        <v>0.9150745493701999</v>
       </c>
       <c r="U11" t="n">
-        <v>1.19825801027288</v>
+        <v>1.198125989012055</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8294769171695218</v>
+        <v>0.8295552769163127</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6540301879762359</v>
+        <v>0.6542060566617065</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8277994753486901</v>
+        <v>0.8278719766778936</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.018376582911224</v>
+        <v>5.014501875597941</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.299119453921174</v>
+        <v>5.300475529855683</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.611274962795059</v>
+        <v>5.60937751270759</v>
       </c>
     </row>
     <row r="12">
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E12" t="n">
+        <v>6455</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>6454</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6453</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1490,52 +1490,52 @@
         <v>39083</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M12" t="n">
         <v>1.54</v>
       </c>
       <c r="N12" t="n">
-        <v>9.617554109199855</v>
+        <v>9.617222910856317</v>
       </c>
       <c r="O12" t="n">
         <v>16.215</v>
       </c>
       <c r="P12" t="n">
-        <v>2.861226917613636</v>
+        <v>2.861472675656494</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.03184074321753</v>
+        <v>10.03174522953336</v>
       </c>
       <c r="R12" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4142866340176777</v>
+        <v>0.414522318677047</v>
       </c>
       <c r="T12" t="n">
-        <v>1.694633891344969</v>
+        <v>1.694447788301102</v>
       </c>
       <c r="U12" t="n">
-        <v>2.154284918952813</v>
+        <v>2.154165408954601</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8231367298256138</v>
+        <v>0.8231360602626578</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6484550631950872</v>
+        <v>0.6484584466156459</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8112284592389722</v>
+        <v>0.8112002024082149</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.087816773678604</v>
+        <v>6.939325738512945</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.457557648149839</v>
+        <v>7.367581367768191</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.827565013797048</v>
+        <v>7.743712160733097</v>
       </c>
     </row>
     <row r="13">
@@ -1553,16 +1553,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E13" t="n">
+        <v>14043</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>14042</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14041</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1579,13 +1579,13 @@
         <v>30682</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M13" t="n">
         <v>0.26</v>
       </c>
       <c r="N13" t="n">
-        <v>8.134099245068015</v>
+        <v>8.13399711579547</v>
       </c>
       <c r="O13" t="n">
         <v>34.0025</v>
@@ -1594,37 +1594,37 @@
         <v>0.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.20387555673298</v>
+        <v>8.203802186560146</v>
       </c>
       <c r="R13" t="n">
         <v>14.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06977631166496498</v>
+        <v>0.06980507076467643</v>
       </c>
       <c r="T13" t="n">
-        <v>1.759841247556907</v>
+        <v>1.759770425278798</v>
       </c>
       <c r="U13" t="n">
-        <v>2.285247044839636</v>
+        <v>2.285200344214135</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7806705733855706</v>
+        <v>0.7806643744223386</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5648967614231388</v>
+        <v>0.5648888672600482</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7803091435569753</v>
+        <v>0.7803023378216738</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.099426426196878</v>
+        <v>6.093879896466462</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.234345802131548</v>
+        <v>6.20060389697934</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.361473138534987</v>
+        <v>6.322116165621164</v>
       </c>
     </row>
     <row r="14">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E14" t="n">
         <v>3099</v>
@@ -1683,37 +1683,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.82516058367071</v>
+        <v>11.82503999215002</v>
       </c>
       <c r="R14" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1387213137155465</v>
+        <v>-0.1388419052362373</v>
       </c>
       <c r="T14" t="n">
-        <v>2.052526096424659</v>
+        <v>2.052514105828003</v>
       </c>
       <c r="U14" t="n">
-        <v>2.697974384932118</v>
+        <v>2.697943782918296</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7947749016721485</v>
+        <v>0.7947855129683991</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6094998989708111</v>
+        <v>0.6095087574846529</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7859126097196837</v>
+        <v>0.7859311731344821</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.032085718465092</v>
+        <v>7.870952815983502</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.195354409550784</v>
+        <v>8.144857647703128</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.368535819238222</v>
+        <v>8.333009729834103</v>
       </c>
     </row>
     <row r="15">
@@ -1731,16 +1731,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E15" t="n">
+        <v>9806</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>9805</v>
-      </c>
-      <c r="F15" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" t="n">
-        <v>9804</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1757,13 +1757,13 @@
         <v>35804</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M15" t="n">
         <v>0.26</v>
       </c>
       <c r="N15" t="n">
-        <v>8.40875135998912</v>
+        <v>8.408512833588304</v>
       </c>
       <c r="O15" t="n">
         <v>131.9</v>
@@ -1772,37 +1772,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.663077033502896</v>
+        <v>8.662918875592325</v>
       </c>
       <c r="R15" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2543256735137758</v>
+        <v>0.2544060420040198</v>
       </c>
       <c r="T15" t="n">
-        <v>3.537584691909693</v>
+        <v>3.537865272702922</v>
       </c>
       <c r="U15" t="n">
-        <v>11.0640081714426</v>
+        <v>11.06361438194357</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04958133622931484</v>
+        <v>0.04955943679836131</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5970625010100612</v>
+        <v>-0.5971000815699585</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03282628058713966</v>
+        <v>0.03280454175648839</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.81315097454897</v>
+        <v>10.80161542816917</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.24476057726472</v>
+        <v>11.25382818534252</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.70095704640943</v>
+        <v>11.72673630745086</v>
       </c>
     </row>
     <row r="16">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E16" t="n">
         <v>2305</v>
@@ -1861,37 +1861,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.955019680519424</v>
+        <v>6.955003837956245</v>
       </c>
       <c r="R16" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S16" t="n">
-        <v>0.37188627487951</v>
+        <v>0.3718704323163314</v>
       </c>
       <c r="T16" t="n">
-        <v>2.040835315932505</v>
+        <v>2.040859866306212</v>
       </c>
       <c r="U16" t="n">
-        <v>2.579908578748651</v>
+        <v>2.579931141164777</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5180820786482546</v>
+        <v>0.518080516359496</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01502187008783062</v>
+        <v>0.01500464189315576</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5147819240135021</v>
+        <v>0.5147806285315646</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.872021247406188</v>
+        <v>2.667476001209895</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.497102840075323</v>
+        <v>4.136592442981486</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.515992224545575</v>
+        <v>5.361938671031083</v>
       </c>
     </row>
     <row r="17">
@@ -1909,16 +1909,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E17" t="n">
+        <v>3209</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>3208</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3207</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1935,13 +1935,13 @@
         <v>42370</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M17" t="n">
         <v>1.81</v>
       </c>
       <c r="N17" t="n">
-        <v>6.499281259744309</v>
+        <v>6.498508416458852</v>
       </c>
       <c r="O17" t="n">
         <v>18.4925</v>
@@ -1950,37 +1950,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.693917952402354</v>
+        <v>6.693383067949556</v>
       </c>
       <c r="R17" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1946366926580461</v>
+        <v>0.1948746514907041</v>
       </c>
       <c r="T17" t="n">
-        <v>1.09897784278212</v>
+        <v>1.099377977882823</v>
       </c>
       <c r="U17" t="n">
-        <v>1.488589078525427</v>
+        <v>1.48893409430651</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6010710624863992</v>
+        <v>0.6010145525892741</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2176248778453787</v>
+        <v>0.217547443422078</v>
       </c>
       <c r="X17" t="n">
-        <v>0.598149978119344</v>
+        <v>0.5980831351002822</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.904206801461247</v>
+        <v>3.810903603932743</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.605974386543087</v>
+        <v>5.192562502533661</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.431727052779645</v>
+        <v>6.294390339143794</v>
       </c>
     </row>
     <row r="18">
@@ -1998,16 +1998,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16660</v>
+        <v>16661</v>
       </c>
       <c r="E18" t="n">
+        <v>7163</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>7162</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7161</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2024,13 +2024,13 @@
         <v>37987</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="M18" t="n">
         <v>0.04</v>
       </c>
       <c r="N18" t="n">
-        <v>10.3714474235442</v>
+        <v>10.37037629153868</v>
       </c>
       <c r="O18" t="n">
         <v>24.5875</v>
@@ -2039,37 +2039,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q18" t="n">
-        <v>11.15534910830626</v>
+        <v>11.15446582536702</v>
       </c>
       <c r="R18" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7839016847620595</v>
+        <v>0.7840895338283447</v>
       </c>
       <c r="T18" t="n">
-        <v>2.037245963529109</v>
+        <v>2.03768776148797</v>
       </c>
       <c r="U18" t="n">
-        <v>2.756649005134139</v>
+        <v>2.757131417345985</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7263142473708095</v>
+        <v>0.7263387120159976</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4692973872044116</v>
+        <v>0.4693420147356044</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6789229805380611</v>
+        <v>0.6789283514315176</v>
       </c>
       <c r="Y18" t="n">
-        <v>7.805692940984459</v>
+        <v>7.774568432955215</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.874745514765029</v>
+        <v>7.851740384401721</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.950231605569276</v>
+        <v>7.929707656935572</v>
       </c>
     </row>
   </sheetData>
@@ -2138,22 +2138,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.805692940984459</v>
+        <v>7.774568432955215</v>
       </c>
       <c r="G2" t="n">
-        <v>7.874745514765027</v>
+        <v>7.851740384401721</v>
       </c>
       <c r="H2" t="n">
-        <v>7.950231605569276</v>
+        <v>7.929707656935572</v>
       </c>
     </row>
     <row r="3">
@@ -2166,22 +2166,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.635907912543326</v>
+        <v>5.621515615205388</v>
       </c>
       <c r="G3" t="n">
-        <v>5.818283667797243</v>
+        <v>5.77421969213418</v>
       </c>
       <c r="H3" t="n">
-        <v>6.022846078872679</v>
+        <v>5.964795628363793</v>
       </c>
     </row>
     <row r="4">
@@ -2194,22 +2194,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.362436079545454</v>
+        <v>4.208148868904629</v>
       </c>
       <c r="G4" t="n">
-        <v>4.58919519803784</v>
+        <v>4.514783153919014</v>
       </c>
       <c r="H4" t="n">
-        <v>4.797168501420455</v>
+        <v>4.798307807960266</v>
       </c>
     </row>
     <row r="5">
@@ -2222,22 +2222,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81315097454897</v>
+        <v>10.80161542816917</v>
       </c>
       <c r="G5" t="n">
-        <v>11.24476057726472</v>
+        <v>11.25382818534252</v>
       </c>
       <c r="H5" t="n">
-        <v>11.70095704640943</v>
+        <v>11.72673630745086</v>
       </c>
     </row>
     <row r="6">
@@ -2250,22 +2250,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>55.34978867161523</v>
+        <v>54.62002736156155</v>
       </c>
       <c r="G6" t="n">
-        <v>94.58901961180834</v>
+        <v>94.19075793545417</v>
       </c>
       <c r="H6" t="n">
-        <v>111.9386664488551</v>
+        <v>110.2660116977248</v>
       </c>
     </row>
     <row r="7">
@@ -2278,22 +2278,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.032085718465092</v>
+        <v>7.870952815983502</v>
       </c>
       <c r="G7" t="n">
-        <v>8.195354409550784</v>
+        <v>8.144857647703128</v>
       </c>
       <c r="H7" t="n">
-        <v>8.368535819238222</v>
+        <v>8.333009729834103</v>
       </c>
     </row>
     <row r="8">
@@ -2306,22 +2306,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.087816773678604</v>
+        <v>6.939325738512945</v>
       </c>
       <c r="G8" t="n">
-        <v>7.457557648149839</v>
+        <v>7.367581367768193</v>
       </c>
       <c r="H8" t="n">
-        <v>7.827565013797048</v>
+        <v>7.743712160733097</v>
       </c>
     </row>
     <row r="9">
@@ -2334,22 +2334,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.018376582911224</v>
+        <v>5.014501875597941</v>
       </c>
       <c r="G9" t="n">
-        <v>5.299119453921174</v>
+        <v>5.300475529855683</v>
       </c>
       <c r="H9" t="n">
-        <v>5.611274962795059</v>
+        <v>5.60937751270759</v>
       </c>
     </row>
     <row r="10">
@@ -2362,22 +2362,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.417649374249502</v>
+        <v>5.417876837077897</v>
       </c>
       <c r="G10" t="n">
-        <v>5.578357533350209</v>
+        <v>5.525841267246117</v>
       </c>
       <c r="H10" t="n">
-        <v>5.959028507264875</v>
+        <v>5.822456982157617</v>
       </c>
     </row>
     <row r="11">
@@ -2390,22 +2390,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.872021247406188</v>
+        <v>2.667476001209895</v>
       </c>
       <c r="G11" t="n">
-        <v>4.497102840075322</v>
+        <v>4.136592442981486</v>
       </c>
       <c r="H11" t="n">
-        <v>5.515992224545575</v>
+        <v>5.361938671031083</v>
       </c>
     </row>
     <row r="12">
@@ -2418,22 +2418,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.099426426196878</v>
+        <v>6.093879896466462</v>
       </c>
       <c r="G12" t="n">
-        <v>6.234345802131548</v>
+        <v>6.20060389697934</v>
       </c>
       <c r="H12" t="n">
-        <v>6.361473138534987</v>
+        <v>6.322116165621164</v>
       </c>
     </row>
     <row r="13">
@@ -2446,22 +2446,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.6975</v>
+        <v>9.638635098665931</v>
       </c>
       <c r="G13" t="n">
-        <v>10.02425683814955</v>
+        <v>9.983637656221976</v>
       </c>
       <c r="H13" t="n">
-        <v>10.18839784026962</v>
+        <v>10.18847836147522</v>
       </c>
     </row>
     <row r="14">
@@ -2474,10 +2474,10 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
@@ -2486,10 +2486,10 @@
         <v>5.824999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>6.002507932875021</v>
+        <v>5.9542641943926</v>
       </c>
       <c r="H14" t="n">
-        <v>6.377110368382586</v>
+        <v>6.229175915694021</v>
       </c>
     </row>
     <row r="15">
@@ -2502,22 +2502,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.584780165674451</v>
+        <v>6.571068511422081</v>
       </c>
       <c r="G15" t="n">
-        <v>6.623875175206199</v>
+        <v>6.606384527979984</v>
       </c>
       <c r="H15" t="n">
-        <v>6.751020666045311</v>
+        <v>6.678056700139964</v>
       </c>
     </row>
     <row r="16">
@@ -2530,22 +2530,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.904206801461247</v>
+        <v>3.810903603932743</v>
       </c>
       <c r="G16" t="n">
-        <v>5.605974386543087</v>
+        <v>5.192562502533661</v>
       </c>
       <c r="H16" t="n">
-        <v>6.431727052779645</v>
+        <v>6.294390339143794</v>
       </c>
     </row>
     <row r="17">
@@ -2558,22 +2558,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.366803950110907</v>
+        <v>4.242369588360539</v>
       </c>
       <c r="G17" t="n">
-        <v>4.702666687417636</v>
+        <v>4.654691175076456</v>
       </c>
       <c r="H17" t="n">
-        <v>4.908515625000001</v>
+        <v>4.907998580553584</v>
       </c>
     </row>
     <row r="18">
@@ -2586,22 +2586,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.618647017045455</v>
+        <v>2.592601135557133</v>
       </c>
       <c r="G18" t="n">
-        <v>2.863510902027563</v>
+        <v>2.800783134391457</v>
       </c>
       <c r="H18" t="n">
-        <v>3.213587376286024</v>
+        <v>3.099729136443566</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet name="metricas_dwlt" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="resumen_forecast_nivel" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="estaciones_saltadas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -829,11 +828,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Santa Clotilde</t>
+          <t>Timicurillo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9032282</v>
+        <v>9036459</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -844,13 +843,13 @@
         <v>16661</v>
       </c>
       <c r="E5" t="n">
-        <v>8837</v>
+        <v>2690</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>8836</v>
+        <v>2690</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -864,65 +863,65 @@
         <v>1</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>36892</v>
+        <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46247</v>
+        <v>46246</v>
       </c>
       <c r="M5" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>6.730774671797193</v>
+        <v>8.95478810408922</v>
       </c>
       <c r="O5" t="n">
-        <v>10.6125</v>
+        <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.616683937823834</v>
+        <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.018731073071335</v>
+        <v>9.313782114822216</v>
       </c>
       <c r="R5" t="n">
-        <v>10.19100035038542</v>
+        <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.287956401274142</v>
+        <v>0.3589940107329972</v>
       </c>
       <c r="T5" t="n">
-        <v>1.482115137231137</v>
+        <v>1.25477807844241</v>
       </c>
       <c r="U5" t="n">
-        <v>1.910672252159408</v>
+        <v>1.748032492511534</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3047696908443753</v>
+        <v>0.8674441770819028</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1980328239852089</v>
+        <v>0.7233934578599799</v>
       </c>
       <c r="X5" t="n">
-        <v>0.280143786521527</v>
+        <v>0.861513018196886</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.571068511422081</v>
+        <v>5.802478839292944</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.606384527979982</v>
+        <v>6.403218831576423</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.678056700139964</v>
+        <v>7.820329931345277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Santa Clotilde</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9036028</v>
+        <v>9032282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -933,13 +932,13 @@
         <v>16661</v>
       </c>
       <c r="E6" t="n">
-        <v>14199</v>
+        <v>8837</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>14198</v>
+        <v>8836</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -953,65 +952,65 @@
         <v>1</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>31048</v>
+        <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M6" t="n">
-        <v>1.025</v>
+        <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>5.582624841526975</v>
+        <v>6.730774671797193</v>
       </c>
       <c r="O6" t="n">
-        <v>10.01</v>
+        <v>10.6125</v>
       </c>
       <c r="P6" t="n">
-        <v>1.33253223495702</v>
+        <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.586455636561203</v>
+        <v>7.018731073071335</v>
       </c>
       <c r="R6" t="n">
-        <v>10.01</v>
+        <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.003830795034226368</v>
+        <v>0.287956401274142</v>
       </c>
       <c r="T6" t="n">
-        <v>1.155923939521207</v>
+        <v>1.482115137231137</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49401941594255</v>
+        <v>1.910672252159408</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5089653155571648</v>
+        <v>0.3047696908443753</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07464646115237838</v>
+        <v>-0.1980328239852089</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5051130378454496</v>
+        <v>0.280143786521527</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.621515615205388</v>
+        <v>6.571068511422081</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.77421969213418</v>
+        <v>6.606384527979982</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.964795628363793</v>
+        <v>6.678056700139964</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nauta</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9040454</v>
+        <v>9036028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1022,13 +1021,13 @@
         <v>16661</v>
       </c>
       <c r="E7" t="n">
-        <v>8997</v>
+        <v>14199</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>8996</v>
+        <v>14198</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1042,65 +1041,65 @@
         <v>1</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>36161</v>
+        <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M7" t="n">
-        <v>0.16</v>
+        <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>7.880412683414852</v>
+        <v>5.582624841526975</v>
       </c>
       <c r="O7" t="n">
-        <v>15.14</v>
+        <v>10.01</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6453438395415473</v>
+        <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>8.117138943756959</v>
+        <v>5.586455636561203</v>
       </c>
       <c r="R7" t="n">
-        <v>14.26297827610371</v>
+        <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2367262603421096</v>
+        <v>0.003830795034226368</v>
       </c>
       <c r="T7" t="n">
-        <v>1.445208063119896</v>
+        <v>1.155923939521207</v>
       </c>
       <c r="U7" t="n">
-        <v>1.824992953055081</v>
+        <v>1.49401941594255</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8087247744568659</v>
+        <v>0.5089653155571648</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6289179699499088</v>
+        <v>0.07464646115237838</v>
       </c>
       <c r="X7" t="n">
-        <v>0.799019987712574</v>
+        <v>0.5051130378454496</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.417876837077897</v>
+        <v>5.621515615205388</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.525841267246117</v>
+        <v>5.77421969213418</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.822456982157617</v>
+        <v>5.964795628363793</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>San Regis</t>
+          <t>Nauta</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9040439</v>
+        <v>9040454</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1111,13 +1110,13 @@
         <v>16661</v>
       </c>
       <c r="E8" t="n">
-        <v>13862</v>
+        <v>8997</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>13861</v>
+        <v>8996</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1131,65 +1130,65 @@
         <v>1</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>31778</v>
+        <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.616058725921651</v>
+        <v>7.880412683414852</v>
       </c>
       <c r="O8" t="n">
-        <v>14.03</v>
+        <v>15.14</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5111462029808375</v>
+        <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.680051219233575</v>
+        <v>8.117138943756959</v>
       </c>
       <c r="R8" t="n">
-        <v>14.03</v>
+        <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.06399249331192496</v>
+        <v>0.2367262603421096</v>
       </c>
       <c r="T8" t="n">
-        <v>1.477393422227689</v>
+        <v>1.445208063119896</v>
       </c>
       <c r="U8" t="n">
-        <v>1.919777958916156</v>
+        <v>1.824992953055081</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7616813207885352</v>
+        <v>0.8087247744568659</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361037641974629</v>
+        <v>0.6289179699499088</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7596960354318436</v>
+        <v>0.799019987712574</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.824999999999999</v>
+        <v>5.417876837077897</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.9542641943926</v>
+        <v>5.525841267246117</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.229175915694021</v>
+        <v>5.822456982157617</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>San Regis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9042153</v>
+        <v>9040439</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1200,13 +1199,13 @@
         <v>16661</v>
       </c>
       <c r="E9" t="n">
-        <v>3737</v>
+        <v>13862</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>3737</v>
+        <v>13861</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1220,65 +1219,65 @@
         <v>1</v>
       </c>
       <c r="K9" s="1" t="n">
-        <v>37257</v>
+        <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>45930</v>
+        <v>46247</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7875</v>
+        <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>10.30505953973775</v>
+        <v>7.616058725921651</v>
       </c>
       <c r="O9" t="n">
-        <v>39.075</v>
+        <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>4.255000000000001</v>
+        <v>0.5111462029808375</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.61962564999381</v>
+        <v>7.680051219233575</v>
       </c>
       <c r="R9" t="n">
-        <v>14.31645908761767</v>
+        <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3145661102560481</v>
+        <v>0.06399249331192496</v>
       </c>
       <c r="T9" t="n">
-        <v>2.051578190706187</v>
+        <v>1.477393422227689</v>
       </c>
       <c r="U9" t="n">
-        <v>2.697278764864449</v>
+        <v>1.919777958916156</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3565918615084092</v>
+        <v>0.7616813207885352</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1197557999870078</v>
+        <v>0.5361037641974629</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3357911284612216</v>
+        <v>0.7596960354318436</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.638635098665931</v>
+        <v>5.824999999999999</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.983637656221976</v>
+        <v>5.9542641943926</v>
       </c>
       <c r="AA9" t="n">
-        <v>10.18847836147522</v>
+        <v>6.229175915694021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Borja</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9040208</v>
+        <v>9042153</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1289,13 +1288,13 @@
         <v>16661</v>
       </c>
       <c r="E10" t="n">
-        <v>13803</v>
+        <v>3737</v>
       </c>
       <c r="F10" t="n">
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>13802</v>
+        <v>3737</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1309,65 +1308,65 @@
         <v>1</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>31413</v>
+        <v>37257</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>46247</v>
+        <v>45930</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4375</v>
+        <v>3.7875</v>
       </c>
       <c r="N10" t="n">
-        <v>5.245892805390523</v>
+        <v>10.30505953973775</v>
       </c>
       <c r="O10" t="n">
-        <v>10.15</v>
+        <v>39.075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8401943005181348</v>
+        <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.218481096109767</v>
+        <v>10.61962564999381</v>
       </c>
       <c r="R10" t="n">
-        <v>9.94</v>
+        <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.02741170928075623</v>
+        <v>0.3145661102560481</v>
       </c>
       <c r="T10" t="n">
-        <v>1.157959341415278</v>
+        <v>2.051578190706187</v>
       </c>
       <c r="U10" t="n">
-        <v>1.476858501200477</v>
+        <v>2.697278764864449</v>
       </c>
       <c r="V10" t="n">
-        <v>0.429441008037597</v>
+        <v>0.3565918615084092</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.08237376307301725</v>
+        <v>-0.1197557999870078</v>
       </c>
       <c r="X10" t="n">
-        <v>0.426829702165243</v>
+        <v>0.3357911284612216</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.208148868904629</v>
+        <v>9.638635098665931</v>
       </c>
       <c r="Z10" t="n">
-        <v>4.514783153919013</v>
+        <v>9.983637656221976</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.798307807960266</v>
+        <v>10.18847836147522</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lagunas</t>
+          <t>Borja</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9043597</v>
+        <v>9040208</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1378,13 +1377,13 @@
         <v>16661</v>
       </c>
       <c r="E11" t="n">
-        <v>4121</v>
+        <v>13803</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>4120</v>
+        <v>13802</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1398,65 +1397,65 @@
         <v>1</v>
       </c>
       <c r="K11" s="1" t="n">
-        <v>41640</v>
+        <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M11" t="n">
-        <v>2.195</v>
+        <v>0.4375</v>
       </c>
       <c r="N11" t="n">
-        <v>7.492422936893204</v>
+        <v>5.245892805390523</v>
       </c>
       <c r="O11" t="n">
-        <v>19.1775</v>
+        <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.204850111028867</v>
+        <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.66499505620931</v>
+        <v>5.218481096109767</v>
       </c>
       <c r="R11" t="n">
-        <v>16.78594914040094</v>
+        <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1725721193161059</v>
+        <v>-0.02741170928075623</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9150745493701999</v>
+        <v>1.157959341415278</v>
       </c>
       <c r="U11" t="n">
-        <v>1.198125989012055</v>
+        <v>1.476858501200477</v>
       </c>
       <c r="V11" t="n">
-        <v>0.8295552769163127</v>
+        <v>0.429441008037597</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6542060566617065</v>
+        <v>-0.08237376307301725</v>
       </c>
       <c r="X11" t="n">
-        <v>0.8278719766778936</v>
+        <v>0.426829702165243</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.014501875597941</v>
+        <v>4.208148868904629</v>
       </c>
       <c r="Z11" t="n">
-        <v>5.300475529855683</v>
+        <v>4.514783153919013</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.60937751270759</v>
+        <v>4.798307807960266</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Genaro Herrera</t>
+          <t>Lagunas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9042214</v>
+        <v>9043597</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1467,13 +1466,13 @@
         <v>16661</v>
       </c>
       <c r="E12" t="n">
-        <v>6455</v>
+        <v>4121</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>6454</v>
+        <v>4120</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1487,65 +1486,65 @@
         <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>39083</v>
+        <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M12" t="n">
-        <v>1.54</v>
+        <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>9.617222910856317</v>
+        <v>7.492422936893204</v>
       </c>
       <c r="O12" t="n">
-        <v>16.215</v>
+        <v>19.1775</v>
       </c>
       <c r="P12" t="n">
-        <v>2.861472675656494</v>
+        <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>10.03174522953336</v>
+        <v>7.66499505620931</v>
       </c>
       <c r="R12" t="n">
-        <v>16.20563653352021</v>
+        <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.414522318677047</v>
+        <v>0.1725721193161059</v>
       </c>
       <c r="T12" t="n">
-        <v>1.694447788301102</v>
+        <v>0.9150745493701999</v>
       </c>
       <c r="U12" t="n">
-        <v>2.154165408954601</v>
+        <v>1.198125989012055</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8231360602626578</v>
+        <v>0.8295552769163127</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6484584466156459</v>
+        <v>0.6542060566617065</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8112002024082149</v>
+        <v>0.8278719766778936</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.939325738512945</v>
+        <v>5.014501875597941</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.367581367768191</v>
+        <v>5.300475529855683</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.743712160733097</v>
+        <v>5.60937751270759</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Genaro Herrera</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9043425</v>
+        <v>9042214</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1556,13 +1555,13 @@
         <v>16661</v>
       </c>
       <c r="E13" t="n">
-        <v>14043</v>
+        <v>6455</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>14042</v>
+        <v>6454</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1576,65 +1575,65 @@
         <v>1</v>
       </c>
       <c r="K13" s="1" t="n">
-        <v>30682</v>
+        <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M13" t="n">
-        <v>0.26</v>
+        <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>8.13399711579547</v>
+        <v>9.617222910856317</v>
       </c>
       <c r="O13" t="n">
-        <v>34.0025</v>
+        <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>0.91</v>
+        <v>2.861472675656494</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.203802186560146</v>
+        <v>10.03174522953336</v>
       </c>
       <c r="R13" t="n">
-        <v>14.32</v>
+        <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06980507076467643</v>
+        <v>0.414522318677047</v>
       </c>
       <c r="T13" t="n">
-        <v>1.759770425278798</v>
+        <v>1.694447788301102</v>
       </c>
       <c r="U13" t="n">
-        <v>2.285200344214135</v>
+        <v>2.154165408954601</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7806643744223386</v>
+        <v>0.8231360602626578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5648888672600482</v>
+        <v>0.6484584466156459</v>
       </c>
       <c r="X13" t="n">
-        <v>0.7803023378216738</v>
+        <v>0.8112002024082149</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.093879896466462</v>
+        <v>6.939325738512945</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.20060389697934</v>
+        <v>7.367581367768191</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.322116165621164</v>
+        <v>7.743712160733097</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flor de Punga</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9044756</v>
+        <v>9043425</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1645,13 +1644,13 @@
         <v>16661</v>
       </c>
       <c r="E14" t="n">
-        <v>3099</v>
+        <v>14043</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>3099</v>
+        <v>14042</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1665,65 +1664,65 @@
         <v>1</v>
       </c>
       <c r="K14" s="1" t="n">
-        <v>42370</v>
+        <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46156</v>
+        <v>46247</v>
       </c>
       <c r="M14" t="n">
-        <v>3.305</v>
+        <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>11.96388189738625</v>
+        <v>8.13399711579547</v>
       </c>
       <c r="O14" t="n">
-        <v>30.745</v>
+        <v>34.0025</v>
       </c>
       <c r="P14" t="n">
-        <v>4.682413027387121</v>
+        <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.82503999215002</v>
+        <v>8.203802186560146</v>
       </c>
       <c r="R14" t="n">
-        <v>21.32952932657494</v>
+        <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1388419052362373</v>
+        <v>0.06980507076467643</v>
       </c>
       <c r="T14" t="n">
-        <v>2.052514105828003</v>
+        <v>1.759770425278798</v>
       </c>
       <c r="U14" t="n">
-        <v>2.697943782918296</v>
+        <v>2.285200344214135</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7947855129683991</v>
+        <v>0.7806643744223386</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6095087574846529</v>
+        <v>0.5648888672600482</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7859311731344821</v>
+        <v>0.7803023378216738</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.870952815983502</v>
+        <v>6.093879896466462</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.144857647703128</v>
+        <v>6.20060389697934</v>
       </c>
       <c r="AA14" t="n">
-        <v>8.333009729834103</v>
+        <v>6.322116165621164</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Contamana</t>
+          <t>Flor de Punga</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9053555</v>
+        <v>9044756</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1734,13 +1733,13 @@
         <v>16661</v>
       </c>
       <c r="E15" t="n">
-        <v>9806</v>
+        <v>3099</v>
       </c>
       <c r="F15" t="n">
         <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>9805</v>
+        <v>3099</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1754,65 +1753,65 @@
         <v>1</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>35804</v>
+        <v>42370</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>46247</v>
+        <v>46156</v>
       </c>
       <c r="M15" t="n">
-        <v>0.26</v>
+        <v>3.305</v>
       </c>
       <c r="N15" t="n">
-        <v>8.408512833588304</v>
+        <v>11.96388189738625</v>
       </c>
       <c r="O15" t="n">
-        <v>131.9</v>
+        <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5268935553946416</v>
+        <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.662918875592325</v>
+        <v>11.82503999215002</v>
       </c>
       <c r="R15" t="n">
-        <v>131.7868211440985</v>
+        <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2544060420040198</v>
+        <v>-0.1388419052362373</v>
       </c>
       <c r="T15" t="n">
-        <v>3.537865272702922</v>
+        <v>2.052514105828003</v>
       </c>
       <c r="U15" t="n">
-        <v>11.06361438194357</v>
+        <v>2.697943782918296</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04955943679836131</v>
+        <v>0.7947855129683991</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.5971000815699585</v>
+        <v>0.6095087574846529</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03280454175648839</v>
+        <v>0.7859311731344821</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.80161542816917</v>
+        <v>7.870952815983502</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.25382818534252</v>
+        <v>8.144857647703128</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.72673630745086</v>
+        <v>8.333009729834103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Puerto Almendra</t>
+          <t>Contamana</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9037610</v>
+        <v>9053555</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1823,13 +1822,13 @@
         <v>16661</v>
       </c>
       <c r="E16" t="n">
-        <v>2305</v>
+        <v>9806</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>2305</v>
+        <v>9805</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1843,65 +1842,65 @@
         <v>1</v>
       </c>
       <c r="K16" s="1" t="n">
-        <v>43252</v>
+        <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46203</v>
+        <v>46247</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>6.583133405639913</v>
+        <v>8.408512833588304</v>
       </c>
       <c r="O16" t="n">
-        <v>12.23</v>
+        <v>131.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.395549592894153</v>
+        <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.955003837956245</v>
+        <v>8.662918875592325</v>
       </c>
       <c r="R16" t="n">
-        <v>12.15738414192614</v>
+        <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3718704323163314</v>
+        <v>0.2544060420040198</v>
       </c>
       <c r="T16" t="n">
-        <v>2.040859866306212</v>
+        <v>3.537865272702922</v>
       </c>
       <c r="U16" t="n">
-        <v>2.579931141164777</v>
+        <v>11.06361438194357</v>
       </c>
       <c r="V16" t="n">
-        <v>0.518080516359496</v>
+        <v>0.04955943679836131</v>
       </c>
       <c r="W16" t="n">
-        <v>0.01500464189315576</v>
+        <v>-0.5971000815699585</v>
       </c>
       <c r="X16" t="n">
-        <v>0.5147806285315646</v>
+        <v>0.03280454175648839</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.667476001209895</v>
+        <v>10.80161542816917</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.136592442981486</v>
+        <v>11.25382818534252</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.361938671031083</v>
+        <v>11.72673630745086</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Santa María de Nanay</t>
+          <t>Puerto Almendra</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9037738</v>
+        <v>9037610</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1912,13 +1911,13 @@
         <v>16661</v>
       </c>
       <c r="E17" t="n">
-        <v>3209</v>
+        <v>2350</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>3208</v>
+        <v>2349</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1932,65 +1931,65 @@
         <v>1</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>42370</v>
+        <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M17" t="n">
-        <v>1.81</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.498508416458852</v>
+        <v>6.541279267773521</v>
       </c>
       <c r="O17" t="n">
-        <v>18.4925</v>
+        <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.826106587712805</v>
+        <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.693383067949556</v>
+        <v>6.911753839976919</v>
       </c>
       <c r="R17" t="n">
-        <v>14.92774999999984</v>
+        <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1948746514907041</v>
+        <v>0.3704745722033992</v>
       </c>
       <c r="T17" t="n">
-        <v>1.099377977882823</v>
+        <v>2.031813451178136</v>
       </c>
       <c r="U17" t="n">
-        <v>1.48893409430651</v>
+        <v>2.566300066934896</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6010145525892741</v>
+        <v>0.520896010144777</v>
       </c>
       <c r="W17" t="n">
-        <v>0.217547443422078</v>
+        <v>0.02203630015711489</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5980831351002822</v>
+        <v>0.5175595971059744</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.810903603932743</v>
+        <v>2.717088244697531</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.192562502533661</v>
+        <v>4.034049954698661</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.294390339143794</v>
+        <v>5.201197777784091</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Angamos</t>
+          <t>Santa María de Nanay</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9043370</v>
+        <v>9037738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2001,13 +2000,13 @@
         <v>16661</v>
       </c>
       <c r="E18" t="n">
-        <v>7163</v>
+        <v>3209</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>7162</v>
+        <v>3208</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2021,54 +2020,143 @@
         <v>1</v>
       </c>
       <c r="K18" s="1" t="n">
-        <v>37987</v>
+        <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
         <v>46247</v>
       </c>
       <c r="M18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.498508416458852</v>
+      </c>
+      <c r="O18" t="n">
+        <v>18.4925</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.826106587712805</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6.693383067949556</v>
+      </c>
+      <c r="R18" t="n">
+        <v>14.92774999999984</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1948746514907041</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.099377977882823</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.48893409430651</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.6010145525892741</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.217547443422078</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.5980831351002822</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.810903603932743</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.192562502533661</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.294390339143794</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Angamos</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>9043370</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>16661</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7163</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7162</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>12</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>37987</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.04</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N19" t="n">
         <v>10.37037629153868</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O19" t="n">
         <v>24.5875</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P19" t="n">
         <v>4.725023439427584</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q19" t="n">
         <v>11.15446582536702</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S19" t="n">
         <v>0.7840895338283447</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2.03768776148797</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>2.757131417345985</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>0.7263387120159976</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>0.4693420147356044</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>0.6789283514315176</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>7.774568432955215</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>7.851740384401721</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AA19" t="n">
         <v>7.929707656935572</v>
       </c>
     </row>
@@ -2083,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,13 +2487,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.667476001209895</v>
+        <v>2.717088244697531</v>
       </c>
       <c r="G11" t="n">
-        <v>4.136592442981486</v>
+        <v>4.034049954698661</v>
       </c>
       <c r="H11" t="n">
-        <v>5.361938671031083</v>
+        <v>5.201197777784091</v>
       </c>
     </row>
     <row r="12">
@@ -2604,50 +2692,32 @@
         <v>3.099729136443566</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>estacion</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>comid</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>motivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Timicurillo</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B19" t="n">
         <v>9036459</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>observado_insuficiente</t>
-        </is>
+      <c r="C19" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>46257</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>5.802478839292944</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.403218831576423</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7.820329931345277</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8517400704246</v>
+        <v>102.8510229477262</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0008889645310845734</v>
+        <v>-0.0016060872294489</v>
       </c>
       <c r="T2" t="n">
-        <v>17.8102554245504</v>
+        <v>17.81037251236812</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18961960822894</v>
+        <v>36.18921106170248</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285504339773765</v>
+        <v>0.1285927227105993</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7375276062683822</v>
+        <v>-0.7374883764080511</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285449648154223</v>
+        <v>0.1285873447764149</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.62002736156155</v>
+        <v>54.73082104178297</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.19075793545417</v>
+        <v>85.79998977340632</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.2660116977248</v>
+        <v>113.6678503433239</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14543</v>
+        <v>14544</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906135597882142</v>
+        <v>4.906011413641364</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959843685721722</v>
+        <v>4.959653976861945</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05370808783957928</v>
+        <v>0.05364256322057959</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350587164245165</v>
+        <v>1.350491220084941</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725346438099607</v>
+        <v>1.725293407011258</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795053382774603</v>
+        <v>0.7795166070352814</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664726154068926</v>
+        <v>0.5664836177596198</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784462656546735</v>
+        <v>0.7784606545623705</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.592601135557133</v>
+        <v>2.591276595744681</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.800783134391457</v>
+        <v>2.747714469549582</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.099729136443566</v>
+        <v>3.027993704288563</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10225</v>
+        <v>10226</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.918221515892421</v>
+        <v>6.917974281243887</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3665578424414478</v>
+        <v>0.3664432624113475</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.24712127535387</v>
+        <v>7.246803423995322</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3288997594614492</v>
+        <v>0.3288291427514338</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293917409639079</v>
+        <v>1.293830250772034</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683972951679149</v>
+        <v>1.683889727014217</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674413508999779</v>
+        <v>0.8674503641601107</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370805370957414</v>
+        <v>0.7370960495191927</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471386373670609</v>
+        <v>0.8471633244806561</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.242369588360539</v>
+        <v>4.065423758865249</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.654691175076457</v>
+        <v>4.575862932985902</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.907998580553584</v>
+        <v>4.908804964539007</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313782114822216</v>
+        <v>9.313618854999097</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3589940107329972</v>
+        <v>0.3588307509098781</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25477807844241</v>
+        <v>1.254735545691164</v>
       </c>
       <c r="U5" t="n">
-        <v>1.748032492511534</v>
+        <v>1.747909206300914</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674441770819028</v>
+        <v>0.8674650311378275</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7233934578599799</v>
+        <v>0.7234324738050324</v>
       </c>
       <c r="X5" t="n">
-        <v>0.861513018196886</v>
+        <v>0.8615384829082438</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.802478839292944</v>
+        <v>5.813726951247699</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.403218831576423</v>
+        <v>6.207330978982242</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.820329931345277</v>
+        <v>7.674964125091845</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8836</v>
+        <v>8837</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.730774671797193</v>
+        <v>6.730817585153333</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018731073071335</v>
+        <v>7.018703597626171</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.287956401274142</v>
+        <v>0.2878860124728384</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482115137231137</v>
+        <v>1.482016489337916</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910672252159408</v>
+        <v>1.910593693880501</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047696908443753</v>
+        <v>0.3047625712819429</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980328239852089</v>
+        <v>-0.1980634864874187</v>
       </c>
       <c r="X6" t="n">
-        <v>0.280143786521527</v>
+        <v>0.2801447679764663</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.571068511422081</v>
+        <v>6.554638940393355</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.606384527979982</v>
+        <v>6.593908167919861</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.678056700139964</v>
+        <v>6.648575045410897</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14198</v>
+        <v>14199</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.582624841526975</v>
+        <v>5.582571836044792</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586455636561203</v>
+        <v>5.586457626462123</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003830795034226368</v>
+        <v>0.003885790417331762</v>
       </c>
       <c r="T7" t="n">
-        <v>1.155923939521207</v>
+        <v>1.155942423119133</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49401941594255</v>
+        <v>1.494015698312922</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089653155571648</v>
+        <v>0.5089452079990595</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07464646115237838</v>
+        <v>0.07460119639210472</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5051130378454496</v>
+        <v>0.5050941387847593</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.621515615205388</v>
+        <v>5.62</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.77421969213418</v>
+        <v>5.740787492299576</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.964795628363793</v>
+        <v>5.917483128324467</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8996</v>
+        <v>8997</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.880412683414852</v>
+        <v>7.880357063465601</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.117138943756959</v>
+        <v>8.116808065523323</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2367262603421096</v>
+        <v>0.2364510020577241</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445208063119896</v>
+        <v>1.445230375771013</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824992953055081</v>
+        <v>1.824967889029288</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087247744568659</v>
+        <v>0.8087114187257426</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6289179699499088</v>
+        <v>0.6288880648809474</v>
       </c>
       <c r="X8" t="n">
-        <v>0.799019987712574</v>
+        <v>0.7990304719725214</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.417876837077897</v>
+        <v>5.417061983141118</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.525841267246117</v>
+        <v>5.48633254419638</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.822456982157617</v>
+        <v>5.69750490954296</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13861</v>
+        <v>13862</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,52 +1222,52 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.616058725921651</v>
+        <v>7.615950800750253</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5111462029808375</v>
+        <v>0.510904255319149</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.680051219233575</v>
+        <v>7.679855776755572</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06399249331192496</v>
+        <v>0.06390497600531965</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477393422227689</v>
+        <v>1.477297960465334</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919777958916156</v>
+        <v>1.919711362115302</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7616813207885352</v>
+        <v>0.7616928578103092</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361037641974629</v>
+        <v>0.5361119108566166</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7596960354318436</v>
+        <v>0.7597124927642027</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.824999999999999</v>
+        <v>5.822106050046785</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.9542641943926</v>
+        <v>5.920268131709418</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.229175915694021</v>
+        <v>6.168536357560394</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61962564999381</v>
+        <v>10.6195422509152</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3145661102560481</v>
+        <v>0.3144827111774465</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051578190706187</v>
+        <v>2.051603882158787</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697278764864449</v>
+        <v>2.697293361498946</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3565918615084092</v>
+        <v>0.356602807772564</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1197557999870078</v>
+        <v>-0.1197679193945953</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3357911284612216</v>
+        <v>0.3358118709798281</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.638635098665931</v>
+        <v>9.664629299978044</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.983637656221976</v>
+        <v>9.967686429010726</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.18847836147522</v>
+        <v>10.1886637205788</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13802</v>
+        <v>13803</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M11" t="n">
         <v>0.4375</v>
       </c>
       <c r="N11" t="n">
-        <v>5.245892805390523</v>
+        <v>5.245876439904369</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218481096109767</v>
+        <v>5.218418147358884</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02741170928075623</v>
+        <v>-0.02745829254548498</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157959341415278</v>
+        <v>1.157894360709922</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476858501200477</v>
+        <v>1.476818356557674</v>
       </c>
       <c r="V11" t="n">
-        <v>0.429441008037597</v>
+        <v>0.4294509472656229</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08237376307301725</v>
+        <v>-0.08239135226198124</v>
       </c>
       <c r="X11" t="n">
-        <v>0.426829702165243</v>
+        <v>0.4268427402101447</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.208148868904629</v>
+        <v>4.364588312243739</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.514783153919013</v>
+        <v>4.57799537360118</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.798307807960266</v>
+        <v>5.664361416792508</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.492422936893204</v>
+        <v>7.491767168163068</v>
       </c>
       <c r="O12" t="n">
         <v>19.1775</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.66499505620931</v>
+        <v>7.664358043061805</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725721193161059</v>
+        <v>0.1725908748987374</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9150745493701999</v>
+        <v>0.9149310923587468</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198125989012055</v>
+        <v>1.19799999493646</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8295552769163127</v>
+        <v>0.8296236225172731</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6542060566617065</v>
+        <v>0.6543424247234271</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8278719766778936</v>
+        <v>0.8279389467224183</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.014501875597941</v>
+        <v>5.014129368496219</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.300475529855683</v>
+        <v>5.298225258524825</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.60937751270759</v>
+        <v>5.608481607421576</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6454</v>
+        <v>6455</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.617222910856317</v>
+        <v>9.616874774076942</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.861472675656494</v>
+        <v>2.861304964539007</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03174522953336</v>
+        <v>10.03119334511832</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.414522318677047</v>
+        <v>0.4143185710413762</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694447788301102</v>
+        <v>1.694197598903179</v>
       </c>
       <c r="U13" t="n">
-        <v>2.154165408954601</v>
+        <v>2.153937898689945</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231360602626578</v>
+        <v>0.8231605862757818</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484584466156459</v>
+        <v>0.6484990733955549</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8112002024082149</v>
+        <v>0.8112459666806742</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.939325738512945</v>
+        <v>6.681853177762529</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.367581367768191</v>
+        <v>7.258540236830251</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.743712160733097</v>
+        <v>7.701687938665148</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14042</v>
+        <v>14043</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.13399711579547</v>
+        <v>8.133883607491278</v>
       </c>
       <c r="O14" t="n">
         <v>34.0025</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.203802186560146</v>
+        <v>8.203505072023274</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06980507076467643</v>
+        <v>0.06962146453199887</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759770425278798</v>
+        <v>1.759559923431554</v>
       </c>
       <c r="U14" t="n">
-        <v>2.285200344214135</v>
+        <v>2.285020309639219</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7806643744223386</v>
+        <v>0.7806966405125342</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5648888672600482</v>
+        <v>0.5649330003946089</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803023378216738</v>
+        <v>0.7803376132800814</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.093879896466462</v>
+        <v>6.074027297948074</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.20060389697934</v>
+        <v>6.166077425812167</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.322116165621164</v>
+        <v>6.284112315083841</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82503999215002</v>
+        <v>11.82492250959979</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1388419052362373</v>
+        <v>-0.1389593877864653</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052514105828003</v>
+        <v>2.052499372827074</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697943782918296</v>
+        <v>2.697909762411452</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7947855129683991</v>
+        <v>0.7947965210768916</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095087574846529</v>
+        <v>0.6095186054483606</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7859311731344821</v>
+        <v>0.7859499356361562</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.870952815983502</v>
+        <v>7.808503371700965</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.144857647703128</v>
+        <v>8.091716171713838</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.333009729834103</v>
+        <v>8.268695864487293</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9805</v>
+        <v>9806</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.408512833588304</v>
+        <v>8.408270276701339</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662918875592325</v>
+        <v>8.663079154697536</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2544060420040198</v>
+        <v>0.2548088779961949</v>
       </c>
       <c r="T16" t="n">
-        <v>3.537865272702922</v>
+        <v>3.538067216814751</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06361438194357</v>
+        <v>11.06319353184847</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04955943679836131</v>
+        <v>0.04954508760577715</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971000815699585</v>
+        <v>-0.597129430664483</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03280454175648839</v>
+        <v>0.03278926383203662</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.80161542816917</v>
+        <v>10.79275213630249</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.25382818534252</v>
+        <v>11.28022201892156</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.72673630745086</v>
+        <v>11.77465791250454</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.541279267773521</v>
+        <v>6.539665957446808</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.911753839976919</v>
+        <v>6.9109875132767</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3704745722033992</v>
+        <v>0.3713215558298907</v>
       </c>
       <c r="T17" t="n">
-        <v>2.031813451178136</v>
+        <v>2.032000582224544</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566300066934896</v>
+        <v>2.566266712757852</v>
       </c>
       <c r="V17" t="n">
-        <v>0.520896010144777</v>
+        <v>0.5210246267058404</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02203630015711489</v>
+        <v>0.02253319684573318</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5175595971059744</v>
+        <v>0.5176698776662829</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.717088244697531</v>
+        <v>3.14363577650791</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.034049954698661</v>
+        <v>4.297748743480243</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.201197777784091</v>
+        <v>8.430552762206746</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.498508416458852</v>
+        <v>6.497760984730445</v>
       </c>
       <c r="O18" t="n">
         <v>18.4925</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693383067949556</v>
+        <v>6.693200100760388</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948746514907041</v>
+        <v>0.1954391160299415</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099377977882823</v>
+        <v>1.09971636891484</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48893409430651</v>
+        <v>1.489202438548427</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6010145525892741</v>
+        <v>0.6009381812117202</v>
       </c>
       <c r="W18" t="n">
-        <v>0.217547443422078</v>
+        <v>0.2175164896546674</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980831351002822</v>
+        <v>0.5979756417963578</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.810903603932743</v>
+        <v>4.260000000000001</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.192562502533661</v>
+        <v>5.406353568005889</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.294390339143794</v>
+        <v>7.217224394499071</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16661</v>
+        <v>16662</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7162</v>
+        <v>7163</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.37037629153868</v>
+        <v>10.36931941923775</v>
       </c>
       <c r="O19" t="n">
         <v>24.5875</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15446582536702</v>
+        <v>11.15388510990214</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7840895338283447</v>
+        <v>0.7845656906643884</v>
       </c>
       <c r="T19" t="n">
-        <v>2.03768776148797</v>
+        <v>2.038120001438481</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757131417345985</v>
+        <v>2.757614432980732</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263387120159976</v>
+        <v>0.726361186594589</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693420147356044</v>
+        <v>0.4693783129109069</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789283514315176</v>
+        <v>0.6788739695788875</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.774568432955215</v>
+        <v>7.765266890990788</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.851740384401721</v>
+        <v>7.837486630503824</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.929707656935572</v>
+        <v>7.921575440520582</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.774568432955215</v>
+        <v>7.765266890990788</v>
       </c>
       <c r="G2" t="n">
-        <v>7.851740384401721</v>
+        <v>7.837486630503823</v>
       </c>
       <c r="H2" t="n">
-        <v>7.929707656935572</v>
+        <v>7.921575440520582</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.621515615205388</v>
+        <v>5.62</v>
       </c>
       <c r="G3" t="n">
-        <v>5.77421969213418</v>
+        <v>5.740787492299576</v>
       </c>
       <c r="H3" t="n">
-        <v>5.964795628363793</v>
+        <v>5.917483128324467</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.208148868904629</v>
+        <v>4.364588312243739</v>
       </c>
       <c r="G4" t="n">
-        <v>4.514783153919014</v>
+        <v>4.577995373601179</v>
       </c>
       <c r="H4" t="n">
-        <v>4.798307807960266</v>
+        <v>5.664361416792508</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.80161542816917</v>
+        <v>10.79275213630249</v>
       </c>
       <c r="G5" t="n">
-        <v>11.25382818534252</v>
+        <v>11.28022201892156</v>
       </c>
       <c r="H5" t="n">
-        <v>11.72673630745086</v>
+        <v>11.77465791250454</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.62002736156155</v>
+        <v>54.73082104178297</v>
       </c>
       <c r="G6" t="n">
-        <v>94.19075793545417</v>
+        <v>85.79998977340634</v>
       </c>
       <c r="H6" t="n">
-        <v>110.2660116977248</v>
+        <v>113.6678503433239</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.870952815983502</v>
+        <v>7.808503371700965</v>
       </c>
       <c r="G7" t="n">
-        <v>8.144857647703128</v>
+        <v>8.091716171713838</v>
       </c>
       <c r="H7" t="n">
-        <v>8.333009729834103</v>
+        <v>8.268695864487293</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.939325738512945</v>
+        <v>6.681853177762529</v>
       </c>
       <c r="G8" t="n">
-        <v>7.367581367768193</v>
+        <v>7.258540236830251</v>
       </c>
       <c r="H8" t="n">
-        <v>7.743712160733097</v>
+        <v>7.701687938665148</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.014501875597941</v>
+        <v>5.014129368496219</v>
       </c>
       <c r="G9" t="n">
-        <v>5.300475529855683</v>
+        <v>5.298225258524826</v>
       </c>
       <c r="H9" t="n">
-        <v>5.60937751270759</v>
+        <v>5.608481607421576</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.417876837077897</v>
+        <v>5.417061983141118</v>
       </c>
       <c r="G10" t="n">
-        <v>5.525841267246117</v>
+        <v>5.48633254419638</v>
       </c>
       <c r="H10" t="n">
-        <v>5.822456982157617</v>
+        <v>5.69750490954296</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.717088244697531</v>
+        <v>3.14363577650791</v>
       </c>
       <c r="G11" t="n">
-        <v>4.034049954698661</v>
+        <v>4.297748743480243</v>
       </c>
       <c r="H11" t="n">
-        <v>5.201197777784091</v>
+        <v>8.430552762206746</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.093879896466462</v>
+        <v>6.074027297948074</v>
       </c>
       <c r="G12" t="n">
-        <v>6.20060389697934</v>
+        <v>6.166077425812167</v>
       </c>
       <c r="H12" t="n">
-        <v>6.322116165621164</v>
+        <v>6.284112315083841</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.638635098665931</v>
+        <v>9.664629299978044</v>
       </c>
       <c r="G13" t="n">
-        <v>9.983637656221976</v>
+        <v>9.967686429010726</v>
       </c>
       <c r="H13" t="n">
-        <v>10.18847836147522</v>
+        <v>10.1886637205788</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.824999999999999</v>
+        <v>5.822106050046785</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9542641943926</v>
+        <v>5.920268131709419</v>
       </c>
       <c r="H14" t="n">
-        <v>6.229175915694021</v>
+        <v>6.168536357560394</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.571068511422081</v>
+        <v>6.554638940393355</v>
       </c>
       <c r="G15" t="n">
-        <v>6.606384527979984</v>
+        <v>6.593908167919861</v>
       </c>
       <c r="H15" t="n">
-        <v>6.678056700139964</v>
+        <v>6.648575045410897</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.810903603932743</v>
+        <v>4.260000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>5.192562502533661</v>
+        <v>5.406353568005889</v>
       </c>
       <c r="H16" t="n">
-        <v>6.294390339143794</v>
+        <v>7.217224394499071</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.242369588360539</v>
+        <v>4.065423758865249</v>
       </c>
       <c r="G17" t="n">
-        <v>4.654691175076456</v>
+        <v>4.575862932985902</v>
       </c>
       <c r="H17" t="n">
-        <v>4.907998580553584</v>
+        <v>4.908804964539007</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.592601135557133</v>
+        <v>2.591276595744681</v>
       </c>
       <c r="G18" t="n">
-        <v>2.800783134391457</v>
+        <v>2.747714469549583</v>
       </c>
       <c r="H18" t="n">
-        <v>3.099729136443566</v>
+        <v>3.027993704288563</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.802478839292944</v>
+        <v>5.813726951247699</v>
       </c>
       <c r="G19" t="n">
-        <v>6.403218831576423</v>
+        <v>6.207330978982241</v>
       </c>
       <c r="H19" t="n">
-        <v>7.820329931345277</v>
+        <v>7.674964125091845</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8510229477262</v>
+        <v>102.8503426747093</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0016060872294489</v>
+        <v>-0.002286360246349168</v>
       </c>
       <c r="T2" t="n">
-        <v>17.81037251236812</v>
+        <v>17.81046256193798</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18921106170248</v>
+        <v>36.18887350519144</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285927227105993</v>
+        <v>0.1286346557368087</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7374883764080511</v>
+        <v>-0.7374559635556122</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285873447764149</v>
+        <v>0.1286293804697493</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.73082104178297</v>
+        <v>53.88798527801997</v>
       </c>
       <c r="Z2" t="n">
-        <v>85.79998977340632</v>
+        <v>81.90347434815757</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.6678503433239</v>
+        <v>113.6680503076447</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959653976861945</v>
+        <v>4.95959865089773</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05364256322057959</v>
+        <v>0.0535872372563662</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350491220084941</v>
+        <v>1.35049104321139</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725293407011258</v>
+        <v>1.725299678462889</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795166070352814</v>
+        <v>0.7795199916456255</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664836177596198</v>
+        <v>0.5664804660847188</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784606545623705</v>
+        <v>0.7784667984093322</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.591276595744681</v>
+        <v>2.581991477741602</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.747714469549582</v>
+        <v>2.712576486784773</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.027993704288563</v>
+        <v>3.026281492121885</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3664432624113475</v>
+        <v>0.3663288447909284</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246803423995322</v>
+        <v>7.246718276818832</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3288291427514338</v>
+        <v>0.328743995574943</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293830250772034</v>
+        <v>1.293823925882399</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683889727014217</v>
+        <v>1.683882862944483</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674503641601107</v>
+        <v>0.8674515666813908</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370960495191927</v>
+        <v>0.7370981928749513</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471633244806561</v>
+        <v>0.8471823020788747</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.065423758865249</v>
+        <v>4.004400863629338</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.575862932985902</v>
+        <v>4.524594072520015</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.908804964539007</v>
+        <v>4.931980864635011</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313618854999097</v>
+        <v>9.313468291051414</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3588307509098781</v>
+        <v>0.3586801869621956</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254735545691164</v>
+        <v>1.254702555284112</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747909206300914</v>
+        <v>1.747804918254224</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674650311378275</v>
+        <v>0.8674831886705413</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234324738050324</v>
+        <v>0.7234654753208309</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615384829082438</v>
+        <v>0.8615609340141106</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.813726951247699</v>
+        <v>5.782418729349418</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.207330978982242</v>
+        <v>6.060653762479506</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.674964125091845</v>
+        <v>7.669249492415918</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018703597626171</v>
+        <v>7.018716779269122</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2878860124728384</v>
+        <v>0.2878991941157893</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482016489337916</v>
+        <v>1.482035316515581</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910593693880501</v>
+        <v>1.910616562007694</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047625712819429</v>
+        <v>0.3047640646950878</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980634864874187</v>
+        <v>-0.1980921661928354</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801447679764663</v>
+        <v>0.2801531289265581</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.554638940393355</v>
+        <v>6.541360039276046</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.593908167919861</v>
+        <v>6.586444956350657</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.648575045410897</v>
+        <v>6.648268695635624</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586457626462123</v>
+        <v>5.586436457929263</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003885790417331762</v>
+        <v>0.003864621884471626</v>
       </c>
       <c r="T7" t="n">
-        <v>1.155942423119133</v>
+        <v>1.155963988077594</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494015698312922</v>
+        <v>1.494036103217407</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089452079990595</v>
+        <v>0.5089384118144509</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07460119639210472</v>
+        <v>0.0745759184741196</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050941387847593</v>
+        <v>0.5050892256658337</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.62</v>
+        <v>5.603223731940104</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.740787492299576</v>
+        <v>5.716635674573947</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.917483128324467</v>
+        <v>5.915809382782526</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116808065523323</v>
+        <v>8.116745455549594</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2364510020577241</v>
+        <v>0.2363883920839949</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445230375771013</v>
+        <v>1.445239969004653</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824967889029288</v>
+        <v>1.824972627471824</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087114187257426</v>
+        <v>0.8087131108100227</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288880648809474</v>
+        <v>0.6288861377293817</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990304719725214</v>
+        <v>0.7990414759983432</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.417061983141118</v>
+        <v>5.410460542658972</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.48633254419638</v>
+        <v>5.46503065620036</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.69750490954296</v>
+        <v>5.697191571467106</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.510904255319149</v>
+        <v>0.5106626506024097</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679855776755572</v>
+        <v>7.679776498097223</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06390497600531965</v>
+        <v>0.06382569734697086</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477297960465334</v>
+        <v>1.477303648494101</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919711362115302</v>
+        <v>1.919714821513665</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7616928578103092</v>
+        <v>0.7616987615007448</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361119108566166</v>
+        <v>0.5361102389645047</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597124927642027</v>
+        <v>0.7597229628255315</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.822106050046785</v>
+        <v>5.815525889841227</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.920268131709418</v>
+        <v>5.892058840909163</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.168536357560394</v>
+        <v>6.167714895529832</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.6195422509152</v>
+        <v>10.61945332562966</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3144827111774465</v>
+        <v>0.3143937858918993</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051603882158787</v>
+        <v>2.051629224749192</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697293361498946</v>
+        <v>2.697306721839158</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356602807772564</v>
+        <v>0.3566144571976703</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1197679193945953</v>
+        <v>-0.1197790123796052</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3358118709798281</v>
+        <v>0.3358334903511079</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.664629299978044</v>
+        <v>9.590374620440702</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.967686429010726</v>
+        <v>9.92860699077757</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.1886637205788</v>
+        <v>10.18885036236669</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218418147358884</v>
+        <v>5.218386339729123</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02745829254548498</v>
+        <v>-0.02749010017524594</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157894360709922</v>
+        <v>1.157898315409949</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476818356557674</v>
+        <v>1.476832029810608</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294509472656229</v>
+        <v>0.4294580568245135</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08239135226198124</v>
+        <v>-0.08241139518625795</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268427402101447</v>
+        <v>0.4268527583793454</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.364588312243739</v>
+        <v>4.168839714499081</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.57799537360118</v>
+        <v>4.521225297162577</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.664361416792508</v>
+        <v>5.664645356256155</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664358043061805</v>
+        <v>7.664346377767289</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725908748987374</v>
+        <v>0.1725792096042216</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149310923587468</v>
+        <v>0.9149368354844541</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19799999493646</v>
+        <v>1.198011694140042</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296236225172731</v>
+        <v>0.829622022131781</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543424247234271</v>
+        <v>0.6543356735746696</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279389467224183</v>
+        <v>0.8279381181469615</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.014129368496219</v>
+        <v>5.013769097435109</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.298225258524825</v>
+        <v>5.318954241036741</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.608481607421576</v>
+        <v>5.609678728719034</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.861304964539007</v>
+        <v>2.861137491141035</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03119334511832</v>
+        <v>10.03100258379659</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4143185710413762</v>
+        <v>0.4141278097196481</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694197598903179</v>
+        <v>1.69416133293073</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153937898689945</v>
+        <v>2.153881705697316</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231605862757818</v>
+        <v>0.8231723809081499</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484990733955549</v>
+        <v>0.6485174134148668</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8112459666806742</v>
+        <v>0.8112782840713493</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.681853177762529</v>
+        <v>6.487385181652312</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.258540236830251</v>
+        <v>7.158454931017556</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.701687938665148</v>
+        <v>7.700025453546634</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.203505072023274</v>
+        <v>8.203345374994711</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06962146453199887</v>
+        <v>0.06946176750343487</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759559923431554</v>
+        <v>1.759468030896321</v>
       </c>
       <c r="U14" t="n">
-        <v>2.285020309639219</v>
+        <v>2.284929612374291</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7806966405125342</v>
+        <v>0.7807233008744462</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5649330003946089</v>
+        <v>0.5649675371588079</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803376132800814</v>
+        <v>0.7803669934982161</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.074027297948074</v>
+        <v>6.039381309415925</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.166077425812167</v>
+        <v>6.139713765662621</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.284112315083841</v>
+        <v>6.280972962471959</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82492250959979</v>
+        <v>11.82480540454196</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1389593877864653</v>
+        <v>-0.1390764928442973</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052499372827074</v>
+        <v>2.052482049615668</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697909762411452</v>
+        <v>2.697874149580598</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7947965210768916</v>
+        <v>0.7948077486491253</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095186054483606</v>
+        <v>0.609528914211291</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7859499356361562</v>
+        <v>0.785968863569281</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.808503371700965</v>
+        <v>7.74609837016007</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.091716171713838</v>
+        <v>8.051998768738553</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.268695864487293</v>
+        <v>8.268499786633004</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.663079154697536</v>
+        <v>8.66296070978153</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2548088779961949</v>
+        <v>0.2546904330801906</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538067216814751</v>
+        <v>3.538079815090161</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06319353184847</v>
+        <v>11.06320129806036</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04954508760577715</v>
+        <v>0.04954226667525485</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.597129430664483</v>
+        <v>-0.5971316729916891</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03278926383203662</v>
+        <v>0.03278674237424661</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.79275213630249</v>
+        <v>10.7835102850365</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.28022201892156</v>
+        <v>11.3117678106549</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.77465791250454</v>
+        <v>11.81052741711589</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.9109875132767</v>
+        <v>6.910950923540661</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3713215558298907</v>
+        <v>0.3712849660938528</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032000582224544</v>
+        <v>2.032012111555993</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566266712757852</v>
+        <v>2.566281456433692</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210246267058404</v>
+        <v>0.5210278328480742</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02253319684573318</v>
+        <v>0.02252196535914097</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176698776662829</v>
+        <v>0.5176737661707667</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.14363577650791</v>
+        <v>2.886211494141786</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.297748743480243</v>
+        <v>4.158007341165876</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.430552762206746</v>
+        <v>8.430850031687818</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693200100760388</v>
+        <v>6.693160618852027</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1954391160299415</v>
+        <v>0.1953996341215816</v>
       </c>
       <c r="T18" t="n">
-        <v>1.09971636891484</v>
+        <v>1.099726526243733</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489202438548427</v>
+        <v>1.489210786598514</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009381812117202</v>
+        <v>0.6009416821431686</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2175164896546674</v>
+        <v>0.2175077168650503</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979756417963578</v>
+        <v>0.5979823384358277</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.260000000000001</v>
+        <v>4.211863414344984</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.406353568005889</v>
+        <v>5.31118203622689</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.217224394499071</v>
+        <v>7.487500000000002</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16662</v>
+        <v>16663</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15388510990214</v>
+        <v>11.15375376088195</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7845656906643884</v>
+        <v>0.7844343416442059</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038120001438481</v>
+        <v>2.038113959081525</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757614432980732</v>
+        <v>2.757621074467685</v>
       </c>
       <c r="V19" t="n">
-        <v>0.726361186594589</v>
+        <v>0.7263581283241359</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693783129109069</v>
+        <v>0.4693757569906786</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6788739695788875</v>
+        <v>0.6788965331574183</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.765266890990788</v>
+        <v>7.735832617919256</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.837486630503824</v>
+        <v>7.822139961123153</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.921575440520582</v>
+        <v>7.920638040579542</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.765266890990788</v>
+        <v>7.735832617919256</v>
       </c>
       <c r="G2" t="n">
-        <v>7.837486630503823</v>
+        <v>7.822139961123153</v>
       </c>
       <c r="H2" t="n">
-        <v>7.921575440520582</v>
+        <v>7.920638040579542</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.62</v>
+        <v>5.603223731940104</v>
       </c>
       <c r="G3" t="n">
-        <v>5.740787492299576</v>
+        <v>5.716635674573946</v>
       </c>
       <c r="H3" t="n">
-        <v>5.917483128324467</v>
+        <v>5.915809382782526</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.364588312243739</v>
+        <v>4.168839714499081</v>
       </c>
       <c r="G4" t="n">
-        <v>4.577995373601179</v>
+        <v>4.521225297162577</v>
       </c>
       <c r="H4" t="n">
-        <v>5.664361416792508</v>
+        <v>5.664645356256155</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.79275213630249</v>
+        <v>10.7835102850365</v>
       </c>
       <c r="G5" t="n">
-        <v>11.28022201892156</v>
+        <v>11.3117678106549</v>
       </c>
       <c r="H5" t="n">
-        <v>11.77465791250454</v>
+        <v>11.81052741711589</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.73082104178297</v>
+        <v>53.88798527801997</v>
       </c>
       <c r="G6" t="n">
-        <v>85.79998977340634</v>
+        <v>81.90347434815757</v>
       </c>
       <c r="H6" t="n">
-        <v>113.6678503433239</v>
+        <v>113.6680503076447</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.808503371700965</v>
+        <v>7.74609837016007</v>
       </c>
       <c r="G7" t="n">
-        <v>8.091716171713838</v>
+        <v>8.051998768738551</v>
       </c>
       <c r="H7" t="n">
-        <v>8.268695864487293</v>
+        <v>8.268499786633004</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.681853177762529</v>
+        <v>6.487385181652312</v>
       </c>
       <c r="G8" t="n">
-        <v>7.258540236830251</v>
+        <v>7.158454931017556</v>
       </c>
       <c r="H8" t="n">
-        <v>7.701687938665148</v>
+        <v>7.700025453546634</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.014129368496219</v>
+        <v>5.013769097435109</v>
       </c>
       <c r="G9" t="n">
-        <v>5.298225258524826</v>
+        <v>5.318954241036742</v>
       </c>
       <c r="H9" t="n">
-        <v>5.608481607421576</v>
+        <v>5.609678728719034</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.417061983141118</v>
+        <v>5.410460542658972</v>
       </c>
       <c r="G10" t="n">
-        <v>5.48633254419638</v>
+        <v>5.46503065620036</v>
       </c>
       <c r="H10" t="n">
-        <v>5.69750490954296</v>
+        <v>5.697191571467106</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.14363577650791</v>
+        <v>2.886211494141786</v>
       </c>
       <c r="G11" t="n">
-        <v>4.297748743480243</v>
+        <v>4.158007341165876</v>
       </c>
       <c r="H11" t="n">
-        <v>8.430552762206746</v>
+        <v>8.430850031687818</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.074027297948074</v>
+        <v>6.039381309415925</v>
       </c>
       <c r="G12" t="n">
-        <v>6.166077425812167</v>
+        <v>6.139713765662621</v>
       </c>
       <c r="H12" t="n">
-        <v>6.284112315083841</v>
+        <v>6.280972962471959</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.664629299978044</v>
+        <v>9.590374620440702</v>
       </c>
       <c r="G13" t="n">
-        <v>9.967686429010726</v>
+        <v>9.92860699077757</v>
       </c>
       <c r="H13" t="n">
-        <v>10.1886637205788</v>
+        <v>10.18885036236669</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.822106050046785</v>
+        <v>5.815525889841227</v>
       </c>
       <c r="G14" t="n">
-        <v>5.920268131709419</v>
+        <v>5.892058840909163</v>
       </c>
       <c r="H14" t="n">
-        <v>6.168536357560394</v>
+        <v>6.167714895529832</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.554638940393355</v>
+        <v>6.541360039276046</v>
       </c>
       <c r="G15" t="n">
-        <v>6.593908167919861</v>
+        <v>6.586444956350657</v>
       </c>
       <c r="H15" t="n">
-        <v>6.648575045410897</v>
+        <v>6.648268695635624</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.260000000000001</v>
+        <v>4.211863414344984</v>
       </c>
       <c r="G16" t="n">
-        <v>5.406353568005889</v>
+        <v>5.311182036226889</v>
       </c>
       <c r="H16" t="n">
-        <v>7.217224394499071</v>
+        <v>7.487500000000002</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.065423758865249</v>
+        <v>4.004400863629338</v>
       </c>
       <c r="G17" t="n">
-        <v>4.575862932985902</v>
+        <v>4.524594072520015</v>
       </c>
       <c r="H17" t="n">
-        <v>4.908804964539007</v>
+        <v>4.931980864635011</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.591276595744681</v>
+        <v>2.581991477741602</v>
       </c>
       <c r="G18" t="n">
-        <v>2.747714469549583</v>
+        <v>2.712576486784773</v>
       </c>
       <c r="H18" t="n">
-        <v>3.027993704288563</v>
+        <v>3.026281492121885</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.813726951247699</v>
+        <v>5.782418729349418</v>
       </c>
       <c r="G19" t="n">
-        <v>6.207330978982241</v>
+        <v>6.060653762479506</v>
       </c>
       <c r="H19" t="n">
-        <v>7.674964125091845</v>
+        <v>7.669249492415918</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8503426747093</v>
+        <v>102.8543768716536</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002286360246349168</v>
+        <v>0.001747836697901938</v>
       </c>
       <c r="T2" t="n">
-        <v>17.81046256193798</v>
+        <v>17.80887780812901</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18887350519144</v>
+        <v>36.18959351680671</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1286346557368087</v>
+        <v>0.1285224201155138</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7374559635556122</v>
+        <v>-0.7375251008786847</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1286293804697493</v>
+        <v>0.1285168313060907</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.88798527801997</v>
+        <v>53.88362296914705</v>
       </c>
       <c r="Z2" t="n">
-        <v>81.90347434815757</v>
+        <v>64.67358396964579</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.6680503076447</v>
+        <v>110.847046012042</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.95959865089773</v>
+        <v>4.959548386762567</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0535872372563662</v>
+        <v>0.05353697312120193</v>
       </c>
       <c r="T3" t="n">
-        <v>1.35049104321139</v>
+        <v>1.350490674439195</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725299678462889</v>
+        <v>1.725305309289989</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795199916456255</v>
+        <v>0.7795232639059908</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664804660847188</v>
+        <v>0.5664776363415108</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784667984093322</v>
+        <v>0.7784726465350081</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.581991477741602</v>
+        <v>2.565458773181727</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.712576486784773</v>
+        <v>2.664632184181536</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.026281492121885</v>
+        <v>2.88147128742822</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3663288447909284</v>
+        <v>0.3662145892351275</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246718276818832</v>
+        <v>7.246637564034154</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.328743995574943</v>
+        <v>0.3286632827902661</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293823925882399</v>
+        <v>1.293819637217244</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683882862944483</v>
+        <v>1.683875024031289</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674515666813908</v>
+        <v>0.8674529602909217</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7370981928749513</v>
+        <v>0.7371006406219922</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471823020788747</v>
+        <v>0.8472006580203418</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.004400863629338</v>
+        <v>3.934029745042494</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.524594072520015</v>
+        <v>4.410813373376007</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.931980864635011</v>
+        <v>4.879854479782288</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313468291051414</v>
+        <v>9.313400723890181</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3586801869621956</v>
+        <v>0.3586126198009633</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254702555284112</v>
+        <v>1.25469973445076</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747804918254224</v>
+        <v>1.747788679936671</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674831886705413</v>
+        <v>0.8674879869831423</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234654753208309</v>
+        <v>0.7234706136912745</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615609340141106</v>
+        <v>0.8615678387468624</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.782418729349418</v>
+        <v>5.766625335353753</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.060653762479506</v>
+        <v>5.909420717848538</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.669249492415918</v>
+        <v>6.207074100588111</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018716779269122</v>
+        <v>7.018731775490588</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2878991941157893</v>
+        <v>0.2879141903372559</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482035316515581</v>
+        <v>1.482055101637728</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910616562007694</v>
+        <v>1.910639106485007</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047640646950878</v>
+        <v>0.3047660056266646</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1980921661928354</v>
+        <v>-0.1981204403338148</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801531289265581</v>
+        <v>0.2801619007839669</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.541360039276046</v>
+        <v>6.531873671720885</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.586444956350657</v>
+        <v>6.574790195227173</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.648268695635624</v>
+        <v>6.596312312677951</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586436457929263</v>
+        <v>5.586417296093315</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003864621884471626</v>
+        <v>0.003845460048522954</v>
       </c>
       <c r="T7" t="n">
-        <v>1.155963988077594</v>
+        <v>1.155982954143557</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494036103217407</v>
+        <v>1.494055467232791</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089384118144509</v>
+        <v>0.5089324937631931</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0745759184741196</v>
+        <v>0.07455192970672364</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050892256658337</v>
+        <v>0.5050852337472254</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.603223731940104</v>
+        <v>5.587445030715677</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.716635674573947</v>
+        <v>5.677325085409662</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.915809382782526</v>
+        <v>5.839999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116745455549594</v>
+        <v>8.116692996729009</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2363883920839949</v>
+        <v>0.2363359332634095</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445239969004653</v>
+        <v>1.44525037501284</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824972627471824</v>
+        <v>1.824980021468033</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087131108100227</v>
+        <v>0.8087141145093134</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288861377293817</v>
+        <v>0.6288831305390183</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990414759983432</v>
+        <v>0.7990508888783363</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.410460542658972</v>
+        <v>5.40440236648816</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.46503065620036</v>
+        <v>5.438953001889542</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.697191571467106</v>
+        <v>5.519883736337237</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5106626506024097</v>
+        <v>0.510421388101983</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679776498097223</v>
+        <v>7.679702818602975</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06382569734697086</v>
+        <v>0.0637520178527238</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477303648494101</v>
+        <v>1.477309397216344</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919714821513665</v>
+        <v>1.919718426429413</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7616987615007448</v>
+        <v>0.7617044733169022</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361102389645047</v>
+        <v>0.5361084967421114</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597229628255315</v>
+        <v>0.7597330954795651</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.815525889841227</v>
+        <v>5.741209626516193</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.892058840909163</v>
+        <v>5.851037176384123</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.167714895529832</v>
+        <v>5.942586756373937</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61945332562966</v>
+        <v>10.61935980976108</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3143937858918993</v>
+        <v>0.3143002700233196</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051629224749192</v>
+        <v>2.051651401139541</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697306721839158</v>
+        <v>2.697319546920817</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566144571976703</v>
+        <v>0.3566268748946616</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1197790123796052</v>
+        <v>-0.1197896609953515</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3358334903511079</v>
+        <v>0.3358561973976484</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.590374620440702</v>
+        <v>9.578396446508883</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.92860699077757</v>
+        <v>9.860816261534367</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.18885036236669</v>
+        <v>10.17033613940078</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218386339729123</v>
+        <v>5.218357755428325</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02749010017524594</v>
+        <v>-0.02751868447604426</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157898315409949</v>
+        <v>1.157905726665871</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476832029810608</v>
+        <v>1.476848605144791</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294580568245135</v>
+        <v>0.4294625110149707</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08241139518625795</v>
+        <v>-0.08243569237228709</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268527583793454</v>
+        <v>0.4268600745439536</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.168839714499081</v>
+        <v>4.205</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.521225297162577</v>
+        <v>4.424628980147187</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.664645356256155</v>
+        <v>4.664403193608357</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664346377767289</v>
+        <v>7.664336629714414</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725792096042216</v>
+        <v>0.1725694615513467</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149368354844541</v>
+        <v>0.9149438585301797</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198011694140042</v>
+        <v>1.198025068853699</v>
       </c>
       <c r="V12" t="n">
-        <v>0.829622022131781</v>
+        <v>0.8296198381376003</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543356735746696</v>
+        <v>0.654327955474393</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279381181469615</v>
+        <v>0.827936633922166</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.013769097435109</v>
+        <v>5.024999999999999</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.318954241036741</v>
+        <v>5.325312952063079</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.609678728719034</v>
+        <v>5.609986376505694</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.861137491141035</v>
+        <v>2.860970254957507</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03100258379659</v>
+        <v>10.03081907974101</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4141278097196481</v>
+        <v>0.4139443056640663</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69416133293073</v>
+        <v>1.694131576562475</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153881705697316</v>
+        <v>2.153835988581318</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231723809081499</v>
+        <v>0.8231824434407962</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485174134148668</v>
+        <v>0.6485323340111151</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8112782840713493</v>
+        <v>0.8113084361432691</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.487385181652312</v>
+        <v>6.200331821121831</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.158454931017556</v>
+        <v>6.986222930500273</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.700025453546634</v>
+        <v>7.468802838363662</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.203345374994711</v>
+        <v>8.203187078262198</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06946176750343487</v>
+        <v>0.06930347077092197</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759468030896321</v>
+        <v>1.759379713915608</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284929612374291</v>
+        <v>2.284843372942257</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807233008744462</v>
+        <v>0.7807491009082755</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5649675371588079</v>
+        <v>0.5650003751458625</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803669934982161</v>
+        <v>0.7803954939941694</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.039381309415925</v>
+        <v>6.023857843964323</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.139713765662621</v>
+        <v>6.102628530195209</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.280972962471959</v>
+        <v>6.237419583871077</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82480540454196</v>
+        <v>11.8246943791473</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1390764928442973</v>
+        <v>-0.1391875182389583</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052482049615668</v>
+        <v>2.052466790002697</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697874149580598</v>
+        <v>2.697841156851453</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948077486491253</v>
+        <v>0.794818291146846</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609528914211291</v>
+        <v>0.6095384644180728</v>
       </c>
       <c r="X15" t="n">
-        <v>0.785968863569281</v>
+        <v>0.7859867354271878</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.74609837016007</v>
+        <v>7.735316285521041</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.051998768738553</v>
+        <v>7.988058850073621</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.268499786633004</v>
+        <v>8.202060324514612</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.66296070978153</v>
+        <v>8.66285882456383</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2546904330801906</v>
+        <v>0.254588547862491</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538079815090161</v>
+        <v>3.538107990401135</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06320129806036</v>
+        <v>11.06321159260951</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04954226667525485</v>
+        <v>0.04953971045595313</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971316729916891</v>
+        <v>-0.597134645324509</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03278674237424661</v>
+        <v>0.03278454376828432</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.7835102850365</v>
+        <v>10.77946638816702</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.3117678106549</v>
+        <v>11.39849168959219</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.81052741711589</v>
+        <v>11.85925755670417</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910950923540661</v>
+        <v>6.910926510428022</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3712849660938528</v>
+        <v>0.371260552981213</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032012111555993</v>
+        <v>2.032032795945048</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566281456433692</v>
+        <v>2.56630093514483</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210278328480742</v>
+        <v>0.521028353818637</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02252196535914097</v>
+        <v>0.02250712670261512</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176737661707667</v>
+        <v>0.5176747615285351</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.886211494141786</v>
+        <v>2.872275677382615</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.158007341165876</v>
+        <v>3.627197445694426</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.430850031687818</v>
+        <v>4.2613120497561</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693160618852027</v>
+        <v>6.693144277084714</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1953996341215816</v>
+        <v>0.1953832923542692</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099726526243733</v>
+        <v>1.099747000083937</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489210786598514</v>
+        <v>1.489230435058758</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009416821431686</v>
+        <v>0.600937379613707</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2175077168650503</v>
+        <v>0.217487068518851</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979823384358277</v>
+        <v>0.5979801859201679</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.211863414344984</v>
+        <v>4.058100873907164</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.31118203622689</v>
+        <v>4.848464320046242</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.487500000000002</v>
+        <v>6.287874967420947</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16663</v>
+        <v>16664</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15375376088195</v>
+        <v>11.15362161954383</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7844343416442059</v>
+        <v>0.784302200306081</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038113959081525</v>
+        <v>2.038108614548109</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757621074467685</v>
+        <v>2.757628698770828</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263581283241359</v>
+        <v>0.7263548592866103</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693757569906786</v>
+        <v>0.4693728228343409</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6788965331574183</v>
+        <v>0.6789191163525424</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.735832617919256</v>
+        <v>7.730055486721053</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.822139961123153</v>
+        <v>7.805488279614082</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.920638040579542</v>
+        <v>7.880961465520272</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.735832617919256</v>
+        <v>7.730055486721053</v>
       </c>
       <c r="G2" t="n">
-        <v>7.822139961123153</v>
+        <v>7.805488279614082</v>
       </c>
       <c r="H2" t="n">
-        <v>7.920638040579542</v>
+        <v>7.880961465520272</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.603223731940104</v>
+        <v>5.587445030715677</v>
       </c>
       <c r="G3" t="n">
-        <v>5.716635674573946</v>
+        <v>5.677325085409662</v>
       </c>
       <c r="H3" t="n">
-        <v>5.915809382782526</v>
+        <v>5.839999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.168839714499081</v>
+        <v>4.205</v>
       </c>
       <c r="G4" t="n">
-        <v>4.521225297162577</v>
+        <v>4.424628980147187</v>
       </c>
       <c r="H4" t="n">
-        <v>5.664645356256155</v>
+        <v>4.664403193608357</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7835102850365</v>
+        <v>10.77946638816702</v>
       </c>
       <c r="G5" t="n">
-        <v>11.3117678106549</v>
+        <v>11.39849168959219</v>
       </c>
       <c r="H5" t="n">
-        <v>11.81052741711589</v>
+        <v>11.85925755670417</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.88798527801997</v>
+        <v>53.88362296914705</v>
       </c>
       <c r="G6" t="n">
-        <v>81.90347434815757</v>
+        <v>64.6735839696458</v>
       </c>
       <c r="H6" t="n">
-        <v>113.6680503076447</v>
+        <v>110.847046012042</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.74609837016007</v>
+        <v>7.735316285521041</v>
       </c>
       <c r="G7" t="n">
-        <v>8.051998768738551</v>
+        <v>7.988058850073621</v>
       </c>
       <c r="H7" t="n">
-        <v>8.268499786633004</v>
+        <v>8.202060324514612</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.487385181652312</v>
+        <v>6.200331821121831</v>
       </c>
       <c r="G8" t="n">
-        <v>7.158454931017556</v>
+        <v>6.986222930500273</v>
       </c>
       <c r="H8" t="n">
-        <v>7.700025453546634</v>
+        <v>7.468802838363662</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.013769097435109</v>
+        <v>5.024999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>5.318954241036742</v>
+        <v>5.325312952063079</v>
       </c>
       <c r="H9" t="n">
-        <v>5.609678728719034</v>
+        <v>5.609986376505694</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.410460542658972</v>
+        <v>5.40440236648816</v>
       </c>
       <c r="G10" t="n">
-        <v>5.46503065620036</v>
+        <v>5.438953001889541</v>
       </c>
       <c r="H10" t="n">
-        <v>5.697191571467106</v>
+        <v>5.519883736337237</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.886211494141786</v>
+        <v>2.872275677382615</v>
       </c>
       <c r="G11" t="n">
-        <v>4.158007341165876</v>
+        <v>3.627197445694426</v>
       </c>
       <c r="H11" t="n">
-        <v>8.430850031687818</v>
+        <v>4.2613120497561</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.039381309415925</v>
+        <v>6.023857843964323</v>
       </c>
       <c r="G12" t="n">
-        <v>6.139713765662621</v>
+        <v>6.102628530195209</v>
       </c>
       <c r="H12" t="n">
-        <v>6.280972962471959</v>
+        <v>6.237419583871077</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.590374620440702</v>
+        <v>9.578396446508883</v>
       </c>
       <c r="G13" t="n">
-        <v>9.92860699077757</v>
+        <v>9.860816261534366</v>
       </c>
       <c r="H13" t="n">
-        <v>10.18885036236669</v>
+        <v>10.17033613940078</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.815525889841227</v>
+        <v>5.741209626516193</v>
       </c>
       <c r="G14" t="n">
-        <v>5.892058840909163</v>
+        <v>5.851037176384122</v>
       </c>
       <c r="H14" t="n">
-        <v>6.167714895529832</v>
+        <v>5.942586756373937</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.541360039276046</v>
+        <v>6.531873671720885</v>
       </c>
       <c r="G15" t="n">
-        <v>6.586444956350657</v>
+        <v>6.574790195227173</v>
       </c>
       <c r="H15" t="n">
-        <v>6.648268695635624</v>
+        <v>6.596312312677951</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.211863414344984</v>
+        <v>4.058100873907164</v>
       </c>
       <c r="G16" t="n">
-        <v>5.311182036226889</v>
+        <v>4.848464320046242</v>
       </c>
       <c r="H16" t="n">
-        <v>7.487500000000002</v>
+        <v>6.287874967420947</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>4.004400863629338</v>
+        <v>3.934029745042494</v>
       </c>
       <c r="G17" t="n">
-        <v>4.524594072520015</v>
+        <v>4.410813373376007</v>
       </c>
       <c r="H17" t="n">
-        <v>4.931980864635011</v>
+        <v>4.879854479782288</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.581991477741602</v>
+        <v>2.565458773181727</v>
       </c>
       <c r="G18" t="n">
-        <v>2.712576486784773</v>
+        <v>2.664632184181536</v>
       </c>
       <c r="H18" t="n">
-        <v>3.026281492121885</v>
+        <v>2.88147128742822</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.782418729349418</v>
+        <v>5.766625335353753</v>
       </c>
       <c r="G19" t="n">
-        <v>6.060653762479506</v>
+        <v>5.909420717848538</v>
       </c>
       <c r="H19" t="n">
-        <v>7.669249492415918</v>
+        <v>6.207074100588111</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -629,13 +629,13 @@
         <v>36.18959351680671</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285224201155138</v>
+        <v>0.128522420115514</v>
       </c>
       <c r="W2" t="n">
         <v>-0.7375251008786847</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285168313060907</v>
+        <v>0.1285168313060909</v>
       </c>
       <c r="Y2" t="n">
         <v>53.88362296914705</v>
@@ -718,13 +718,13 @@
         <v>1.725305309289989</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795232639059908</v>
+        <v>0.7795232639059904</v>
       </c>
       <c r="W3" t="n">
         <v>0.5664776363415108</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784726465350081</v>
+        <v>0.7784726465350077</v>
       </c>
       <c r="Y3" t="n">
         <v>2.565458773181727</v>
@@ -807,13 +807,13 @@
         <v>1.683875024031289</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674529602909217</v>
+        <v>0.867452960290922</v>
       </c>
       <c r="W4" t="n">
         <v>0.7371006406219922</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472006580203418</v>
+        <v>0.8472006580203422</v>
       </c>
       <c r="Y4" t="n">
         <v>3.934029745042494</v>
@@ -896,13 +896,13 @@
         <v>1.747788679936671</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674879869831423</v>
+        <v>0.8674879869831428</v>
       </c>
       <c r="W5" t="n">
         <v>0.7234706136912745</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615678387468624</v>
+        <v>0.8615678387468627</v>
       </c>
       <c r="Y5" t="n">
         <v>5.766625335353753</v>
@@ -1163,13 +1163,13 @@
         <v>1.824980021468033</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087141145093134</v>
+        <v>0.808714114509313</v>
       </c>
       <c r="W8" t="n">
         <v>0.6288831305390183</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990508888783363</v>
+        <v>0.7990508888783359</v>
       </c>
       <c r="Y8" t="n">
         <v>5.40440236648816</v>
@@ -1252,13 +1252,13 @@
         <v>1.919718426429413</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617044733169022</v>
+        <v>0.7617044733169018</v>
       </c>
       <c r="W9" t="n">
         <v>0.5361084967421114</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597330954795651</v>
+        <v>0.7597330954795648</v>
       </c>
       <c r="Y9" t="n">
         <v>5.741209626516193</v>
@@ -1341,13 +1341,13 @@
         <v>2.697319546920817</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566268748946616</v>
+        <v>0.3566268748946617</v>
       </c>
       <c r="W10" t="n">
         <v>-0.1197896609953515</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3358561973976484</v>
+        <v>0.3358561973976485</v>
       </c>
       <c r="Y10" t="n">
         <v>9.578396446508883</v>
@@ -1430,13 +1430,13 @@
         <v>1.476848605144791</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294625110149707</v>
+        <v>0.4294625110149708</v>
       </c>
       <c r="W11" t="n">
         <v>-0.08243569237228709</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268600745439536</v>
+        <v>0.4268600745439538</v>
       </c>
       <c r="Y11" t="n">
         <v>4.205</v>
@@ -1519,13 +1519,13 @@
         <v>1.198025068853699</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296198381376003</v>
+        <v>0.8296198381376007</v>
       </c>
       <c r="W12" t="n">
         <v>0.654327955474393</v>
       </c>
       <c r="X12" t="n">
-        <v>0.827936633922166</v>
+        <v>0.8279366339221663</v>
       </c>
       <c r="Y12" t="n">
         <v>5.024999999999999</v>
@@ -1608,13 +1608,13 @@
         <v>2.153835988581318</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231824434407962</v>
+        <v>0.8231824434407964</v>
       </c>
       <c r="W13" t="n">
         <v>0.6485323340111151</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8113084361432691</v>
+        <v>0.8113084361432693</v>
       </c>
       <c r="Y13" t="n">
         <v>6.200331821121831</v>
@@ -1697,13 +1697,13 @@
         <v>2.284843372942257</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807491009082755</v>
+        <v>0.7807491009082757</v>
       </c>
       <c r="W14" t="n">
         <v>0.5650003751458625</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803954939941694</v>
+        <v>0.7803954939941695</v>
       </c>
       <c r="Y14" t="n">
         <v>6.023857843964323</v>
@@ -1786,13 +1786,13 @@
         <v>2.697841156851453</v>
       </c>
       <c r="V15" t="n">
-        <v>0.794818291146846</v>
+        <v>0.7948182911468458</v>
       </c>
       <c r="W15" t="n">
         <v>0.6095384644180728</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7859867354271878</v>
+        <v>0.7859867354271876</v>
       </c>
       <c r="Y15" t="n">
         <v>7.735316285521041</v>
@@ -1875,7 +1875,7 @@
         <v>11.06321159260951</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953971045595313</v>
+        <v>0.04953971045595312</v>
       </c>
       <c r="W16" t="n">
         <v>-0.597134645324509</v>
@@ -2053,13 +2053,13 @@
         <v>1.489230435058758</v>
       </c>
       <c r="V18" t="n">
-        <v>0.600937379613707</v>
+        <v>0.6009373796137073</v>
       </c>
       <c r="W18" t="n">
         <v>0.217487068518851</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979801859201679</v>
+        <v>0.5979801859201683</v>
       </c>
       <c r="Y18" t="n">
         <v>4.058100873907164</v>
@@ -2142,13 +2142,13 @@
         <v>2.757628698770828</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263548592866103</v>
+        <v>0.7263548592866101</v>
       </c>
       <c r="W19" t="n">
         <v>0.4693728228343409</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789191163525424</v>
+        <v>0.6789191163525423</v>
       </c>
       <c r="Y19" t="n">
         <v>7.730055486721053</v>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8543768716536</v>
+        <v>102.8584126075164</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001747836697901938</v>
+        <v>0.005783572560714375</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80887780812901</v>
+        <v>17.80499036813145</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18959351680671</v>
+        <v>36.18702953091429</v>
       </c>
       <c r="V2" t="n">
-        <v>0.128522420115514</v>
+        <v>0.1285717008434944</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7375251008786847</v>
+        <v>-0.7372789067881556</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285168313060909</v>
+        <v>0.1285658007024932</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.88362296914705</v>
+        <v>54.62569296474383</v>
       </c>
       <c r="Z2" t="n">
-        <v>64.67358396964579</v>
+        <v>87.22371712332644</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.847046012042</v>
+        <v>112.9620603674578</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959548386762567</v>
+        <v>4.959498113913162</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05353697312120193</v>
+        <v>0.0534867002717969</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350490674439195</v>
+        <v>1.350487553082963</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725305309289989</v>
+        <v>1.725309839845798</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795232639059904</v>
+        <v>0.7795268409699974</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664776363415108</v>
+        <v>0.5664753595272782</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784726465350077</v>
+        <v>0.7784788040498611</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.565458773181727</v>
+        <v>2.558124289023677</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.664632184181536</v>
+        <v>2.635473535025278</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.88147128742822</v>
+        <v>2.807707006369427</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3662145892351275</v>
+        <v>0.3661004953998584</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246637564034154</v>
+        <v>7.246557594572773</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3286632827902661</v>
+        <v>0.3285833133288848</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293819637217244</v>
+        <v>1.293820169073055</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683875024031289</v>
+        <v>1.683872461236543</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867452960290922</v>
+        <v>0.867453488385944</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371006406219922</v>
+        <v>0.7371014408673484</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472006580203422</v>
+        <v>0.8472181446343394</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.934029745042494</v>
+        <v>3.949126857749469</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.410813373376007</v>
+        <v>4.369244355332713</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.879854479782288</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313400723890181</v>
+        <v>9.313368285528</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3586126198009633</v>
+        <v>0.3585801814387816</v>
       </c>
       <c r="T5" t="n">
-        <v>1.25469973445076</v>
+        <v>1.254686546573227</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747788679936671</v>
+        <v>1.747772807251434</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674879869831428</v>
+        <v>0.867492715213743</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234706136912745</v>
+        <v>0.7234756363167523</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615678387468627</v>
+        <v>0.8615735026200183</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.766625335353753</v>
+        <v>5.805694305791429</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.909420717848538</v>
+        <v>5.906710058175214</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.207074100588111</v>
+        <v>6.098719150900536</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018731775490588</v>
+        <v>7.018750596784288</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2879141903372559</v>
+        <v>0.2879330116309559</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482055101637728</v>
+        <v>1.48207411015781</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910639106485007</v>
+        <v>1.910661343636481</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047660056266646</v>
+        <v>0.3047681037150564</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981204403338148</v>
+        <v>-0.1981483293691291</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801619007839669</v>
+        <v>0.2801705803679889</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.531873671720885</v>
+        <v>6.549286981907136</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.574790195227173</v>
+        <v>6.577303226727951</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.596312312677951</v>
+        <v>6.591012967761306</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586417296093315</v>
+        <v>5.586402590365644</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003845460048522954</v>
+        <v>0.003830754320851901</v>
       </c>
       <c r="T7" t="n">
-        <v>1.155982954143557</v>
+        <v>1.156001534308347</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494055467232791</v>
+        <v>1.494076061193973</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089324937631931</v>
+        <v>0.5089260135958888</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07455192970672364</v>
+        <v>0.07452641690160355</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050852337472254</v>
+        <v>0.5050807481693256</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.587445030715677</v>
+        <v>5.587080726797089</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.677325085409662</v>
+        <v>5.661387335947123</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.839999999999999</v>
+        <v>5.781175572173638</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116692996729009</v>
+        <v>8.116646762869628</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2363359332634095</v>
+        <v>0.2362896994040279</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44525037501284</v>
+        <v>1.445268120811674</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824980021468033</v>
+        <v>1.824992434995467</v>
       </c>
       <c r="V8" t="n">
-        <v>0.808714114509313</v>
+        <v>0.8087139603448765</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288831305390183</v>
+        <v>0.628878081842535</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990508888783359</v>
+        <v>0.7990586117174976</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.40440236648816</v>
+        <v>5.367401051130217</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.438953001889542</v>
+        <v>5.421945681699152</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.519883736337237</v>
+        <v>5.474953001560999</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.510421388101983</v>
+        <v>0.5101804670912952</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679702818602975</v>
+        <v>7.679634243348593</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0637520178527238</v>
+        <v>0.06368344259834056</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477309397216344</v>
+        <v>1.477315459949943</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919718426429413</v>
+        <v>1.919722268666838</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617044733169018</v>
+        <v>0.7617099232574848</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361084967421114</v>
+        <v>0.5361066398207484</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597330954795648</v>
+        <v>0.7597427995522884</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.741209626516193</v>
+        <v>5.672452229299362</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.851037176384123</v>
+        <v>5.828319553284036</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.942586756373937</v>
+        <v>5.906008492569003</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61935980976108</v>
+        <v>10.61927039093353</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3143002700233196</v>
+        <v>0.314210851195768</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051651401139541</v>
+        <v>2.051670344667273</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697319546920817</v>
+        <v>2.697333640128392</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566268748946617</v>
+        <v>0.3566383927661269</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1197896609953515</v>
+        <v>-0.1198013625895358</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3358561973976485</v>
+        <v>0.335877795596792</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.578396446508883</v>
+        <v>9.633288575716575</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.860816261534367</v>
+        <v>9.882352293455702</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.17033613940078</v>
+        <v>10.11406970830538</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218357755428325</v>
+        <v>5.218331379128025</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02751868447604426</v>
+        <v>-0.02754506077634401</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157905726665871</v>
+        <v>1.157915399512265</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476848605144791</v>
+        <v>1.476866497194637</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294625110149708</v>
+        <v>0.4294656913248853</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08243569237228709</v>
+        <v>-0.08246191999048902</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268600745439538</v>
+        <v>0.4268660862015664</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.205</v>
+        <v>4.332850583372386</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.424628980147187</v>
+        <v>4.512526257851787</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.664403193608357</v>
+        <v>4.675318471337579</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664336629714414</v>
+        <v>7.664317696120657</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725694615513467</v>
+        <v>0.1725505279575896</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149438585301797</v>
+        <v>0.9149406101245448</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198025068853699</v>
+        <v>1.198034327553449</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296198381376007</v>
+        <v>0.8296193731717479</v>
       </c>
       <c r="W12" t="n">
-        <v>0.654327955474393</v>
+        <v>0.6543226125377171</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279366339221663</v>
+        <v>0.8279372312510067</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.024999999999999</v>
+        <v>5.035011639175089</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.325312952063079</v>
+        <v>5.326315713151743</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.609986376505694</v>
+        <v>5.611008533419266</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860970254957507</v>
+        <v>2.860803255484784</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03081907974101</v>
+        <v>10.0306395278058</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4139443056640663</v>
+        <v>0.4137647537288608</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694131576562475</v>
+        <v>1.694104237941933</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153835988581318</v>
+        <v>2.153794457611741</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231824434407964</v>
+        <v>0.8231918560539556</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485323340111151</v>
+        <v>0.648545888109283</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8113084361432693</v>
+        <v>0.8113377358006452</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.200331821121831</v>
+        <v>6.163747163042682</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.986222930500273</v>
+        <v>6.857461520350813</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.468802838363662</v>
+        <v>7.360279839096015</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.203187078262198</v>
+        <v>8.20302998288969</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06930347077092197</v>
+        <v>0.06914637539841285</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759379713915608</v>
+        <v>1.759292885467599</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284843372942257</v>
+        <v>2.284759398638941</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807491009082757</v>
+        <v>0.7807744681092741</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5650003751458625</v>
+        <v>0.5650323494331203</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803954939941695</v>
+        <v>0.7804235439792748</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.023857843964323</v>
+        <v>6.011873642634637</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.102628530195209</v>
+        <v>6.076721070911233</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.237419583871077</v>
+        <v>6.1532160176047</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.8246943791473</v>
+        <v>11.82458985440803</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1391875182389583</v>
+        <v>-0.1392920429782252</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052466790002697</v>
+        <v>2.052448501555933</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697841156851453</v>
+        <v>2.697809015420801</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948182911468458</v>
+        <v>0.7948284085587265</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095384644180728</v>
+        <v>0.6095477680922921</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7859867354271876</v>
+        <v>0.7860037870806665</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.735316285521041</v>
+        <v>7.733432008022392</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.988058850073621</v>
+        <v>7.943626434673466</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.202060324514612</v>
+        <v>8.187751646653904</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.66285882456383</v>
+        <v>8.662770112366003</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.254588547862491</v>
+        <v>0.2544998356646622</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538107990401135</v>
+        <v>3.538143818998976</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06321159260951</v>
+        <v>11.06322305378657</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953971045595312</v>
+        <v>0.04953742241237644</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.597134645324509</v>
+        <v>-0.5971379544996613</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03278454376828432</v>
+        <v>0.0327826410348695</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.77946638816702</v>
+        <v>10.77844141784804</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.39849168959219</v>
+        <v>11.546227253908</v>
       </c>
       <c r="AA16" t="n">
-        <v>11.85925755670417</v>
+        <v>12.11416249488671</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910926510428022</v>
+        <v>6.910933462523443</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.371260552981213</v>
+        <v>0.3712675050766349</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032032795945048</v>
+        <v>2.032066986465126</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56630093514483</v>
+        <v>2.566330639233826</v>
       </c>
       <c r="V17" t="n">
-        <v>0.521028353818637</v>
+        <v>0.5210212512563162</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02250712670261512</v>
+        <v>0.02248449825484333</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176747615285351</v>
+        <v>0.5176675989423487</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.872275677382615</v>
+        <v>3.958455424845097</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.627197445694426</v>
+        <v>4.803791040067241</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.2613120497561</v>
+        <v>7.283671804970647</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693144277084714</v>
+        <v>6.693145188716639</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1953832923542692</v>
+        <v>0.1953842039861926</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099747000083937</v>
+        <v>1.099774890939513</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489230435058758</v>
+        <v>1.489259742847926</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009373796137073</v>
+        <v>0.6009257812746559</v>
       </c>
       <c r="W18" t="n">
-        <v>0.217487068518851</v>
+        <v>0.2174562687861262</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979801859201683</v>
+        <v>0.5979697657972877</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.058100873907164</v>
+        <v>5.174327042466015</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.848464320046242</v>
+        <v>6.059021555916143</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.287874967420947</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16664</v>
+        <v>16665</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15362161954383</v>
+        <v>11.15349453652766</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.784302200306081</v>
+        <v>0.7841751172899144</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038108614548109</v>
+        <v>2.038105355915333</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757628698770828</v>
+        <v>2.757637192759483</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263548592866101</v>
+        <v>0.7263514654585723</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693728228343409</v>
+        <v>0.4693695539764513</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789191163525423</v>
+        <v>0.6789406443991768</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.730055486721053</v>
+        <v>7.771650136097461</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.805488279614082</v>
+        <v>7.845778410060757</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.880961465520272</v>
+        <v>7.892677663167563</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.730055486721053</v>
+        <v>7.771650136097461</v>
       </c>
       <c r="G2" t="n">
-        <v>7.805488279614082</v>
+        <v>7.845778410060757</v>
       </c>
       <c r="H2" t="n">
-        <v>7.880961465520272</v>
+        <v>7.892677663167563</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.587445030715677</v>
+        <v>5.587080726797089</v>
       </c>
       <c r="G3" t="n">
-        <v>5.677325085409662</v>
+        <v>5.661387335947123</v>
       </c>
       <c r="H3" t="n">
-        <v>5.839999999999999</v>
+        <v>5.781175572173638</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.205</v>
+        <v>4.332850583372386</v>
       </c>
       <c r="G4" t="n">
-        <v>4.424628980147187</v>
+        <v>4.512526257851787</v>
       </c>
       <c r="H4" t="n">
-        <v>4.664403193608357</v>
+        <v>4.675318471337579</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.77946638816702</v>
+        <v>10.77844141784804</v>
       </c>
       <c r="G5" t="n">
-        <v>11.39849168959219</v>
+        <v>11.546227253908</v>
       </c>
       <c r="H5" t="n">
-        <v>11.85925755670417</v>
+        <v>12.11416249488671</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.88362296914705</v>
+        <v>54.62569296474383</v>
       </c>
       <c r="G6" t="n">
-        <v>64.6735839696458</v>
+        <v>87.22371712332644</v>
       </c>
       <c r="H6" t="n">
-        <v>110.847046012042</v>
+        <v>112.9620603674578</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.735316285521041</v>
+        <v>7.733432008022392</v>
       </c>
       <c r="G7" t="n">
-        <v>7.988058850073621</v>
+        <v>7.943626434673466</v>
       </c>
       <c r="H7" t="n">
-        <v>8.202060324514612</v>
+        <v>8.187751646653904</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.200331821121831</v>
+        <v>6.163747163042682</v>
       </c>
       <c r="G8" t="n">
-        <v>6.986222930500273</v>
+        <v>6.857461520350813</v>
       </c>
       <c r="H8" t="n">
-        <v>7.468802838363662</v>
+        <v>7.360279839096015</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.024999999999999</v>
+        <v>5.035011639175089</v>
       </c>
       <c r="G9" t="n">
-        <v>5.325312952063079</v>
+        <v>5.326315713151743</v>
       </c>
       <c r="H9" t="n">
-        <v>5.609986376505694</v>
+        <v>5.611008533419266</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.40440236648816</v>
+        <v>5.367401051130217</v>
       </c>
       <c r="G10" t="n">
-        <v>5.438953001889541</v>
+        <v>5.421945681699153</v>
       </c>
       <c r="H10" t="n">
-        <v>5.519883736337237</v>
+        <v>5.474953001560999</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.872275677382615</v>
+        <v>3.958455424845097</v>
       </c>
       <c r="G11" t="n">
-        <v>3.627197445694426</v>
+        <v>4.803791040067241</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2613120497561</v>
+        <v>7.283671804970647</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.023857843964323</v>
+        <v>6.011873642634637</v>
       </c>
       <c r="G12" t="n">
-        <v>6.102628530195209</v>
+        <v>6.076721070911234</v>
       </c>
       <c r="H12" t="n">
-        <v>6.237419583871077</v>
+        <v>6.1532160176047</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.578396446508883</v>
+        <v>9.633288575716575</v>
       </c>
       <c r="G13" t="n">
-        <v>9.860816261534366</v>
+        <v>9.882352293455702</v>
       </c>
       <c r="H13" t="n">
-        <v>10.17033613940078</v>
+        <v>10.11406970830538</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.741209626516193</v>
+        <v>5.672452229299362</v>
       </c>
       <c r="G14" t="n">
-        <v>5.851037176384122</v>
+        <v>5.828319553284036</v>
       </c>
       <c r="H14" t="n">
-        <v>5.942586756373937</v>
+        <v>5.906008492569003</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.531873671720885</v>
+        <v>6.549286981907136</v>
       </c>
       <c r="G15" t="n">
-        <v>6.574790195227173</v>
+        <v>6.577303226727951</v>
       </c>
       <c r="H15" t="n">
-        <v>6.596312312677951</v>
+        <v>6.591012967761306</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.058100873907164</v>
+        <v>5.174327042466015</v>
       </c>
       <c r="G16" t="n">
-        <v>4.848464320046242</v>
+        <v>6.059021555916142</v>
       </c>
       <c r="H16" t="n">
-        <v>6.287874967420947</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.934029745042494</v>
+        <v>3.949126857749469</v>
       </c>
       <c r="G17" t="n">
-        <v>4.410813373376007</v>
+        <v>4.369244355332713</v>
       </c>
       <c r="H17" t="n">
-        <v>4.879854479782288</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.565458773181727</v>
+        <v>2.558124289023677</v>
       </c>
       <c r="G18" t="n">
-        <v>2.664632184181536</v>
+        <v>2.635473535025278</v>
       </c>
       <c r="H18" t="n">
-        <v>2.88147128742822</v>
+        <v>2.807707006369427</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.766625335353753</v>
+        <v>5.805694305791429</v>
       </c>
       <c r="G19" t="n">
-        <v>5.909420717848538</v>
+        <v>5.906710058175214</v>
       </c>
       <c r="H19" t="n">
-        <v>6.207074100588111</v>
+        <v>6.098719150900536</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8584126075164</v>
+        <v>102.8604235098902</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.005783572560714375</v>
+        <v>0.007794474934513867</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80499036813145</v>
+        <v>17.80313532873799</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18702953091429</v>
+        <v>36.18651296297458</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285717008434944</v>
+        <v>0.1285918721585763</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7372789067881556</v>
+        <v>-0.7372293080124681</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285658007024932</v>
+        <v>0.1285859504189382</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.62569296474383</v>
+        <v>54.6211168347924</v>
       </c>
       <c r="Z2" t="n">
-        <v>87.22371712332644</v>
+        <v>85.76752254840014</v>
       </c>
       <c r="AA2" t="n">
-        <v>112.9620603674578</v>
+        <v>112.0442451555832</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959498113913162</v>
+        <v>4.959452540619178</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0534867002717969</v>
+        <v>0.05344112697781393</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350487553082963</v>
+        <v>1.350482254526217</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725309839845798</v>
+        <v>1.725312076525368</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795268409699974</v>
+        <v>0.7795307713581335</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664753595272782</v>
+        <v>0.5664742354899457</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784788040498611</v>
+        <v>0.7784851523225209</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.558124289023677</v>
+        <v>2.49939179632249</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.635473535025278</v>
+        <v>2.615070257508525</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.807707006369427</v>
+        <v>2.70833388801065</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3661004953998584</v>
+        <v>0.3659865629420084</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246557594572773</v>
+        <v>7.246481300766394</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3285833133288848</v>
+        <v>0.3285070195225063</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293820169073055</v>
+        <v>1.2938262951701</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683872461236543</v>
+        <v>1.683871373714836</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867453488385944</v>
+        <v>0.867453818463486</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371014408673484</v>
+        <v>0.7371017804510211</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472181446343394</v>
+        <v>0.8472349186718949</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.949126857749469</v>
+        <v>3.924611032531824</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.369244355332713</v>
+        <v>4.336353622841807</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.82</v>
+        <v>4.674070014144272</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313368285528</v>
+        <v>9.313339530333712</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3585801814387816</v>
+        <v>0.3585514262444932</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254686546573227</v>
+        <v>1.254681991420696</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747772807251434</v>
+        <v>1.747764142109944</v>
       </c>
       <c r="V5" t="n">
-        <v>0.867492715213743</v>
+        <v>0.8674962812237701</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234756363167523</v>
+        <v>0.7234783782255255</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615735026200183</v>
+        <v>0.8615779269320812</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.805694305791429</v>
+        <v>5.799377725132942</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.906710058175214</v>
+        <v>5.898489830491287</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.098719150900536</v>
+        <v>6.037284797416499</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018750596784288</v>
+        <v>7.018769831030919</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2879330116309559</v>
+        <v>0.2879522458775874</v>
       </c>
       <c r="T6" t="n">
-        <v>1.48207411015781</v>
+        <v>1.482092500162924</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910661343636481</v>
+        <v>1.91068208991177</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047681037150564</v>
+        <v>0.3047713073023302</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981483293691291</v>
+        <v>-0.1981743488938481</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801705803679889</v>
+        <v>0.2801802888629902</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.549286981907136</v>
+        <v>6.562428071882835</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.577303226727951</v>
+        <v>6.577111201101031</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.591012967761306</v>
+        <v>6.585592054787766</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586402590365644</v>
+        <v>5.586391501948986</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003830754320851901</v>
+        <v>0.003819665904194805</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156001534308347</v>
+        <v>1.156017170083121</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494076061193973</v>
+        <v>1.494095561908901</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089260135958888</v>
+        <v>0.5089205067348027</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07452641690160355</v>
+        <v>0.07450225813919054</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050807481693256</v>
+        <v>0.5050772935253243</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.587080726797089</v>
+        <v>5.580042626193423</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.661387335947123</v>
+        <v>5.645753574640366</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.781175572173638</v>
+        <v>5.725406647807638</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116646762869628</v>
+        <v>8.116605411480007</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2362896994040279</v>
+        <v>0.2362483480144065</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445268120811674</v>
+        <v>1.445287819224454</v>
       </c>
       <c r="U8" t="n">
-        <v>1.824992434995467</v>
+        <v>1.82500663931063</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087139603448765</v>
+        <v>0.8087133288419879</v>
       </c>
       <c r="W8" t="n">
-        <v>0.628878081842535</v>
+        <v>0.6288723047739805</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990586117174976</v>
+        <v>0.7990653628094071</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.367401051130217</v>
+        <v>5.308520088841414</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.421945681699152</v>
+        <v>5.404077726668723</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.474953001560999</v>
+        <v>5.435984023586827</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5101804670912952</v>
+        <v>0.5099398868458275</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679634243348593</v>
+        <v>7.679572757630008</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06368344259834056</v>
+        <v>0.06362195687975497</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477315459949943</v>
+        <v>1.477319056213269</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919722268666838</v>
+        <v>1.919724143368125</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617099232574848</v>
+        <v>0.7617155481477431</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361066398207484</v>
+        <v>0.5361057337918731</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597427995522884</v>
+        <v>0.7597524265201956</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.672452229299362</v>
+        <v>5.626403080402034</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.828319553284036</v>
+        <v>5.803181426319687</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.906008492569003</v>
+        <v>5.910332390381895</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61927039093353</v>
+        <v>10.61918486553082</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.314210851195768</v>
+        <v>0.3141253257930637</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051670344667273</v>
+        <v>2.051690671286011</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697333640128392</v>
+        <v>2.697349719545359</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566383927661269</v>
+        <v>0.356648730843015</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198013625895358</v>
+        <v>-0.1198147134086029</v>
       </c>
       <c r="X10" t="n">
-        <v>0.335877795596792</v>
+        <v>0.3358980519383509</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.633288575716575</v>
+        <v>9.68558869739025</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.882352293455702</v>
+        <v>9.849120578148129</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.11406970830538</v>
+        <v>10.08054972965162</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218331379128025</v>
+        <v>5.218311132777632</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02754506077634401</v>
+        <v>-0.02756530712673708</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157915399512265</v>
+        <v>1.157928698458719</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476866497194637</v>
+        <v>1.47688747097498</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294656913248853</v>
+        <v>0.4294652007761488</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08246191999048902</v>
+        <v>-0.08249266546381961</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268660862015664</v>
+        <v>0.4268682455718533</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.332850583372386</v>
+        <v>4.369999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.512526257851787</v>
+        <v>4.482164080268619</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.675318471337579</v>
+        <v>4.557407907920308</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664317696120657</v>
+        <v>7.664284248396989</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725505279575896</v>
+        <v>0.1725170802339213</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149406101245448</v>
+        <v>0.9149272023707614</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198034327553449</v>
+        <v>1.198032795280875</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296193731717479</v>
+        <v>0.8296227994500958</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543226125377171</v>
+        <v>0.6543234967722158</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279372312510067</v>
+        <v>0.8279422626569213</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.035011639175089</v>
+        <v>5.033967837253909</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.326315713151743</v>
+        <v>5.302580169062682</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.611008533419266</v>
+        <v>5.611396288190514</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860803255484784</v>
+        <v>2.86063649222065</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.0306395278058</v>
+        <v>10.03046531125368</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4137647537288608</v>
+        <v>0.4135905371767377</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694104237941933</v>
+        <v>1.694074446582166</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153794457611741</v>
+        <v>2.153753874062719</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231918560539556</v>
+        <v>0.8232011309000814</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648545888109283</v>
+        <v>0.6485591327536349</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8113377358006452</v>
+        <v>0.8113664539696223</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.163747163042682</v>
+        <v>6.154234007182665</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.857461520350813</v>
+        <v>6.735242265623343</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.360279839096015</v>
+        <v>7.327515458530251</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.20302998288969</v>
+        <v>8.202877772546854</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06914637539841285</v>
+        <v>0.06899416505557766</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759292885467599</v>
+        <v>1.759202914525183</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284759398638941</v>
+        <v>2.284677995813784</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807744681092741</v>
+        <v>0.7807992265255167</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5650323494331203</v>
+        <v>0.5650633434755278</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804235439792748</v>
+        <v>0.7804509235689823</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.011873642634637</v>
+        <v>5.963788204067809</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.076721070911233</v>
+        <v>6.051898649677002</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.1532160176047</v>
+        <v>6.112559034599331</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82458985440803</v>
+        <v>11.82448898562392</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1392920429782252</v>
+        <v>-0.1393929117623309</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052448501555933</v>
+        <v>2.052430868257724</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697809015420801</v>
+        <v>2.69777826558255</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948284085587265</v>
+        <v>0.7948381538304415</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095477680922921</v>
+        <v>0.6095566688517474</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860037870806665</v>
+        <v>0.7860202617056544</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.733432008022392</v>
+        <v>7.729515382507109</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.943626434673466</v>
+        <v>7.910886338309195</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.187751646653904</v>
+        <v>8.150128938749388</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662770112366003</v>
+        <v>8.662697511922218</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2544998356646622</v>
+        <v>0.2544272352208797</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538143818998976</v>
+        <v>3.538190481873933</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06322305378657</v>
+        <v>11.0632358976108</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953742241237644</v>
+        <v>0.04953552113426687</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971379544996613</v>
+        <v>-0.5971416628893353</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0327826410348695</v>
+        <v>0.03278116794409502</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.77844141784804</v>
+        <v>10.81216528162287</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.546227253908</v>
+        <v>11.68970394844909</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.11416249488671</v>
+        <v>12.18842995769197</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910933462523443</v>
+        <v>6.910961788215769</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3712675050766349</v>
+        <v>0.3712958307689606</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032066986465126</v>
+        <v>2.032109384967555</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566330639233826</v>
+        <v>2.566362614490889</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210212512563162</v>
+        <v>0.5210102431759985</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02248449825484333</v>
+        <v>0.02246013934824453</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176675989423487</v>
+        <v>0.5176561560319961</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.958455424845097</v>
+        <v>4.28766390762083</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.803791040067241</v>
+        <v>5.156164834735483</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.283671804970647</v>
+        <v>6.056735432296174</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693145188716639</v>
+        <v>6.693126311018241</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1953842039861926</v>
+        <v>0.1953653262877952</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099774890939513</v>
+        <v>1.099795104097261</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489259742847926</v>
+        <v>1.489278381912625</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009257812746559</v>
+        <v>0.6009222808479047</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174562687861262</v>
+        <v>0.2174366805650891</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979697657972877</v>
+        <v>0.5979685463435229</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.174327042466015</v>
+        <v>4.708204446714913</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.059021555916143</v>
+        <v>6.055438926327406</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.22</v>
+        <v>6.584541239781075</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16665</v>
+        <v>16666</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15349453652766</v>
+        <v>11.15336597621786</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7841751172899144</v>
+        <v>0.7840465569801075</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038105355915333</v>
+        <v>2.038109684962841</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757637192759483</v>
+        <v>2.757647197248168</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263514654585723</v>
+        <v>0.7263477097295203</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693695539764513</v>
+        <v>0.4693657037992508</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789406443991768</v>
+        <v>0.6789621190938815</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.771650136097461</v>
+        <v>7.729354988526294</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.845778410060757</v>
+        <v>7.867024025038724</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.892677663167563</v>
+        <v>7.954411710944682</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.771650136097461</v>
+        <v>7.729354988526294</v>
       </c>
       <c r="G2" t="n">
-        <v>7.845778410060757</v>
+        <v>7.867024025038724</v>
       </c>
       <c r="H2" t="n">
-        <v>7.892677663167563</v>
+        <v>7.954411710944682</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.587080726797089</v>
+        <v>5.580042626193423</v>
       </c>
       <c r="G3" t="n">
-        <v>5.661387335947123</v>
+        <v>5.645753574640367</v>
       </c>
       <c r="H3" t="n">
-        <v>5.781175572173638</v>
+        <v>5.725406647807638</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.332850583372386</v>
+        <v>4.369999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>4.512526257851787</v>
+        <v>4.482164080268619</v>
       </c>
       <c r="H4" t="n">
-        <v>4.675318471337579</v>
+        <v>4.557407907920308</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.77844141784804</v>
+        <v>10.81216528162287</v>
       </c>
       <c r="G5" t="n">
-        <v>11.546227253908</v>
+        <v>11.68970394844909</v>
       </c>
       <c r="H5" t="n">
-        <v>12.11416249488671</v>
+        <v>12.18842995769197</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.62569296474383</v>
+        <v>54.6211168347924</v>
       </c>
       <c r="G6" t="n">
-        <v>87.22371712332644</v>
+        <v>85.76752254840012</v>
       </c>
       <c r="H6" t="n">
-        <v>112.9620603674578</v>
+        <v>112.0442451555832</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.733432008022392</v>
+        <v>7.729515382507109</v>
       </c>
       <c r="G7" t="n">
-        <v>7.943626434673466</v>
+        <v>7.910886338309195</v>
       </c>
       <c r="H7" t="n">
-        <v>8.187751646653904</v>
+        <v>8.150128938749388</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.163747163042682</v>
+        <v>6.154234007182665</v>
       </c>
       <c r="G8" t="n">
-        <v>6.857461520350813</v>
+        <v>6.735242265623343</v>
       </c>
       <c r="H8" t="n">
-        <v>7.360279839096015</v>
+        <v>7.327515458530251</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.035011639175089</v>
+        <v>5.033967837253909</v>
       </c>
       <c r="G9" t="n">
-        <v>5.326315713151743</v>
+        <v>5.302580169062683</v>
       </c>
       <c r="H9" t="n">
-        <v>5.611008533419266</v>
+        <v>5.611396288190514</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.367401051130217</v>
+        <v>5.308520088841414</v>
       </c>
       <c r="G10" t="n">
-        <v>5.421945681699153</v>
+        <v>5.404077726668723</v>
       </c>
       <c r="H10" t="n">
-        <v>5.474953001560999</v>
+        <v>5.435984023586827</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.958455424845097</v>
+        <v>4.28766390762083</v>
       </c>
       <c r="G11" t="n">
-        <v>4.803791040067241</v>
+        <v>5.156164834735483</v>
       </c>
       <c r="H11" t="n">
-        <v>7.283671804970647</v>
+        <v>6.056735432296174</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>6.011873642634637</v>
+        <v>5.963788204067809</v>
       </c>
       <c r="G12" t="n">
-        <v>6.076721070911234</v>
+        <v>6.051898649677002</v>
       </c>
       <c r="H12" t="n">
-        <v>6.1532160176047</v>
+        <v>6.112559034599331</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.633288575716575</v>
+        <v>9.68558869739025</v>
       </c>
       <c r="G13" t="n">
-        <v>9.882352293455702</v>
+        <v>9.849120578148131</v>
       </c>
       <c r="H13" t="n">
-        <v>10.11406970830538</v>
+        <v>10.08054972965162</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.672452229299362</v>
+        <v>5.626403080402034</v>
       </c>
       <c r="G14" t="n">
-        <v>5.828319553284036</v>
+        <v>5.803181426319687</v>
       </c>
       <c r="H14" t="n">
-        <v>5.906008492569003</v>
+        <v>5.910332390381895</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.549286981907136</v>
+        <v>6.562428071882835</v>
       </c>
       <c r="G15" t="n">
-        <v>6.577303226727951</v>
+        <v>6.577111201101031</v>
       </c>
       <c r="H15" t="n">
-        <v>6.591012967761306</v>
+        <v>6.585592054787766</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>5.174327042466015</v>
+        <v>4.708204446714913</v>
       </c>
       <c r="G16" t="n">
-        <v>6.059021555916142</v>
+        <v>6.055438926327406</v>
       </c>
       <c r="H16" t="n">
-        <v>7.22</v>
+        <v>6.584541239781075</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.949126857749469</v>
+        <v>3.924611032531824</v>
       </c>
       <c r="G17" t="n">
-        <v>4.369244355332713</v>
+        <v>4.336353622841808</v>
       </c>
       <c r="H17" t="n">
-        <v>4.82</v>
+        <v>4.674070014144272</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.558124289023677</v>
+        <v>2.49939179632249</v>
       </c>
       <c r="G18" t="n">
-        <v>2.635473535025278</v>
+        <v>2.615070257508525</v>
       </c>
       <c r="H18" t="n">
-        <v>2.807707006369427</v>
+        <v>2.70833388801065</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.805694305791429</v>
+        <v>5.799377725132942</v>
       </c>
       <c r="G19" t="n">
-        <v>5.906710058175214</v>
+        <v>5.898489830491288</v>
       </c>
       <c r="H19" t="n">
-        <v>6.098719150900536</v>
+        <v>6.037284797416499</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8604235098902</v>
+        <v>102.8626731375705</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.007794474934513867</v>
+        <v>0.01004410261477891</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80313532873799</v>
+        <v>17.80104504415612</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18651296297458</v>
+        <v>36.18460795661986</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285918721585763</v>
+        <v>0.1286124849884109</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7372293080124681</v>
+        <v>-0.7370464030852255</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285859504189382</v>
+        <v>0.1286062559577337</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.6211168347924</v>
+        <v>59.15329113902406</v>
       </c>
       <c r="Z2" t="n">
-        <v>85.76752254840014</v>
+        <v>94.63006987497236</v>
       </c>
       <c r="AA2" t="n">
-        <v>112.0442451555832</v>
+        <v>113.9922968697009</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959452540619178</v>
+        <v>4.959414558407012</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05344112697781393</v>
+        <v>0.05340314476564753</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350482254526217</v>
+        <v>1.350478239481448</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725312076525368</v>
+        <v>1.725315031223425</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795307713581335</v>
+        <v>0.7795340247619683</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664742354899457</v>
+        <v>0.5664727506121104</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784851523225209</v>
+        <v>0.7784905229666079</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.49939179632249</v>
+        <v>2.445638402716431</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.615070257508525</v>
+        <v>2.573441394380306</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.70833388801065</v>
+        <v>2.674946996466431</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3659865629420084</v>
+        <v>0.3658727915194346</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246481300766394</v>
+        <v>7.246419724230914</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3285070195225063</v>
+        <v>0.3284454429870255</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2938262951701</v>
+        <v>1.293828636347027</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683871373714836</v>
+        <v>1.683865967803498</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867453818463486</v>
+        <v>0.8674550862785382</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371017804510211</v>
+        <v>0.7371034684685346</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472349186718949</v>
+        <v>0.8472505590454078</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.924611032531824</v>
+        <v>3.885847948183525</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.336353622841807</v>
+        <v>4.259021248369841</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.674070014144272</v>
+        <v>4.608136734623455</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313339530333712</v>
+        <v>9.313311967805086</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3585514262444932</v>
+        <v>0.3585238637158676</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254681991420696</v>
+        <v>1.254675260826265</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747764142109944</v>
+        <v>1.747755013349622</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674962812237701</v>
+        <v>0.8674999156413288</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234783782255255</v>
+        <v>0.7234812668223972</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615779269320812</v>
+        <v>0.861582373055551</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.799377725132942</v>
+        <v>5.770565592144677</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.898489830491287</v>
+        <v>5.890562408202157</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.037284797416499</v>
+        <v>6.096317273560557</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018769831030919</v>
+        <v>7.018788765136435</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2879522458775874</v>
+        <v>0.2879711799831019</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482092500162924</v>
+        <v>1.482110948195825</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91068208991177</v>
+        <v>1.910703090798069</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047713073023302</v>
+        <v>0.304774103918983</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1981743488938481</v>
+        <v>-0.1982006880338718</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801802888629902</v>
+        <v>0.2801895345584406</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.562428071882835</v>
+        <v>6.562038913174199</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.577111201101031</v>
+        <v>6.582828210824509</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.585592054787766</v>
+        <v>6.625611176808722</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586391501948986</v>
+        <v>5.586383504344056</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003819665904194805</v>
+        <v>0.0038116682992639</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156017170083121</v>
+        <v>1.15603431439665</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494095561908901</v>
+        <v>1.49411629164892</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089205067348027</v>
+        <v>0.5089142323993999</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07450225813919054</v>
+        <v>0.07447657643427319</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050772935253243</v>
+        <v>0.505073086407575</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.580042626193423</v>
+        <v>5.577490031721812</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.645753574640366</v>
+        <v>5.633272734415386</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.725406647807638</v>
+        <v>5.692228377594965</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116605411480007</v>
+        <v>8.116567762894622</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2362483480144065</v>
+        <v>0.2362106994290235</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445287819224454</v>
+        <v>1.445305240844807</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82500663931063</v>
+        <v>1.825018084678882</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087133288419879</v>
+        <v>0.8087132104481943</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288723047739805</v>
+        <v>0.6288676497701375</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990653628094071</v>
+        <v>0.7990721919306918</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.308520088841414</v>
+        <v>5.216193172871638</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.404077726668723</v>
+        <v>5.377940056339471</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.435984023586827</v>
+        <v>5.436575579777574</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5099398868458275</v>
+        <v>0.5096996466431095</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679572757630008</v>
+        <v>7.679516632445966</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06362195687975497</v>
+        <v>0.06356583169571436</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477319056213269</v>
+        <v>1.477321981550402</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919724143368125</v>
+        <v>1.91972708473116</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617155481477431</v>
+        <v>0.7617206614827138</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361057337918731</v>
+        <v>0.5361043122517035</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597524265201956</v>
+        <v>0.7597613517118305</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.626403080402034</v>
+        <v>5.566335733215547</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.803181426319687</v>
+        <v>5.778244459316131</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.910332390381895</v>
+        <v>5.911660777385159</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61918486553082</v>
+        <v>10.61910249816041</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3141253257930637</v>
+        <v>0.3140429584226542</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051690671286011</v>
+        <v>2.051710628299085</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697349719545359</v>
+        <v>2.697365581625455</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356648730843015</v>
+        <v>0.3566591942143267</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198147134086029</v>
+        <v>-0.1198278838497779</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3358980519383509</v>
+        <v>0.3359183427675683</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.68558869739025</v>
+        <v>9.602034854573828</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.849120578148129</v>
+        <v>9.788038175830513</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.08054972965162</v>
+        <v>9.975761191788486</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218311132777632</v>
+        <v>5.218292671141351</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02756530712673708</v>
+        <v>-0.02758376876301671</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157928698458719</v>
+        <v>1.157943984260399</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47688747097498</v>
+        <v>1.476909630513449</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294652007761488</v>
+        <v>0.4294636090702663</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08249266546381961</v>
+        <v>-0.08252514961483426</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268682455718533</v>
+        <v>0.4268692832236881</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.369999999999999</v>
+        <v>4.25103981836958</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.482164080268619</v>
+        <v>4.434844109961792</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.557407907920308</v>
+        <v>4.546789015789727</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664284248396989</v>
+        <v>7.66424036056941</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1725170802339213</v>
+        <v>0.172473192406342</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149272023707614</v>
+        <v>0.9149116264879299</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198032795280875</v>
+        <v>1.198026728284773</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296227994500958</v>
+        <v>0.8296280197515591</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543234967722158</v>
+        <v>0.6543269978661688</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279422626569213</v>
+        <v>0.8279494683846561</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.033967837253909</v>
+        <v>5.032605399587728</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.302580169062682</v>
+        <v>5.240346643344685</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.611396288190514</v>
+        <v>5.611013922807209</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.86063649222065</v>
+        <v>2.860469964664311</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03046531125368</v>
+        <v>10.0302962618014</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4135905371767377</v>
+        <v>0.413421487724454</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694074446582166</v>
+        <v>1.694044205614099</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153753874062719</v>
+        <v>2.153711723113596</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232011309000814</v>
+        <v>0.8232106309089449</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485591327536349</v>
+        <v>0.6485728886626418</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8113664539696223</v>
+        <v>0.8113948118407692</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.154234007182665</v>
+        <v>6.150227283749368</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.735242265623343</v>
+        <v>6.608103221547571</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.327515458530251</v>
+        <v>7.244511649513971</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202877772546854</v>
+        <v>8.202727396985219</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06899416505557766</v>
+        <v>0.06884378949394312</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759202914525183</v>
+        <v>1.759115899559259</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284677995813784</v>
+        <v>2.284596852622398</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807992265255167</v>
+        <v>0.7808238774583075</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5650633434755278</v>
+        <v>0.5650942375636254</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804509235689823</v>
+        <v>0.780478162687384</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.963788204067809</v>
+        <v>5.92951531100154</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.051898649677002</v>
+        <v>6.026715885091707</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.112559034599331</v>
+        <v>6.095943210458485</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82448898562392</v>
+        <v>11.82438925140955</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1393929117623309</v>
+        <v>-0.1394926459767021</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052430868257724</v>
+        <v>2.052409119142188</v>
       </c>
       <c r="U15" t="n">
-        <v>2.69777826558255</v>
+        <v>2.697746480503629</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948381538304415</v>
+        <v>0.794848032057815</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095566688517474</v>
+        <v>0.6095658691623472</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860202617056544</v>
+        <v>0.7860368334161398</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.729515382507109</v>
+        <v>7.724868627217198</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.910886338309195</v>
+        <v>7.899087521053116</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.150128938749388</v>
+        <v>8.092488420348159</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662697511922218</v>
+        <v>8.662622176386311</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2544272352208797</v>
+        <v>0.2543518996849722</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538190481873933</v>
+        <v>3.538233641107893</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0632358976108</v>
+        <v>11.06324782636034</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953552113426687</v>
+        <v>0.04953365609710188</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971416628893353</v>
+        <v>-0.5971451070738962</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03278116794409502</v>
+        <v>0.03277971854637041</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.81216528162287</v>
+        <v>11.10305899370715</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.68970394844909</v>
+        <v>11.80949604350149</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.18842995769197</v>
+        <v>12.21240887027493</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910961788215769</v>
+        <v>6.910968621349413</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3712958307689606</v>
+        <v>0.3713026639026053</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032109384967555</v>
+        <v>2.03214403690267</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566362614490889</v>
+        <v>2.566392276452262</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210102431759985</v>
+        <v>0.5210032477769038</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02246013934824453</v>
+        <v>0.02243754245021479</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176561560319961</v>
+        <v>0.5176491022774596</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.28766390762083</v>
+        <v>3.954316431543088</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.156164834735483</v>
+        <v>5.701936497898343</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.056735432296174</v>
+        <v>8.186110966791093</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693126311018241</v>
+        <v>6.693084750297616</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1953653262877952</v>
+        <v>0.1953237655671707</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099795104097261</v>
+        <v>1.099805271309135</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489278381912625</v>
+        <v>1.489288079088407</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009222808479047</v>
+        <v>0.6009247798134625</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174366805650891</v>
+        <v>0.2174264894834661</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979685463435229</v>
+        <v>0.5979742359427269</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.708204446714913</v>
+        <v>5.188578728584537</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.055438926327406</v>
+        <v>6.306621437175205</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.584541239781075</v>
+        <v>7.076742149080221</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16666</v>
+        <v>16667</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15336597621786</v>
+        <v>11.15323609699889</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7840465569801075</v>
+        <v>0.7839166777611436</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038109684962841</v>
+        <v>2.038112259630836</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757647197248168</v>
+        <v>2.757654069042213</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263477097295203</v>
+        <v>0.726344652606582</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693657037992508</v>
+        <v>0.4693630592157499</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789621190938815</v>
+        <v>0.6789844381084614</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.729354988526294</v>
+        <v>7.731242699080854</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.867024025038724</v>
+        <v>7.83898229609985</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.954411710944682</v>
+        <v>7.916708773434299</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.729354988526294</v>
+        <v>7.731242699080854</v>
       </c>
       <c r="G2" t="n">
-        <v>7.867024025038724</v>
+        <v>7.838982296099852</v>
       </c>
       <c r="H2" t="n">
-        <v>7.954411710944682</v>
+        <v>7.916708773434299</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.580042626193423</v>
+        <v>5.577490031721812</v>
       </c>
       <c r="G3" t="n">
-        <v>5.645753574640367</v>
+        <v>5.633272734415387</v>
       </c>
       <c r="H3" t="n">
-        <v>5.725406647807638</v>
+        <v>5.692228377594965</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.369999999999999</v>
+        <v>4.25103981836958</v>
       </c>
       <c r="G4" t="n">
-        <v>4.482164080268619</v>
+        <v>4.434844109961792</v>
       </c>
       <c r="H4" t="n">
-        <v>4.557407907920308</v>
+        <v>4.546789015789727</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81216528162287</v>
+        <v>11.10305899370715</v>
       </c>
       <c r="G5" t="n">
-        <v>11.68970394844909</v>
+        <v>11.80949604350149</v>
       </c>
       <c r="H5" t="n">
-        <v>12.18842995769197</v>
+        <v>12.21240887027493</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.6211168347924</v>
+        <v>59.15329113902406</v>
       </c>
       <c r="G6" t="n">
-        <v>85.76752254840012</v>
+        <v>94.63006987497235</v>
       </c>
       <c r="H6" t="n">
-        <v>112.0442451555832</v>
+        <v>113.9922968697009</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.729515382507109</v>
+        <v>7.724868627217198</v>
       </c>
       <c r="G7" t="n">
-        <v>7.910886338309195</v>
+        <v>7.899087521053116</v>
       </c>
       <c r="H7" t="n">
-        <v>8.150128938749388</v>
+        <v>8.092488420348159</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.154234007182665</v>
+        <v>6.150227283749368</v>
       </c>
       <c r="G8" t="n">
-        <v>6.735242265623343</v>
+        <v>6.608103221547571</v>
       </c>
       <c r="H8" t="n">
-        <v>7.327515458530251</v>
+        <v>7.244511649513971</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.033967837253909</v>
+        <v>5.032605399587728</v>
       </c>
       <c r="G9" t="n">
-        <v>5.302580169062683</v>
+        <v>5.240346643344685</v>
       </c>
       <c r="H9" t="n">
-        <v>5.611396288190514</v>
+        <v>5.611013922807209</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.308520088841414</v>
+        <v>5.216193172871638</v>
       </c>
       <c r="G10" t="n">
-        <v>5.404077726668723</v>
+        <v>5.377940056339471</v>
       </c>
       <c r="H10" t="n">
-        <v>5.435984023586827</v>
+        <v>5.436575579777574</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>4.28766390762083</v>
+        <v>3.954316431543088</v>
       </c>
       <c r="G11" t="n">
-        <v>5.156164834735483</v>
+        <v>5.701936497898343</v>
       </c>
       <c r="H11" t="n">
-        <v>6.056735432296174</v>
+        <v>8.186110966791093</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.963788204067809</v>
+        <v>5.92951531100154</v>
       </c>
       <c r="G12" t="n">
-        <v>6.051898649677002</v>
+        <v>6.026715885091706</v>
       </c>
       <c r="H12" t="n">
-        <v>6.112559034599331</v>
+        <v>6.095943210458485</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.68558869739025</v>
+        <v>9.602034854573828</v>
       </c>
       <c r="G13" t="n">
-        <v>9.849120578148131</v>
+        <v>9.788038175830515</v>
       </c>
       <c r="H13" t="n">
-        <v>10.08054972965162</v>
+        <v>9.975761191788486</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.626403080402034</v>
+        <v>5.566335733215547</v>
       </c>
       <c r="G14" t="n">
-        <v>5.803181426319687</v>
+        <v>5.778244459316132</v>
       </c>
       <c r="H14" t="n">
-        <v>5.910332390381895</v>
+        <v>5.911660777385159</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.562428071882835</v>
+        <v>6.562038913174199</v>
       </c>
       <c r="G15" t="n">
-        <v>6.577111201101031</v>
+        <v>6.582828210824509</v>
       </c>
       <c r="H15" t="n">
-        <v>6.585592054787766</v>
+        <v>6.625611176808722</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.708204446714913</v>
+        <v>5.188578728584537</v>
       </c>
       <c r="G16" t="n">
-        <v>6.055438926327406</v>
+        <v>6.306621437175205</v>
       </c>
       <c r="H16" t="n">
-        <v>6.584541239781075</v>
+        <v>7.076742149080221</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.924611032531824</v>
+        <v>3.885847948183525</v>
       </c>
       <c r="G17" t="n">
-        <v>4.336353622841808</v>
+        <v>4.259021248369841</v>
       </c>
       <c r="H17" t="n">
-        <v>4.674070014144272</v>
+        <v>4.608136734623455</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.49939179632249</v>
+        <v>2.445638402716431</v>
       </c>
       <c r="G18" t="n">
-        <v>2.615070257508525</v>
+        <v>2.573441394380306</v>
       </c>
       <c r="H18" t="n">
-        <v>2.70833388801065</v>
+        <v>2.674946996466431</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.799377725132942</v>
+        <v>5.770565592144677</v>
       </c>
       <c r="G19" t="n">
-        <v>5.898489830491288</v>
+        <v>5.890562408202157</v>
       </c>
       <c r="H19" t="n">
-        <v>6.037284797416499</v>
+        <v>6.096317273560557</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8626731375705</v>
+        <v>102.8669468962853</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01004410261477891</v>
+        <v>0.01431786132962335</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80104504415612</v>
+        <v>17.80040204691646</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18460795661986</v>
+        <v>36.18461621153075</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1286124849884109</v>
+        <v>0.1285254938479626</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7370464030852255</v>
+        <v>-0.7370471956412721</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1286062559577337</v>
+        <v>0.1285188781037331</v>
       </c>
       <c r="Y2" t="n">
-        <v>59.15329113902406</v>
+        <v>59.1602037164707</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.63006987497236</v>
+        <v>95.61718641982159</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.9922968697009</v>
+        <v>113.3027921830776</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959414558407012</v>
+        <v>4.959380882197909</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05340314476564753</v>
+        <v>0.05336946855654458</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350478239481448</v>
+        <v>1.350472705801517</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725315031223425</v>
+        <v>1.725316641757152</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795340247619683</v>
+        <v>0.7795373621563021</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664727506121104</v>
+        <v>0.5664719412404073</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784905229666079</v>
+        <v>0.7784958123514411</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.445638402716431</v>
+        <v>2.404726292081958</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.573441394380306</v>
+        <v>2.542080559915212</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.674946996466431</v>
+        <v>2.637662919039107</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3658727915194346</v>
+        <v>0.3657591807909604</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246419724230914</v>
+        <v>7.246358825111003</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3284454429870255</v>
+        <v>0.3283845438671155</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293828636347027</v>
+        <v>1.293830994080791</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683865967803498</v>
+        <v>1.683859271713745</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674550862785382</v>
+        <v>0.8674565951873591</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371034684685346</v>
+        <v>0.7371055593419229</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472505590454078</v>
+        <v>0.8472663921158866</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.885847948183525</v>
+        <v>3.788238877118644</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.259021248369841</v>
+        <v>4.184923864370847</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.608136734623455</v>
+        <v>4.548066737288136</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313311967805086</v>
+        <v>9.31328662060799</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3585238637158676</v>
+        <v>0.35849851651877</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254675260826265</v>
+        <v>1.254671419729082</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747755013349622</v>
+        <v>1.747751586395628</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8674999156413288</v>
+        <v>0.8675026723642005</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234812668223972</v>
+        <v>0.723482351203264</v>
       </c>
       <c r="X5" t="n">
-        <v>0.861582373055551</v>
+        <v>0.8615859023959636</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.770565592144677</v>
+        <v>5.614457307563012</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.890562408202157</v>
+        <v>5.847701679382401</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.096317273560557</v>
+        <v>5.929703372340327</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018788765136435</v>
+        <v>7.018807810203534</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2879711799831019</v>
+        <v>0.2879902250502017</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482110948195825</v>
+        <v>1.48213012356042</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910703090798069</v>
+        <v>1.910724681539229</v>
       </c>
       <c r="V6" t="n">
-        <v>0.304774103918983</v>
+        <v>0.3047764173196704</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1982006880338718</v>
+        <v>-0.1982277672668533</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801895345584406</v>
+        <v>0.2801982936928722</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.562038913174199</v>
+        <v>6.560677410666935</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.582828210824509</v>
+        <v>6.576679982278089</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.625611176808722</v>
+        <v>6.586425173197223</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586383504344056</v>
+        <v>5.586377773661895</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0038116682992639</v>
+        <v>0.003805937617103257</v>
       </c>
       <c r="T7" t="n">
-        <v>1.15603431439665</v>
+        <v>1.15605537694032</v>
       </c>
       <c r="U7" t="n">
-        <v>1.49411629164892</v>
+        <v>1.494140080483892</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089142323993999</v>
+        <v>0.5089060516203086</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07447657643427319</v>
+        <v>0.0744471044321493</v>
       </c>
       <c r="X7" t="n">
-        <v>0.505073086407575</v>
+        <v>0.5050670159889633</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.577490031721812</v>
+        <v>5.573696994775617</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.633272734415386</v>
+        <v>5.616595363340542</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.692228377594965</v>
+        <v>5.667581885386322</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116567762894622</v>
+        <v>8.116533923412588</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2362106994290235</v>
+        <v>0.2361768599469871</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445305240844807</v>
+        <v>1.445320209664826</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825018084678882</v>
+        <v>1.825030665135193</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087132104481943</v>
+        <v>0.8087127679795122</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288676497701375</v>
+        <v>0.6288625330751858</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990721919306918</v>
+        <v>0.7990782946875183</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.216193172871638</v>
+        <v>5.149996103074825</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.377940056339471</v>
+        <v>5.351291958272722</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.436575579777574</v>
+        <v>5.437681746134257</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5096996466431095</v>
+        <v>0.5094597457627119</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679516632445966</v>
+        <v>7.679458743258412</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06356583169571436</v>
+        <v>0.06350794250815939</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477321981550402</v>
+        <v>1.477326882824285</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91972708473116</v>
+        <v>1.919733229498319</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617206614827138</v>
+        <v>0.761725100596564</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361043122517035</v>
+        <v>0.536101342521712</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597613517118305</v>
+        <v>0.7597696905661706</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.566335733215547</v>
+        <v>5.488812165878286</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.778244459316131</v>
+        <v>5.746371008424085</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.911660777385159</v>
+        <v>5.912987288135594</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61910249816041</v>
+        <v>10.61902686422934</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3140429584226542</v>
+        <v>0.3139673244915815</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051710628299085</v>
+        <v>2.05173033507391</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697365581625455</v>
+        <v>2.697382785250898</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566591942143267</v>
+        <v>0.3566686956166933</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198278838497779</v>
+        <v>-0.119842168276806</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3359183427675683</v>
+        <v>0.3359373779150524</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.602034854573828</v>
+        <v>9.563639405068569</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.788038175830513</v>
+        <v>9.750300605541238</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.975761191788486</v>
+        <v>9.92144627091257</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218292671141351</v>
+        <v>5.218275752279708</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02758376876301671</v>
+        <v>-0.0276006876246604</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157943984260399</v>
+        <v>1.157960185407619</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476909630513449</v>
+        <v>1.476932089273641</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294636090702663</v>
+        <v>0.4294615126768789</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08252514961483426</v>
+        <v>-0.08255807289881534</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268692832236881</v>
+        <v>0.4268697762506228</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.25103981836958</v>
+        <v>4.154432796557327</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.434844109961792</v>
+        <v>4.427582737704282</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.546789015789727</v>
+        <v>4.797384494415111</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.66424036056941</v>
+        <v>7.664193247287486</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.172473192406342</v>
+        <v>0.1724260791244171</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9149116264879299</v>
+        <v>0.9148999161425344</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198026728284773</v>
+        <v>1.198022286783129</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296280197515591</v>
+        <v>0.8296329148214996</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543269978661688</v>
+        <v>0.6543295609214409</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279494683846561</v>
+        <v>0.8279564694872861</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.032605399587728</v>
+        <v>5.034532623153825</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.240346643344685</v>
+        <v>5.192368964375194</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.611013922807209</v>
+        <v>5.550960540067943</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860469964664311</v>
+        <v>2.860303672316384</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.0302962618014</v>
+        <v>10.03013429144608</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.413421487724454</v>
+        <v>0.4132595173691374</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694044205614099</v>
+        <v>1.694019717705846</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153711723113596</v>
+        <v>2.153673840596019</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232106309089449</v>
+        <v>0.8232194322277044</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485728886626418</v>
+        <v>0.6485852513446999</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8113948118407692</v>
+        <v>0.8114219303052521</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.150227283749368</v>
+        <v>6.126291302171052</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.608103221547571</v>
+        <v>6.52557725334533</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.244511649513971</v>
+        <v>7.11716841692084</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202727396985219</v>
+        <v>8.202579011069618</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06884378949394312</v>
+        <v>0.06869540357834023</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759115899559259</v>
+        <v>1.759033930869108</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284596852622398</v>
+        <v>2.284521303399272</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808238774583075</v>
+        <v>0.7808474252303429</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5650942375636254</v>
+        <v>0.5651230008433941</v>
       </c>
       <c r="X14" t="n">
-        <v>0.780478162687384</v>
+        <v>0.7805042720926838</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.92951531100154</v>
+        <v>5.884379768443516</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.026715885091707</v>
+        <v>5.99374825715752</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.095943210458485</v>
+        <v>6.073030922426484</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82438925140955</v>
+        <v>11.82429545715865</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1394926459767021</v>
+        <v>-0.139586440227603</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052409119142188</v>
+        <v>2.0523892164171</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697746480503629</v>
+        <v>2.697716146641408</v>
       </c>
       <c r="V15" t="n">
-        <v>0.794848032057815</v>
+        <v>0.7948574545691808</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095658691623472</v>
+        <v>0.6095746493117293</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860368334161398</v>
+        <v>0.7860526577832085</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.724868627217198</v>
+        <v>7.719895529007967</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.899087521053116</v>
+        <v>7.901721955546057</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.092488420348159</v>
+        <v>8.140385739333723</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662622176386311</v>
+        <v>8.662524823865473</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2543518996849722</v>
+        <v>0.2542545471641329</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538233641107893</v>
+        <v>3.53826176801757</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06324782636034</v>
+        <v>11.0632571053243</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953365609710188</v>
+        <v>0.04953133232404149</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971451070738962</v>
+        <v>-0.5971477861891696</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03277971854637041</v>
+        <v>0.03277773790882765</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.10305899370715</v>
+        <v>11.5215816863368</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.80949604350149</v>
+        <v>11.92355797862959</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.21240887027493</v>
+        <v>12.28892202985687</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910968621349413</v>
+        <v>6.910943499886433</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3713026639026053</v>
+        <v>0.3712775424396254</v>
       </c>
       <c r="T17" t="n">
-        <v>2.03214403690267</v>
+        <v>2.032167613929715</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566392276452262</v>
+        <v>2.56641372743566</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210032477769038</v>
+        <v>0.5210028996312795</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02243754245021479</v>
+        <v>0.02242120062759012</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176491022774596</v>
+        <v>0.5176492455903716</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.954316431543088</v>
+        <v>3.596439240362792</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.701936497898343</v>
+        <v>5.456169733192485</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.186110966791093</v>
+        <v>6.939408583401979</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693084750297616</v>
+        <v>6.693016390828307</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1953237655671707</v>
+        <v>0.1952554060978611</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099805271309135</v>
+        <v>1.09979510453292</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489288079088407</v>
+        <v>1.489278325940251</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009247798134625</v>
+        <v>0.6009375315826112</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174264894834661</v>
+        <v>0.2174367393881094</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979742359427269</v>
+        <v>0.5979908004382368</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.188578728584537</v>
+        <v>4.385762957731743</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.306621437175205</v>
+        <v>6.080458732772944</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.076742149080221</v>
+        <v>6.887481600968441</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16667</v>
+        <v>16668</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15323609699889</v>
+        <v>11.15310549329118</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7839166777611436</v>
+        <v>0.783786074053428</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038112259630836</v>
+        <v>2.038115677337758</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757654069042213</v>
+        <v>2.757660684033706</v>
       </c>
       <c r="V19" t="n">
-        <v>0.726344652606582</v>
+        <v>0.7263416563099953</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693630592157499</v>
+        <v>0.4693605134554979</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789844381084614</v>
+        <v>0.6790069636250309</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.731242699080854</v>
+        <v>7.689067571876785</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.83898229609985</v>
+        <v>7.813841717093029</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.916708773434299</v>
+        <v>7.912109865642914</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.731242699080854</v>
+        <v>7.689067571876785</v>
       </c>
       <c r="G2" t="n">
-        <v>7.838982296099852</v>
+        <v>7.813841717093029</v>
       </c>
       <c r="H2" t="n">
-        <v>7.916708773434299</v>
+        <v>7.912109865642914</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.577490031721812</v>
+        <v>5.573696994775617</v>
       </c>
       <c r="G3" t="n">
-        <v>5.633272734415387</v>
+        <v>5.616595363340543</v>
       </c>
       <c r="H3" t="n">
-        <v>5.692228377594965</v>
+        <v>5.667581885386322</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.25103981836958</v>
+        <v>4.154432796557327</v>
       </c>
       <c r="G4" t="n">
-        <v>4.434844109961792</v>
+        <v>4.427582737704282</v>
       </c>
       <c r="H4" t="n">
-        <v>4.546789015789727</v>
+        <v>4.797384494415111</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.10305899370715</v>
+        <v>11.5215816863368</v>
       </c>
       <c r="G5" t="n">
-        <v>11.80949604350149</v>
+        <v>11.92355797862959</v>
       </c>
       <c r="H5" t="n">
-        <v>12.21240887027493</v>
+        <v>12.28892202985687</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>59.15329113902406</v>
+        <v>59.1602037164707</v>
       </c>
       <c r="G6" t="n">
-        <v>94.63006987497235</v>
+        <v>95.61718641982159</v>
       </c>
       <c r="H6" t="n">
-        <v>113.9922968697009</v>
+        <v>113.3027921830776</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.724868627217198</v>
+        <v>7.719895529007967</v>
       </c>
       <c r="G7" t="n">
-        <v>7.899087521053116</v>
+        <v>7.901721955546057</v>
       </c>
       <c r="H7" t="n">
-        <v>8.092488420348159</v>
+        <v>8.140385739333723</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.150227283749368</v>
+        <v>6.126291302171052</v>
       </c>
       <c r="G8" t="n">
-        <v>6.608103221547571</v>
+        <v>6.52557725334533</v>
       </c>
       <c r="H8" t="n">
-        <v>7.244511649513971</v>
+        <v>7.11716841692084</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.032605399587728</v>
+        <v>5.034532623153825</v>
       </c>
       <c r="G9" t="n">
-        <v>5.240346643344685</v>
+        <v>5.192368964375194</v>
       </c>
       <c r="H9" t="n">
-        <v>5.611013922807209</v>
+        <v>5.550960540067943</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.216193172871638</v>
+        <v>5.149996103074825</v>
       </c>
       <c r="G10" t="n">
-        <v>5.377940056339471</v>
+        <v>5.351291958272723</v>
       </c>
       <c r="H10" t="n">
-        <v>5.436575579777574</v>
+        <v>5.437681746134257</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.954316431543088</v>
+        <v>3.596439240362792</v>
       </c>
       <c r="G11" t="n">
-        <v>5.701936497898343</v>
+        <v>5.456169733192485</v>
       </c>
       <c r="H11" t="n">
-        <v>8.186110966791093</v>
+        <v>6.939408583401979</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.92951531100154</v>
+        <v>5.884379768443516</v>
       </c>
       <c r="G12" t="n">
-        <v>6.026715885091706</v>
+        <v>5.993748257157519</v>
       </c>
       <c r="H12" t="n">
-        <v>6.095943210458485</v>
+        <v>6.073030922426484</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.602034854573828</v>
+        <v>9.563639405068569</v>
       </c>
       <c r="G13" t="n">
-        <v>9.788038175830515</v>
+        <v>9.750300605541238</v>
       </c>
       <c r="H13" t="n">
-        <v>9.975761191788486</v>
+        <v>9.92144627091257</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.566335733215547</v>
+        <v>5.488812165878286</v>
       </c>
       <c r="G14" t="n">
-        <v>5.778244459316132</v>
+        <v>5.746371008424085</v>
       </c>
       <c r="H14" t="n">
-        <v>5.911660777385159</v>
+        <v>5.912987288135594</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.562038913174199</v>
+        <v>6.560677410666935</v>
       </c>
       <c r="G15" t="n">
-        <v>6.582828210824509</v>
+        <v>6.576679982278089</v>
       </c>
       <c r="H15" t="n">
-        <v>6.625611176808722</v>
+        <v>6.586425173197223</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>5.188578728584537</v>
+        <v>4.385762957731743</v>
       </c>
       <c r="G16" t="n">
-        <v>6.306621437175205</v>
+        <v>6.080458732772943</v>
       </c>
       <c r="H16" t="n">
-        <v>7.076742149080221</v>
+        <v>6.887481600968441</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.885847948183525</v>
+        <v>3.788238877118644</v>
       </c>
       <c r="G17" t="n">
-        <v>4.259021248369841</v>
+        <v>4.184923864370848</v>
       </c>
       <c r="H17" t="n">
-        <v>4.608136734623455</v>
+        <v>4.548066737288136</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.445638402716431</v>
+        <v>2.404726292081958</v>
       </c>
       <c r="G18" t="n">
-        <v>2.573441394380306</v>
+        <v>2.542080559915213</v>
       </c>
       <c r="H18" t="n">
-        <v>2.674946996466431</v>
+        <v>2.637662919039107</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.770565592144677</v>
+        <v>5.614457307563012</v>
       </c>
       <c r="G19" t="n">
-        <v>5.890562408202157</v>
+        <v>5.847701679382401</v>
       </c>
       <c r="H19" t="n">
-        <v>6.096317273560557</v>
+        <v>5.929703372340327</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8669468962853</v>
+        <v>102.8695707050443</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01431786132962335</v>
+        <v>0.01694167008861014</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80040204691646</v>
+        <v>17.80280304596018</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18461621153075</v>
+        <v>36.18721060057605</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1285254938479626</v>
+        <v>0.1283749204728815</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7370471956412721</v>
+        <v>-0.737296292536316</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1285188781037331</v>
+        <v>0.1283681862933157</v>
       </c>
       <c r="Y2" t="n">
-        <v>59.1602037164707</v>
+        <v>54.76288860164523</v>
       </c>
       <c r="Z2" t="n">
-        <v>95.61718641982159</v>
+        <v>96.43295515451616</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.3027921830776</v>
+        <v>111.0451807949476</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959380882197909</v>
+        <v>4.959349139249797</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05336946855654458</v>
+        <v>0.05333772560843238</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350472705801517</v>
+        <v>1.350466716868356</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725316641757152</v>
+        <v>1.725317582846378</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795373621563021</v>
+        <v>0.7795407705362968</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664719412404073</v>
+        <v>0.5664714682968479</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7784958123514411</v>
+        <v>0.7785011041289502</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.404726292081958</v>
+        <v>2.383424641484571</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.542080559915212</v>
+        <v>2.514083818294677</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.637662919039107</v>
+        <v>2.592053634438956</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3657591807909604</v>
+        <v>0.3656457304163726</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246358825111003</v>
+        <v>7.246300815844519</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3283845438671155</v>
+        <v>0.3283265346006301</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293830994080791</v>
+        <v>1.293831623647854</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683859271713745</v>
+        <v>1.683852826153668</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674565951873591</v>
+        <v>0.8674581078071869</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371055593419229</v>
+        <v>0.7371075719788414</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472663921158866</v>
+        <v>0.8472818477817439</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.788238877118644</v>
+        <v>3.695593683839097</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.184923864370847</v>
+        <v>4.103254599775488</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.548066737288136</v>
+        <v>4.478276434956481</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.31328662060799</v>
+        <v>9.313268386025877</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.35849851651877</v>
+        <v>0.3584802819366584</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254671419729082</v>
+        <v>1.254670589250463</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747751586395628</v>
+        <v>1.747753431875939</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675026723642005</v>
+        <v>0.8675045262339497</v>
       </c>
       <c r="W5" t="n">
-        <v>0.723482351203264</v>
+        <v>0.7234817672436786</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615859023959636</v>
+        <v>0.8615883273758972</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.614457307563012</v>
+        <v>5.58004622106891</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.847701679382401</v>
+        <v>5.813167475248191</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.929703372340327</v>
+        <v>5.899450251903981</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018807810203534</v>
+        <v>7.018826533309831</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2879902250502017</v>
+        <v>0.2880089481564982</v>
       </c>
       <c r="T6" t="n">
-        <v>1.48213012356042</v>
+        <v>1.482149458830778</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910724681539229</v>
+        <v>1.910746705394164</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047764173196704</v>
+        <v>0.3047782790250949</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1982277672668533</v>
+        <v>-0.198255390028907</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801982936928722</v>
+        <v>0.2802065850222558</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.560677410666935</v>
+        <v>6.560446709569892</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.576679982278089</v>
+        <v>6.574108291913068</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.586425173197223</v>
+        <v>6.583910553336841</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586377773661895</v>
+        <v>5.586373664264453</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003805937617103257</v>
+        <v>0.003801828219660981</v>
       </c>
       <c r="T7" t="n">
-        <v>1.15605537694032</v>
+        <v>1.156076115208717</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494140080483892</v>
+        <v>1.494164520092433</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5089060516203086</v>
+        <v>0.508897476810417</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0744471044321493</v>
+        <v>0.07441682569758346</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050670159889633</v>
+        <v>0.505060562396475</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.573696994775617</v>
+        <v>5.583496802616821</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.616595363340542</v>
+        <v>5.608031470616096</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.667581885386322</v>
+        <v>5.641253211560516</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116533923412588</v>
+        <v>8.116498570951327</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2361768599469871</v>
+        <v>0.2361415074857275</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445320209664826</v>
+        <v>1.445333762795696</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825030665135193</v>
+        <v>1.82504265157489</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087127679795122</v>
+        <v>0.8087125105346789</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288625330751858</v>
+        <v>0.6288576579445262</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990782946875183</v>
+        <v>0.7990847812931576</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.149996103074825</v>
+        <v>5.134374020154606</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.351291958272722</v>
+        <v>5.328031220188963</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.437681746134257</v>
+        <v>5.438499568064973</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5094597457627119</v>
+        <v>0.5092201834862385</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679458743258412</v>
+        <v>7.679399529601411</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06350794250815939</v>
+        <v>0.06344872885115857</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477326882824285</v>
+        <v>1.477334376554305</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919733229498319</v>
+        <v>1.919742422532855</v>
       </c>
       <c r="V9" t="n">
-        <v>0.761725100596564</v>
+        <v>0.7617289312538013</v>
       </c>
       <c r="W9" t="n">
-        <v>0.536101342521712</v>
+        <v>0.536096899564196</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597696905661706</v>
+        <v>0.7597775193241229</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.488812165878286</v>
+        <v>5.434218066854215</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.746371008424085</v>
+        <v>5.710217930765157</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.912987288135594</v>
+        <v>5.914311926605505</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61902686422934</v>
+        <v>10.61896211848633</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3139673244915815</v>
+        <v>0.3139025787485703</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05173033507391</v>
+        <v>2.05175508949763</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697382785250898</v>
+        <v>2.697402816742136</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566686956166933</v>
+        <v>0.3566767136431851</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.119842168276806</v>
+        <v>-0.1198588008378192</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3359373779150524</v>
+        <v>0.3359546235499821</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.563639405068569</v>
+        <v>9.57752662688147</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.750300605541238</v>
+        <v>9.716488518192843</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.92144627091257</v>
+        <v>9.860058733554288</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218275752279708</v>
+        <v>5.218260312889051</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0276006876246604</v>
+        <v>-0.02761612701531824</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157960185407619</v>
+        <v>1.157976198825981</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476932089273641</v>
+        <v>1.476954790874493</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294615126768789</v>
+        <v>0.4294589330397364</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08255807289881534</v>
+        <v>-0.08259135268239204</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268697762506228</v>
+        <v>0.4268697419519492</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.154432796557327</v>
+        <v>4.122040207135316</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.427582737704282</v>
+        <v>4.364749368662047</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.797384494415111</v>
+        <v>4.495733730983154</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664193247287486</v>
+        <v>7.66414994507184</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1724260791244171</v>
+        <v>0.1723827769087729</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148999161425344</v>
+        <v>0.9148868354242885</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198022286783129</v>
+        <v>1.19801829485406</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296329148214996</v>
+        <v>0.8296374991869981</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543295609214409</v>
+        <v>0.6543318645339705</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279564694872861</v>
+        <v>0.8279630085282765</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.034532623153825</v>
+        <v>5.019564495348099</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.192368964375194</v>
+        <v>5.134204195990942</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.550960540067943</v>
+        <v>5.43283874740829</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860303672316384</v>
+        <v>2.860137614678899</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.03013429144608</v>
+        <v>10.02997882074563</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4132595173691374</v>
+        <v>0.4131040466686832</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694019717705846</v>
+        <v>1.693998620066241</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153673840596019</v>
+        <v>2.153640350979593</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232194322277044</v>
+        <v>0.8232275417109635</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485852513446999</v>
+        <v>0.648596180254561</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8114219303052521</v>
+        <v>0.8114479242769962</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.126291302171052</v>
+        <v>6.124904217875483</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.52557725334533</v>
+        <v>6.500604356672636</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.11716841692084</v>
+        <v>7.055870269907972</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202579011069618</v>
+        <v>8.202431115499307</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06869540357834023</v>
+        <v>0.06854750800802935</v>
       </c>
       <c r="T14" t="n">
-        <v>1.759033930869108</v>
+        <v>1.758950888077853</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284521303399272</v>
+        <v>2.284450173437456</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808474252303429</v>
+        <v>0.7808701182823767</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651230008433941</v>
+        <v>0.5651500807421397</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805042720926838</v>
+        <v>0.7805295130068802</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.884379768443516</v>
+        <v>5.860890933956352</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.99374825715752</v>
+        <v>5.965188660089201</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.073030922426484</v>
+        <v>6.053909141126624</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82429545715865</v>
+        <v>11.82420814821894</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.139586440227603</v>
+        <v>-0.1396737491673164</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0523892164171</v>
+        <v>2.052371823973652</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697716146641408</v>
+        <v>2.697688689677586</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948574545691808</v>
+        <v>0.7948661773415692</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095746493117293</v>
+        <v>0.6095825966565152</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860526577832085</v>
+        <v>0.7860674674064944</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.719895529007967</v>
+        <v>7.718886076246982</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.901721955546057</v>
+        <v>7.912213360333022</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.140385739333723</v>
+        <v>8.175656855141376</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662524823865473</v>
+        <v>8.662396189094551</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2542545471641329</v>
+        <v>0.2541259123932108</v>
       </c>
       <c r="T16" t="n">
-        <v>3.53826176801757</v>
+        <v>3.538261431411234</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0632571053243</v>
+        <v>11.06326054844518</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04953133232404149</v>
+        <v>0.04952870139872921</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971477861891696</v>
+        <v>-0.5971487803220337</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03277773790882765</v>
+        <v>0.03277533744537264</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.5215816863368</v>
+        <v>11.72760572173063</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.92355797862959</v>
+        <v>11.98919089159435</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.28892202985687</v>
+        <v>12.23332078666879</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910943499886433</v>
+        <v>6.910844281386224</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3712775424396254</v>
+        <v>0.3711783239394156</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032167613929715</v>
+        <v>2.03212765747667</v>
       </c>
       <c r="U17" t="n">
-        <v>2.56641372743566</v>
+        <v>2.566394753362707</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210028996312795</v>
+        <v>0.5210220083068117</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02242120062759012</v>
+        <v>0.02243565549329696</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176492455903716</v>
+        <v>0.5176700743179666</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.596439240362792</v>
+        <v>3.425526934367252</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.456169733192485</v>
+        <v>5.216873493111257</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.939408583401979</v>
+        <v>6.502236022281703</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.693016390828307</v>
+        <v>6.692942729685857</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1952554060978611</v>
+        <v>0.195181744955411</v>
       </c>
       <c r="T18" t="n">
-        <v>1.09979510453292</v>
+        <v>1.0997808789534</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489278325940251</v>
+        <v>1.489266146605329</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009375315826112</v>
+        <v>0.6009515131177614</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174367393881094</v>
+        <v>0.2174495389580891</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5979908004382368</v>
+        <v>0.5980087153034712</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.385762957731743</v>
+        <v>4.43505838401345</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.080458732772944</v>
+        <v>5.918805667347064</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.887481600968441</v>
+        <v>6.962753140363286</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16668</v>
+        <v>16669</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15310549329118</v>
+        <v>11.15297618377718</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.783786074053428</v>
+        <v>0.7836567645394313</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038115677337758</v>
+        <v>2.038120450076919</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757660684033706</v>
+        <v>2.757668257936922</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263416563099953</v>
+        <v>0.7263384618260501</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693605134554979</v>
+        <v>0.4693575986533567</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790069636250309</v>
+        <v>0.6790290647063871</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.689067571876785</v>
+        <v>7.660417943337635</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.813841717093029</v>
+        <v>7.798202636709891</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.912109865642914</v>
+        <v>7.895531290675435</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.689067571876785</v>
+        <v>7.660417943337635</v>
       </c>
       <c r="G2" t="n">
-        <v>7.813841717093029</v>
+        <v>7.798202636709891</v>
       </c>
       <c r="H2" t="n">
-        <v>7.912109865642914</v>
+        <v>7.895531290675435</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.573696994775617</v>
+        <v>5.583496802616821</v>
       </c>
       <c r="G3" t="n">
-        <v>5.616595363340543</v>
+        <v>5.608031470616096</v>
       </c>
       <c r="H3" t="n">
-        <v>5.667581885386322</v>
+        <v>5.641253211560516</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.154432796557327</v>
+        <v>4.122040207135316</v>
       </c>
       <c r="G4" t="n">
-        <v>4.427582737704282</v>
+        <v>4.364749368662047</v>
       </c>
       <c r="H4" t="n">
-        <v>4.797384494415111</v>
+        <v>4.495733730983154</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.5215816863368</v>
+        <v>11.72760572173063</v>
       </c>
       <c r="G5" t="n">
-        <v>11.92355797862959</v>
+        <v>11.98919089159435</v>
       </c>
       <c r="H5" t="n">
-        <v>12.28892202985687</v>
+        <v>12.23332078666879</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>59.1602037164707</v>
+        <v>54.76288860164523</v>
       </c>
       <c r="G6" t="n">
-        <v>95.61718641982159</v>
+        <v>96.43295515451616</v>
       </c>
       <c r="H6" t="n">
-        <v>113.3027921830776</v>
+        <v>111.0451807949476</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.719895529007967</v>
+        <v>7.718886076246982</v>
       </c>
       <c r="G7" t="n">
-        <v>7.901721955546057</v>
+        <v>7.912213360333022</v>
       </c>
       <c r="H7" t="n">
-        <v>8.140385739333723</v>
+        <v>8.175656855141376</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.126291302171052</v>
+        <v>6.124904217875483</v>
       </c>
       <c r="G8" t="n">
-        <v>6.52557725334533</v>
+        <v>6.500604356672636</v>
       </c>
       <c r="H8" t="n">
-        <v>7.11716841692084</v>
+        <v>7.055870269907972</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.034532623153825</v>
+        <v>5.019564495348099</v>
       </c>
       <c r="G9" t="n">
-        <v>5.192368964375194</v>
+        <v>5.134204195990942</v>
       </c>
       <c r="H9" t="n">
-        <v>5.550960540067943</v>
+        <v>5.43283874740829</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.149996103074825</v>
+        <v>5.134374020154606</v>
       </c>
       <c r="G10" t="n">
-        <v>5.351291958272723</v>
+        <v>5.328031220188963</v>
       </c>
       <c r="H10" t="n">
-        <v>5.437681746134257</v>
+        <v>5.438499568064973</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.596439240362792</v>
+        <v>3.425526934367252</v>
       </c>
       <c r="G11" t="n">
-        <v>5.456169733192485</v>
+        <v>5.216873493111256</v>
       </c>
       <c r="H11" t="n">
-        <v>6.939408583401979</v>
+        <v>6.502236022281703</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.884379768443516</v>
+        <v>5.860890933956352</v>
       </c>
       <c r="G12" t="n">
-        <v>5.993748257157519</v>
+        <v>5.965188660089201</v>
       </c>
       <c r="H12" t="n">
-        <v>6.073030922426484</v>
+        <v>6.053909141126624</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.563639405068569</v>
+        <v>9.57752662688147</v>
       </c>
       <c r="G13" t="n">
-        <v>9.750300605541238</v>
+        <v>9.716488518192843</v>
       </c>
       <c r="H13" t="n">
-        <v>9.92144627091257</v>
+        <v>9.860058733554288</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.488812165878286</v>
+        <v>5.434218066854215</v>
       </c>
       <c r="G14" t="n">
-        <v>5.746371008424085</v>
+        <v>5.710217930765157</v>
       </c>
       <c r="H14" t="n">
-        <v>5.912987288135594</v>
+        <v>5.914311926605505</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.560677410666935</v>
+        <v>6.560446709569892</v>
       </c>
       <c r="G15" t="n">
-        <v>6.576679982278089</v>
+        <v>6.574108291913069</v>
       </c>
       <c r="H15" t="n">
-        <v>6.586425173197223</v>
+        <v>6.583910553336841</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.385762957731743</v>
+        <v>4.43505838401345</v>
       </c>
       <c r="G16" t="n">
-        <v>6.080458732772943</v>
+        <v>5.918805667347064</v>
       </c>
       <c r="H16" t="n">
-        <v>6.887481600968441</v>
+        <v>6.962753140363286</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.788238877118644</v>
+        <v>3.695593683839097</v>
       </c>
       <c r="G17" t="n">
-        <v>4.184923864370848</v>
+        <v>4.103254599775488</v>
       </c>
       <c r="H17" t="n">
-        <v>4.548066737288136</v>
+        <v>4.478276434956481</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.404726292081958</v>
+        <v>2.383424641484571</v>
       </c>
       <c r="G18" t="n">
-        <v>2.542080559915213</v>
+        <v>2.514083818294677</v>
       </c>
       <c r="H18" t="n">
-        <v>2.637662919039107</v>
+        <v>2.592053634438956</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.614457307563012</v>
+        <v>5.58004622106891</v>
       </c>
       <c r="G19" t="n">
-        <v>5.847701679382401</v>
+        <v>5.813167475248191</v>
       </c>
       <c r="H19" t="n">
-        <v>5.929703372340327</v>
+        <v>5.899450251903981</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8695707050443</v>
+        <v>102.8700854799055</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01694167008861014</v>
+        <v>0.01745644494982596</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80280304596018</v>
+        <v>17.80335164646652</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18721060057605</v>
+        <v>36.18812805892382</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1283749204728815</v>
+        <v>0.1283444543495988</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.737296292536316</v>
+        <v>-0.7373843853826449</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1283681862933157</v>
+        <v>0.1283377811316883</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.76288860164523</v>
+        <v>54.57549783578607</v>
       </c>
       <c r="Z2" t="n">
-        <v>96.43295515451616</v>
+        <v>101.0918492761358</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.0451807949476</v>
+        <v>108.8924687728891</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959349139249797</v>
+        <v>4.959319191493573</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05333772560843238</v>
+        <v>0.05330777785220802</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350466716868356</v>
+        <v>1.350461493068619</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725317582846378</v>
+        <v>1.725319442964034</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795407705362968</v>
+        <v>0.779543853433221</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664714682968479</v>
+        <v>0.5664705334956046</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785011041289502</v>
+        <v>0.7785060098320837</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.383424641484571</v>
+        <v>2.364266572637518</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.514083818294677</v>
+        <v>2.486211413413529</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.592053634438956</v>
+        <v>2.564572407981806</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3656457304163726</v>
+        <v>0.3655324400564174</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246300815844519</v>
+        <v>7.246250554304211</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3283265346006301</v>
+        <v>0.3282762730603228</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293831623647854</v>
+        <v>1.293836246479646</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683852826153668</v>
+        <v>1.683851757365232</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674581078071869</v>
+        <v>0.8674588043373636</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371075719788414</v>
+        <v>0.7371079057090744</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472818477817439</v>
+        <v>0.8472953698138745</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.695593683839097</v>
+        <v>3.537502534982011</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.103254599775488</v>
+        <v>4.037206566641517</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.478276434956481</v>
+        <v>4.424340620592384</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313268386025877</v>
+        <v>9.313252372778086</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584802819366584</v>
+        <v>0.3584642686888654</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254670589250463</v>
+        <v>1.254670707662627</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747753431875939</v>
+        <v>1.747757376611421</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675045262339497</v>
+        <v>0.8675060167550115</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234817672436786</v>
+        <v>0.7234805190212515</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615883273758972</v>
+        <v>0.8615903275306587</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.58004622106891</v>
+        <v>5.498220204448643</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.813167475248191</v>
+        <v>5.751450378226695</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.899450251903981</v>
+        <v>5.869990637914737</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018826533309831</v>
+        <v>7.018843820339229</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880089481564982</v>
+        <v>0.2880262351858961</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482149458830778</v>
+        <v>1.482167479558585</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910746705394164</v>
+        <v>1.910768938516205</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047782790250949</v>
+        <v>0.3047798526408423</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.198255390028907</v>
+        <v>-0.1982832755809196</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802065850222558</v>
+        <v>0.2802146249169379</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.560446709569892</v>
+        <v>6.538371057403346</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.574108291913068</v>
+        <v>6.565106137762382</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.583910553336841</v>
+        <v>6.581218941334292</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586373664264453</v>
+        <v>5.58637104184505</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003801828219660981</v>
+        <v>0.003799205800258124</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156076115208717</v>
+        <v>1.1560968918996</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494164520092433</v>
+        <v>1.494189808828679</v>
       </c>
       <c r="V7" t="n">
-        <v>0.508897476810417</v>
+        <v>0.5088884321986539</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07441682569758346</v>
+        <v>0.07438549443983455</v>
       </c>
       <c r="X7" t="n">
-        <v>0.505060562396475</v>
+        <v>0.5050536654983089</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.583496802616821</v>
+        <v>5.528121549760627</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.608031470616096</v>
+        <v>5.591954530470024</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.641253211560516</v>
+        <v>5.636815937940761</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116498570951327</v>
+        <v>8.116463144146909</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2361415074857275</v>
+        <v>0.2361060806813083</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445333762795696</v>
+        <v>1.445347685470029</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82504265157489</v>
+        <v>1.825056951165292</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087125105346789</v>
+        <v>0.8087117628327464</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288576579445262</v>
+        <v>0.6288518419661882</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990847812931576</v>
+        <v>0.7990908150888696</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.134374020154606</v>
+        <v>5.088420914837554</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.328031220188963</v>
+        <v>5.297075655240691</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.438499568064973</v>
+        <v>5.43929264960368</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5092201834862385</v>
+        <v>0.5089809590973202</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679399529601411</v>
+        <v>7.679341406671035</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06344872885115857</v>
+        <v>0.06339060592078245</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477334376554305</v>
+        <v>1.477342994522596</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919742422532855</v>
+        <v>1.919750739962227</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617289312538013</v>
+        <v>0.7617328849700808</v>
       </c>
       <c r="W9" t="n">
-        <v>0.536096899564196</v>
+        <v>0.536092879764887</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597775193241229</v>
+        <v>0.7597854015097285</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.434218066854215</v>
+        <v>5.443046544428772</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.710217930765157</v>
+        <v>5.669740066221641</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.914311926605505</v>
+        <v>5.915634696755994</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61896211848633</v>
+        <v>10.61890037070743</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3139025787485703</v>
+        <v>0.3138408309696689</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05175508949763</v>
+        <v>2.051779626427442</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697402816742136</v>
+        <v>2.697424285647871</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566767136431851</v>
+        <v>0.356684018063493</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198588008378192</v>
+        <v>-0.1198766270509146</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3359546235499821</v>
+        <v>0.3359710879779837</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.57752662688147</v>
+        <v>9.54879216192267</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.716488518192843</v>
+        <v>9.712264327940794</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.860058733554288</v>
+        <v>9.834142115370829</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218260312889051</v>
+        <v>5.218246984936423</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02761612701531824</v>
+        <v>-0.02762945496794583</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157976198825981</v>
+        <v>1.157993305635384</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476954790874493</v>
+        <v>1.476977881306665</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294589330397364</v>
+        <v>0.4294556581472084</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08259135268239204</v>
+        <v>-0.08262520300436127</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268697419519492</v>
+        <v>0.4268689549368656</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.122040207135316</v>
+        <v>3.856404760363408</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.364749368662047</v>
+        <v>4.370535868632078</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.495733730983154</v>
+        <v>4.57668633129205</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.66414994507184</v>
+        <v>7.664114162760416</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1723827769087729</v>
+        <v>0.1723469945973484</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148868354242885</v>
+        <v>0.914875192876506</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19801829485406</v>
+        <v>1.198017331891372</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296374991869981</v>
+        <v>0.8296408851096339</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543318645339705</v>
+        <v>0.6543324202272924</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279630085282765</v>
+        <v>0.8279680731483929</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.019564495348099</v>
+        <v>4.90825918173319</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.134204195990942</v>
+        <v>5.056560253269464</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.43283874740829</v>
+        <v>5.278508884839126</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.860137614678899</v>
+        <v>2.859915373765867</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02997882074563</v>
+        <v>10.0298340954385</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4131040466686832</v>
+        <v>0.4129593213615559</v>
       </c>
       <c r="T13" t="n">
-        <v>1.693998620066241</v>
+        <v>1.693984389599413</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153640350979593</v>
+        <v>2.153613080770127</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232275417109635</v>
+        <v>0.8232345629545623</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648596180254561</v>
+        <v>0.6486050794146241</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8114479242769962</v>
+        <v>0.8114718860317554</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.124904217875483</v>
+        <v>6.122184650792434</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.500604356672636</v>
+        <v>6.492557192536724</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.055870269907972</v>
+        <v>7.057360928805975</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202431115499307</v>
+        <v>8.202284985097059</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06854750800802935</v>
+        <v>0.06840137760578147</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758950888077853</v>
+        <v>1.758866092302535</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284450173437456</v>
+        <v>2.284379474188048</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808701182823767</v>
+        <v>0.7808926565018552</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651500807421397</v>
+        <v>0.5651769958287789</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805295130068802</v>
+        <v>0.7805545643288536</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.860890933956352</v>
+        <v>5.833907512792434</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.965188660089201</v>
+        <v>5.938431706178003</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.053909141126624</v>
+        <v>6.036994717083</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82420814821894</v>
+        <v>11.82413166301753</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1396737491673164</v>
+        <v>-0.1397502343687185</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052371823973652</v>
+        <v>2.052349797271817</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697688689677586</v>
+        <v>2.697654785141217</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948661773415692</v>
+        <v>0.7948755336386248</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6095825966565152</v>
+        <v>0.609592410122332</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860674674064944</v>
+        <v>0.7860824404392357</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.718886076246982</v>
+        <v>7.718092070989541</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.912213360333022</v>
+        <v>7.927946679216626</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.175656855141376</v>
+        <v>8.186336503171116</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662396189094551</v>
+        <v>8.662247842719049</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2541259123932108</v>
+        <v>0.2539775660177093</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538261431411234</v>
+        <v>3.538241406727963</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06326054844518</v>
+        <v>11.06325953026031</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04952870139872921</v>
+        <v>0.04952593320778974</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971487803220337</v>
+        <v>-0.5971484863413146</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03277533744537264</v>
+        <v>0.03277271171788065</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.72760572173063</v>
+        <v>11.79953471227841</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.98919089159435</v>
+        <v>12.03681198532542</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.23332078666879</v>
+        <v>12.23272298188824</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910844281386224</v>
+        <v>6.910729090832763</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3711783239394156</v>
+        <v>0.3710631333859544</v>
       </c>
       <c r="T17" t="n">
-        <v>2.03212765747667</v>
+        <v>2.03208439333684</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566394753362707</v>
+        <v>2.566371718173762</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210220083068117</v>
+        <v>0.5210430885925</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02243565549329696</v>
+        <v>0.02245320406277829</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176700743179666</v>
+        <v>0.5176931499748223</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.425526934367252</v>
+        <v>2.680315815657934</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.216873493111257</v>
+        <v>4.451664400345104</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.502236022281703</v>
+        <v>5.606285823460461</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692942729685857</v>
+        <v>6.692877862955195</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.195181744955411</v>
+        <v>0.1951168782247489</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0997808789534</v>
+        <v>1.099772769107038</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489266146605329</v>
+        <v>1.489260404937107</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009515131177614</v>
+        <v>0.600961970327851</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174495389580891</v>
+        <v>0.2174555729856038</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980087153034712</v>
+        <v>0.5980228662020172</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.43505838401345</v>
+        <v>3.548678031554742</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.918805667347064</v>
+        <v>5.270540205214958</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.962753140363286</v>
+        <v>6.149842374278358</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16669</v>
+        <v>16670</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15297618377718</v>
+        <v>11.15284552365137</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7836567645394313</v>
+        <v>0.7835261044136148</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038120450076919</v>
+        <v>2.038128787055666</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757668257936922</v>
+        <v>2.757678249265482</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263384618260501</v>
+        <v>0.7263347099995924</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693575986533567</v>
+        <v>0.4693537534974582</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790290647063871</v>
+        <v>0.6790509464797708</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.660417943337635</v>
+        <v>7.612377687218028</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.798202636709891</v>
+        <v>7.767439677037304</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.895531290675435</v>
+        <v>7.878890345866614</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.660417943337635</v>
+        <v>7.612377687218028</v>
       </c>
       <c r="G2" t="n">
-        <v>7.798202636709891</v>
+        <v>7.767439677037304</v>
       </c>
       <c r="H2" t="n">
-        <v>7.895531290675435</v>
+        <v>7.878890345866614</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.583496802616821</v>
+        <v>5.528121549760627</v>
       </c>
       <c r="G3" t="n">
-        <v>5.608031470616096</v>
+        <v>5.591954530470025</v>
       </c>
       <c r="H3" t="n">
-        <v>5.641253211560516</v>
+        <v>5.636815937940761</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.122040207135316</v>
+        <v>3.856404760363408</v>
       </c>
       <c r="G4" t="n">
-        <v>4.364749368662047</v>
+        <v>4.370535868632078</v>
       </c>
       <c r="H4" t="n">
-        <v>4.495733730983154</v>
+        <v>4.57668633129205</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.72760572173063</v>
+        <v>11.79953471227841</v>
       </c>
       <c r="G5" t="n">
-        <v>11.98919089159435</v>
+        <v>12.03681198532542</v>
       </c>
       <c r="H5" t="n">
-        <v>12.23332078666879</v>
+        <v>12.23272298188824</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.76288860164523</v>
+        <v>54.57549783578607</v>
       </c>
       <c r="G6" t="n">
-        <v>96.43295515451616</v>
+        <v>101.0918492761358</v>
       </c>
       <c r="H6" t="n">
-        <v>111.0451807949476</v>
+        <v>108.8924687728891</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.718886076246982</v>
+        <v>7.718092070989541</v>
       </c>
       <c r="G7" t="n">
-        <v>7.912213360333022</v>
+        <v>7.927946679216626</v>
       </c>
       <c r="H7" t="n">
-        <v>8.175656855141376</v>
+        <v>8.186336503171116</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.124904217875483</v>
+        <v>6.122184650792434</v>
       </c>
       <c r="G8" t="n">
-        <v>6.500604356672636</v>
+        <v>6.492557192536724</v>
       </c>
       <c r="H8" t="n">
-        <v>7.055870269907972</v>
+        <v>7.057360928805975</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.019564495348099</v>
+        <v>4.90825918173319</v>
       </c>
       <c r="G9" t="n">
-        <v>5.134204195990942</v>
+        <v>5.056560253269463</v>
       </c>
       <c r="H9" t="n">
-        <v>5.43283874740829</v>
+        <v>5.278508884839126</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.134374020154606</v>
+        <v>5.088420914837554</v>
       </c>
       <c r="G10" t="n">
-        <v>5.328031220188963</v>
+        <v>5.297075655240691</v>
       </c>
       <c r="H10" t="n">
-        <v>5.438499568064973</v>
+        <v>5.43929264960368</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>3.425526934367252</v>
+        <v>2.680315815657934</v>
       </c>
       <c r="G11" t="n">
-        <v>5.216873493111256</v>
+        <v>4.451664400345105</v>
       </c>
       <c r="H11" t="n">
-        <v>6.502236022281703</v>
+        <v>5.606285823460461</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.860890933956352</v>
+        <v>5.833907512792434</v>
       </c>
       <c r="G12" t="n">
-        <v>5.965188660089201</v>
+        <v>5.938431706178003</v>
       </c>
       <c r="H12" t="n">
-        <v>6.053909141126624</v>
+        <v>6.036994717083</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.57752662688147</v>
+        <v>9.54879216192267</v>
       </c>
       <c r="G13" t="n">
-        <v>9.716488518192843</v>
+        <v>9.712264327940794</v>
       </c>
       <c r="H13" t="n">
-        <v>9.860058733554288</v>
+        <v>9.834142115370829</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.434218066854215</v>
+        <v>5.443046544428772</v>
       </c>
       <c r="G14" t="n">
-        <v>5.710217930765157</v>
+        <v>5.669740066221641</v>
       </c>
       <c r="H14" t="n">
-        <v>5.914311926605505</v>
+        <v>5.915634696755994</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.560446709569892</v>
+        <v>6.538371057403346</v>
       </c>
       <c r="G15" t="n">
-        <v>6.574108291913069</v>
+        <v>6.565106137762382</v>
       </c>
       <c r="H15" t="n">
-        <v>6.583910553336841</v>
+        <v>6.581218941334292</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>4.43505838401345</v>
+        <v>3.548678031554742</v>
       </c>
       <c r="G16" t="n">
-        <v>5.918805667347064</v>
+        <v>5.270540205214958</v>
       </c>
       <c r="H16" t="n">
-        <v>6.962753140363286</v>
+        <v>6.149842374278358</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.695593683839097</v>
+        <v>3.537502534982011</v>
       </c>
       <c r="G17" t="n">
-        <v>4.103254599775488</v>
+        <v>4.037206566641517</v>
       </c>
       <c r="H17" t="n">
-        <v>4.478276434956481</v>
+        <v>4.424340620592384</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.383424641484571</v>
+        <v>2.364266572637518</v>
       </c>
       <c r="G18" t="n">
-        <v>2.514083818294677</v>
+        <v>2.486211413413528</v>
       </c>
       <c r="H18" t="n">
-        <v>2.592053634438956</v>
+        <v>2.564572407981806</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.58004622106891</v>
+        <v>5.498220204448643</v>
       </c>
       <c r="G19" t="n">
-        <v>5.813167475248191</v>
+        <v>5.751450378226695</v>
       </c>
       <c r="H19" t="n">
-        <v>5.899450251903981</v>
+        <v>5.869990637914737</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8700854799055</v>
+        <v>102.8701475045962</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01745644494982596</v>
+        <v>0.01751846964055075</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80335164646652</v>
+        <v>17.80344282141962</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18812805892382</v>
+        <v>36.18841135784634</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1283444543495988</v>
+        <v>0.1283439734080809</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7373843853826449</v>
+        <v>-0.7374115877319991</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1283377811316883</v>
+        <v>0.1283373590019142</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.57549783578607</v>
+        <v>6.76180007429619</v>
       </c>
       <c r="Z2" t="n">
-        <v>101.0918492761358</v>
+        <v>65.77198779489075</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.8924687728891</v>
+        <v>109.0775451319873</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959319191493573</v>
+        <v>4.959292788671315</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05330777785220802</v>
+        <v>0.05328137502995056</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350461493068619</v>
+        <v>1.350458058856289</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725319442964034</v>
+        <v>1.725322911508741</v>
       </c>
       <c r="V3" t="n">
-        <v>0.779543853433221</v>
+        <v>0.7795462785873385</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664705334956046</v>
+        <v>0.5664687903774196</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785060098320837</v>
+        <v>0.7785101128220477</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.364266572637518</v>
+        <v>2.36310358995111</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.486211413413529</v>
+        <v>2.464309223236711</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.564572407981806</v>
+        <v>2.565183376263646</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3655324400564174</v>
+        <v>0.3654193093727977</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246250554304211</v>
+        <v>7.24620664879397</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3282762730603228</v>
+        <v>0.3282323675500824</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293836246479646</v>
+        <v>1.293839462865648</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683851757365232</v>
+        <v>1.683851532020336</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674588043373636</v>
+        <v>0.8674594143735965</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371079057090744</v>
+        <v>0.7371079760732109</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472953698138745</v>
+        <v>0.8473077670549048</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.537502534982011</v>
+        <v>3.409866102889359</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.037206566641517</v>
+        <v>3.951828529288135</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.424340620592384</v>
+        <v>4.337646229739253</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313252372778086</v>
+        <v>9.31323896258634</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584642686888654</v>
+        <v>0.3584508584971209</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254670707662627</v>
+        <v>1.254669445282238</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747757376611421</v>
+        <v>1.747761966550194</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675060167550115</v>
+        <v>0.8675074105462111</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234805190212515</v>
+        <v>0.7234790666352733</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615903275306587</v>
+        <v>0.8615921465731775</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.498220204448643</v>
+        <v>5.488790361969085</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.751450378226695</v>
+        <v>5.689301134904268</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.869990637914737</v>
+        <v>5.835958296535599</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018843820339229</v>
+        <v>7.018862083558869</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880262351858961</v>
+        <v>0.2880444984055363</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482167479558585</v>
+        <v>1.4821848496398</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910768938516205</v>
+        <v>1.910791526877223</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047798526408423</v>
+        <v>0.3047811401652761</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1982832755809196</v>
+        <v>-0.1983116070182522</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802146249169379</v>
+        <v>0.2802223278190273</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.538371057403346</v>
+        <v>6.519354397103169</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.565106137762382</v>
+        <v>6.558750974971417</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.581218941334292</v>
+        <v>6.578523023058566</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.58637104184505</v>
+        <v>5.586368877834818</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003799205800258124</v>
+        <v>0.00379704179002552</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1560968918996</v>
+        <v>1.156117149326284</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494189808828679</v>
+        <v>1.494214847725833</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088884321986539</v>
+        <v>0.5088795519955388</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07438549443983455</v>
+        <v>0.0743544721955911</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050536654983089</v>
+        <v>0.505046930551971</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.528121549760627</v>
+        <v>5.517647897160978</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.591954530470024</v>
+        <v>5.579437040866467</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.636815937940761</v>
+        <v>5.628024121445888</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116463144146909</v>
+        <v>8.11642394939595</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2361060806813083</v>
+        <v>0.2360668859303517</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445347685470029</v>
+        <v>1.445362706513805</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825056951165292</v>
+        <v>1.825072023420517</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087117628327464</v>
+        <v>0.8087109402269829</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288518419661882</v>
+        <v>0.6288457116776404</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990908150888696</v>
+        <v>0.7990972042408212</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.088420914837554</v>
+        <v>5.062112033466737</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.297075655240691</v>
+        <v>5.260139975275261</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.43929264960368</v>
+        <v>5.440228653959134</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5089809590973202</v>
+        <v>0.5087420718816067</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679341406671035</v>
+        <v>7.679281023352432</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06339060592078245</v>
+        <v>0.06333022260217974</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477342994522596</v>
+        <v>1.477349527043618</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919750739962227</v>
+        <v>1.919756111554059</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617328849700808</v>
+        <v>0.7617376456732488</v>
       </c>
       <c r="W9" t="n">
-        <v>0.536092879764887</v>
+        <v>0.5360902836745383</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597854015097285</v>
+        <v>0.7597941422443749</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.443046544428772</v>
+        <v>5.400770915040113</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.669740066221641</v>
+        <v>5.61588010743468</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.915634696755994</v>
+        <v>5.916955602536998</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61890037070743</v>
+        <v>10.61883999889948</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3138408309696689</v>
+        <v>0.3137804591617211</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051779626427442</v>
+        <v>2.051808859762343</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697424285647871</v>
+        <v>2.697450249256887</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356684018063493</v>
+        <v>0.3566890837655574</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198766270509146</v>
+        <v>-0.1198981855272574</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3359710879779837</v>
+        <v>0.335985335833084</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.54879216192267</v>
+        <v>9.44879183177447</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.712264327940794</v>
+        <v>9.661842777493762</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.834142115370829</v>
+        <v>9.781893486121293</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218246984936423</v>
+        <v>5.218238137386008</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02762945496794583</v>
+        <v>-0.02763830251836133</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157993305635384</v>
+        <v>1.15800963844785</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476977881306665</v>
+        <v>1.477000157951283</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294556581472084</v>
+        <v>0.4294518791293669</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08262520300436127</v>
+        <v>-0.08265786082420079</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268689549368656</v>
+        <v>0.4268674875607058</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.856404760363408</v>
+        <v>3.795036532487392</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.370535868632078</v>
+        <v>4.268560038008553</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.57668633129205</v>
+        <v>4.400423774629859</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664114162760416</v>
+        <v>7.664088313615491</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1723469945973484</v>
+        <v>0.1723211454524244</v>
       </c>
       <c r="T12" t="n">
-        <v>0.914875192876506</v>
+        <v>0.914867627951029</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198017331891372</v>
+        <v>1.198019462555703</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296408851096339</v>
+        <v>0.82964287822424</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543324202272924</v>
+        <v>0.6543311906920963</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279680731483929</v>
+        <v>0.8279713657108509</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.90825918173319</v>
+        <v>4.90445803221453</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.056560253269464</v>
+        <v>5.032482310319336</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.278508884839126</v>
+        <v>5.160316186945687</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.859915373765867</v>
+        <v>2.859418604651163</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.0298340954385</v>
+        <v>10.02970519803595</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4129593213615559</v>
+        <v>0.4128304239590089</v>
       </c>
       <c r="T13" t="n">
-        <v>1.693984389599413</v>
+        <v>1.693973530347516</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153613080770127</v>
+        <v>2.15359276854957</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232345629545623</v>
+        <v>0.8232403785951523</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486050794146241</v>
+        <v>0.6486117078824146</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8114718860317554</v>
+        <v>0.811493278924927</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.122184650792434</v>
+        <v>6.120902501446722</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.492557192536724</v>
+        <v>6.510814914872495</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.057360928805975</v>
+        <v>7.101370997101239</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202284985097059</v>
+        <v>8.202141954011195</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06840137760578147</v>
+        <v>0.06825834651991754</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758866092302535</v>
+        <v>1.758784929714321</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284379474188048</v>
+        <v>2.284310548836229</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808926565018552</v>
+        <v>0.7809147113582048</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651769958287789</v>
+        <v>0.5652032347936624</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805545643288536</v>
+        <v>0.7805790773278871</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.833907512792434</v>
+        <v>5.808928979470446</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.938431706178003</v>
+        <v>5.910113416669162</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.036994717083</v>
+        <v>6.018879444504805</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82413166301753</v>
+        <v>11.82408224025376</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1397502343687185</v>
+        <v>-0.1397996571324936</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052349797271817</v>
+        <v>2.052329207533894</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697654785141217</v>
+        <v>2.697625810257865</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948755336386248</v>
+        <v>0.7948830953683712</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609592410122332</v>
+        <v>0.6096007966317466</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860824404392357</v>
+        <v>0.7860943385524966</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.718092070989541</v>
+        <v>7.717304145496055</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.927946679216626</v>
+        <v>7.960861996140132</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.186336503171116</v>
+        <v>8.195309589098445</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662247842719049</v>
+        <v>8.662094478258791</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2539775660177093</v>
+        <v>0.253824201557451</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538241406727963</v>
+        <v>3.538215332080178</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06325953026031</v>
+        <v>11.06325710002606</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04952593320778974</v>
+        <v>0.04952321039383657</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971484863413146</v>
+        <v>-0.5971477846594078</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03277271171788065</v>
+        <v>0.03277011343363267</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.79953471227841</v>
+        <v>11.79467005147619</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.03681198532542</v>
+        <v>12.07401331194374</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.23272298188824</v>
+        <v>12.2273456345364</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910729090832763</v>
+        <v>6.910638749632487</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3710631333859544</v>
+        <v>0.3709727921856792</v>
       </c>
       <c r="T17" t="n">
-        <v>2.03208439333684</v>
+        <v>2.032051977664303</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566371718173762</v>
+        <v>2.566358012011487</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210430885925</v>
+        <v>0.5210601123824642</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02245320406277829</v>
+        <v>0.02246364555817282</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5176931499748223</v>
+        <v>0.5177117402682629</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.680315815657934</v>
+        <v>2.570414112261725</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.451664400345104</v>
+        <v>3.72598976280056</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.606285823460461</v>
+        <v>4.984911003187393</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692877862955195</v>
+        <v>6.692838770241162</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1951168782247489</v>
+        <v>0.1950777855107163</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099772769107038</v>
+        <v>1.099783723869309</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489260404937107</v>
+        <v>1.489270681126537</v>
       </c>
       <c r="V18" t="n">
-        <v>0.600961970327851</v>
+        <v>0.6009639539075831</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174555729856038</v>
+        <v>0.2174447735277156</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980228662020172</v>
+        <v>0.5980279102459788</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.548678031554742</v>
+        <v>3.517886153513982</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.270540205214958</v>
+        <v>4.619873730198178</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.149842374278358</v>
+        <v>5.736853900727662</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16670</v>
+        <v>16671</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15284552365137</v>
+        <v>11.15271843835093</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7835261044136148</v>
+        <v>0.7833990191131859</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038128787055666</v>
+        <v>2.038141529747971</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757678249265482</v>
+        <v>2.757691388179865</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263347099995924</v>
+        <v>0.7263303108517383</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693537534974582</v>
+        <v>0.4693486969741227</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790509464797708</v>
+        <v>0.6790716477703308</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.612377687218028</v>
+        <v>7.591418548405776</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.767439677037304</v>
+        <v>7.731417617803659</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.878890345866614</v>
+        <v>7.87198965338793</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.612377687218028</v>
+        <v>7.591418548405776</v>
       </c>
       <c r="G2" t="n">
-        <v>7.767439677037304</v>
+        <v>7.731417617803659</v>
       </c>
       <c r="H2" t="n">
-        <v>7.878890345866614</v>
+        <v>7.87198965338793</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.528121549760627</v>
+        <v>5.517647897160978</v>
       </c>
       <c r="G3" t="n">
-        <v>5.591954530470025</v>
+        <v>5.579437040866466</v>
       </c>
       <c r="H3" t="n">
-        <v>5.636815937940761</v>
+        <v>5.628024121445888</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.856404760363408</v>
+        <v>3.795036532487392</v>
       </c>
       <c r="G4" t="n">
-        <v>4.370535868632078</v>
+        <v>4.268560038008553</v>
       </c>
       <c r="H4" t="n">
-        <v>4.57668633129205</v>
+        <v>4.400423774629859</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.79953471227841</v>
+        <v>11.79467005147619</v>
       </c>
       <c r="G5" t="n">
-        <v>12.03681198532542</v>
+        <v>12.07401331194374</v>
       </c>
       <c r="H5" t="n">
-        <v>12.23272298188824</v>
+        <v>12.2273456345364</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.57549783578607</v>
+        <v>6.76180007429619</v>
       </c>
       <c r="G6" t="n">
-        <v>101.0918492761358</v>
+        <v>65.77198779489075</v>
       </c>
       <c r="H6" t="n">
-        <v>108.8924687728891</v>
+        <v>109.0775451319873</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.718092070989541</v>
+        <v>7.717304145496055</v>
       </c>
       <c r="G7" t="n">
-        <v>7.927946679216626</v>
+        <v>7.960861996140132</v>
       </c>
       <c r="H7" t="n">
-        <v>8.186336503171116</v>
+        <v>8.195309589098445</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.122184650792434</v>
+        <v>6.120902501446722</v>
       </c>
       <c r="G8" t="n">
-        <v>6.492557192536724</v>
+        <v>6.510814914872495</v>
       </c>
       <c r="H8" t="n">
-        <v>7.057360928805975</v>
+        <v>7.101370997101239</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.90825918173319</v>
+        <v>4.90445803221453</v>
       </c>
       <c r="G9" t="n">
-        <v>5.056560253269463</v>
+        <v>5.032482310319336</v>
       </c>
       <c r="H9" t="n">
-        <v>5.278508884839126</v>
+        <v>5.160316186945687</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.088420914837554</v>
+        <v>5.062112033466737</v>
       </c>
       <c r="G10" t="n">
-        <v>5.297075655240691</v>
+        <v>5.260139975275261</v>
       </c>
       <c r="H10" t="n">
-        <v>5.43929264960368</v>
+        <v>5.440228653959134</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.680315815657934</v>
+        <v>2.570414112261725</v>
       </c>
       <c r="G11" t="n">
-        <v>4.451664400345105</v>
+        <v>3.72598976280056</v>
       </c>
       <c r="H11" t="n">
-        <v>5.606285823460461</v>
+        <v>4.984911003187393</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.833907512792434</v>
+        <v>5.808928979470446</v>
       </c>
       <c r="G12" t="n">
-        <v>5.938431706178003</v>
+        <v>5.910113416669162</v>
       </c>
       <c r="H12" t="n">
-        <v>6.036994717083</v>
+        <v>6.018879444504805</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.54879216192267</v>
+        <v>9.44879183177447</v>
       </c>
       <c r="G13" t="n">
-        <v>9.712264327940794</v>
+        <v>9.66184277749376</v>
       </c>
       <c r="H13" t="n">
-        <v>9.834142115370829</v>
+        <v>9.781893486121293</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.443046544428772</v>
+        <v>5.400770915040113</v>
       </c>
       <c r="G14" t="n">
-        <v>5.669740066221641</v>
+        <v>5.615880107434679</v>
       </c>
       <c r="H14" t="n">
-        <v>5.915634696755994</v>
+        <v>5.916955602536998</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.538371057403346</v>
+        <v>6.519354397103169</v>
       </c>
       <c r="G15" t="n">
-        <v>6.565106137762382</v>
+        <v>6.558750974971417</v>
       </c>
       <c r="H15" t="n">
-        <v>6.581218941334292</v>
+        <v>6.578523023058566</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.548678031554742</v>
+        <v>3.517886153513982</v>
       </c>
       <c r="G16" t="n">
-        <v>5.270540205214958</v>
+        <v>4.619873730198178</v>
       </c>
       <c r="H16" t="n">
-        <v>6.149842374278358</v>
+        <v>5.736853900727662</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.537502534982011</v>
+        <v>3.409866102889359</v>
       </c>
       <c r="G17" t="n">
-        <v>4.037206566641517</v>
+        <v>3.951828529288135</v>
       </c>
       <c r="H17" t="n">
-        <v>4.424340620592384</v>
+        <v>4.337646229739253</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.364266572637518</v>
+        <v>2.36310358995111</v>
       </c>
       <c r="G18" t="n">
-        <v>2.486211413413528</v>
+        <v>2.464309223236711</v>
       </c>
       <c r="H18" t="n">
-        <v>2.564572407981806</v>
+        <v>2.565183376263646</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.498220204448643</v>
+        <v>5.488790361969085</v>
       </c>
       <c r="G19" t="n">
-        <v>5.751450378226695</v>
+        <v>5.689301134904268</v>
       </c>
       <c r="H19" t="n">
-        <v>5.869990637914737</v>
+        <v>5.835958296535599</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8701475045962</v>
+        <v>102.8709216150927</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01751846964055075</v>
+        <v>0.01829258013697947</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80344282141962</v>
+        <v>17.80282801825294</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18841135784634</v>
+        <v>36.18774536926671</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1283439734080809</v>
+        <v>0.1283553014493155</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7374115877319991</v>
+        <v>-0.7373476398777066</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1283373590019142</v>
+        <v>0.1283485923529722</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.76180007429619</v>
+        <v>6.928909096798718</v>
       </c>
       <c r="Z2" t="n">
-        <v>65.77198779489075</v>
+        <v>58.44869892302923</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.0775451319873</v>
+        <v>108.7517849517069</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959292788671315</v>
+        <v>4.959265363240084</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05328137502995056</v>
+        <v>0.05325394959871961</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350458058856289</v>
+        <v>1.350454006290991</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725322911508741</v>
+        <v>1.725325331281716</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795462785873385</v>
+        <v>0.7795490128868782</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664687903774196</v>
+        <v>0.5664675743177088</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785101128220477</v>
+        <v>0.7785145518973335</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.36310358995111</v>
+        <v>2.362390735035211</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.464309223236711</v>
+        <v>2.444110150811109</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.565183376263646</v>
+        <v>2.564521551419067</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3654193093727977</v>
+        <v>0.365306338028169</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.24620664879397</v>
+        <v>7.246169260851521</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3282323675500824</v>
+        <v>0.3281949796076335</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293839462865648</v>
+        <v>1.293842209860603</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683851532020336</v>
+        <v>1.683851244969865</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674594143735965</v>
+        <v>0.8674600939018494</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371079760732109</v>
+        <v>0.7371080657049527</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473077670549048</v>
+        <v>0.8473191724451592</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.409866102889359</v>
+        <v>3.33475352112676</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.951828529288135</v>
+        <v>3.860727104893</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.337646229739253</v>
+        <v>4.238172535211268</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.31323896258634</v>
+        <v>9.313229078010291</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584508584971209</v>
+        <v>0.3584409739210713</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254669445282238</v>
+        <v>1.254668979224067</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747761966550194</v>
+        <v>1.747768465606011</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675074105462111</v>
+        <v>0.8675084903373049</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234790666352733</v>
+        <v>0.7234770101443364</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615921465731775</v>
+        <v>0.8615935460995557</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.488790361969085</v>
+        <v>5.496648649592405</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.689301134904268</v>
+        <v>5.679071988298855</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.835958296535599</v>
+        <v>5.818697926553889</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018862083558869</v>
+        <v>7.018880730133799</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880444984055363</v>
+        <v>0.2880631449804664</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4821848496398</v>
+        <v>1.482201070125221</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910791526877223</v>
+        <v>1.910813673194301</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047811401652761</v>
+        <v>0.3047826774530446</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1983116070182522</v>
+        <v>-0.1983393843474104</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802223278190273</v>
+        <v>0.2802302139391833</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.519354397103169</v>
+        <v>6.518088748551847</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.558750974971417</v>
+        <v>6.555996941234389</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.578523023058566</v>
+        <v>6.580381843496737</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586368877834818</v>
+        <v>5.586366861923605</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00379704179002552</v>
+        <v>0.003795025878814066</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156117149326284</v>
+        <v>1.156138026836602</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494214847725833</v>
+        <v>1.494239956711108</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088795519955388</v>
+        <v>0.5088707227426841</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0743544721955911</v>
+        <v>0.07432336259278616</v>
       </c>
       <c r="X7" t="n">
-        <v>0.505046930551971</v>
+        <v>0.5050402716984921</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.517647897160978</v>
+        <v>5.515237375031438</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.579437040866467</v>
+        <v>5.56988989535896</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.628024121445888</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.11642394939595</v>
+        <v>8.116381909788547</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2360668859303517</v>
+        <v>0.236024846322947</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445362706513805</v>
+        <v>1.445379451668644</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825072023420517</v>
+        <v>1.825088070298521</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087109402269829</v>
+        <v>0.8087099873074537</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288457116776404</v>
+        <v>0.6288391849283477</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7990972042408212</v>
+        <v>0.7991038087169164</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.062112033466737</v>
+        <v>5.059164683988866</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.260139975275261</v>
+        <v>5.221453908602689</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.440228653959134</v>
+        <v>5.441096665241053</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5087420718816067</v>
+        <v>0.5085035211267606</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679281023352432</v>
+        <v>7.679220518320881</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06333022260217974</v>
+        <v>0.06326971757062909</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477349527043618</v>
+        <v>1.477357590119955</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919756111554059</v>
+        <v>1.919763465345096</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617376456732488</v>
+        <v>0.7617419082660241</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360902836745383</v>
+        <v>0.5360867295755278</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597941422443749</v>
+        <v>0.7598023827856302</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.400770915040113</v>
+        <v>5.412005618930871</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.61588010743468</v>
+        <v>5.567118713594059</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.916955602536998</v>
+        <v>5.863188981112657</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61883999889948</v>
+        <v>10.61877823187335</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3137804591617211</v>
+        <v>0.313718692135588</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051808859762343</v>
+        <v>2.051841813319846</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697450249256887</v>
+        <v>2.697479476365682</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566890837655574</v>
+        <v>0.3566932738794863</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1198981855272574</v>
+        <v>-0.119922454047829</v>
       </c>
       <c r="X10" t="n">
-        <v>0.335985335833084</v>
+        <v>0.3359990868057994</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.44879183177447</v>
+        <v>9.447583881764444</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.661842777493762</v>
+        <v>9.668400394753865</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.781893486121293</v>
+        <v>9.765086572712452</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218238137386008</v>
+        <v>5.218231035951047</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02763830251836133</v>
+        <v>-0.02764540395332193</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15800963844785</v>
+        <v>1.158024978617857</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477000157951283</v>
+        <v>1.477021258137165</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294518791293669</v>
+        <v>0.4294484620125537</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08265786082420079</v>
+        <v>-0.08268879439609189</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268674875607058</v>
+        <v>0.4268662916940498</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.795036532487392</v>
+        <v>3.790021861965309</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.268560038008553</v>
+        <v>4.289764510482488</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.400423774629859</v>
+        <v>4.553660881511556</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664088313615491</v>
+        <v>7.664066742079696</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1723211454524244</v>
+        <v>0.1722995739166291</v>
       </c>
       <c r="T12" t="n">
-        <v>0.914867627951029</v>
+        <v>0.9148658981503709</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198019462555703</v>
+        <v>1.198025827639252</v>
       </c>
       <c r="V12" t="n">
-        <v>0.82964287822424</v>
+        <v>0.8296434368939056</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543311906920963</v>
+        <v>0.6543275176020253</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279713657108509</v>
+        <v>0.8279730697760215</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.90445803221453</v>
+        <v>5.031167469411233</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.032482310319336</v>
+        <v>5.292234593917787</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.160316186945687</v>
+        <v>5.766668871950078</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.859418604651163</v>
+        <v>2.858922535211267</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02970519803595</v>
+        <v>10.02960288126553</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4128304239590089</v>
+        <v>0.4127281071885881</v>
       </c>
       <c r="T13" t="n">
-        <v>1.693973530347516</v>
+        <v>1.69398111425679</v>
       </c>
       <c r="U13" t="n">
-        <v>2.15359276854957</v>
+        <v>2.153603093252619</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232403785951523</v>
+        <v>0.8232408634733498</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486117078824146</v>
+        <v>0.6486083386396118</v>
       </c>
       <c r="X13" t="n">
-        <v>0.811493278924927</v>
+        <v>0.8115071728955867</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.120902501446722</v>
+        <v>6.120047720058925</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.510814914872495</v>
+        <v>6.566045001199218</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.101370997101239</v>
+        <v>7.132459085695904</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.202141954011195</v>
+        <v>8.201999578481583</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06825834651991754</v>
+        <v>0.06811597099030586</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758784929714321</v>
+        <v>1.758707254685627</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284310548836229</v>
+        <v>2.284244148119771</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809147113582048</v>
+        <v>0.7809362631339195</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652032347936624</v>
+        <v>0.5652285119146977</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7805790773278871</v>
+        <v>0.7806030702435247</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.808928979470446</v>
+        <v>5.795346036438108</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.910113416669162</v>
+        <v>5.883620800557672</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.018879444504805</v>
+        <v>6.001954091299062</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82408224025376</v>
+        <v>11.82404010830672</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1397996571324936</v>
+        <v>-0.1398417890795378</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052329207533894</v>
+        <v>2.052309283643472</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697625810257865</v>
+        <v>2.697598749840943</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7948830953683712</v>
+        <v>0.79489003813926</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096007966317466</v>
+        <v>0.6096086289353837</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7860943385524966</v>
+        <v>0.7861051964153452</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.717304145496055</v>
+        <v>7.716559573425161</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.960861996140132</v>
+        <v>8.003437350731138</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.195309589098445</v>
+        <v>8.213961802792225</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.662094478258791</v>
+        <v>8.661940962347503</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.253824201557451</v>
+        <v>0.2536706856461647</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538215332080178</v>
+        <v>3.53818889127083</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06325710002606</v>
+        <v>11.06325561399289</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04952321039383657</v>
+        <v>0.0495203587752792</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971477846594078</v>
+        <v>-0.5971473555968989</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03277011343363267</v>
+        <v>0.03276739597718059</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.79467005147619</v>
+        <v>11.81452233334586</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.07401331194374</v>
+        <v>12.12346495306331</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.2273456345364</v>
+        <v>12.25120846792801</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910638749632487</v>
+        <v>6.91060968490918</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3709727921856792</v>
+        <v>0.3709437274623716</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032051977664303</v>
+        <v>2.032070699946114</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566358012011487</v>
+        <v>2.566374756378949</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210601123824642</v>
+        <v>0.5210619897327861</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02246364555817282</v>
+        <v>0.02245088951926677</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177117402682629</v>
+        <v>0.517714161223767</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.570414112261725</v>
+        <v>2.814851400989769</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.72598976280056</v>
+        <v>4.104431563454307</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.984911003187393</v>
+        <v>4.921032392944955</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692838770241162</v>
+        <v>6.692810667117814</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1950777855107163</v>
+        <v>0.1950496823873679</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099783723869309</v>
+        <v>1.099800818041939</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489270681126537</v>
+        <v>1.489285573230909</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009639539075831</v>
+        <v>0.6009631667420366</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174447735277156</v>
+        <v>0.2174291229780553</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980279102459788</v>
+        <v>0.5980298139582503</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.517886153513982</v>
+        <v>3.867618429566554</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.619873730198178</v>
+        <v>5.191220486701549</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.736853900727662</v>
+        <v>6.099471149154141</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16671</v>
+        <v>16672</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15271843835093</v>
+        <v>11.15259023226326</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7833990191131859</v>
+        <v>0.7832708130255097</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038141529747971</v>
+        <v>2.038147050741673</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757691388179865</v>
+        <v>2.757700572588251</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263303108517383</v>
+        <v>0.726326796209403</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693486969741227</v>
+        <v>0.469345162331766</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790716477703308</v>
+        <v>0.6790933064218797</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.591418548405776</v>
+        <v>7.570996427063744</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.731417617803659</v>
+        <v>7.719601179958024</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.87198965338793</v>
+        <v>7.854540874070603</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.591418548405776</v>
+        <v>7.570996427063744</v>
       </c>
       <c r="G2" t="n">
-        <v>7.731417617803659</v>
+        <v>7.719601179958026</v>
       </c>
       <c r="H2" t="n">
-        <v>7.87198965338793</v>
+        <v>7.854540874070603</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.517647897160978</v>
+        <v>5.515237375031438</v>
       </c>
       <c r="G3" t="n">
-        <v>5.579437040866466</v>
+        <v>5.56988989535896</v>
       </c>
       <c r="H3" t="n">
-        <v>5.628024121445888</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.795036532487392</v>
+        <v>3.790021861965309</v>
       </c>
       <c r="G4" t="n">
-        <v>4.268560038008553</v>
+        <v>4.289764510482488</v>
       </c>
       <c r="H4" t="n">
-        <v>4.400423774629859</v>
+        <v>4.553660881511556</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.79467005147619</v>
+        <v>11.81452233334586</v>
       </c>
       <c r="G5" t="n">
-        <v>12.07401331194374</v>
+        <v>12.12346495306331</v>
       </c>
       <c r="H5" t="n">
-        <v>12.2273456345364</v>
+        <v>12.25120846792801</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.76180007429619</v>
+        <v>6.928909096798718</v>
       </c>
       <c r="G6" t="n">
-        <v>65.77198779489075</v>
+        <v>58.44869892302923</v>
       </c>
       <c r="H6" t="n">
-        <v>109.0775451319873</v>
+        <v>108.7517849517069</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.717304145496055</v>
+        <v>7.716559573425161</v>
       </c>
       <c r="G7" t="n">
-        <v>7.960861996140132</v>
+        <v>8.003437350731138</v>
       </c>
       <c r="H7" t="n">
-        <v>8.195309589098445</v>
+        <v>8.213961802792225</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.120902501446722</v>
+        <v>6.120047720058925</v>
       </c>
       <c r="G8" t="n">
-        <v>6.510814914872495</v>
+        <v>6.566045001199218</v>
       </c>
       <c r="H8" t="n">
-        <v>7.101370997101239</v>
+        <v>7.132459085695904</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.90445803221453</v>
+        <v>5.031167469411233</v>
       </c>
       <c r="G9" t="n">
-        <v>5.032482310319336</v>
+        <v>5.292234593917787</v>
       </c>
       <c r="H9" t="n">
-        <v>5.160316186945687</v>
+        <v>5.766668871950078</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.062112033466737</v>
+        <v>5.059164683988866</v>
       </c>
       <c r="G10" t="n">
-        <v>5.260139975275261</v>
+        <v>5.221453908602689</v>
       </c>
       <c r="H10" t="n">
-        <v>5.440228653959134</v>
+        <v>5.441096665241053</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.570414112261725</v>
+        <v>2.814851400989769</v>
       </c>
       <c r="G11" t="n">
-        <v>3.72598976280056</v>
+        <v>4.104431563454307</v>
       </c>
       <c r="H11" t="n">
-        <v>4.984911003187393</v>
+        <v>4.921032392944955</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.808928979470446</v>
+        <v>5.795346036438108</v>
       </c>
       <c r="G12" t="n">
-        <v>5.910113416669162</v>
+        <v>5.88362080055767</v>
       </c>
       <c r="H12" t="n">
-        <v>6.018879444504805</v>
+        <v>6.001954091299062</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.44879183177447</v>
+        <v>9.447583881764444</v>
       </c>
       <c r="G13" t="n">
-        <v>9.66184277749376</v>
+        <v>9.668400394753865</v>
       </c>
       <c r="H13" t="n">
-        <v>9.781893486121293</v>
+        <v>9.765086572712452</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.400770915040113</v>
+        <v>5.412005618930871</v>
       </c>
       <c r="G14" t="n">
-        <v>5.615880107434679</v>
+        <v>5.567118713594059</v>
       </c>
       <c r="H14" t="n">
-        <v>5.916955602536998</v>
+        <v>5.863188981112657</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.519354397103169</v>
+        <v>6.518088748551847</v>
       </c>
       <c r="G15" t="n">
-        <v>6.558750974971417</v>
+        <v>6.555996941234389</v>
       </c>
       <c r="H15" t="n">
-        <v>6.578523023058566</v>
+        <v>6.580381843496737</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.517886153513982</v>
+        <v>3.867618429566554</v>
       </c>
       <c r="G16" t="n">
-        <v>4.619873730198178</v>
+        <v>5.19122048670155</v>
       </c>
       <c r="H16" t="n">
-        <v>5.736853900727662</v>
+        <v>6.099471149154141</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.409866102889359</v>
+        <v>3.33475352112676</v>
       </c>
       <c r="G17" t="n">
-        <v>3.951828529288135</v>
+        <v>3.860727104893</v>
       </c>
       <c r="H17" t="n">
-        <v>4.337646229739253</v>
+        <v>4.238172535211268</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.36310358995111</v>
+        <v>2.362390735035211</v>
       </c>
       <c r="G18" t="n">
-        <v>2.464309223236711</v>
+        <v>2.444110150811109</v>
       </c>
       <c r="H18" t="n">
-        <v>2.565183376263646</v>
+        <v>2.564521551419067</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.488790361969085</v>
+        <v>5.496648649592405</v>
       </c>
       <c r="G19" t="n">
-        <v>5.689301134904268</v>
+        <v>5.679071988298855</v>
       </c>
       <c r="H19" t="n">
-        <v>5.835958296535599</v>
+        <v>5.818697926553889</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8709216150927</v>
+        <v>102.8758732000237</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01829258013697947</v>
+        <v>0.02324416506806445</v>
       </c>
       <c r="T2" t="n">
-        <v>17.80282801825294</v>
+        <v>17.7980275873979</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18774536926671</v>
+        <v>36.18331976059537</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1283553014493155</v>
+        <v>0.1284251237200844</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7373476398777066</v>
+        <v>-0.7369227252804273</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1283485923529722</v>
+        <v>0.1284177418143806</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.928909096798718</v>
+        <v>29.24369190782571</v>
       </c>
       <c r="Z2" t="n">
-        <v>58.44869892302923</v>
+        <v>57.71549993794472</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.7517849517069</v>
+        <v>107.7957687378621</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959265363240084</v>
+        <v>4.959236130617219</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05325394959871961</v>
+        <v>0.0532247169758549</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350454006290991</v>
+        <v>1.350450023086249</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725325331281716</v>
+        <v>1.725327521059698</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795490128868782</v>
+        <v>0.7795519382654719</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664675743177088</v>
+        <v>0.5664664738407779</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785145518973335</v>
+        <v>0.778519256760973</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.362390735035211</v>
+        <v>2.361460239268121</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.444110150811109</v>
+        <v>2.423179070275834</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.564521551419067</v>
+        <v>2.55835503166784</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.365306338028169</v>
+        <v>0.3651935256861365</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246169260851521</v>
+        <v>7.24613188233078</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3281949796076335</v>
+        <v>0.3281576010868915</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293842209860603</v>
+        <v>1.293845223500169</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683851244969865</v>
+        <v>1.683850806980675</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674600939018494</v>
+        <v>0.867460833897872</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371080657049527</v>
+        <v>0.7371082024674023</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473191724451592</v>
+        <v>0.8473307975716902</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.33475352112676</v>
+        <v>3.314120599627243</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.860727104893</v>
+        <v>3.769163765790472</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.238172535211268</v>
+        <v>4.130570713493779</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313229078010291</v>
+        <v>9.313221238744763</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584409739210713</v>
+        <v>0.3584331346555443</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254668979224067</v>
+        <v>1.254669689756912</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747768465606011</v>
+        <v>1.747773519293898</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675084903373049</v>
+        <v>0.8675097622416179</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234770101443364</v>
+        <v>0.723475411004711</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615935460995557</v>
+        <v>0.8615950592010491</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.496648649592405</v>
+        <v>5.492973355822898</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.679071988298855</v>
+        <v>5.656008579828367</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.818697926553889</v>
+        <v>5.80886975479847</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018880730133799</v>
+        <v>7.018899175865864</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880631449804664</v>
+        <v>0.2880815907125321</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482201070125221</v>
+        <v>1.482217500512688</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910813673194301</v>
+        <v>1.910836527214854</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047826774530446</v>
+        <v>0.3047837241536683</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1983393843474104</v>
+        <v>-0.198368049661128</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802302139391833</v>
+        <v>0.2802376568605657</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.518088748551847</v>
+        <v>6.49016220593559</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.555996941234389</v>
+        <v>6.550341575019165</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.580381843496737</v>
+        <v>6.580837218735279</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586366861923605</v>
+        <v>5.58636604277537</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003795025878814066</v>
+        <v>0.003794206730578004</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156138026836602</v>
+        <v>1.156159602873995</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494239956711108</v>
+        <v>1.494265226760757</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088707227426841</v>
+        <v>0.5088616756282007</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07432336259278616</v>
+        <v>0.07429205290617524</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050402716984921</v>
+        <v>0.5050333648463855</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.515237375031438</v>
+        <v>5.496239103607292</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.56988989535896</v>
+        <v>5.557090052906483</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.62</v>
+        <v>5.599608731288852</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116381909788547</v>
+        <v>8.116340357116124</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.236024846322947</v>
+        <v>0.2359832936505255</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445379451668644</v>
+        <v>1.445397557761087</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825088070298521</v>
+        <v>1.825103646029974</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087099873074537</v>
+        <v>0.8087091009615579</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288391849283477</v>
+        <v>0.6288328497536853</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991038087169164</v>
+        <v>0.7991103743729651</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.059164683988866</v>
+        <v>5.060206841357232</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.221453908602689</v>
+        <v>5.181706628823039</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.441096665241053</v>
+        <v>5.429687128042687</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5085035211267606</v>
+        <v>0.508265306122449</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679220518320881</v>
+        <v>7.679160267321614</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06326971757062909</v>
+        <v>0.06320946657136249</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477357590119955</v>
+        <v>1.477366261304021</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919763465345096</v>
+        <v>1.919770671696112</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617419082660241</v>
+        <v>0.7617462262486212</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360867295755278</v>
+        <v>0.5360832467213092</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7598023827856302</v>
+        <v>0.7598106819016059</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.412005618930871</v>
+        <v>5.431964285714287</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.567118713594059</v>
+        <v>5.526004218648634</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.863188981112657</v>
+        <v>5.760036412876894</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61877823187335</v>
+        <v>10.61871878000832</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.313718692135588</v>
+        <v>0.3136592402705576</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051841813319846</v>
+        <v>2.051874874914108</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697479476365682</v>
+        <v>2.697508390854479</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566932738794863</v>
+        <v>0.3566976779306786</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.119922454047829</v>
+        <v>-0.1199464632453688</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3359990868057994</v>
+        <v>0.33601300045829</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.447583881764444</v>
+        <v>9.44985003832026</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.668400394753865</v>
+        <v>9.65775622448235</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.765086572712452</v>
+        <v>9.699442672380615</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218231035951047</v>
+        <v>5.218223993969934</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02764540395332193</v>
+        <v>-0.02765244593443562</v>
       </c>
       <c r="T11" t="n">
-        <v>1.158024978617857</v>
+        <v>1.158039571366848</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477021258137165</v>
+        <v>1.477042200412784</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294484620125537</v>
+        <v>0.4294452399400313</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08268879439609189</v>
+        <v>-0.08271949690326452</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268662916940498</v>
+        <v>0.4268653017233005</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.790021861965309</v>
+        <v>3.797536569232132</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.289764510482488</v>
+        <v>4.284177613329371</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.553660881511556</v>
+        <v>4.503497536945813</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664066742079696</v>
+        <v>7.664051119040069</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722995739166291</v>
+        <v>0.1722839508770019</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148658981503709</v>
+        <v>0.9148694822705695</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198025827639252</v>
+        <v>1.19803523930266</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296434368939056</v>
+        <v>0.8296427624286618</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543275176020253</v>
+        <v>0.6543220863905145</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279730697760215</v>
+        <v>0.8279733065244425</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.031167469411233</v>
+        <v>5.030730942112656</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.292234593917787</v>
+        <v>5.369863226679875</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.766668871950078</v>
+        <v>5.780840909935923</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.858922535211267</v>
+        <v>2.858427163969036</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02960288126553</v>
+        <v>10.02952359738974</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4127281071885881</v>
+        <v>0.4126488233128011</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69398111425679</v>
+        <v>1.69399967284452</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153603093252619</v>
+        <v>2.153634475448457</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232408634733498</v>
+        <v>0.823237638340159</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486083386396118</v>
+        <v>0.6485980976418042</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115071728955867</v>
+        <v>0.8115153595461385</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.120047720058925</v>
+        <v>6.117356167230176</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.566045001199218</v>
+        <v>6.650417952147554</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.132459085695904</v>
+        <v>7.228926047837877</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201999578481583</v>
+        <v>8.20185788614025</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06811597099030586</v>
+        <v>0.06797427864897204</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758707254685627</v>
+        <v>1.75862867076231</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284244148119771</v>
+        <v>2.284179449928313</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809362631339195</v>
+        <v>0.7809574864793749</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652285119146977</v>
+        <v>0.5652531402195509</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806030702435247</v>
+        <v>0.7806267204853484</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.795346036438108</v>
+        <v>5.765238311483428</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.883620800557672</v>
+        <v>5.85493684156391</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.001954091299062</v>
+        <v>5.961898511976426</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82404010830672</v>
+        <v>11.82400006975335</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1398417890795378</v>
+        <v>-0.1398818276328973</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052309283643472</v>
+        <v>2.052292675387153</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697598749840943</v>
+        <v>2.697574181860613</v>
       </c>
       <c r="V15" t="n">
-        <v>0.79489003813926</v>
+        <v>0.794896522287309</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096086289353837</v>
+        <v>0.6096157397659702</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861051964153452</v>
+        <v>0.7861155180144674</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.716559573425161</v>
+        <v>7.715687038338872</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.003437350731138</v>
+        <v>8.057359343154777</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.213961802792225</v>
+        <v>8.266196675375442</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661940962347503</v>
+        <v>8.661792450619464</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2536706856461647</v>
+        <v>0.2535221739181248</v>
       </c>
       <c r="T16" t="n">
-        <v>3.53818889127083</v>
+        <v>3.538160772128218</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06325561399289</v>
+        <v>11.06325346054991</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0495203587752792</v>
+        <v>0.04951770458690176</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971473555968989</v>
+        <v>-0.5971467338331888</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03276739597718059</v>
+        <v>0.03276486527458267</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.81452233334586</v>
+        <v>11.86260563034055</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.12346495306331</v>
+        <v>12.16668449801571</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.25120846792801</v>
+        <v>12.25182016359525</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.91060968490918</v>
+        <v>6.910595331613006</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3709437274623716</v>
+        <v>0.370929374166198</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032070699946114</v>
+        <v>2.032091951763696</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566374756378949</v>
+        <v>2.566393765528388</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210619897327861</v>
+        <v>0.5210616267878774</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02245088951926677</v>
+        <v>0.02243640804426084</v>
       </c>
       <c r="X17" t="n">
-        <v>0.517714161223767</v>
+        <v>0.5177140847055413</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.814851400989769</v>
+        <v>2.59952215296169</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.104431563454307</v>
+        <v>4.114131634213033</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.921032392944955</v>
+        <v>4.945172638312185</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692810667117814</v>
+        <v>6.692788600821713</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1950496823873679</v>
+        <v>0.1950276160912676</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099800818041939</v>
+        <v>1.099821726432015</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489285573230909</v>
+        <v>1.489303517111001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009631667420366</v>
+        <v>0.600960318515796</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174291229780553</v>
+        <v>0.2174102650198118</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980298139582503</v>
+        <v>0.5980293922193101</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.867618429566554</v>
+        <v>3.642449596277713</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.191220486701549</v>
+        <v>5.336001657530754</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.099471149154141</v>
+        <v>6.605165504195869</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16672</v>
+        <v>16673</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15259023226326</v>
+        <v>11.15246392591818</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7832708130255097</v>
+        <v>0.7831445066804361</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038147050741673</v>
+        <v>2.038152854696659</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757700572588251</v>
+        <v>2.75771101288585</v>
       </c>
       <c r="V19" t="n">
-        <v>0.726326796209403</v>
+        <v>0.7263230343675305</v>
       </c>
       <c r="W19" t="n">
-        <v>0.469345162331766</v>
+        <v>0.4693411443430331</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790933064218797</v>
+        <v>0.6791144198627788</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.570996427063744</v>
+        <v>7.528273485817985</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.719601179958024</v>
+        <v>7.696259796959525</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.854540874070603</v>
+        <v>7.820555761779511</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.570996427063744</v>
+        <v>7.528273485817985</v>
       </c>
       <c r="G2" t="n">
-        <v>7.719601179958026</v>
+        <v>7.696259796959526</v>
       </c>
       <c r="H2" t="n">
-        <v>7.854540874070603</v>
+        <v>7.820555761779511</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.515237375031438</v>
+        <v>5.496239103607292</v>
       </c>
       <c r="G3" t="n">
-        <v>5.56988989535896</v>
+        <v>5.557090052906483</v>
       </c>
       <c r="H3" t="n">
-        <v>5.62</v>
+        <v>5.599608731288852</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.790021861965309</v>
+        <v>3.797536569232132</v>
       </c>
       <c r="G4" t="n">
-        <v>4.289764510482488</v>
+        <v>4.284177613329371</v>
       </c>
       <c r="H4" t="n">
-        <v>4.553660881511556</v>
+        <v>4.503497536945813</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.81452233334586</v>
+        <v>11.86260563034055</v>
       </c>
       <c r="G5" t="n">
-        <v>12.12346495306331</v>
+        <v>12.16668449801571</v>
       </c>
       <c r="H5" t="n">
-        <v>12.25120846792801</v>
+        <v>12.25182016359525</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.928909096798718</v>
+        <v>29.24369190782571</v>
       </c>
       <c r="G6" t="n">
-        <v>58.44869892302923</v>
+        <v>57.71549993794472</v>
       </c>
       <c r="H6" t="n">
-        <v>108.7517849517069</v>
+        <v>107.7957687378621</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.716559573425161</v>
+        <v>7.715687038338872</v>
       </c>
       <c r="G7" t="n">
-        <v>8.003437350731138</v>
+        <v>8.057359343154779</v>
       </c>
       <c r="H7" t="n">
-        <v>8.213961802792225</v>
+        <v>8.266196675375442</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.120047720058925</v>
+        <v>6.117356167230176</v>
       </c>
       <c r="G8" t="n">
-        <v>6.566045001199218</v>
+        <v>6.650417952147554</v>
       </c>
       <c r="H8" t="n">
-        <v>7.132459085695904</v>
+        <v>7.228926047837877</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.031167469411233</v>
+        <v>5.030730942112656</v>
       </c>
       <c r="G9" t="n">
-        <v>5.292234593917787</v>
+        <v>5.369863226679874</v>
       </c>
       <c r="H9" t="n">
-        <v>5.766668871950078</v>
+        <v>5.780840909935923</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.059164683988866</v>
+        <v>5.060206841357232</v>
       </c>
       <c r="G10" t="n">
-        <v>5.221453908602689</v>
+        <v>5.181706628823039</v>
       </c>
       <c r="H10" t="n">
-        <v>5.441096665241053</v>
+        <v>5.429687128042687</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.814851400989769</v>
+        <v>2.59952215296169</v>
       </c>
       <c r="G11" t="n">
-        <v>4.104431563454307</v>
+        <v>4.114131634213033</v>
       </c>
       <c r="H11" t="n">
-        <v>4.921032392944955</v>
+        <v>4.945172638312185</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.795346036438108</v>
+        <v>5.765238311483428</v>
       </c>
       <c r="G12" t="n">
-        <v>5.88362080055767</v>
+        <v>5.854936841563911</v>
       </c>
       <c r="H12" t="n">
-        <v>6.001954091299062</v>
+        <v>5.961898511976426</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.447583881764444</v>
+        <v>9.44985003832026</v>
       </c>
       <c r="G13" t="n">
-        <v>9.668400394753865</v>
+        <v>9.657756224482348</v>
       </c>
       <c r="H13" t="n">
-        <v>9.765086572712452</v>
+        <v>9.699442672380615</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.412005618930871</v>
+        <v>5.431964285714287</v>
       </c>
       <c r="G14" t="n">
-        <v>5.567118713594059</v>
+        <v>5.526004218648634</v>
       </c>
       <c r="H14" t="n">
-        <v>5.863188981112657</v>
+        <v>5.760036412876894</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.518088748551847</v>
+        <v>6.49016220593559</v>
       </c>
       <c r="G15" t="n">
-        <v>6.555996941234389</v>
+        <v>6.550341575019165</v>
       </c>
       <c r="H15" t="n">
-        <v>6.580381843496737</v>
+        <v>6.580837218735279</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.867618429566554</v>
+        <v>3.642449596277713</v>
       </c>
       <c r="G16" t="n">
-        <v>5.19122048670155</v>
+        <v>5.336001657530754</v>
       </c>
       <c r="H16" t="n">
-        <v>6.099471149154141</v>
+        <v>6.605165504195869</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.33475352112676</v>
+        <v>3.314120599627243</v>
       </c>
       <c r="G17" t="n">
-        <v>3.860727104893</v>
+        <v>3.769163765790472</v>
       </c>
       <c r="H17" t="n">
-        <v>4.238172535211268</v>
+        <v>4.130570713493779</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.362390735035211</v>
+        <v>2.361460239268121</v>
       </c>
       <c r="G18" t="n">
-        <v>2.444110150811109</v>
+        <v>2.423179070275834</v>
       </c>
       <c r="H18" t="n">
-        <v>2.564521551419067</v>
+        <v>2.55835503166784</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.496648649592405</v>
+        <v>5.492973355822898</v>
       </c>
       <c r="G19" t="n">
-        <v>5.679071988298855</v>
+        <v>5.656008579828367</v>
       </c>
       <c r="H19" t="n">
-        <v>5.818697926553889</v>
+        <v>5.80886975479847</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8758732000237</v>
+        <v>102.8797425257855</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02324416506806445</v>
+        <v>0.02711349082977949</v>
       </c>
       <c r="T2" t="n">
-        <v>17.7980275873979</v>
+        <v>17.79431188873552</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18331976059537</v>
+        <v>36.18211242194685</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284251237200844</v>
+        <v>0.1284657359251865</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7369227252804273</v>
+        <v>-0.7368068144705235</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284177418143806</v>
+        <v>0.1284582594921391</v>
       </c>
       <c r="Y2" t="n">
-        <v>29.24369190782571</v>
+        <v>6.891696115617952</v>
       </c>
       <c r="Z2" t="n">
-        <v>57.71549993794472</v>
+        <v>59.50207249202018</v>
       </c>
       <c r="AA2" t="n">
-        <v>107.7957687378621</v>
+        <v>108.9327110709404</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959236130617219</v>
+        <v>4.959207015582241</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0532247169758549</v>
+        <v>0.05319560194087663</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350450023086249</v>
+        <v>1.350445732557895</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725327521059698</v>
+        <v>1.725330030730464</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795519382654719</v>
+        <v>0.7795547823329856</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664664738407779</v>
+        <v>0.5664652125994254</v>
       </c>
       <c r="X3" t="n">
-        <v>0.778519256760973</v>
+        <v>0.7785238776638026</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.361460239268121</v>
+        <v>2.359661128691983</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.423179070275834</v>
+        <v>2.402670620729535</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.55835503166784</v>
+        <v>2.536770824752647</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3651935256861365</v>
+        <v>0.3650808720112517</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.24613188233078</v>
+        <v>7.246096744397481</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3281576010868915</v>
+        <v>0.3281224631535925</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293845223500169</v>
+        <v>1.293852883029755</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683850806980675</v>
+        <v>1.683854028530396</v>
       </c>
       <c r="V4" t="n">
-        <v>0.867460833897872</v>
+        <v>0.8674609707540889</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371082024674023</v>
+        <v>0.7371071965352809</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473307975716902</v>
+        <v>0.8473414530297958</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.314120599627243</v>
+        <v>3.248375603039531</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.769163765790472</v>
+        <v>3.673625333612367</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.130570713493779</v>
+        <v>4.069562032615657</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313221238744763</v>
+        <v>9.313211498176619</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584331346555443</v>
+        <v>0.3584233940873984</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254669689756912</v>
+        <v>1.254669263396156</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747773519293898</v>
+        <v>1.747777323314675</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675097622416179</v>
+        <v>0.8675112804682031</v>
       </c>
       <c r="W5" t="n">
-        <v>0.723475411004711</v>
+        <v>0.723474207294488</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615950592010491</v>
+        <v>0.8615968691064078</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.492973355822898</v>
+        <v>5.489673563911233</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.656008579828367</v>
+        <v>5.623615167183888</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.80886975479847</v>
+        <v>5.804165543898018</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018899175865864</v>
+        <v>7.018918225053896</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880815907125321</v>
+        <v>0.288100639900563</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482217500512688</v>
+        <v>1.482233424086887</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910836527214854</v>
+        <v>1.910858968301329</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047837241536683</v>
+        <v>0.3047848237259185</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.198368049661128</v>
+        <v>-0.1983961973739887</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802376568605657</v>
+        <v>0.2802450106092189</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.49016220593559</v>
+        <v>6.453719721831536</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.550341575019165</v>
+        <v>6.541272596817616</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.580837218735279</v>
+        <v>6.581432784369243</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.58636604277537</v>
+        <v>5.58636718854196</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003794206730578004</v>
+        <v>0.003795352497168522</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156159602873995</v>
+        <v>1.156183617069646</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494265226760757</v>
+        <v>1.494291955743465</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088616756282007</v>
+        <v>0.5088517069482063</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07429205290617524</v>
+        <v>0.07425893501978165</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050333648463855</v>
+        <v>0.5050255526801432</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.496239103607292</v>
+        <v>5.487648907238925</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.557090052906483</v>
+        <v>5.544920194473617</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.599608731288852</v>
+        <v>5.586930986754096</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116340357116124</v>
+        <v>8.116299885261766</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2359832936505255</v>
+        <v>0.235942821796166</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445397557761087</v>
+        <v>1.445420163324311</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825103646029974</v>
+        <v>1.825120788358995</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087091009615579</v>
+        <v>0.8087078408435231</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288328497536853</v>
+        <v>0.6288258773285234</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991103743729651</v>
+        <v>0.7991164360867514</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.060206841357232</v>
+        <v>5.059370659722222</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.181706628823039</v>
+        <v>5.144600114744231</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.429687128042687</v>
+        <v>5.359753587258659</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.508265306122449</v>
+        <v>0.5080274261603376</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679160267321614</v>
+        <v>7.679105540756113</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06320946657136249</v>
+        <v>0.06315474000586045</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477366261304021</v>
+        <v>1.477375379228216</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919770671696112</v>
+        <v>1.919780533363179</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617462262486212</v>
+        <v>0.7617496102566792</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360832467213092</v>
+        <v>0.5360784805225273</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7598106819016059</v>
+        <v>0.759817844902126</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.431964285714287</v>
+        <v>5.428976793248945</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.526004218648634</v>
+        <v>5.49614602285335</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.760036412876894</v>
+        <v>5.668090717299577</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61871878000832</v>
+        <v>10.61865976977615</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3136592402705576</v>
+        <v>0.3136002300383941</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051874874914108</v>
+        <v>2.051915849622194</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697508390854479</v>
+        <v>2.697540431137553</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3566976779306786</v>
+        <v>0.3567005478422564</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1199464632453688</v>
+        <v>-0.1199730682523727</v>
       </c>
       <c r="X10" t="n">
-        <v>0.33601300045829</v>
+        <v>0.3360254180021119</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.44985003832026</v>
+        <v>9.182855475554524</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.65775622448235</v>
+        <v>9.619819980339354</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.699442672380615</v>
+        <v>9.701890160090331</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218223993969934</v>
+        <v>5.218216388146794</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02765244593443562</v>
+        <v>-0.02766005175757559</v>
       </c>
       <c r="T11" t="n">
-        <v>1.158039571366848</v>
+        <v>1.158054424589669</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477042200412784</v>
+        <v>1.477063945298363</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294452399400313</v>
+        <v>0.4294416498371947</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08271949690326452</v>
+        <v>-0.08275137654065179</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268653017233005</v>
+        <v>0.4268639857352431</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.797536569232132</v>
+        <v>3.758640027251229</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.284177613329371</v>
+        <v>4.235216426091563</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.503497536945813</v>
+        <v>4.506821378340366</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664051119040069</v>
+        <v>7.664036526140015</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722839508770019</v>
+        <v>0.1722693579769463</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148694822705695</v>
+        <v>0.9148736977907455</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19803523930266</v>
+        <v>1.198044877921741</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296427624286618</v>
+        <v>0.8296419572801061</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543220863905145</v>
+        <v>0.6543165241649176</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279733065244425</v>
+        <v>0.8279733690175385</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.030730942112656</v>
+        <v>5.030151159135315</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.369863226679875</v>
+        <v>5.409786494097125</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.780840909935923</v>
+        <v>5.781067035963294</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.858427163969036</v>
+        <v>2.857932489451477</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02952359738974</v>
+        <v>10.02947506095348</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4126488233128011</v>
+        <v>0.4126002868765352</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69399967284452</v>
+        <v>1.69403609950756</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153634475448457</v>
+        <v>2.153686105640179</v>
       </c>
       <c r="V13" t="n">
-        <v>0.823237638340159</v>
+        <v>0.8232307179722214</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485980976418042</v>
+        <v>0.648581248761205</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115153595461385</v>
+        <v>0.8115169364620614</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.117356167230176</v>
+        <v>6.1136317923495</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.650417952147554</v>
+        <v>6.762819955577095</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.228926047837877</v>
+        <v>7.322945094112205</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.20185788614025</v>
+        <v>8.201719380662595</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06797427864897204</v>
+        <v>0.06783577317131788</v>
       </c>
       <c r="T14" t="n">
-        <v>1.75862867076231</v>
+        <v>1.758550760523274</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284179449928313</v>
+        <v>2.284116319629998</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809574864793749</v>
+        <v>0.7809782770210071</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652531402195509</v>
+        <v>0.5652771710107193</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806267204853484</v>
+        <v>0.7806498853763374</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.765238311483428</v>
+        <v>5.750527098537789</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.85493684156391</v>
+        <v>5.826936603439402</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.961898511976426</v>
+        <v>5.920734849371494</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82400006975335</v>
+        <v>11.82395866754132</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1398818276328973</v>
+        <v>-0.1399232298449313</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052292675387153</v>
+        <v>2.052274824825906</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697574181860613</v>
+        <v>2.697548921593134</v>
       </c>
       <c r="V15" t="n">
-        <v>0.794896522287309</v>
+        <v>0.7949031850423254</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096157397659702</v>
+        <v>0.6096230509010849</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861155180144674</v>
+        <v>0.7861261136114155</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.715687038338872</v>
+        <v>7.755113673185671</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.057359343154777</v>
+        <v>8.118285752125399</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.266196675375442</v>
+        <v>8.323571628830614</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661792450619464</v>
+        <v>8.661639902554036</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2535221739181248</v>
+        <v>0.2533696258526975</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538160772128218</v>
+        <v>3.538134661283621</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06325346054991</v>
+        <v>11.06325087227946</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04951770458690176</v>
+        <v>0.04951503087777295</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971467338331888</v>
+        <v>-0.5971459865218789</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03276486527458267</v>
+        <v>0.03276231448537348</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.86260563034055</v>
+        <v>12.08533829264826</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.16668449801571</v>
+        <v>12.21014036015968</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.25182016359525</v>
+        <v>12.29491250220567</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910595331613006</v>
+        <v>6.910588458779021</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.370929374166198</v>
+        <v>0.3709225013322117</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032091951763696</v>
+        <v>2.03212164841967</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566393765528388</v>
+        <v>2.566415813879682</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210616267878774</v>
+        <v>0.5210592125645072</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02243640804426084</v>
+        <v>0.02241961112216506</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177140847055413</v>
+        <v>0.5177118318255046</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.59952215296169</v>
+        <v>2.55757688206244</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.114131634213033</v>
+        <v>3.982664411644803</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.945172638312185</v>
+        <v>4.947511820198892</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692788600821713</v>
+        <v>6.692756183587846</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1950276160912676</v>
+        <v>0.1949951988574013</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099821726432015</v>
+        <v>1.099836384996849</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489303517111001</v>
+        <v>1.489316086004865</v>
       </c>
       <c r="V18" t="n">
-        <v>0.600960318515796</v>
+        <v>0.6009611533088729</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2174102650198118</v>
+        <v>0.217397055719341</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980293922193101</v>
+        <v>0.5980331188426484</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.642449596277713</v>
+        <v>3.541494477243642</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.336001657530754</v>
+        <v>5.198416631064318</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.605165504195869</v>
+        <v>6.425523053612531</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16673</v>
+        <v>16674</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15246392591818</v>
+        <v>11.15233799871728</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7831445066804361</v>
+        <v>0.783018579479531</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038152854696659</v>
+        <v>2.038159129415761</v>
       </c>
       <c r="U19" t="n">
-        <v>2.75771101288585</v>
+        <v>2.757722035722342</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263230343675305</v>
+        <v>0.7263191882840598</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693411443430331</v>
+        <v>0.4693369021454554</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6791144198627788</v>
+        <v>0.6791355077708079</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.528273485817985</v>
+        <v>7.521950960806005</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.696259796959525</v>
+        <v>7.663961391538807</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.820555761779511</v>
+        <v>7.800685733962482</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.528273485817985</v>
+        <v>7.521950960806005</v>
       </c>
       <c r="G2" t="n">
-        <v>7.696259796959526</v>
+        <v>7.663961391538807</v>
       </c>
       <c r="H2" t="n">
-        <v>7.820555761779511</v>
+        <v>7.800685733962482</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.496239103607292</v>
+        <v>5.487648907238925</v>
       </c>
       <c r="G3" t="n">
-        <v>5.557090052906483</v>
+        <v>5.544920194473617</v>
       </c>
       <c r="H3" t="n">
-        <v>5.599608731288852</v>
+        <v>5.586930986754096</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.797536569232132</v>
+        <v>3.758640027251229</v>
       </c>
       <c r="G4" t="n">
-        <v>4.284177613329371</v>
+        <v>4.235216426091563</v>
       </c>
       <c r="H4" t="n">
-        <v>4.503497536945813</v>
+        <v>4.506821378340366</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.86260563034055</v>
+        <v>12.08533829264826</v>
       </c>
       <c r="G5" t="n">
-        <v>12.16668449801571</v>
+        <v>12.21014036015968</v>
       </c>
       <c r="H5" t="n">
-        <v>12.25182016359525</v>
+        <v>12.29491250220567</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>29.24369190782571</v>
+        <v>6.891696115617952</v>
       </c>
       <c r="G6" t="n">
-        <v>57.71549993794472</v>
+        <v>59.50207249202018</v>
       </c>
       <c r="H6" t="n">
-        <v>107.7957687378621</v>
+        <v>108.9327110709404</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.715687038338872</v>
+        <v>7.755113673185671</v>
       </c>
       <c r="G7" t="n">
-        <v>8.057359343154779</v>
+        <v>8.118285752125399</v>
       </c>
       <c r="H7" t="n">
-        <v>8.266196675375442</v>
+        <v>8.323571628830614</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.117356167230176</v>
+        <v>6.1136317923495</v>
       </c>
       <c r="G8" t="n">
-        <v>6.650417952147554</v>
+        <v>6.762819955577095</v>
       </c>
       <c r="H8" t="n">
-        <v>7.228926047837877</v>
+        <v>7.322945094112205</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.030730942112656</v>
+        <v>5.030151159135315</v>
       </c>
       <c r="G9" t="n">
-        <v>5.369863226679874</v>
+        <v>5.409786494097125</v>
       </c>
       <c r="H9" t="n">
-        <v>5.780840909935923</v>
+        <v>5.781067035963294</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.060206841357232</v>
+        <v>5.059370659722222</v>
       </c>
       <c r="G10" t="n">
-        <v>5.181706628823039</v>
+        <v>5.144600114744231</v>
       </c>
       <c r="H10" t="n">
-        <v>5.429687128042687</v>
+        <v>5.359753587258659</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.59952215296169</v>
+        <v>2.55757688206244</v>
       </c>
       <c r="G11" t="n">
-        <v>4.114131634213033</v>
+        <v>3.982664411644802</v>
       </c>
       <c r="H11" t="n">
-        <v>4.945172638312185</v>
+        <v>4.947511820198892</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.765238311483428</v>
+        <v>5.750527098537789</v>
       </c>
       <c r="G12" t="n">
-        <v>5.854936841563911</v>
+        <v>5.826936603439402</v>
       </c>
       <c r="H12" t="n">
-        <v>5.961898511976426</v>
+        <v>5.920734849371494</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.44985003832026</v>
+        <v>9.182855475554524</v>
       </c>
       <c r="G13" t="n">
-        <v>9.657756224482348</v>
+        <v>9.619819980339354</v>
       </c>
       <c r="H13" t="n">
-        <v>9.699442672380615</v>
+        <v>9.701890160090331</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.431964285714287</v>
+        <v>5.428976793248945</v>
       </c>
       <c r="G14" t="n">
-        <v>5.526004218648634</v>
+        <v>5.49614602285335</v>
       </c>
       <c r="H14" t="n">
-        <v>5.760036412876894</v>
+        <v>5.668090717299577</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.49016220593559</v>
+        <v>6.453719721831536</v>
       </c>
       <c r="G15" t="n">
-        <v>6.550341575019165</v>
+        <v>6.541272596817616</v>
       </c>
       <c r="H15" t="n">
-        <v>6.580837218735279</v>
+        <v>6.581432784369243</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.642449596277713</v>
+        <v>3.541494477243642</v>
       </c>
       <c r="G16" t="n">
-        <v>5.336001657530754</v>
+        <v>5.198416631064318</v>
       </c>
       <c r="H16" t="n">
-        <v>6.605165504195869</v>
+        <v>6.425523053612531</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.314120599627243</v>
+        <v>3.248375603039531</v>
       </c>
       <c r="G17" t="n">
-        <v>3.769163765790472</v>
+        <v>3.673625333612367</v>
       </c>
       <c r="H17" t="n">
-        <v>4.130570713493779</v>
+        <v>4.069562032615657</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.361460239268121</v>
+        <v>2.359661128691983</v>
       </c>
       <c r="G18" t="n">
-        <v>2.423179070275834</v>
+        <v>2.402670620729534</v>
       </c>
       <c r="H18" t="n">
-        <v>2.55835503166784</v>
+        <v>2.536770824752647</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.492973355822898</v>
+        <v>5.489673563911233</v>
       </c>
       <c r="G19" t="n">
-        <v>5.656008579828367</v>
+        <v>5.623615167183889</v>
       </c>
       <c r="H19" t="n">
-        <v>5.80886975479847</v>
+        <v>5.804165543898018</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8797425257855</v>
+        <v>102.8799635705354</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02711349082977949</v>
+        <v>0.02733453557967147</v>
       </c>
       <c r="T2" t="n">
-        <v>17.79431188873552</v>
+        <v>17.79426693433119</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18211242194685</v>
+        <v>36.18219862143121</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284657359251865</v>
+        <v>0.1284664476710176</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7368068144705235</v>
+        <v>-0.7368150899425818</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284582594921391</v>
+        <v>0.1284589935926443</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.891696115617952</v>
+        <v>25.37509080525783</v>
       </c>
       <c r="Z2" t="n">
-        <v>59.50207249202018</v>
+        <v>70.93375663856884</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.9327110709404</v>
+        <v>108.9891001154161</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959207015582241</v>
+        <v>4.959180711184412</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05319560194087663</v>
+        <v>0.05316929754304758</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350445732557895</v>
+        <v>1.350442540230949</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725330030730464</v>
+        <v>1.725333779285397</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795547823329856</v>
+        <v>0.7795571114275331</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664652125994254</v>
+        <v>0.5664633287503038</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785238776638026</v>
+        <v>0.778527867601758</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.359661128691983</v>
+        <v>2.358138762005153</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.402670620729535</v>
+        <v>2.388903248066122</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.536770824752647</v>
+        <v>2.535164260516096</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3650808720112517</v>
+        <v>0.3649683766690091</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246096744397481</v>
+        <v>7.246064939632997</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3281224631535925</v>
+        <v>0.3280906583891096</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293852883029755</v>
+        <v>1.293861279143206</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683854028530396</v>
+        <v>1.683858991168306</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674609707540889</v>
+        <v>0.8674608729011417</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371071965352809</v>
+        <v>0.7371056469428658</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473414530297958</v>
+        <v>0.8473514833716889</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.248375603039531</v>
+        <v>3.219443629079191</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.673625333612367</v>
+        <v>3.612644062726424</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.069562032615657</v>
+        <v>4.067086380179298</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313211498176619</v>
+        <v>9.313200449414685</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584233940873984</v>
+        <v>0.3584123453254677</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254669263396156</v>
+        <v>1.254666361061508</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747777323314675</v>
+        <v>1.747779963031171</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675112804682031</v>
+        <v>0.8675130352997911</v>
       </c>
       <c r="W5" t="n">
-        <v>0.723474207294488</v>
+        <v>0.7234733720047307</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615968691064078</v>
+        <v>0.8615989467826963</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.489673563911233</v>
+        <v>5.488872668926053</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.623615167183888</v>
+        <v>5.609666658126889</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.804165543898018</v>
+        <v>5.803284190739974</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018918225053896</v>
+        <v>7.018937193327051</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.288100639900563</v>
+        <v>0.2881196081737187</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482233424086887</v>
+        <v>1.482248275251922</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910858968301329</v>
+        <v>1.91088143838154</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047848237259185</v>
+        <v>0.3047860895017538</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1983961973739887</v>
+        <v>-0.1984243817847187</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802450106092189</v>
+        <v>0.2802526038631767</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.453719721831536</v>
+        <v>6.428590233663111</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.541272596817616</v>
+        <v>6.53111181897828</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.581432784369243</v>
+        <v>6.582013281631135</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.58636718854196</v>
+        <v>5.586368872412248</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003795352497168522</v>
+        <v>0.003797036367457302</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156183617069646</v>
+        <v>1.156207374788974</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494291955743465</v>
+        <v>1.494317837755257</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088517069482063</v>
+        <v>0.5088421412693735</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07425893501978165</v>
+        <v>0.07422686598726258</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050255526801432</v>
+        <v>0.5050180970074261</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.487648907238925</v>
+        <v>5.478291806265464</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.544920194473617</v>
+        <v>5.534711959501228</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.586930986754096</v>
+        <v>5.587091033755049</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116299885261766</v>
+        <v>8.116266867442061</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.235942821796166</v>
+        <v>0.235909803976461</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445420163324311</v>
+        <v>1.445442699383002</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825120788358995</v>
+        <v>1.825141240719321</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087078408435231</v>
+        <v>0.8087057351970074</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288258773285234</v>
+        <v>0.6288175585043847</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991164360867514</v>
+        <v>0.7991209227047704</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.059370659722222</v>
+        <v>5.058761035224877</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.144600114744231</v>
+        <v>5.122370766193518</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.359753587258659</v>
+        <v>5.356963518990357</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5080274261603376</v>
+        <v>0.5077898805340829</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679105540756113</v>
+        <v>7.679058559139315</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06315474000586045</v>
+        <v>0.06310775838906232</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477375379228216</v>
+        <v>1.477387750083575</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919780533363179</v>
+        <v>1.919798063213711</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617496102566792</v>
+        <v>0.7617507566561439</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360784805225273</v>
+        <v>0.5360700081874006</v>
       </c>
       <c r="X9" t="n">
-        <v>0.759817844902126</v>
+        <v>0.7598225274086957</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.428976793248945</v>
+        <v>5.423281799016165</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.49614602285335</v>
+        <v>5.482431455717327</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.668090717299577</v>
+        <v>5.669546732255798</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61865976977615</v>
+        <v>10.61860070943681</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3136002300383941</v>
+        <v>0.3135411696990473</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051915849622194</v>
+        <v>2.051956992400397</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697540431137553</v>
+        <v>2.69757224581799</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567005478422564</v>
+        <v>0.3567035482520799</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1199730682523727</v>
+        <v>-0.1199994862403828</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360254180021119</v>
+        <v>0.336037968487225</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.182855475554524</v>
+        <v>9.024699896007288</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.619819980339354</v>
+        <v>9.576767697215713</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.701890160090331</v>
+        <v>9.704195340954358</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218216388146794</v>
+        <v>5.218203102275945</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02766005175757559</v>
+        <v>-0.02767333762842325</v>
       </c>
       <c r="T11" t="n">
-        <v>1.158054424589669</v>
+        <v>1.158069985759435</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477063945298363</v>
+        <v>1.477086048859137</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294416498371947</v>
+        <v>0.4294392068066683</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08275137654065179</v>
+        <v>-0.08278378250384888</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268639857352431</v>
+        <v>0.4268640322819051</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.758640027251229</v>
+        <v>3.679434081906056</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.235216426091563</v>
+        <v>4.173635104817662</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.506821378340366</v>
+        <v>4.510035137034434</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664036526140015</v>
+        <v>7.664022034821261</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722693579769463</v>
+        <v>0.1722548666581936</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148736977907455</v>
+        <v>0.9148781869788847</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198044877921741</v>
+        <v>1.198055460957254</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296419572801061</v>
+        <v>0.8296408897617582</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543165241649176</v>
+        <v>0.6543104168867563</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279733690175385</v>
+        <v>0.8279731700879114</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.030151159135315</v>
+        <v>5.029591231626475</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.409786494097125</v>
+        <v>5.430983170732152</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.781067035963294</v>
+        <v>5.786957675712982</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.857932489451477</v>
+        <v>2.85743851018974</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02947506095348</v>
+        <v>10.02943285489229</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4126002868765352</v>
+        <v>0.4125580808153484</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69403609950756</v>
+        <v>1.694072130679657</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153686105640179</v>
+        <v>2.153736081118427</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232307179722214</v>
+        <v>0.823224000941999</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648581248761205</v>
+        <v>0.648564939491367</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115169364620614</v>
+        <v>0.8115179839103567</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.1136317923495</v>
+        <v>6.110704632927254</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.762819955577095</v>
+        <v>6.856755638233861</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.322945094112205</v>
+        <v>7.362671604948501</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201719380662595</v>
+        <v>8.201584540742184</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06783577317131788</v>
+        <v>0.06770093325090677</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758550760523274</v>
+        <v>1.758476512236222</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284116319629998</v>
+        <v>2.284056251690035</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809782770210071</v>
+        <v>0.7809983169726691</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652771710107193</v>
+        <v>0.5653000354867603</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806498853763374</v>
+        <v>0.7806722396811139</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.750527098537789</v>
+        <v>5.737499999999999</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.826936603439402</v>
+        <v>5.808318121711054</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.920734849371494</v>
+        <v>5.916268322716139</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82395866754132</v>
+        <v>11.82391510973876</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1399232298449313</v>
+        <v>-0.139966787647493</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052274824825906</v>
+        <v>2.052255639338034</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697548921593134</v>
+        <v>2.697523543929119</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949031850423254</v>
+        <v>0.7949099719612587</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096230509010849</v>
+        <v>0.6096303959455982</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861261136114155</v>
+        <v>0.786136977042404</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.755113673185671</v>
+        <v>7.753831091546047</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.118285752125399</v>
+        <v>8.16280926682194</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.323571628830614</v>
+        <v>8.348142062766122</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661639902554036</v>
+        <v>8.661472209028549</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2533696258526975</v>
+        <v>0.253201932327209</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538134661283621</v>
+        <v>3.538098400246003</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06325087227946</v>
+        <v>11.06324503142441</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04951503087777295</v>
+        <v>0.04951214367820555</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971459865218789</v>
+        <v>-0.5971443000924841</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03276231448537348</v>
+        <v>0.0327594690319214</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.08533829264826</v>
+        <v>12.08279764732665</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.21014036015968</v>
+        <v>12.23218665513539</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.29491250220567</v>
+        <v>12.37854493336474</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910588458779021</v>
+        <v>6.910566906081492</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3709225013322117</v>
+        <v>0.3709009486346828</v>
       </c>
       <c r="T17" t="n">
-        <v>2.03212164841967</v>
+        <v>2.032143729437636</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566415813879682</v>
+        <v>2.566434250896705</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210592125645072</v>
+        <v>0.5210596614041626</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02241961112216506</v>
+        <v>0.02240556528367366</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177118318255046</v>
+        <v>0.517712693087703</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.55757688206244</v>
+        <v>2.556812597535341</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.982664411644803</v>
+        <v>4.124587295383273</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.947511820198892</v>
+        <v>6.285882693511653</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692756183587846</v>
+        <v>6.692707140164901</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1949951988574013</v>
+        <v>0.1949461554344562</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099836384996849</v>
+        <v>1.099836727255959</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489316086004865</v>
+        <v>1.48932171235413</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009611533088729</v>
+        <v>0.6009658871533028</v>
       </c>
       <c r="W18" t="n">
-        <v>0.217397055719341</v>
+        <v>0.2173911426618522</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980331188426484</v>
+        <v>0.59804123128285</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.541494477243642</v>
+        <v>3.540404178946212</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.198416631064318</v>
+        <v>5.291650620458647</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.425523053612531</v>
+        <v>6.782203911291773</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16674</v>
+        <v>16675</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15233799871728</v>
+        <v>11.15221410937033</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.783018579479531</v>
+        <v>0.7828946901325792</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038159129415761</v>
+        <v>2.038161735984791</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757722035722342</v>
+        <v>2.757731235595638</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263191882840598</v>
+        <v>0.7263158114371486</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693369021454554</v>
+        <v>0.4693333615120316</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6791355077708079</v>
+        <v>0.6791566942341747</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.521950960806005</v>
+        <v>7.519986720419787</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.663961391538807</v>
+        <v>7.636055277931773</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.800685733962482</v>
+        <v>7.796495360457675</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.521950960806005</v>
+        <v>7.519986720419787</v>
       </c>
       <c r="G2" t="n">
-        <v>7.663961391538807</v>
+        <v>7.636055277931773</v>
       </c>
       <c r="H2" t="n">
-        <v>7.800685733962482</v>
+        <v>7.796495360457675</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.487648907238925</v>
+        <v>5.478291806265464</v>
       </c>
       <c r="G3" t="n">
-        <v>5.544920194473617</v>
+        <v>5.534711959501228</v>
       </c>
       <c r="H3" t="n">
-        <v>5.586930986754096</v>
+        <v>5.587091033755049</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.758640027251229</v>
+        <v>3.679434081906056</v>
       </c>
       <c r="G4" t="n">
-        <v>4.235216426091563</v>
+        <v>4.173635104817661</v>
       </c>
       <c r="H4" t="n">
-        <v>4.506821378340366</v>
+        <v>4.510035137034434</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.08533829264826</v>
+        <v>12.08279764732665</v>
       </c>
       <c r="G5" t="n">
-        <v>12.21014036015968</v>
+        <v>12.23218665513539</v>
       </c>
       <c r="H5" t="n">
-        <v>12.29491250220567</v>
+        <v>12.37854493336474</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.891696115617952</v>
+        <v>25.37509080525783</v>
       </c>
       <c r="G6" t="n">
-        <v>59.50207249202018</v>
+        <v>70.93375663856884</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9327110709404</v>
+        <v>108.9891001154161</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.755113673185671</v>
+        <v>7.753831091546047</v>
       </c>
       <c r="G7" t="n">
-        <v>8.118285752125399</v>
+        <v>8.162809266821938</v>
       </c>
       <c r="H7" t="n">
-        <v>8.323571628830614</v>
+        <v>8.348142062766122</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.1136317923495</v>
+        <v>6.110704632927254</v>
       </c>
       <c r="G8" t="n">
-        <v>6.762819955577095</v>
+        <v>6.856755638233861</v>
       </c>
       <c r="H8" t="n">
-        <v>7.322945094112205</v>
+        <v>7.362671604948501</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.030151159135315</v>
+        <v>5.029591231626475</v>
       </c>
       <c r="G9" t="n">
-        <v>5.409786494097125</v>
+        <v>5.430983170732152</v>
       </c>
       <c r="H9" t="n">
-        <v>5.781067035963294</v>
+        <v>5.786957675712982</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.059370659722222</v>
+        <v>5.058761035224877</v>
       </c>
       <c r="G10" t="n">
-        <v>5.144600114744231</v>
+        <v>5.122370766193518</v>
       </c>
       <c r="H10" t="n">
-        <v>5.359753587258659</v>
+        <v>5.356963518990357</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.55757688206244</v>
+        <v>2.556812597535341</v>
       </c>
       <c r="G11" t="n">
-        <v>3.982664411644802</v>
+        <v>4.124587295383273</v>
       </c>
       <c r="H11" t="n">
-        <v>4.947511820198892</v>
+        <v>6.285882693511653</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.750527098537789</v>
+        <v>5.737499999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>5.826936603439402</v>
+        <v>5.808318121711054</v>
       </c>
       <c r="H12" t="n">
-        <v>5.920734849371494</v>
+        <v>5.916268322716139</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.182855475554524</v>
+        <v>9.024699896007288</v>
       </c>
       <c r="G13" t="n">
-        <v>9.619819980339354</v>
+        <v>9.576767697215713</v>
       </c>
       <c r="H13" t="n">
-        <v>9.701890160090331</v>
+        <v>9.704195340954358</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.428976793248945</v>
+        <v>5.423281799016165</v>
       </c>
       <c r="G14" t="n">
-        <v>5.49614602285335</v>
+        <v>5.482431455717327</v>
       </c>
       <c r="H14" t="n">
-        <v>5.668090717299577</v>
+        <v>5.669546732255798</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.453719721831536</v>
+        <v>6.428590233663111</v>
       </c>
       <c r="G15" t="n">
-        <v>6.541272596817616</v>
+        <v>6.53111181897828</v>
       </c>
       <c r="H15" t="n">
-        <v>6.581432784369243</v>
+        <v>6.582013281631135</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.541494477243642</v>
+        <v>3.540404178946212</v>
       </c>
       <c r="G16" t="n">
-        <v>5.198416631064318</v>
+        <v>5.291650620458647</v>
       </c>
       <c r="H16" t="n">
-        <v>6.425523053612531</v>
+        <v>6.782203911291773</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.248375603039531</v>
+        <v>3.219443629079191</v>
       </c>
       <c r="G17" t="n">
-        <v>3.673625333612367</v>
+        <v>3.612644062726424</v>
       </c>
       <c r="H17" t="n">
-        <v>4.069562032615657</v>
+        <v>4.067086380179298</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.359661128691983</v>
+        <v>2.358138762005153</v>
       </c>
       <c r="G18" t="n">
-        <v>2.402670620729534</v>
+        <v>2.388903248066122</v>
       </c>
       <c r="H18" t="n">
-        <v>2.536770824752647</v>
+        <v>2.535164260516096</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.489673563911233</v>
+        <v>5.488872668926053</v>
       </c>
       <c r="G19" t="n">
-        <v>5.623615167183889</v>
+        <v>5.609666658126889</v>
       </c>
       <c r="H19" t="n">
-        <v>5.804165543898018</v>
+        <v>5.803284190739974</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8799635705354</v>
+        <v>102.8802018303673</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02733453557967147</v>
+        <v>0.02757279541160854</v>
       </c>
       <c r="T2" t="n">
-        <v>17.79426693433119</v>
+        <v>17.79420210712422</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18219862143121</v>
+        <v>36.18225089454136</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284664476710176</v>
+        <v>0.1284676480666898</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7368150899425818</v>
+        <v>-0.7368201083657595</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284589935926443</v>
+        <v>0.1284602108252176</v>
       </c>
       <c r="Y2" t="n">
-        <v>25.37509080525783</v>
+        <v>53.81167528206624</v>
       </c>
       <c r="Z2" t="n">
-        <v>70.93375663856884</v>
+        <v>77.30907300392838</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.9891001154161</v>
+        <v>109.5726679137047</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959180711184412</v>
+        <v>4.959157290913775</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05316929754304758</v>
+        <v>0.05314587727241053</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350442540230949</v>
+        <v>1.350440853240253</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725333779285397</v>
+        <v>1.725338637516127</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795571114275331</v>
+        <v>0.779558987554037</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664633287503038</v>
+        <v>0.5664608872237199</v>
       </c>
       <c r="X3" t="n">
-        <v>0.778527867601758</v>
+        <v>0.7785312992639086</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.358138762005153</v>
+        <v>2.357015357999766</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.388903248066122</v>
+        <v>2.377692877212847</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.535164260516096</v>
+        <v>2.413893544629272</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3649683766690091</v>
+        <v>0.3648560393258427</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246064939632997</v>
+        <v>7.246041830114228</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3280906583891096</v>
+        <v>0.3280675488703397</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293861279143206</v>
+        <v>1.293869308174623</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683858991168306</v>
+        <v>1.683864306350765</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674608729011417</v>
+        <v>0.8674607754125908</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371056469428658</v>
+        <v>0.7371039872627305</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473514833716889</v>
+        <v>0.8473600178655563</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.219443629079191</v>
+        <v>3.162110938482963</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.612644062726424</v>
+        <v>3.517640792372362</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.067086380179298</v>
+        <v>4.00308286516854</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313200449414685</v>
+        <v>9.313189387454251</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3584123453254677</v>
+        <v>0.358401283365033</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254666361061508</v>
+        <v>1.254661794639771</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747779963031171</v>
+        <v>1.747781917821525</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675130352997911</v>
+        <v>0.8675148896800107</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234733720047307</v>
+        <v>0.7234727534464469</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8615989467826963</v>
+        <v>0.8616011174027675</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.488872668926053</v>
+        <v>5.488609170033763</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.609666658126889</v>
+        <v>5.577223777530682</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.803284190739974</v>
+        <v>5.764000166562689</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018937193327051</v>
+        <v>7.018955251587717</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2881196081737187</v>
+        <v>0.2881376664343838</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482248275251922</v>
+        <v>1.482263729206586</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91088143838154</v>
+        <v>1.910905554986068</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047860895017538</v>
+        <v>0.3047863366303695</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1984243817847187</v>
+        <v>-0.1984546318134988</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802526038631767</v>
+        <v>0.2802593596551595</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.428590233663111</v>
+        <v>6.378119238764045</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.53111181897828</v>
+        <v>6.506520001538824</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.582013281631135</v>
+        <v>6.5825976645248</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586368872412248</v>
+        <v>5.586370312216182</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003797036367457302</v>
+        <v>0.003798476171390414</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156207374788974</v>
+        <v>1.156229939339565</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494317837755257</v>
+        <v>1.494342420167739</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088421412693735</v>
+        <v>0.5088333719569239</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07422686598726258</v>
+        <v>0.07419640670522887</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050180970074261</v>
+        <v>0.5050114143745519</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.478291806265464</v>
+        <v>5.464982207223271</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.534711959501228</v>
+        <v>5.522167291684857</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.587091033755049</v>
+        <v>5.585787433067065</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116266867442061</v>
+        <v>8.116235549883969</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.235909803976461</v>
+        <v>0.2358784864183691</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445442699383002</v>
+        <v>1.445464700201859</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825141240719321</v>
+        <v>1.825161315306526</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087057351970074</v>
+        <v>0.8087036929042627</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288175585043847</v>
+        <v>0.628809393245606</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991209227047704</v>
+        <v>0.7991253149044182</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.058761035224877</v>
+        <v>5.058339401618267</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.122370766193518</v>
+        <v>5.095403446156327</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.356963518990357</v>
+        <v>5.188234499480908</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5077898805340829</v>
+        <v>0.5075526685393258</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679058559139315</v>
+        <v>7.679010344156012</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06310775838906232</v>
+        <v>0.06305954340575932</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477387750083575</v>
+        <v>1.477397566882757</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919798063213711</v>
+        <v>1.919815644850135</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617507566561439</v>
+        <v>0.7617520236054955</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360700081874006</v>
+        <v>0.5360615107459787</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7598225274086957</v>
+        <v>0.759827412363731</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.423281799016165</v>
+        <v>5.414940308988765</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.482431455717327</v>
+        <v>5.458982345060742</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.669546732255798</v>
+        <v>5.50584029691889</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61860070943681</v>
+        <v>10.61853993038964</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3135411696990473</v>
+        <v>0.3134803906518836</v>
       </c>
       <c r="T10" t="n">
-        <v>2.051956992400397</v>
+        <v>2.052000300926013</v>
       </c>
       <c r="U10" t="n">
-        <v>2.69757224581799</v>
+        <v>2.697607075951206</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567035482520799</v>
+        <v>0.356705134696288</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1199994862403828</v>
+        <v>-0.1200284085302001</v>
       </c>
       <c r="X10" t="n">
-        <v>0.336037968487225</v>
+        <v>0.3360492291064946</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.024699896007288</v>
+        <v>8.835232531005508</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.576767697215713</v>
+        <v>9.492888183010999</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.704195340954358</v>
+        <v>9.706331448293515</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218203102275945</v>
+        <v>5.218188803896952</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02767333762842325</v>
+        <v>-0.02768763600741559</v>
       </c>
       <c r="T11" t="n">
-        <v>1.158069985759435</v>
+        <v>1.15808377173903</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477086048859137</v>
+        <v>1.477107108454039</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294392068066683</v>
+        <v>0.4294376643833713</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08278378250384888</v>
+        <v>-0.08281465836297786</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268640322819051</v>
+        <v>0.4268649855121517</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.679434081906056</v>
+        <v>3.675509099621005</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.173635104817662</v>
+        <v>4.075765457114538</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.510035137034434</v>
+        <v>4.446993663942683</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664022034821261</v>
+        <v>7.664007916384938</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722548666581936</v>
+        <v>0.1722407482218698</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148781869788847</v>
+        <v>0.9148825000940239</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198055460957254</v>
+        <v>1.198065546286949</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296408897617582</v>
+        <v>0.8296399527683659</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543104168867563</v>
+        <v>0.6543045967754084</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279731700879114</v>
+        <v>0.8279730854395908</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.029591231626475</v>
+        <v>5.029522768946488</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.430983170732152</v>
+        <v>5.443220994392019</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.786957675712982</v>
+        <v>5.791142762312604</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85743851018974</v>
+        <v>2.856945224719101</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02943285489229</v>
+        <v>10.02938972581541</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4125580808153484</v>
+        <v>0.4125149517384676</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694072130679657</v>
+        <v>1.69410702922704</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153736081118427</v>
+        <v>2.153785115783678</v>
       </c>
       <c r="V13" t="n">
-        <v>0.823224000941999</v>
+        <v>0.8232174529429181</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648564939491367</v>
+        <v>0.6485489368837412</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115179839103567</v>
+        <v>0.8115192804835814</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.110704632927254</v>
+        <v>6.190096558988764</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.856755638233861</v>
+        <v>7.026377033795423</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.362671604948501</v>
+        <v>7.473845480155719</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201584540742184</v>
+        <v>8.201450665532146</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06770093325090677</v>
+        <v>0.06756705804086968</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758476512236222</v>
+        <v>1.758407651061292</v>
       </c>
       <c r="U14" t="n">
-        <v>2.284056251690035</v>
+        <v>2.283997161646402</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7809983169726691</v>
+        <v>0.781018174326671</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653000354867603</v>
+        <v>0.5653225271461391</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806722396811139</v>
+        <v>0.7806943973271367</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.737499999999999</v>
+        <v>5.685296503018705</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.808318121711054</v>
+        <v>5.780055265430107</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.916268322716139</v>
+        <v>5.860968494566081</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82391510973876</v>
+        <v>11.82386376296822</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.139966787647493</v>
+        <v>-0.1400181344180302</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052255639338034</v>
+        <v>2.052232970126628</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697523543929119</v>
+        <v>2.697495932743458</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949099719612587</v>
+        <v>0.7949174550012866</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096303959455982</v>
+        <v>0.6096383873586666</v>
       </c>
       <c r="X15" t="n">
-        <v>0.786136977042404</v>
+        <v>0.78614899258494</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.753831091546047</v>
+        <v>8.049030308080019</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.16280926682194</v>
+        <v>8.227986291388477</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.348142062766122</v>
+        <v>8.367889058324987</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661472209028549</v>
+        <v>8.661294900756381</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.253201932327209</v>
+        <v>0.2530246240550422</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538098400246003</v>
+        <v>3.538056631575054</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06324503142441</v>
+        <v>11.06323681021305</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04951214367820555</v>
+        <v>0.0495091608582255</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971443000924841</v>
+        <v>-0.5971419263845978</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0327594690319214</v>
+        <v>0.03275647246342162</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.08279764732665</v>
+        <v>12.20283102609153</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.23218665513539</v>
+        <v>12.26427704550337</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.37854493336474</v>
+        <v>12.41282123726156</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910566906081492</v>
+        <v>6.910540653197995</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3709009486346828</v>
+        <v>0.3708746957511864</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032143729437636</v>
+        <v>2.032164357018839</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566434250896705</v>
+        <v>2.566452889483378</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210596614041626</v>
+        <v>0.5210604397137858</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02240556528367366</v>
+        <v>0.02239136578118472</v>
       </c>
       <c r="X17" t="n">
-        <v>0.517712693087703</v>
+        <v>0.5177139674122689</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.556812597535341</v>
+        <v>2.449853817881908</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.124587295383273</v>
+        <v>3.979707648708838</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.285882693511653</v>
+        <v>6.077538235079836</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692707140164901</v>
+        <v>6.692655812854359</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1949461554344562</v>
+        <v>0.1948948281239128</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099836727255959</v>
+        <v>1.099834860150734</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48932171235413</v>
+        <v>1.48932559877309</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009658871533028</v>
+        <v>0.6009715840674508</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2173911426618522</v>
+        <v>0.2173870581852148</v>
       </c>
       <c r="X18" t="n">
-        <v>0.59804123128285</v>
+        <v>0.5980503676065971</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.540404178946212</v>
+        <v>3.457488594570587</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.291650620458647</v>
+        <v>5.146677979966482</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.782203911291773</v>
+        <v>6.591643862932228</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16675</v>
+        <v>16676</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15221410937033</v>
+        <v>11.15209500224264</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7828946901325792</v>
+        <v>0.7827755830048929</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038161735984791</v>
+        <v>2.038165424436543</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757731235595638</v>
+        <v>2.757740778689364</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263158114371486</v>
+        <v>0.7263124730034237</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693333615120316</v>
+        <v>0.4693296887754247</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6791566942341747</v>
+        <v>0.6791771775365385</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.519986720419787</v>
+        <v>7.464397684993696</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.636055277931773</v>
+        <v>7.620256223695584</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.796495360457675</v>
+        <v>7.741969323377361</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.519986720419787</v>
+        <v>7.464397684993696</v>
       </c>
       <c r="G2" t="n">
-        <v>7.636055277931773</v>
+        <v>7.620256223695584</v>
       </c>
       <c r="H2" t="n">
-        <v>7.796495360457675</v>
+        <v>7.741969323377361</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.478291806265464</v>
+        <v>5.464982207223271</v>
       </c>
       <c r="G3" t="n">
-        <v>5.534711959501228</v>
+        <v>5.522167291684857</v>
       </c>
       <c r="H3" t="n">
-        <v>5.587091033755049</v>
+        <v>5.585787433067065</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.679434081906056</v>
+        <v>3.675509099621005</v>
       </c>
       <c r="G4" t="n">
-        <v>4.173635104817661</v>
+        <v>4.075765457114538</v>
       </c>
       <c r="H4" t="n">
-        <v>4.510035137034434</v>
+        <v>4.446993663942683</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.08279764732665</v>
+        <v>12.20283102609153</v>
       </c>
       <c r="G5" t="n">
-        <v>12.23218665513539</v>
+        <v>12.26427704550337</v>
       </c>
       <c r="H5" t="n">
-        <v>12.37854493336474</v>
+        <v>12.41282123726156</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>25.37509080525783</v>
+        <v>53.81167528206624</v>
       </c>
       <c r="G6" t="n">
-        <v>70.93375663856884</v>
+        <v>77.30907300392838</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9891001154161</v>
+        <v>109.5726679137047</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>7.753831091546047</v>
+        <v>8.049030308080019</v>
       </c>
       <c r="G7" t="n">
-        <v>8.162809266821938</v>
+        <v>8.227986291388479</v>
       </c>
       <c r="H7" t="n">
-        <v>8.348142062766122</v>
+        <v>8.367889058324987</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.110704632927254</v>
+        <v>6.190096558988764</v>
       </c>
       <c r="G8" t="n">
-        <v>6.856755638233861</v>
+        <v>7.026377033795423</v>
       </c>
       <c r="H8" t="n">
-        <v>7.362671604948501</v>
+        <v>7.473845480155719</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.029591231626475</v>
+        <v>5.029522768946488</v>
       </c>
       <c r="G9" t="n">
-        <v>5.430983170732152</v>
+        <v>5.443220994392019</v>
       </c>
       <c r="H9" t="n">
-        <v>5.786957675712982</v>
+        <v>5.791142762312604</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.058761035224877</v>
+        <v>5.058339401618267</v>
       </c>
       <c r="G10" t="n">
-        <v>5.122370766193518</v>
+        <v>5.095403446156327</v>
       </c>
       <c r="H10" t="n">
-        <v>5.356963518990357</v>
+        <v>5.188234499480908</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.556812597535341</v>
+        <v>2.449853817881908</v>
       </c>
       <c r="G11" t="n">
-        <v>4.124587295383273</v>
+        <v>3.979707648708838</v>
       </c>
       <c r="H11" t="n">
-        <v>6.285882693511653</v>
+        <v>6.077538235079836</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.737499999999999</v>
+        <v>5.685296503018705</v>
       </c>
       <c r="G12" t="n">
-        <v>5.808318121711054</v>
+        <v>5.780055265430107</v>
       </c>
       <c r="H12" t="n">
-        <v>5.916268322716139</v>
+        <v>5.860968494566081</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.024699896007288</v>
+        <v>8.835232531005508</v>
       </c>
       <c r="G13" t="n">
-        <v>9.576767697215713</v>
+        <v>9.492888183010997</v>
       </c>
       <c r="H13" t="n">
-        <v>9.704195340954358</v>
+        <v>9.706331448293515</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.423281799016165</v>
+        <v>5.414940308988765</v>
       </c>
       <c r="G14" t="n">
-        <v>5.482431455717327</v>
+        <v>5.458982345060742</v>
       </c>
       <c r="H14" t="n">
-        <v>5.669546732255798</v>
+        <v>5.50584029691889</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.428590233663111</v>
+        <v>6.378119238764045</v>
       </c>
       <c r="G15" t="n">
-        <v>6.53111181897828</v>
+        <v>6.506520001538824</v>
       </c>
       <c r="H15" t="n">
-        <v>6.582013281631135</v>
+        <v>6.5825976645248</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.540404178946212</v>
+        <v>3.457488594570587</v>
       </c>
       <c r="G16" t="n">
-        <v>5.291650620458647</v>
+        <v>5.146677979966482</v>
       </c>
       <c r="H16" t="n">
-        <v>6.782203911291773</v>
+        <v>6.591643862932228</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.219443629079191</v>
+        <v>3.162110938482963</v>
       </c>
       <c r="G17" t="n">
-        <v>3.612644062726424</v>
+        <v>3.517640792372362</v>
       </c>
       <c r="H17" t="n">
-        <v>4.067086380179298</v>
+        <v>4.00308286516854</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.358138762005153</v>
+        <v>2.357015357999766</v>
       </c>
       <c r="G18" t="n">
-        <v>2.388903248066122</v>
+        <v>2.377692877212847</v>
       </c>
       <c r="H18" t="n">
-        <v>2.535164260516096</v>
+        <v>2.413893544629272</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.488872668926053</v>
+        <v>5.488609170033763</v>
       </c>
       <c r="G19" t="n">
-        <v>5.609666658126889</v>
+        <v>5.577223777530683</v>
       </c>
       <c r="H19" t="n">
-        <v>5.803284190739974</v>
+        <v>5.764000166562689</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8802018303673</v>
+        <v>102.8804959892079</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02757279541160854</v>
+        <v>0.02786695425219045</v>
       </c>
       <c r="T2" t="n">
-        <v>17.79420210712422</v>
+        <v>17.79408084810726</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18225089454136</v>
+        <v>36.18223998751424</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284676480666898</v>
+        <v>0.1284696005266151</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7368201083657595</v>
+        <v>-0.736819061247866</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284602108252176</v>
+        <v>0.1284621690803107</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.81167528206624</v>
+        <v>53.8113590992585</v>
       </c>
       <c r="Z2" t="n">
-        <v>77.30907300392838</v>
+        <v>76.58925228370541</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.5726679137047</v>
+        <v>111.5843586804372</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959157290913775</v>
+        <v>4.959137967009146</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05314587727241053</v>
+        <v>0.0531265533677813</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350440853240253</v>
+        <v>1.350438851161255</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725338637516127</v>
+        <v>1.72534291845177</v>
       </c>
       <c r="V3" t="n">
-        <v>0.779558987554037</v>
+        <v>0.7795607271465116</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664608872237199</v>
+        <v>0.5664587358137849</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785312992639086</v>
+        <v>0.7785344255355162</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.357015357999766</v>
+        <v>2.355662938596491</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.377692877212847</v>
+        <v>2.375732828218138</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.413893544629272</v>
+        <v>2.41221052631579</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3648560393258427</v>
+        <v>0.3647438596491228</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246041830114228</v>
+        <v>7.246018321378752</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3280675488703397</v>
+        <v>0.3280440401348647</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293869308174623</v>
+        <v>1.293875916112136</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683864306350765</v>
+        <v>1.683869884317106</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674607754125908</v>
+        <v>0.8674606455485464</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371039872627305</v>
+        <v>0.7371022455219813</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473600178655563</v>
+        <v>0.8473686571225396</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.162110938482963</v>
+        <v>3.121033333333334</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.517640792372362</v>
+        <v>3.422294897495039</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.00308286516854</v>
+        <v>3.921157894736842</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313189387454251</v>
+        <v>9.313176771854828</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.358401283365033</v>
+        <v>0.3583886677656099</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254661794639771</v>
+        <v>1.254661242975055</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747781917821525</v>
+        <v>1.747785415600376</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675148896800107</v>
+        <v>0.86751654978572</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234727534464469</v>
+        <v>0.7234716466354508</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616011174027675</v>
+        <v>0.8616031509483466</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.488609170033763</v>
+        <v>5.493099059077945</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.577223777530682</v>
+        <v>5.54567468541615</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.764000166562689</v>
+        <v>5.693452631578947</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018955251587717</v>
+        <v>7.018975239253121</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2881376664343838</v>
+        <v>0.2881576540997888</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482263729206586</v>
+        <v>1.48228013149254</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910905554986068</v>
+        <v>1.910931012320235</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047863366303695</v>
+        <v>0.3047856908786492</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1984546318134988</v>
+        <v>-0.1984865639654492</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802593596551595</v>
+        <v>0.2802651991262287</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.378119238764045</v>
+        <v>6.347474232879496</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.506520001538824</v>
+        <v>6.481170853606187</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.5825976645248</v>
+        <v>6.581319785402147</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586370312216182</v>
+        <v>5.586371771327391</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003798476171390414</v>
+        <v>0.003799935282598481</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156229939339565</v>
+        <v>1.15625182088861</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494342420167739</v>
+        <v>1.494366741173318</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088333719569239</v>
+        <v>0.5088247685300625</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07419640670522887</v>
+        <v>0.07416627083103289</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050114143745519</v>
+        <v>0.5050048938432543</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.464982207223271</v>
+        <v>5.45</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.522167291684857</v>
+        <v>5.509897371904797</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.585787433067065</v>
+        <v>5.586148741776316</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116235549883969</v>
+        <v>8.116212890279034</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2358784864183691</v>
+        <v>0.235855826813433</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445464700201859</v>
+        <v>1.445483417384956</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825161315306526</v>
+        <v>1.82518296567866</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087036929042627</v>
+        <v>0.8087011198611491</v>
       </c>
       <c r="W8" t="n">
-        <v>0.628809393245606</v>
+        <v>0.6288005869418933</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991253149044182</v>
+        <v>0.7991282438401993</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.058339401618267</v>
+        <v>5.057563461042311</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.095403446156327</v>
+        <v>5.081659548941643</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.188234499480908</v>
+        <v>5.140229762333649</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5075526685393258</v>
+        <v>0.5073157894736843</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.679010344156012</v>
+        <v>7.678970411354577</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06305954340575932</v>
+        <v>0.06301961060432411</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477397566882757</v>
+        <v>1.477411649551479</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919815644850135</v>
+        <v>1.919833159102698</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617520236054955</v>
+        <v>0.7617527723284238</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360615107459787</v>
+        <v>0.5360530457947104</v>
       </c>
       <c r="X9" t="n">
-        <v>0.759827412363731</v>
+        <v>0.7598314020237749</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.414940308988765</v>
+        <v>5.38537692875365</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.458982345060742</v>
+        <v>5.442155852161889</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.50584029691889</v>
+        <v>5.501080645188124</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61853993038964</v>
+        <v>10.61847485302881</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3134803906518836</v>
+        <v>0.313415313291052</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052000300926013</v>
+        <v>2.052046105132485</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697607075951206</v>
+        <v>2.697644577502389</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356705134696288</v>
+        <v>0.3567060277543339</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1200284085302001</v>
+        <v>-0.1200595495329213</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360492291064946</v>
+        <v>0.3360602049220444</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.835232531005508</v>
+        <v>8.631464227164843</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.492888183010999</v>
+        <v>9.38794343574062</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.706331448293515</v>
+        <v>9.708458547034192</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218188803896952</v>
+        <v>5.218178930100371</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02768763600741559</v>
+        <v>-0.02769750980399743</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15808377173903</v>
+        <v>1.158097606010426</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477107108454039</v>
+        <v>1.477127446541283</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294376643833713</v>
+        <v>0.4294352439877769</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08281465836297786</v>
+        <v>-0.08284447682431528</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268649855121517</v>
+        <v>0.4268648344128397</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.675509099621005</v>
+        <v>3.6751378282692</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.075765457114538</v>
+        <v>3.989387378086155</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.446993663942683</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.664007916384938</v>
+        <v>7.663992004628844</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722407482218698</v>
+        <v>0.1722248364657764</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148825000940239</v>
+        <v>0.9148855142485643</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198065546286949</v>
+        <v>1.198075300508691</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296399527683659</v>
+        <v>0.8296392220560928</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6543045967754084</v>
+        <v>0.6542989676955044</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279730854395908</v>
+        <v>0.8279732777591687</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.029522768946488</v>
+        <v>4.88865932688865</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.443220994392019</v>
+        <v>5.427058289827587</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.791142762312604</v>
+        <v>5.790551977457985</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.856945224719101</v>
+        <v>2.856452631578947</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02938972581541</v>
+        <v>10.02933949250868</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4125149517384676</v>
+        <v>0.412464718431733</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69410702922704</v>
+        <v>1.694139947021636</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153785115783678</v>
+        <v>2.153836132298142</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232174529429181</v>
+        <v>0.8232106471249144</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485489368837412</v>
+        <v>0.6485322871070623</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115192804835814</v>
+        <v>0.8115211141183096</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.190096558988764</v>
+        <v>6.51606357643612</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.026377033795423</v>
+        <v>7.157190665009615</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.473845480155719</v>
+        <v>7.496896388028895</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201450665532146</v>
+        <v>8.201318045262239</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06756705804086968</v>
+        <v>0.06743443777096272</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758407651061292</v>
+        <v>1.758340474150294</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283997161646402</v>
+        <v>2.283939452220622</v>
       </c>
       <c r="V14" t="n">
-        <v>0.781018174326671</v>
+        <v>0.7810377724459555</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653225271461391</v>
+        <v>0.5653444927342492</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7806943973271367</v>
+        <v>0.7807162802818185</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.685296503018705</v>
+        <v>5.662377686795568</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.780055265430107</v>
+        <v>5.753209597328956</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.860968494566081</v>
+        <v>5.834052065647991</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82386376296822</v>
+        <v>11.82379360186534</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1400181344180302</v>
+        <v>-0.1400882955209135</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052232970126628</v>
+        <v>2.052201584861661</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697495932743458</v>
+        <v>2.697456540785099</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949174550012866</v>
+        <v>0.7949275488384075</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096383873586666</v>
+        <v>0.6096497882997591</v>
       </c>
       <c r="X15" t="n">
-        <v>0.78614899258494</v>
+        <v>0.7861645876477613</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.049030308080019</v>
+        <v>8.142742431299487</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.227986291388477</v>
+        <v>8.258406671366419</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.367889058324987</v>
+        <v>8.367895958006461</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661294900756381</v>
+        <v>8.661114416909873</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2530246240550422</v>
+        <v>0.2528441402085342</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538056631575054</v>
+        <v>3.538013284070084</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06323681021305</v>
+        <v>11.06322751103158</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0495091608582255</v>
+        <v>0.04950621426080914</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971419263845978</v>
+        <v>-0.5971392414368539</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03275647246342162</v>
+        <v>0.03275349543507022</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.20283102609153</v>
+        <v>12.19944027194115</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.26427704550337</v>
+        <v>12.27539869221618</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.41282123726156</v>
+        <v>12.40765716695299</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910540653197995</v>
+        <v>6.910515846641801</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3708746957511864</v>
+        <v>0.370849889194992</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032164357018839</v>
+        <v>2.03218575594767</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566452889483378</v>
+        <v>2.566472703470675</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210604397137858</v>
+        <v>0.521060590631385</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02239136578118472</v>
+        <v>0.0223762707058669</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177139674122689</v>
+        <v>0.5177145910901881</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.449853817881908</v>
+        <v>2.821068080498486</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.979707648708838</v>
+        <v>3.664647646552735</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.077538235079836</v>
+        <v>4.988895690351775</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692655812854359</v>
+        <v>6.692623521242465</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948948281239128</v>
+        <v>0.1948625365120192</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099834860150734</v>
+        <v>1.099848653929772</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48932559877309</v>
+        <v>1.489338857489405</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009715840674508</v>
+        <v>0.6009722745548213</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2173870581852148</v>
+        <v>0.2173731237048351</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980503676065971</v>
+        <v>0.5980539989343168</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.457488594570587</v>
+        <v>3.885747758006145</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.146677979966482</v>
+        <v>4.932722106059918</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.591643862932228</v>
+        <v>6.473059027179137</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16676</v>
+        <v>16677</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15209500224264</v>
+        <v>11.15198017556644</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7827755830048929</v>
+        <v>0.7826607563286861</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038165424436543</v>
+        <v>2.03816527613878</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757740778689364</v>
+        <v>2.757749321076525</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263124730034237</v>
+        <v>0.7263094445359948</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693296887754247</v>
+        <v>0.4693264011580318</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6791771775365385</v>
+        <v>0.679197201574009</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.464397684993696</v>
+        <v>7.479862627669783</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.620256223695584</v>
+        <v>7.582717150339707</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.741969323377361</v>
+        <v>7.696822322380537</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.464397684993696</v>
+        <v>7.479862627669783</v>
       </c>
       <c r="G2" t="n">
-        <v>7.620256223695584</v>
+        <v>7.582717150339707</v>
       </c>
       <c r="H2" t="n">
-        <v>7.741969323377361</v>
+        <v>7.696822322380537</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.464982207223271</v>
+        <v>5.45</v>
       </c>
       <c r="G3" t="n">
-        <v>5.522167291684857</v>
+        <v>5.509897371904797</v>
       </c>
       <c r="H3" t="n">
-        <v>5.585787433067065</v>
+        <v>5.586148741776316</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.675509099621005</v>
+        <v>3.6751378282692</v>
       </c>
       <c r="G4" t="n">
-        <v>4.075765457114538</v>
+        <v>3.989387378086155</v>
       </c>
       <c r="H4" t="n">
-        <v>4.446993663942683</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.20283102609153</v>
+        <v>12.19944027194115</v>
       </c>
       <c r="G5" t="n">
-        <v>12.26427704550337</v>
+        <v>12.27539869221618</v>
       </c>
       <c r="H5" t="n">
-        <v>12.41282123726156</v>
+        <v>12.40765716695299</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.81167528206624</v>
+        <v>53.8113590992585</v>
       </c>
       <c r="G6" t="n">
-        <v>77.30907300392838</v>
+        <v>76.58925228370541</v>
       </c>
       <c r="H6" t="n">
-        <v>109.5726679137047</v>
+        <v>111.5843586804372</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.049030308080019</v>
+        <v>8.142742431299487</v>
       </c>
       <c r="G7" t="n">
-        <v>8.227986291388479</v>
+        <v>8.258406671366419</v>
       </c>
       <c r="H7" t="n">
-        <v>8.367889058324987</v>
+        <v>8.367895958006461</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.190096558988764</v>
+        <v>6.51606357643612</v>
       </c>
       <c r="G8" t="n">
-        <v>7.026377033795423</v>
+        <v>7.157190665009615</v>
       </c>
       <c r="H8" t="n">
-        <v>7.473845480155719</v>
+        <v>7.496896388028895</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>5.029522768946488</v>
+        <v>4.88865932688865</v>
       </c>
       <c r="G9" t="n">
-        <v>5.443220994392019</v>
+        <v>5.427058289827587</v>
       </c>
       <c r="H9" t="n">
-        <v>5.791142762312604</v>
+        <v>5.790551977457985</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.058339401618267</v>
+        <v>5.057563461042311</v>
       </c>
       <c r="G10" t="n">
-        <v>5.095403446156327</v>
+        <v>5.081659548941643</v>
       </c>
       <c r="H10" t="n">
-        <v>5.188234499480908</v>
+        <v>5.140229762333649</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.449853817881908</v>
+        <v>2.821068080498486</v>
       </c>
       <c r="G11" t="n">
-        <v>3.979707648708838</v>
+        <v>3.664647646552735</v>
       </c>
       <c r="H11" t="n">
-        <v>6.077538235079836</v>
+        <v>4.988895690351775</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.685296503018705</v>
+        <v>5.662377686795568</v>
       </c>
       <c r="G12" t="n">
-        <v>5.780055265430107</v>
+        <v>5.753209597328957</v>
       </c>
       <c r="H12" t="n">
-        <v>5.860968494566081</v>
+        <v>5.834052065647991</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>8.835232531005508</v>
+        <v>8.631464227164843</v>
       </c>
       <c r="G13" t="n">
-        <v>9.492888183010997</v>
+        <v>9.38794343574062</v>
       </c>
       <c r="H13" t="n">
-        <v>9.706331448293515</v>
+        <v>9.708458547034192</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.414940308988765</v>
+        <v>5.38537692875365</v>
       </c>
       <c r="G14" t="n">
-        <v>5.458982345060742</v>
+        <v>5.442155852161889</v>
       </c>
       <c r="H14" t="n">
-        <v>5.50584029691889</v>
+        <v>5.501080645188124</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.378119238764045</v>
+        <v>6.347474232879496</v>
       </c>
       <c r="G15" t="n">
-        <v>6.506520001538824</v>
+        <v>6.481170853606185</v>
       </c>
       <c r="H15" t="n">
-        <v>6.5825976645248</v>
+        <v>6.581319785402147</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.457488594570587</v>
+        <v>3.885747758006145</v>
       </c>
       <c r="G16" t="n">
-        <v>5.146677979966482</v>
+        <v>4.932722106059918</v>
       </c>
       <c r="H16" t="n">
-        <v>6.591643862932228</v>
+        <v>6.473059027179137</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.162110938482963</v>
+        <v>3.121033333333334</v>
       </c>
       <c r="G17" t="n">
-        <v>3.517640792372362</v>
+        <v>3.422294897495039</v>
       </c>
       <c r="H17" t="n">
-        <v>4.00308286516854</v>
+        <v>3.921157894736842</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.357015357999766</v>
+        <v>2.355662938596491</v>
       </c>
       <c r="G18" t="n">
-        <v>2.377692877212847</v>
+        <v>2.375732828218138</v>
       </c>
       <c r="H18" t="n">
-        <v>2.413893544629272</v>
+        <v>2.41221052631579</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.488609170033763</v>
+        <v>5.493099059077945</v>
       </c>
       <c r="G19" t="n">
-        <v>5.577223777530683</v>
+        <v>5.54567468541615</v>
       </c>
       <c r="H19" t="n">
-        <v>5.764000166562689</v>
+        <v>5.693452631578947</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E2" t="n">
         <v>9965</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8804959892079</v>
+        <v>102.8808699016457</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02786695425219045</v>
+        <v>0.02824086669005615</v>
       </c>
       <c r="T2" t="n">
-        <v>17.79408084810726</v>
+        <v>17.79387715177367</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18223998751424</v>
+        <v>36.18211135545523</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284696005266151</v>
+        <v>0.1284730177187951</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.736819061247866</v>
+        <v>-0.7368067120834725</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284621690803107</v>
+        <v>0.1284655718931461</v>
       </c>
       <c r="Y2" t="n">
-        <v>53.8113590992585</v>
+        <v>6.779915940319707</v>
       </c>
       <c r="Z2" t="n">
-        <v>76.58925228370541</v>
+        <v>61.60049016595825</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.5843586804372</v>
+        <v>113.6871824875759</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E3" t="n">
         <v>14544</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959137967009146</v>
+        <v>4.959121117581077</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0531265533677813</v>
+        <v>0.05310970393971277</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350438851161255</v>
+        <v>1.350436468986679</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72534291845177</v>
+        <v>1.725346708643728</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795607271465116</v>
+        <v>0.7795624227984262</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664587358137849</v>
+        <v>0.5664568310255828</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785344255355162</v>
+        <v>0.7785374063652714</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.355662938596491</v>
+        <v>2.354343151005143</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.375732828218138</v>
+        <v>2.378160030414087</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.41221052631579</v>
+        <v>2.425413744740533</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E4" t="n">
         <v>10226</v>
@@ -789,40 +789,40 @@
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3647438596491228</v>
+        <v>0.3646318373071529</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246018321378752</v>
+        <v>7.246004740709422</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3280440401348647</v>
+        <v>0.3280304594655336</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293875916112136</v>
+        <v>1.293881835818342</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683869884317106</v>
+        <v>1.683876342026507</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674606455485464</v>
+        <v>0.8674604421552005</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371022455219813</v>
+        <v>0.7371002290709816</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473686571225396</v>
+        <v>0.8473755538084683</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.121033333333334</v>
+        <v>3.069817671809257</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.422294897495039</v>
+        <v>3.323721962872383</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.921157894736842</v>
+        <v>3.78656381486676</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313176771854828</v>
+        <v>9.313173985103596</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3583886677656099</v>
+        <v>0.3583858810143764</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254661242975055</v>
+        <v>1.254671363523135</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747785415600376</v>
+        <v>1.747802171092971</v>
       </c>
       <c r="V5" t="n">
-        <v>0.86751654978572</v>
+        <v>0.8675159960489112</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234716466354508</v>
+        <v>0.7234663446218912</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616031509483466</v>
+        <v>0.8616027395273647</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.493099059077945</v>
+        <v>5.492220254409895</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.54567468541615</v>
+        <v>5.520548619005933</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.693452631578947</v>
+        <v>5.616644852905435</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E6" t="n">
         <v>8837</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018975239253121</v>
+        <v>7.018995385618139</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2881576540997888</v>
+        <v>0.2881778004648057</v>
       </c>
       <c r="T6" t="n">
-        <v>1.48228013149254</v>
+        <v>1.482297613960537</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910931012320235</v>
+        <v>1.910956628683486</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047856908786492</v>
+        <v>0.3047846997467092</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1984865639654492</v>
+        <v>-0.1985186960233318</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802651991262287</v>
+        <v>0.2802706052882724</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.347474232879496</v>
+        <v>6.334772521277599</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.481170853606187</v>
+        <v>6.457578602561989</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.581319785402147</v>
+        <v>6.553300030268006</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E7" t="n">
         <v>14199</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586371771327391</v>
+        <v>5.586373244884039</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003799935282598481</v>
+        <v>0.003801408839248445</v>
       </c>
       <c r="T7" t="n">
-        <v>1.15625182088861</v>
+        <v>1.156274014382261</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494366741173318</v>
+        <v>1.494392108455455</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088247685300625</v>
+        <v>0.5088155594709983</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07416627083103289</v>
+        <v>0.07413483800519038</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5050048938432543</v>
+        <v>0.504997794656004</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.45</v>
+        <v>5.421912108461898</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.509897371904797</v>
+        <v>5.493721762514741</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.586148741776316</v>
+        <v>5.58658330776648</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E8" t="n">
         <v>8997</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116212890279034</v>
+        <v>8.116195756098076</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.235855826813433</v>
+        <v>0.235838692632477</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445483417384956</v>
+        <v>1.445497549455948</v>
       </c>
       <c r="U8" t="n">
-        <v>1.82518296567866</v>
+        <v>1.825202248431199</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8087011198611491</v>
+        <v>0.8086989136737037</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6288005869418933</v>
+        <v>0.6287927435811242</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991282438401993</v>
+        <v>0.7991308756524551</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.057563461042311</v>
+        <v>5.051564423991519</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.081659548941643</v>
+        <v>5.071332216233717</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.140229762333649</v>
+        <v>5.098928894463176</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E9" t="n">
         <v>13862</v>
@@ -1234,40 +1234,40 @@
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5073157894736843</v>
+        <v>0.5070792426367461</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.678970411354577</v>
+        <v>7.678938942515691</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06301961060432411</v>
+        <v>0.06298814176543827</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477411649551479</v>
+        <v>1.477425481621679</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919833159102698</v>
+        <v>1.919850213322672</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617527723284238</v>
+        <v>0.7617532165858771</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360530457947104</v>
+        <v>0.5360448031112057</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7598314020237749</v>
+        <v>0.7598347732403602</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.38537692875365</v>
+        <v>5.338997082553773</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.442155852161889</v>
+        <v>5.430171164893284</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.501080645188124</v>
+        <v>5.5037147827683</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61847485302881</v>
+        <v>10.61840905299219</v>
       </c>
       <c r="R10" t="n">
         <v>14.31645908761767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.313415313291052</v>
+        <v>0.3133495132544339</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052046105132485</v>
+        <v>2.05209209420786</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697644577502389</v>
+        <v>2.697682582117695</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567060277543339</v>
+        <v>0.3567063156688055</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1200595495329213</v>
+        <v>-0.1200911087179233</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360602049220444</v>
+        <v>0.3360704612193633</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.631464227164843</v>
+        <v>8.829352782559743</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.38794343574062</v>
+        <v>9.46776054862031</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.708458547034192</v>
+        <v>9.6975</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E11" t="n">
         <v>13803</v>
@@ -1415,37 +1415,37 @@
         <v>0.8401943005181348</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218178930100371</v>
+        <v>5.218173832845966</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02769750980399743</v>
+        <v>-0.02770260705840326</v>
       </c>
       <c r="T11" t="n">
-        <v>1.158097606010426</v>
+        <v>1.15811271365606</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477127446541283</v>
+        <v>1.477148894147647</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294352439877769</v>
+        <v>0.4294308888262925</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08284447682431528</v>
+        <v>-0.08287592243959252</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268648344128397</v>
+        <v>0.4268625911690527</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.6751378282692</v>
+        <v>3.714509116409537</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.989387378086155</v>
+        <v>4.054062933294</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.38</v>
+        <v>4.36934885794919</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E12" t="n">
         <v>4121</v>
@@ -1504,37 +1504,37 @@
         <v>2.204850111028867</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.663992004628844</v>
+        <v>7.663966005296595</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1722248364657764</v>
+        <v>0.1721988371335275</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148855142485643</v>
+        <v>0.9148818070071246</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198075300508691</v>
+        <v>1.198080256415399</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8296392220560928</v>
+        <v>0.829640509377564</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6542989676955044</v>
+        <v>0.6542961076655751</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279732777591687</v>
+        <v>0.8279758845797973</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.88865932688865</v>
+        <v>4.695699667807226</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.427058289827587</v>
+        <v>5.371932800127952</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.790551977457985</v>
+        <v>5.788250884541244</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E13" t="n">
         <v>6455</v>
@@ -1590,40 +1590,40 @@
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.856452631578947</v>
+        <v>2.855960729312763</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02933949250868</v>
+        <v>10.02924903794622</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.412464718431733</v>
+        <v>0.4123742638692721</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694139947021636</v>
+        <v>1.694148983335669</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153836132298142</v>
+        <v>2.153858919057276</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232106471249144</v>
+        <v>0.8232089814865454</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485322871070623</v>
+        <v>0.6485248502808694</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115211141183096</v>
+        <v>0.8115318648634863</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.51606357643612</v>
+        <v>6.859999999999999</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.157190665009615</v>
+        <v>7.256918234424125</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.496896388028895</v>
+        <v>7.50614516227732</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E14" t="n">
         <v>14043</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201318045262239</v>
+        <v>8.201190508550814</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06743443777096272</v>
+        <v>0.06730690105953779</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758340474150294</v>
+        <v>1.758276864338461</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283939452220622</v>
+        <v>2.283885818514942</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810377724459555</v>
+        <v>0.7810563480446803</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653444927342492</v>
+        <v>0.5653649065081838</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807162802818185</v>
+        <v>0.7807370600311463</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.662377686795568</v>
+        <v>5.646205864428153</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.753209597328956</v>
+        <v>5.730629748839364</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.834052065647991</v>
+        <v>5.808826002356566</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82379360186534</v>
+        <v>11.82371367533084</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1400882955209135</v>
+        <v>-0.1401682220554102</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052201584861661</v>
+        <v>2.052160499712931</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697456540785099</v>
+        <v>2.697406829799576</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949275488384075</v>
+        <v>0.7949396183613539</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096497882997591</v>
+        <v>0.6096641755676364</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861645876477613</v>
+        <v>0.7861825869125624</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.142742431299487</v>
+        <v>8.185170225780448</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.258406671366419</v>
+        <v>8.278050773082438</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.367895958006461</v>
+        <v>8.367926939890825</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E16" t="n">
         <v>9806</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.661114416909873</v>
+        <v>8.660930998633022</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2528441402085342</v>
+        <v>0.2526607219316838</v>
       </c>
       <c r="T16" t="n">
-        <v>3.538013284070084</v>
+        <v>3.537965856759897</v>
       </c>
       <c r="U16" t="n">
-        <v>11.06322751103158</v>
+        <v>11.0632167060009</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04950621426080914</v>
+        <v>0.04950337898753105</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971392414368539</v>
+        <v>-0.5971361217088973</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03275349543507022</v>
+        <v>0.03275061065089158</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.19944027194115</v>
+        <v>12.19450070642606</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.27539869221618</v>
+        <v>12.26178715115043</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.40765716695299</v>
+        <v>12.38018225903756</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E17" t="n">
         <v>2350</v>
@@ -1949,37 +1949,37 @@
         <v>1.395549592894153</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910515846641801</v>
+        <v>6.910507843997997</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.370849889194992</v>
+        <v>0.3708418865511887</v>
       </c>
       <c r="T17" t="n">
-        <v>2.03218575594767</v>
+        <v>2.032212527567567</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566472703470675</v>
+        <v>2.566495551540985</v>
       </c>
       <c r="V17" t="n">
-        <v>0.521060590631385</v>
+        <v>0.5210579016806873</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0223762707058669</v>
+        <v>0.02235886400202791</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177145910901881</v>
+        <v>0.5177120840106946</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.821068080498486</v>
+        <v>2.620849998451471</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.664647646552735</v>
+        <v>3.282241302959277</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.988895690351775</v>
+        <v>4.766382813429945</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E18" t="n">
         <v>3209</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692623521242465</v>
+        <v>6.692629678808957</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948625365120192</v>
+        <v>0.1948686940785115</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099848653929772</v>
+        <v>1.099878204578519</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489338857489405</v>
+        <v>1.489365611231031</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009722745548213</v>
+        <v>0.6009616198817331</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2173731237048351</v>
+        <v>0.2173450060132905</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980539989343168</v>
+        <v>0.5980442351169446</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.885747758006145</v>
+        <v>3.515307564166402</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.932722106059918</v>
+        <v>4.556273079160695</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.473059027179137</v>
+        <v>6.378712431775681</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16677</v>
+        <v>16678</v>
       </c>
       <c r="E19" t="n">
         <v>7163</v>
@@ -2127,37 +2127,37 @@
         <v>4.725023439427584</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15198017556644</v>
+        <v>11.15187197536088</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7826607563286861</v>
+        <v>0.7825525561231313</v>
       </c>
       <c r="T19" t="n">
-        <v>2.03816527613878</v>
+        <v>2.038171329826008</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757749321076525</v>
+        <v>2.757761652829005</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263094445359948</v>
+        <v>0.7263057187853237</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693264011580318</v>
+        <v>0.4693216551500827</v>
       </c>
       <c r="X19" t="n">
-        <v>0.679197201574009</v>
+        <v>0.6792156189390337</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.479862627669783</v>
+        <v>7.364946877106063</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.582717150339707</v>
+        <v>7.527914108458809</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.696822322380537</v>
+        <v>7.661101343825539</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.479862627669783</v>
+        <v>7.364946877106063</v>
       </c>
       <c r="G2" t="n">
-        <v>7.582717150339707</v>
+        <v>7.527914108458809</v>
       </c>
       <c r="H2" t="n">
-        <v>7.696822322380537</v>
+        <v>7.661101343825539</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.45</v>
+        <v>5.421912108461898</v>
       </c>
       <c r="G3" t="n">
-        <v>5.509897371904797</v>
+        <v>5.493721762514741</v>
       </c>
       <c r="H3" t="n">
-        <v>5.586148741776316</v>
+        <v>5.58658330776648</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6751378282692</v>
+        <v>3.714509116409537</v>
       </c>
       <c r="G4" t="n">
-        <v>3.989387378086155</v>
+        <v>4.054062933294</v>
       </c>
       <c r="H4" t="n">
-        <v>4.38</v>
+        <v>4.36934885794919</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.19944027194115</v>
+        <v>12.19450070642606</v>
       </c>
       <c r="G5" t="n">
-        <v>12.27539869221618</v>
+        <v>12.26178715115043</v>
       </c>
       <c r="H5" t="n">
-        <v>12.40765716695299</v>
+        <v>12.38018225903756</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>53.8113590992585</v>
+        <v>6.779915940319707</v>
       </c>
       <c r="G6" t="n">
-        <v>76.58925228370541</v>
+        <v>61.60049016595824</v>
       </c>
       <c r="H6" t="n">
-        <v>111.5843586804372</v>
+        <v>113.6871824875759</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.142742431299487</v>
+        <v>8.185170225780448</v>
       </c>
       <c r="G7" t="n">
-        <v>8.258406671366419</v>
+        <v>8.278050773082438</v>
       </c>
       <c r="H7" t="n">
-        <v>8.367895958006461</v>
+        <v>8.367926939890825</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.51606357643612</v>
+        <v>6.859999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>7.157190665009615</v>
+        <v>7.256918234424125</v>
       </c>
       <c r="H8" t="n">
-        <v>7.496896388028895</v>
+        <v>7.50614516227732</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.88865932688865</v>
+        <v>4.695699667807226</v>
       </c>
       <c r="G9" t="n">
-        <v>5.427058289827587</v>
+        <v>5.371932800127952</v>
       </c>
       <c r="H9" t="n">
-        <v>5.790551977457985</v>
+        <v>5.788250884541244</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.057563461042311</v>
+        <v>5.051564423991519</v>
       </c>
       <c r="G10" t="n">
-        <v>5.081659548941643</v>
+        <v>5.071332216233718</v>
       </c>
       <c r="H10" t="n">
-        <v>5.140229762333649</v>
+        <v>5.098928894463176</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.821068080498486</v>
+        <v>2.620849998451471</v>
       </c>
       <c r="G11" t="n">
-        <v>3.664647646552735</v>
+        <v>3.282241302959277</v>
       </c>
       <c r="H11" t="n">
-        <v>4.988895690351775</v>
+        <v>4.766382813429945</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.662377686795568</v>
+        <v>5.646205864428153</v>
       </c>
       <c r="G12" t="n">
-        <v>5.753209597328957</v>
+        <v>5.730629748839364</v>
       </c>
       <c r="H12" t="n">
-        <v>5.834052065647991</v>
+        <v>5.808826002356566</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>8.631464227164843</v>
+        <v>8.829352782559743</v>
       </c>
       <c r="G13" t="n">
-        <v>9.38794343574062</v>
+        <v>9.46776054862031</v>
       </c>
       <c r="H13" t="n">
-        <v>9.708458547034192</v>
+        <v>9.6975</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.38537692875365</v>
+        <v>5.338997082553773</v>
       </c>
       <c r="G14" t="n">
-        <v>5.442155852161889</v>
+        <v>5.430171164893284</v>
       </c>
       <c r="H14" t="n">
-        <v>5.501080645188124</v>
+        <v>5.5037147827683</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.347474232879496</v>
+        <v>6.334772521277599</v>
       </c>
       <c r="G15" t="n">
-        <v>6.481170853606185</v>
+        <v>6.457578602561989</v>
       </c>
       <c r="H15" t="n">
-        <v>6.581319785402147</v>
+        <v>6.553300030268006</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.885747758006145</v>
+        <v>3.515307564166402</v>
       </c>
       <c r="G16" t="n">
-        <v>4.932722106059918</v>
+        <v>4.556273079160695</v>
       </c>
       <c r="H16" t="n">
-        <v>6.473059027179137</v>
+        <v>6.378712431775681</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.121033333333334</v>
+        <v>3.069817671809257</v>
       </c>
       <c r="G17" t="n">
-        <v>3.422294897495039</v>
+        <v>3.323721962872383</v>
       </c>
       <c r="H17" t="n">
-        <v>3.921157894736842</v>
+        <v>3.78656381486676</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.355662938596491</v>
+        <v>2.354343151005143</v>
       </c>
       <c r="G18" t="n">
-        <v>2.375732828218138</v>
+        <v>2.378160030414087</v>
       </c>
       <c r="H18" t="n">
-        <v>2.41221052631579</v>
+        <v>2.425413744740533</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.493099059077945</v>
+        <v>5.492220254409895</v>
       </c>
       <c r="G19" t="n">
-        <v>5.54567468541615</v>
+        <v>5.520548619005934</v>
       </c>
       <c r="H19" t="n">
-        <v>5.693452631578947</v>
+        <v>5.616644852905435</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,13 +576,13 @@
         <v>16678</v>
       </c>
       <c r="E2" t="n">
-        <v>9965</v>
+        <v>10015</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9965</v>
+        <v>10013</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46247</v>
+        <v>46264</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.8526290349557</v>
+        <v>102.6906714604348</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.8808699016457</v>
+        <v>102.6896485617225</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02824086669005615</v>
+        <v>-0.001022898712237852</v>
       </c>
       <c r="T2" t="n">
-        <v>17.79387715177367</v>
+        <v>17.90088743388012</v>
       </c>
       <c r="U2" t="n">
-        <v>36.18211135545523</v>
+        <v>36.07609960298244</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1284730177187951</v>
+        <v>0.1330197394166979</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7368067120834725</v>
+        <v>-0.7292778802905544</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1284655718931461</v>
+        <v>0.1330155202651051</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.779915940319707</v>
+        <v>54.2122702924672</v>
       </c>
       <c r="Z2" t="n">
-        <v>61.60049016595825</v>
+        <v>63.4043961066006</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.6871824875759</v>
+        <v>113.6672677238978</v>
       </c>
     </row>
     <row r="3">
@@ -665,13 +665,13 @@
         <v>16678</v>
       </c>
       <c r="E3" t="n">
-        <v>14544</v>
+        <v>14609</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14544</v>
+        <v>14607</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.906011413641364</v>
+        <v>4.910867734647772</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.959121117581077</v>
+        <v>4.970398674220679</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05310970393971277</v>
+        <v>0.05953093957290757</v>
       </c>
       <c r="T3" t="n">
-        <v>1.350436468986679</v>
+        <v>1.346116545584293</v>
       </c>
       <c r="U3" t="n">
-        <v>1.725346708643728</v>
+        <v>1.721342780531437</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7795624227984262</v>
+        <v>0.7809582707555675</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5664568310255828</v>
+        <v>0.568608232859743</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7785374063652714</v>
+        <v>0.7799559403364523</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.354343151005143</v>
+        <v>2.368756428237494</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.378160030414087</v>
+        <v>2.392235083316735</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.425413744740533</v>
+        <v>2.453702664796634</v>
       </c>
     </row>
     <row r="4">
@@ -754,13 +754,13 @@
         <v>16678</v>
       </c>
       <c r="E4" t="n">
-        <v>10226</v>
+        <v>10244</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10226</v>
+        <v>10242</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M4" t="n">
         <v>3.469446951953614e-18</v>
       </c>
       <c r="N4" t="n">
-        <v>6.917974281243887</v>
+        <v>6.912781439172037</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3646318373071529</v>
+        <v>0.3677910238429172</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.246004740709422</v>
+        <v>7.241560048762221</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3280304594655336</v>
+        <v>0.3287786095901843</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293881835818342</v>
+        <v>1.293012288785153</v>
       </c>
       <c r="U4" t="n">
-        <v>1.683876342026507</v>
+        <v>1.682672605421835</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8674604421552005</v>
+        <v>0.8676547257090895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7371002290709816</v>
+        <v>0.7374881233164372</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473755538084683</v>
+        <v>0.8473207637085373</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.069817671809257</v>
+        <v>3.118541374474054</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.323721962872383</v>
+        <v>3.346306899098113</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.78656381486676</v>
+        <v>3.781882889200561</v>
       </c>
     </row>
     <row r="5">
@@ -896,13 +896,13 @@
         <v>1.747802171092971</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675159960489112</v>
+        <v>0.8675159960489113</v>
       </c>
       <c r="W5" t="n">
         <v>0.7234663446218912</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616027395273647</v>
+        <v>0.8616027395273648</v>
       </c>
       <c r="Y5" t="n">
         <v>5.492220254409895</v>
@@ -932,13 +932,13 @@
         <v>16678</v>
       </c>
       <c r="E6" t="n">
-        <v>8837</v>
+        <v>8856</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8837</v>
+        <v>8854</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.730817585153333</v>
+        <v>6.732042579625029</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.018995385618139</v>
+        <v>7.020374396260856</v>
       </c>
       <c r="R6" t="n">
         <v>10.19100035038542</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2881778004648057</v>
+        <v>0.2883318166358275</v>
       </c>
       <c r="T6" t="n">
-        <v>1.482297613960537</v>
+        <v>1.480249685323974</v>
       </c>
       <c r="U6" t="n">
-        <v>1.910956628683486</v>
+        <v>1.909117711413435</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047846997467092</v>
+        <v>0.3048342458819045</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1985186960233318</v>
+        <v>-0.1976769646224596</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2802706052882724</v>
+        <v>0.2801152948671131</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.334772521277599</v>
+        <v>6.357777109107677</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.457578602561989</v>
+        <v>6.490042110411133</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.553300030268006</v>
+        <v>6.587712205457368</v>
       </c>
     </row>
     <row r="7">
@@ -1021,13 +1021,13 @@
         <v>16678</v>
       </c>
       <c r="E7" t="n">
-        <v>14199</v>
+        <v>14217</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14199</v>
+        <v>14215</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.582571836044792</v>
+        <v>5.581389201547662</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.586373244884039</v>
+        <v>5.585202384584176</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003801408839248445</v>
+        <v>0.00381318303651521</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156274014382261</v>
+        <v>1.156312095166979</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494392108455455</v>
+        <v>1.494036536503168</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5088155594709983</v>
+        <v>0.50863825256256</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07413483800519038</v>
+        <v>0.07403789190274879</v>
       </c>
       <c r="X7" t="n">
-        <v>0.504997794656004</v>
+        <v>0.5047877710869111</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.421912108461898</v>
+        <v>5.397098527349229</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.493721762514741</v>
+        <v>5.475465026698958</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.58658330776648</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="8">
@@ -1110,13 +1110,13 @@
         <v>16678</v>
       </c>
       <c r="E8" t="n">
-        <v>8997</v>
+        <v>9015</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>8997</v>
+        <v>9013</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.880357063465601</v>
+        <v>7.878841118384555</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116195756098076</v>
+        <v>8.117218328758954</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.235838692632477</v>
+        <v>0.238377210374398</v>
       </c>
       <c r="T8" t="n">
-        <v>1.445497549455948</v>
+        <v>1.446544339168464</v>
       </c>
       <c r="U8" t="n">
-        <v>1.825202248431199</v>
+        <v>1.826213462409566</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8086989136737037</v>
+        <v>0.8080747106445102</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6287927435811242</v>
+        <v>0.6277758918006988</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7991308756524551</v>
+        <v>0.7981870460652147</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.051564423991519</v>
+        <v>5.094949317271679</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.071332216233717</v>
+        <v>5.145003302011466</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.098928894463176</v>
+        <v>5.1796597919792</v>
       </c>
     </row>
     <row r="9">
@@ -1199,13 +1199,13 @@
         <v>16678</v>
       </c>
       <c r="E9" t="n">
-        <v>13862</v>
+        <v>13880</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13862</v>
+        <v>13878</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,52 +1222,52 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.615950800750253</v>
+        <v>7.613738470961233</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5070792426367461</v>
+        <v>0.5121458625525946</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.678938942515691</v>
+        <v>7.678078446575436</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06298814176543827</v>
+        <v>0.06433997561420315</v>
       </c>
       <c r="T9" t="n">
-        <v>1.477425481621679</v>
+        <v>1.476179811014038</v>
       </c>
       <c r="U9" t="n">
-        <v>1.919850213322672</v>
+        <v>1.918676437483803</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617532165858771</v>
+        <v>0.7617774583110782</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5360448031112057</v>
+        <v>0.5363425552563017</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7598347732403602</v>
+        <v>0.7597724265854706</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.338997082553773</v>
+        <v>5.357439265482557</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.430171164893284</v>
+        <v>5.454027783678277</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5037147827683</v>
+        <v>5.518064921790469</v>
       </c>
     </row>
     <row r="10">
@@ -1341,13 +1341,13 @@
         <v>2.697682582117695</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567063156688055</v>
+        <v>0.3567063156688057</v>
       </c>
       <c r="W10" t="n">
         <v>-0.1200911087179233</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360704612193633</v>
+        <v>0.3360704612193636</v>
       </c>
       <c r="Y10" t="n">
         <v>8.829352782559743</v>
@@ -1377,13 +1377,13 @@
         <v>16678</v>
       </c>
       <c r="E11" t="n">
-        <v>13803</v>
+        <v>13821</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13803</v>
+        <v>13819</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M11" t="n">
         <v>0.4375</v>
       </c>
       <c r="N11" t="n">
-        <v>5.245876439904369</v>
+        <v>5.244698060641146</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8401943005181348</v>
+        <v>0.8404015544041452</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.218173832845966</v>
+        <v>5.21728327729781</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02770260705840326</v>
+        <v>-0.02741478334333645</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15811271365606</v>
+        <v>1.157075611545854</v>
       </c>
       <c r="U11" t="n">
-        <v>1.477148894147647</v>
+        <v>1.476030978350841</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4294308888262925</v>
+        <v>0.4297876430155478</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08287592243959252</v>
+        <v>-0.08166853196224944</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4268625911690527</v>
+        <v>0.4271701418310883</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.714509116409537</v>
+        <v>3.71983783309958</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.054062933294</v>
+        <v>4.055040572658466</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.36934885794919</v>
+        <v>4.35998245012409</v>
       </c>
     </row>
     <row r="12">
@@ -1466,13 +1466,13 @@
         <v>16678</v>
       </c>
       <c r="E12" t="n">
-        <v>4121</v>
+        <v>4139</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4121</v>
+        <v>4137</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.491767168163068</v>
+        <v>7.482060067681894</v>
       </c>
       <c r="O12" t="n">
         <v>19.1775</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204850111028867</v>
+        <v>2.204872316802369</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.663966005296595</v>
+        <v>7.655459097966594</v>
       </c>
       <c r="R12" t="n">
         <v>16.78594914040094</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1721988371335275</v>
+        <v>0.1733990302846998</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9148818070071246</v>
+        <v>0.9136527960891979</v>
       </c>
       <c r="U12" t="n">
-        <v>1.198080256415399</v>
+        <v>1.196170430765482</v>
       </c>
       <c r="V12" t="n">
-        <v>0.829640509377564</v>
+        <v>0.8304246164533504</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6542961076655751</v>
+        <v>0.6561472742802531</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8279758845797973</v>
+        <v>0.8286790991683607</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.695699667807226</v>
+        <v>4.710124182062195</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.371932800127952</v>
+        <v>5.370678306531769</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.788250884541244</v>
+        <v>5.77222446347162</v>
       </c>
     </row>
     <row r="13">
@@ -1555,13 +1555,13 @@
         <v>16678</v>
       </c>
       <c r="E13" t="n">
-        <v>6455</v>
+        <v>6474</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6455</v>
+        <v>6472</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.616874774076942</v>
+        <v>9.610354089410796</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.855960729312763</v>
+        <v>2.867012622720898</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02924903794622</v>
+        <v>10.02853746801837</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4123742638692721</v>
+        <v>0.4181833786075758</v>
       </c>
       <c r="T13" t="n">
-        <v>1.694148983335669</v>
+        <v>1.692211330191271</v>
       </c>
       <c r="U13" t="n">
-        <v>2.153858919057276</v>
+        <v>2.152694898477574</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8232089814865454</v>
+        <v>0.8230682552892155</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485248502808694</v>
+        <v>0.6484136234160192</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8115318648634863</v>
+        <v>0.8106865637972768</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.859999999999999</v>
+        <v>7.056242033203179</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.256918234424125</v>
+        <v>7.28958317125318</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.50614516227732</v>
+        <v>7.501802957145521</v>
       </c>
     </row>
     <row r="14">
@@ -1644,13 +1644,13 @@
         <v>16678</v>
       </c>
       <c r="E14" t="n">
-        <v>14043</v>
+        <v>14061</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14043</v>
+        <v>14059</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.133883607491278</v>
+        <v>8.131185183867986</v>
       </c>
       <c r="O14" t="n">
         <v>34.0025</v>
@@ -1682,37 +1682,37 @@
         <v>0.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201190508550814</v>
+        <v>8.201715527948073</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06730690105953779</v>
+        <v>0.07053034408008757</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758276864338461</v>
+        <v>1.758172926293024</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283885818514942</v>
+        <v>2.283838549602897</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7810563480446803</v>
+        <v>0.7807328873536158</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653649065081838</v>
+        <v>0.5651191280682917</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7807370600311463</v>
+        <v>0.7803566372965142</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.646205864428153</v>
+        <v>5.701408138729529</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.730629748839364</v>
+        <v>5.766247428597521</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.808826002356566</v>
+        <v>5.834615881708721</v>
       </c>
     </row>
     <row r="15">
@@ -1786,13 +1786,13 @@
         <v>2.697406829799576</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949396183613539</v>
+        <v>0.794939618361354</v>
       </c>
       <c r="W15" t="n">
         <v>0.6096641755676364</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861825869125624</v>
+        <v>0.7861825869125625</v>
       </c>
       <c r="Y15" t="n">
         <v>8.185170225780448</v>
@@ -1822,13 +1822,13 @@
         <v>16678</v>
       </c>
       <c r="E16" t="n">
-        <v>9806</v>
+        <v>9824</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9806</v>
+        <v>9822</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.408270276701339</v>
+        <v>8.366959207221884</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.660930998633022</v>
+        <v>8.625148189088787</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2526607219316838</v>
+        <v>0.2581889818669041</v>
       </c>
       <c r="T16" t="n">
-        <v>3.537965856759897</v>
+        <v>3.587316728530579</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0632167060009</v>
+        <v>11.09633709582225</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04950337898753105</v>
+        <v>0.04207552692998427</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.5971361217088973</v>
+        <v>-0.6093092090031025</v>
       </c>
       <c r="X16" t="n">
-        <v>0.03275061065089158</v>
+        <v>0.02541403475121007</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.19450070642606</v>
+        <v>12.04843065824692</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.26178715115043</v>
+        <v>12.1136840635425</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.38018225903756</v>
+        <v>12.18738811809945</v>
       </c>
     </row>
     <row r="17">
@@ -1911,13 +1911,13 @@
         <v>16678</v>
       </c>
       <c r="E17" t="n">
-        <v>2350</v>
+        <v>2368</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2350</v>
+        <v>2366</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.539665957446808</v>
+        <v>6.514172654268807</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.395549592894153</v>
+        <v>1.397677646188009</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.910507843997997</v>
+        <v>6.884195960672264</v>
       </c>
       <c r="R17" t="n">
         <v>12.15738414192614</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3708418865511887</v>
+        <v>0.3700233064034543</v>
       </c>
       <c r="T17" t="n">
-        <v>2.032212527567567</v>
+        <v>2.030350113354972</v>
       </c>
       <c r="U17" t="n">
-        <v>2.566495551540985</v>
+        <v>2.563155766623516</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5210579016806873</v>
+        <v>0.5257589173893789</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02235886400202791</v>
+        <v>0.03210804649115162</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5177120840106946</v>
+        <v>0.5223685423255398</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.620849998451471</v>
+        <v>2.597023484543472</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.282241302959277</v>
+        <v>3.114960790894268</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.766382813429945</v>
+        <v>4.648058107735491</v>
       </c>
     </row>
     <row r="18">
@@ -2000,13 +2000,13 @@
         <v>16678</v>
       </c>
       <c r="E18" t="n">
-        <v>3209</v>
+        <v>3227</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3209</v>
+        <v>3225</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.497760984730445</v>
+        <v>6.486362015503876</v>
       </c>
       <c r="O18" t="n">
         <v>18.4925</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.692629678808957</v>
+        <v>6.683016701540381</v>
       </c>
       <c r="R18" t="n">
         <v>14.92774999999984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1948686940785115</v>
+        <v>0.1966546860365051</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099878204578519</v>
+        <v>1.102217887414638</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489365611231031</v>
+        <v>1.490104293322378</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6009616198817331</v>
+        <v>0.6020703850564639</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2173450060132905</v>
+        <v>0.2199812876005672</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5980442351169446</v>
+        <v>0.5990283513925507</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.515307564166402</v>
+        <v>3.601300529742196</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.556273079160695</v>
+        <v>4.480520733664797</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.378712431775681</v>
+        <v>6.360579189983765</v>
       </c>
     </row>
     <row r="19">
@@ -2089,13 +2089,13 @@
         <v>16678</v>
       </c>
       <c r="E19" t="n">
-        <v>7163</v>
+        <v>7181</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7163</v>
+        <v>7179</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46248</v>
+        <v>46264</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.36931941923775</v>
+        <v>10.35208315921438</v>
       </c>
       <c r="O19" t="n">
         <v>24.5875</v>
       </c>
       <c r="P19" t="n">
-        <v>4.725023439427584</v>
+        <v>3.792826086956522</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.15187197536088</v>
+        <v>11.13861741242315</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7825525561231313</v>
+        <v>0.7865342532087775</v>
       </c>
       <c r="T19" t="n">
-        <v>2.038171329826008</v>
+        <v>2.044422729484063</v>
       </c>
       <c r="U19" t="n">
-        <v>2.757761652829005</v>
+        <v>2.76508019754934</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7263057187853237</v>
+        <v>0.7268636728717575</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4693216551500827</v>
+        <v>0.470299285624082</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6792156189390337</v>
+        <v>0.6792741998830152</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.364946877106063</v>
+        <v>7.265520998023715</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.527914108458809</v>
+        <v>7.477395941551142</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.661101343825539</v>
+        <v>7.631835153651756</v>
       </c>
     </row>
   </sheetData>
@@ -2235,13 +2235,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.364946877106063</v>
+        <v>7.265520998023715</v>
       </c>
       <c r="G2" t="n">
-        <v>7.527914108458809</v>
+        <v>7.477395941551142</v>
       </c>
       <c r="H2" t="n">
-        <v>7.661101343825539</v>
+        <v>7.631835153651756</v>
       </c>
     </row>
     <row r="3">
@@ -2263,13 +2263,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.421912108461898</v>
+        <v>5.397098527349229</v>
       </c>
       <c r="G3" t="n">
-        <v>5.493721762514741</v>
+        <v>5.475465026698958</v>
       </c>
       <c r="H3" t="n">
-        <v>5.58658330776648</v>
+        <v>5.56</v>
       </c>
     </row>
     <row r="4">
@@ -2291,13 +2291,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.714509116409537</v>
+        <v>3.71983783309958</v>
       </c>
       <c r="G4" t="n">
-        <v>4.054062933294</v>
+        <v>4.055040572658466</v>
       </c>
       <c r="H4" t="n">
-        <v>4.36934885794919</v>
+        <v>4.35998245012409</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.19450070642606</v>
+        <v>12.04843065824692</v>
       </c>
       <c r="G5" t="n">
-        <v>12.26178715115043</v>
+        <v>12.1136840635425</v>
       </c>
       <c r="H5" t="n">
-        <v>12.38018225903756</v>
+        <v>12.18738811809945</v>
       </c>
     </row>
     <row r="6">
@@ -2347,13 +2347,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>6.779915940319707</v>
+        <v>54.2122702924672</v>
       </c>
       <c r="G6" t="n">
-        <v>61.60049016595824</v>
+        <v>63.4043961066006</v>
       </c>
       <c r="H6" t="n">
-        <v>113.6871824875759</v>
+        <v>113.6672677238978</v>
       </c>
     </row>
     <row r="7">
@@ -2403,13 +2403,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>6.859999999999999</v>
+        <v>7.056242033203179</v>
       </c>
       <c r="G8" t="n">
-        <v>7.256918234424125</v>
+        <v>7.28958317125318</v>
       </c>
       <c r="H8" t="n">
-        <v>7.50614516227732</v>
+        <v>7.501802957145521</v>
       </c>
     </row>
     <row r="9">
@@ -2431,13 +2431,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.695699667807226</v>
+        <v>4.710124182062195</v>
       </c>
       <c r="G9" t="n">
-        <v>5.371932800127952</v>
+        <v>5.370678306531769</v>
       </c>
       <c r="H9" t="n">
-        <v>5.788250884541244</v>
+        <v>5.77222446347162</v>
       </c>
     </row>
     <row r="10">
@@ -2459,13 +2459,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.051564423991519</v>
+        <v>5.094949317271679</v>
       </c>
       <c r="G10" t="n">
-        <v>5.071332216233718</v>
+        <v>5.145003302011466</v>
       </c>
       <c r="H10" t="n">
-        <v>5.098928894463176</v>
+        <v>5.1796597919792</v>
       </c>
     </row>
     <row r="11">
@@ -2487,13 +2487,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.620849998451471</v>
+        <v>2.597023484543472</v>
       </c>
       <c r="G11" t="n">
-        <v>3.282241302959277</v>
+        <v>3.114960790894268</v>
       </c>
       <c r="H11" t="n">
-        <v>4.766382813429945</v>
+        <v>4.648058107735491</v>
       </c>
     </row>
     <row r="12">
@@ -2515,13 +2515,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.646205864428153</v>
+        <v>5.701408138729529</v>
       </c>
       <c r="G12" t="n">
-        <v>5.730629748839364</v>
+        <v>5.766247428597519</v>
       </c>
       <c r="H12" t="n">
-        <v>5.808826002356566</v>
+        <v>5.834615881708721</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.338997082553773</v>
+        <v>5.357439265482557</v>
       </c>
       <c r="G14" t="n">
-        <v>5.430171164893284</v>
+        <v>5.454027783678278</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5037147827683</v>
+        <v>5.518064921790469</v>
       </c>
     </row>
     <row r="15">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.334772521277599</v>
+        <v>6.357777109107677</v>
       </c>
       <c r="G15" t="n">
-        <v>6.457578602561989</v>
+        <v>6.490042110411133</v>
       </c>
       <c r="H15" t="n">
-        <v>6.553300030268006</v>
+        <v>6.587712205457368</v>
       </c>
     </row>
     <row r="16">
@@ -2627,13 +2627,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.515307564166402</v>
+        <v>3.601300529742196</v>
       </c>
       <c r="G16" t="n">
-        <v>4.556273079160695</v>
+        <v>4.480520733664797</v>
       </c>
       <c r="H16" t="n">
-        <v>6.378712431775681</v>
+        <v>6.360579189983765</v>
       </c>
     </row>
     <row r="17">
@@ -2655,13 +2655,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.069817671809257</v>
+        <v>3.118541374474054</v>
       </c>
       <c r="G17" t="n">
-        <v>3.323721962872383</v>
+        <v>3.346306899098112</v>
       </c>
       <c r="H17" t="n">
-        <v>3.78656381486676</v>
+        <v>3.781882889200561</v>
       </c>
     </row>
     <row r="18">
@@ -2683,13 +2683,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.354343151005143</v>
+        <v>2.368756428237494</v>
       </c>
       <c r="G18" t="n">
-        <v>2.378160030414087</v>
+        <v>2.392235083316735</v>
       </c>
       <c r="H18" t="n">
-        <v>2.425413744740533</v>
+        <v>2.453702664796634</v>
       </c>
     </row>
     <row r="19">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -605,7 +605,7 @@
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6906714604348</v>
+        <v>102.6906714937248</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,28 +614,28 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6896485617225</v>
+        <v>102.6896485674421</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.001022898712237852</v>
+        <v>-0.001022926282754524</v>
       </c>
       <c r="T2" t="n">
-        <v>17.90088743388012</v>
+        <v>17.90088739487052</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07609960298244</v>
+        <v>36.07609952424219</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1330197394166979</v>
+        <v>0.1330197402686656</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7292778802905544</v>
+        <v>-0.7292778825454089</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1330155202651051</v>
+        <v>0.1330155211242021</v>
       </c>
       <c r="Y2" t="n">
         <v>54.2122702924672</v>
@@ -694,7 +694,7 @@
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910867734647772</v>
+        <v>4.910869548846443</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,34 +703,34 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.970398674220679</v>
+        <v>4.970370017927257</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05953093957290757</v>
+        <v>0.05950046908081324</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346116545584293</v>
+        <v>1.346114496846615</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721342780531437</v>
+        <v>1.721338736015662</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809582707555675</v>
+        <v>0.7809574529211892</v>
       </c>
       <c r="W3" t="n">
-        <v>0.568608232859743</v>
+        <v>0.5686104801736256</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799559403364523</v>
+        <v>0.7799548270661774</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.368756428237494</v>
+        <v>2.369005142589995</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.392235083316735</v>
+        <v>2.392320820138494</v>
       </c>
       <c r="AA3" t="n">
         <v>2.453702664796634</v>
@@ -754,13 +754,13 @@
         <v>16678</v>
       </c>
       <c r="E4" t="n">
-        <v>10244</v>
+        <v>10243</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10242</v>
+        <v>10241</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -780,10 +780,10 @@
         <v>46264</v>
       </c>
       <c r="M4" t="n">
-        <v>3.469446951953614e-18</v>
+        <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.912781439172037</v>
+        <v>6.913455717215117</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3677910238429172</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241560048762221</v>
+        <v>7.242082981964778</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3287786095901843</v>
+        <v>0.3286272647496611</v>
       </c>
       <c r="T4" t="n">
-        <v>1.293012288785153</v>
+        <v>1.292816266018385</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682672605421835</v>
+        <v>1.682416827161258</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676547257090895</v>
+        <v>0.8676517776654372</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374881233164372</v>
+        <v>0.7374801615420601</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473207637085373</v>
+        <v>0.8473485961396809</v>
       </c>
       <c r="Y4" t="n">
         <v>3.118541374474054</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.346306899098113</v>
+        <v>3.346248615062225</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.781882889200561</v>
+        <v>3.782207573632538</v>
       </c>
     </row>
     <row r="5">
@@ -896,13 +896,13 @@
         <v>1.747802171092971</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675159960489113</v>
+        <v>0.8675159960489112</v>
       </c>
       <c r="W5" t="n">
         <v>0.7234663446218912</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616027395273648</v>
+        <v>0.8616027395273647</v>
       </c>
       <c r="Y5" t="n">
         <v>5.492220254409895</v>
@@ -961,7 +961,7 @@
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732042579625029</v>
+        <v>6.73203851366614</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,34 +970,34 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020374396260856</v>
+        <v>7.020255453840806</v>
       </c>
       <c r="R6" t="n">
-        <v>10.19100035038542</v>
+        <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2883318166358275</v>
+        <v>0.2882169401746674</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480249685323974</v>
+        <v>1.480257906305684</v>
       </c>
       <c r="U6" t="n">
-        <v>1.909117711413435</v>
+        <v>1.909120111367177</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3048342458819045</v>
+        <v>0.3048265809678665</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1976769646224596</v>
+        <v>-0.1976852961869282</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801152948671131</v>
+        <v>0.2801132029583591</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.357777109107677</v>
+        <v>6.357332530929214</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.490042110411133</v>
+        <v>6.490100414261017</v>
       </c>
       <c r="AA6" t="n">
         <v>6.587712205457368</v>
@@ -1050,7 +1050,7 @@
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581389201547662</v>
+        <v>5.581389271895884</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,34 +1059,34 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585202384584176</v>
+        <v>5.585148475078397</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.00381318303651521</v>
+        <v>0.003759203182511718</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156312095166979</v>
+        <v>1.156312495922632</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494036536503168</v>
+        <v>1.494038869952501</v>
       </c>
       <c r="V7" t="n">
-        <v>0.50863825256256</v>
+        <v>0.508634330922404</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07403789190274879</v>
+        <v>0.07403524890662194</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047877710869111</v>
+        <v>0.5047832346992097</v>
       </c>
       <c r="Y7" t="n">
         <v>5.397098527349229</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.475465026698958</v>
+        <v>5.474961035545775</v>
       </c>
       <c r="AA7" t="n">
         <v>5.56</v>
@@ -1139,7 +1139,7 @@
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878841118384555</v>
+        <v>7.878839731498948</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,28 +1148,28 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.117218328758954</v>
+        <v>8.117183441579579</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.238377210374398</v>
+        <v>0.2383437100806337</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446544339168464</v>
+        <v>1.446544878590861</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826213462409566</v>
+        <v>1.826215009027135</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8080747106445102</v>
+        <v>0.8080740643588548</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6277758918006988</v>
+        <v>0.6277751815559078</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7981870460652147</v>
+        <v>0.7981883172933928</v>
       </c>
       <c r="Y8" t="n">
         <v>5.094949317271679</v>
@@ -1228,7 +1228,7 @@
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613738470961233</v>
+        <v>7.613740092232309</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,34 +1237,34 @@
         <v>0.5121458625525946</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.678078446575436</v>
+        <v>7.678046640746859</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06433997561420315</v>
+        <v>0.06430654851454878</v>
       </c>
       <c r="T9" t="n">
-        <v>1.476179811014038</v>
+        <v>1.476188755886866</v>
       </c>
       <c r="U9" t="n">
-        <v>1.918676437483803</v>
+        <v>1.91868199542625</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617774583110782</v>
+        <v>0.7617773745827052</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363425552563017</v>
+        <v>0.5363394941218308</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597724265854706</v>
+        <v>0.7597735214341813</v>
       </c>
       <c r="Y9" t="n">
         <v>5.357439265482557</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.454027783678277</v>
+        <v>5.454004456785436</v>
       </c>
       <c r="AA9" t="n">
         <v>5.518064921790469</v>
@@ -1314,49 +1314,49 @@
         <v>45930</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7875</v>
+        <v>3.788</v>
       </c>
       <c r="N10" t="n">
-        <v>10.30505953973775</v>
+        <v>10.30506168049237</v>
       </c>
       <c r="O10" t="n">
         <v>39.075</v>
       </c>
       <c r="P10" t="n">
-        <v>4.255000000000001</v>
+        <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61840905299219</v>
+        <v>10.61836788664196</v>
       </c>
       <c r="R10" t="n">
-        <v>14.31645908761767</v>
+        <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3133495132544339</v>
+        <v>0.3133062061495803</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05209209420786</v>
+        <v>2.052080469910438</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697682582117695</v>
+        <v>2.697681247345577</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567063156688057</v>
+        <v>0.356708186815885</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1200911087179233</v>
+        <v>-0.1200922659209638</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360704612193636</v>
+        <v>0.3360745962683287</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.829352782559743</v>
+        <v>8.829309634730393</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.46776054862031</v>
+        <v>9.46711515441522</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.6975</v>
+        <v>9.697780688277769</v>
       </c>
     </row>
     <row r="11">
@@ -1403,46 +1403,46 @@
         <v>46264</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4375</v>
+        <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244698060641146</v>
+        <v>5.244697119907374</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8404015544041452</v>
+        <v>0.8407564766839378</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21728327729781</v>
+        <v>5.21721316105104</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02741478334333645</v>
+        <v>-0.02748395885633394</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157075611545854</v>
+        <v>1.15706934557196</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476030978350841</v>
+        <v>1.476025167121765</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4297876430155478</v>
+        <v>0.4297842119340852</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08166853196224944</v>
+        <v>-0.08165905808942964</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4271701418310883</v>
+        <v>0.4271649610703731</v>
       </c>
       <c r="Y11" t="n">
         <v>3.71983783309958</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.055040572658466</v>
+        <v>4.054971624631458</v>
       </c>
       <c r="AA11" t="n">
         <v>4.35998245012409</v>
@@ -1495,46 +1495,46 @@
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.482060067681894</v>
+        <v>7.48205668358714</v>
       </c>
       <c r="O12" t="n">
-        <v>19.1775</v>
+        <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204872316802369</v>
+        <v>2.204846780162842</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.655459097966594</v>
+        <v>7.655344301024669</v>
       </c>
       <c r="R12" t="n">
-        <v>16.78594914040094</v>
+        <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1733990302846998</v>
+        <v>0.1732876174375279</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136527960891979</v>
+        <v>0.913659172876124</v>
       </c>
       <c r="U12" t="n">
-        <v>1.196170430765482</v>
+        <v>1.196184947295903</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8304246164533504</v>
+        <v>0.8304182677573997</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6561472742802531</v>
+        <v>0.6561384272702433</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8286790991683607</v>
+        <v>0.828675583330149</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.710124182062195</v>
+        <v>4.710449236591382</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.370678306531769</v>
+        <v>5.371077816683594</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.77222446347162</v>
+        <v>5.772463261796216</v>
       </c>
     </row>
     <row r="13">
@@ -1584,7 +1584,7 @@
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.610354089410796</v>
+        <v>9.610350355377008</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,34 +1593,34 @@
         <v>2.867012622720898</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02853746801837</v>
+        <v>10.02853607326574</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4181833786075758</v>
+        <v>0.4181857178887262</v>
       </c>
       <c r="T13" t="n">
-        <v>1.692211330191271</v>
+        <v>1.692233950813718</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152694898477574</v>
+        <v>2.152717391396771</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230682552892155</v>
+        <v>0.8230662531430464</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484136234160192</v>
+        <v>0.6484066101242858</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106865637972768</v>
+        <v>0.8106879612178957</v>
       </c>
       <c r="Y13" t="n">
         <v>7.056242033203179</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.28958317125318</v>
+        <v>7.289546329880511</v>
       </c>
       <c r="AA13" t="n">
         <v>7.501802957145521</v>
@@ -1676,34 +1676,34 @@
         <v>8.131185183867986</v>
       </c>
       <c r="O14" t="n">
-        <v>34.0025</v>
+        <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.91</v>
+        <v>0.9072958302491981</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201715527948073</v>
+        <v>8.201682753277163</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07053034408008757</v>
+        <v>0.0704975694091797</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758172926293024</v>
+        <v>1.758178748701143</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283838549602897</v>
+        <v>2.283851056139783</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807328873536158</v>
+        <v>0.7807311512766536</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651191280682917</v>
+        <v>0.5651143839329245</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803566372965142</v>
+        <v>0.7803552372026163</v>
       </c>
       <c r="Y14" t="n">
         <v>5.701408138729529</v>
@@ -1762,7 +1762,7 @@
         <v>3.305</v>
       </c>
       <c r="N15" t="n">
-        <v>11.96388189738625</v>
+        <v>11.96388738302678</v>
       </c>
       <c r="O15" t="n">
         <v>30.745</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82371367533084</v>
+        <v>11.82363221201932</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1401682220554102</v>
+        <v>-0.1402551710074623</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052160499712931</v>
+        <v>2.052155899484289</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697406829799576</v>
+        <v>2.697410842317068</v>
       </c>
       <c r="V15" t="n">
-        <v>0.794939618361354</v>
+        <v>0.7949431031984362</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096641755676364</v>
+        <v>0.6096624848440153</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861825869125625</v>
+        <v>0.7861921477450722</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.185170225780448</v>
+        <v>8.185204270936538</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.278050773082438</v>
+        <v>8.278402865034325</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.367926939890825</v>
+        <v>8.36834155191266</v>
       </c>
     </row>
     <row r="16">
@@ -1851,7 +1851,7 @@
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.366959207221884</v>
+        <v>8.36695825697414</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,34 +1860,34 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625148189088787</v>
+        <v>8.62512287130502</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2581889818669041</v>
+        <v>0.2581646143308801</v>
       </c>
       <c r="T16" t="n">
-        <v>3.587316728530579</v>
+        <v>3.587316132499874</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09633709582225</v>
+        <v>11.09633421613992</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04207552692998427</v>
+        <v>0.0420766611842518</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6093092090031025</v>
+        <v>-0.6093084797202026</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02541403475121007</v>
+        <v>0.02541539293940942</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.04843065824692</v>
+        <v>12.04832603546338</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.1136840635425</v>
+        <v>12.11373755936092</v>
       </c>
       <c r="AA16" t="n">
         <v>12.18738811809945</v>
@@ -1940,43 +1940,43 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.514172654268807</v>
+        <v>6.514169484361792</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.397677646188009</v>
+        <v>1.397828275351592</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.884195960672264</v>
+        <v>6.884215441836128</v>
       </c>
       <c r="R17" t="n">
-        <v>12.15738414192614</v>
+        <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3700233064034543</v>
+        <v>0.3700459574743356</v>
       </c>
       <c r="T17" t="n">
-        <v>2.030350113354972</v>
+        <v>2.030358657046226</v>
       </c>
       <c r="U17" t="n">
-        <v>2.563155766623516</v>
+        <v>2.563167060092099</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5257589173893789</v>
+        <v>0.5257542071878871</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03210804649115162</v>
+        <v>0.03210480538320581</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5223685423255398</v>
+        <v>0.5223634334889888</v>
       </c>
       <c r="Y17" t="n">
         <v>2.597023484543472</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.114960790894268</v>
+        <v>3.114948264342488</v>
       </c>
       <c r="AA17" t="n">
         <v>4.648058107735491</v>
@@ -2029,46 +2029,46 @@
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.486362015503876</v>
+        <v>6.486369457364341</v>
       </c>
       <c r="O18" t="n">
-        <v>18.4925</v>
+        <v>18.492</v>
       </c>
       <c r="P18" t="n">
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.683016701540381</v>
+        <v>6.682879172389714</v>
       </c>
       <c r="R18" t="n">
-        <v>14.92774999999984</v>
+        <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1966546860365051</v>
+        <v>0.1965097150253723</v>
       </c>
       <c r="T18" t="n">
-        <v>1.102217887414638</v>
+        <v>1.102213031019378</v>
       </c>
       <c r="U18" t="n">
-        <v>1.490104293322378</v>
+        <v>1.490082844441327</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6020703850564639</v>
+        <v>0.6020713489038736</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2199812876005672</v>
+        <v>0.2199995356822289</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5990283513925507</v>
+        <v>0.5990314796927951</v>
       </c>
       <c r="Y18" t="n">
         <v>3.601300529742196</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.480520733664797</v>
+        <v>4.480402340304797</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.360579189983765</v>
+        <v>6.360463351987012</v>
       </c>
     </row>
     <row r="19">
@@ -2118,46 +2118,46 @@
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.35208315921438</v>
+        <v>10.35208406463296</v>
       </c>
       <c r="O19" t="n">
-        <v>24.5875</v>
+        <v>24.588</v>
       </c>
       <c r="P19" t="n">
         <v>3.792826086956522</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13861741242315</v>
+        <v>11.1385144630683</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7865342532087775</v>
+        <v>0.7864303984353401</v>
       </c>
       <c r="T19" t="n">
-        <v>2.044422729484063</v>
+        <v>2.044428868705638</v>
       </c>
       <c r="U19" t="n">
-        <v>2.76508019754934</v>
+        <v>2.765075385918426</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7268636728717575</v>
+        <v>0.7268626909168581</v>
       </c>
       <c r="W19" t="n">
-        <v>0.470299285624082</v>
+        <v>0.4703005431211329</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6792741998830152</v>
+        <v>0.6792915741614496</v>
       </c>
       <c r="Y19" t="n">
         <v>7.265520998023715</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.477395941551142</v>
+        <v>7.477466845616521</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.631835153651756</v>
+        <v>7.631835153651755</v>
       </c>
     </row>
   </sheetData>
@@ -2238,10 +2238,10 @@
         <v>7.265520998023715</v>
       </c>
       <c r="G2" t="n">
-        <v>7.477395941551142</v>
+        <v>7.477466845616521</v>
       </c>
       <c r="H2" t="n">
-        <v>7.631835153651756</v>
+        <v>7.631835153651755</v>
       </c>
     </row>
     <row r="3">
@@ -2266,7 +2266,7 @@
         <v>5.397098527349229</v>
       </c>
       <c r="G3" t="n">
-        <v>5.475465026698958</v>
+        <v>5.474961035545776</v>
       </c>
       <c r="H3" t="n">
         <v>5.56</v>
@@ -2294,7 +2294,7 @@
         <v>3.71983783309958</v>
       </c>
       <c r="G4" t="n">
-        <v>4.055040572658466</v>
+        <v>4.054971624631458</v>
       </c>
       <c r="H4" t="n">
         <v>4.35998245012409</v>
@@ -2319,10 +2319,10 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04843065824692</v>
+        <v>12.04832603546338</v>
       </c>
       <c r="G5" t="n">
-        <v>12.1136840635425</v>
+        <v>12.11373755936092</v>
       </c>
       <c r="H5" t="n">
         <v>12.18738811809945</v>
@@ -2375,13 +2375,13 @@
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.185170225780448</v>
+        <v>8.185204270936538</v>
       </c>
       <c r="G7" t="n">
-        <v>8.278050773082438</v>
+        <v>8.278402865034323</v>
       </c>
       <c r="H7" t="n">
-        <v>8.367926939890825</v>
+        <v>8.36834155191266</v>
       </c>
     </row>
     <row r="8">
@@ -2406,7 +2406,7 @@
         <v>7.056242033203179</v>
       </c>
       <c r="G8" t="n">
-        <v>7.28958317125318</v>
+        <v>7.289546329880511</v>
       </c>
       <c r="H8" t="n">
         <v>7.501802957145521</v>
@@ -2431,13 +2431,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.710124182062195</v>
+        <v>4.710449236591382</v>
       </c>
       <c r="G9" t="n">
-        <v>5.370678306531769</v>
+        <v>5.371077816683594</v>
       </c>
       <c r="H9" t="n">
-        <v>5.77222446347162</v>
+        <v>5.772463261796216</v>
       </c>
     </row>
     <row r="10">
@@ -2490,7 +2490,7 @@
         <v>2.597023484543472</v>
       </c>
       <c r="G11" t="n">
-        <v>3.114960790894268</v>
+        <v>3.114948264342488</v>
       </c>
       <c r="H11" t="n">
         <v>4.648058107735491</v>
@@ -2543,13 +2543,13 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>8.829352782559743</v>
+        <v>8.829309634730393</v>
       </c>
       <c r="G13" t="n">
-        <v>9.46776054862031</v>
+        <v>9.467115154415222</v>
       </c>
       <c r="H13" t="n">
-        <v>9.6975</v>
+        <v>9.697780688277769</v>
       </c>
     </row>
     <row r="14">
@@ -2574,7 +2574,7 @@
         <v>5.357439265482557</v>
       </c>
       <c r="G14" t="n">
-        <v>5.454027783678278</v>
+        <v>5.454004456785436</v>
       </c>
       <c r="H14" t="n">
         <v>5.518064921790469</v>
@@ -2599,10 +2599,10 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.357777109107677</v>
+        <v>6.357332530929214</v>
       </c>
       <c r="G15" t="n">
-        <v>6.490042110411133</v>
+        <v>6.490100414261017</v>
       </c>
       <c r="H15" t="n">
         <v>6.587712205457368</v>
@@ -2630,10 +2630,10 @@
         <v>3.601300529742196</v>
       </c>
       <c r="G16" t="n">
-        <v>4.480520733664797</v>
+        <v>4.480402340304797</v>
       </c>
       <c r="H16" t="n">
-        <v>6.360579189983765</v>
+        <v>6.360463351987012</v>
       </c>
     </row>
     <row r="17">
@@ -2658,10 +2658,10 @@
         <v>3.118541374474054</v>
       </c>
       <c r="G17" t="n">
-        <v>3.346306899098112</v>
+        <v>3.346248615062225</v>
       </c>
       <c r="H17" t="n">
-        <v>3.781882889200561</v>
+        <v>3.782207573632538</v>
       </c>
     </row>
     <row r="18">
@@ -2683,10 +2683,10 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.368756428237494</v>
+        <v>2.369005142589995</v>
       </c>
       <c r="G18" t="n">
-        <v>2.392235083316735</v>
+        <v>2.392320820138494</v>
       </c>
       <c r="H18" t="n">
         <v>2.453702664796634</v>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E2" t="n">
         <v>10015</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10013</v>
+        <v>10014</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6906714937248</v>
+        <v>102.6861792157646</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6896485674421</v>
+        <v>102.689009739731</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.001022926282754524</v>
+        <v>0.002830523966421524</v>
       </c>
       <c r="T2" t="n">
-        <v>17.90088739487052</v>
+        <v>17.89545808065111</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07609952424219</v>
+        <v>36.07129767522719</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1330197402686656</v>
+        <v>0.1333210387063704</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7292778825454089</v>
+        <v>-0.7285260922411831</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1330155211242021</v>
+        <v>0.1333165408876003</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.2122702924672</v>
+        <v>2.912843569578527</v>
       </c>
       <c r="Z2" t="n">
-        <v>63.4043961066006</v>
+        <v>41.28640940351707</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.6672677238978</v>
+        <v>110.8510766285012</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E3" t="n">
         <v>14609</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14607</v>
+        <v>14608</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910869548846443</v>
+        <v>4.910752430175247</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.970370017927257</v>
+        <v>4.970179215595354</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05950046908081324</v>
+        <v>0.0594267854201071</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346114496846615</v>
+        <v>1.346078553930526</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721338736015662</v>
+        <v>1.721298200603118</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809574529211892</v>
+        <v>0.7809650820394611</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5686104801736256</v>
+        <v>0.5686138504388025</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799548270661774</v>
+        <v>0.7799657123183301</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.369005142589995</v>
+        <v>2.347744263508512</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.392320820138494</v>
+        <v>2.373438806456725</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.453702664796634</v>
+        <v>2.416773131014064</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E4" t="n">
         <v>10243</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10241</v>
+        <v>10242</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,52 +777,52 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.913455717215117</v>
+        <v>6.913086555360283</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3677910238429172</v>
+        <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.242082981964778</v>
+        <v>7.241735353995565</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3286272647496611</v>
+        <v>0.328648798635284</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292816266018385</v>
+        <v>1.292757047722621</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682416827161258</v>
+        <v>1.682354161106473</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676517776654372</v>
+        <v>0.8676680839744625</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374801615420601</v>
+        <v>0.7375080658394116</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473485961396809</v>
+        <v>0.8473657121876228</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.118541374474054</v>
+        <v>3.166029607698001</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.346248615062225</v>
+        <v>3.272003314150408</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.782207573632538</v>
+        <v>3.43879348630644</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E5" t="n">
         <v>2690</v>
@@ -881,37 +881,37 @@
         <v>2.758763878608438</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313173985103596</v>
+        <v>9.313175399067909</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3583858810143764</v>
+        <v>0.3583872949786904</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254671363523135</v>
+        <v>1.254686531588547</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747802171092971</v>
+        <v>1.747826966371136</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675159960489112</v>
+        <v>0.8675140680676153</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234663446218912</v>
+        <v>0.7234584984506744</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616027395273647</v>
+        <v>0.8616008721326505</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.492220254409895</v>
+        <v>5.219952690330059</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.520548619005933</v>
+        <v>5.388487454562475</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.616644852905435</v>
+        <v>5.941239710217962</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E6" t="n">
         <v>8856</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8854</v>
+        <v>8855</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.73203851366614</v>
+        <v>6.732223771880294</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020255453840806</v>
+        <v>7.020228076727549</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2882169401746674</v>
+        <v>0.2880043048472559</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480257906305684</v>
+        <v>1.480309133597139</v>
       </c>
       <c r="U6" t="n">
-        <v>1.909120111367177</v>
+        <v>1.909129978063244</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3048265809678665</v>
+        <v>0.3047778290225198</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1976852961869282</v>
+        <v>-0.1977133364709032</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2801132029583591</v>
+        <v>0.2800651629809493</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.357332530929214</v>
+        <v>6.685588129914337</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.490100414261017</v>
+        <v>6.911493649875285</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.587712205457368</v>
+        <v>7.251740517686113</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E7" t="n">
         <v>14217</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14215</v>
+        <v>14216</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581389271895884</v>
+        <v>5.581388470737198</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585148475078397</v>
+        <v>5.585148741193324</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003759203182511718</v>
+        <v>0.003760270456127311</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156312495922632</v>
+        <v>1.156256777005878</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494038869952501</v>
+        <v>1.494012953552759</v>
       </c>
       <c r="V7" t="n">
-        <v>0.508634330922404</v>
+        <v>0.5086243111430219</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07403524890662194</v>
+        <v>0.07400223898013114</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047832346992097</v>
+        <v>0.5047753488012495</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.397098527349229</v>
+        <v>5.108303608695206</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.474961035545775</v>
+        <v>5.309195241233996</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.56</v>
+        <v>5.480871803221572</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E8" t="n">
         <v>9015</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9013</v>
+        <v>9014</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878839731498948</v>
+        <v>7.878764144663855</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.117183441579579</v>
+        <v>8.116841819602385</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2383437100806337</v>
+        <v>0.2380776749385301</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446544878590861</v>
+        <v>1.446620655820945</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826215009027135</v>
+        <v>1.826252932599022</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8080740643588548</v>
+        <v>0.808048175760023</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6277751815559078</v>
+        <v>0.6277205614557897</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7981883172933928</v>
+        <v>0.7981875352456688</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.094949317271679</v>
+        <v>5.315295939018699</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.145003302011466</v>
+        <v>5.402180135270693</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.1796597919792</v>
+        <v>5.435626785389175</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E9" t="n">
         <v>13880</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13878</v>
+        <v>13879</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,52 +1222,52 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613740092232309</v>
+        <v>7.613666510555515</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5121458625525946</v>
+        <v>0.511906096706377</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.678046640746859</v>
+        <v>7.67785423973371</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06430654851454878</v>
+        <v>0.06418772917819393</v>
       </c>
       <c r="T9" t="n">
-        <v>1.476188755886866</v>
+        <v>1.476165890152578</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91868199542625</v>
+        <v>1.91864458966539</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617773745827052</v>
+        <v>0.7617796237350358</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363394941218308</v>
+        <v>0.5363285524892349</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597735214341813</v>
+        <v>0.7597814086819279</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.357439265482557</v>
+        <v>5.473918578830497</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.454004456785436</v>
+        <v>5.612451432889739</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.518064921790469</v>
+        <v>5.669135115963484</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61836788664196</v>
+        <v>10.61830360848261</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3133062061495803</v>
+        <v>0.3132419279902305</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052080469910438</v>
+        <v>2.052127457844854</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697681247345577</v>
+        <v>2.697717988689959</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356708186815885</v>
+        <v>0.3567090026347503</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1200922659209638</v>
+        <v>-0.1201227765500246</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360745962683287</v>
+        <v>0.3360852749066027</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.829309634730393</v>
+        <v>9.550298577384853</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.46711515441522</v>
+        <v>9.708684097299713</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.697780688277769</v>
+        <v>9.88868319351849</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E11" t="n">
         <v>13821</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13819</v>
+        <v>13820</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244697119907374</v>
+        <v>5.244614833574529</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
@@ -1415,37 +1415,37 @@
         <v>0.8407564766839378</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21721316105104</v>
+        <v>5.217146335888257</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02748395885633394</v>
+        <v>-0.0274684976862732</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15706934557196</v>
+        <v>1.157019496623679</v>
       </c>
       <c r="U11" t="n">
-        <v>1.476025167121765</v>
+        <v>1.475995519512648</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4297842119340852</v>
+        <v>0.4298000096164736</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08165905808942964</v>
+        <v>-0.08164362437919426</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4271649610703731</v>
+        <v>0.4271820817016625</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.71983783309958</v>
+        <v>4.06412188502344</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.054971624631458</v>
+        <v>4.329292964809264</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.35998245012409</v>
+        <v>5.161031965227258</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E12" t="n">
         <v>4139</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4137</v>
+        <v>4138</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.48205668358714</v>
+        <v>7.481523924601255</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
@@ -1504,37 +1504,37 @@
         <v>2.204846780162842</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.655344301024669</v>
+        <v>7.65476037729406</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732876174375279</v>
+        <v>0.173236452692802</v>
       </c>
       <c r="T12" t="n">
-        <v>0.913659172876124</v>
+        <v>0.9134554389495751</v>
       </c>
       <c r="U12" t="n">
-        <v>1.196184947295903</v>
+        <v>1.196039966154902</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8304182677573997</v>
+        <v>0.8304713705209866</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6561384272702433</v>
+        <v>0.656235706463669</v>
       </c>
       <c r="X12" t="n">
-        <v>0.828675583330149</v>
+        <v>0.82873057801929</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.710449236591382</v>
+        <v>4.5952371684785</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.371077816683594</v>
+        <v>5.267672983692693</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.772463261796216</v>
+        <v>5.669282478707776</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E13" t="n">
         <v>6474</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6472</v>
+        <v>6473</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,52 +1578,52 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.610350355377008</v>
+        <v>9.610049436119265</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
       </c>
       <c r="P13" t="n">
-        <v>2.867012622720898</v>
+        <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02853607326574</v>
+        <v>10.02793187941023</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4181857178887262</v>
+        <v>0.4178824432909616</v>
       </c>
       <c r="T13" t="n">
-        <v>1.692233950813718</v>
+        <v>1.692048846736125</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152717391396771</v>
+        <v>2.152547161816404</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230662531430464</v>
+        <v>0.8230770572156101</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484066101242858</v>
+        <v>0.6484235316213709</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106879612178957</v>
+        <v>0.8107280587331728</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.056242033203179</v>
+        <v>8.320828988284271</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.289546329880511</v>
+        <v>8.414392829066648</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.501802957145521</v>
+        <v>8.491946242742888</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E14" t="n">
         <v>14061</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14059</v>
+        <v>14060</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.131185183867986</v>
+        <v>8.131050675675676</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
@@ -1682,37 +1682,37 @@
         <v>0.9072958302491981</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201682753277163</v>
+        <v>8.201388995370802</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0704975694091797</v>
+        <v>0.07033831969512572</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758178748701143</v>
+        <v>1.758012138682411</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283851056139783</v>
+        <v>2.28371717660352</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807311512766536</v>
+        <v>0.7807551858481971</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651143839329245</v>
+        <v>0.5651436621401921</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803552372026163</v>
+        <v>0.7803820680486027</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.701408138729529</v>
+        <v>5.515473195085712</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.766247428597521</v>
+        <v>5.800247899732044</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.834615881708721</v>
+        <v>6.21972569691054</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1771,37 +1771,37 @@
         <v>4.682413027387121</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82363221201932</v>
+        <v>11.82354900480542</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1402551710074623</v>
+        <v>-0.1403383782213606</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052155899484289</v>
+        <v>2.052113450111469</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697410842317068</v>
+        <v>2.697360330414803</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949431031984362</v>
+        <v>0.7949554435801198</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096624848440153</v>
+        <v>0.6096771036818271</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7861921477450722</v>
+        <v>0.7862106033520293</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.185204270936538</v>
+        <v>11.09294973219496</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.278402865034325</v>
+        <v>11.55848666803439</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.36834155191266</v>
+        <v>11.79955244946211</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E16" t="n">
         <v>9824</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9822</v>
+        <v>9823</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.36695825697414</v>
+        <v>8.366753435813907</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.62512287130502</v>
+        <v>8.625278087253589</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2581646143308801</v>
+        <v>0.2585246514396822</v>
       </c>
       <c r="T16" t="n">
-        <v>3.587316132499874</v>
+        <v>3.587500062973692</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09633421613992</v>
+        <v>11.0959100569033</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0420766611842518</v>
+        <v>0.04206209729435336</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6093084797202026</v>
+        <v>-0.6093406166411812</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02541539293940942</v>
+        <v>0.02540034576852568</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.04832603546338</v>
+        <v>12.83111414945146</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.11373755936092</v>
+        <v>12.86483031325012</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.18738811809945</v>
+        <v>12.99633139431796</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E17" t="n">
         <v>2368</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,13 +1934,13 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.514169484361792</v>
+        <v>6.512787283481201</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
@@ -1949,37 +1949,37 @@
         <v>1.397828275351592</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.884215441836128</v>
+        <v>6.882926515015086</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3700459574743356</v>
+        <v>0.3701392315338852</v>
       </c>
       <c r="T17" t="n">
-        <v>2.030358657046226</v>
+        <v>2.029754379563208</v>
       </c>
       <c r="U17" t="n">
-        <v>2.563167060092099</v>
+        <v>2.562680416195622</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5257542071878871</v>
+        <v>0.5260447680774073</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03210480538320581</v>
+        <v>0.03270779629649212</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5223634334889888</v>
+        <v>0.5226487401125328</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.597023484543472</v>
+        <v>1.323176307200624</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.114948264342488</v>
+        <v>2.098657013693816</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.648058107735491</v>
+        <v>4.574819839253124</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E18" t="n">
         <v>3227</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.486369457364341</v>
+        <v>6.485747520148791</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.682879172389714</v>
+        <v>6.682226385540707</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1965097150253723</v>
+        <v>0.1964788653919158</v>
       </c>
       <c r="T18" t="n">
-        <v>1.102213031019378</v>
+        <v>1.101894901304984</v>
       </c>
       <c r="U18" t="n">
-        <v>1.490082844441327</v>
+        <v>1.489868827317752</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6020713489038736</v>
+        <v>0.6022587093027405</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2199995356822289</v>
+        <v>0.2203235671553052</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5990314796927951</v>
+        <v>0.5992232457030866</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.601300529742196</v>
+        <v>2.28904133116156</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.480402340304797</v>
+        <v>3.509924092771352</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.360463351987012</v>
+        <v>6.196869140787154</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16678</v>
+        <v>16679</v>
       </c>
       <c r="E19" t="n">
         <v>7181</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7179</v>
+        <v>7180</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,52 +2112,52 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.35208406463296</v>
+        <v>10.3508254178273</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
       </c>
       <c r="P19" t="n">
-        <v>3.792826086956522</v>
+        <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1385144630683</v>
+        <v>11.13790698365469</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7864303984353401</v>
+        <v>0.7870815658273955</v>
       </c>
       <c r="T19" t="n">
-        <v>2.044428868705638</v>
+        <v>2.045032590804798</v>
       </c>
       <c r="U19" t="n">
-        <v>2.765075385918426</v>
+        <v>2.765904959039616</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7268626909168581</v>
+        <v>0.7268715413346257</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4703005431211329</v>
+        <v>0.4703262312123877</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6792915741614496</v>
+        <v>0.679179781275532</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.265520998023715</v>
+        <v>7.453208835732179</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.477466845616521</v>
+        <v>7.511053037503913</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.631835153651755</v>
+        <v>7.609357555145422</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.265520998023715</v>
+        <v>7.453208835732179</v>
       </c>
       <c r="G2" t="n">
-        <v>7.477466845616521</v>
+        <v>7.511053037503913</v>
       </c>
       <c r="H2" t="n">
-        <v>7.631835153651755</v>
+        <v>7.609357555145422</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.397098527349229</v>
+        <v>5.108303608695206</v>
       </c>
       <c r="G3" t="n">
-        <v>5.474961035545776</v>
+        <v>5.309195241233996</v>
       </c>
       <c r="H3" t="n">
-        <v>5.56</v>
+        <v>5.480871803221572</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>3.71983783309958</v>
+        <v>4.06412188502344</v>
       </c>
       <c r="G4" t="n">
-        <v>4.054971624631458</v>
+        <v>4.329292964809264</v>
       </c>
       <c r="H4" t="n">
-        <v>4.35998245012409</v>
+        <v>5.161031965227258</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.04832603546338</v>
+        <v>12.83111414945146</v>
       </c>
       <c r="G5" t="n">
-        <v>12.11373755936092</v>
+        <v>12.86483031325012</v>
       </c>
       <c r="H5" t="n">
-        <v>12.18738811809945</v>
+        <v>12.99633139431796</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>54.2122702924672</v>
+        <v>2.912843569578527</v>
       </c>
       <c r="G6" t="n">
-        <v>63.4043961066006</v>
+        <v>41.28640940351706</v>
       </c>
       <c r="H6" t="n">
-        <v>113.6672677238978</v>
+        <v>110.8510766285012</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>8.185204270936538</v>
+        <v>11.09294973219496</v>
       </c>
       <c r="G7" t="n">
-        <v>8.278402865034323</v>
+        <v>11.55848666803439</v>
       </c>
       <c r="H7" t="n">
-        <v>8.36834155191266</v>
+        <v>11.79955244946211</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.056242033203179</v>
+        <v>8.320828988284271</v>
       </c>
       <c r="G8" t="n">
-        <v>7.289546329880511</v>
+        <v>8.414392829066648</v>
       </c>
       <c r="H8" t="n">
-        <v>7.501802957145521</v>
+        <v>8.491946242742888</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.710449236591382</v>
+        <v>4.5952371684785</v>
       </c>
       <c r="G9" t="n">
-        <v>5.371077816683594</v>
+        <v>5.267672983692692</v>
       </c>
       <c r="H9" t="n">
-        <v>5.772463261796216</v>
+        <v>5.669282478707776</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.094949317271679</v>
+        <v>5.315295939018699</v>
       </c>
       <c r="G10" t="n">
-        <v>5.145003302011466</v>
+        <v>5.402180135270693</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1796597919792</v>
+        <v>5.435626785389175</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.597023484543472</v>
+        <v>1.323176307200624</v>
       </c>
       <c r="G11" t="n">
-        <v>3.114948264342488</v>
+        <v>2.098657013693816</v>
       </c>
       <c r="H11" t="n">
-        <v>4.648058107735491</v>
+        <v>4.574819839253124</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.701408138729529</v>
+        <v>5.515473195085712</v>
       </c>
       <c r="G12" t="n">
-        <v>5.766247428597519</v>
+        <v>5.800247899732043</v>
       </c>
       <c r="H12" t="n">
-        <v>5.834615881708721</v>
+        <v>6.21972569691054</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>8.829309634730393</v>
+        <v>9.550298577384853</v>
       </c>
       <c r="G13" t="n">
-        <v>9.467115154415222</v>
+        <v>9.708684097299713</v>
       </c>
       <c r="H13" t="n">
-        <v>9.697780688277769</v>
+        <v>9.88868319351849</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.357439265482557</v>
+        <v>5.473918578830497</v>
       </c>
       <c r="G14" t="n">
-        <v>5.454004456785436</v>
+        <v>5.612451432889739</v>
       </c>
       <c r="H14" t="n">
-        <v>5.518064921790469</v>
+        <v>5.669135115963484</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.357332530929214</v>
+        <v>6.685588129914337</v>
       </c>
       <c r="G15" t="n">
-        <v>6.490100414261017</v>
+        <v>6.911493649875285</v>
       </c>
       <c r="H15" t="n">
-        <v>6.587712205457368</v>
+        <v>7.251740517686113</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.601300529742196</v>
+        <v>2.28904133116156</v>
       </c>
       <c r="G16" t="n">
-        <v>4.480402340304797</v>
+        <v>3.509924092771352</v>
       </c>
       <c r="H16" t="n">
-        <v>6.360463351987012</v>
+        <v>6.196869140787154</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.118541374474054</v>
+        <v>3.166029607698001</v>
       </c>
       <c r="G17" t="n">
-        <v>3.346248615062225</v>
+        <v>3.272003314150408</v>
       </c>
       <c r="H17" t="n">
-        <v>3.782207573632538</v>
+        <v>3.43879348630644</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.369005142589995</v>
+        <v>2.347744263508512</v>
       </c>
       <c r="G18" t="n">
-        <v>2.392320820138494</v>
+        <v>2.373438806456725</v>
       </c>
       <c r="H18" t="n">
-        <v>2.453702664796634</v>
+        <v>2.416773131014064</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.492220254409895</v>
+        <v>5.219952690330059</v>
       </c>
       <c r="G19" t="n">
-        <v>5.520548619005934</v>
+        <v>5.388487454562474</v>
       </c>
       <c r="H19" t="n">
-        <v>5.616644852905435</v>
+        <v>5.941239710217962</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E2" t="n">
+        <v>10016</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10015</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10014</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6861792157646</v>
+        <v>102.6764671659178</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.689009739731</v>
+        <v>102.6774189772207</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002830523966421524</v>
+        <v>0.000951811302875612</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89545808065111</v>
+        <v>17.89510056671887</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07129767522719</v>
+        <v>36.07293505305891</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1333210387063704</v>
+        <v>0.1344149327570468</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7285260922411831</v>
+        <v>-0.726688745996938</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1333165408876003</v>
+        <v>0.1344110502479218</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.912843569578527</v>
+        <v>2.955066549745007</v>
       </c>
       <c r="Z2" t="n">
-        <v>41.28640940351707</v>
+        <v>40.9973511174681</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.8510766285012</v>
+        <v>109.1716324514088</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E3" t="n">
+        <v>14610</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14609</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14608</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910752430175247</v>
+        <v>4.910638236703401</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.970179215595354</v>
+        <v>4.970060715046746</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0594267854201071</v>
+        <v>0.05942247834334379</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346078553930526</v>
+        <v>1.346065823875161</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721298200603118</v>
+        <v>1.721271807772525</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809650820394611</v>
+        <v>0.7809617117565155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5686138504388025</v>
+        <v>0.5686095148078856</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799657123183301</v>
+        <v>0.7799619598074733</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.347744263508512</v>
+        <v>2.35200073964497</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.373438806456725</v>
+        <v>2.379917866080047</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.416773131014064</v>
+        <v>2.418139816735623</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E4" t="n">
+        <v>10244</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10243</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10242</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.913086555360283</v>
+        <v>6.912754564092551</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241735353995565</v>
+        <v>7.241535934634335</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.328648798635284</v>
+        <v>0.3287813705417831</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292757047722621</v>
+        <v>1.292698886507293</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682354161106473</v>
+        <v>1.682345429770503</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676680839744625</v>
+        <v>0.8676706030935449</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375080658394116</v>
+        <v>0.7375126451370809</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473657121876228</v>
+        <v>0.8473402596760227</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.166029607698001</v>
+        <v>3.176627623428254</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.272003314150408</v>
+        <v>3.257686488082342</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.43879348630644</v>
+        <v>3.388985933743991</v>
       </c>
     </row>
     <row r="5">
@@ -840,16 +840,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E5" t="n">
-        <v>2690</v>
+        <v>2710</v>
       </c>
       <c r="F5" t="n">
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>2690</v>
+        <v>2710</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -866,52 +866,52 @@
         <v>42370</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>46246</v>
+        <v>46266</v>
       </c>
       <c r="M5" t="n">
         <v>1.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.95478810408922</v>
+        <v>8.941302583025831</v>
       </c>
       <c r="O5" t="n">
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.758763878608438</v>
+        <v>2.761153846153846</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.313175399067909</v>
+        <v>9.303354230131582</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3583872949786904</v>
+        <v>0.3620516471057513</v>
       </c>
       <c r="T5" t="n">
-        <v>1.254686531588547</v>
+        <v>1.253819562291128</v>
       </c>
       <c r="U5" t="n">
-        <v>1.747826966371136</v>
+        <v>1.750193642874946</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8675140680676153</v>
+        <v>0.8661774835563326</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7234584984506744</v>
+        <v>0.7212962738651094</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8616008721326505</v>
+        <v>0.860147053751165</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.219952690330059</v>
+        <v>5.320686079906707</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.388487454562475</v>
+        <v>5.548691814307327</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.941239710217962</v>
+        <v>6.122414910788667</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E6" t="n">
+        <v>8857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8856</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8855</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732223771880294</v>
+        <v>6.732379911924119</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020228076727549</v>
+        <v>7.020458125261293</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880043048472559</v>
+        <v>0.2880782133371745</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480309133597139</v>
+        <v>1.480265931656288</v>
       </c>
       <c r="U6" t="n">
-        <v>1.909129978063244</v>
+        <v>1.909083045338225</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047778290225198</v>
+        <v>0.3047674236556175</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977133364709032</v>
+        <v>-0.1977047251550779</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2800651629809493</v>
+        <v>0.2800444754863231</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.685588129914337</v>
+        <v>6.694265358952044</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.911493649875285</v>
+        <v>6.863099408480466</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.251740517686113</v>
+        <v>7.153903878427974</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E7" t="n">
+        <v>14218</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14217</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14216</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581388470737198</v>
+        <v>5.581397165365408</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585148741193324</v>
+        <v>5.585167507591905</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003760270456127311</v>
+        <v>0.003770342226497716</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156256777005878</v>
+        <v>1.156206767777291</v>
       </c>
       <c r="U7" t="n">
-        <v>1.494012953552759</v>
+        <v>1.493974659652995</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5086243111430219</v>
+        <v>0.5086136452224364</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07400223898013114</v>
+        <v>0.07398498643623885</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047753488012495</v>
+        <v>0.5047643584599875</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.108303608695206</v>
+        <v>5.075766272189349</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.309195241233996</v>
+        <v>5.276047009670624</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.480871803221572</v>
+        <v>5.462444683127619</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E8" t="n">
+        <v>9016</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9015</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9014</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878764144663855</v>
+        <v>7.878678868552414</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116841819602385</v>
+        <v>8.116789872021329</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2380776749385301</v>
+        <v>0.2381110034689157</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446620655820945</v>
+        <v>1.446721474198235</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826252932599022</v>
+        <v>1.826326027852952</v>
       </c>
       <c r="V8" t="n">
-        <v>0.808048175760023</v>
+        <v>0.8080066516505505</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6277205614557897</v>
+        <v>0.6276521813450813</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7981875352456688</v>
+        <v>0.7981350104730931</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.315295939018699</v>
+        <v>5.233659137786206</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.402180135270693</v>
+        <v>5.385888045061009</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.435626785389175</v>
+        <v>5.441015132884007</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E9" t="n">
+        <v>13881</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13880</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13879</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613666510555515</v>
+        <v>7.613572766570605</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.511906096706377</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.67785423973371</v>
+        <v>7.677757301301495</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06418772917819393</v>
+        <v>0.06418453473088982</v>
       </c>
       <c r="T9" t="n">
-        <v>1.476165890152578</v>
+        <v>1.476116310779629</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91864458966539</v>
+        <v>1.918590660693813</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617796237350358</v>
+        <v>0.761778604358042</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363285524892349</v>
+        <v>0.5363283352249553</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597814086819279</v>
+        <v>0.7597798924438595</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.473918578830497</v>
+        <v>5.427034325305103</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.612451432889739</v>
+        <v>5.598846047629269</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.669135115963484</v>
+        <v>5.687886143936066</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61830360848261</v>
+        <v>10.61817804610986</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3132419279902305</v>
+        <v>0.3131163656174871</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052127457844854</v>
+        <v>2.052152499647309</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697717988689959</v>
+        <v>2.697751956273629</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567090026347503</v>
+        <v>0.3567255144401292</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1201227765500246</v>
+        <v>-0.1201509841713004</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3360852749066027</v>
+        <v>0.336118975544026</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.550298577384853</v>
+        <v>9.549667316762898</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.708684097299713</v>
+        <v>9.710916499885469</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.88868319351849</v>
+        <v>9.83824174512476</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E11" t="n">
+        <v>13822</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13821</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13820</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244614833574529</v>
+        <v>5.244532378264959</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8407564766839378</v>
+        <v>0.8407825443786981</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217146335888257</v>
+        <v>5.217048074473244</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0274684976862732</v>
+        <v>-0.02748430379171498</v>
       </c>
       <c r="T11" t="n">
-        <v>1.157019496623679</v>
+        <v>1.156954614066764</v>
       </c>
       <c r="U11" t="n">
-        <v>1.475995519512648</v>
+        <v>1.475942238524999</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4298000096164736</v>
+        <v>0.4298326072188683</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08164362437919426</v>
+        <v>-0.08159333472106334</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4271820817016625</v>
+        <v>0.4272155078594754</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.06412188502344</v>
+        <v>4.075337771203156</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.329292964809264</v>
+        <v>4.365085962205673</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.161031965227258</v>
+        <v>5.232426035502959</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E12" t="n">
+        <v>4140</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4139</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4138</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.481523924601255</v>
+        <v>7.480885117178062</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204846780162842</v>
+        <v>2.204866863905325</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.65476037729406</v>
+        <v>7.654181070687196</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.173236452692802</v>
+        <v>0.1732959535091332</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9134554389495751</v>
+        <v>0.9133695320875145</v>
       </c>
       <c r="U12" t="n">
-        <v>1.196039966154902</v>
+        <v>1.195894092637583</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8304713705209866</v>
+        <v>0.8305359725361786</v>
       </c>
       <c r="W12" t="n">
-        <v>0.656235706463669</v>
+        <v>0.6563759725791032</v>
       </c>
       <c r="X12" t="n">
-        <v>0.82873057801929</v>
+        <v>0.8287910178598961</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.5952371684785</v>
+        <v>4.491852120518724</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.267672983692693</v>
+        <v>5.165785832583198</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.669282478707776</v>
+        <v>5.667059204930549</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E13" t="n">
+        <v>6475</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6474</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6473</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.610049436119265</v>
+        <v>9.60975749150448</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02793187941023</v>
+        <v>10.02795597924861</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4178824432909616</v>
+        <v>0.4181984877441328</v>
       </c>
       <c r="T13" t="n">
-        <v>1.692048846736125</v>
+        <v>1.692056108004618</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152547161816404</v>
+        <v>2.152474535073456</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230770572156101</v>
+        <v>0.8230664635889743</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484235316213709</v>
+        <v>0.6484076655674791</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8107280587331728</v>
+        <v>0.8106824558262981</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.320828988284271</v>
+        <v>8.327828547223149</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.414392829066648</v>
+        <v>8.429390786818034</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.491946242742888</v>
+        <v>8.490963262018017</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E14" t="n">
+        <v>14062</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14061</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14060</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.131050675675676</v>
+        <v>8.130921876111231</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9072958302491981</v>
+        <v>0.9073200197238659</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201388995370802</v>
+        <v>8.201293747513965</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07033831969512572</v>
+        <v>0.07037187140273683</v>
       </c>
       <c r="T14" t="n">
-        <v>1.758012138682411</v>
+        <v>1.757925731537852</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28371717660352</v>
+        <v>2.283664145078505</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807551858481971</v>
+        <v>0.7807516487235271</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651436621401921</v>
+        <v>0.5651413885685119</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803820680486027</v>
+        <v>0.7803778417895992</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.515473195085712</v>
+        <v>5.44466722618164</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.800247899732044</v>
+        <v>5.72492662383496</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.21972569691054</v>
+        <v>6.099323805848555</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.682413027387121</v>
+        <v>4.681582840236686</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82354900480542</v>
+        <v>11.8234370969358</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1403383782213606</v>
+        <v>-0.1404502860909851</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052113450111469</v>
+        <v>2.052114723720082</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697360330414803</v>
+        <v>2.697382024225949</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949554435801198</v>
+        <v>0.7949582614355937</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096771036818271</v>
+        <v>0.6096708252286638</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862106033520293</v>
+        <v>0.7862222200979516</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.09294973219496</v>
+        <v>11.12173676671869</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.55848666803439</v>
+        <v>11.6265072490042</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.79955244946211</v>
+        <v>11.79907218290898</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E16" t="n">
+        <v>9825</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9824</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9823</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.366753435813907</v>
+        <v>8.366526771172637</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625278087253589</v>
+        <v>8.625198081785001</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2585246514396822</v>
+        <v>0.2586713106123624</v>
       </c>
       <c r="T16" t="n">
-        <v>3.587500062973692</v>
+        <v>3.587890735229663</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0959100569033</v>
+        <v>11.09555668660874</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04206209729435336</v>
+        <v>0.04203263691478584</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6093406166411812</v>
+        <v>-0.6093913188280511</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02540034576852568</v>
+        <v>0.02537093677355884</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.83111414945146</v>
+        <v>12.57933763888335</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.86483031325012</v>
+        <v>12.82946657792365</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.99633139431796</v>
+        <v>12.86980764160884</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E17" t="n">
+        <v>2369</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2368</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2367</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.512787283481201</v>
+        <v>6.511333403716216</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.397828275351592</v>
+        <v>1.399653846153846</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.882926515015086</v>
+        <v>6.880606301749925</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3701392315338852</v>
+        <v>0.3692728980337073</v>
       </c>
       <c r="T17" t="n">
-        <v>2.029754379563208</v>
+        <v>2.029033633950661</v>
       </c>
       <c r="U17" t="n">
-        <v>2.562680416195622</v>
+        <v>2.562026508708781</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5260447680774073</v>
+        <v>0.5266130027136088</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03270779629649212</v>
+        <v>0.03350545957579798</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5226487401125328</v>
+        <v>0.5232278524948644</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.323176307200624</v>
+        <v>1.492560745177853</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.098657013693816</v>
+        <v>2.472152017109406</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.574819839253124</v>
+        <v>5.712388201430596</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E18" t="n">
+        <v>3228</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3227</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3226</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.485747520148791</v>
+        <v>6.485073287883483</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.682226385540707</v>
+        <v>6.681175862866853</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1964788653919158</v>
+        <v>0.1961025749833714</v>
       </c>
       <c r="T18" t="n">
-        <v>1.101894901304984</v>
+        <v>1.101859671791393</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489868827317752</v>
+        <v>1.489701478181641</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6022587093027405</v>
+        <v>0.6025357791349135</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2203235671553052</v>
+        <v>0.2206586529430019</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5992232457030866</v>
+        <v>0.5995362642329428</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.28904133116156</v>
+        <v>2.332418731332321</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.509924092771352</v>
+        <v>3.89613316632608</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.196869140787154</v>
+        <v>6.168510277487306</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16679</v>
+        <v>16680</v>
       </c>
       <c r="E19" t="n">
+        <v>7182</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7181</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7180</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.3508254178273</v>
+        <v>10.34953439632363</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13790698365469</v>
+        <v>11.13703519006323</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7870815658273955</v>
+        <v>0.7875007937395994</v>
       </c>
       <c r="T19" t="n">
-        <v>2.045032590804798</v>
+        <v>2.045653495403108</v>
       </c>
       <c r="U19" t="n">
-        <v>2.765904959039616</v>
+        <v>2.766731932260018</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7268715413346257</v>
+        <v>0.7268906529323574</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4703262312123877</v>
+        <v>0.4703745255129362</v>
       </c>
       <c r="X19" t="n">
-        <v>0.679179781275532</v>
+        <v>0.6791233659533635</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.453208835732179</v>
+        <v>7.443750388286007</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.511053037503913</v>
+        <v>7.486708724041523</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.609357555145422</v>
+        <v>7.559836986721103</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.453208835732179</v>
+        <v>7.443750388286007</v>
       </c>
       <c r="G2" t="n">
-        <v>7.511053037503913</v>
+        <v>7.486708724041525</v>
       </c>
       <c r="H2" t="n">
-        <v>7.609357555145422</v>
+        <v>7.559836986721103</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.108303608695206</v>
+        <v>5.075766272189349</v>
       </c>
       <c r="G3" t="n">
-        <v>5.309195241233996</v>
+        <v>5.276047009670624</v>
       </c>
       <c r="H3" t="n">
-        <v>5.480871803221572</v>
+        <v>5.462444683127619</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.06412188502344</v>
+        <v>4.075337771203156</v>
       </c>
       <c r="G4" t="n">
-        <v>4.329292964809264</v>
+        <v>4.365085962205672</v>
       </c>
       <c r="H4" t="n">
-        <v>5.161031965227258</v>
+        <v>5.232426035502959</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.83111414945146</v>
+        <v>12.57933763888335</v>
       </c>
       <c r="G5" t="n">
-        <v>12.86483031325012</v>
+        <v>12.82946657792365</v>
       </c>
       <c r="H5" t="n">
-        <v>12.99633139431796</v>
+        <v>12.86980764160884</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.912843569578527</v>
+        <v>2.955066549745007</v>
       </c>
       <c r="G6" t="n">
-        <v>41.28640940351706</v>
+        <v>40.9973511174681</v>
       </c>
       <c r="H6" t="n">
-        <v>110.8510766285012</v>
+        <v>109.1716324514088</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.09294973219496</v>
+        <v>11.12173676671869</v>
       </c>
       <c r="G7" t="n">
-        <v>11.55848666803439</v>
+        <v>11.6265072490042</v>
       </c>
       <c r="H7" t="n">
-        <v>11.79955244946211</v>
+        <v>11.79907218290898</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.320828988284271</v>
+        <v>8.327828547223149</v>
       </c>
       <c r="G8" t="n">
-        <v>8.414392829066648</v>
+        <v>8.429390786818033</v>
       </c>
       <c r="H8" t="n">
-        <v>8.491946242742888</v>
+        <v>8.490963262018017</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5952371684785</v>
+        <v>4.491852120518724</v>
       </c>
       <c r="G9" t="n">
-        <v>5.267672983692692</v>
+        <v>5.165785832583198</v>
       </c>
       <c r="H9" t="n">
-        <v>5.669282478707776</v>
+        <v>5.667059204930549</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.315295939018699</v>
+        <v>5.233659137786206</v>
       </c>
       <c r="G10" t="n">
-        <v>5.402180135270693</v>
+        <v>5.385888045061009</v>
       </c>
       <c r="H10" t="n">
-        <v>5.435626785389175</v>
+        <v>5.441015132884007</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.323176307200624</v>
+        <v>1.492560745177853</v>
       </c>
       <c r="G11" t="n">
-        <v>2.098657013693816</v>
+        <v>2.472152017109406</v>
       </c>
       <c r="H11" t="n">
-        <v>4.574819839253124</v>
+        <v>5.712388201430596</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.515473195085712</v>
+        <v>5.44466722618164</v>
       </c>
       <c r="G12" t="n">
-        <v>5.800247899732043</v>
+        <v>5.724926623834961</v>
       </c>
       <c r="H12" t="n">
-        <v>6.21972569691054</v>
+        <v>6.099323805848555</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.550298577384853</v>
+        <v>9.549667316762898</v>
       </c>
       <c r="G13" t="n">
-        <v>9.708684097299713</v>
+        <v>9.710916499885467</v>
       </c>
       <c r="H13" t="n">
-        <v>9.88868319351849</v>
+        <v>9.83824174512476</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.473918578830497</v>
+        <v>5.427034325305103</v>
       </c>
       <c r="G14" t="n">
-        <v>5.612451432889739</v>
+        <v>5.598846047629269</v>
       </c>
       <c r="H14" t="n">
-        <v>5.669135115963484</v>
+        <v>5.687886143936066</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.685588129914337</v>
+        <v>6.694265358952044</v>
       </c>
       <c r="G15" t="n">
-        <v>6.911493649875285</v>
+        <v>6.863099408480466</v>
       </c>
       <c r="H15" t="n">
-        <v>7.251740517686113</v>
+        <v>7.153903878427974</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.28904133116156</v>
+        <v>2.332418731332321</v>
       </c>
       <c r="G16" t="n">
-        <v>3.509924092771352</v>
+        <v>3.89613316632608</v>
       </c>
       <c r="H16" t="n">
-        <v>6.196869140787154</v>
+        <v>6.168510277487306</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.166029607698001</v>
+        <v>3.176627623428254</v>
       </c>
       <c r="G17" t="n">
-        <v>3.272003314150408</v>
+        <v>3.257686488082342</v>
       </c>
       <c r="H17" t="n">
-        <v>3.43879348630644</v>
+        <v>3.388985933743991</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.347744263508512</v>
+        <v>2.35200073964497</v>
       </c>
       <c r="G18" t="n">
-        <v>2.373438806456725</v>
+        <v>2.379917866080047</v>
       </c>
       <c r="H18" t="n">
-        <v>2.416773131014064</v>
+        <v>2.418139816735623</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.219952690330059</v>
+        <v>5.320686079906707</v>
       </c>
       <c r="G19" t="n">
-        <v>5.388487454562474</v>
+        <v>5.548691814307327</v>
       </c>
       <c r="H19" t="n">
-        <v>5.941239710217962</v>
+        <v>6.122414910788667</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E2" t="n">
+        <v>10017</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10016</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10015</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6764671659178</v>
+        <v>102.6667620473908</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6774189772207</v>
+        <v>102.6673186213425</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.000951811302875612</v>
+        <v>0.0005565739517091112</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89510056671887</v>
+        <v>17.89342401400162</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07293505305891</v>
+        <v>36.07070998033659</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1344149327570468</v>
+        <v>0.1355389928243041</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.726688745996938</v>
+        <v>-0.7244893520373306</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1344110502479218</v>
+        <v>0.1355351795762973</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.955066549745007</v>
+        <v>2.963233803362154</v>
       </c>
       <c r="Z2" t="n">
-        <v>40.9973511174681</v>
+        <v>78.99744556278208</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.1716324514088</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E3" t="n">
+        <v>14611</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14610</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14609</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910638236703401</v>
+        <v>4.910516358658453</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.970060715046746</v>
+        <v>4.969948679975816</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05942247834334379</v>
+        <v>0.05943232131736263</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346065823875161</v>
+        <v>1.346045908135891</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721271807772525</v>
+        <v>1.721245815305955</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809617117565155</v>
+        <v>0.7809583429784459</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5686095148078856</v>
+        <v>0.5686066467184845</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799619598074733</v>
+        <v>0.7799577203730155</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.35200073964497</v>
+        <v>2.345357538802661</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.379917866080047</v>
+        <v>2.385825826021182</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.418139816735623</v>
+        <v>2.444828301113267</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E4" t="n">
+        <v>10245</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10244</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10243</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.912754564092551</v>
+        <v>6.912450946895745</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241535934634335</v>
+        <v>7.241375119875122</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3287813705417831</v>
+        <v>0.3289241729793778</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292698886507293</v>
+        <v>1.292707280377983</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682345429770503</v>
+        <v>1.682374526175786</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676706030935449</v>
+        <v>0.8676645222499522</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375126451370809</v>
+        <v>0.7375009280615386</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473402596760227</v>
+        <v>0.8473051013326205</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.176627623428254</v>
+        <v>3.188436807095343</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.257686488082342</v>
+        <v>3.248835375647353</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.388985933743991</v>
+        <v>3.348651951681449</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.761153846153846</v>
+        <v>2.759970436067997</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.303354230131582</v>
+        <v>9.303260265651728</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3620516471057513</v>
+        <v>0.3619576826258967</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253819562291128</v>
+        <v>1.253822704062056</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750193642874946</v>
+        <v>1.750185821092359</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661774835563326</v>
+        <v>0.8661813592713015</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212962738651094</v>
+        <v>0.7212987649666966</v>
       </c>
       <c r="X5" t="n">
-        <v>0.860147053751165</v>
+        <v>0.8601548249202852</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.320686079906707</v>
+        <v>5.32151506378835</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.548691814307327</v>
+        <v>5.790962836621371</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.122414910788667</v>
+        <v>6.949423734651264</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E6" t="n">
         <v>8857</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8856</v>
+        <v>8857</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732379911924119</v>
+        <v>6.732530935982838</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020458125261293</v>
+        <v>7.020405817138722</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880782133371745</v>
+        <v>0.2878748811558839</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480265931656288</v>
+        <v>1.480212437774721</v>
       </c>
       <c r="U6" t="n">
-        <v>1.909083045338225</v>
+        <v>1.909012386026772</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047674236556175</v>
+        <v>0.3047744561638638</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977047251550779</v>
+        <v>-0.1976717905495831</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2800444754863231</v>
+        <v>0.2800570084117425</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.694265358952044</v>
+        <v>6.689686784313448</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.863099408480466</v>
+        <v>6.816900004685128</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.153903878427974</v>
+        <v>7.014127219047727</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E7" t="n">
+        <v>14219</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14218</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14217</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581397165365408</v>
+        <v>5.581407265438177</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585167507591905</v>
+        <v>5.58518090053873</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003770342226497716</v>
+        <v>0.003773635100553186</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156206767777291</v>
+        <v>1.156154554457888</v>
       </c>
       <c r="U7" t="n">
-        <v>1.493974659652995</v>
+        <v>1.493933950729251</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5086136452224364</v>
+        <v>0.5086044985818953</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07398498643623885</v>
+        <v>0.07397087767353983</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047643584599875</v>
+        <v>0.5047548379740783</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.075766272189349</v>
+        <v>5.049520448482765</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.276047009670624</v>
+        <v>5.235574122115706</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.462444683127619</v>
+        <v>5.422125078432958</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E8" t="n">
+        <v>9017</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9016</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9015</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878678868552414</v>
+        <v>7.878576419698313</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116789872021329</v>
+        <v>8.116737541269506</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2381110034689157</v>
+        <v>0.238161121571193</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446721474198235</v>
+        <v>1.44680742203595</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826326027852952</v>
+        <v>1.826389549682334</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8080066516505505</v>
+        <v>0.8079681429053261</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6276521813450813</v>
+        <v>0.627588907542267</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7981350104730931</v>
+        <v>0.79808474955208</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.233659137786206</v>
+        <v>5.16787055038666</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.385888045061009</v>
+        <v>5.367333532520262</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.441015132884007</v>
+        <v>5.453551490471698</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E9" t="n">
+        <v>13882</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13881</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13880</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613572766570605</v>
+        <v>7.613455262589151</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.511906096706377</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.677757301301495</v>
+        <v>7.677635419377268</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06418453473088982</v>
+        <v>0.0641801567881182</v>
       </c>
       <c r="T9" t="n">
-        <v>1.476116310779629</v>
+        <v>1.476034796521947</v>
       </c>
       <c r="U9" t="n">
-        <v>1.918590660693813</v>
+        <v>1.918523451999134</v>
       </c>
       <c r="V9" t="n">
-        <v>0.761778604358042</v>
+        <v>0.7617833112248342</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363283352249553</v>
+        <v>0.5363386099944678</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597798924438595</v>
+        <v>0.7597842504001798</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.427034325305103</v>
+        <v>5.366076619857107</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.598846047629269</v>
+        <v>5.577736257156308</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.687886143936066</v>
+        <v>5.689890854813378</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61817804610986</v>
+        <v>10.6180641460345</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3131163656174871</v>
+        <v>0.3130024655421217</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052152499647309</v>
+        <v>2.052182136208033</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697751956273629</v>
+        <v>2.697790499493602</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567255144401292</v>
+        <v>0.356739521808561</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1201509841713004</v>
+        <v>-0.1201829919577126</v>
       </c>
       <c r="X10" t="n">
-        <v>0.336118975544026</v>
+        <v>0.336149804563871</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.549667316762898</v>
+        <v>9.603363117970124</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.710916499885469</v>
+        <v>9.747830679691329</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.83824174512476</v>
+        <v>9.885578782902519</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E11" t="n">
+        <v>13823</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13822</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13821</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244532378264959</v>
+        <v>5.244425155549125</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8407825443786981</v>
+        <v>0.8408085735402808</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217048074473244</v>
+        <v>5.216919651755506</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02748430379171498</v>
+        <v>-0.027505503793619</v>
       </c>
       <c r="T11" t="n">
-        <v>1.156954614066764</v>
+        <v>1.156918604025081</v>
       </c>
       <c r="U11" t="n">
-        <v>1.475942238524999</v>
+        <v>1.475901277617386</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4298326072188683</v>
+        <v>0.4298784338146974</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08159333472106334</v>
+        <v>-0.08152622387815023</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4272155078594754</v>
+        <v>0.4272628356496141</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.075337771203156</v>
+        <v>4.092965426623963</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.365085962205673</v>
+        <v>4.465434278904044</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.232426035502959</v>
+        <v>4.727553903680152</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E12" t="n">
+        <v>4141</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4140</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4139</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.480885117178062</v>
+        <v>7.480157850241545</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204866863905325</v>
+        <v>2.204886917960089</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.654181070687196</v>
+        <v>7.653507099736235</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1732959535091332</v>
+        <v>0.1733492494946885</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9133695320875145</v>
+        <v>0.9133155870357498</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195894092637583</v>
+        <v>1.195776415245998</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8305359725361786</v>
+        <v>0.8306164984572412</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6563759725791032</v>
+        <v>0.656541291620602</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8287910178598961</v>
+        <v>0.8288683692845127</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.491852120518724</v>
+        <v>4.487544769467629</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.165785832583198</v>
+        <v>5.055102617799302</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.667059204930549</v>
+        <v>5.664934856077734</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E13" t="n">
+        <v>6476</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6475</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6474</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.60975749150448</v>
+        <v>9.609457142857144</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02795597924861</v>
+        <v>10.02791112303746</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4181984877441328</v>
+        <v>0.4184539801803164</v>
       </c>
       <c r="T13" t="n">
-        <v>1.692056108004618</v>
+        <v>1.691998684510549</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152474535073456</v>
+        <v>2.152345478903543</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230664635889743</v>
+        <v>0.8230659736339423</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484076655674791</v>
+        <v>0.648411107763841</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106824558262981</v>
+        <v>0.8106516945039377</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.327828547223149</v>
+        <v>8.335643638096165</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.429390786818034</v>
+        <v>8.443814483033172</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.490963262018017</v>
+        <v>8.491067612948004</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E14" t="n">
+        <v>14063</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14062</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14061</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130921876111231</v>
+        <v>8.130787583558527</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073200197238659</v>
+        <v>0.9073441734417345</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201293747513965</v>
+        <v>8.201184555491377</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07037187140273683</v>
+        <v>0.07039697193285031</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757925731537852</v>
+        <v>1.757834130294043</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283664145078505</v>
+        <v>2.283604043439134</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807516487235271</v>
+        <v>0.7807501110983188</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651413885685119</v>
+        <v>0.5651425482282733</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803778417895992</v>
+        <v>0.7803757159927844</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.44466722618164</v>
+        <v>5.404900881436571</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.72492662383496</v>
+        <v>5.660276038742301</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.099323805848555</v>
+        <v>5.995435657386878</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.681582840236686</v>
+        <v>4.680753880266075</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.8234370969358</v>
+        <v>11.82332477542035</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1404502860909851</v>
+        <v>-0.1405626076064354</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052114723720082</v>
+        <v>2.052115733816223</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697382024225949</v>
+        <v>2.697403743939393</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949582614355937</v>
+        <v>0.7949611124012568</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096708252286638</v>
+        <v>0.6096645392284745</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862222200979516</v>
+        <v>0.7862339189207049</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.12173676671869</v>
+        <v>11.37226475346843</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.6265072490042</v>
+        <v>11.69878976455099</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.79907218290898</v>
+        <v>11.8339531765274</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E16" t="n">
+        <v>9826</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9825</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9824</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.366526771172637</v>
+        <v>8.36627368956743</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625198081785001</v>
+        <v>8.625117914995093</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2586713106123624</v>
+        <v>0.2588442254276639</v>
       </c>
       <c r="T16" t="n">
-        <v>3.587890735229663</v>
+        <v>3.588312002846224</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09555668660874</v>
+        <v>11.09522205082779</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04203263691478584</v>
+        <v>0.04200110574090984</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6093913188280511</v>
+        <v>-0.6094448159723527</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02537093677355884</v>
+        <v>0.02533929739981766</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.57933763888335</v>
+        <v>12.37603394964643</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.82946657792365</v>
+        <v>12.80138102302272</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.86980764160884</v>
+        <v>12.87091515774632</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E17" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2369</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2368</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.511333403716216</v>
+        <v>6.509824820599409</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.399653846153846</v>
+        <v>1.401476718403548</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.880606301749925</v>
+        <v>6.878232865219802</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3692728980337073</v>
+        <v>0.3684080446203926</v>
       </c>
       <c r="T17" t="n">
-        <v>2.029033633950661</v>
+        <v>2.028294022049624</v>
       </c>
       <c r="U17" t="n">
-        <v>2.562026508708781</v>
+        <v>2.561360111897746</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5266130027136088</v>
+        <v>0.527217217513327</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03350545957579798</v>
+        <v>0.03436680234546408</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5232278524948644</v>
+        <v>0.5238421550681354</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.492560745177853</v>
+        <v>2.296196085017402</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.472152017109406</v>
+        <v>3.334848554552343</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.712388201430596</v>
+        <v>6.989208552039508</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E18" t="n">
+        <v>3229</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3228</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3227</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.485073287883483</v>
+        <v>6.484368494423792</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.681175862866853</v>
+        <v>6.680162920144049</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1961025749833714</v>
+        <v>0.1957944257202579</v>
       </c>
       <c r="T18" t="n">
-        <v>1.101859671791393</v>
+        <v>1.10172059242112</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489701478181641</v>
+        <v>1.489464423186992</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6025357791349135</v>
+        <v>0.6028462923844961</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2206586529430019</v>
+        <v>0.2211038329142834</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5995362642329428</v>
+        <v>0.5998741822384539</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.332418731332321</v>
+        <v>2.322282161200548</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.89613316632608</v>
+        <v>4.537064920149219</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.168510277487306</v>
+        <v>7.096370951219138</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16680</v>
+        <v>16681</v>
       </c>
       <c r="E19" t="n">
+        <v>7183</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7182</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7181</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34953439632363</v>
+        <v>10.34822667780563</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13703519006323</v>
+        <v>11.13615645602373</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7875007937395994</v>
+        <v>0.7879297782181042</v>
       </c>
       <c r="T19" t="n">
-        <v>2.045653495403108</v>
+        <v>2.046260155413509</v>
       </c>
       <c r="U19" t="n">
-        <v>2.766731932260018</v>
+        <v>2.767562734943652</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7268906529323574</v>
+        <v>0.7269148580693253</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4703745255129362</v>
+        <v>0.4704326226233532</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6791233659533635</v>
+        <v>0.6790684361569692</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.443750388286007</v>
+        <v>7.445853819640406</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.486708724041523</v>
+        <v>7.479106478742875</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.559836986721103</v>
+        <v>7.509520977545092</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.443750388286007</v>
+        <v>7.445853819640406</v>
       </c>
       <c r="G2" t="n">
-        <v>7.486708724041525</v>
+        <v>7.479106478742875</v>
       </c>
       <c r="H2" t="n">
-        <v>7.559836986721103</v>
+        <v>7.509520977545092</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.075766272189349</v>
+        <v>5.049520448482765</v>
       </c>
       <c r="G3" t="n">
-        <v>5.276047009670624</v>
+        <v>5.235574122115707</v>
       </c>
       <c r="H3" t="n">
-        <v>5.462444683127619</v>
+        <v>5.422125078432958</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.075337771203156</v>
+        <v>4.092965426623963</v>
       </c>
       <c r="G4" t="n">
-        <v>4.365085962205672</v>
+        <v>4.465434278904044</v>
       </c>
       <c r="H4" t="n">
-        <v>5.232426035502959</v>
+        <v>4.727553903680152</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.57933763888335</v>
+        <v>12.37603394964643</v>
       </c>
       <c r="G5" t="n">
-        <v>12.82946657792365</v>
+        <v>12.80138102302272</v>
       </c>
       <c r="H5" t="n">
-        <v>12.86980764160884</v>
+        <v>12.87091515774632</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.955066549745007</v>
+        <v>2.963233803362154</v>
       </c>
       <c r="G6" t="n">
-        <v>40.9973511174681</v>
+        <v>78.99744556278208</v>
       </c>
       <c r="H6" t="n">
-        <v>109.1716324514088</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.12173676671869</v>
+        <v>11.37226475346843</v>
       </c>
       <c r="G7" t="n">
-        <v>11.6265072490042</v>
+        <v>11.69878976455099</v>
       </c>
       <c r="H7" t="n">
-        <v>11.79907218290898</v>
+        <v>11.8339531765274</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.327828547223149</v>
+        <v>8.335643638096165</v>
       </c>
       <c r="G8" t="n">
-        <v>8.429390786818033</v>
+        <v>8.443814483033174</v>
       </c>
       <c r="H8" t="n">
-        <v>8.490963262018017</v>
+        <v>8.491067612948004</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.491852120518724</v>
+        <v>4.487544769467629</v>
       </c>
       <c r="G9" t="n">
-        <v>5.165785832583198</v>
+        <v>5.055102617799301</v>
       </c>
       <c r="H9" t="n">
-        <v>5.667059204930549</v>
+        <v>5.664934856077734</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.233659137786206</v>
+        <v>5.16787055038666</v>
       </c>
       <c r="G10" t="n">
-        <v>5.385888045061009</v>
+        <v>5.367333532520262</v>
       </c>
       <c r="H10" t="n">
-        <v>5.441015132884007</v>
+        <v>5.453551490471698</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.492560745177853</v>
+        <v>2.296196085017402</v>
       </c>
       <c r="G11" t="n">
-        <v>2.472152017109406</v>
+        <v>3.334848554552343</v>
       </c>
       <c r="H11" t="n">
-        <v>5.712388201430596</v>
+        <v>6.989208552039508</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.44466722618164</v>
+        <v>5.404900881436571</v>
       </c>
       <c r="G12" t="n">
-        <v>5.724926623834961</v>
+        <v>5.660276038742301</v>
       </c>
       <c r="H12" t="n">
-        <v>6.099323805848555</v>
+        <v>5.995435657386878</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.549667316762898</v>
+        <v>9.603363117970124</v>
       </c>
       <c r="G13" t="n">
-        <v>9.710916499885467</v>
+        <v>9.747830679691329</v>
       </c>
       <c r="H13" t="n">
-        <v>9.83824174512476</v>
+        <v>9.885578782902519</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.427034325305103</v>
+        <v>5.366076619857107</v>
       </c>
       <c r="G14" t="n">
-        <v>5.598846047629269</v>
+        <v>5.577736257156308</v>
       </c>
       <c r="H14" t="n">
-        <v>5.687886143936066</v>
+        <v>5.689890854813378</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.694265358952044</v>
+        <v>6.689686784313448</v>
       </c>
       <c r="G15" t="n">
-        <v>6.863099408480466</v>
+        <v>6.816900004685128</v>
       </c>
       <c r="H15" t="n">
-        <v>7.153903878427974</v>
+        <v>7.014127219047727</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.332418731332321</v>
+        <v>2.322282161200548</v>
       </c>
       <c r="G16" t="n">
-        <v>3.89613316632608</v>
+        <v>4.537064920149219</v>
       </c>
       <c r="H16" t="n">
-        <v>6.168510277487306</v>
+        <v>7.096370951219138</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.176627623428254</v>
+        <v>3.188436807095343</v>
       </c>
       <c r="G17" t="n">
-        <v>3.257686488082342</v>
+        <v>3.248835375647353</v>
       </c>
       <c r="H17" t="n">
-        <v>3.388985933743991</v>
+        <v>3.348651951681449</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.35200073964497</v>
+        <v>2.345357538802661</v>
       </c>
       <c r="G18" t="n">
-        <v>2.379917866080047</v>
+        <v>2.385825826021182</v>
       </c>
       <c r="H18" t="n">
-        <v>2.418139816735623</v>
+        <v>2.444828301113267</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.320686079906707</v>
+        <v>5.32151506378835</v>
       </c>
       <c r="G19" t="n">
-        <v>5.548691814307327</v>
+        <v>5.790962836621371</v>
       </c>
       <c r="H19" t="n">
-        <v>6.122414910788667</v>
+        <v>6.949423734651264</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E2" t="n">
+        <v>10018</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10017</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10016</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6667620473908</v>
+        <v>102.6570339090213</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6673186213425</v>
+        <v>102.6571462411601</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0005565739517091112</v>
+        <v>0.0001123321387959327</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89342401400162</v>
+        <v>17.89186478611563</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07070998033659</v>
+        <v>36.06873747245711</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1355389928243041</v>
+        <v>0.1366569056593932</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7244893520373306</v>
+        <v>-0.7223088958819064</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1355351795762973</v>
+        <v>0.1366531727439204</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.963233803362154</v>
+        <v>2.915278305254414</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.99744556278208</v>
+        <v>51.4339092119144</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.56</v>
+        <v>109.2722404337466</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E3" t="n">
+        <v>14612</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14611</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14610</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910516358658453</v>
+        <v>4.910382520019163</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01756303724928367</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.969948679975816</v>
+        <v>4.969832614138848</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05943232131736263</v>
+        <v>0.05945009411968397</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346045908135891</v>
+        <v>1.346011446212224</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721245815305955</v>
+        <v>1.721211468650319</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809583429784459</v>
+        <v>0.7809582309084562</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5686066467184845</v>
+        <v>0.5686107768927517</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799577203730155</v>
+        <v>0.7799564911649091</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.345357538802661</v>
+        <v>2.288553545051698</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.385825826021182</v>
+        <v>2.379444123629738</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.444828301113267</v>
+        <v>2.436395864106351</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E4" t="n">
+        <v>10246</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10245</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10244</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.912450946895745</v>
+        <v>6.912168862859933</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241375119875122</v>
+        <v>7.241218352707952</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289241729793778</v>
+        <v>0.3290494898480191</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292707280377983</v>
+        <v>1.29274139838796</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682374526175786</v>
+        <v>1.682410088094794</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676645222499522</v>
+        <v>0.8676555665749075</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375009280615386</v>
+        <v>0.7374840523781273</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8473051013326205</v>
+        <v>0.8472701130343343</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.188436807095343</v>
+        <v>3.153905465288036</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.248835375647353</v>
+        <v>3.219635136387393</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.348651951681449</v>
+        <v>3.298953325505447</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.759970436067997</v>
+        <v>2.759748892171344</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.303260265651728</v>
+        <v>9.3031671975967</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3619576826258967</v>
+        <v>0.3618646145708707</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253822704062056</v>
+        <v>1.253826626074554</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750185821092359</v>
+        <v>1.750178956052324</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661813592713015</v>
+        <v>0.8661850661261836</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212987649666966</v>
+        <v>0.721300951353263</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8601548249202852</v>
+        <v>0.8601623829596194</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.32151506378835</v>
+        <v>5.182639961611631</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.790962836621371</v>
+        <v>5.592375924631712</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.949423734651264</v>
+        <v>5.899094287894956</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E6" t="n">
-        <v>8857</v>
+        <v>8859</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8857</v>
+        <v>8858</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732530935982838</v>
+        <v>6.732699424249266</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020405817138722</v>
+        <v>7.020971068614799</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2878748811558839</v>
+        <v>0.2882716443655341</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480212437774721</v>
+        <v>1.480196326245886</v>
       </c>
       <c r="U6" t="n">
-        <v>1.909012386026772</v>
+        <v>1.908992393795541</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047744561638638</v>
+        <v>0.3047703456602692</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1976717905495831</v>
+        <v>-0.1976831063206714</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2800570084117425</v>
+        <v>0.2800320109052251</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.689686784313448</v>
+        <v>6.678130257271427</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.816900004685128</v>
+        <v>6.786885579282242</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.014127219047727</v>
+        <v>6.980983508146435</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E7" t="n">
+        <v>14220</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14219</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14218</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581407265438177</v>
+        <v>5.581410331246923</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.33253223495702</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.58518090053873</v>
+        <v>5.585171449227119</v>
       </c>
       <c r="R7" t="n">
         <v>10.01</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003773635100553186</v>
+        <v>0.003761117980196539</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156154554457888</v>
+        <v>1.156082398179051</v>
       </c>
       <c r="U7" t="n">
-        <v>1.493933950729251</v>
+        <v>1.493877893897884</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5086044985818953</v>
+        <v>0.5086054895802059</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07397087767353983</v>
+        <v>0.07397529656615609</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047548379740783</v>
+        <v>0.5047554594480386</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.049520448482765</v>
+        <v>5.036730674544559</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.235574122115706</v>
+        <v>5.192137197598877</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.422125078432958</v>
+        <v>5.375297430612253</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E8" t="n">
+        <v>9018</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9017</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9016</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878576419698313</v>
+        <v>7.878449040700899</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116737541269506</v>
+        <v>8.116682077916034</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.238161121571193</v>
+        <v>0.2382330372151358</v>
       </c>
       <c r="T8" t="n">
-        <v>1.44680742203595</v>
+        <v>1.446860316785276</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826389549682334</v>
+        <v>1.826418843179948</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079681429053261</v>
+        <v>0.8079384459419147</v>
       </c>
       <c r="W8" t="n">
-        <v>0.627588907542267</v>
+        <v>0.6275417380723529</v>
       </c>
       <c r="X8" t="n">
-        <v>0.79808474955208</v>
+        <v>0.7980418782391374</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.16787055038666</v>
+        <v>5.099511337759846</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.367333532520262</v>
+        <v>5.342743598665264</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.453551490471698</v>
+        <v>5.460050661734519</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E9" t="n">
+        <v>13883</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13882</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13881</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613455262589151</v>
+        <v>7.613317425443021</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.511906096706377</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.677635419377268</v>
+        <v>7.677496226932599</v>
       </c>
       <c r="R9" t="n">
         <v>14.03</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0641801567881182</v>
+        <v>0.06417880148958027</v>
       </c>
       <c r="T9" t="n">
-        <v>1.476034796521947</v>
+        <v>1.475930337637121</v>
       </c>
       <c r="U9" t="n">
-        <v>1.918523451999134</v>
+        <v>1.918451618711712</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617833112248342</v>
+        <v>0.7617914420783759</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363386099944678</v>
+        <v>0.5363553341480209</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597842504001798</v>
+        <v>0.7597920338252521</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.366076619857107</v>
+        <v>5.330919313798526</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.577736257156308</v>
+        <v>5.549030797849191</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.689890854813378</v>
+        <v>5.689559454913682</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.6180641460345</v>
+        <v>10.61795737300448</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3130024655421217</v>
+        <v>0.3128956925121033</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052182136208033</v>
+        <v>2.05221181058171</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697790499493602</v>
+        <v>2.697832239798239</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356739521808561</v>
+        <v>0.3567516612137712</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1201829919577126</v>
+        <v>-0.1202176552431335</v>
       </c>
       <c r="X10" t="n">
-        <v>0.336149804563871</v>
+        <v>0.3361784899665597</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.603363117970124</v>
+        <v>9.576699197179297</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.747830679691329</v>
+        <v>9.73462236968402</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.885578782902519</v>
+        <v>9.828887738120315</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E11" t="n">
+        <v>13824</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13823</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13822</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244425155549125</v>
+        <v>5.244305830861608</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8408085735402808</v>
+        <v>0.840834564254062</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216919651755506</v>
+        <v>5.216806880101102</v>
       </c>
       <c r="R11" t="n">
         <v>9.94</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.027505503793619</v>
+        <v>-0.02749895076050395</v>
       </c>
       <c r="T11" t="n">
-        <v>1.156918604025081</v>
+        <v>1.15689299293466</v>
       </c>
       <c r="U11" t="n">
-        <v>1.475901277617386</v>
+        <v>1.475864123516137</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4298784338146974</v>
+        <v>0.4299205248210144</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08152622387815023</v>
+        <v>-0.08144433581180288</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4272628356496141</v>
+        <v>0.4273045513650992</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.092965426623963</v>
+        <v>4.046982435578609</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.465434278904044</v>
+        <v>4.424492507981627</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.727553903680152</v>
+        <v>4.621438330871491</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E12" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4141</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4140</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.480157850241545</v>
+        <v>7.479368751509297</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204886917960089</v>
+        <v>2.20490694239291</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.653507099736235</v>
+        <v>7.652792216303054</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1733492494946885</v>
+        <v>0.1734234647937563</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9133155870357498</v>
+        <v>0.9133786929456785</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195776415245998</v>
+        <v>1.19578393698298</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8306164984572412</v>
+        <v>0.8306757194321579</v>
       </c>
       <c r="W12" t="n">
-        <v>0.656541291620602</v>
+        <v>0.6566666552518448</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8288683692845127</v>
+        <v>0.8289237501160737</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.487544769467629</v>
+        <v>4.430268344667017</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.055102617799302</v>
+        <v>4.91726849391864</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.664934856077734</v>
+        <v>5.56233271313106</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E13" t="n">
+        <v>6477</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6476</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6475</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.609457142857144</v>
+        <v>9.609136040765906</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02791112303746</v>
+        <v>10.02780789390202</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4184539801803164</v>
+        <v>0.4186718531361179</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691998684510549</v>
+        <v>1.691896182900326</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152345478903543</v>
+        <v>2.152172711276484</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230659736339423</v>
+        <v>0.8230742135416397</v>
       </c>
       <c r="W13" t="n">
-        <v>0.648411107763841</v>
+        <v>0.6484310746666715</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106516945039377</v>
+        <v>0.8106326236033533</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.335643638096165</v>
+        <v>8.348802386014915</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.443814483033172</v>
+        <v>8.457637991047072</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.491067612948004</v>
+        <v>8.490639734276861</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E14" t="n">
+        <v>14064</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14063</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14062</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130787583558527</v>
+        <v>8.130643532674394</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073441734417345</v>
+        <v>0.9073682914820286</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.201184555491377</v>
+        <v>8.20106119058277</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07039697193285031</v>
+        <v>0.07041765790837626</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757834130294043</v>
+        <v>1.757734394490347</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283604043439134</v>
+        <v>2.283536597401001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807501110983188</v>
+        <v>0.7807508759230875</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651425482282733</v>
+        <v>0.5651478940613255</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803757159927844</v>
+        <v>0.7803759530994571</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.404900881436571</v>
+        <v>5.348562609310292</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.660276038742301</v>
+        <v>5.593749865934753</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.995435657386878</v>
+        <v>5.883661009822204</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.680753880266075</v>
+        <v>4.679926144756278</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82332477542035</v>
+        <v>11.82320444569163</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1405626076064354</v>
+        <v>-0.140682937335153</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052115733816223</v>
+        <v>2.052123071950576</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697403743939393</v>
+        <v>2.697425692839427</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949611124012568</v>
+        <v>0.7949639882662458</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096645392284745</v>
+        <v>0.6096581868469417</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862339189207049</v>
+        <v>0.7862455891244384</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.37226475346843</v>
+        <v>11.49161258572306</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.69878976455099</v>
+        <v>11.74670741633319</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.8339531765274</v>
+        <v>11.85670534419797</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E16" t="n">
+        <v>9827</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9826</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9825</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.36627368956743</v>
+        <v>8.366001323020557</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625117914995093</v>
+        <v>8.625038957451858</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2588442254276639</v>
+        <v>0.259037634431301</v>
       </c>
       <c r="T16" t="n">
-        <v>3.588312002846224</v>
+        <v>3.588752401239618</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09522205082779</v>
+        <v>11.09490167072006</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04200110574090984</v>
+        <v>0.0419679660024803</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6094448159723527</v>
+        <v>-0.6095003335983882</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02533929739981766</v>
+        <v>0.02530590737966665</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.37603394964643</v>
+        <v>12.07265665559148</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.80138102302272</v>
+        <v>12.71191915829096</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87091515774632</v>
+        <v>12.87070899663289</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E17" t="n">
+        <v>2371</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2370</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2369</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.509824820599409</v>
+        <v>6.508272151898734</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.401476718403548</v>
+        <v>1.403296898079764</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.878232865219802</v>
+        <v>6.876039592759198</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3684080446203926</v>
+        <v>0.3677674408604626</v>
       </c>
       <c r="T17" t="n">
-        <v>2.028294022049624</v>
+        <v>2.027347770214075</v>
       </c>
       <c r="U17" t="n">
-        <v>2.561360111897746</v>
+        <v>2.560654916387715</v>
       </c>
       <c r="V17" t="n">
-        <v>0.527217217513327</v>
+        <v>0.5277960860569225</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03436680234546408</v>
+        <v>0.03530233403020155</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5238421550681354</v>
+        <v>0.5244268441296301</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.296196085017402</v>
+        <v>1.253810873362248</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.334848554552343</v>
+        <v>2.511087279125056</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.989208552039508</v>
+        <v>3.465390431560945</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E18" t="n">
+        <v>3230</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3229</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3228</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.484368494423792</v>
+        <v>6.483626974295447</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.680162920144049</v>
+        <v>6.679259865688116</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1957944257202579</v>
+        <v>0.1956328913926684</v>
       </c>
       <c r="T18" t="n">
-        <v>1.10172059242112</v>
+        <v>1.101391524908859</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489464423186992</v>
+        <v>1.489171464356832</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6028462923844961</v>
+        <v>0.6031637659660196</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2211038329142834</v>
+        <v>0.2216541853064091</v>
       </c>
       <c r="X18" t="n">
-        <v>0.5998741822384539</v>
+        <v>0.6002024470911504</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.322282161200548</v>
+        <v>2.231972325527164</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.537064920149219</v>
+        <v>3.836796827615488</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.096370951219138</v>
+        <v>4.982499485817923</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16681</v>
+        <v>16682</v>
       </c>
       <c r="E19" t="n">
+        <v>7184</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7183</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7182</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34822667780563</v>
+        <v>10.34690052902687</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13615645602373</v>
+        <v>11.13526843826738</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7879297782181042</v>
+        <v>0.7883679092405128</v>
       </c>
       <c r="T19" t="n">
-        <v>2.046260155413509</v>
+        <v>2.046897959607826</v>
       </c>
       <c r="U19" t="n">
-        <v>2.767562734943652</v>
+        <v>2.768438077036501</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7269148580693253</v>
+        <v>0.7269354908124002</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4704326226233532</v>
+        <v>0.470486278814877</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790684361569692</v>
+        <v>0.6790070239416982</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.445853819640406</v>
+        <v>7.428617788626842</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.479106478742875</v>
+        <v>7.818743553169526</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.509520977545092</v>
+        <v>9.498337416931165</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.445853819640406</v>
+        <v>7.428617788626842</v>
       </c>
       <c r="G2" t="n">
-        <v>7.479106478742875</v>
+        <v>7.818743553169526</v>
       </c>
       <c r="H2" t="n">
-        <v>7.509520977545092</v>
+        <v>9.498337416931165</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.049520448482765</v>
+        <v>5.036730674544559</v>
       </c>
       <c r="G3" t="n">
-        <v>5.235574122115707</v>
+        <v>5.192137197598878</v>
       </c>
       <c r="H3" t="n">
-        <v>5.422125078432958</v>
+        <v>5.375297430612253</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.092965426623963</v>
+        <v>4.046982435578609</v>
       </c>
       <c r="G4" t="n">
-        <v>4.465434278904044</v>
+        <v>4.424492507981627</v>
       </c>
       <c r="H4" t="n">
-        <v>4.727553903680152</v>
+        <v>4.621438330871491</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.37603394964643</v>
+        <v>12.07265665559148</v>
       </c>
       <c r="G5" t="n">
-        <v>12.80138102302272</v>
+        <v>12.71191915829096</v>
       </c>
       <c r="H5" t="n">
-        <v>12.87091515774632</v>
+        <v>12.87070899663289</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.963233803362154</v>
+        <v>2.915278305254414</v>
       </c>
       <c r="G6" t="n">
-        <v>78.99744556278208</v>
+        <v>51.43390921191438</v>
       </c>
       <c r="H6" t="n">
-        <v>111.56</v>
+        <v>109.2722404337466</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.37226475346843</v>
+        <v>11.49161258572306</v>
       </c>
       <c r="G7" t="n">
-        <v>11.69878976455099</v>
+        <v>11.74670741633319</v>
       </c>
       <c r="H7" t="n">
-        <v>11.8339531765274</v>
+        <v>11.85670534419797</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.335643638096165</v>
+        <v>8.348802386014915</v>
       </c>
       <c r="G8" t="n">
-        <v>8.443814483033174</v>
+        <v>8.457637991047072</v>
       </c>
       <c r="H8" t="n">
-        <v>8.491067612948004</v>
+        <v>8.490639734276861</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.487544769467629</v>
+        <v>4.430268344667017</v>
       </c>
       <c r="G9" t="n">
-        <v>5.055102617799301</v>
+        <v>4.917268493918639</v>
       </c>
       <c r="H9" t="n">
-        <v>5.664934856077734</v>
+        <v>5.56233271313106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.16787055038666</v>
+        <v>5.099511337759846</v>
       </c>
       <c r="G10" t="n">
-        <v>5.367333532520262</v>
+        <v>5.342743598665264</v>
       </c>
       <c r="H10" t="n">
-        <v>5.453551490471698</v>
+        <v>5.460050661734519</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.296196085017402</v>
+        <v>1.253810873362248</v>
       </c>
       <c r="G11" t="n">
-        <v>3.334848554552343</v>
+        <v>2.511087279125056</v>
       </c>
       <c r="H11" t="n">
-        <v>6.989208552039508</v>
+        <v>3.465390431560945</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.404900881436571</v>
+        <v>5.348562609310292</v>
       </c>
       <c r="G12" t="n">
-        <v>5.660276038742301</v>
+        <v>5.593749865934752</v>
       </c>
       <c r="H12" t="n">
-        <v>5.995435657386878</v>
+        <v>5.883661009822204</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.603363117970124</v>
+        <v>9.576699197179297</v>
       </c>
       <c r="G13" t="n">
-        <v>9.747830679691329</v>
+        <v>9.734622369684018</v>
       </c>
       <c r="H13" t="n">
-        <v>9.885578782902519</v>
+        <v>9.828887738120315</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.366076619857107</v>
+        <v>5.330919313798526</v>
       </c>
       <c r="G14" t="n">
-        <v>5.577736257156308</v>
+        <v>5.54903079784919</v>
       </c>
       <c r="H14" t="n">
-        <v>5.689890854813378</v>
+        <v>5.689559454913682</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.689686784313448</v>
+        <v>6.678130257271427</v>
       </c>
       <c r="G15" t="n">
-        <v>6.816900004685128</v>
+        <v>6.786885579282243</v>
       </c>
       <c r="H15" t="n">
-        <v>7.014127219047727</v>
+        <v>6.980983508146435</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.322282161200548</v>
+        <v>2.231972325527164</v>
       </c>
       <c r="G16" t="n">
-        <v>4.537064920149219</v>
+        <v>3.836796827615488</v>
       </c>
       <c r="H16" t="n">
-        <v>7.096370951219138</v>
+        <v>4.982499485817923</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.188436807095343</v>
+        <v>3.153905465288036</v>
       </c>
       <c r="G17" t="n">
-        <v>3.248835375647353</v>
+        <v>3.219635136387393</v>
       </c>
       <c r="H17" t="n">
-        <v>3.348651951681449</v>
+        <v>3.298953325505447</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.345357538802661</v>
+        <v>2.288553545051698</v>
       </c>
       <c r="G18" t="n">
-        <v>2.385825826021182</v>
+        <v>2.379444123629738</v>
       </c>
       <c r="H18" t="n">
-        <v>2.444828301113267</v>
+        <v>2.436395864106351</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.32151506378835</v>
+        <v>5.182639961611631</v>
       </c>
       <c r="G19" t="n">
-        <v>5.790962836621371</v>
+        <v>5.592375924631712</v>
       </c>
       <c r="H19" t="n">
-        <v>6.949423734651264</v>
+        <v>5.899094287894956</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E2" t="n">
+        <v>10019</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10018</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10017</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6570339090213</v>
+        <v>102.6472867505157</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6571462411601</v>
+        <v>102.6452616808064</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001123321387959327</v>
+        <v>-0.002025069709328786</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89186478611563</v>
+        <v>17.89216340218298</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06873747245711</v>
+        <v>36.07001030120582</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1366569056593932</v>
+        <v>0.1377335806640506</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7223088958819064</v>
+        <v>-0.7204345798354164</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1366531727439204</v>
+        <v>0.1377302965823725</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.915278305254414</v>
+        <v>2.954362705692132</v>
       </c>
       <c r="Z2" t="n">
-        <v>51.4339092119144</v>
+        <v>74.7156122946712</v>
       </c>
       <c r="AA2" t="n">
-        <v>109.2722404337466</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E3" t="n">
+        <v>14613</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14612</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14611</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,52 +688,52 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910382520019163</v>
+        <v>4.910240145086231</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01756303724928367</v>
+        <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.969832614138848</v>
+        <v>4.967664937522925</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05945009411968397</v>
+        <v>0.05742479243669449</v>
       </c>
       <c r="T3" t="n">
-        <v>1.346011446212224</v>
+        <v>1.345180635313871</v>
       </c>
       <c r="U3" t="n">
-        <v>1.721211468650319</v>
+        <v>1.719608334174518</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7809582309084562</v>
+        <v>0.7812188834979926</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5686107768927517</v>
+        <v>0.5694030951347135</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7799564911649091</v>
+        <v>0.7801899289462053</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.288553545051698</v>
+        <v>2.26699926199262</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.379444123629738</v>
+        <v>2.376744396610848</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.436395864106351</v>
+        <v>2.450081180811809</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E4" t="n">
+        <v>10247</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10246</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10245</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.912168862859933</v>
+        <v>6.911891957837204</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241218352707952</v>
+        <v>7.241053994668468</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3290494898480191</v>
+        <v>0.3291620368312633</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29274139838796</v>
+        <v>1.292776822704201</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682410088094794</v>
+        <v>1.682444277031299</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676555665749075</v>
+        <v>0.8676463083738811</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374840523781273</v>
+        <v>0.7374668870225429</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472701130343343</v>
+        <v>0.8472366838444724</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.153905465288036</v>
+        <v>3.195413284132842</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.219635136387393</v>
+        <v>3.271696290351971</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.298953325505447</v>
+        <v>3.523063172662976</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.759748892171344</v>
+        <v>2.759527675276753</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.3031671975967</v>
+        <v>9.303068425487769</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3618646145708707</v>
+        <v>0.3617658424619399</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253826626074554</v>
+        <v>1.253839036191161</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750178956052324</v>
+        <v>1.750173991560109</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661850661261836</v>
+        <v>0.8661885468650095</v>
       </c>
       <c r="W5" t="n">
-        <v>0.721300951353263</v>
+        <v>0.721302532445631</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8601623829596194</v>
+        <v>0.8601699405777891</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.182639961611631</v>
+        <v>5.092481990352563</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.592375924631712</v>
+        <v>5.677957550954441</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.899094287894956</v>
+        <v>6.495943920469296</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E6" t="n">
+        <v>8860</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8859</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8858</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732699424249266</v>
+        <v>6.732891861383903</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.020971068614799</v>
+        <v>7.021216260521161</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2882716443655341</v>
+        <v>0.288324399137257</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480196326245886</v>
+        <v>1.480198376052279</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908992393795541</v>
+        <v>1.908963045547744</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047703456602692</v>
+        <v>0.3047684891369857</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1976831063206714</v>
+        <v>-0.197652356156653</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2800320109052251</v>
+        <v>0.280018994898128</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.678130257271427</v>
+        <v>6.696661070007455</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.786885579282242</v>
+        <v>6.770374358457616</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.980983508146435</v>
+        <v>6.909967462934278</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E7" t="n">
+        <v>14221</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14220</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14219</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,52 +1044,52 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581410331246923</v>
+        <v>5.581395464135021</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.33253223495702</v>
+        <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.585171449227119</v>
+        <v>5.567964653515936</v>
       </c>
       <c r="R7" t="n">
-        <v>10.01</v>
+        <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>0.003761117980196539</v>
+        <v>-0.01343081061908412</v>
       </c>
       <c r="T7" t="n">
-        <v>1.156082398179051</v>
+        <v>1.167608406475142</v>
       </c>
       <c r="U7" t="n">
-        <v>1.493877893897884</v>
+        <v>1.510714439450444</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5086054895802059</v>
+        <v>0.5047179801916382</v>
       </c>
       <c r="W7" t="n">
-        <v>0.07397529656615609</v>
+        <v>0.0529190365979183</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5047554594480386</v>
+        <v>0.5025694602654009</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.036730674544559</v>
+        <v>5.028085538334189</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.192137197598877</v>
+        <v>5.167107597525694</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.375297430612253</v>
+        <v>5.33884221402214</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E8" t="n">
+        <v>9019</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9018</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9017</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878449040700899</v>
+        <v>7.878304224883566</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116682077916034</v>
+        <v>8.1166146528408</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2382330372151358</v>
+        <v>0.2383104279572333</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446860316785276</v>
+        <v>1.446899646588764</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826418843179948</v>
+        <v>1.826434505616604</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079384459419147</v>
+        <v>0.8079129063955852</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275417380723529</v>
+        <v>0.6275019088880953</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7980418782391374</v>
+        <v>0.798003092877048</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.099511337759846</v>
+        <v>5.046316549131353</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.342743598665264</v>
+        <v>5.313230106453211</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.460050661734519</v>
+        <v>5.472472213413822</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E9" t="n">
+        <v>13884</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13883</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13882</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,52 +1222,52 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613317425443021</v>
+        <v>7.613165922351076</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
       </c>
       <c r="P9" t="n">
-        <v>0.511906096706377</v>
+        <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.677496226932599</v>
+        <v>7.65875367318092</v>
       </c>
       <c r="R9" t="n">
-        <v>14.03</v>
+        <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06417880148958027</v>
+        <v>0.04558775082984242</v>
       </c>
       <c r="T9" t="n">
-        <v>1.475930337637121</v>
+        <v>1.49484628354202</v>
       </c>
       <c r="U9" t="n">
-        <v>1.918451618711712</v>
+        <v>1.942789531148375</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7617914420783759</v>
+        <v>0.7564908090093488</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5363553341480209</v>
+        <v>0.5245017483519698</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7597920338252521</v>
+        <v>0.7550829110202868</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.330919313798526</v>
+        <v>5.328734317343174</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.549030797849191</v>
+        <v>5.518774626805401</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.689559454913682</v>
+        <v>5.689468869349631</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61795737300448</v>
+        <v>10.61785147063127</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3128956925121033</v>
+        <v>0.3127897901388941</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05221181058171</v>
+        <v>2.052241379078954</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697832239798239</v>
+        <v>2.697873759124766</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567516612137712</v>
+        <v>0.356763370945333</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1202176552431335</v>
+        <v>-0.1202521355490771</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3361784899665597</v>
+        <v>0.3362064981549989</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.576699197179297</v>
+        <v>9.635717162704379</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.73462236968402</v>
+        <v>9.804149781915189</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.828887738120315</v>
+        <v>9.926240185401854</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E11" t="n">
+        <v>13825</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13824</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13823</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244305830861608</v>
+        <v>5.244199182581019</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.840834564254062</v>
+        <v>0.4578664206642067</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.216806880101102</v>
+        <v>5.217626238040746</v>
       </c>
       <c r="R11" t="n">
-        <v>9.94</v>
+        <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02749895076050395</v>
+        <v>-0.0265729445402724</v>
       </c>
       <c r="T11" t="n">
-        <v>1.15689299293466</v>
+        <v>1.1620620401114</v>
       </c>
       <c r="U11" t="n">
-        <v>1.475864123516137</v>
+        <v>1.483522933579032</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4299205248210144</v>
+        <v>0.4290643776081454</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08144433581180288</v>
+        <v>-0.09269124464271505</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4273045513650992</v>
+        <v>0.4272584766900005</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.046982435578609</v>
+        <v>4.226409594095942</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.424492507981627</v>
+        <v>4.561393486786233</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.621438330871491</v>
+        <v>4.743843173431734</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E12" t="n">
+        <v>4143</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4142</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4141</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.479368751509297</v>
+        <v>7.47852752293578</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.20490694239291</v>
+        <v>2.204926937269373</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.652792216303054</v>
+        <v>7.652042106407651</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1734234647937563</v>
+        <v>0.1735145834718716</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9133786929456785</v>
+        <v>0.9134756515514481</v>
       </c>
       <c r="U12" t="n">
-        <v>1.19578393698298</v>
+        <v>1.195831326783832</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8306757194321579</v>
+        <v>0.8307352370389887</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6566666552518448</v>
+        <v>0.6567980694944564</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8289237501160737</v>
+        <v>0.8289782104625532</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.430268344667017</v>
+        <v>4.443196238152299</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.91726849391864</v>
+        <v>4.835362442709794</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.56233271313106</v>
+        <v>5.480203607328424</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E13" t="n">
+        <v>6478</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6477</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6476</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.609136040765906</v>
+        <v>9.60878840512583</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02780789390202</v>
+        <v>10.02767847152865</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4186718531361179</v>
+        <v>0.4188900664028207</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691896182900326</v>
+        <v>1.69179776617286</v>
       </c>
       <c r="U13" t="n">
-        <v>2.152172711276484</v>
+        <v>2.151987900322738</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230742135416397</v>
+        <v>0.8230863533196592</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484310746666715</v>
+        <v>0.6484580591672223</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106326236033533</v>
+        <v>0.8106176150892088</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.348802386014915</v>
+        <v>8.396115513717463</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.457637991047072</v>
+        <v>8.471917673578442</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.490639734276861</v>
+        <v>8.495886704374328</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E14" t="n">
+        <v>14065</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14064</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14063</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130643532674394</v>
+        <v>8.130484748293515</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073682914820286</v>
+        <v>0.9073923739237393</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.20106119058277</v>
+        <v>8.200926249857927</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07041765790837626</v>
+        <v>0.07044150156441156</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757734394490347</v>
+        <v>1.757626781046548</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283536597401001</v>
+        <v>2.28346624723425</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807508759230875</v>
+        <v>0.780753308069368</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651478940613255</v>
+        <v>0.5651566255730263</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803759530994571</v>
+        <v>0.7803778261481102</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.348562609310292</v>
+        <v>5.315944194264254</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.593749865934753</v>
+        <v>5.546837096244948</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.883661009822204</v>
+        <v>5.786240080423604</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.679926144756278</v>
+        <v>4.67909963099631</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82320444569163</v>
+        <v>11.82307869302649</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.140682937335153</v>
+        <v>-0.1408086900002876</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052123071950576</v>
+        <v>2.052139111622562</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697425692839427</v>
+        <v>2.697446238759891</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949639882662458</v>
+        <v>0.7949669763873326</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096581868469417</v>
+        <v>0.609652240464499</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862455891244384</v>
+        <v>0.7862570704159578</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.49161258572306</v>
+        <v>11.64095782018896</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.74670741633319</v>
+        <v>11.78888834483005</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.85670534419797</v>
+        <v>11.89960467978018</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E16" t="n">
+        <v>9828</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9827</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9826</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.366001323020557</v>
+        <v>8.36571323903531</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625038957451858</v>
+        <v>8.624950850720868</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.259037634431301</v>
+        <v>0.2592376116855568</v>
       </c>
       <c r="T16" t="n">
-        <v>3.588752401239618</v>
+        <v>3.589200907529671</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09490167072006</v>
+        <v>11.09459172475595</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0419679660024803</v>
+        <v>0.04193400479062569</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6095003335983882</v>
+        <v>-0.609557036554393</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02530590737966665</v>
+        <v>0.02527165789313013</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.07265665559148</v>
+        <v>11.93633521149583</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.71191915829096</v>
+        <v>12.61442964205227</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87070899663289</v>
+        <v>12.87059962932987</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E17" t="n">
+        <v>2372</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2371</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2370</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.508272151898734</v>
+        <v>6.506674398987769</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.403296898079764</v>
+        <v>1.405114391143911</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.876039592759198</v>
+        <v>6.873869888184253</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3677674408604626</v>
+        <v>0.3671954891964839</v>
       </c>
       <c r="T17" t="n">
-        <v>2.027347770214075</v>
+        <v>2.026332016117387</v>
       </c>
       <c r="U17" t="n">
-        <v>2.560654916387715</v>
+        <v>2.559942581670834</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5277960860569225</v>
+        <v>0.5283847886976363</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03530233403020155</v>
+        <v>0.03629036366897587</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5244268441296301</v>
+        <v>0.5250198508939766</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.253810873362248</v>
+        <v>1.729834273005751</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.511087279125056</v>
+        <v>2.804973536354557</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.465390431560945</v>
+        <v>4.354323631531114</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E18" t="n">
+        <v>3231</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3230</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3229</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.483626974295447</v>
+        <v>6.482876625386997</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.679259865688116</v>
+        <v>6.678370222489059</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1956328913926684</v>
+        <v>0.1954935971020625</v>
       </c>
       <c r="T18" t="n">
-        <v>1.101391524908859</v>
+        <v>1.10103941761726</v>
       </c>
       <c r="U18" t="n">
-        <v>1.489171464356832</v>
+        <v>1.488870877527627</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6031637659660196</v>
+        <v>0.6034840216097006</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2216541853064091</v>
+        <v>0.2222238580703465</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6002024470911504</v>
+        <v>0.6005309755590503</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.231972325527164</v>
+        <v>3.293677779338347</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.836796827615488</v>
+        <v>4.252958307223551</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.982499485817923</v>
+        <v>5.854962366077947</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16682</v>
+        <v>16683</v>
       </c>
       <c r="E19" t="n">
+        <v>7185</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7184</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7183</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34690052902687</v>
+        <v>10.34556013363029</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13526843826738</v>
+        <v>11.1343738620298</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7883679092405128</v>
+        <v>0.7888137283995118</v>
       </c>
       <c r="T19" t="n">
-        <v>2.046897959607826</v>
+        <v>2.047556364059985</v>
       </c>
       <c r="U19" t="n">
-        <v>2.768438077036501</v>
+        <v>2.769343793492026</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7269354908124002</v>
+        <v>0.7269543019789464</v>
       </c>
       <c r="W19" t="n">
-        <v>0.470486278814877</v>
+        <v>0.470538131030654</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6790070239416982</v>
+        <v>0.6789411663432485</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.428617788626842</v>
+        <v>7.426667103778476</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.818743553169526</v>
+        <v>7.456258418822868</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.498337416931165</v>
+        <v>7.487302944324107</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.428617788626842</v>
+        <v>7.426667103778476</v>
       </c>
       <c r="G2" t="n">
-        <v>7.818743553169526</v>
+        <v>7.456258418822868</v>
       </c>
       <c r="H2" t="n">
-        <v>9.498337416931165</v>
+        <v>7.487302944324107</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.036730674544559</v>
+        <v>5.028085538334189</v>
       </c>
       <c r="G3" t="n">
-        <v>5.192137197598878</v>
+        <v>5.167107597525694</v>
       </c>
       <c r="H3" t="n">
-        <v>5.375297430612253</v>
+        <v>5.33884221402214</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.046982435578609</v>
+        <v>4.226409594095942</v>
       </c>
       <c r="G4" t="n">
-        <v>4.424492507981627</v>
+        <v>4.561393486786232</v>
       </c>
       <c r="H4" t="n">
-        <v>4.621438330871491</v>
+        <v>4.743843173431734</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>12.07265665559148</v>
+        <v>11.93633521149583</v>
       </c>
       <c r="G5" t="n">
-        <v>12.71191915829096</v>
+        <v>12.61442964205227</v>
       </c>
       <c r="H5" t="n">
-        <v>12.87070899663289</v>
+        <v>12.87059962932987</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.915278305254414</v>
+        <v>2.954362705692132</v>
       </c>
       <c r="G6" t="n">
-        <v>51.43390921191438</v>
+        <v>74.71561229467122</v>
       </c>
       <c r="H6" t="n">
-        <v>109.2722404337466</v>
+        <v>111.56</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.49161258572306</v>
+        <v>11.64095782018896</v>
       </c>
       <c r="G7" t="n">
-        <v>11.74670741633319</v>
+        <v>11.78888834483005</v>
       </c>
       <c r="H7" t="n">
-        <v>11.85670534419797</v>
+        <v>11.89960467978018</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.348802386014915</v>
+        <v>8.396115513717463</v>
       </c>
       <c r="G8" t="n">
-        <v>8.457637991047072</v>
+        <v>8.471917673578442</v>
       </c>
       <c r="H8" t="n">
-        <v>8.490639734276861</v>
+        <v>8.495886704374328</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.430268344667017</v>
+        <v>4.443196238152299</v>
       </c>
       <c r="G9" t="n">
-        <v>4.917268493918639</v>
+        <v>4.835362442709794</v>
       </c>
       <c r="H9" t="n">
-        <v>5.56233271313106</v>
+        <v>5.480203607328424</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.099511337759846</v>
+        <v>5.046316549131353</v>
       </c>
       <c r="G10" t="n">
-        <v>5.342743598665264</v>
+        <v>5.313230106453211</v>
       </c>
       <c r="H10" t="n">
-        <v>5.460050661734519</v>
+        <v>5.472472213413822</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.253810873362248</v>
+        <v>1.729834273005751</v>
       </c>
       <c r="G11" t="n">
-        <v>2.511087279125056</v>
+        <v>2.804973536354557</v>
       </c>
       <c r="H11" t="n">
-        <v>3.465390431560945</v>
+        <v>4.354323631531114</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.348562609310292</v>
+        <v>5.315944194264254</v>
       </c>
       <c r="G12" t="n">
-        <v>5.593749865934752</v>
+        <v>5.546837096244948</v>
       </c>
       <c r="H12" t="n">
-        <v>5.883661009822204</v>
+        <v>5.786240080423604</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.576699197179297</v>
+        <v>9.635717162704379</v>
       </c>
       <c r="G13" t="n">
-        <v>9.734622369684018</v>
+        <v>9.804149781915189</v>
       </c>
       <c r="H13" t="n">
-        <v>9.828887738120315</v>
+        <v>9.926240185401854</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.330919313798526</v>
+        <v>5.328734317343174</v>
       </c>
       <c r="G14" t="n">
-        <v>5.54903079784919</v>
+        <v>5.518774626805401</v>
       </c>
       <c r="H14" t="n">
-        <v>5.689559454913682</v>
+        <v>5.689468869349631</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.678130257271427</v>
+        <v>6.696661070007455</v>
       </c>
       <c r="G15" t="n">
-        <v>6.786885579282243</v>
+        <v>6.770374358457618</v>
       </c>
       <c r="H15" t="n">
-        <v>6.980983508146435</v>
+        <v>6.909967462934278</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.231972325527164</v>
+        <v>3.293677779338347</v>
       </c>
       <c r="G16" t="n">
-        <v>3.836796827615488</v>
+        <v>4.252958307223551</v>
       </c>
       <c r="H16" t="n">
-        <v>4.982499485817923</v>
+        <v>5.854962366077947</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.153905465288036</v>
+        <v>3.195413284132842</v>
       </c>
       <c r="G17" t="n">
-        <v>3.219635136387393</v>
+        <v>3.271696290351971</v>
       </c>
       <c r="H17" t="n">
-        <v>3.298953325505447</v>
+        <v>3.523063172662976</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.288553545051698</v>
+        <v>2.26699926199262</v>
       </c>
       <c r="G18" t="n">
-        <v>2.379444123629738</v>
+        <v>2.376744396610848</v>
       </c>
       <c r="H18" t="n">
-        <v>2.436395864106351</v>
+        <v>2.450081180811809</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.182639961611631</v>
+        <v>5.092481990352563</v>
       </c>
       <c r="G19" t="n">
-        <v>5.592375924631712</v>
+        <v>5.677957550954441</v>
       </c>
       <c r="H19" t="n">
-        <v>5.899094287894956</v>
+        <v>6.495943920469296</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E2" t="n">
         <v>10019</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10018</v>
+        <v>10019</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6472867505157</v>
+        <v>102.6375245699837</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6452616808064</v>
+        <v>102.637740905098</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.002025069709328786</v>
+        <v>0.0002163351142485555</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89216340218298</v>
+        <v>17.88840142533172</v>
       </c>
       <c r="U2" t="n">
-        <v>36.07001030120582</v>
+        <v>36.06450270281622</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1377335806640506</v>
+        <v>0.1388680450003575</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7204345798354164</v>
+        <v>-0.717911883979736</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1377302965823725</v>
+        <v>0.1388643265631246</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.954362705692132</v>
+        <v>2.970173187209827</v>
       </c>
       <c r="Z2" t="n">
-        <v>74.7156122946712</v>
+        <v>94.23733977776757</v>
       </c>
       <c r="AA2" t="n">
-        <v>111.56</v>
+        <v>110.5615810918087</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E3" t="n">
         <v>14613</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14612</v>
+        <v>14613</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910240145086231</v>
+        <v>4.910088209128858</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.967664937522925</v>
+        <v>4.967429247818525</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05742479243669449</v>
+        <v>0.05734103868966731</v>
       </c>
       <c r="T3" t="n">
-        <v>1.345180635313871</v>
+        <v>1.345110195443517</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719608334174518</v>
+        <v>1.719552005763086</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812188834979926</v>
+        <v>0.7812362980142893</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5694030951347135</v>
+        <v>0.5694229882347026</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7801899289462053</v>
+        <v>0.7802112984611337</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.26699926199262</v>
+        <v>2.228804326450344</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.376744396610848</v>
+        <v>2.364825794050943</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.450081180811809</v>
+        <v>2.450363815142576</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E4" t="n">
         <v>10247</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10246</v>
+        <v>10247</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.911891957837204</v>
+        <v>6.911609739435934</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.241053994668468</v>
+        <v>7.240577255790699</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3291620368312633</v>
+        <v>0.3289675163547665</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292776822704201</v>
+        <v>1.292687022552367</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682444277031299</v>
+        <v>1.682345284134077</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676463083738811</v>
+        <v>0.8676600129664125</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374668870225429</v>
+        <v>0.7374920310505539</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472366838444724</v>
+        <v>0.847289627900915</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.195413284132842</v>
+        <v>3.239221238938053</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.271696290351971</v>
+        <v>3.250858116346647</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.523063172662976</v>
+        <v>3.277610619469026</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.759527675276753</v>
+        <v>2.759306784660767</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.303068425487769</v>
+        <v>9.302970096585515</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3617658424619399</v>
+        <v>0.3616675135596847</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253839036191161</v>
+        <v>1.253851658404295</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750173991560109</v>
+        <v>1.750169671043864</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661885468650095</v>
+        <v>0.8661919283286279</v>
       </c>
       <c r="W5" t="n">
-        <v>0.721302532445631</v>
+        <v>0.7213039084407671</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8601699405777891</v>
+        <v>0.8601773712448768</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.092481990352563</v>
+        <v>4.996092600235603</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.677957550954441</v>
+        <v>5.730987784150704</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.495943920469296</v>
+        <v>6.881269525883063</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E6" t="n">
         <v>8860</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8859</v>
+        <v>8860</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.732891861383903</v>
+        <v>6.73306309255079</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021216260521161</v>
+        <v>7.021155658947484</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.288324399137257</v>
+        <v>0.2880925663966936</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480198376052279</v>
+        <v>1.480194293551444</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908963045547744</v>
+        <v>1.908924779687538</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047684891369857</v>
+        <v>0.3047555024287197</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.197652356156653</v>
+        <v>-0.1976372776187734</v>
       </c>
       <c r="X6" t="n">
-        <v>0.280018994898128</v>
+        <v>0.2800102551916979</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.696661070007455</v>
+        <v>6.666959093480791</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.770374358457616</v>
+        <v>6.74067272580879</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.909967462934278</v>
+        <v>6.858677624817086</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E7" t="n">
         <v>14221</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14220</v>
+        <v>14221</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581395464135021</v>
+        <v>5.581367941776247</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567964653515936</v>
+        <v>5.567902239225603</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01343081061908412</v>
+        <v>-0.0134657025506421</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167608406475142</v>
+        <v>1.167560101876504</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510714439450444</v>
+        <v>1.510681304579498</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047179801916382</v>
+        <v>0.5047189602998706</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0529190365979183</v>
+        <v>0.05289821584947674</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025694602654009</v>
+        <v>0.5025727063416566</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.028085538334189</v>
+        <v>5.023924958158502</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.167107597525694</v>
+        <v>5.131009512370326</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.33884221402214</v>
+        <v>5.279149586397839</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E8" t="n">
         <v>9019</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9018</v>
+        <v>9019</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878304224883566</v>
+        <v>7.878149185053775</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.1166146528408</v>
+        <v>8.116216790988913</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2383104279572333</v>
+        <v>0.2380676059351385</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446899646588764</v>
+        <v>1.446859691790461</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826434505616604</v>
+        <v>1.826371152193566</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079129063955852</v>
+        <v>0.8079152355268466</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6275019088880953</v>
+        <v>0.6274954645071715</v>
       </c>
       <c r="X8" t="n">
-        <v>0.798003092877048</v>
+        <v>0.7980326802992739</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.046316549131353</v>
+        <v>5.030907038760295</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.313230106453211</v>
+        <v>5.271166854712463</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.472472213413822</v>
+        <v>5.480959127144179</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E9" t="n">
         <v>13884</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13883</v>
+        <v>13884</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613165922351076</v>
+        <v>7.613003637280323</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.65875367318092</v>
+        <v>7.658520693495301</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04558775082984242</v>
+        <v>0.04551705621497807</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49484628354202</v>
+        <v>1.494774672664487</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942789531148375</v>
+        <v>1.94272731389373</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7564908090093488</v>
+        <v>0.756507454123455</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5245017483519698</v>
+        <v>0.524519857936838</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7550829110202868</v>
+        <v>0.7551033009764081</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.328734317343174</v>
+        <v>5.323805309734514</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.518774626805401</v>
+        <v>5.48332354615116</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.689468869349631</v>
+        <v>5.689753837112832</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61785147063127</v>
+        <v>10.61774361978213</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3127897901388941</v>
+        <v>0.3126819392897629</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052241379078954</v>
+        <v>2.052272427864546</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697873759124766</v>
+        <v>2.697915651902522</v>
       </c>
       <c r="V10" t="n">
-        <v>0.356763370945333</v>
+        <v>0.3567751270699397</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1202521355490771</v>
+        <v>-0.1202869265306468</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3362064981549989</v>
+        <v>0.3362346966301496</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.635717162704379</v>
+        <v>9.66369168245034</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.804149781915189</v>
+        <v>9.843434084912268</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.926240185401854</v>
+        <v>10.05135476381224</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E11" t="n">
         <v>13825</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13824</v>
+        <v>13825</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244199182581019</v>
+        <v>5.244094719710668</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578664206642067</v>
+        <v>0.4578318584070797</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217626238040746</v>
+        <v>5.217543352111445</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0265729445402724</v>
+        <v>-0.02655136759922467</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1620620401114</v>
+        <v>1.162040788336431</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483522933579032</v>
+        <v>1.48349500227608</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4290643776081454</v>
+        <v>0.4290896706145981</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09269124464271505</v>
+        <v>-0.09264729708962371</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4272584766900005</v>
+        <v>0.4272840946843733</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.226409594095942</v>
+        <v>4.369734513274336</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.561393486786233</v>
+        <v>4.612937865100457</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.743843173431734</v>
+        <v>4.861773239266062</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E12" t="n">
         <v>4143</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.47852752293578</v>
+        <v>7.477663770214819</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204926937269373</v>
+        <v>2.204920353982301</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.652042106407651</v>
+        <v>7.65144225202088</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735145834718716</v>
+        <v>0.1737784818060594</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9134756515514481</v>
+        <v>0.9136175555507314</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195831326783832</v>
+        <v>1.195925666440055</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8307352370389887</v>
+        <v>0.8307756625022293</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6567980694944564</v>
+        <v>0.6569155544999679</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8289782104625532</v>
+        <v>0.8290051987784066</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.443196238152299</v>
+        <v>4.462914312603409</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.835362442709794</v>
+        <v>4.763045130915099</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.480203607328424</v>
+        <v>5.340778696592125</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E13" t="n">
         <v>6478</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6477</v>
+        <v>6478</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.60878840512583</v>
+        <v>9.608419651126891</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02767847152865</v>
+        <v>10.02724887458725</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4188900664028207</v>
+        <v>0.4188292234603591</v>
       </c>
       <c r="T13" t="n">
-        <v>1.69179776617286</v>
+        <v>1.691614019101161</v>
       </c>
       <c r="U13" t="n">
-        <v>2.151987900322738</v>
+        <v>2.151805885309385</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8230863533196592</v>
+        <v>0.823105695563125</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484580591672223</v>
+        <v>0.6484867618405419</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106176150892088</v>
+        <v>0.8106483848172641</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.396115513717463</v>
+        <v>8.459384193148297</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.471917673578442</v>
+        <v>8.488106266931458</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.495886704374328</v>
+        <v>8.528900204005476</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E14" t="n">
         <v>14065</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14064</v>
+        <v>14065</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130484748293515</v>
+        <v>8.130316210451475</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073923739237393</v>
+        <v>0.9072812192723697</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.200926249857927</v>
+        <v>8.200585625229754</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07044150156441156</v>
+        <v>0.0702694147782799</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757626781046548</v>
+        <v>1.757387003350902</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28346624723425</v>
+        <v>2.283290626291289</v>
       </c>
       <c r="V14" t="n">
-        <v>0.780753308069368</v>
+        <v>0.7807904762494966</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651566255730263</v>
+        <v>0.5652070827052992</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803778261481102</v>
+        <v>0.7804183385710692</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.315944194264254</v>
+        <v>5.294844115431459</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.546837096244948</v>
+        <v>5.751485438432121</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.786240080423604</v>
+        <v>7.166802346691327</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.67909963099631</v>
+        <v>4.678274336283185</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82307869302649</v>
+        <v>11.82294912940108</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1408086900002876</v>
+        <v>-0.1409382536257048</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052139111622562</v>
+        <v>2.052158757602537</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697446238759891</v>
+        <v>2.697467471431551</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949669763873326</v>
+        <v>0.7949700023576437</v>
       </c>
       <c r="W15" t="n">
-        <v>0.609652240464499</v>
+        <v>0.6096460952755334</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862570704159578</v>
+        <v>0.7862687637690471</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.64095782018896</v>
+        <v>11.75409004985291</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.78888834483005</v>
+        <v>11.8190562150858</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89960467978018</v>
+        <v>11.93079680664426</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E16" t="n">
         <v>9828</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9827</v>
+        <v>9828</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.36571323903531</v>
+        <v>8.3654185999186</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624950850720868</v>
+        <v>8.625181414369463</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2592376116855568</v>
+        <v>0.259762814450864</v>
       </c>
       <c r="T16" t="n">
-        <v>3.589200907529671</v>
+        <v>3.589526434132289</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09459172475595</v>
+        <v>11.09425594154507</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04193400479062569</v>
+        <v>0.04190911612651608</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.609557036554393</v>
+        <v>-0.6096054316868011</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02527165789313013</v>
+        <v>0.02524559972853246</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.93633521149583</v>
+        <v>11.83825972872013</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.61442964205227</v>
+        <v>12.52900427942348</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87059962932987</v>
+        <v>12.87077424554081</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E17" t="n">
         <v>2372</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.506674398987769</v>
+        <v>6.505069561551434</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.405114391143911</v>
+        <v>1.404827433628319</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.873869888184253</v>
+        <v>6.872082162662096</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3671954891964839</v>
+        <v>0.367012601110663</v>
       </c>
       <c r="T17" t="n">
-        <v>2.026332016117387</v>
+        <v>2.025595110908379</v>
       </c>
       <c r="U17" t="n">
-        <v>2.559942581670834</v>
+        <v>2.559426106699333</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5283847886976363</v>
+        <v>0.5288501328681406</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03629036366897587</v>
+        <v>0.03713791410168188</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5250198508939766</v>
+        <v>0.5254833937286322</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.729834273005751</v>
+        <v>2.434477637516698</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.804973536354557</v>
+        <v>3.220615243881451</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.354323631531114</v>
+        <v>7.164311987294462</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E18" t="n">
         <v>3231</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3230</v>
+        <v>3231</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.482876625386997</v>
+        <v>6.482114360878984</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.678370222489059</v>
+        <v>6.677540385424092</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1954935971020625</v>
+        <v>0.1954260245451068</v>
       </c>
       <c r="T18" t="n">
-        <v>1.10103941761726</v>
+        <v>1.100728281011795</v>
       </c>
       <c r="U18" t="n">
-        <v>1.488870877527627</v>
+        <v>1.488657455113204</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6034840216097006</v>
+        <v>0.6037724640980108</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2222238580703465</v>
+        <v>0.2227180914755399</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6005309755590503</v>
+        <v>0.6008277028571569</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.293677779338347</v>
+        <v>3.469734243196284</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.252958307223551</v>
+        <v>4.460276624884792</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.854962366077947</v>
+        <v>7.088499725580444</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16683</v>
+        <v>16684</v>
       </c>
       <c r="E19" t="n">
         <v>7185</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7184</v>
+        <v>7185</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34556013363029</v>
+        <v>10.34421350034795</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1343738620298</v>
+        <v>11.13377312853024</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7888137283995118</v>
+        <v>0.7895596281822985</v>
       </c>
       <c r="T19" t="n">
-        <v>2.047556364059985</v>
+        <v>2.048230525776716</v>
       </c>
       <c r="U19" t="n">
-        <v>2.769343793492026</v>
+        <v>2.77031720594002</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7269543019789464</v>
+        <v>0.726961677552431</v>
       </c>
       <c r="W19" t="n">
-        <v>0.470538131030654</v>
+        <v>0.4705683360232533</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6789411663432485</v>
+        <v>0.6788006013552322</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.426667103778476</v>
+        <v>7.423672554398437</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.456258418822868</v>
+        <v>8.388399033181368</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.487302944324107</v>
+        <v>10.43</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.426667103778476</v>
+        <v>7.423672554398437</v>
       </c>
       <c r="G2" t="n">
-        <v>7.456258418822868</v>
+        <v>8.388399033181368</v>
       </c>
       <c r="H2" t="n">
-        <v>7.487302944324107</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.028085538334189</v>
+        <v>5.023924958158502</v>
       </c>
       <c r="G3" t="n">
-        <v>5.167107597525694</v>
+        <v>5.131009512370326</v>
       </c>
       <c r="H3" t="n">
-        <v>5.33884221402214</v>
+        <v>5.279149586397839</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.226409594095942</v>
+        <v>4.369734513274336</v>
       </c>
       <c r="G4" t="n">
-        <v>4.561393486786232</v>
+        <v>4.612937865100457</v>
       </c>
       <c r="H4" t="n">
-        <v>4.743843173431734</v>
+        <v>4.861773239266062</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.93633521149583</v>
+        <v>11.83825972872013</v>
       </c>
       <c r="G5" t="n">
-        <v>12.61442964205227</v>
+        <v>12.52900427942348</v>
       </c>
       <c r="H5" t="n">
-        <v>12.87059962932987</v>
+        <v>12.87077424554081</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.954362705692132</v>
+        <v>2.970173187209827</v>
       </c>
       <c r="G6" t="n">
-        <v>74.71561229467122</v>
+        <v>94.23733977776757</v>
       </c>
       <c r="H6" t="n">
-        <v>111.56</v>
+        <v>110.5615810918087</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.64095782018896</v>
+        <v>11.75409004985291</v>
       </c>
       <c r="G7" t="n">
-        <v>11.78888834483005</v>
+        <v>11.8190562150858</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89960467978018</v>
+        <v>11.93079680664426</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.396115513717463</v>
+        <v>8.459384193148297</v>
       </c>
       <c r="G8" t="n">
-        <v>8.471917673578442</v>
+        <v>8.48810626693146</v>
       </c>
       <c r="H8" t="n">
-        <v>8.495886704374328</v>
+        <v>8.528900204005476</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.443196238152299</v>
+        <v>4.462914312603409</v>
       </c>
       <c r="G9" t="n">
-        <v>4.835362442709794</v>
+        <v>4.763045130915098</v>
       </c>
       <c r="H9" t="n">
-        <v>5.480203607328424</v>
+        <v>5.340778696592125</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.046316549131353</v>
+        <v>5.030907038760295</v>
       </c>
       <c r="G10" t="n">
-        <v>5.313230106453211</v>
+        <v>5.271166854712462</v>
       </c>
       <c r="H10" t="n">
-        <v>5.472472213413822</v>
+        <v>5.480959127144179</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.729834273005751</v>
+        <v>2.434477637516698</v>
       </c>
       <c r="G11" t="n">
-        <v>2.804973536354557</v>
+        <v>3.220615243881451</v>
       </c>
       <c r="H11" t="n">
-        <v>4.354323631531114</v>
+        <v>7.164311987294462</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.315944194264254</v>
+        <v>5.294844115431459</v>
       </c>
       <c r="G12" t="n">
-        <v>5.546837096244948</v>
+        <v>5.751485438432121</v>
       </c>
       <c r="H12" t="n">
-        <v>5.786240080423604</v>
+        <v>7.166802346691327</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.635717162704379</v>
+        <v>9.66369168245034</v>
       </c>
       <c r="G13" t="n">
-        <v>9.804149781915189</v>
+        <v>9.843434084912266</v>
       </c>
       <c r="H13" t="n">
-        <v>9.926240185401854</v>
+        <v>10.05135476381224</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.328734317343174</v>
+        <v>5.323805309734514</v>
       </c>
       <c r="G14" t="n">
-        <v>5.518774626805401</v>
+        <v>5.483323546151159</v>
       </c>
       <c r="H14" t="n">
-        <v>5.689468869349631</v>
+        <v>5.689753837112832</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.696661070007455</v>
+        <v>6.666959093480791</v>
       </c>
       <c r="G15" t="n">
-        <v>6.770374358457618</v>
+        <v>6.740672725808791</v>
       </c>
       <c r="H15" t="n">
-        <v>6.909967462934278</v>
+        <v>6.858677624817086</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.293677779338347</v>
+        <v>3.469734243196284</v>
       </c>
       <c r="G16" t="n">
-        <v>4.252958307223551</v>
+        <v>4.460276624884793</v>
       </c>
       <c r="H16" t="n">
-        <v>5.854962366077947</v>
+        <v>7.088499725580444</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.195413284132842</v>
+        <v>3.239221238938053</v>
       </c>
       <c r="G17" t="n">
-        <v>3.271696290351971</v>
+        <v>3.250858116346647</v>
       </c>
       <c r="H17" t="n">
-        <v>3.523063172662976</v>
+        <v>3.277610619469026</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.26699926199262</v>
+        <v>2.228804326450344</v>
       </c>
       <c r="G18" t="n">
-        <v>2.376744396610848</v>
+        <v>2.364825794050943</v>
       </c>
       <c r="H18" t="n">
-        <v>2.450081180811809</v>
+        <v>2.450363815142576</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>5.092481990352563</v>
+        <v>4.996092600235603</v>
       </c>
       <c r="G19" t="n">
-        <v>5.677957550954441</v>
+        <v>5.730987784150704</v>
       </c>
       <c r="H19" t="n">
-        <v>6.495943920469296</v>
+        <v>6.881269525883063</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E2" t="n">
-        <v>10019</v>
+        <v>10021</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10019</v>
+        <v>10020</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6375245699837</v>
+        <v>102.6277433799069</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.637740905098</v>
+        <v>102.6208305825044</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002163351142485555</v>
+        <v>-0.006912797402435467</v>
       </c>
       <c r="T2" t="n">
-        <v>17.88840142533172</v>
+        <v>17.89332773768761</v>
       </c>
       <c r="U2" t="n">
-        <v>36.06450270281622</v>
+        <v>36.0741817636328</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1388680450003575</v>
+        <v>0.1398716699720201</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.717911883979736</v>
+        <v>-0.7168318767293473</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1388643265631246</v>
+        <v>0.1398693578830493</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.970173187209827</v>
+        <v>3.75422816133342</v>
       </c>
       <c r="Z2" t="n">
-        <v>94.23733977776757</v>
+        <v>97.45926824295944</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.5615810918087</v>
+        <v>108.9652061844723</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E3" t="n">
-        <v>14613</v>
+        <v>14615</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14613</v>
+        <v>14614</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.910088209128858</v>
+        <v>4.909920213493909</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.967429247818525</v>
+        <v>4.967381896011523</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05734103868966731</v>
+        <v>0.0574616825176134</v>
       </c>
       <c r="T3" t="n">
-        <v>1.345110195443517</v>
+        <v>1.345032166624579</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719552005763086</v>
+        <v>1.719498281439026</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812362980142893</v>
+        <v>0.7812369248440363</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5694229882347026</v>
+        <v>0.5694462396237483</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7802112984611337</v>
+        <v>0.7802057721068474</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.228804326450344</v>
+        <v>2.226668268120213</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.364825794050943</v>
+        <v>2.348202936425254</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.450363815142576</v>
+        <v>2.440249939549557</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E4" t="n">
-        <v>10247</v>
+        <v>10249</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10247</v>
+        <v>10248</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.911609739435934</v>
+        <v>6.91131318306011</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.240577255790699</v>
+        <v>7.240661458176894</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3289675163547665</v>
+        <v>0.3293482751167859</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292687022552367</v>
+        <v>1.292801832558539</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682345284134077</v>
+        <v>1.682475963330605</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676600129664125</v>
+        <v>0.8676356391524604</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374920310505539</v>
+        <v>0.7374475564857064</v>
       </c>
       <c r="X4" t="n">
-        <v>0.847289627900915</v>
+        <v>0.8471843283523179</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.239221238938053</v>
+        <v>3.25002947678703</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.250858116346647</v>
+        <v>3.300658756224007</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.277610619469026</v>
+        <v>3.414340592184046</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.759306784660767</v>
+        <v>2.759086219602063</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302970096585515</v>
+        <v>9.302869495181417</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3616675135596847</v>
+        <v>0.3615669121555872</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253851658404295</v>
+        <v>1.253866407511083</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750169671043864</v>
+        <v>1.750168701514172</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661919283286279</v>
+        <v>0.8661948223005264</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213039084407671</v>
+        <v>0.7213042172154709</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8601773712448768</v>
+        <v>0.8601844136982174</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.996092600235603</v>
+        <v>4.874492081613734</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.730987784150704</v>
+        <v>5.545237347922788</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.881269525883063</v>
+        <v>5.83350430433552</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E6" t="n">
-        <v>8860</v>
+        <v>8862</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8860</v>
+        <v>8861</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.73306309255079</v>
+        <v>6.733168265432795</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021155658947484</v>
+        <v>7.021557198765141</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2880925663966936</v>
+        <v>0.2883889333323454</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480194293551444</v>
+        <v>1.480198818158355</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908924779687538</v>
+        <v>1.908896880416282</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3047555024287197</v>
+        <v>0.3046821048850257</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1976372776187734</v>
+        <v>-0.1977031674365752</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2800102551916979</v>
+        <v>0.2799090289266972</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.666959093480791</v>
+        <v>6.624985254488076</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.74067272580879</v>
+        <v>6.728690126382759</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.858677624817086</v>
+        <v>6.813935459880642</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E7" t="n">
-        <v>14221</v>
+        <v>14223</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14221</v>
+        <v>14222</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581367941776247</v>
+        <v>5.581353431303614</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567902239225603</v>
+        <v>5.567941513394746</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0134657025506421</v>
+        <v>-0.01341191790886836</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167560101876504</v>
+        <v>1.167452213765738</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510681304579498</v>
+        <v>1.510604933909503</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047189602998706</v>
+        <v>0.5047193378841559</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05289821584947674</v>
+        <v>0.05292830043726882</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025727063416566</v>
+        <v>0.502570160189747</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.023924958158502</v>
+        <v>5.020227610285811</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.131009512370326</v>
+        <v>5.109070182243091</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.279149586397839</v>
+        <v>5.254048145418816</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E8" t="n">
-        <v>9019</v>
+        <v>9021</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9019</v>
+        <v>9020</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878149185053775</v>
+        <v>7.877970620842571</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116216790988913</v>
+        <v>8.116472489099021</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2380676059351385</v>
+        <v>0.2385018682564483</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446859691790461</v>
+        <v>1.446914007466952</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826371152193566</v>
+        <v>1.826399804648053</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8079152355268466</v>
+        <v>0.8078789726290285</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274954645071715</v>
+        <v>0.6274543845369871</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7980326802992739</v>
+        <v>0.7979395082064384</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.030907038760295</v>
+        <v>4.995519370579172</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.271166854712463</v>
+        <v>5.234534673573055</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.480959127144179</v>
+        <v>5.486466854117576</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E9" t="n">
-        <v>13884</v>
+        <v>13886</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13884</v>
+        <v>13885</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.613003637280323</v>
+        <v>7.612817068779258</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.658520693495301</v>
+        <v>7.658390060174877</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04551705621497807</v>
+        <v>0.04557299139561897</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494774672664487</v>
+        <v>1.494706699622501</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94272731389373</v>
+        <v>1.942660351480504</v>
       </c>
       <c r="V9" t="n">
-        <v>0.756507454123455</v>
+        <v>0.7565147076531242</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524519857936838</v>
+        <v>0.524547211279752</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551033009764081</v>
+        <v>0.7551070175800474</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.323805309734514</v>
+        <v>5.293383935151068</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.48332354615116</v>
+        <v>5.439324214958881</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.689753837112832</v>
+        <v>5.649068802678243</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61774361978213</v>
+        <v>10.61763375807974</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3126819392897629</v>
+        <v>0.3125720775873675</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052272427864546</v>
+        <v>2.052306811872219</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697915651902522</v>
+        <v>2.697959172486559</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567751270699397</v>
+        <v>0.3567868661718981</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1202869265306468</v>
+        <v>-0.1203230699397555</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3362346966301496</v>
+        <v>0.3362632606060501</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.66369168245034</v>
+        <v>9.600906418623643</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.843434084912268</v>
+        <v>9.777343672326253</v>
       </c>
       <c r="AA10" t="n">
-        <v>10.05135476381224</v>
+        <v>9.872562888370343</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E11" t="n">
-        <v>13825</v>
+        <v>13827</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13825</v>
+        <v>13826</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244094719710668</v>
+        <v>5.244008896282367</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578318584070797</v>
+        <v>0.4578769344141489</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217543352111445</v>
+        <v>5.21747177908374</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02655136759922467</v>
+        <v>-0.02653711719862643</v>
       </c>
       <c r="T11" t="n">
-        <v>1.162040788336431</v>
+        <v>1.16196482176163</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48349500227608</v>
+        <v>1.483425234198247</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4290896706145981</v>
+        <v>0.4291167074635002</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09264729708962371</v>
+        <v>-0.09256810154295958</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4272840946843733</v>
+        <v>0.4273090294201444</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.369734513274336</v>
+        <v>4.258324351327943</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.612937865100457</v>
+        <v>4.487697435961249</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.861773239266062</v>
+        <v>4.649358879882093</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E12" t="n">
-        <v>4143</v>
+        <v>4145</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4143</v>
+        <v>4144</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.477663770214819</v>
+        <v>7.476800434362935</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204920353982301</v>
+        <v>2.204966838614591</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.65144225202088</v>
+        <v>7.65050597219258</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1737784818060594</v>
+        <v>0.1737055378296452</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136175555507314</v>
+        <v>0.9136576290594484</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195925666440055</v>
+        <v>1.195865501186449</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8307756625022293</v>
+        <v>0.8308807024768355</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6569155544999679</v>
+        <v>0.6571213175214929</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8290051987784066</v>
+        <v>0.8291118765026096</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.462914312603409</v>
+        <v>4.399197777002549</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.763045130915099</v>
+        <v>4.629851885777078</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.340778696592125</v>
+        <v>5.102303994743625</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E13" t="n">
-        <v>6478</v>
+        <v>6480</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6478</v>
+        <v>6479</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.608419651126891</v>
+        <v>9.607988501311931</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02724887458725</v>
+        <v>10.02745350683425</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4188292234603591</v>
+        <v>0.4194650055223219</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691614019101161</v>
+        <v>1.691723770058798</v>
       </c>
       <c r="U13" t="n">
-        <v>2.151805885309385</v>
+        <v>2.151676425101453</v>
       </c>
       <c r="V13" t="n">
-        <v>0.823105695563125</v>
+        <v>0.8231082373653731</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6484867618405419</v>
+        <v>0.6485068054119651</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8106483848172641</v>
+        <v>0.8105734160883595</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.459384193148297</v>
+        <v>8.468796912118728</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.488106266931458</v>
+        <v>8.486597068678746</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.528900204005476</v>
+        <v>8.509387696942008</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E14" t="n">
-        <v>14065</v>
+        <v>14067</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14065</v>
+        <v>14066</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130316210451475</v>
+        <v>8.130124768946395</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9072812192723697</v>
+        <v>0.9074404323262097</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.200585625229754</v>
+        <v>8.20059681636873</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0702694147782799</v>
+        <v>0.07047204742233372</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757387003350902</v>
+        <v>1.757394786445525</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283290626291289</v>
+        <v>2.28330612538888</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807904762494966</v>
+        <v>0.7807665588614311</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652070827052992</v>
+        <v>0.5651888901575897</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804183385710692</v>
+        <v>0.7803902322920511</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.294844115431459</v>
+        <v>5.279949121872268</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.751485438432121</v>
+        <v>5.426729346667422</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.166802346691327</v>
+        <v>5.611439098852511</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.678274336283185</v>
+        <v>4.677450257921887</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82294912940108</v>
+        <v>11.82281051622497</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1409382536257048</v>
+        <v>-0.1410768668018126</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052158757602537</v>
+        <v>2.052192090631159</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697467471431551</v>
+        <v>2.69748716270927</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949700023576437</v>
+        <v>0.7949730704890277</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096460952755334</v>
+        <v>0.6096403961556859</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862687637690471</v>
+        <v>0.7862799689564134</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.75409004985291</v>
+        <v>11.7347444995811</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.8190562150858</v>
+        <v>11.80819981884571</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.93079680664426</v>
+        <v>11.89671306158439</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E16" t="n">
-        <v>9828</v>
+        <v>9830</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9828</v>
+        <v>9829</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.3654185999186</v>
+        <v>8.365120459863668</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.625181414369463</v>
+        <v>8.624780069840156</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.259762814450864</v>
+        <v>0.2596596099764881</v>
       </c>
       <c r="T16" t="n">
-        <v>3.589526434132289</v>
+        <v>3.590128847900532</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09425594154507</v>
+        <v>11.09398163908368</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04190911612651608</v>
+        <v>0.04186546366191744</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6096054316868011</v>
+        <v>-0.6096712167682823</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02524559972853246</v>
+        <v>0.02520241686508495</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.83825972872013</v>
+        <v>11.73570997203814</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.52900427942348</v>
+        <v>12.38425605539324</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.87077424554081</v>
+        <v>12.86995282734599</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E17" t="n">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.505069561551434</v>
+        <v>6.503459755583649</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.404827433628319</v>
+        <v>1.40874134119381</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.872082162662096</v>
+        <v>6.869647628238305</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.367012601110663</v>
+        <v>0.3661878726546555</v>
       </c>
       <c r="T17" t="n">
-        <v>2.025595110908379</v>
+        <v>2.024245413541365</v>
       </c>
       <c r="U17" t="n">
-        <v>2.559426106699333</v>
+        <v>2.558564976008614</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5288501328681406</v>
+        <v>0.5295239059235123</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03713791410168188</v>
+        <v>0.03824940160045653</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5254833937286322</v>
+        <v>0.5261650612116124</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.434477637516698</v>
+        <v>1.525950122690794</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.220615243881451</v>
+        <v>2.722261779257232</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.164311987294462</v>
+        <v>3.124254060781789</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E18" t="n">
-        <v>3231</v>
+        <v>3233</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3231</v>
+        <v>3232</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.482114360878984</v>
+        <v>6.481385055693068</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.677540385424092</v>
+        <v>6.676653910506</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1954260245451068</v>
+        <v>0.1952688548129312</v>
       </c>
       <c r="T18" t="n">
-        <v>1.100728281011795</v>
+        <v>1.100318810640692</v>
       </c>
       <c r="U18" t="n">
-        <v>1.488657455113204</v>
+        <v>1.488277919703503</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6037724640980108</v>
+        <v>0.6040978121138578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2227180914755399</v>
+        <v>0.2233419876529619</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6008277028571569</v>
+        <v>0.6011558840362753</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.469734243196284</v>
+        <v>2.265646008353458</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.460276624884792</v>
+        <v>3.943975158749276</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.088499725580444</v>
+        <v>4.766630719620615</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16684</v>
+        <v>16685</v>
       </c>
       <c r="E19" t="n">
-        <v>7185</v>
+        <v>7187</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7185</v>
+        <v>7186</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34421350034795</v>
+        <v>10.34285993598664</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13377312853024</v>
+        <v>11.13259761166621</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7895596281822985</v>
+        <v>0.78973767567957</v>
       </c>
       <c r="T19" t="n">
-        <v>2.048230525776716</v>
+        <v>2.048857926782373</v>
       </c>
       <c r="U19" t="n">
-        <v>2.77031720594002</v>
+        <v>2.771193247318666</v>
       </c>
       <c r="V19" t="n">
-        <v>0.726961677552431</v>
+        <v>0.7269904283104949</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4705683360232533</v>
+        <v>0.4706404928628181</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6788006013552322</v>
+        <v>0.6787999344094253</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.423672554398437</v>
+        <v>7.426517720379465</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.388399033181368</v>
+        <v>7.447580992961656</v>
       </c>
       <c r="AA19" t="n">
-        <v>10.43</v>
+        <v>7.470658442015038</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.423672554398437</v>
+        <v>7.426517720379465</v>
       </c>
       <c r="G2" t="n">
-        <v>8.388399033181368</v>
+        <v>7.447580992961657</v>
       </c>
       <c r="H2" t="n">
-        <v>10.43</v>
+        <v>7.470658442015038</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.023924958158502</v>
+        <v>5.020227610285811</v>
       </c>
       <c r="G3" t="n">
-        <v>5.131009512370326</v>
+        <v>5.109070182243091</v>
       </c>
       <c r="H3" t="n">
-        <v>5.279149586397839</v>
+        <v>5.254048145418816</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.369734513274336</v>
+        <v>4.258324351327943</v>
       </c>
       <c r="G4" t="n">
-        <v>4.612937865100457</v>
+        <v>4.487697435961249</v>
       </c>
       <c r="H4" t="n">
-        <v>4.861773239266062</v>
+        <v>4.649358879882093</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.83825972872013</v>
+        <v>11.73570997203814</v>
       </c>
       <c r="G5" t="n">
-        <v>12.52900427942348</v>
+        <v>12.38425605539324</v>
       </c>
       <c r="H5" t="n">
-        <v>12.87077424554081</v>
+        <v>12.86995282734599</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.970173187209827</v>
+        <v>3.75422816133342</v>
       </c>
       <c r="G6" t="n">
-        <v>94.23733977776757</v>
+        <v>97.45926824295944</v>
       </c>
       <c r="H6" t="n">
-        <v>110.5615810918087</v>
+        <v>108.9652061844723</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.75409004985291</v>
+        <v>11.7347444995811</v>
       </c>
       <c r="G7" t="n">
-        <v>11.8190562150858</v>
+        <v>11.80819981884571</v>
       </c>
       <c r="H7" t="n">
-        <v>11.93079680664426</v>
+        <v>11.89671306158439</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.459384193148297</v>
+        <v>8.468796912118728</v>
       </c>
       <c r="G8" t="n">
-        <v>8.48810626693146</v>
+        <v>8.486597068678748</v>
       </c>
       <c r="H8" t="n">
-        <v>8.528900204005476</v>
+        <v>8.509387696942008</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.462914312603409</v>
+        <v>4.399197777002549</v>
       </c>
       <c r="G9" t="n">
-        <v>4.763045130915098</v>
+        <v>4.629851885777079</v>
       </c>
       <c r="H9" t="n">
-        <v>5.340778696592125</v>
+        <v>5.102303994743625</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.030907038760295</v>
+        <v>4.995519370579172</v>
       </c>
       <c r="G10" t="n">
-        <v>5.271166854712462</v>
+        <v>5.234534673573054</v>
       </c>
       <c r="H10" t="n">
-        <v>5.480959127144179</v>
+        <v>5.486466854117576</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2.434477637516698</v>
+        <v>1.525950122690794</v>
       </c>
       <c r="G11" t="n">
-        <v>3.220615243881451</v>
+        <v>2.722261779257232</v>
       </c>
       <c r="H11" t="n">
-        <v>7.164311987294462</v>
+        <v>3.124254060781789</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.294844115431459</v>
+        <v>5.279949121872268</v>
       </c>
       <c r="G12" t="n">
-        <v>5.751485438432121</v>
+        <v>5.426729346667422</v>
       </c>
       <c r="H12" t="n">
-        <v>7.166802346691327</v>
+        <v>5.611439098852511</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.66369168245034</v>
+        <v>9.600906418623643</v>
       </c>
       <c r="G13" t="n">
-        <v>9.843434084912266</v>
+        <v>9.777343672326253</v>
       </c>
       <c r="H13" t="n">
-        <v>10.05135476381224</v>
+        <v>9.872562888370343</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.323805309734514</v>
+        <v>5.293383935151068</v>
       </c>
       <c r="G14" t="n">
-        <v>5.483323546151159</v>
+        <v>5.439324214958881</v>
       </c>
       <c r="H14" t="n">
-        <v>5.689753837112832</v>
+        <v>5.649068802678243</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.666959093480791</v>
+        <v>6.624985254488076</v>
       </c>
       <c r="G15" t="n">
-        <v>6.740672725808791</v>
+        <v>6.728690126382759</v>
       </c>
       <c r="H15" t="n">
-        <v>6.858677624817086</v>
+        <v>6.813935459880642</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>3.469734243196284</v>
+        <v>2.265646008353458</v>
       </c>
       <c r="G16" t="n">
-        <v>4.460276624884793</v>
+        <v>3.943975158749276</v>
       </c>
       <c r="H16" t="n">
-        <v>7.088499725580444</v>
+        <v>4.766630719620615</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.239221238938053</v>
+        <v>3.25002947678703</v>
       </c>
       <c r="G17" t="n">
-        <v>3.250858116346647</v>
+        <v>3.300658756224007</v>
       </c>
       <c r="H17" t="n">
-        <v>3.277610619469026</v>
+        <v>3.414340592184046</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.228804326450344</v>
+        <v>2.226668268120213</v>
       </c>
       <c r="G18" t="n">
-        <v>2.364825794050943</v>
+        <v>2.348202936425254</v>
       </c>
       <c r="H18" t="n">
-        <v>2.450363815142576</v>
+        <v>2.440249939549557</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>4.996092600235603</v>
+        <v>4.874492081613734</v>
       </c>
       <c r="G19" t="n">
-        <v>5.730987784150704</v>
+        <v>5.545237347922788</v>
       </c>
       <c r="H19" t="n">
-        <v>6.881269525883063</v>
+        <v>5.83350430433552</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -576,7 +576,7 @@
         <v>16685</v>
       </c>
       <c r="E2" t="n">
-        <v>10021</v>
+        <v>10022</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6208305825044</v>
+        <v>102.6101748341305</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.006912797402435467</v>
+        <v>-0.01756854577632006</v>
       </c>
       <c r="T2" t="n">
-        <v>17.89332773768761</v>
+        <v>17.90372909413183</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0741817636328</v>
+        <v>36.08139943141293</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1398716699720201</v>
+        <v>0.1399938465882483</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7168318767293473</v>
+        <v>-0.7175189477121506</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1398693578830493</v>
+        <v>0.1399926053583457</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.75422816133342</v>
+        <v>3.769856802117444</v>
       </c>
       <c r="Z2" t="n">
-        <v>97.45926824295944</v>
+        <v>97.44892879912864</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.9652061844723</v>
+        <v>108.9638433558469</v>
       </c>
     </row>
     <row r="3">
@@ -665,7 +665,7 @@
         <v>16685</v>
       </c>
       <c r="E3" t="n">
-        <v>14615</v>
+        <v>14616</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.967381896011523</v>
+        <v>4.967456304218857</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0574616825176134</v>
+        <v>0.05753609072494714</v>
       </c>
       <c r="T3" t="n">
-        <v>1.345032166624579</v>
+        <v>1.345047260277852</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719498281439026</v>
+        <v>1.719503971463945</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812369248440363</v>
+        <v>0.7812280883843278</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5694462396237483</v>
+        <v>0.5694433901115322</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7802057721068474</v>
+        <v>0.7801930001979087</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.226668268120213</v>
+        <v>2.226167104485544</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.348202936425254</v>
+        <v>2.347711652943616</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.440249939549557</v>
+        <v>2.439721648622689</v>
       </c>
     </row>
     <row r="4">
@@ -754,7 +754,7 @@
         <v>16685</v>
       </c>
       <c r="E4" t="n">
-        <v>10249</v>
+        <v>10250</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.240661458176894</v>
+        <v>7.240901839312547</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3293482751167859</v>
+        <v>0.3295886562524381</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292801832558539</v>
+        <v>1.29287414123771</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682475963330605</v>
+        <v>1.682549020066435</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676356391524604</v>
+        <v>0.8676228379992954</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374475564857064</v>
+        <v>0.7374247548036968</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471843283523179</v>
+        <v>0.8471194542280746</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.25002947678703</v>
+        <v>3.251550478997789</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.300658756224007</v>
+        <v>3.307057511629658</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.414340592184046</v>
+        <v>3.421500854462202</v>
       </c>
     </row>
     <row r="5">
@@ -932,7 +932,7 @@
         <v>16685</v>
       </c>
       <c r="E6" t="n">
-        <v>8862</v>
+        <v>8863</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021557198765141</v>
+        <v>7.021789937337237</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2883889333323454</v>
+        <v>0.2886216719044422</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480198818158355</v>
+        <v>1.480210335497951</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908896880416282</v>
+        <v>1.908911926566164</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3046821048850257</v>
+        <v>0.30465419159114</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977031674365752</v>
+        <v>-0.1977220483856472</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2799090289266972</v>
+        <v>0.2798625217827065</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.624985254488076</v>
+        <v>6.637357986904973</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.728690126382759</v>
+        <v>6.731800622264613</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.813935459880642</v>
+        <v>6.816162292410292</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
         <v>16685</v>
       </c>
       <c r="E7" t="n">
-        <v>14223</v>
+        <v>14224</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567941513394746</v>
+        <v>5.567970591723348</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01341191790886836</v>
+        <v>-0.01338283958026545</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167452213765738</v>
+        <v>1.1674201177987</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510604933909503</v>
+        <v>1.510577685590904</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047193378841559</v>
+        <v>0.5047249699079408</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05292830043726882</v>
+        <v>0.05296246672135985</v>
       </c>
       <c r="X7" t="n">
-        <v>0.502570160189747</v>
+        <v>0.5025734078023709</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.020227610285811</v>
+        <v>5.025068858307571</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.109070182243091</v>
+        <v>5.108633786556211</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.254048145418816</v>
+        <v>5.249935980103169</v>
       </c>
     </row>
     <row r="8">
@@ -1110,7 +1110,7 @@
         <v>16685</v>
       </c>
       <c r="E8" t="n">
-        <v>9021</v>
+        <v>9022</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116472489099021</v>
+        <v>8.116793320530141</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2385018682564483</v>
+        <v>0.2388226996875703</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446914007466952</v>
+        <v>1.446972475466501</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826399804648053</v>
+        <v>1.826457079099295</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078789726290285</v>
+        <v>0.8078563341255417</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274543845369871</v>
+        <v>0.6274310186997866</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7979395082064384</v>
+        <v>0.7978757677560413</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.995519370579172</v>
+        <v>5.004249533497303</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.234534673573055</v>
+        <v>5.241923509467554</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.486466854117576</v>
+        <v>5.494680127851285</v>
       </c>
     </row>
     <row r="9">
@@ -1199,7 +1199,7 @@
         <v>16685</v>
       </c>
       <c r="E9" t="n">
-        <v>13886</v>
+        <v>13887</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.658390060174877</v>
+        <v>7.658428209928556</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04557299139561897</v>
+        <v>0.04561114114929854</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494706699622501</v>
+        <v>1.494695588667584</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942660351480504</v>
+        <v>1.942654606847102</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565147076531242</v>
+        <v>0.7565107728650059</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524547211279752</v>
+        <v>0.524550023194795</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551070175800474</v>
+        <v>0.7551003705456798</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.293383935151068</v>
+        <v>5.292574797347089</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.439324214958881</v>
+        <v>5.438524135537802</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.649068802678243</v>
+        <v>5.648186932197633</v>
       </c>
     </row>
     <row r="10">
@@ -1377,7 +1377,7 @@
         <v>16685</v>
       </c>
       <c r="E11" t="n">
-        <v>13827</v>
+        <v>13828</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
@@ -1412,40 +1412,40 @@
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578769344141489</v>
+        <v>0.4579167280766397</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21747177908374</v>
+        <v>5.217444562202032</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02653711719862643</v>
+        <v>-0.02656433408033455</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16196482176163</v>
+        <v>1.161949853281922</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483425234198247</v>
+        <v>1.483410629938707</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4291167074635002</v>
+        <v>0.4291286892860851</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09256810154295958</v>
+        <v>-0.09254658907410285</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4273090294201444</v>
+        <v>0.4273209763770759</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.258324351327943</v>
+        <v>4.257832691184758</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.487697435961249</v>
+        <v>4.486911191916347</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.649358879882093</v>
+        <v>4.649027266028003</v>
       </c>
     </row>
     <row r="12">
@@ -1466,7 +1466,7 @@
         <v>16685</v>
       </c>
       <c r="E12" t="n">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
@@ -1501,40 +1501,40 @@
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204966838614591</v>
+        <v>2.204993367722918</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.65050597219258</v>
+        <v>7.650315054484551</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1737055378296452</v>
+        <v>0.1735146201216171</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136576290594484</v>
+        <v>0.9136152495095385</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195865501186449</v>
+        <v>1.195824576354346</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8308807024768355</v>
+        <v>0.8309058298067176</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6571213175214929</v>
+        <v>0.6571447850642773</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8291118765026096</v>
+        <v>0.8291461875594424</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.399197777002549</v>
+        <v>4.39198534439013</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.629851885777078</v>
+        <v>4.62529131326057</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.102303994743625</v>
+        <v>5.098941579707359</v>
       </c>
     </row>
     <row r="13">
@@ -1555,7 +1555,7 @@
         <v>16685</v>
       </c>
       <c r="E13" t="n">
-        <v>6480</v>
+        <v>6481</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02745350683425</v>
+        <v>10.02776696884247</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4194650055223219</v>
+        <v>0.4197784675305431</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691723770058798</v>
+        <v>1.691813880156576</v>
       </c>
       <c r="U13" t="n">
-        <v>2.151676425101453</v>
+        <v>2.151651361748171</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231082373653731</v>
+        <v>0.8231061015192128</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485068054119651</v>
+        <v>0.6485149939543511</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8105734160883595</v>
+        <v>0.8105286124338469</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.468796912118728</v>
+        <v>8.468263701524364</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.486597068678746</v>
+        <v>8.486139727112491</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.509387696942008</v>
+        <v>8.508730144233402</v>
       </c>
     </row>
     <row r="14">
@@ -1644,7 +1644,7 @@
         <v>16685</v>
       </c>
       <c r="E14" t="n">
-        <v>14067</v>
+        <v>14068</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
@@ -1679,40 +1679,40 @@
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9074404323262097</v>
+        <v>0.907575534266765</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.20059681636873</v>
+        <v>8.200747290471618</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07047204742233372</v>
+        <v>0.07062252152522085</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757394786445525</v>
+        <v>1.757482057603595</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28330612538888</v>
+        <v>2.283380114898333</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807665588614311</v>
+        <v>0.7807407590105108</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651888901575897</v>
+        <v>0.5651607099835732</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803902322920511</v>
+        <v>0.7803611939858556</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.279949121872268</v>
+        <v>5.278864846891866</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.426729346667422</v>
+        <v>5.422517319752226</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.611439098852511</v>
+        <v>5.609728918833561</v>
       </c>
     </row>
     <row r="15">
@@ -1822,7 +1822,7 @@
         <v>16685</v>
       </c>
       <c r="E16" t="n">
-        <v>9830</v>
+        <v>9831</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624780069840156</v>
+        <v>8.624474441455252</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2596596099764881</v>
+        <v>0.2593539815915828</v>
       </c>
       <c r="T16" t="n">
-        <v>3.590128847900532</v>
+        <v>3.590249814311195</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09398163908368</v>
+        <v>11.09400876879166</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04186546366191744</v>
+        <v>0.04185642181653586</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6096712167682823</v>
+        <v>-0.6096790894987156</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02520241686508495</v>
+        <v>0.02519411912302361</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.73570997203814</v>
+        <v>11.73516444086846</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.38425605539324</v>
+        <v>12.38347540660107</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.86995282734599</v>
+        <v>12.86967193946729</v>
       </c>
     </row>
     <row r="17">
@@ -1911,7 +1911,7 @@
         <v>16685</v>
       </c>
       <c r="E17" t="n">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
@@ -1946,40 +1946,40 @@
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.40874134119381</v>
+        <v>1.410841562269713</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.869647628238305</v>
+        <v>6.869337494366117</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3661878726546555</v>
+        <v>0.365877738782467</v>
       </c>
       <c r="T17" t="n">
-        <v>2.024245413541365</v>
+        <v>2.023996089361611</v>
       </c>
       <c r="U17" t="n">
-        <v>2.558564976008614</v>
+        <v>2.558406137030202</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5295239059235123</v>
+        <v>0.5296221532443053</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03824940160045653</v>
+        <v>0.03836881130245173</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5261650612116124</v>
+        <v>0.5262679743752965</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.525950122690794</v>
+        <v>1.52745787735759</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.722261779257232</v>
+        <v>2.716250765032647</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.124254060781789</v>
+        <v>3.11522600763089</v>
       </c>
     </row>
     <row r="18">
@@ -2000,7 +2000,7 @@
         <v>16685</v>
       </c>
       <c r="E18" t="n">
-        <v>3233</v>
+        <v>3234</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.676653910506</v>
+        <v>6.676608519491677</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1952688548129312</v>
+        <v>0.1952234637986087</v>
       </c>
       <c r="T18" t="n">
-        <v>1.100318810640692</v>
+        <v>1.100254057928317</v>
       </c>
       <c r="U18" t="n">
-        <v>1.488277919703503</v>
+        <v>1.48820591867806</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6040978121138578</v>
+        <v>0.6041245752433848</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2233419876529619</v>
+        <v>0.2234171333228576</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6011558840362753</v>
+        <v>0.6011806698686606</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.265646008353458</v>
+        <v>2.266529627088542</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.943975158749276</v>
+        <v>3.942825179461268</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.766630719620615</v>
+        <v>4.764442370951057</v>
       </c>
     </row>
     <row r="19">
@@ -2089,7 +2089,7 @@
         <v>16685</v>
       </c>
       <c r="E19" t="n">
-        <v>7187</v>
+        <v>7188</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13259761166621</v>
+        <v>11.13231216533586</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.78973767567957</v>
+        <v>0.78945222934922</v>
       </c>
       <c r="T19" t="n">
-        <v>2.048857926782373</v>
+        <v>2.048838188039506</v>
       </c>
       <c r="U19" t="n">
-        <v>2.771193247318666</v>
+        <v>2.771140719736681</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7269904283104949</v>
+        <v>0.7270006919428205</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4706404928628181</v>
+        <v>0.4706605605440658</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6787999344094253</v>
+        <v>0.6788699689981009</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.426517720379465</v>
+        <v>7.426173774613734</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.447580992961656</v>
+        <v>7.44677307849328</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.470658442015038</v>
+        <v>7.469728986617255</v>
       </c>
     </row>
   </sheetData>
@@ -2235,13 +2235,13 @@
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.426517720379465</v>
+        <v>7.426173774613734</v>
       </c>
       <c r="G2" t="n">
-        <v>7.447580992961657</v>
+        <v>7.44677307849328</v>
       </c>
       <c r="H2" t="n">
-        <v>7.470658442015038</v>
+        <v>7.469728986617255</v>
       </c>
     </row>
     <row r="3">
@@ -2263,13 +2263,13 @@
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.020227610285811</v>
+        <v>5.025068858307571</v>
       </c>
       <c r="G3" t="n">
-        <v>5.109070182243091</v>
+        <v>5.108633786556211</v>
       </c>
       <c r="H3" t="n">
-        <v>5.254048145418816</v>
+        <v>5.249935980103169</v>
       </c>
     </row>
     <row r="4">
@@ -2291,13 +2291,13 @@
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.258324351327943</v>
+        <v>4.257832691184758</v>
       </c>
       <c r="G4" t="n">
-        <v>4.487697435961249</v>
+        <v>4.486911191916347</v>
       </c>
       <c r="H4" t="n">
-        <v>4.649358879882093</v>
+        <v>4.649027266028003</v>
       </c>
     </row>
     <row r="5">
@@ -2319,13 +2319,13 @@
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.73570997203814</v>
+        <v>11.73516444086846</v>
       </c>
       <c r="G5" t="n">
-        <v>12.38425605539324</v>
+        <v>12.38347540660108</v>
       </c>
       <c r="H5" t="n">
-        <v>12.86995282734599</v>
+        <v>12.86967193946729</v>
       </c>
     </row>
     <row r="6">
@@ -2347,13 +2347,13 @@
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.75422816133342</v>
+        <v>3.769856802117444</v>
       </c>
       <c r="G6" t="n">
-        <v>97.45926824295944</v>
+        <v>97.44892879912862</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9652061844723</v>
+        <v>108.9638433558469</v>
       </c>
     </row>
     <row r="7">
@@ -2403,13 +2403,13 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.468796912118728</v>
+        <v>8.468263701524364</v>
       </c>
       <c r="G8" t="n">
-        <v>8.486597068678748</v>
+        <v>8.486139727112491</v>
       </c>
       <c r="H8" t="n">
-        <v>8.509387696942008</v>
+        <v>8.508730144233402</v>
       </c>
     </row>
     <row r="9">
@@ -2431,13 +2431,13 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.399197777002549</v>
+        <v>4.39198534439013</v>
       </c>
       <c r="G9" t="n">
-        <v>4.629851885777079</v>
+        <v>4.62529131326057</v>
       </c>
       <c r="H9" t="n">
-        <v>5.102303994743625</v>
+        <v>5.098941579707359</v>
       </c>
     </row>
     <row r="10">
@@ -2459,13 +2459,13 @@
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.995519370579172</v>
+        <v>5.004249533497303</v>
       </c>
       <c r="G10" t="n">
-        <v>5.234534673573054</v>
+        <v>5.241923509467553</v>
       </c>
       <c r="H10" t="n">
-        <v>5.486466854117576</v>
+        <v>5.494680127851285</v>
       </c>
     </row>
     <row r="11">
@@ -2487,13 +2487,13 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.525950122690794</v>
+        <v>1.52745787735759</v>
       </c>
       <c r="G11" t="n">
-        <v>2.722261779257232</v>
+        <v>2.716250765032647</v>
       </c>
       <c r="H11" t="n">
-        <v>3.124254060781789</v>
+        <v>3.11522600763089</v>
       </c>
     </row>
     <row r="12">
@@ -2515,13 +2515,13 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.279949121872268</v>
+        <v>5.278864846891866</v>
       </c>
       <c r="G12" t="n">
-        <v>5.426729346667422</v>
+        <v>5.422517319752226</v>
       </c>
       <c r="H12" t="n">
-        <v>5.611439098852511</v>
+        <v>5.609728918833561</v>
       </c>
     </row>
     <row r="13">
@@ -2571,13 +2571,13 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.293383935151068</v>
+        <v>5.292574797347089</v>
       </c>
       <c r="G14" t="n">
-        <v>5.439324214958881</v>
+        <v>5.438524135537802</v>
       </c>
       <c r="H14" t="n">
-        <v>5.649068802678243</v>
+        <v>5.648186932197633</v>
       </c>
     </row>
     <row r="15">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.624985254488076</v>
+        <v>6.637357986904973</v>
       </c>
       <c r="G15" t="n">
-        <v>6.728690126382759</v>
+        <v>6.731800622264612</v>
       </c>
       <c r="H15" t="n">
-        <v>6.813935459880642</v>
+        <v>6.816162292410292</v>
       </c>
     </row>
     <row r="16">
@@ -2627,13 +2627,13 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.265646008353458</v>
+        <v>2.266529627088542</v>
       </c>
       <c r="G16" t="n">
-        <v>3.943975158749276</v>
+        <v>3.942825179461268</v>
       </c>
       <c r="H16" t="n">
-        <v>4.766630719620615</v>
+        <v>4.764442370951057</v>
       </c>
     </row>
     <row r="17">
@@ -2655,13 +2655,13 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.25002947678703</v>
+        <v>3.251550478997789</v>
       </c>
       <c r="G17" t="n">
-        <v>3.300658756224007</v>
+        <v>3.307057511629658</v>
       </c>
       <c r="H17" t="n">
-        <v>3.414340592184046</v>
+        <v>3.421500854462202</v>
       </c>
     </row>
     <row r="18">
@@ -2683,13 +2683,13 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.226668268120213</v>
+        <v>2.226167104485544</v>
       </c>
       <c r="G18" t="n">
-        <v>2.348202936425254</v>
+        <v>2.347711652943616</v>
       </c>
       <c r="H18" t="n">
-        <v>2.440249939549557</v>
+        <v>2.439721648622689</v>
       </c>
     </row>
     <row r="19">

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E2" t="n">
         <v>10022</v>
@@ -582,7 +582,7 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10020</v>
+        <v>10022</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6277433799069</v>
+        <v>102.6081299807091</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6101748341305</v>
+        <v>102.6026761730889</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01756854577632006</v>
+        <v>-0.005453807620190749</v>
       </c>
       <c r="T2" t="n">
-        <v>17.90372909413183</v>
+        <v>17.88840241485032</v>
       </c>
       <c r="U2" t="n">
-        <v>36.08139943141293</v>
+        <v>36.0684221698123</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1399938465882483</v>
+        <v>0.142104735607799</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7175189477121506</v>
+        <v>-0.7122717715266358</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1399926053583457</v>
+        <v>0.1421022767928583</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.769856802117444</v>
+        <v>2.916586825617892</v>
       </c>
       <c r="Z2" t="n">
-        <v>97.44892879912864</v>
+        <v>55.91525830458848</v>
       </c>
       <c r="AA2" t="n">
-        <v>108.9638433558469</v>
+        <v>110.4041525034457</v>
       </c>
     </row>
     <row r="3">
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E3" t="n">
         <v>14616</v>
@@ -671,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14614</v>
+        <v>14616</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.909920213493909</v>
+        <v>4.909556410782703</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.967456304218857</v>
+        <v>4.966980822301371</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05753609072494714</v>
+        <v>0.0574244115186674</v>
       </c>
       <c r="T3" t="n">
-        <v>1.345047260277852</v>
+        <v>1.344872572390505</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719503971463945</v>
+        <v>1.719378648397252</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812280883843278</v>
+        <v>0.7812717933175565</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5694433901115322</v>
+        <v>0.5695078902933919</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7801930001979087</v>
+        <v>0.7802423363719371</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.226167104485544</v>
+        <v>2.217566225165563</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.347711652943616</v>
+        <v>2.304403060109094</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.439721648622689</v>
+        <v>2.439635148393426</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E4" t="n">
         <v>10250</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10248</v>
+        <v>10250</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.91131318306011</v>
+        <v>6.910700487804878</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.240901839312547</v>
+        <v>7.239960430762789</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295886562524381</v>
+        <v>0.3292599429579107</v>
       </c>
       <c r="T4" t="n">
-        <v>1.29287414123771</v>
+        <v>1.292656574486361</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682549020066435</v>
+        <v>1.682348744402725</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676228379992954</v>
+        <v>0.8676541608458425</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374247548036968</v>
+        <v>0.7374828853381401</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471194542280746</v>
+        <v>0.8472157507706407</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.251550478997789</v>
+        <v>3.198107335644316</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.307057511629658</v>
+        <v>3.293696536909429</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.421500854462202</v>
+        <v>3.372869757174393</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.759086219602063</v>
+        <v>2.758646063281825</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302869495181417</v>
+        <v>9.302649539648822</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3615669121555872</v>
+        <v>0.3613469566229915</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253866407511083</v>
+        <v>1.253914136021931</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750168701514172</v>
+        <v>1.750182622566772</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661948223005264</v>
+        <v>0.8661983110732562</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7213042172154709</v>
+        <v>0.7212997836382069</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8601844136982174</v>
+        <v>0.860196993068584</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.874492081613734</v>
+        <v>4.896992042626673</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.545237347922788</v>
+        <v>5.364606427688901</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.83350430433552</v>
+        <v>5.806240660273916</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E6" t="n">
         <v>8863</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8861</v>
+        <v>8863</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733168265432795</v>
+        <v>6.733400823648878</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021789937337237</v>
+        <v>7.021661041114544</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2886216719044422</v>
+        <v>0.2882602174656666</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480210335497951</v>
+        <v>1.480123101713638</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908911926566164</v>
+        <v>1.908787107188363</v>
       </c>
       <c r="V6" t="n">
-        <v>0.30465419159114</v>
+        <v>0.3046358448472594</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977220483856472</v>
+        <v>-0.1977413168303059</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2798625217827065</v>
+        <v>0.2798613613927535</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.637357986904973</v>
+        <v>6.486446346278253</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.731800622264613</v>
+        <v>6.665571928695377</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.816162292410292</v>
+        <v>6.747839699821181</v>
       </c>
     </row>
     <row r="7">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E7" t="n">
         <v>14224</v>
@@ -1027,7 +1027,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14222</v>
+        <v>14224</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581353431303614</v>
+        <v>5.581293131327334</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567970591723348</v>
+        <v>5.56783438236113</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01338283958026545</v>
+        <v>-0.01345874896620423</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1674201177987</v>
+        <v>1.167321402122803</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510577685590904</v>
+        <v>1.510516307391687</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047249699079408</v>
+        <v>0.5047259232949456</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05296246672135985</v>
+        <v>0.0529168949860771</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025734078023709</v>
+        <v>0.5025790950911222</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.025068858307571</v>
+        <v>5.008206065229923</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.108633786556211</v>
+        <v>5.05404668156855</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.249935980103169</v>
+        <v>5.150592481260932</v>
       </c>
     </row>
     <row r="8">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E8" t="n">
         <v>9022</v>
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9020</v>
+        <v>9022</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.877970620842571</v>
+        <v>7.877580082021725</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116793320530141</v>
+        <v>8.115981665816383</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2388226996875703</v>
+        <v>0.2384015837946578</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446972475466501</v>
+        <v>1.446786573522368</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826457079099295</v>
+        <v>1.826265196958619</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078563341255417</v>
+        <v>0.8078803782218908</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274310186997866</v>
+        <v>0.6274553600175942</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978757677560413</v>
+        <v>0.7979485506649623</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.004249533497303</v>
+        <v>4.934156311681083</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.241923509467554</v>
+        <v>5.129856374328506</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.494680127851285</v>
+        <v>5.38708982870934</v>
       </c>
     </row>
     <row r="9">
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E9" t="n">
         <v>13887</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13885</v>
+        <v>13887</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.612817068779258</v>
+        <v>7.612424209692518</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.658428209928556</v>
+        <v>7.657956557898032</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04561114114929854</v>
+        <v>0.04553234820551315</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494695588667584</v>
+        <v>1.494612590862856</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942654606847102</v>
+        <v>1.942542798300039</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565107728650059</v>
+        <v>0.7565464836024315</v>
       </c>
       <c r="W9" t="n">
-        <v>0.524550023194795</v>
+        <v>0.5246004631648011</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551003705456798</v>
+        <v>0.7551409194404201</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.292574797347089</v>
+        <v>5.260670355184188</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.438524135537802</v>
+        <v>5.362687550074731</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.648186932197633</v>
+        <v>5.545209468785206</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61763375807974</v>
+        <v>10.61740851777895</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3125720775873675</v>
+        <v>0.3123468372865759</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052306811872219</v>
+        <v>2.052388693396149</v>
       </c>
       <c r="U10" t="n">
-        <v>2.697959172486559</v>
+        <v>2.698055583296065</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3567868661718981</v>
+        <v>0.3568064736120795</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1203230699397555</v>
+        <v>-0.1204031402277412</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3362632606060501</v>
+        <v>0.3363170917479009</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.600906418623643</v>
+        <v>9.549316857266481</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.777343672326253</v>
+        <v>9.723608005306833</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.872562888370343</v>
+        <v>9.839341520776234</v>
       </c>
     </row>
     <row r="11">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E11" t="n">
         <v>13828</v>
@@ -1383,7 +1383,7 @@
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13826</v>
+        <v>13828</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.244008896282367</v>
+        <v>5.243818122649696</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4579167280766397</v>
+        <v>0.4578476821192053</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217444562202032</v>
+        <v>5.21727600286166</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02656433408033455</v>
+        <v>-0.02654211978803545</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161949853281922</v>
+        <v>1.16189503999759</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483410629938707</v>
+        <v>1.483349753681771</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4291286892860851</v>
+        <v>0.4291763734523883</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09254658907410285</v>
+        <v>-0.09247605719371244</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4273209763770759</v>
+        <v>0.4273701296706892</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.257832691184758</v>
+        <v>4.059743046357616</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.486911191916347</v>
+        <v>4.366988520753055</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.649027266028003</v>
+        <v>4.564415220859675</v>
       </c>
     </row>
     <row r="12">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E12" t="n">
         <v>4146</v>
@@ -1472,7 +1472,7 @@
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4144</v>
+        <v>4146</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.476800434362935</v>
+        <v>7.475033405692233</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204993367722918</v>
+        <v>2.204980132450331</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.650315054484551</v>
+        <v>7.648936536957421</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1735146201216171</v>
+        <v>0.1739031312651874</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136152495095385</v>
+        <v>0.9137330192589023</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195824576354346</v>
+        <v>1.195825288346841</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8309058298067176</v>
+        <v>0.8310580667992485</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6571447850642773</v>
+        <v>0.6575104588450003</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8291461875594424</v>
+        <v>0.8292764365286283</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.39198534439013</v>
+        <v>4.340056245713813</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.62529131326057</v>
+        <v>4.457872885553112</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.098941579707359</v>
+        <v>4.672441563331953</v>
       </c>
     </row>
     <row r="13">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E13" t="n">
         <v>6481</v>
@@ -1561,7 +1561,7 @@
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6479</v>
+        <v>6481</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.607988501311931</v>
+        <v>9.60706102453325</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02776696884247</v>
+        <v>10.02685116762883</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4197784675305431</v>
+        <v>0.4197901430955805</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691813880156576</v>
+        <v>1.691610003109531</v>
       </c>
       <c r="U13" t="n">
-        <v>2.151651361748171</v>
+        <v>2.1514241528515</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231061015192128</v>
+        <v>0.8231361703139705</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485149939543511</v>
+        <v>0.6485551446599243</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8105286124338469</v>
+        <v>0.8105716887272579</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.468263701524364</v>
+        <v>8.462824810572933</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.486139727112491</v>
+        <v>8.485342411980458</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.508730144233402</v>
+        <v>8.516563348227264</v>
       </c>
     </row>
     <row r="14">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E14" t="n">
         <v>14068</v>
@@ -1650,7 +1650,7 @@
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14066</v>
+        <v>14068</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.130124768946395</v>
+        <v>8.129711224054592</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.907575534266765</v>
+        <v>0.9073534461613932</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.200747290471618</v>
+        <v>8.200055716537479</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07062252152522085</v>
+        <v>0.07034449248288628</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757482057603595</v>
+        <v>1.757069255456955</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283380114898333</v>
+        <v>2.283049646081841</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7807407590105108</v>
+        <v>0.7808152208260632</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5651607099835732</v>
+        <v>0.5652683919865431</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7803611939858556</v>
+        <v>0.7804413014760421</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.278864846891866</v>
+        <v>5.238001097140473</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.422517319752226</v>
+        <v>5.339798664991706</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.609728918833561</v>
+        <v>5.49875168104721</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.677450257921887</v>
+        <v>4.675805739514349</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82281051622497</v>
+        <v>11.82254260638502</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1410768668018126</v>
+        <v>-0.1413447766417594</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052192090631159</v>
+        <v>2.052256750701916</v>
       </c>
       <c r="U15" t="n">
-        <v>2.69748716270927</v>
+        <v>2.697531290935369</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949730704890277</v>
+        <v>0.7949783668585507</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096403961556859</v>
+        <v>0.6096276242559743</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7862799689564134</v>
+        <v>0.7863015290987956</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.7347444995811</v>
+        <v>11.22398028644545</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.80819981884571</v>
+        <v>11.70681009307872</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89671306158439</v>
+        <v>11.89912902679923</v>
       </c>
     </row>
     <row r="16">
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E16" t="n">
         <v>9831</v>
@@ -1828,7 +1828,7 @@
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9829</v>
+        <v>9831</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.365120459863668</v>
+        <v>8.364533007832366</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624474441455252</v>
+        <v>8.624908711397223</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2593539815915828</v>
+        <v>0.2603757035648576</v>
       </c>
       <c r="T16" t="n">
-        <v>3.590249814311195</v>
+        <v>3.590902758923515</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09400876879166</v>
+        <v>11.09332919768609</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04185642181653586</v>
+        <v>0.04180709471131555</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6096790894987156</v>
+        <v>-0.6097736572904284</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02519411912302361</v>
+        <v>0.02514239784001837</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.73516444086846</v>
+        <v>11.66786544169128</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.38347540660107</v>
+        <v>12.15227416749987</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.86967193946729</v>
+        <v>12.84057536461028</v>
       </c>
     </row>
     <row r="17">
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E17" t="n">
         <v>2375</v>
@@ -1917,7 +1917,7 @@
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.503459755583649</v>
+        <v>6.500153684210527</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.410841562269713</v>
+        <v>1.410260485651214</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.869337494366117</v>
+        <v>6.865842588228053</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.365877738782467</v>
+        <v>0.3656889040175255</v>
       </c>
       <c r="T17" t="n">
-        <v>2.023996089361611</v>
+        <v>2.022422788937408</v>
       </c>
       <c r="U17" t="n">
-        <v>2.558406137030202</v>
+        <v>2.557380905669803</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5296221532443053</v>
+        <v>0.5305566787283894</v>
       </c>
       <c r="W17" t="n">
-        <v>0.03836881130245173</v>
+        <v>0.04015994668106238</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5262679743752965</v>
+        <v>0.5271955544359199</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.52745787735759</v>
+        <v>1.713862016042998</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.716250765032647</v>
+        <v>2.714960451336473</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.11522600763089</v>
+        <v>3.351738674237951</v>
       </c>
     </row>
     <row r="18">
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E18" t="n">
         <v>3234</v>
@@ -2006,7 +2006,7 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3232</v>
+        <v>3234</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.481385055693068</v>
+        <v>6.479918521954236</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.676608519491677</v>
+        <v>6.674960366861923</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1952234637986087</v>
+        <v>0.1950418449076864</v>
       </c>
       <c r="T18" t="n">
-        <v>1.100254057928317</v>
+        <v>1.099677826244653</v>
       </c>
       <c r="U18" t="n">
-        <v>1.48820591867806</v>
+        <v>1.487772178365638</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6041245752433848</v>
+        <v>0.6046732908822743</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2234171333228576</v>
+        <v>0.2243354796068237</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6011806698686606</v>
+        <v>0.6017495035477453</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.266529627088542</v>
+        <v>2.41361948183334</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.942825179461268</v>
+        <v>3.981639739749073</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.764442370951057</v>
+        <v>4.785120719016083</v>
       </c>
     </row>
     <row r="19">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="E19" t="n">
         <v>7188</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7186</v>
+        <v>7188</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34285993598664</v>
+        <v>10.34015115470228</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13231216533586</v>
+        <v>11.13109949935348</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.78945222934922</v>
+        <v>0.7909483446511998</v>
       </c>
       <c r="T19" t="n">
-        <v>2.048838188039506</v>
+        <v>2.050196447397293</v>
       </c>
       <c r="U19" t="n">
-        <v>2.771140719736681</v>
+        <v>2.773116556528339</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270006919428205</v>
+        <v>0.7270143805551331</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4706605605440658</v>
+        <v>0.4707200363924753</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6788699689981009</v>
+        <v>0.6785856643221119</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.426173774613734</v>
+        <v>7.390415195964133</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.44677307849328</v>
+        <v>7.483035789454459</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.469728986617255</v>
+        <v>8.395882070643351</v>
       </c>
     </row>
   </sheetData>
@@ -2226,22 +2226,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.426173774613734</v>
+        <v>7.390415195964133</v>
       </c>
       <c r="G2" t="n">
-        <v>7.44677307849328</v>
+        <v>7.48303578945446</v>
       </c>
       <c r="H2" t="n">
-        <v>7.469728986617255</v>
+        <v>8.395882070643351</v>
       </c>
     </row>
     <row r="3">
@@ -2254,22 +2254,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.025068858307571</v>
+        <v>5.008206065229923</v>
       </c>
       <c r="G3" t="n">
-        <v>5.108633786556211</v>
+        <v>5.054046681568551</v>
       </c>
       <c r="H3" t="n">
-        <v>5.249935980103169</v>
+        <v>5.150592481260932</v>
       </c>
     </row>
     <row r="4">
@@ -2282,22 +2282,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.257832691184758</v>
+        <v>4.059743046357616</v>
       </c>
       <c r="G4" t="n">
-        <v>4.486911191916347</v>
+        <v>4.366988520753055</v>
       </c>
       <c r="H4" t="n">
-        <v>4.649027266028003</v>
+        <v>4.564415220859675</v>
       </c>
     </row>
     <row r="5">
@@ -2310,22 +2310,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.73516444086846</v>
+        <v>11.66786544169128</v>
       </c>
       <c r="G5" t="n">
-        <v>12.38347540660108</v>
+        <v>12.15227416749987</v>
       </c>
       <c r="H5" t="n">
-        <v>12.86967193946729</v>
+        <v>12.84057536461028</v>
       </c>
     </row>
     <row r="6">
@@ -2338,22 +2338,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>3.769856802117444</v>
+        <v>2.916586825617892</v>
       </c>
       <c r="G6" t="n">
-        <v>97.44892879912862</v>
+        <v>55.91525830458848</v>
       </c>
       <c r="H6" t="n">
-        <v>108.9638433558469</v>
+        <v>110.4041525034457</v>
       </c>
     </row>
     <row r="7">
@@ -2366,22 +2366,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.7347444995811</v>
+        <v>11.22398028644545</v>
       </c>
       <c r="G7" t="n">
-        <v>11.80819981884571</v>
+        <v>11.70681009307872</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89671306158439</v>
+        <v>11.89912902679923</v>
       </c>
     </row>
     <row r="8">
@@ -2394,22 +2394,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.468263701524364</v>
+        <v>8.462824810572933</v>
       </c>
       <c r="G8" t="n">
-        <v>8.486139727112491</v>
+        <v>8.485342411980458</v>
       </c>
       <c r="H8" t="n">
-        <v>8.508730144233402</v>
+        <v>8.516563348227264</v>
       </c>
     </row>
     <row r="9">
@@ -2422,22 +2422,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.39198534439013</v>
+        <v>4.340056245713813</v>
       </c>
       <c r="G9" t="n">
-        <v>4.62529131326057</v>
+        <v>4.457872885553112</v>
       </c>
       <c r="H9" t="n">
-        <v>5.098941579707359</v>
+        <v>4.672441563331953</v>
       </c>
     </row>
     <row r="10">
@@ -2450,22 +2450,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>5.004249533497303</v>
+        <v>4.934156311681083</v>
       </c>
       <c r="G10" t="n">
-        <v>5.241923509467553</v>
+        <v>5.129856374328506</v>
       </c>
       <c r="H10" t="n">
-        <v>5.494680127851285</v>
+        <v>5.38708982870934</v>
       </c>
     </row>
     <row r="11">
@@ -2478,22 +2478,22 @@
         <v>9037610</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.52745787735759</v>
+        <v>1.713862016042998</v>
       </c>
       <c r="G11" t="n">
-        <v>2.716250765032647</v>
+        <v>2.714960451336472</v>
       </c>
       <c r="H11" t="n">
-        <v>3.11522600763089</v>
+        <v>3.351738674237951</v>
       </c>
     </row>
     <row r="12">
@@ -2506,22 +2506,22 @@
         <v>9043425</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.278864846891866</v>
+        <v>5.238001097140473</v>
       </c>
       <c r="G12" t="n">
-        <v>5.422517319752226</v>
+        <v>5.339798664991706</v>
       </c>
       <c r="H12" t="n">
-        <v>5.609728918833561</v>
+        <v>5.49875168104721</v>
       </c>
     </row>
     <row r="13">
@@ -2534,22 +2534,22 @@
         <v>9042153</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.600906418623643</v>
+        <v>9.549316857266481</v>
       </c>
       <c r="G13" t="n">
-        <v>9.777343672326253</v>
+        <v>9.723608005306831</v>
       </c>
       <c r="H13" t="n">
-        <v>9.872562888370343</v>
+        <v>9.839341520776234</v>
       </c>
     </row>
     <row r="14">
@@ -2562,22 +2562,22 @@
         <v>9040439</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.292574797347089</v>
+        <v>5.260670355184188</v>
       </c>
       <c r="G14" t="n">
-        <v>5.438524135537802</v>
+        <v>5.362687550074731</v>
       </c>
       <c r="H14" t="n">
-        <v>5.648186932197633</v>
+        <v>5.545209468785206</v>
       </c>
     </row>
     <row r="15">
@@ -2590,22 +2590,22 @@
         <v>9032282</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.637357986904973</v>
+        <v>6.486446346278253</v>
       </c>
       <c r="G15" t="n">
-        <v>6.731800622264612</v>
+        <v>6.665571928695377</v>
       </c>
       <c r="H15" t="n">
-        <v>6.816162292410292</v>
+        <v>6.747839699821181</v>
       </c>
     </row>
     <row r="16">
@@ -2618,22 +2618,22 @@
         <v>9037738</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.266529627088542</v>
+        <v>2.41361948183334</v>
       </c>
       <c r="G16" t="n">
-        <v>3.942825179461268</v>
+        <v>3.981639739749073</v>
       </c>
       <c r="H16" t="n">
-        <v>4.764442370951057</v>
+        <v>4.785120719016083</v>
       </c>
     </row>
     <row r="17">
@@ -2646,22 +2646,22 @@
         <v>9039635</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.251550478997789</v>
+        <v>3.198107335644316</v>
       </c>
       <c r="G17" t="n">
-        <v>3.307057511629658</v>
+        <v>3.293696536909428</v>
       </c>
       <c r="H17" t="n">
-        <v>3.421500854462202</v>
+        <v>3.372869757174393</v>
       </c>
     </row>
     <row r="18">
@@ -2674,22 +2674,22 @@
         <v>9038269</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.226167104485544</v>
+        <v>2.217566225165563</v>
       </c>
       <c r="G18" t="n">
-        <v>2.347711652943616</v>
+        <v>2.304403060109094</v>
       </c>
       <c r="H18" t="n">
-        <v>2.439721648622689</v>
+        <v>2.439635148393426</v>
       </c>
     </row>
     <row r="19">
@@ -2702,22 +2702,22 @@
         <v>9036459</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>4.874492081613734</v>
+        <v>4.896992042626673</v>
       </c>
       <c r="G19" t="n">
-        <v>5.545237347922788</v>
+        <v>5.364606427688901</v>
       </c>
       <c r="H19" t="n">
-        <v>5.83350430433552</v>
+        <v>5.806240660273916</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2158,6 +2158,184 @@
       </c>
       <c r="AA19" t="n">
         <v>8.395882070643351</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Puerto Alegria</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9038835</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16687</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10022</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10022</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>12</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>35325</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>45350</v>
+      </c>
+      <c r="M20" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>13.75804552057581</v>
+      </c>
+      <c r="O20" t="n">
+        <v>22.08804784</v>
+      </c>
+      <c r="P20" t="n">
+        <v>7.450085959885387</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>14.04791926568749</v>
+      </c>
+      <c r="R20" t="n">
+        <v>21.74397615007625</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2898737451116739</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.262838672378833</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.655866786358523</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.890705823134583</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.77864525836096</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.886865658970889</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>9.661051470870632</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9.793689003916242</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>9.883457487320841</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yurimaguas</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9046779</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cdf_empirica_mensual_ordenada</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16687</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10226</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10226</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1,2,3,4,5,6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>36039</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="M21" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>130.8731929395658</v>
+      </c>
+      <c r="O21" t="n">
+        <v>135.52</v>
+      </c>
+      <c r="P21" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>130.9775087193635</v>
+      </c>
+      <c r="R21" t="n">
+        <v>135.52</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1043157797977151</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.7978004580338239</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.046583899573891</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.8648007695995915</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.730495786207253</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.8640830951794183</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>128.0366227737635</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>128.1520477465941</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>128.8987833096963</v>
       </c>
     </row>
   </sheetData>
@@ -2171,7 +2349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2471,11 +2649,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Puerto Almendra</t>
+          <t>Puerto Alegria</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9037610</v>
+        <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>46274</v>
@@ -2487,23 +2665,23 @@
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>1.713862016042998</v>
+        <v>9.661051470870632</v>
       </c>
       <c r="G11" t="n">
-        <v>2.714960451336472</v>
+        <v>9.793689003916242</v>
       </c>
       <c r="H11" t="n">
-        <v>3.351738674237951</v>
+        <v>9.883457487320841</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Requena</t>
+          <t>Puerto Almendra</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9043425</v>
+        <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>46274</v>
@@ -2515,23 +2693,23 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5.238001097140473</v>
+        <v>1.713862016042998</v>
       </c>
       <c r="G12" t="n">
-        <v>5.339798664991706</v>
+        <v>2.714960451336472</v>
       </c>
       <c r="H12" t="n">
-        <v>5.49875168104721</v>
+        <v>3.351738674237951</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Requena</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9042153</v>
+        <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>46274</v>
@@ -2543,23 +2721,23 @@
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>9.549316857266481</v>
+        <v>5.238001097140473</v>
       </c>
       <c r="G13" t="n">
-        <v>9.723608005306831</v>
+        <v>5.339798664991706</v>
       </c>
       <c r="H13" t="n">
-        <v>9.839341520776234</v>
+        <v>5.49875168104721</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>San Regis</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9040439</v>
+        <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>46274</v>
@@ -2571,23 +2749,23 @@
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>5.260670355184188</v>
+        <v>9.549316857266481</v>
       </c>
       <c r="G14" t="n">
-        <v>5.362687550074731</v>
+        <v>9.723608005306831</v>
       </c>
       <c r="H14" t="n">
-        <v>5.545209468785206</v>
+        <v>9.839341520776234</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Santa Clotilde</t>
+          <t>San Regis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9032282</v>
+        <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>46274</v>
@@ -2599,23 +2777,23 @@
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>6.486446346278253</v>
+        <v>5.260670355184188</v>
       </c>
       <c r="G15" t="n">
-        <v>6.665571928695377</v>
+        <v>5.362687550074731</v>
       </c>
       <c r="H15" t="n">
-        <v>6.747839699821181</v>
+        <v>5.545209468785206</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Santa María de Nanay</t>
+          <t>Santa Clotilde</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9037738</v>
+        <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>46274</v>
@@ -2627,23 +2805,23 @@
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>2.41361948183334</v>
+        <v>6.486446346278253</v>
       </c>
       <c r="G16" t="n">
-        <v>3.981639739749073</v>
+        <v>6.665571928695377</v>
       </c>
       <c r="H16" t="n">
-        <v>4.785120719016083</v>
+        <v>6.747839699821181</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Santa María de Nanay</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9039635</v>
+        <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
         <v>46274</v>
@@ -2655,23 +2833,23 @@
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.198107335644316</v>
+        <v>2.41361948183334</v>
       </c>
       <c r="G17" t="n">
-        <v>3.293696536909428</v>
+        <v>3.981639739749073</v>
       </c>
       <c r="H17" t="n">
-        <v>3.372869757174393</v>
+        <v>4.785120719016083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tamshiyacu</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>9038269</v>
+        <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
         <v>46274</v>
@@ -2683,23 +2861,23 @@
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>2.217566225165563</v>
+        <v>3.198107335644316</v>
       </c>
       <c r="G18" t="n">
-        <v>2.304403060109094</v>
+        <v>3.293696536909428</v>
       </c>
       <c r="H18" t="n">
-        <v>2.439635148393426</v>
+        <v>3.372869757174393</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Timicurillo</t>
+          <t>Tamshiyacu</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9036459</v>
+        <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>46274</v>
@@ -2711,13 +2889,69 @@
         <v>10</v>
       </c>
       <c r="F19" t="n">
+        <v>2.217566225165563</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.304403060109094</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.439635148393426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Timicurillo</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>9036459</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
         <v>4.896992042626673</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>5.364606427688901</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>5.806240660273916</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Yurimaguas</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9046779</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>128.0366227737635</v>
+      </c>
+      <c r="G21" t="n">
+        <v>128.1520477465941</v>
+      </c>
+      <c r="H21" t="n">
+        <v>128.8987833096963</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E2" t="n">
-        <v>10022</v>
+        <v>10024</v>
       </c>
       <c r="F2" t="n">
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10022</v>
+        <v>10023</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6081299807091</v>
+        <v>102.6401934217965</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6026761730889</v>
+        <v>102.6210348468465</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.005453807620190749</v>
+        <v>-0.01915857495004063</v>
       </c>
       <c r="T2" t="n">
-        <v>17.88840241485032</v>
+        <v>17.92084831171142</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0684221698123</v>
+        <v>36.05590548087464</v>
       </c>
       <c r="V2" t="n">
-        <v>0.142104735607799</v>
+        <v>0.1375506114751729</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.7122717715266358</v>
+        <v>-0.722637334889993</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1421022767928583</v>
+        <v>0.1375495928229944</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.916586825617892</v>
+        <v>2.859156075158237</v>
       </c>
       <c r="Z2" t="n">
-        <v>55.91525830458848</v>
+        <v>66.71469946523099</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.4041525034457</v>
+        <v>110.4031025372064</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E3" t="n">
-        <v>14616</v>
+        <v>14618</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>14616</v>
+        <v>14617</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.909556410782703</v>
+        <v>4.909358042005884</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966980822301371</v>
+        <v>4.966869406629901</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0574244115186674</v>
+        <v>0.05751136462401766</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344872572390505</v>
+        <v>1.344815915639666</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719378648397252</v>
+        <v>1.719320971108818</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812717933175565</v>
+        <v>0.7812815394242243</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5695078902933919</v>
+        <v>0.5695433208646259</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7802423363719371</v>
+        <v>0.78024750279085</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.217566225165563</v>
+        <v>2.208828978869868</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.304403060109094</v>
+        <v>2.283912339375278</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.439635148393426</v>
+        <v>2.438113970588236</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E4" t="n">
-        <v>10250</v>
+        <v>10252</v>
       </c>
       <c r="F4" t="n">
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10250</v>
+        <v>10251</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.910700487804878</v>
+        <v>6.910368500634084</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.239960430762789</v>
+        <v>7.239905369550713</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3292599429579107</v>
+        <v>0.3295368689166275</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292656574486361</v>
+        <v>1.292655493271272</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682348744402725</v>
+        <v>1.682361676067788</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676541608458425</v>
+        <v>0.8676526108544037</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374828853381401</v>
+        <v>0.7374807168755585</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8472157507706407</v>
+        <v>0.8471538725201219</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.198107335644316</v>
+        <v>3.250367647058824</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.293696536909429</v>
+        <v>3.308990281635551</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.372869757174393</v>
+        <v>3.389588235294118</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.758646063281825</v>
+        <v>2.758426470588235</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302649539648822</v>
+        <v>9.302527584850989</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3613469566229915</v>
+        <v>0.3612250018251582</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253914136021931</v>
+        <v>1.253939717587138</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750182622566772</v>
+        <v>1.750189884345819</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8661983110732562</v>
+        <v>0.8662002392761822</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212997836382069</v>
+        <v>0.7212974708925951</v>
       </c>
       <c r="X5" t="n">
-        <v>0.860196993068584</v>
+        <v>0.8602039168574274</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.896992042626673</v>
+        <v>4.870570102349984</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.364606427688901</v>
+        <v>5.32933579975823</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.806240660273916</v>
+        <v>5.806428148976981</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E6" t="n">
-        <v>8863</v>
+        <v>8865</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8863</v>
+        <v>8864</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733400823648878</v>
+        <v>6.73348561597473</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021661041114544</v>
+        <v>7.021986514483771</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2882602174656666</v>
+        <v>0.2885008985090426</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480123101713638</v>
+        <v>1.480019828499391</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908787107188363</v>
+        <v>1.908691625318766</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3046358448472594</v>
+        <v>0.3045941470264492</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977413168303059</v>
+        <v>-0.19773243613439</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2798613613927535</v>
+        <v>0.2797880969387548</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.486446346278253</v>
+        <v>6.467302386196443</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.665571928695377</v>
+        <v>6.649666020763567</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.747839699821181</v>
+        <v>6.749136091929754</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E7" t="n">
-        <v>14224</v>
+        <v>14226</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14224</v>
+        <v>14225</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581293131327334</v>
+        <v>5.581253145869947</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.56783438236113</v>
+        <v>5.567831189381732</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01345874896620423</v>
+        <v>-0.01342195648821472</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167321402122803</v>
+        <v>1.167207453873282</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510516307391687</v>
+        <v>1.510429162898177</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047259232949456</v>
+        <v>0.5047390346819002</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0529168949860771</v>
+        <v>0.05296853445103156</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025790950911222</v>
+        <v>0.5025894756018432</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.008206065229923</v>
+        <v>4.971538191312902</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.05404668156855</v>
+        <v>5.039669872236572</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.150592481260932</v>
+        <v>5.145129185323924</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E8" t="n">
-        <v>9022</v>
+        <v>9024</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>9022</v>
+        <v>9023</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.877580082021725</v>
+        <v>7.877358694447524</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.115981665816383</v>
+        <v>8.11616137330037</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2384015837946578</v>
+        <v>0.2388026788528475</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446786573522368</v>
+        <v>1.446712473428141</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826265196958619</v>
+        <v>1.826233482768617</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078803782218908</v>
+        <v>0.8078618063111659</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274553600175942</v>
+        <v>0.6274453665273254</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7979485506649623</v>
+        <v>0.797876788320356</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.934156311681083</v>
+        <v>4.895448881684713</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.129856374328506</v>
+        <v>5.10333737858505</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.38708982870934</v>
+        <v>5.397712388702573</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E9" t="n">
-        <v>13887</v>
+        <v>13889</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>13887</v>
+        <v>13888</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.612424209692518</v>
+        <v>7.612219002016129</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657956557898032</v>
+        <v>7.657790066263708</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04553234820551315</v>
+        <v>0.04557106424757886</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494612590862856</v>
+        <v>1.494561299704026</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942542798300039</v>
+        <v>1.942484706890063</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565464836024315</v>
+        <v>0.7565570241788571</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5246004631648011</v>
+        <v>0.5246296776436736</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551409194404201</v>
+        <v>0.7551490918321718</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.260670355184188</v>
+        <v>5.22261925561098</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.362687550074731</v>
+        <v>5.334758091973446</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.545209468785206</v>
+        <v>5.535984764483778</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61740851777895</v>
+        <v>10.61729166578519</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3123468372865759</v>
+        <v>0.3122299852928171</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052388693396149</v>
+        <v>2.05243981651836</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698055583296065</v>
+        <v>2.698107986053119</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568064736120795</v>
+        <v>0.3568145599944468</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1204031402277412</v>
+        <v>-0.1204466625214182</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3363170917479009</v>
+        <v>0.3363426015788475</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.549316857266481</v>
+        <v>9.55904284626933</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.723608005306833</v>
+        <v>9.698423001815716</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.839341520776234</v>
+        <v>9.839476314238251</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E11" t="n">
-        <v>13828</v>
+        <v>13830</v>
       </c>
       <c r="F11" t="n">
         <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>13828</v>
+        <v>13829</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243818122649696</v>
+        <v>5.243700701424543</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578476821192053</v>
+        <v>0.4578926470588235</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.21727600286166</v>
+        <v>5.217154212916308</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02654211978803545</v>
+        <v>-0.02654648850823374</v>
       </c>
       <c r="T11" t="n">
-        <v>1.16189503999759</v>
+        <v>1.161854152472563</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483349753681771</v>
+        <v>1.483298267013617</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4291763734523883</v>
+        <v>0.4292233572837483</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09247605719371244</v>
+        <v>-0.09237613510864229</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4273701296706892</v>
+        <v>0.4274161835584696</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.059743046357616</v>
+        <v>4.168535877281947</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.366988520753055</v>
+        <v>4.358364588220014</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.564415220859675</v>
+        <v>4.714335552459916</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E12" t="n">
-        <v>4146</v>
+        <v>4148</v>
       </c>
       <c r="F12" t="n">
         <v>10</v>
       </c>
       <c r="G12" t="n">
-        <v>4146</v>
+        <v>4147</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.475033405692233</v>
+        <v>7.474134555100073</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.204980132450331</v>
+        <v>2.205044117647059</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.648936536957421</v>
+        <v>7.64779240946156</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1739031312651874</v>
+        <v>0.1736578543614873</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9137330192589023</v>
+        <v>0.9136876128412654</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195825288346841</v>
+        <v>1.195730992306831</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8310580667992485</v>
+        <v>0.8311959400913269</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6575104588450003</v>
+        <v>0.6577565082796109</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8292764365286283</v>
+        <v>0.8294244532228753</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.340056245713813</v>
+        <v>4.325969793524327</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.457872885553112</v>
+        <v>4.410704995879141</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.672441563331953</v>
+        <v>4.666266550096728</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E13" t="n">
-        <v>6481</v>
+        <v>6483</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>6481</v>
+        <v>6482</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.60706102453325</v>
+        <v>9.606579373650108</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02685116762883</v>
+        <v>10.026964116144</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4197901430955805</v>
+        <v>0.420384742493891</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691610003109531</v>
+        <v>1.691643608568783</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1514241528515</v>
+        <v>2.15123386907055</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231361703139705</v>
+        <v>0.8231553406913343</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6485551446599243</v>
+        <v>0.6486032047922794</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8105716887272579</v>
+        <v>0.8105196419420337</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.462824810572933</v>
+        <v>8.3659948887307</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.485342411980458</v>
+        <v>8.47411022276912</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.516563348227264</v>
+        <v>8.516671295700013</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E14" t="n">
-        <v>14068</v>
+        <v>14070</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>14068</v>
+        <v>14069</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.129711224054592</v>
+        <v>8.12948148411401</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073534461613932</v>
+        <v>0.9075122549019609</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.200055716537479</v>
+        <v>8.199978628416979</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07034449248288628</v>
+        <v>0.07049714430296847</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757069255456955</v>
+        <v>1.757026247784107</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283049646081841</v>
+        <v>2.283009420160737</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808152208260632</v>
+        <v>0.7808093022640511</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652683919865431</v>
+        <v>0.5652796695706566</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804413014760421</v>
+        <v>0.7804320914676875</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.238001097140473</v>
+        <v>5.220591944077436</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.339798664991706</v>
+        <v>5.306957541592512</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.49875168104721</v>
+        <v>5.488543505846495</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.675805739514349</v>
+        <v>4.674985294117647</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82254260638502</v>
+        <v>11.82240520066709</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1413447766417594</v>
+        <v>-0.1414821823596916</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052256750701916</v>
+        <v>2.052289978127739</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697531290935369</v>
+        <v>2.697555039592728</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949783668585507</v>
+        <v>0.7949809007848454</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096276242559743</v>
+        <v>0.6096207506670492</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863015290987956</v>
+        <v>0.786312379703427</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.22398028644545</v>
+        <v>11.02549211160407</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.70681009307872</v>
+        <v>11.64700856598263</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89912902679923</v>
+        <v>11.89802209738195</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E16" t="n">
-        <v>9831</v>
+        <v>9833</v>
       </c>
       <c r="F16" t="n">
         <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>9831</v>
+        <v>9832</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.364533007832366</v>
+        <v>8.364266578519121</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624908711397223</v>
+        <v>8.624544129387269</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2603757035648576</v>
+        <v>0.2602775508681475</v>
       </c>
       <c r="T16" t="n">
-        <v>3.590902758923515</v>
+        <v>3.591467670912076</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09332919768609</v>
+        <v>11.09303698346365</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04180709471131555</v>
+        <v>0.04176593861139232</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6097736572904284</v>
+        <v>-0.6098379207646232</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02514239784001837</v>
+        <v>0.02510195033367979</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.66786544169128</v>
+        <v>11.67021012625146</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.15227416749987</v>
+        <v>12.06108156915331</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.84057536461028</v>
+        <v>12.83963543911982</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E17" t="n">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="F17" t="n">
         <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.500153684210527</v>
+        <v>6.498423821548822</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.410260485651214</v>
+        <v>1.414161764705882</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.865842588228053</v>
+        <v>6.863338651120654</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3656889040175255</v>
+        <v>0.3649148295718319</v>
       </c>
       <c r="T17" t="n">
-        <v>2.022422788937408</v>
+        <v>2.02131674895441</v>
       </c>
       <c r="U17" t="n">
-        <v>2.557380905669803</v>
+        <v>2.556597063719214</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5305566787283894</v>
+        <v>0.5312579160629711</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04015994668106238</v>
+        <v>0.04134407838066889</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5271955544359199</v>
+        <v>0.5279030760246999</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.713862016042998</v>
+        <v>1.717620819627904</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.714960451336473</v>
+        <v>2.777118322693554</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.351738674237951</v>
+        <v>3.537717979947023</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E18" t="n">
-        <v>3234</v>
+        <v>3236</v>
       </c>
       <c r="F18" t="n">
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.479918521954236</v>
+        <v>6.479062287480679</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.674960366861923</v>
+        <v>6.673816399864205</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1950418449076864</v>
+        <v>0.1947541123835258</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099677826244653</v>
+        <v>1.099334535634291</v>
       </c>
       <c r="U18" t="n">
-        <v>1.487772178365638</v>
+        <v>1.487478061377266</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6046732908822743</v>
+        <v>0.6050922902583785</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2243354796068237</v>
+        <v>0.2250422251078293</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6017495035477453</v>
+        <v>0.6021877232688061</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.41361948183334</v>
+        <v>2.421420498901102</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.981639739749073</v>
+        <v>4.017221835667445</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.785120719016083</v>
+        <v>4.945533316505774</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E19" t="n">
-        <v>7188</v>
+        <v>7190</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7188</v>
+        <v>7189</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34015115470228</v>
+        <v>10.33886270691334</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.13109949935348</v>
+        <v>11.12993829747639</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7909483446511998</v>
+        <v>0.7910755905630473</v>
       </c>
       <c r="T19" t="n">
-        <v>2.050196447397293</v>
+        <v>2.050756140746665</v>
       </c>
       <c r="U19" t="n">
-        <v>2.773116556528339</v>
+        <v>2.773812447714668</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270143805551331</v>
+        <v>0.7270599514158688</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4707200363924753</v>
+        <v>0.4708149999698175</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6785856643221119</v>
+        <v>0.6786150048679285</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.390415195964133</v>
+        <v>7.407721238084079</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.483035789454459</v>
+        <v>7.491450060649029</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.395882070643351</v>
+        <v>8.395016033746353</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E20" t="n">
-        <v>10022</v>
+        <v>618</v>
       </c>
       <c r="F20" t="n">
         <v>10</v>
       </c>
       <c r="G20" t="n">
-        <v>10022</v>
+        <v>617</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2198,55 +2198,55 @@
         <v>1</v>
       </c>
       <c r="K20" s="1" t="n">
-        <v>35325</v>
+        <v>45658</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>45350</v>
+        <v>46274</v>
       </c>
       <c r="M20" t="n">
-        <v>6.75</v>
+        <v>10.17</v>
       </c>
       <c r="N20" t="n">
-        <v>13.75804552057581</v>
+        <v>15.54713533225284</v>
       </c>
       <c r="O20" t="n">
-        <v>22.08804784</v>
+        <v>19.03</v>
       </c>
       <c r="P20" t="n">
-        <v>7.450085959885387</v>
+        <v>10.80896323529412</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.04791926568749</v>
+        <v>16.38066493652289</v>
       </c>
       <c r="R20" t="n">
-        <v>21.74397615007625</v>
+        <v>19.01911469282878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2898737451116739</v>
+        <v>0.8335296042700525</v>
       </c>
       <c r="T20" t="n">
-        <v>1.262838672378833</v>
+        <v>0.8869504228486376</v>
       </c>
       <c r="U20" t="n">
-        <v>1.655866786358523</v>
+        <v>1.263286564196537</v>
       </c>
       <c r="V20" t="n">
-        <v>0.890705823134583</v>
+        <v>0.9368242409993496</v>
       </c>
       <c r="W20" t="n">
-        <v>0.77864525836096</v>
+        <v>0.7832183008847218</v>
       </c>
       <c r="X20" t="n">
-        <v>0.886865658970889</v>
+        <v>0.8997506008946337</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.661051470870632</v>
+        <v>10.80701656967405</v>
       </c>
       <c r="Z20" t="n">
-        <v>9.793689003916242</v>
+        <v>10.81082019345841</v>
       </c>
       <c r="AA20" t="n">
-        <v>9.883457487320841</v>
+        <v>10.81626760151583</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16687</v>
+        <v>16688</v>
       </c>
       <c r="E21" t="n">
-        <v>10226</v>
+        <v>10236</v>
       </c>
       <c r="F21" t="n">
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10226</v>
+        <v>10235</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8731929395658</v>
+        <v>130.8714646800196</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9775087193635</v>
+        <v>130.9760085148853</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1043157797977151</v>
+        <v>0.1045438348657684</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7978004580338239</v>
+        <v>0.7976486706293027</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046583899573891</v>
+        <v>1.04634513831057</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8648007695995915</v>
+        <v>0.864860478451286</v>
       </c>
       <c r="W21" t="n">
-        <v>0.730495786207253</v>
+        <v>0.730651547857698</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8640830951794183</v>
+        <v>0.8641214218472654</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0366227737635</v>
+        <v>128.0399592640021</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.1520477465941</v>
+        <v>128.2017026470019</v>
       </c>
       <c r="AA21" t="n">
-        <v>128.8987833096963</v>
+        <v>129.3440382887003</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.390415195964133</v>
+        <v>7.407721238084079</v>
       </c>
       <c r="G2" t="n">
-        <v>7.48303578945446</v>
+        <v>7.491450060649029</v>
       </c>
       <c r="H2" t="n">
-        <v>8.395882070643351</v>
+        <v>8.395016033746353</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>5.008206065229923</v>
+        <v>4.971538191312902</v>
       </c>
       <c r="G3" t="n">
-        <v>5.054046681568551</v>
+        <v>5.039669872236572</v>
       </c>
       <c r="H3" t="n">
-        <v>5.150592481260932</v>
+        <v>5.145129185323924</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.059743046357616</v>
+        <v>4.168535877281947</v>
       </c>
       <c r="G4" t="n">
-        <v>4.366988520753055</v>
+        <v>4.358364588220013</v>
       </c>
       <c r="H4" t="n">
-        <v>4.564415220859675</v>
+        <v>4.714335552459916</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.66786544169128</v>
+        <v>11.67021012625146</v>
       </c>
       <c r="G5" t="n">
-        <v>12.15227416749987</v>
+        <v>12.06108156915331</v>
       </c>
       <c r="H5" t="n">
-        <v>12.84057536461028</v>
+        <v>12.83963543911982</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.916586825617892</v>
+        <v>2.859156075158237</v>
       </c>
       <c r="G6" t="n">
-        <v>55.91525830458848</v>
+        <v>66.71469946523099</v>
       </c>
       <c r="H6" t="n">
-        <v>110.4041525034457</v>
+        <v>110.4031025372064</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.22398028644545</v>
+        <v>11.02549211160407</v>
       </c>
       <c r="G7" t="n">
-        <v>11.70681009307872</v>
+        <v>11.64700856598263</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89912902679923</v>
+        <v>11.89802209738195</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.462824810572933</v>
+        <v>8.3659948887307</v>
       </c>
       <c r="G8" t="n">
-        <v>8.485342411980458</v>
+        <v>8.474110222769122</v>
       </c>
       <c r="H8" t="n">
-        <v>8.516563348227264</v>
+        <v>8.516671295700013</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.340056245713813</v>
+        <v>4.325969793524327</v>
       </c>
       <c r="G9" t="n">
-        <v>4.457872885553112</v>
+        <v>4.410704995879141</v>
       </c>
       <c r="H9" t="n">
-        <v>4.672441563331953</v>
+        <v>4.666266550096728</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.934156311681083</v>
+        <v>4.895448881684713</v>
       </c>
       <c r="G10" t="n">
-        <v>5.129856374328506</v>
+        <v>5.10333737858505</v>
       </c>
       <c r="H10" t="n">
-        <v>5.38708982870934</v>
+        <v>5.397712388702573</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>9.661051470870632</v>
+        <v>10.80701656967405</v>
       </c>
       <c r="G11" t="n">
-        <v>9.793689003916242</v>
+        <v>10.81082019345841</v>
       </c>
       <c r="H11" t="n">
-        <v>9.883457487320841</v>
+        <v>10.81626760151583</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.713862016042998</v>
+        <v>1.717620819627904</v>
       </c>
       <c r="G12" t="n">
-        <v>2.714960451336472</v>
+        <v>2.777118322693554</v>
       </c>
       <c r="H12" t="n">
-        <v>3.351738674237951</v>
+        <v>3.537717979947023</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.238001097140473</v>
+        <v>5.220591944077436</v>
       </c>
       <c r="G13" t="n">
-        <v>5.339798664991706</v>
+        <v>5.306957541592512</v>
       </c>
       <c r="H13" t="n">
-        <v>5.49875168104721</v>
+        <v>5.488543505846495</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.549316857266481</v>
+        <v>9.55904284626933</v>
       </c>
       <c r="G14" t="n">
-        <v>9.723608005306831</v>
+        <v>9.698423001815716</v>
       </c>
       <c r="H14" t="n">
-        <v>9.839341520776234</v>
+        <v>9.839476314238251</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.260670355184188</v>
+        <v>5.22261925561098</v>
       </c>
       <c r="G15" t="n">
-        <v>5.362687550074731</v>
+        <v>5.334758091973446</v>
       </c>
       <c r="H15" t="n">
-        <v>5.545209468785206</v>
+        <v>5.535984764483778</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.486446346278253</v>
+        <v>6.467302386196443</v>
       </c>
       <c r="G16" t="n">
-        <v>6.665571928695377</v>
+        <v>6.649666020763568</v>
       </c>
       <c r="H16" t="n">
-        <v>6.747839699821181</v>
+        <v>6.749136091929754</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.41361948183334</v>
+        <v>2.421420498901102</v>
       </c>
       <c r="G17" t="n">
-        <v>3.981639739749073</v>
+        <v>4.017221835667445</v>
       </c>
       <c r="H17" t="n">
-        <v>4.785120719016083</v>
+        <v>4.945533316505774</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.198107335644316</v>
+        <v>3.250367647058824</v>
       </c>
       <c r="G18" t="n">
-        <v>3.293696536909428</v>
+        <v>3.308990281635551</v>
       </c>
       <c r="H18" t="n">
-        <v>3.372869757174393</v>
+        <v>3.389588235294118</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.217566225165563</v>
+        <v>2.208828978869868</v>
       </c>
       <c r="G19" t="n">
-        <v>2.304403060109094</v>
+        <v>2.283912339375278</v>
       </c>
       <c r="H19" t="n">
-        <v>2.439635148393426</v>
+        <v>2.438113970588236</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.896992042626673</v>
+        <v>4.870570102349984</v>
       </c>
       <c r="G20" t="n">
-        <v>5.364606427688901</v>
+        <v>5.32933579975823</v>
       </c>
       <c r="H20" t="n">
-        <v>5.806240660273916</v>
+        <v>5.806428148976981</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0366227737635</v>
+        <v>128.0399592640021</v>
       </c>
       <c r="G21" t="n">
-        <v>128.1520477465941</v>
+        <v>128.201702647002</v>
       </c>
       <c r="H21" t="n">
-        <v>128.8987833096963</v>
+        <v>129.3440382887003</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E2" t="n">
+        <v>10025</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10024</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10023</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6401934217965</v>
+        <v>102.6303530194201</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.6210348468465</v>
+        <v>102.607388303476</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.01915857495004063</v>
+        <v>-0.02296471594405652</v>
       </c>
       <c r="T2" t="n">
-        <v>17.92084831171142</v>
+        <v>17.91887411185959</v>
       </c>
       <c r="U2" t="n">
-        <v>36.05590548087464</v>
+        <v>36.0543920504278</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1375506114751729</v>
+        <v>0.1388683122817788</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.722637334889993</v>
+        <v>-0.72045173657039</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1375495928229944</v>
+        <v>0.13886763947054</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.859156075158237</v>
+        <v>2.94450809818094</v>
       </c>
       <c r="Z2" t="n">
-        <v>66.71469946523099</v>
+        <v>75.53600320476531</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.4031025372064</v>
+        <v>110.5661568183036</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E3" t="n">
+        <v>14619</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14618</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14617</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.909358042005884</v>
+        <v>4.909156792994938</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966869406629901</v>
+        <v>4.966679455387762</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05751136462401766</v>
+        <v>0.05752266239282455</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344815915639666</v>
+        <v>1.344746022983074</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719320971108818</v>
+        <v>1.719258300135343</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7812815394242243</v>
+        <v>0.7813003466358438</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5695433208646259</v>
+        <v>0.5695823619959178</v>
       </c>
       <c r="X3" t="n">
-        <v>0.78024750279085</v>
+        <v>0.7802656147341658</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.208828978869868</v>
+        <v>2.179274812033199</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.283912339375278</v>
+        <v>2.251937330002357</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.438113970588236</v>
+        <v>2.383752073032747</v>
       </c>
     </row>
     <row r="4">
@@ -751,16 +751,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E4" t="n">
+        <v>10253</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
         <v>10252</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>10251</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.910368500634084</v>
+        <v>6.910021946937184</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.239905369550713</v>
+        <v>7.239576773440381</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295368689166275</v>
+        <v>0.3295548265031971</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292655493271272</v>
+        <v>1.292549975018422</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682361676067788</v>
+        <v>1.682288710359103</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676526108544037</v>
+        <v>0.8676667810117276</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7374807168755585</v>
+        <v>0.7375078579316339</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471538725201219</v>
+        <v>0.8471607458697743</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.250367647058824</v>
+        <v>3.173897869213814</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.308990281635551</v>
+        <v>3.302156820174222</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.389588235294118</v>
+        <v>3.578691334496694</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.758426470588235</v>
+        <v>2.758207200587803</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302527584850989</v>
+        <v>9.302404626249698</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3612250018251582</v>
+        <v>0.3611020432238677</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253939717587138</v>
+        <v>1.253963970092311</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750189884345819</v>
+        <v>1.750194268287937</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8662002392761822</v>
+        <v>0.8662026611246131</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212974708925951</v>
+        <v>0.7212960746814787</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8602039168574274</v>
+        <v>0.8602113333632055</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.870570102349984</v>
+        <v>4.869900068910122</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.32933579975823</v>
+        <v>5.246184875452939</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.806428148976981</v>
+        <v>5.800742683105024</v>
       </c>
     </row>
     <row r="6">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E6" t="n">
+        <v>8866</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" t="n">
         <v>8865</v>
-      </c>
-      <c r="F6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8864</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.73348561597473</v>
+        <v>6.733563338973492</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.021986514483771</v>
+        <v>7.02207192502565</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2885008985090426</v>
+        <v>0.2885085860521591</v>
       </c>
       <c r="T6" t="n">
-        <v>1.480019828499391</v>
+        <v>1.47992177100515</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908691625318766</v>
+        <v>1.908606394835888</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3045941470264492</v>
+        <v>0.3045610425559322</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.19773243613439</v>
+        <v>-0.1977394952390039</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2797880969387548</v>
+        <v>0.2797434684906245</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.467302386196443</v>
+        <v>6.452433431300514</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.649666020763567</v>
+        <v>6.616726811092832</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.749136091929754</v>
+        <v>6.715790040003266</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E7" t="n">
+        <v>14227</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14226</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14225</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581253145869947</v>
+        <v>5.581204203570927</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567831189381732</v>
+        <v>5.567778698839679</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.01342195648821472</v>
+        <v>-0.0134255047312471</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167207453873282</v>
+        <v>1.167138184868847</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510429162898177</v>
+        <v>1.510373495811545</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047390346819002</v>
+        <v>0.5047477731445078</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05296853445103156</v>
+        <v>0.05298516479317339</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025894756018432</v>
+        <v>0.5025981727752924</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.971538191312902</v>
+        <v>4.951470905814327</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.039669872236572</v>
+        <v>5.018104709716176</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.145129185323924</v>
+        <v>5.074931926465025</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E8" t="n">
+        <v>9025</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9024</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9023</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.877358694447524</v>
+        <v>7.877129321808511</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.11616137330037</v>
+        <v>8.116016201034224</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2388026788528475</v>
+        <v>0.2388868792257122</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446712473428141</v>
+        <v>1.446614318471754</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826233482768617</v>
+        <v>1.826168880130695</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078618063111659</v>
+        <v>0.8078606942846747</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274453665273254</v>
+        <v>0.6274501956762804</v>
       </c>
       <c r="X8" t="n">
-        <v>0.797876788320356</v>
+        <v>0.7978623099384136</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.895448881684713</v>
+        <v>4.818835883563609</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.10333737858505</v>
+        <v>5.041178512352625</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.397712388702573</v>
+        <v>5.266943639628443</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E9" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13889</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13888</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.612219002016129</v>
+        <v>7.612015623875009</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657790066263708</v>
+        <v>7.657593097570364</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04557106424757886</v>
+        <v>0.04557747369535346</v>
       </c>
       <c r="T9" t="n">
-        <v>1.494561299704026</v>
+        <v>1.49451009672102</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942484706890063</v>
+        <v>1.942424783919813</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565570241788571</v>
+        <v>0.7565716698946948</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5246296776436736</v>
+        <v>0.5246591828942169</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551490918321718</v>
+        <v>0.7551633811828686</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.22261925561098</v>
+        <v>5.158198236590742</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.334758091973446</v>
+        <v>5.294787231763591</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.535984764483778</v>
+        <v>5.419427689468517</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61729166578519</v>
+        <v>10.61717327144113</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3122299852928171</v>
+        <v>0.3121115909487598</v>
       </c>
       <c r="T10" t="n">
-        <v>2.05243981651836</v>
+        <v>2.052487106626596</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698107986053119</v>
+        <v>2.698157589793543</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568145599944468</v>
+        <v>0.3568248135848515</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1204466625214182</v>
+        <v>-0.120487860914209</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3363426015788475</v>
+        <v>0.3363705756388508</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.55904284626933</v>
+        <v>9.576294632428789</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.698423001815716</v>
+        <v>9.706267571723476</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.839476314238251</v>
+        <v>9.945967014080209</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E11" t="n">
+        <v>13831</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13830</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13829</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243700701424543</v>
+        <v>5.243603362255966</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578926470588235</v>
+        <v>0.4578978692138134</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217154212916308</v>
+        <v>5.217097554510511</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02654648850823374</v>
+        <v>-0.02650580774545434</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161854152472563</v>
+        <v>1.161809016434998</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483298267013617</v>
+        <v>1.483249852772454</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4292233572837483</v>
+        <v>0.4292430890157864</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.09237613510864229</v>
+        <v>-0.0923127477604726</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4274161835584696</v>
+        <v>0.4274340710116739</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.168535877281947</v>
+        <v>4.24370870202574</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.358364588220014</v>
+        <v>4.5056613927973</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.714335552459916</v>
+        <v>5.081786476152071</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E12" t="n">
+        <v>4149</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4148</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4147</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.474134555100073</v>
+        <v>7.473239151398264</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205044117647059</v>
+        <v>2.205077149155033</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.64779240946156</v>
+        <v>7.646881235850767</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1736578543614873</v>
+        <v>0.1736420844525023</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136876128412654</v>
+        <v>0.9136396511762697</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195730992306831</v>
+        <v>1.195629425454884</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8311959400913269</v>
+        <v>0.8313177000360236</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6577565082796109</v>
+        <v>0.6580043813901171</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8294244532228753</v>
+        <v>0.8295447204730897</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.325969793524327</v>
+        <v>4.320978848998554</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.410704995879141</v>
+        <v>4.404031099439464</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.666266550096728</v>
+        <v>5.048759627533772</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E13" t="n">
+        <v>6484</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6483</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6482</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.606579373650108</v>
+        <v>9.606075505167361</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.026964116144</v>
+        <v>10.02674862998137</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.420384742493891</v>
+        <v>0.4206731248140135</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691643608568783</v>
+        <v>1.691615478187331</v>
       </c>
       <c r="U13" t="n">
-        <v>2.15123386907055</v>
+        <v>2.15110800811715</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231553406913343</v>
+        <v>0.8231706783816928</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486032047922794</v>
+        <v>0.6486340296420007</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8105196419420337</v>
+        <v>0.8105038089818533</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.3659948887307</v>
+        <v>8.30845001805751</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.47411022276912</v>
+        <v>8.452030878948952</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.516671295700013</v>
+        <v>8.504805665854581</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E14" t="n">
+        <v>14071</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14070</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14069</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.12948148411401</v>
+        <v>8.129247157071784</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9075122549019609</v>
+        <v>0.9075361253979917</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199978628416979</v>
+        <v>8.199756285732827</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07049714430296847</v>
+        <v>0.07050912866104202</v>
       </c>
       <c r="T14" t="n">
-        <v>1.757026247784107</v>
+        <v>1.756907141243673</v>
       </c>
       <c r="U14" t="n">
-        <v>2.283009420160737</v>
+        <v>2.282901997148521</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7808093022640511</v>
+        <v>0.780827363431491</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5652796695706566</v>
+        <v>0.5653176918655611</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804320914676875</v>
+        <v>0.7804498070443744</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.220591944077436</v>
+        <v>5.199950017522127</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.306957541592512</v>
+        <v>5.269300047609929</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.488543505846495</v>
+        <v>5.373738130981663</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.674985294117647</v>
+        <v>4.674166054371786</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82240520066709</v>
+        <v>11.82227343674934</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1414821823596916</v>
+        <v>-0.141613946277446</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052289978127739</v>
+        <v>2.052317647612782</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697555039592728</v>
+        <v>2.697575043003574</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949809007848454</v>
+        <v>0.7949838159030088</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096207506670492</v>
+        <v>0.6096149610202404</v>
       </c>
       <c r="X15" t="n">
-        <v>0.786312379703427</v>
+        <v>0.7863233476228582</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.02549211160407</v>
+        <v>10.98505714630375</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.64700856598263</v>
+        <v>11.55674684385697</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89802209738195</v>
+        <v>11.89824839379299</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E16" t="n">
+        <v>9834</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9833</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9832</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.364266578519121</v>
+        <v>8.364020034577443</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624544129387269</v>
+        <v>8.624469794495491</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2602775508681475</v>
+        <v>0.2604497599180476</v>
       </c>
       <c r="T16" t="n">
-        <v>3.591467670912076</v>
+        <v>3.591876788120668</v>
       </c>
       <c r="U16" t="n">
-        <v>11.09303698346365</v>
+        <v>11.0926903439179</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04176593861139232</v>
+        <v>0.04173648182409201</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6098379207646232</v>
+        <v>-0.6098884635538486</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02510195033367979</v>
+        <v>0.02507240159218471</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.67021012625146</v>
+        <v>11.66188490602033</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.06108156915331</v>
+        <v>11.9309712043167</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.83963543911982</v>
+        <v>12.5872227453101</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E17" t="n">
+        <v>2378</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2377</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2376</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.498423821548822</v>
+        <v>6.496680689945309</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.414161764705882</v>
+        <v>1.415675973548861</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.863338651120654</v>
+        <v>6.86116921329772</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3649148295718319</v>
+        <v>0.3644885233524118</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02131674895441</v>
+        <v>2.020460091175063</v>
       </c>
       <c r="U17" t="n">
-        <v>2.556597063719214</v>
+        <v>2.555979285855456</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5312579160629711</v>
+        <v>0.531858427513175</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04134407838066889</v>
+        <v>0.04241842980046218</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5279030760246999</v>
+        <v>0.5285045543664828</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.717620819627904</v>
+        <v>2.428320702276426</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.777118322693554</v>
+        <v>2.923653779064621</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.537717979947023</v>
+        <v>4.267467526957439</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E18" t="n">
+        <v>3237</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3236</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3235</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.479062287480679</v>
+        <v>6.478239029666255</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.673816399864205</v>
+        <v>6.672876154162922</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1947541123835258</v>
+        <v>0.1946371244966672</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099334535634291</v>
+        <v>1.099000603708154</v>
       </c>
       <c r="U18" t="n">
-        <v>1.487478061377266</v>
+        <v>1.487194183310067</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6050922902583785</v>
+        <v>0.6054522101656887</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2250422251078293</v>
+        <v>0.2256933269686457</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6021877232688061</v>
+        <v>0.6025544912913834</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.421420498901102</v>
+        <v>3.366519468172819</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.017221835667445</v>
+        <v>4.321211807094597</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.945533316505774</v>
+        <v>5.567603618180248</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E19" t="n">
+        <v>7191</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7190</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7189</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33886270691334</v>
+        <v>10.33756175243394</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.12993829747639</v>
+        <v>11.1290260982925</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7910755905630473</v>
+        <v>0.7914643458585658</v>
       </c>
       <c r="T19" t="n">
-        <v>2.050756140746665</v>
+        <v>2.05135965163044</v>
       </c>
       <c r="U19" t="n">
-        <v>2.773812447714668</v>
+        <v>2.774598483083927</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270599514158688</v>
+        <v>0.7270913576579299</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4708149999698175</v>
+        <v>0.4708842378745464</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6786150048679285</v>
+        <v>0.6785756531963556</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.407721238084079</v>
+        <v>7.422390749609829</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.491450060649029</v>
+        <v>7.428445395235242</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.395016033746353</v>
+        <v>7.438433960486369</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E20" t="n">
+        <v>619</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>618</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>617</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>45658</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M20" t="n">
         <v>10.17</v>
       </c>
       <c r="N20" t="n">
-        <v>15.54713533225284</v>
+        <v>15.5385355987055</v>
       </c>
       <c r="O20" t="n">
         <v>19.03</v>
       </c>
       <c r="P20" t="n">
-        <v>10.80896323529412</v>
+        <v>10.80766164584864</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.38066493652289</v>
+        <v>16.37155002816282</v>
       </c>
       <c r="R20" t="n">
         <v>19.01911469282878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8335296042700525</v>
+        <v>0.8330144294573116</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8869504228486376</v>
+        <v>0.8863754598681084</v>
       </c>
       <c r="U20" t="n">
-        <v>1.263286564196537</v>
+        <v>1.262461793528511</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9368242409993496</v>
+        <v>0.9372131515709129</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7832183008847218</v>
+        <v>0.7844883578780706</v>
       </c>
       <c r="X20" t="n">
-        <v>0.8997506008946337</v>
+        <v>0.9004245400410086</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.80701656967405</v>
+        <v>10.79266592793231</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.81082019345841</v>
+        <v>10.80925518009541</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.81626760151583</v>
+        <v>10.83956141107388</v>
       </c>
     </row>
     <row r="21">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16688</v>
+        <v>16689</v>
       </c>
       <c r="E21" t="n">
+        <v>10237</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G21" t="n">
         <v>10236</v>
-      </c>
-      <c r="F21" t="n">
-        <v>10</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10235</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8714646800196</v>
+        <v>130.8711118601016</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9760085148853</v>
+        <v>130.9756256144393</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045438348657684</v>
+        <v>0.1045137543376413</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976486706293027</v>
+        <v>0.7976734768297853</v>
       </c>
       <c r="U21" t="n">
-        <v>1.04634513831057</v>
+        <v>1.046354578126214</v>
       </c>
       <c r="V21" t="n">
-        <v>0.864860478451286</v>
+        <v>0.8648888763654931</v>
       </c>
       <c r="W21" t="n">
-        <v>0.730651547857698</v>
+        <v>0.7307047879383601</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641214218472654</v>
+        <v>0.8641517627011583</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0399592640021</v>
+        <v>128.0365749414335</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.2017026470019</v>
+        <v>128.3440796433171</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.3440382887003</v>
+        <v>129.5478048836164</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.407721238084079</v>
+        <v>7.422390749609829</v>
       </c>
       <c r="G2" t="n">
-        <v>7.491450060649029</v>
+        <v>7.428445395235242</v>
       </c>
       <c r="H2" t="n">
-        <v>8.395016033746353</v>
+        <v>7.438433960486369</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.971538191312902</v>
+        <v>4.951470905814327</v>
       </c>
       <c r="G3" t="n">
-        <v>5.039669872236572</v>
+        <v>5.018104709716176</v>
       </c>
       <c r="H3" t="n">
-        <v>5.145129185323924</v>
+        <v>5.074931926465025</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.168535877281947</v>
+        <v>4.24370870202574</v>
       </c>
       <c r="G4" t="n">
-        <v>4.358364588220013</v>
+        <v>4.5056613927973</v>
       </c>
       <c r="H4" t="n">
-        <v>4.714335552459916</v>
+        <v>5.081786476152071</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.67021012625146</v>
+        <v>11.66188490602033</v>
       </c>
       <c r="G5" t="n">
-        <v>12.06108156915331</v>
+        <v>11.9309712043167</v>
       </c>
       <c r="H5" t="n">
-        <v>12.83963543911982</v>
+        <v>12.5872227453101</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.859156075158237</v>
+        <v>2.94450809818094</v>
       </c>
       <c r="G6" t="n">
-        <v>66.71469946523099</v>
+        <v>75.53600320476531</v>
       </c>
       <c r="H6" t="n">
-        <v>110.4031025372064</v>
+        <v>110.5661568183036</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>11.02549211160407</v>
+        <v>10.98505714630375</v>
       </c>
       <c r="G7" t="n">
-        <v>11.64700856598263</v>
+        <v>11.55674684385697</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89802209738195</v>
+        <v>11.89824839379299</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.3659948887307</v>
+        <v>8.30845001805751</v>
       </c>
       <c r="G8" t="n">
-        <v>8.474110222769122</v>
+        <v>8.452030878948953</v>
       </c>
       <c r="H8" t="n">
-        <v>8.516671295700013</v>
+        <v>8.504805665854581</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.325969793524327</v>
+        <v>4.320978848998554</v>
       </c>
       <c r="G9" t="n">
-        <v>4.410704995879141</v>
+        <v>4.404031099439464</v>
       </c>
       <c r="H9" t="n">
-        <v>4.666266550096728</v>
+        <v>5.048759627533772</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.895448881684713</v>
+        <v>4.818835883563609</v>
       </c>
       <c r="G10" t="n">
-        <v>5.10333737858505</v>
+        <v>5.041178512352625</v>
       </c>
       <c r="H10" t="n">
-        <v>5.397712388702573</v>
+        <v>5.266943639628443</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.80701656967405</v>
+        <v>10.79266592793231</v>
       </c>
       <c r="G11" t="n">
-        <v>10.81082019345841</v>
+        <v>10.80925518009541</v>
       </c>
       <c r="H11" t="n">
-        <v>10.81626760151583</v>
+        <v>10.83956141107388</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>1.717620819627904</v>
+        <v>2.428320702276426</v>
       </c>
       <c r="G12" t="n">
-        <v>2.777118322693554</v>
+        <v>2.923653779064621</v>
       </c>
       <c r="H12" t="n">
-        <v>3.537717979947023</v>
+        <v>4.267467526957439</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.220591944077436</v>
+        <v>5.199950017522127</v>
       </c>
       <c r="G13" t="n">
-        <v>5.306957541592512</v>
+        <v>5.269300047609929</v>
       </c>
       <c r="H13" t="n">
-        <v>5.488543505846495</v>
+        <v>5.373738130981663</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.55904284626933</v>
+        <v>9.576294632428789</v>
       </c>
       <c r="G14" t="n">
-        <v>9.698423001815716</v>
+        <v>9.706267571723476</v>
       </c>
       <c r="H14" t="n">
-        <v>9.839476314238251</v>
+        <v>9.945967014080209</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.22261925561098</v>
+        <v>5.158198236590742</v>
       </c>
       <c r="G15" t="n">
-        <v>5.334758091973446</v>
+        <v>5.294787231763591</v>
       </c>
       <c r="H15" t="n">
-        <v>5.535984764483778</v>
+        <v>5.419427689468517</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.467302386196443</v>
+        <v>6.452433431300514</v>
       </c>
       <c r="G16" t="n">
-        <v>6.649666020763568</v>
+        <v>6.616726811092832</v>
       </c>
       <c r="H16" t="n">
-        <v>6.749136091929754</v>
+        <v>6.715790040003266</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>2.421420498901102</v>
+        <v>3.366519468172819</v>
       </c>
       <c r="G17" t="n">
-        <v>4.017221835667445</v>
+        <v>4.321211807094598</v>
       </c>
       <c r="H17" t="n">
-        <v>4.945533316505774</v>
+        <v>5.567603618180248</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.250367647058824</v>
+        <v>3.173897869213814</v>
       </c>
       <c r="G18" t="n">
-        <v>3.308990281635551</v>
+        <v>3.302156820174223</v>
       </c>
       <c r="H18" t="n">
-        <v>3.389588235294118</v>
+        <v>3.578691334496694</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.208828978869868</v>
+        <v>2.179274812033199</v>
       </c>
       <c r="G19" t="n">
-        <v>2.283912339375278</v>
+        <v>2.251937330002357</v>
       </c>
       <c r="H19" t="n">
-        <v>2.438113970588236</v>
+        <v>2.383752073032747</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.870570102349984</v>
+        <v>4.869900068910122</v>
       </c>
       <c r="G20" t="n">
-        <v>5.32933579975823</v>
+        <v>5.246184875452939</v>
       </c>
       <c r="H20" t="n">
-        <v>5.806428148976981</v>
+        <v>5.800742683105024</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0399592640021</v>
+        <v>128.0365749414335</v>
       </c>
       <c r="G21" t="n">
-        <v>128.201702647002</v>
+        <v>128.3440796433171</v>
       </c>
       <c r="H21" t="n">
-        <v>129.3440382887003</v>
+        <v>129.5478048836164</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/metricas_dwlt_estaciones.xlsx
+++ b/outputs/metricas_dwlt_estaciones.xlsx
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E2" t="n">
+        <v>10026</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
         <v>10025</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>10024</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -599,13 +599,13 @@
         <v>36161</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M2" t="n">
         <v>1.78</v>
       </c>
       <c r="N2" t="n">
-        <v>102.6303530194201</v>
+        <v>102.6205066001663</v>
       </c>
       <c r="O2" t="n">
         <v>118.97</v>
@@ -614,37 +614,37 @@
         <v>1.843123209169055</v>
       </c>
       <c r="Q2" t="n">
-        <v>102.607388303476</v>
+        <v>102.5931657179678</v>
       </c>
       <c r="R2" t="n">
         <v>118.8919225199131</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02296471594405652</v>
+        <v>-0.02734088219847836</v>
       </c>
       <c r="T2" t="n">
-        <v>17.91887411185959</v>
+        <v>17.91768909780116</v>
       </c>
       <c r="U2" t="n">
-        <v>36.0543920504278</v>
+        <v>36.0553248564454</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1388683122817788</v>
+        <v>0.1401580122222274</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.72045173657039</v>
+        <v>-0.7185017679962451</v>
       </c>
       <c r="X2" t="n">
-        <v>0.13886763947054</v>
+        <v>0.1401576954494871</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.94450809818094</v>
+        <v>2.975828943454343</v>
       </c>
       <c r="Z2" t="n">
-        <v>75.53600320476531</v>
+        <v>80.91433054852874</v>
       </c>
       <c r="AA2" t="n">
-        <v>110.5661568183036</v>
+        <v>110.2664412526513</v>
       </c>
     </row>
     <row r="3">
@@ -662,16 +662,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E3" t="n">
+        <v>14620</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>14619</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>14618</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -688,13 +688,13 @@
         <v>30317</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M3" t="n">
         <v>0.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.909156792994938</v>
+        <v>4.908950954237636</v>
       </c>
       <c r="O3" t="n">
         <v>11.07</v>
@@ -703,37 +703,37 @@
         <v>0.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.966679455387762</v>
+        <v>4.966491300692143</v>
       </c>
       <c r="R3" t="n">
         <v>11.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05752266239282455</v>
+        <v>0.05754034645450718</v>
       </c>
       <c r="T3" t="n">
-        <v>1.344746022983074</v>
+        <v>1.344678651577674</v>
       </c>
       <c r="U3" t="n">
-        <v>1.719258300135343</v>
+        <v>1.719196561490579</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7813003466358438</v>
+        <v>0.7813193129006681</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5695823619959178</v>
+        <v>0.5696226494754484</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7802656147341658</v>
+        <v>0.7802836051556702</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.179274812033199</v>
+        <v>2.150881791483113</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.251937330002357</v>
+        <v>2.225661007061721</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.383752073032747</v>
+        <v>2.331233021292217</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E4" t="n">
         <v>10253</v>
@@ -760,7 +760,7 @@
         <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10252</v>
+        <v>10253</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -777,13 +777,13 @@
         <v>35065</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M4" t="n">
         <v>0.005</v>
       </c>
       <c r="N4" t="n">
-        <v>6.910021946937184</v>
+        <v>6.909661074807374</v>
       </c>
       <c r="O4" t="n">
         <v>12.93</v>
@@ -792,37 +792,37 @@
         <v>0.3676769446391031</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.239576773440381</v>
+        <v>7.239112466735863</v>
       </c>
       <c r="R4" t="n">
         <v>12.72990889978977</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3295548265031971</v>
+        <v>0.3294513919284887</v>
       </c>
       <c r="T4" t="n">
-        <v>1.292549975018422</v>
+        <v>1.292410023992817</v>
       </c>
       <c r="U4" t="n">
-        <v>1.682288710359103</v>
+        <v>1.682184810210951</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8676667810117276</v>
+        <v>0.8676885492328213</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7375078579316339</v>
+        <v>0.737547182802971</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8471607458697743</v>
+        <v>0.8472055693195504</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.173897869213814</v>
+        <v>3.181960352422907</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.302156820174222</v>
+        <v>3.304003187825538</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.578691334496694</v>
+        <v>3.496518272400334</v>
       </c>
     </row>
     <row r="5">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E5" t="n">
         <v>2710</v>
@@ -878,40 +878,40 @@
         <v>15.51</v>
       </c>
       <c r="P5" t="n">
-        <v>2.758207200587803</v>
+        <v>2.75798825256975</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.302404626249698</v>
+        <v>9.302284779643362</v>
       </c>
       <c r="R5" t="n">
         <v>15.38127820602663</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3611020432238677</v>
+        <v>0.3609821966175324</v>
       </c>
       <c r="T5" t="n">
-        <v>1.253963970092311</v>
+        <v>1.253989156906</v>
       </c>
       <c r="U5" t="n">
-        <v>1.750194268287937</v>
+        <v>1.750199988890713</v>
       </c>
       <c r="V5" t="n">
-        <v>0.8662026611246131</v>
+        <v>0.866204813272385</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7212960746814787</v>
+        <v>0.721294252761383</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8602113333632055</v>
+        <v>0.8602183440303083</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.869900068910122</v>
+        <v>4.871414572875782</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.246184875452939</v>
+        <v>5.19583926257148</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.800742683105024</v>
+        <v>5.726413692731685</v>
       </c>
     </row>
     <row r="6">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E6" t="n">
         <v>8866</v>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8865</v>
+        <v>8866</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -955,13 +955,13 @@
         <v>36892</v>
       </c>
       <c r="L6" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M6" t="n">
         <v>1.52</v>
       </c>
       <c r="N6" t="n">
-        <v>6.733563338973492</v>
+        <v>6.733623843898037</v>
       </c>
       <c r="O6" t="n">
         <v>10.6125</v>
@@ -970,37 +970,37 @@
         <v>1.616683937823834</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.02207192502565</v>
+        <v>7.022006934507797</v>
       </c>
       <c r="R6" t="n">
         <v>10.19050035038543</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2885085860521591</v>
+        <v>0.2883830906097593</v>
       </c>
       <c r="T6" t="n">
-        <v>1.47992177100515</v>
+        <v>1.479832553395997</v>
       </c>
       <c r="U6" t="n">
-        <v>1.908606394835888</v>
+        <v>1.908528354104267</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3045610425559322</v>
+        <v>0.304557461770588</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.1977394952390039</v>
+        <v>-0.1977638642666655</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2797434684906245</v>
+        <v>0.2797509018709516</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.452433431300514</v>
+        <v>6.381102378142341</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.616726811092832</v>
+        <v>6.583618469081034</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.715790040003266</v>
+        <v>6.711995028099045</v>
       </c>
     </row>
     <row r="7">
@@ -1018,16 +1018,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E7" t="n">
+        <v>14228</v>
+      </c>
+      <c r="F7" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" t="n">
         <v>14227</v>
-      </c>
-      <c r="F7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" t="n">
-        <v>14226</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,13 +1044,13 @@
         <v>31048</v>
       </c>
       <c r="L7" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M7" t="n">
         <v>1.025</v>
       </c>
       <c r="N7" t="n">
-        <v>5.581204203570927</v>
+        <v>5.581147360652281</v>
       </c>
       <c r="O7" t="n">
         <v>10.01</v>
@@ -1059,37 +1059,37 @@
         <v>1.1435</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.567778698839679</v>
+        <v>5.567707221829661</v>
       </c>
       <c r="R7" t="n">
         <v>9.695129642606867</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0134255047312471</v>
+        <v>-0.01344013882262098</v>
       </c>
       <c r="T7" t="n">
-        <v>1.167138184868847</v>
+        <v>1.167084647303406</v>
       </c>
       <c r="U7" t="n">
-        <v>1.510373495811545</v>
+        <v>1.510326062908891</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5047477731445078</v>
+        <v>0.5047558869009385</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05298516479317339</v>
+        <v>0.05299615225730514</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5025981727752924</v>
+        <v>0.5026066851421211</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.951470905814327</v>
+        <v>4.930685139429564</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.018104709716176</v>
+        <v>5.00339928342277</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.074931926465025</v>
+        <v>5.051737517240016</v>
       </c>
     </row>
     <row r="8">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E8" t="n">
+        <v>9026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" t="n">
         <v>9025</v>
-      </c>
-      <c r="F8" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9024</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1133,13 +1133,13 @@
         <v>36161</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M8" t="n">
         <v>0.16</v>
       </c>
       <c r="N8" t="n">
-        <v>7.877129321808511</v>
+        <v>7.876887257617729</v>
       </c>
       <c r="O8" t="n">
         <v>15.14</v>
@@ -1148,37 +1148,37 @@
         <v>0.6453438395415473</v>
       </c>
       <c r="Q8" t="n">
-        <v>8.116016201034224</v>
+        <v>8.115837105028387</v>
       </c>
       <c r="R8" t="n">
         <v>14.26297827610371</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2388868792257122</v>
+        <v>0.2389498474106584</v>
       </c>
       <c r="T8" t="n">
-        <v>1.446614318471754</v>
+        <v>1.446516052246957</v>
       </c>
       <c r="U8" t="n">
-        <v>1.826168880130695</v>
+        <v>1.826095366888119</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8078606942846747</v>
+        <v>0.807863206912252</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6274501956762804</v>
+        <v>0.6274609164852973</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7978623099384136</v>
+        <v>0.797853774270515</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.818835883563609</v>
+        <v>4.764292458331322</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.041178512352625</v>
+        <v>4.994657804820511</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.266943639628443</v>
+        <v>5.218376753554645</v>
       </c>
     </row>
     <row r="9">
@@ -1196,16 +1196,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E9" t="n">
+        <v>13891</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
         <v>13890</v>
-      </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13889</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1222,13 +1222,13 @@
         <v>31778</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M9" t="n">
         <v>0.06</v>
       </c>
       <c r="N9" t="n">
-        <v>7.612015623875009</v>
+        <v>7.611813354931606</v>
       </c>
       <c r="O9" t="n">
         <v>14.03</v>
@@ -1237,37 +1237,37 @@
         <v>0.409614576033637</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.657593097570364</v>
+        <v>7.657392629727465</v>
       </c>
       <c r="R9" t="n">
         <v>13.66547972483708</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04557747369535346</v>
+        <v>0.04557927479586086</v>
       </c>
       <c r="T9" t="n">
-        <v>1.49451009672102</v>
+        <v>1.494454068628206</v>
       </c>
       <c r="U9" t="n">
-        <v>1.942424783919813</v>
+        <v>1.942362115990856</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7565716698946948</v>
+        <v>0.7565871654135065</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5246591828942169</v>
+        <v>0.5246896613534281</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7551633811828686</v>
+        <v>0.7551787062391889</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.158198236590742</v>
+        <v>5.116181955096716</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.294787231763591</v>
+        <v>5.263307288412771</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.419427689468517</v>
+        <v>5.361600587371512</v>
       </c>
     </row>
     <row r="10">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E10" t="n">
         <v>3737</v>
@@ -1326,37 +1326,37 @@
         <v>4.255</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.61717327144113</v>
+        <v>10.61705334931016</v>
       </c>
       <c r="R10" t="n">
         <v>14.31670311368574</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3121115909487598</v>
+        <v>0.3119916688177878</v>
       </c>
       <c r="T10" t="n">
-        <v>2.052487106626596</v>
+        <v>2.052529428273189</v>
       </c>
       <c r="U10" t="n">
-        <v>2.698157589793543</v>
+        <v>2.698204420852664</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3568248135848515</v>
+        <v>0.356837871736162</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.120487860914209</v>
+        <v>-0.1205267571512865</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3363705756388508</v>
+        <v>0.3364019047413548</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.576294632428789</v>
+        <v>9.490076015867068</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.706267571723476</v>
+        <v>9.794306710035501</v>
       </c>
       <c r="AA10" t="n">
-        <v>9.945967014080209</v>
+        <v>10.92479894014703</v>
       </c>
     </row>
     <row r="11">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E11" t="n">
+        <v>13832</v>
+      </c>
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
         <v>13831</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" t="n">
-        <v>13830</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1400,52 +1400,52 @@
         <v>31413</v>
       </c>
       <c r="L11" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M11" t="n">
         <v>0.438</v>
       </c>
       <c r="N11" t="n">
-        <v>5.243603362255966</v>
+        <v>5.243540561058492</v>
       </c>
       <c r="O11" t="n">
         <v>10.15</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4578978692138134</v>
+        <v>0.4579030837004405</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.217097554510511</v>
+        <v>5.2170371100722</v>
       </c>
       <c r="R11" t="n">
         <v>9.96782041998552</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.02650580774545434</v>
+        <v>-0.02650345098629179</v>
       </c>
       <c r="T11" t="n">
-        <v>1.161809016434998</v>
+        <v>1.161727306651721</v>
       </c>
       <c r="U11" t="n">
-        <v>1.483249852772454</v>
+        <v>1.483193481715616</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4292430890157864</v>
+        <v>0.4292594939922887</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0923127477604726</v>
+        <v>-0.09227911487965712</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4274340710116739</v>
+        <v>0.4274502578848689</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.24370870202574</v>
+        <v>4.069848874204602</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5056613927973</v>
+        <v>4.607848468541699</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.081786476152071</v>
+        <v>5.455567566903852</v>
       </c>
     </row>
     <row r="12">
@@ -1463,16 +1463,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E12" t="n">
+        <v>4150</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" t="n">
         <v>4149</v>
-      </c>
-      <c r="F12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4148</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1489,52 +1489,52 @@
         <v>41640</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M12" t="n">
         <v>2.195</v>
       </c>
       <c r="N12" t="n">
-        <v>7.473239151398264</v>
+        <v>7.472374909616775</v>
       </c>
       <c r="O12" t="n">
         <v>19.178</v>
       </c>
       <c r="P12" t="n">
-        <v>2.205077149155033</v>
+        <v>2.20511013215859</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.646881235850767</v>
+        <v>7.645967740067685</v>
       </c>
       <c r="R12" t="n">
         <v>16.78633667621756</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1736420844525023</v>
+        <v>0.1735928304509096</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9136396511762697</v>
+        <v>0.9135210157863671</v>
       </c>
       <c r="U12" t="n">
-        <v>1.195629425454884</v>
+        <v>1.195486757749265</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8313177000360236</v>
+        <v>0.8314450999029892</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6580043813901171</v>
+        <v>0.658256926424848</v>
       </c>
       <c r="X12" t="n">
-        <v>0.8295447204730897</v>
+        <v>0.8296724632923537</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.320978848998554</v>
+        <v>4.291847932012725</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.404031099439464</v>
+        <v>4.447259244732281</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.048759627533772</v>
+        <v>5.261474665264195</v>
       </c>
     </row>
     <row r="13">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E13" t="n">
+        <v>6485</v>
+      </c>
+      <c r="F13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" t="n">
         <v>6484</v>
-      </c>
-      <c r="F13" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6483</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1578,13 +1578,13 @@
         <v>39083</v>
       </c>
       <c r="L13" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
       </c>
       <c r="N13" t="n">
-        <v>9.606075505167361</v>
+        <v>9.605567165330044</v>
       </c>
       <c r="O13" t="n">
         <v>16.215</v>
@@ -1593,37 +1593,37 @@
         <v>2.866674842326559</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.02674862998137</v>
+        <v>10.02653430527363</v>
       </c>
       <c r="R13" t="n">
         <v>16.20563653352021</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4206731248140135</v>
+        <v>0.4209671399435899</v>
       </c>
       <c r="T13" t="n">
-        <v>1.691615478187331</v>
+        <v>1.691594796210649</v>
       </c>
       <c r="U13" t="n">
-        <v>2.15110800811715</v>
+        <v>2.150994788191994</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8231706783816928</v>
+        <v>0.8231844240901107</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6486340296420007</v>
+        <v>0.648661523915858</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8105038089818533</v>
+        <v>0.8104862542112194</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.30845001805751</v>
+        <v>8.095916956552648</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.452030878948952</v>
+        <v>8.414631067479345</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.504805665854581</v>
+        <v>8.504605235412651</v>
       </c>
     </row>
     <row r="14">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E14" t="n">
+        <v>14072</v>
+      </c>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
         <v>14071</v>
-      </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
-        <v>14070</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1667,52 +1667,52 @@
         <v>30682</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M14" t="n">
         <v>0.26</v>
       </c>
       <c r="N14" t="n">
-        <v>8.129247157071784</v>
+        <v>8.129009132257835</v>
       </c>
       <c r="O14" t="n">
         <v>34.002</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9075361253979917</v>
+        <v>0.9075599608418992</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.199756285732827</v>
+        <v>8.199533929339131</v>
       </c>
       <c r="R14" t="n">
         <v>14.32</v>
       </c>
       <c r="S14" t="n">
-        <v>0.07050912866104202</v>
+        <v>0.07052479708129507</v>
       </c>
       <c r="T14" t="n">
-        <v>1.756907141243673</v>
+        <v>1.756791903163342</v>
       </c>
       <c r="U14" t="n">
-        <v>2.282901997148521</v>
+        <v>2.282800757222165</v>
       </c>
       <c r="V14" t="n">
-        <v>0.780827363431491</v>
+        <v>0.7808444975098474</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5653176918655611</v>
+        <v>0.5653542535218699</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7804498070443744</v>
+        <v>0.7804665355412211</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.199950017522127</v>
+        <v>5.182085354725964</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.269300047609929</v>
+        <v>5.251798942180962</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.373738130981663</v>
+        <v>5.333237217994927</v>
       </c>
     </row>
     <row r="15">
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E15" t="n">
         <v>3099</v>
@@ -1768,40 +1768,40 @@
         <v>30.745</v>
       </c>
       <c r="P15" t="n">
-        <v>4.674166054371786</v>
+        <v>4.673348017621145</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.82227343674934</v>
+        <v>11.82214649833608</v>
       </c>
       <c r="R15" t="n">
         <v>21.32952932657494</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.141613946277446</v>
+        <v>-0.1417408846907007</v>
       </c>
       <c r="T15" t="n">
-        <v>2.052317647612782</v>
+        <v>2.052342338424996</v>
       </c>
       <c r="U15" t="n">
-        <v>2.697575043003574</v>
+        <v>2.697594903444394</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7949838159030088</v>
+        <v>0.7949867055369728</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6096149610202404</v>
+        <v>0.6096092127111992</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7863233476228582</v>
+        <v>0.7863342903167907</v>
       </c>
       <c r="Y15" t="n">
-        <v>10.98505714630375</v>
+        <v>10.9146802566502</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.55674684385697</v>
+        <v>11.47024104993337</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.89824839379299</v>
+        <v>11.8986089989068</v>
       </c>
     </row>
     <row r="16">
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E16" t="n">
+        <v>9835</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
         <v>9834</v>
-      </c>
-      <c r="F16" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" t="n">
-        <v>9833</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1845,13 +1845,13 @@
         <v>35804</v>
       </c>
       <c r="L16" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M16" t="n">
         <v>0.26</v>
       </c>
       <c r="N16" t="n">
-        <v>8.364020034577443</v>
+        <v>8.363813199105145</v>
       </c>
       <c r="O16" t="n">
         <v>131.9</v>
@@ -1860,37 +1860,37 @@
         <v>0.5268935553946416</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.624469794495491</v>
+        <v>8.624373071903522</v>
       </c>
       <c r="R16" t="n">
         <v>131.7868211440985</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2604497599180476</v>
+        <v>0.2605598727983763</v>
       </c>
       <c r="T16" t="n">
-        <v>3.591876788120668</v>
+        <v>3.59225820027089</v>
       </c>
       <c r="U16" t="n">
-        <v>11.0926903439179</v>
+        <v>11.09231864172644</v>
       </c>
       <c r="V16" t="n">
-        <v>0.04173648182409201</v>
+        <v>0.04171001288694214</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6098884635538486</v>
+        <v>-0.6099354251380775</v>
       </c>
       <c r="X16" t="n">
-        <v>0.02507240159218471</v>
+        <v>0.0250462350960402</v>
       </c>
       <c r="Y16" t="n">
-        <v>11.66188490602033</v>
+        <v>11.67317419041749</v>
       </c>
       <c r="Z16" t="n">
-        <v>11.9309712043167</v>
+        <v>11.84462858314012</v>
       </c>
       <c r="AA16" t="n">
-        <v>12.5872227453101</v>
+        <v>12.29480447072659</v>
       </c>
     </row>
     <row r="17">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E17" t="n">
+        <v>2379</v>
+      </c>
+      <c r="F17" t="n">
+        <v>10</v>
+      </c>
+      <c r="G17" t="n">
         <v>2378</v>
-      </c>
-      <c r="F17" t="n">
-        <v>10</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2377</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1934,52 +1934,52 @@
         <v>43252</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>6.496680689945309</v>
+        <v>6.494915895710681</v>
       </c>
       <c r="O17" t="n">
         <v>12.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.415675973548861</v>
+        <v>1.416938325991189</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.86116921329772</v>
+        <v>6.859011435850739</v>
       </c>
       <c r="R17" t="n">
         <v>12.15775235336712</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3644885233524118</v>
+        <v>0.3640955401400583</v>
       </c>
       <c r="T17" t="n">
-        <v>2.020460091175063</v>
+        <v>2.019635178994044</v>
       </c>
       <c r="U17" t="n">
-        <v>2.555979285855456</v>
+        <v>2.555376646656593</v>
       </c>
       <c r="V17" t="n">
-        <v>0.531858427513175</v>
+        <v>0.5324572448836055</v>
       </c>
       <c r="W17" t="n">
-        <v>0.04241842980046218</v>
+        <v>0.04350561296634237</v>
       </c>
       <c r="X17" t="n">
-        <v>0.5285045543664828</v>
+        <v>0.5291037257120532</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.428320702276426</v>
+        <v>2.42901347388417</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.923653779064621</v>
+        <v>3.109052148873424</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.267467526957439</v>
+        <v>4.373651612063481</v>
       </c>
     </row>
     <row r="18">
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E18" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10</v>
+      </c>
+      <c r="G18" t="n">
         <v>3237</v>
-      </c>
-      <c r="F18" t="n">
-        <v>10</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3236</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2023,13 +2023,13 @@
         <v>42370</v>
       </c>
       <c r="L18" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M18" t="n">
         <v>1.81</v>
       </c>
       <c r="N18" t="n">
-        <v>6.478239029666255</v>
+        <v>6.477426320667283</v>
       </c>
       <c r="O18" t="n">
         <v>18.492</v>
@@ -2038,37 +2038,37 @@
         <v>1.826106587712805</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.672876154162922</v>
+        <v>6.671940610170693</v>
       </c>
       <c r="R18" t="n">
         <v>14.92762307692291</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1946371244966672</v>
+        <v>0.1945142895034078</v>
       </c>
       <c r="T18" t="n">
-        <v>1.099000603708154</v>
+        <v>1.09866568198048</v>
       </c>
       <c r="U18" t="n">
-        <v>1.487194183310067</v>
+        <v>1.486918199494539</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6054522101656887</v>
+        <v>0.6058011176596961</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2256933269686457</v>
+        <v>0.2263205890156228</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6025544912913834</v>
+        <v>0.6029108188996035</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.366519468172819</v>
+        <v>3.065100466388778</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.321211807094597</v>
+        <v>4.427640372361481</v>
       </c>
       <c r="AA18" t="n">
-        <v>5.567603618180248</v>
+        <v>5.851688262856731</v>
       </c>
     </row>
     <row r="19">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E19" t="n">
+        <v>7192</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10</v>
+      </c>
+      <c r="G19" t="n">
         <v>7191</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7190</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2112,13 +2112,13 @@
         <v>37987</v>
       </c>
       <c r="L19" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M19" t="n">
         <v>0.04</v>
       </c>
       <c r="N19" t="n">
-        <v>10.33756175243394</v>
+        <v>10.33624794882492</v>
       </c>
       <c r="O19" t="n">
         <v>24.588</v>
@@ -2127,37 +2127,37 @@
         <v>3.790455501051156</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.1290260982925</v>
+        <v>11.12812323577417</v>
       </c>
       <c r="R19" t="n">
         <v>17.53862298528381</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7914643458585658</v>
+        <v>0.7918752869492509</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05135965163044</v>
+        <v>2.0519559141632</v>
       </c>
       <c r="U19" t="n">
-        <v>2.774598483083927</v>
+        <v>2.775412154571399</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7270913576579299</v>
+        <v>0.7271211058638399</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4708842378745464</v>
+        <v>0.4709515563977114</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6785756531963556</v>
+        <v>0.678529178107754</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.422390749609829</v>
+        <v>7.373783103762445</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.428445395235242</v>
+        <v>7.641359266893268</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.438433960486369</v>
+        <v>9.483260125984224</v>
       </c>
     </row>
     <row r="20">
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E20" t="n">
+        <v>620</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10</v>
+      </c>
+      <c r="G20" t="n">
         <v>619</v>
-      </c>
-      <c r="F20" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" t="n">
-        <v>618</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2201,52 +2201,52 @@
         <v>45658</v>
       </c>
       <c r="L20" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M20" t="n">
         <v>10.17</v>
       </c>
       <c r="N20" t="n">
-        <v>15.5385355987055</v>
+        <v>15.53037964458805</v>
       </c>
       <c r="O20" t="n">
         <v>19.03</v>
       </c>
       <c r="P20" t="n">
-        <v>10.80766164584864</v>
+        <v>10.80578193832599</v>
       </c>
       <c r="Q20" t="n">
-        <v>16.37155002816282</v>
+        <v>16.36246131691289</v>
       </c>
       <c r="R20" t="n">
         <v>19.01911469282878</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8330144294573116</v>
+        <v>0.8320816723248445</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8863754598681084</v>
+        <v>0.8853762187692525</v>
       </c>
       <c r="U20" t="n">
-        <v>1.262461793528511</v>
+        <v>1.261488999175827</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9372131515709129</v>
+        <v>0.9375384673387651</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7844883578780706</v>
+        <v>0.785665515605934</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9004245400410086</v>
+        <v>0.9012171840144266</v>
       </c>
       <c r="Y20" t="n">
-        <v>10.79266592793231</v>
+        <v>10.79127888241834</v>
       </c>
       <c r="Z20" t="n">
-        <v>10.80925518009541</v>
+        <v>10.80724653607479</v>
       </c>
       <c r="AA20" t="n">
-        <v>10.83956141107388</v>
+        <v>10.82395906754772</v>
       </c>
     </row>
     <row r="21">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16689</v>
+        <v>16690</v>
       </c>
       <c r="E21" t="n">
         <v>10237</v>
@@ -2273,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>10236</v>
+        <v>10237</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2290,13 +2290,13 @@
         <v>36039</v>
       </c>
       <c r="L21" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="M21" t="n">
         <v>125.4</v>
       </c>
       <c r="N21" t="n">
-        <v>130.8711118601016</v>
+        <v>130.8707669239035</v>
       </c>
       <c r="O21" t="n">
         <v>135.52</v>
@@ -2305,37 +2305,37 @@
         <v>125.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>130.9756256144393</v>
+        <v>130.9753584184409</v>
       </c>
       <c r="R21" t="n">
         <v>135.52</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1045137543376413</v>
+        <v>0.1045914945373727</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7976734768297853</v>
+        <v>0.7976783616021335</v>
       </c>
       <c r="U21" t="n">
-        <v>1.046354578126214</v>
+        <v>1.046341146593539</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8648888763654931</v>
+        <v>0.864915864325453</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7307047879383601</v>
+        <v>0.7307660521977413</v>
       </c>
       <c r="X21" t="n">
-        <v>0.8641517627011583</v>
+        <v>0.8641736514562061</v>
       </c>
       <c r="Y21" t="n">
-        <v>128.0365749414335</v>
+        <v>128.035504300431</v>
       </c>
       <c r="Z21" t="n">
-        <v>128.3440796433171</v>
+        <v>128.4669467051054</v>
       </c>
       <c r="AA21" t="n">
-        <v>129.5478048836164</v>
+        <v>129.6620647167807</v>
       </c>
     </row>
   </sheetData>
@@ -2404,22 +2404,22 @@
         <v>9043370</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>7.422390749609829</v>
+        <v>7.373783103762445</v>
       </c>
       <c r="G2" t="n">
-        <v>7.428445395235242</v>
+        <v>7.641359266893268</v>
       </c>
       <c r="H2" t="n">
-        <v>7.438433960486369</v>
+        <v>9.483260125984224</v>
       </c>
     </row>
     <row r="3">
@@ -2432,22 +2432,22 @@
         <v>9036028</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4.951470905814327</v>
+        <v>4.930685139429564</v>
       </c>
       <c r="G3" t="n">
-        <v>5.018104709716176</v>
+        <v>5.00339928342277</v>
       </c>
       <c r="H3" t="n">
-        <v>5.074931926465025</v>
+        <v>5.051737517240016</v>
       </c>
     </row>
     <row r="4">
@@ -2460,22 +2460,22 @@
         <v>9040208</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4.24370870202574</v>
+        <v>4.069848874204602</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5056613927973</v>
+        <v>4.607848468541699</v>
       </c>
       <c r="H4" t="n">
-        <v>5.081786476152071</v>
+        <v>5.455567566903852</v>
       </c>
     </row>
     <row r="5">
@@ -2488,22 +2488,22 @@
         <v>9053555</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>11.66188490602033</v>
+        <v>11.67317419041749</v>
       </c>
       <c r="G5" t="n">
-        <v>11.9309712043167</v>
+        <v>11.84462858314012</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5872227453101</v>
+        <v>12.29480447072659</v>
       </c>
     </row>
     <row r="6">
@@ -2516,22 +2516,22 @@
         <v>9038134</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2.94450809818094</v>
+        <v>2.975828943454343</v>
       </c>
       <c r="G6" t="n">
-        <v>75.53600320476531</v>
+        <v>80.91433054852874</v>
       </c>
       <c r="H6" t="n">
-        <v>110.5661568183036</v>
+        <v>110.2664412526513</v>
       </c>
     </row>
     <row r="7">
@@ -2544,22 +2544,22 @@
         <v>9044756</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>10.98505714630375</v>
+        <v>10.9146802566502</v>
       </c>
       <c r="G7" t="n">
-        <v>11.55674684385697</v>
+        <v>11.47024104993337</v>
       </c>
       <c r="H7" t="n">
-        <v>11.89824839379299</v>
+        <v>11.8986089989068</v>
       </c>
     </row>
     <row r="8">
@@ -2572,22 +2572,22 @@
         <v>9042214</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E8" t="n">
         <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>8.30845001805751</v>
+        <v>8.095916956552648</v>
       </c>
       <c r="G8" t="n">
-        <v>8.452030878948953</v>
+        <v>8.414631067479345</v>
       </c>
       <c r="H8" t="n">
-        <v>8.504805665854581</v>
+        <v>8.504605235412651</v>
       </c>
     </row>
     <row r="9">
@@ -2600,22 +2600,22 @@
         <v>9043597</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E9" t="n">
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>4.320978848998554</v>
+        <v>4.291847932012725</v>
       </c>
       <c r="G9" t="n">
-        <v>4.404031099439464</v>
+        <v>4.447259244732282</v>
       </c>
       <c r="H9" t="n">
-        <v>5.048759627533772</v>
+        <v>5.261474665264195</v>
       </c>
     </row>
     <row r="10">
@@ -2628,22 +2628,22 @@
         <v>9040454</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>4.818835883563609</v>
+        <v>4.764292458331322</v>
       </c>
       <c r="G10" t="n">
-        <v>5.041178512352625</v>
+        <v>4.994657804820511</v>
       </c>
       <c r="H10" t="n">
-        <v>5.266943639628443</v>
+        <v>5.218376753554645</v>
       </c>
     </row>
     <row r="11">
@@ -2656,22 +2656,22 @@
         <v>9038835</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>10.79266592793231</v>
+        <v>10.79127888241834</v>
       </c>
       <c r="G11" t="n">
-        <v>10.80925518009541</v>
+        <v>10.80724653607479</v>
       </c>
       <c r="H11" t="n">
-        <v>10.83956141107388</v>
+        <v>10.82395906754772</v>
       </c>
     </row>
     <row r="12">
@@ -2684,22 +2684,22 @@
         <v>9037610</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E12" t="n">
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>2.428320702276426</v>
+        <v>2.42901347388417</v>
       </c>
       <c r="G12" t="n">
-        <v>2.923653779064621</v>
+        <v>3.109052148873424</v>
       </c>
       <c r="H12" t="n">
-        <v>4.267467526957439</v>
+        <v>4.373651612063481</v>
       </c>
     </row>
     <row r="13">
@@ -2712,22 +2712,22 @@
         <v>9043425</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>5.199950017522127</v>
+        <v>5.182085354725964</v>
       </c>
       <c r="G13" t="n">
-        <v>5.269300047609929</v>
+        <v>5.251798942180962</v>
       </c>
       <c r="H13" t="n">
-        <v>5.373738130981663</v>
+        <v>5.333237217994927</v>
       </c>
     </row>
     <row r="14">
@@ -2740,22 +2740,22 @@
         <v>9042153</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>9.576294632428789</v>
+        <v>9.490076015867068</v>
       </c>
       <c r="G14" t="n">
-        <v>9.706267571723476</v>
+        <v>9.794306710035503</v>
       </c>
       <c r="H14" t="n">
-        <v>9.945967014080209</v>
+        <v>10.92479894014703</v>
       </c>
     </row>
     <row r="15">
@@ -2768,22 +2768,22 @@
         <v>9040439</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E15" t="n">
         <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>5.158198236590742</v>
+        <v>5.116181955096716</v>
       </c>
       <c r="G15" t="n">
-        <v>5.294787231763591</v>
+        <v>5.263307288412771</v>
       </c>
       <c r="H15" t="n">
-        <v>5.419427689468517</v>
+        <v>5.361600587371512</v>
       </c>
     </row>
     <row r="16">
@@ -2796,22 +2796,22 @@
         <v>9032282</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>6.452433431300514</v>
+        <v>6.381102378142341</v>
       </c>
       <c r="G16" t="n">
-        <v>6.616726811092832</v>
+        <v>6.583618469081034</v>
       </c>
       <c r="H16" t="n">
-        <v>6.715790040003266</v>
+        <v>6.711995028099045</v>
       </c>
     </row>
     <row r="17">
@@ -2824,22 +2824,22 @@
         <v>9037738</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3.366519468172819</v>
+        <v>3.065100466388778</v>
       </c>
       <c r="G17" t="n">
-        <v>4.321211807094598</v>
+        <v>4.427640372361481</v>
       </c>
       <c r="H17" t="n">
-        <v>5.567603618180248</v>
+        <v>5.851688262856731</v>
       </c>
     </row>
     <row r="18">
@@ -2852,22 +2852,22 @@
         <v>9039635</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>3.173897869213814</v>
+        <v>3.181960352422907</v>
       </c>
       <c r="G18" t="n">
-        <v>3.302156820174223</v>
+        <v>3.304003187825538</v>
       </c>
       <c r="H18" t="n">
-        <v>3.578691334496694</v>
+        <v>3.496518272400334</v>
       </c>
     </row>
     <row r="19">
@@ -2880,22 +2880,22 @@
         <v>9038269</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2.179274812033199</v>
+        <v>2.150881791483113</v>
       </c>
       <c r="G19" t="n">
-        <v>2.251937330002357</v>
+        <v>2.225661007061721</v>
       </c>
       <c r="H19" t="n">
-        <v>2.383752073032747</v>
+        <v>2.331233021292217</v>
       </c>
     </row>
     <row r="20">
@@ -2908,22 +2908,22 @@
         <v>9036459</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4.869900068910122</v>
+        <v>4.871414572875782</v>
       </c>
       <c r="G20" t="n">
-        <v>5.246184875452939</v>
+        <v>5.19583926257148</v>
       </c>
       <c r="H20" t="n">
-        <v>5.800742683105024</v>
+        <v>5.726413692731685</v>
       </c>
     </row>
     <row r="21">
@@ -2936,22 +2936,22 @@
         <v>9046779</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>46276</v>
+        <v>46277</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>128.0365749414335</v>
+        <v>128.035504300431</v>
       </c>
       <c r="G21" t="n">
-        <v>128.3440796433171</v>
+        <v>128.4669467051054</v>
       </c>
       <c r="H21" t="n">
-        <v>129.5478048836164</v>
+        <v>129.6620647167807</v>
       </c>
     </row>
   </sheetData>
